--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,135 +501,135 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
+          <t>Aarti Kapoor to head people &amp; organisation ops for region international, at Sandoz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Investing.com Australia</t>
+          <t>HR Katha</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQREtHTHhjZUVrUUZnTF9VZFFzX3NpWldwb01fNzRsZGdFNk96NUdRR2ppUkkwRHV1MkFzVktnRlhpeTRNV1VYV3VUc01MWE00eFFtZFVmc2NXZ2ZZSGtfb01GZXA4QlA3WGJaTDk3X0lFcjdvY0d4R1F1dVVfMUgta0JiclVDNGJCTVVlbkxteHU2VUdMeU45dlg4S2ItRzNSQ2NDQTg5QW1SeWRkRGdfN3h2a3I4alhlclE3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZGFjU3RIbmI4SmZaM2tIU1pfelRubDJpZkhJUkNGTEVLdGZmbDk5ckIxc3dYUmFpRndJYm8tQzhtSWU3WkN0RDJyYUxQcjJSRlJtU2V0Z0dRM0VkdjU1LVZ4d1V3T3FYXzBvLUY4Q3lFNnFzT0prQ0lzaFJnVVZBbTJYWnhFZUI2cUF3R2FfWEh3RExLZEJUbnJoWkREcEkxOGNlOFVvb1ltTHRkeGt0MWJTUGl2UGNHVFBLcw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08-05-2026 11:50 UTC</t>
+          <t>08-05-2026 15:44 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ribo And Boehringer Ingelheim Reach Third Milestone In siRNA Collaboration Targeting MASH Therapies</t>
+          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQT19nV2Q4OF9qclN3b3hHZ3JYM0Y5UmRYYnFYMFc5Z1k2djdOXzB5aTJnVFhaV3lVaWlyTGFOdUN3MXVKcVJycmFlYVFneldZdHpEam1mWnRhQjdfS3ZTWk15YzQydE03YXRXZERGcG9YeDdIQl9wVGFCMXpaNkh6Y0oyNDBWMGp4S29KWEw5VmxPYi1ZZG4zMVRSajhENXRfZ2Zvb3Y0RlFaR2Rwc0t6UDN3RmszYWJmZk9MQ1hFcVJxdG1TMFhOQXNBd2Rhc0RGLXo2S3FXaTlIY1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOUW1zaDgzbHQ3TUt6MVNRR0ZCcnhBSnE4aFY5eEQxalh3dGdPZ2JzdU9NV3I0eUVQX253Zld6Z25OTTdxTzh5ZWRScjZzSDQxV0dMZW9zSzhLZXlOaUUtYkZJUnNiSl9lT3B5MkNjRmtHVTZxOTJXNlJHdUJoVWpGaU9LNEctVnRTdmN5OGI3clhlekktVVZZNEhpVkdKLVNuYmxQR2pEVVU4TWdOMDREUkk2QlVJRVY2VzZHOQ?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>07-05-2026 20:51 UTC</t>
+          <t>08-05-2026 12:07 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
+          <t>Sandoz Secures SBTi Validation For 2030 Climate Targets Across Operations And Suppliers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACCESS Newswire</t>
+          <t>ESG News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNndMWTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaHgwM2tGQmdvYUlic21xWXdRM3JlLXd1VHZEd1JBM1hhODc0a1JwTHRtRGRteHAxZHpYVVFNajRCNjFWRHNDbVhtNTFBVHU2aWR6MU9IZzRuN3h5WTAyUGtZYlNjdmVoVGtJZ2Y2OFFsMUxTTDdkYWpLUENrZm1WTDI4UG1wSG5MLXd5Q0lsN1JxS0ZyNmxRM3M5eWdEcERRbUtqbmFkLURLMXlu?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08-05-2026 03:23 UTC</t>
+          <t>08-05-2026 13:35 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMGEN TO PRESENT AT THE BANK OF AMERICA MERRILL LYNCH GLOBAL HEALTHCARE CONFERENCE</t>
+          <t>Sandoz to Launch Generic Version of Semaglutide in Canada, Brazil This Year, CEO Says</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPcldIVU5iSjdvUWstWVZuTXUwTjdZWmdKS1FzM0duS0kzc2xpcVNYVXpyOTZBUk14alRRemhONDRFMEZWN1g4WGNyZU5CanhMdV9rTll3TGFMbUpvQmRsaC1zUHNFNjZVdVU4emRhS2VYckVSYXZubVl1NFZ3SUVrRVlFc2FzdWxydDEyYlJ5V1dRUFAxT01ScVNKOGdzNVZkNC1rTXplcVJuWFMyZ2wzS2ZhelA0S2FJNndZUlp1dUt1Nkc0QzJtQ0RkbWFTclBtVmR3WVQzVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNX1hhUGMzX2pJcVdRYjNMRFFHTjM1OExKVjd4ZWs3b1lCME5YdnViNWYyWlFFXzFTb19xeEdWM2ltRUx4ZF81cks4aUFtVDd2YnpyalEwR2tqZFVRU1BnYUpDNHF1MzBDNkZrd2tiTDZsSTV3SDJzc2tlSGNhRURDY0RjNl9fZ2VxSlVoR2xXcFhYcmJXOVRBakRscmJQdy1yemc0aWtKY3c5QQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>07-05-2026 20:01 UTC</t>
+          <t>08-05-2026 14:40 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Rating upgrade and Q1 beat amid tax and regulatory overhangs</t>
+          <t>Formycon AG Stock (DE000A1EWVY8): Analyst Upgrade and Price Target Revision</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZEJQQnJSd0pxb1cxY19BLWhUUHk4d3pVTUpWMTZILXU2R0pxSEF1MHliQ25CTzVPTHYzcXRIVnFUcFFmMlk0V21TSHFzRl9qVDlfSWtDTXhPQ1RINFNCX3VMLTNwWFUwbWdCUWZZQzRyRmNkM0d3RnF2WmFNT19NNkxMdEFLYWdwWHdiRmdRNkZPOU9KX3U1MU54bVpLWUNMUmFOOWJYeVJfd1JwbEJlTWZfbktEVFV2QjFXRFVxQkhfYlJWZEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQekFSMzhrQ1pRVUlmRldJM1RJTkxHeEYwa3ViZjc5U3FndHV0cXMwekkybm5NNHRiaDNLLXhxSDJiOW1JLUdBSGpOZGZ0aHB2M3k2b3NoRkJ5cHZpMVF3cm1RU2NlR1pfdVptS0FLcWVpY0ZGSXNlYVdiNVE0czJnWTFkbFUxcDg3WE8wZGNQZXJOUlBEdS01ZjA1UjlJUGFDSEhWUHRTN0lXRGJRN2JITU9uZ0h2OVU0cnM5UGp0aw?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>08-05-2026 13:34 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -656,155 +656,155 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WJournalpr</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUUp2Uno3MHpvcFQ1YWdPVmxFTER5UEVIZ3l4Z0tINHFrdV9xV1NVVHBxWDQwR2hydy0zNjg2QzNHYktrcE9wNXpZb2w1UjJqMFlIaGd6RFJPdXlPMUdNbU5IU0gzbWxicDRrdm9hVW05VlE4UDRXd2FSa3A2SHpFRXYzczAwUTZ0TnluOWhhRXB2T1g3N09sX2gtMEx1c3dXYm52dzhxOXdRdEp2dG5WaWNvX211OG9aVmU0M2U3dWE?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-05-2026 10:00 UTC</t>
+          <t>09-05-2026 07:53 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amneal Pharmaceuticals (NASDAQ: AMRX) posts Q1 profit surge and inks $375M Kashiv acquisition</t>
+          <t>BioLargo Subsidiary Clyra Medical Signs Exclusive Distribution Agreement with Al- Hikma FZCO for ViaCLYR(TM) Across the Middle East, North Africa, and Adjacent Markets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSzZubmgzTWJxdVRtSmZNRHR3ZGIzWFNZdFpLVnJING1rMUhQa2NxbnBKRnU3bDhNa1lzN2U5dGhOM2lNOUw5YUFyZ3BCZG4waldTU0lFdEM4ZTFpTm5PZndud0Q5WDNvUnpNbzRZd29WTFZZcjNiMHJ0LWN2VFNQMF84VGVlTF9kdTN2UUthTjcycWt0Wi1KWFdQRXkwbDh5a1BlSGxhMTFhZ3k2UHFsM2JjV3VncnJPWi1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNmdMWTE?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>07-05-2026 20:22 UTC</t>
+          <t>09-05-2026 05:56 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Assessing Organon (OGN) Valuation After A Sharp Recent Share Price Move</t>
+          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQeW9pQ2FpSlp4QkxhLU8yZ3VwODVab0N5S2lGc1JhcWhDYjB4eUhnY01XQ1B1N0xNV195MnY1b1psTHdiWl8wUDQzdFAyU0hTMUFJZFdlZHdJZUJtUjVUaUFwMEtMaWtDajgzTDFuSGlKbERBZGZ1eC13c3Q4VEZFYTRLR3lpdFp4cDJqQXhGUTN6YlJVa1NwNHBFR2d6bnEyTDZreVpJLVZtZFlpUHZUU041Z2FaaUxBZUFrTXBJUElIMkxUanhJVENXSlphYmtXVV9MQtIB2gFBVV95cUxNVnRncnBoU3NsNmtLQUx5Zmg2YmdiVkFQcmxtdkptOWVVRDRpV0NJVnFVVTRyTGxIX0oxLW1jX2U4WHZFUV9kYTVaeXNMSnR2NVdPU0xIeFRSWXdLcXhpLTZseV9FUVFDYmNLc0N6T18ycENSemUycl9yWC1rQ0wwcFJQeUtxN0RnUXlmUWVHVkpGd2owWU1KX1lJc2pOZXla01lUFRPdE4xcGJSc3BZbE9GWnhLazdNQWo5RzFRZ0JBa0pwS1d4XzdkazBveXh6WmQ4Zm1vQzJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2empEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>07-05-2026 18:03 UTC</t>
+          <t>08-05-2026 16:38 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Healthy Returns: First Ozempic generics in Canada will be a test case for Novo Nordisk</t>
+          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>WJournalpr</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUTVjQVNuLTZLbENlVDc1T0ZjU2duNFFJSzNiaTJVSlk4MC1SY21kejRyMGNGaE1HSmJSRThHMXcwMDVvWWpDc2YyR1UyMXlBTTRTcVRfZEZqQ2JPRHZ4ZFhCNEpQLXNSU0pVcWl6YlZwaXhjeWF0enhkSkdFQjhFYlczbUFVeC05NXA2Q2VCdDZKdkFyTmJjVGs0RkV2dWxw0gGmAUFVX3lxTFBmSmhNTmpYSXlKSmZBaEVNQklsclZnclk2cDBFeXV0dzBFRnBZZmF0c3hRdFRhRWFGNThUVnVKbjFvUl9taE5NdFdHV2RBRkpTUEs0M2JxcElnX3lJMkVIckQwcFh5a19Odl90WUJvVHQwSHI2LWlpeHJZZEZickM1eXhiZlk5ZUtRTzVrWnNRdXkxRjYybC1EZWRnZjV0VDhjTlF2MHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>07-05-2026 18:33 UTC</t>
+          <t>08-05-2026 10:00 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Viatris Q1 2026 slides: earnings beat drives shares higher</t>
+          <t>Amgen Inc. Stock (US0311621009): Shares Dip After Strong Q1 2026 Earnings Beat and Analyst Downgrade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOYTJER0pNZDUwRVhVY0dPdlNUM3M1cmF2cnFDMzYwSVZxX3Vob0FCazJsY0VJbzZXdlg0bnpJZVplTllGYWxpWXpodE1pdkRSc2RIZEJXM1ZTQTlRUkV1QmNVbjFTR2Vvc2tYYUprdW1MVldZdjBxNWxmVmxfQzVLZ0tsYjNNNU5GY0lWZC1FZlhOcUctV0NjSFlaeG9ZSXRDNks5S3dVaE1WSVdSeTVIbjl2T2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONmlOQnhETkloS1Y4eHJJaTk2bDNacldPN1FhODB6NlBHa2FnZnlmUDl5MkhoSkNCQW5NLU9SdlZyeUt1UlBPdHA3b2VQNDFpTy1RQk9UTE12TlZWRkhGN1Y3N3RDZ0ZKUmtYaU5fLWZwYUY5aXBqUEFDT0lWTHprV0tPaFlpb1YzOXZUWFdHdlVqQnV0ZHRPVFRwWXZseHBuTUJ4LUpsejV5Y2tYX3RpajJUT204bVg4eVZ3NWpvaTlEVTc5NFRr?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>07-05-2026 17:32 UTC</t>
+          <t>08-05-2026 11:17 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -816,27 +816,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Assessing Pfizer’s (PFE) Valuation As Shares Hover Near Recent Levels</t>
+          <t>Amgen (NASDAQ:AMGN) Stock Rating Upgraded by Freedom Capital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWG84cDJKWW54R1JuOEt2b082V2VhVmtvYW4wUEJIVHcwVUVoVzJiOVRJdE4xeU5RU3NHR1huNVFLb0JZbTk1Tlc1eUpkU2tZaHlnQ0VTcmEtbkZHRmtjVWtxdmlQY1VWTXdVYzlXWW9ZOEp4a0hDSk5waE1TSXdENUJnM3VVNU9UM1FwdXg0WTJQY2xjV0VkMVBOYWJYd3pqdV9CVms4SWxIaGlKMmNYWWpZczFtZVlUY05CZTBtYXdOQVBLRTVFYTMzb1BmMEdLeFHSAdcBQVVfeXFMTS1qbFhORzE2Q3p3UGtXYkI1Y3A2RDVzTGo1QWlsQmFPdHR4Q0xIMGxMekdpUXFtMjFSUWJYdnExLTNBNHFJYnZoU0p3Z2JfNzloVkhHRnVXeEFDWEcyWTY4d0s4NFI3bTlQS2dlajZTRUdxV0VvR1gwZVdZSEZBTEJkWkEtMlN1TDJoWEpzUm12WTJzSFlOcDktbl9UbFdENXhVWjlZd2k2MzNjV2FIR2FsQ2ZGQVdKUDFnZHBHRk9ILXpvWlpfcDFnamNYSGljendoZE5YZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONk16NnJSWXhHbE8wcV9mM09URE1peDFPR1lWdVhpNktQcEhITC1waW9QZmYzWkJlMDNYUl9BN3hVZHY2ak1MX1BZR1U3MUgtVDlLUFJHdHl1Ty1ueW4wdUpOeGl6d09jLXNPaXpqNTFJTEZDakRlQkt6WVYwSkRGbmtRcFJnSjdIcWpIbGx6Y0g2MVlxNVZqUS1fQ3ZUWmEtcThicG0zTjY2QjBjRlhSTg?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08-05-2026 07:52 UTC</t>
+          <t>08-05-2026 09:47 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -848,155 +848,155 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Depo-Provera MDL Sees Massive Influx of Lawsuits, Pfizer Doubles Down on Argument to Dismiss Cases</t>
+          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Legal Examiner</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNakhSd3RMUVgyTlVnZzZWRlN1ZUUxNmR1NS02SlhybG1PWmZ0akZvOFlrOF8yRGZia2ZBUExxTmZmYzhCY1VPbGpxckdhb2JjeHNKWk5fazFveEhVd0NrVEkzallxcmFLTVBiakNnbmI3S0ZyRkctam1sbWQ1NjllZFpZT3p4Q0pESEM5d1NySGliQV9IUVRnUlQ2RnhCWlJoWmRDdkxneXFDTzAweEdIR1VrbnRGZUFSNF9RQVl6OE1iV2VlSUVGMUVJVUJJbXkwY1V3R3RR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyTjkyS0dIUVRYSW1YbTg1ZGFRR3Ytalg?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08-05-2026 15:43 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Judge Knocks Out Pfizer Partner's Vax Case Against GSK</t>
+          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5GVTBoZllzbnlPLWEwQ3RyTDg1ZXVKNmhIX21jZkJSc0dVMGhRMm9MVzhfQ2lnV1ZKRHY4azU1VFZEYVJkWFBOa09RaTNTc09wWnpTWkp30gFWQVVfeXFMTkZVMGhmWXNueU8tYTBDdHJMODVldUo2aEhfbWNmQlJzR1UwaFEyb0xXOF9DaWdXVkpEdjhrNTVUVkRhUmRYUE5rT1FpM1NzT3BaelNaSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>07-05-2026 22:57 UTC</t>
+          <t>08-05-2026 20:28 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Update on FDA Priority Review of LEQEMBI® IQLIK™ (lecanemab-irmb) Subcutaneous Injection as a Starting Dose for Early Alzheimer’s Disease</t>
+          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQd1JkMUwtM0lxWF9nQTF3UEpYTTlwWFZfOXhkcE5WVjVTUmZfUWxoN2Jqa0RhdkhTM1hwX1M5dC01bEtTSV9hM2h2NEJYekxaczlJVkNmSTYzS2tkZW5HdE1nMkFHbXlwVUpjazhsMEJZX3E2LWZiVVBSXzhZTnJReVJDV253NTVvMVNFb3c0VnZ6T3VCbmpDaVRZVlJvY1BzVmRWMTBVSVo5VWdJUVF0aFVXRnJ2bXZFQnNtOTRSbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08-05-2026 06:35 UTC</t>
+          <t>08-05-2026 20:23 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
+          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE8ySngzYV8zUkJLYkJQdTdvT1NHMFNUcDI4cFRFRHk4Q0Fwbkc5OWs5QVg3YkJ6OHFER0FLR2t4Ui12dTdQNmNrMXVkQVVWOW9vWnRpSXNFSi1HZTlHUVhzbGJiamJOM3RwS050QlV30gFyQVVfeXFMTjNIXy1zNmtuZnR5MlZQMHRzZDJtOXNldzZzU3puRTEtUnljbnllb0ZWV1BNQzlqS09wR1ZaSHlQRG9W01oUmFUa05tRW9pMTNRX2tQN09wV0FJSXBNb25mNEpmeV9EcFJnNC02TTFfNWt3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08-05-2026 08:08 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
+          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08-05-2026 15:31 UTC</t>
+          <t>08-05-2026 20:29 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,59 +1008,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The FDA’s Approval of High-Dose Nusinersen: What Doctors Should Know</t>
+          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CGTLive®</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE8xQkJzazlldUhIX0xpcGZwUVZvVnh6U2pQZEJzX1Z2cnZRMVlsVXltVExZTGc2Unc0M0ZJcllRVWFfbWhVR2NncmhUVFJzOFg1ZmtKb3hDQlBYd05NYUExRkhkdFljajNlQnN5eUFzY1AwMlV2ejhiYWpOLXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07-05-2026 20:50 UTC</t>
+          <t>08-05-2026 20:24 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
+          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>hcamag.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08-05-2026 12:52 UTC</t>
+          <t>08-05-2026 18:48 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1072,59 +1072,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNc3J5STlSazVqak9JX00zcXRDc0hPUHlYQ1lSb2xVc2JtZUdoNWhLT0d6N2NKU1FVY0hBa3p3cDhJUE9LaXB5QUszc0Q1QW5uUnRlSW1TUVNYRVc2aXNuR3AtX09ObVVHdC1DMDBLdDRSTnVEUmI2YmhuY3VLUzF0Mmc0Y0pFSjFqZGFESWRHQlgtQmVlMWt1cW9pMEVPT05rRXZnRVQ4Y1NRYzVTeXVVT0d3OGFpNnhwaGplaE8taVctYWZuSmZBTkc5blpFMlQ3Y0pSX3k0VEVjUDZq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>08-05-2026 17:46 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biocon Q4FY26 Total Income at Rs 4,569 Cr EBITDA at Rs 1,073 Cr; Net Profit</t>
+          <t>Novavax Stock Jumps As Pfizer Deal Cash Puts Vaccine Turnaround Back In Focus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>TechStock²</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBKcXVWQTlVUjN5aklyZnp2eVVuNTNrSWxsZWlBV2hPREpUUGhJR05tamtwVlEzTWQ2bmMxMEtKUDdqQkRIVnpXUDdpOHJaNUxGbWR5RENfcFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdjdLQXA5dEc4TnJ5b3ZiUFBZUWJGbzBEUE5acG9DdFZJb1VzUkVZUWJLRXZtYXotcDNHX2lqbjV5TmVaUjQxWFcyNHVOUjlKTjRyRmtMWm9kOUhlMkpMOFZkNnlQOTN1WTZMaWt2ajZYcWtzdHZLRVFwTXBacGVpZnJzRGxMQzJPaEFKNTBnd1JUdTJPa0tnU0hoTDFnSGc?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07-05-2026 18:22 UTC</t>
+          <t>08-05-2026 17:55 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1136,59 +1136,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>As Kiran Mazumdar-Shaw plans succession, Biocon bets on biosimilars and obesity drugs for next growth wave</t>
+          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxQVjNPcE1hTy1nWTZhQWJXc3RXaVNjSDZuTDVzOEwtLUFkU0lZNnFWYXNRUWhHTGFVenNoSzlsTVRuSVd4RU94Ykt6T0xzY3JTdUVIcTFkc29uRVlyUlc3RkhXWEwyenZkaU8tVXNYQV9nRXFlRWpHb1NQRjFUVEFsaTBoTko3YzItWU9keTFqRWZ2NzZSMTE4eklGWG9PLTZORUw0R0dlaDV0V0pUR1NfZ25kbE1KbjVfREdmNm1zOE1LTWRIRXNaUE5tYVIxaXpIWjB5TnFqSTRrYWExYXZvYnB0Wi0wTXFqZ25YNjhEeWxRTDJyMDJVVWsxNlI0RlFMUjloY3dn0gGLAkFVX3lxTE4zVUgzX29EOGxfTGZzOURyU3ZFb19Fa1htVzk3X2JaT1BsYVVXaUp5NjRpbmtnVkN3NVM0bDRiVnl2RWRySHRDV2dBMDl5ZHcyNVptTVZpX2JUQ01rYUl3dnB2RjlHYlZqTlctaEo5RDNta25RZG9zaG9ncFpOTkVTNGtqOXl3WGJ1VjNjQ2pPLXN0ZFdJUVFrYUc4Mk9iWENzejBhWnY3UXZOYmRBcG1PWVVDWDNabDZiMU9hVUdxcWpaVUdDcFlCUWdKZ08xYkZjU0U1NTQ1TTNDcDU5WGZUTjlPQV9ZRHkyc1JNMVQ4WkVrNkh0NjlLb1RaX3E4dFBiWXN1V1hHWkVpRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08-05-2026 11:04 UTC</t>
+          <t>08-05-2026 22:36 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The handover will happen over 5 years. Kiran Mazumdar Shaw lays out the roadmap — Claire Mazumdar will transition over the next 5 years, stepping into board-level roles across the Biocon Group before taking the reins. Ekta Batra | Kiran Mazumdar Shaw |</t>
+          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQSkQ2ODJvd1BFd3BDd21vbHVDZzQ3YWUwSm41XzVESjZ3V0pVV1VOMkN0a2Q0RmZ5bFEzcU9TNEttZFBaSWFKRHF5UlBCOHJOX3ZmYnNNNkkwR0FldXNLbkctdkVaWTdscktjbHRqVkFMUnFZNEwtdHRLNThKMHExUEthcnZWTy0tQ2NQOTBCS3F6YnFGX0tlWDNRTy11LTlXMjV2N0Npa0VIVnpPMHVWQ1JOeWxlRHhi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08-05-2026 09:41 UTC</t>
+          <t>08-05-2026 17:09 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1200,123 +1200,123 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1504</t>
+          <t>Pfizer Viagra stock: What health-conscious consumers should know before considering alternatives</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxORGNMOGZNdkNzYVZMcFhWX2NTZmM5TXFrcWZpd2NwbXRhZEFSMHlGYVZiRFpoTWxKWHN2OUZTTzEtZE11TEF1aUxEU1VqcnVRd184NE43eGw1MlNPNERXUjFMRU5DMkNKRWRoZVFwdmczek1JTXVvUnN0NzBYNldHUDdMdzFhVW5heXQ5c2JmZWpVY3BURzQ2OGFPUE0wSWdyY1NMTDV6UEY4YWpwdFI0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPZGdqUGIwcVY3NlpISG1ULWNyQlZOVW51bVgycHc2RUlYWXlIbE5jazdUQ2t3NFlvYVRkWjFXRVMzMWdVVm9adDVFMlRQRmhMSFdwUDhWTXRreUlqTFpfRXd1ZUxwNG5DeE1qdmxXaDZMUWlWOXVWbHlqT3NqUURucXFkNjVzLUVlRjMzeHpOa1JJRzliZUMteksxcG45X1dfQlBVODR1ZWQ2NnZ1NERka3J5cUdUY0Ezb3VjR29Ucm95N05td3lMRXVNMHhrRVRZRTZzS0hqajR1MzhTOXVRVDNsY0NqV01QWlpyZlBHODRwMHB3clVhaERUV1NpeUk0VV9tZEt6dU56ZmJL?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08-05-2026 05:28 UTC</t>
+          <t>08-05-2026 14:54 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zydus Ahmedabad Biologics Plant Under USFDA Lens, Inspection Closes with 7 Observations</t>
+          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUDBxSVFpdklXTm5xQzEyUkFncXlEeDRzWVQyOXVjTzNDZWpTQTdiXzhOM053dzlwQVYtdjNVMzM5V2dVUDZESVZZQTFvb2kyZ0E5aVJ2VFQxOWYtcTZEZjk5RjdFOXFUZ2gtVG1GZkNmSUxqSTZjU3FzVjZzdHhTb3JVVks0SDhYTG1LaWlud29ibm5BYW51bVZkZ1J5dXdRRDI1VUNUV3JlUU5EdlZIdzZUeEszQ1YzeGZaSjZ2NUp1NHJDY1I2SGJMRjg5b05FRkRObFdNd1E5UdIB3wFBVV95cUxQdWxWa0UtdXNtZHJ1X1B3aEtzZUlOYlM4NTBmVFg1Y3MydExZLW1DcDhYei1CWTNwZVYwbkJyLThudUxaZmEzenhLZ09SQkVBdE1kZW5LdXBITmk5QnF0YmE1Q2ZuZVI0T01HWVkzMElfaFBfZEpNQ3lFWnNCUXVEZ0hSNW9XNWQ1dE5rYjJQWHNOemNuaE1zeU1oNXViR0pDQWhUSlJHOU5ncjJnM2dsWWZaR0pnMmV2cXJFeG9ZaU5ET1owSDhZTTQtcFA4cnJPMUExdkRjY2M0ZXBNb2tr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckHmZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07-05-2026 17:37 UTC</t>
+          <t>08-05-2026 16:47 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
+          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrd9IBckFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrdw?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08-05-2026 14:17 UTC</t>
+          <t>08-05-2026 08:28 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Celltrions U.S. Strategy Boosts Sales of Jimpenetra, Achieving Record Prescriptions</t>
+          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>aju press</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5YeDRtQlNlbDVNQjQyWXdCVEJnaHJBdGYtMDlnMFFoWFFsVlIyeVVpczZrVWZPVzBYcjhwMzV1cEsySVgySGM3WU9qN2xvTFg2YjltU0pIWURpMU3SAVdBVV95cUxQWURTd3Rmc2hYVmdQOGFfUlhQT1BxdVY5RUFFZkZXQ1FyUldCWW92Nld1NjdhZDZlcW1UTk9NWmN3UUxJSWlBd0V6Q01HS0YwY052c21uNjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VTX0dZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfTXVVMG53RElIeG1TeGJTRVpfdXlhZHZPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08-05-2026 04:33 UTC</t>
+          <t>08-05-2026 18:54 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1328,27 +1328,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tranche Update on Celltrion, Inc.'s Equity Buyback Plan announced on April 22, 2026.</t>
+          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNSWxOU1MtWDFnLWx5RFNHVmQxZFdYdExoR3BTdGVFQUp3aXVURFlWQ29BRmhZRUVUdE9QOWJTUklpdzI2dmtTSU5OWVh0ZDhvdDdydXVrREJSZnRpd19sekJXdmFtbEltYm05MHlnS2p5NjRENjlXSXo2TU5DOURPUEpGc1hkeDR5NXR2SE42OXdCZ0RBVzlXWFhlNlluaWsyUnc0X05YOG9NSFNNMEZmMVpRVjhRLUJOTDRaNjJvNzJhQkx1Q0tkUFowOG5wZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOd0luWGNUam9MUlA2N3pBU3hZeXJoX0R5NVNrdThOc0s3TWlSV3JDZEp2dnVfS1hNeGJZdzlNQWdtSTMySnlOMGFJY3FXVjhydzF5OFRLNW0yZGNvdlhmcS1FTmlIb2g1eGlicS1uNm1YbW05UVpyYjFwaklmOVhFTi03L1VVRDhkY05vMDlvU2h4SjctcEFZVG5nV1YzV09nOUJGZzlGSXBHVFJsakJEOXZJSW81UTF3aUlhRjdn?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08-05-2026 05:50 UTC</t>
+          <t>08-05-2026 23:47 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,27 +1360,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo takes $610M profit hit linked to ADC manufacturing overbuild</t>
+          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVlJIWnFlWXo2TjdzQmxPZWYyeXk2c2NfRHVwdWliajZUSEZiSUhJSlAtT0o5MENTYzZMdGEyMEJPejVoX2dsLWNYQ0d6c1UxbHZGYW1qWUFNSDVNSHhhRW5vQ2liV2xMbUZWZ2hBT3ZMd2dBNkJVU0ZmUG9ENmRKejdIdjktY2RXNWloeUNvUWN4Y3hJd3kyZlpKMHZTQy1zclZETmQ0aHhRd09yVF9oM0ZqbzI4ZzRicFZQTzRna0xqWTNvUjl6TVRGbzV3a0M5?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08-05-2026 14:47 UTC</t>
+          <t>08-05-2026 21:40 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,91 +1392,91 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
+          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleanroom Technology</t>
+          <t>The Indian Practitioner</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08-05-2026 11:30 UTC</t>
+          <t>08-05-2026 12:52 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
+          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6TEl2MlV3aE9IWGQtdHNkREo2UDFXNkh3QXZuQVEzall1WEJaS0FGelNpUkNkNjZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPVnRxYWF5YzVBNXF5cU56TjlzSmgyc0ZsMmtGenA1OVJWMEVBYzJSWFRpZUZ0dTRpb0Z2WTh3aUZXVmdtZGZSMjF0YWRNOHNhUXZ0dGlONzlTZ3pKRmlibXRKdWp4Y2I5eE9TS2VRWmtNdUdzTktiUUN3Q19HMkpraldTcEhVdjF0TWdRZEZfY1RrLVhkeDhfeDc3LU1ZWVJCRUxab1lLZWFBOGtBaEYtWU5xOA?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08-05-2026 10:37 UTC</t>
+          <t>08-05-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
+          <t>Biocon reports 63% YoY fall in Q4 profit, final dividend of Rs. 0.50 recommended</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGwxNEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWWVrTmpvZE83YjI5NFp1djBMczliVmROVVdxeVlnaWFkZmk0bWVLUGdCU2VWMlQ2WEotUWlQYmlrWmY2aGVISGhjaDh4aTlzTnJuQV9WREVGelVob29GbUV2ZnBSNGM2WmU0Q2MxUHVqWjB6WWJoT1lGUS1wTV8xaDlRNVl2R2hldlJFa1RnU0ZENlhwb3pTaDJQQUg4RTBnWFhyUWhMdmxGa2JKb2xTSkdnYjBWZ0U1ZU5jRkZqWHF4aWpyWUpVUTREcE9lbHBWZVJ3enFmbk9ob0hnSy1pYlNpMkZQTTdibkhR0gHwAUFVX3lxTE1kNHVlZDFzaHZpbUd4U1c3VWd1WEVlc1Y3X2NNT2lENGVOSEJBdEt5NElTMGRLcnBjUlVGLXl4RGdDeGhdTGdDZWdBMl8yOWsyc18ybW4ydHY1Uzc2MWRFX0FmR0h5WFFLYkZNb1Nuc3JGLU1pZ0tRN0k5Wll0SkFYajlfNzV6N0M3RkhhY3g1WlhDRm1CS0lNNmVpeGg2NzBoNjJB?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08-05-2026 08:59 UTC</t>
+          <t>08-05-2026 10:58 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1488,128 +1488,576 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group eyes growth amid restructuring</t>
+          <t>Biocon eyes in-licensing deals to expand biosimilars portfolio in FY27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTFJUb2hNMG1QVDNjYXZFMWY3VHNfOHdKa1BaS1pqNGhzOXhmZlRRZjlfSU5hZWN3VGZwRFZwcnROSUYwbmZ3a3FKaEs2ekZWd283MWs4QkFETWc3SWhJX3R6Z0dOS3gxa3BWZFJuR2ZyS2M2bEF0YWxjMEQ5NXBhaUVpMUFuMjdXaHBBSnpEanJjeTFXWHNFcjVYdmxQLTlIdUZrcThPeWlQRVJjY0ViZHVGOUtDWXdoZDJMRXpRS09sUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQcUhDX3BBemNPc1RTTGhHUU1PUkZUR05iS1RNbFJwSFg5dktHcnphX052QjdKc19uOF9GVnZhRlhoT2czRWNERFI3YXh2RTZLU3FKTG0taWNCREhiM1I3cmFYVm5uWjE3WGM3dU10dEZKWmhsbFVGd3RuTnFYdVBOTzFxUVBldnlRbmU3Nkg2SDBucDNvbGpieHRKZlE2RnE1Q0dzWWUtMzVDbGhMbUpDb2Zzb2pEakg1OFpTNV9zMnp0Qmp4bFg2NzZjMDVXYkpucXhqMlJXZndQR1XSAdsBQVVfeXFMUHFIQ19wQXpjT3NUU0xoR1FNT1JGVEdOYktUTWxScEhYOXZLR3J6YV9OdkI3SnNfbjhfRlZ2YUZYaE9nM0VjRERSN2F4dkU2S1NxSkxtLWljQkRIYjNSN3JhWFZubloxN1hjN3VNdHRGSlpobGxVRnd0bk5xWHVQTk8xcVFQZXZ5UW5lNzZINkgwbnAzb2xqYnh0SmZRNkZxNUNHc1llLTM1Q2xoTG1KQ29mc29qRGpINThaUzVfczJ6dEJqeGxYNjc2YzA1V2JKbnF4ajJSV2Z3UEdV?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08-05-2026 11:57 UTC</t>
+          <t>08-05-2026 12:54 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
+          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQQVJIODRkT2tUdGZTWUZaRk9NQkcwZXJubDNTUWpsUVY0bG83blNwdGdJbHFVemkyblIwQW5EYV84S0JBTkwyWGp6Q3NpOURxWHBTVWxRTDc0Y0lDNVRoVXYtWlNuSmJvMkF4ckU3Z21mSTZIWVRYM2duamVKM1FtUnVYSnZ3d2l6MmVwMm5EYVFJR2syWDhHZDNZQWlOWjZSR2RyNXh0alA0RUJiWnRmRFZJWmdsdFVGQ01EODdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqWzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqWzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08-05-2026 10:27 UTC</t>
+          <t>08-05-2026 18:15 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teva can pursue monopoly claims over rival’s ‘exclusive pharmacy deal’</t>
+          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Life Sciences Intellectual Property Review</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQTNnUFVOTzhtN0RkNnBSQzFPWndBZkV4SGJIeFM1QWYweVdXYU9HUS1fX2NrSkVFdWFtM0RjNWxtNW84NG9aZVU4TC1VaUVfMzZJekRpTFdaQ3VETEpPTl82UTZPcG5ZMDE1SVRFREhFM1pEaHRwWUdQbmxhLUxMQXdCTHQ1VFAzcFVhS2ZLYTdUX0lhbVpIbGdaUXNJOXZQMEwxYUt1N2txSWt1aWtaZkhDaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>07-05-2026 21:04 UTC</t>
+          <t>08-05-2026 16:42 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cartography Biosciences Secures Strategic Investment From Samsung Ventures To Advance Precision Oncology Pipeline</t>
+          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>indiaherald.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNekYxT2tMV20zSURQNjk1RFlERnM3bHY5RF9mRXplcnA3LXgzODFqQ1dpdXhDeFFySmxEbEdPVFpGN096bHhNNDlOV0E2bXA5VEs0SHpaX3k5Y3dkS0RUU3dVRlNIUDdpUUU3OW9zRGVjbW5iM1psWVRmTG5NYXBuNC1ISTVRZm9fLXl1Mm9WNDZQSFYzUy1XT0RkTzJEWjVOQWdHVFZGT0lEcUJfeEszbXdFUjIzcldUZVZEOGIzTjZjWTN5R092Q1RWTVBtN3hFRG53MmhZNnBoV0Q3TWllZGUteUlQNl9FYi1uRWdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fcjNZaldTbnc2b1gxRk5xZ2tjRm96am5mcld5ZktIRXRSQXlHX2M3TFFnNTZlekhRMUHSAa4BQVVfeXFMTmNaVjgwdkJHQl9xMFdXbEtjN1UwQ09FdzRlakZZS2wzWDNCamlJU1F2ZmRac1p1ZjFSUWNfQnFXYV9qMHJXWFQxbFFjaGo2UWhDb185N3Q5QWlrVHRoeUxFcGY3bGk3TWN2ekZaa25oZUNQc2hMNlBzeXMtX3IzWWpXU253Nm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>07-05-2026 23:30 UTC</t>
+          <t>09-05-2026 06:04 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08-05-2026 14:17 UTC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>09-05-2026 07:21 UTC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fierce Pharma</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>08-05-2026 14:47 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cleanroom Technology</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>08-05-2026 11:30 UTC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6eExJdjJVd2hPSFhkLXRzRERKNlAxVzZId0F2bkFRM2pYdVhCWktBRnpTaVJDZDZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>08-05-2026 10:37 UTC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGw4NEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>08-05-2026 08:59 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>09-05-2026 07:53 UTC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Infusion Therapy Market Is Going to Boom | Baxter International, B. Braun Melsungen AG, Fresenius Kabi AG</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSUQxSmFjRG9xUWJPSXhGMzhYVnkxNk52dXNvalRVSG1FNmVFbkRMY2FQSnBjcGZfMDRWTk9sQVN5cGppY1hDcjFVeHdFWXpaU21wWnlGTU9KdGZHOW9xMncwZXEzbl9OWE5Qa01QY2VnRk5Bdm5fTVFSZ00tMVFZQmNTckhhdzlBWE9BNi1yTXktSDV2MzkyX3Y2bE9rZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>08-05-2026 11:31 UTC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvVXRyRGZ6UnhQSVZSazU5Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>09-05-2026 05:06 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alvotech Earnings Call Balances Risk and Growth</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>09-05-2026 02:07 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1NTHp4RmJRVXNtRC1nYWMwNlh5MzV1SjhWZzY2ck5VY0NTeko4MVVBWHNTcXhnZVk3NFoyX1M2NVhSbGtiTVZ5aWVmdTRZVG91Mm1qWmNfV1BjY2NJMzFwQVdFVXFwS1AzZ2FPSlkzUDB5VHphdTZCb01lc2x5RHc?oc=5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>08-05-2026 15:32 UTC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Investing.com Australia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPdmZOYlZveWVsQklZNl93RzVEeVBScF9MUnlHeUlxMlRUOE9QY2RLcE5IYmxicm5QblJYSHVsUkhpNUlJUHNEcnc5bnlpMG1vX3FNSVI4V1hJZzgyRVJJczJYVUI1c2UwOVgyVXdTaG5aQm9uS2ptY19sYTlaWmFYekxoUXpkT2Noa0FoV2dMZmlNWkV4WXlHUWZiR3FXb1I5eWFUUkNFdjAwbTJOb1Q0V1lyQWt0TXFqWUJSdXJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>08-05-2026 12:20 UTC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGoySDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>08-05-2026 19:21 UTC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How Teva (TEVA) revenue breaks down and what it means (Near Lows) 2026-05-08 - Verified Stock Signals</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>newser.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeTMxM19VWXRKbS1yTkdvajFEOWRxYWRYejNmdlZudVhCb0FlMGNzanZyUTgxdzNJM2ZCcWM0UjR6MHVXYzlVbGRvZzhqb24xWHdqOUQtc0N5bmhkQnNGaE9HOGFDY0x3dXE2aDRYTjZHWkFPS1ExblduYkQwcjlLcnIxc2hjQWpZanAwdmpiRzUyc3ZpVG1SM0JDNWtIWnpyZHdYTG91dHJIMzFIb3VLSmhqNjV5S2c?oc=5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>08-05-2026 08:43 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1637,7 +2085,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-05-2026 21:39:13</t>
+          <t>09-05-2026 13:58:42</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,27 +469,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz CEO Says Size of Weight-Loss Generics Market Is Unknown</t>
+          <t>Aarti A Kapoor Joins Sandoz as Head of People &amp; Organization Operations for Region International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQZUR0LXdsMlNCVENXM1BoeDU0eFNlWHhqVXpxdEVNUERmdGZKb0htZmoyZWtCNmJEYnAya0ZVbzI5Z0NhTXAtek9GOE5XbjR2WFhNNkxGakwwX1B2Mk1sTTN5Wi1MdmF6WVk5UHhjTEZqMl9KX29XU3lYd1dxZVJUTmYxbE5wRGlaSDhOOUZOWXBrbUhpOVdUcllWQkFUMUN4dGx3RTlrRUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNbTNUaWpydDduWXgwVlVPQzYxSHZHZjA5enA4aHdZeE5QR1RfcWNlREhOVW91N1ZOSmdaUzA5ck1mckExSHV4bXpyVE5vZFd3OTllVWVJZXJzQVIyNjd3REFVRlhMNm8xS3pBMEZqTmtPd2F1Yll1dUJyMmtIZGNrQThTU0J4b3JqQjUxT0tHNVBfcVM3MEktd3dIM3VLYWV4SlNSVTZEVTN1OE5TOVFvcUlIV3o?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08-05-2026 13:15 UTC</t>
+          <t>09-05-2026 07:25 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -501,54 +501,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aarti Kapoor to head people &amp; organisation ops for region international, at Sandoz</t>
+          <t>Novartis AG stock (CH0012005267): Pharma giant eyes growth in weight-loss and cancer drugs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HR Katha</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQZGFjU3RIbmI4SmZaM2tIU1pfelRubDJpZkhJUkNGTEVLdGZmbDk5ckIxc3dYUmFpRndJYm8tQzhtSWU3WkN0RDJyYUxQcjJSRlJtU2V0Z0dRM0VkdjU1LVZ4d1V3T3FYXzBvLUY4Q3lFNnFzT0prQ0lzaFJnVVZBbTJYWnhFZUI2cUF3R2FfWEh3RExLZEJUbnJoWkREcEkxOGNlOFVvb1ltTHRkeGt0MWJTUGl2UGNHVFBLcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOU25LNXBac2dEVGpvdFIyZVQtdmllQ0Jia09DeDlWZ29iV2RXNDBaakpkd05EdlFOU3VSZjhqRmtJR252b0tqYUhpLXlUbmJSRE5LTDhwdkFydHprLWpJeVNzUW9OOUw1RWcyb09oQ3VLdG9lRU5qLXFkUFdiV183V2lOT2xlb3dBVm9Lc0ZUR2pmSHFWM1J0LVB2ZFBpMV9WRXVQTXpCOWZZNF9ubEFwNTRQS1cxVVBnUTdSRXpEZ3ZfdlZSTXlKOA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08-05-2026 15:44 UTC</t>
+          <t>09-05-2026 13:47 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Sandoz sees stock surge in Q1 2026 By Investing.com</t>
+          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOUW1zaDgzbHQ3TUt6MVNRR0ZCcnhBSnE4aFY5eEQxalh3dGdPZ2JzdU9NV3I0eUVQX253Zld6Z25OTTdxTzh5ZWRScjZzSDQxV0dMZW9zSzhLZXlOaUUtYkZJUnNiSl9lT3B5MkNjRmtHVTZxOTJXNlJHdUJoVWpGaU9LNEctVnRTdmN5OGI3clhlekktVVZZNEhpVkdKLVNuYmxQR2pEVVU4TWdOMDREUkk2QlVJRVY2VzZHOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08-05-2026 12:07 UTC</t>
+          <t>09-05-2026 14:08 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,91 +560,91 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandoz Secures SBTi Validation For 2030 Climate Targets Across Operations And Suppliers</t>
+          <t>Richter Expands Rheumatology Portfolio with EU-Approved Medicine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESG News</t>
+          <t>Hungary Today</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNaHgwM2tGQmdvYUlic21xWXdRM3JlLXd1VHZEd1JBM1hhODc0a1JwTHRtRGRteHAxZHpYVVFNajRCNjFWRHNDbVhtNTFBVHU2aWR6MU9IZzRuN3h5WTAyUGtZYlNjdmVoVGtJZ2Y2OFFsMUxTTDdkYWpLUENrZm1WTDI4UG1wSG5MLXd5Q0lsN1JxS0ZyNmxRM3M5eWdEcERRbUtqbmFkLURLMXlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNV2c0Tzh0bkRONDdNX3doQmtZMUdVc0ZJQ0FiVFY0ZHdPbGJKVUpieUFpN3Q0aTc4cHMtdWdicWowZ0h4a0FnaGRjSldZLXdMWWZLUG5WV1REcFlWbnZCQnhlWHlWZ29IYlRJZVZLdE83N0hicWp5X2RfZnhabldpaS1ReU5HNXZqYTE1SWFtUVVuNmc?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08-05-2026 13:35 UTC</t>
+          <t>09-05-2026 07:03 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandoz to Launch Generic Version of Semaglutide in Canada, Brazil This Year, CEO Says</t>
+          <t>Boehringer Ingelheim group comments on export prospects of Kazakhstan-made FMD vaccines (Exclusive)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moomoo</t>
+          <t>trend.az</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNX1hhUGMzX2pJcVdRYjNMRFFHTjM1OExKVjd4ZWs3b1lCME5YdnViNWYyWlFFXzFTb19xeEdWM2ltRUx4ZF81cks4aUFtVDd2YnpyalEwR2tqZFVRU1BnYUpDNHF1MzBDNkZrd2tiTDZsSTV3SDJzc2tlSGNhRURDY0RjNl9fZ2VxSlVoR2xXcFhYcmJXOVRBakRscmJQdy1yemc0aWtKY3c5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9XRVFhQVgyZjFwWm9aYmVPb2c2MzFFa19UVzgzdXpmM3N6YVp6RkhIWmpUanZlTjJPQldZdjI0ZjRnNnE3VWx6TVUzMEZrQVRwaG13UUtaMVBfTlkxRW5B?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08-05-2026 14:40 UTC</t>
+          <t>09-05-2026 09:15 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Formycon AG Stock (DE000A1EWVY8): Analyst Upgrade and Price Target Revision</t>
+          <t>German pharma faces “historic” squeeze as Merz targets €40B deficit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com UK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQekFSMzhrQ1pRVUlmRldJM1RJTkxHeEYwa3ViZjc5U3FndHV0cXMwekkybm5NNHRiaDNLLXhxSDJiOW1JLUdBSGpOZGZ0aHB2M3k2b3NoRkJ5cHZpMVF3cm1RU2NlR1pfdVptS0FLcWVpY0ZGSXNlYVdiNVE0czJnWTFkbFUxcDg3WE8wZGNQZXJOUlBEdS01ZjA1UjlJUGFDSEhWUHRTN0lXRGJRN2JITU9uZ0h2OVU0cnM5UGp0aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWFdPdXFZb2tVelgzZVBIay1xU3ltUmdvVGw1aFh4VG90UXViakF4TEUyODNzOWdNQUdmUmhpZXpFX2V0MGlVTkhlS3RNSmRvaG12UDRhUEFBSFNkTk9DYm5IV3MzdW1CLUJzaWdzSUU3LW42QlhlUzFFckM0bHRFNmNFaEdVcUxQU1NDMHhiMXJidDA1dlRnLTBFeEFSaFplZ1AxWEwtdXJHWmM4UHd5ZWJaTnZUdnVQRGx0XzJWLVJadHVpNGc?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08-05-2026 13:34 UTC</t>
+          <t>09-05-2026 05:55 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGVLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNmdMWTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQLVNxU2Vzd2R2dWxBamRzc3hOLWZaQ0pYU2RLR282cU1FR1BQSnJ4NnVUVHFSU01JeC03U2RacktmdlhKeXMtUlFkQU9wb21aX0l0Q1NkbjNKcDZ3eHJxZDc4SDdwdXV1QnA0Q3pmcUsxNGxLMmx0T1lZX3BqRmxZb2lQT2l0TU5RcEVXb3BoMXRzN2h3MUFNemo3Nm4xMXFzc25mTVllRVVMX1ZpUm9BRGR3TGgyWW9sclZGV2lqNWZIdzJLaVFFbTVuT2ZocFowTGMwY1d0My1oQlNkQ3VmNmdMWTE?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -725,27 +725,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
+          <t>Mounia Benbelkacem: Advancing Translational Research Through the Amgen Experience</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Oncodaily</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2empEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE90REE2dGRKVnJmcFRudURVQnU1OTgwNzZPc0F4dFNkaWZ2QzE1YUJJZzEyVXJzNWJOSGtXaTJ3OXRxSG5zV3o4eFFKY1Y5TWpfR3o4cDM5b215cFJ2Q0FleWlLMDA?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-05-2026 16:38 UTC</t>
+          <t>09-05-2026 08:39 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -757,27 +757,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Puerto Rico attracts manufacturing investment with Amgen expansion</t>
+          <t>Amgen Inc. stock (US0311621009): Biotech giant eyes growth amid patent cliffs and pipeline bets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WJournalpr</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNTFdhNy1iell0NUFZQUlrMUhsYndJZzJ4WlJXa2l0MERjbnlVZzBBaldBNFpHUTFtNEVLV0FOT1lMUHVONF9Gd1lMY0NVWnhlX0liZ1Y4TEFSR0RxM3NnRU52Nng3U1kxQ0NVbFF6c2NZQTJFNTB6LVpIczhKbUF2QkY5NXR0VUVVWENGQmFQa3ZtM2NoN3gyd1VfSHZNUEkyQ2dESXRlbGdNdDFQeUFSOW5ac1BPRF80YkM5SlE5bEFrMTVUV01yenJld0FWN29kQUVzM0FGcWU2U0FnMHFHZnBOV1BGUDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0VvTzJmZm9WYUY1YUVrcnJXdmtldlNEbGw1UmJEZWkyRkRVOXlFb3FDbmV5YXl6dnRhajJUTFB5Q2dybEVIaEFDaVhZakQxOG1jaXRSRF93cGdHSkItTlV3b2Y1b1IxSkdPZVFONEpQSUxLN3VJNTFFZVpBSGd0dDluOUotRHcwb0RQbmg4UW9KTk12WFZWNjJKNWZfdDhQZmJHV1VaTHBJcmNDbk41UnlFdUYtd2EzUkdlUzdDZUNNQzg?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08-05-2026 10:00 UTC</t>
+          <t>09-05-2026 11:08 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -789,22 +789,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Inc. Stock (US0311621009): Shares Dip After Strong Q1 2026 Earnings Beat and Analyst Downgrade</t>
+          <t>Amgen Inc. $AMGN Shares Acquired by Wesbanco Bank Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONmlOQnhETkloS1Y4eHJJaTk2bDNacldPN1FhODB6NlBHa2FnZnlmUDl5MkhoSkNCQW5NLU9SdlZyeUt1UlBPdHA3b2VQNDFpTy1RQk9UTE12TlZWRkhGN1Y3N3RDZ0ZKUmtYaU5fLWZwYUY5aXBqUEFDT0lWTHprV0tPaFlpb1YzOXZUWFdHdlVqQnV0ZHRPVFRwWXZseHBuTUJ4LUpsejV5Y2tYX3RpajJUT204bVg4eVZ3NWpvaTlEVTc5NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUjNOZ25oNFdGMTc2Y29HNlRuXzdyVk1HRVVRb0p2Rnh1Q0R2TTF6TkR4Z01BQTBTeEp5WWVMN2pJRkV1WjM1bDc1NDhhdUpIUzIyVHdBb0F1N3I3clJVRVpmQnpKSTB6bnhaRlpuVVQ4SVk5OUNhSXdNWWl4bEdoS2dQLVhRclBGOEI5NkJNS0tVLWxNVVQwTmNKaVR1N19kV3puWktmQTAxaDBMeV9rV1F3?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08-05-2026 11:17 UTC</t>
+          <t>09-05-2026 12:05 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen (NASDAQ:AMGN) Stock Rating Upgraded by Freedom Capital</t>
+          <t>Is Amgen Stock Poised for a Rally?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONk16NnJSWXhHbE8wcV9mM09URE1peDFPR1lWdVhpNktQcEhITC1waW9QZmYzWkJlMDNYUl9BN3hVZHY2ak1MX1BZR1U3MUgtVDlLUFJHdHl1Ty1ueW4wdUpOeGl6d09jLXNPaXpqNTFJTEZDakRlQkt6WVYwSkRGbmtRcFJnSjdIcWpIbGx6Y0g2MVlxNVZqUS1fQ3ZUWmEtcThicG0zTjY2QjBjRlhSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNcFdKMmk0TXo5QWVRUU5RSDNHVGJiZjdvR09uZGxsdlFzZjZKOTI4RHhkRU8xTVlFU0hGUTdfOVR3MTdySmdWSzVnV3J1QXIybVV5UENEZHRJNHVKbEtzUnQ3T2lqZkJZdFRxSnBxMlF0Qmc4VmJqM3dxT1F3LUZaYlg5OW91TDRCeVJaZk4zWGttYkprdDhLNGZwbUx4QQ?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08-05-2026 09:47 UTC</t>
+          <t>08-05-2026 17:43 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -848,27 +848,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
+          <t>Is It Time To Reassess Amgen (AMGN) After A Steady Share Price And Strong DCF Case</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyTjkyS0dIUVRYSW1YbTg1ZGFRR3Ytalg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQRE4tVS1pWFJya2JYbVVzVmkwRkJCRlNxMjd3RXoybnk0ejNJWFF5WWhvNG1tNENHRlJVWmo2NXZFc29qeXE1ZWthbER6ZUllRDhVV3BsVkVzRjNFNV9GY3lZN3U4WG1NREdDcVRHdUcwelRLY2UtY0MxQ3Atbk54ZjRfaFlkaVppcG53WmlfaFNyUzhvUFh6MzhsV1NGaGxGWkJNT3hmalJKeVhaNF9pY3pUbXlKZ19WWloxOHVIQjMzWVRkeVRxZUVrZWZDcGN1WVlldEFpVVMxQknSAdsBQVVfeXFMUEROLVUtaVhScmtiWW1Vc1ZpMEZCQkZTcTI3d0V6Mm55NHozSVhReVlobzRtbTRDR0ZSVVpqNjV2RXNvanlxNWVrYWxEemVJZUQ4VVdwbFZFc0YzRTVfRmN5WTd1OFhtTURHQ3FUR3VHMHpUS2NlLWNDMUNwLW5OeGY0X2hZZGlaaXBud1ppX2hTclM4b1BYejM4bFdTRmhsRlpCTU94ZmpSSnlYWjRfaWN6VG15SmdfVlpaMTh1SEIzM1lUZHlUcWVFa2VmQ3BjdVlZZXRBaVVTMUJJ?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08-05-2026 20:22 UTC</t>
+          <t>09-05-2026 01:03 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -880,27 +880,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
+          <t>Amgen quarterly earnings beat but stock drops sharply, MarketWise reports</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9mZEtia2R1ME9vUV9nMkdoaXppN1dLOUs0WlU4S2dnU2NxeGlqZWx0NFNWQXFUWWpyalBXRG1tWU5Ha05NT0tNR0V4UnRmQjlzLUE5TWlydURfSHVaNVNPbWtFbE5GNy12T3hRcDBHY2dpaXUxa00yVzEwMk1uMXc?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08-05-2026 20:28 UTC</t>
+          <t>08-05-2026 17:25 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -912,27 +912,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
+          <t>Amgen Inc. stock (US0311621009): U.S. manufacturing push and Q1 2026 results in focus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTjlvSWVSZRENTUkyV3JRdXpQLWNLU3NWcWN0WmY0cGpCSi0zOWIzcmRnM3gyZUQzSmsyQXhteU5Vd3B0SGdFa2Q4RTI5dmFBRnlDVnVuZHRjRDFCRC1EOGQ5Ul91Nll0SVlqcFZBbjdhMVRGX25MNURIaERtWnlaTHhEZGdqU2lvY0hNSko5dTVVNXJJVUFWZVFKVi0wWkRSb1pRdk1BRS1hN3F1blJnOV9sdnVNaVZNaWZRd3pROA?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08-05-2026 20:23 UTC</t>
+          <t>09-05-2026 13:49 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -944,27 +944,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
+          <t>Ethic Inc. Boosts Stock Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNamNaUl9jR1p6bkRKbnhxUXVueTBmN25hUHZ0Q1YzWXhwcGNKWGlRVzRReGhlejQzbFFXeDBQNUtMREVYNDBPWUpKblNCalpLWFpuQklwMXVoR2hYS2t3cUZ4clZtMXJZR3VPZjNQVUxCMXNCUk5hTVJIOU9Pci1UTWw4NExBNnlOUG9rbGYxalJOa0JvN0tKOXlFY1lIdVR2ZkVwSThWME1TWmpMejR3?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08-05-2026 20:22 UTC</t>
+          <t>09-05-2026 08:34 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,59 +976,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
+          <t>Amgen Halts Phase 2 HZN-1116 Trial in Sjögren’s: What Investors Should Know</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQNUNQNElnVzlNTDlDV0dIMHhJWC1XMVV0eXB4SGRsdjhnb0c2eUpXazR1eGhDN252LVRuVVNaV2NmdnQ5eXkyYnNGdGFaUWFPZDdHYXAwMnlPVkFOSmJEX09PRUdUSHZuZXhBU28zT3RNaUJyNjlYUGtWc1YxMkFZZ2Z6dVdsXzJRc2RIRl85UFRyZjhEVk0wVENzenJzaklhcHF2cmpEem9fWU5zUjBjSTh5MVQyRnFtRTM4b1RNMnFJMnc?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08-05-2026 20:29 UTC</t>
+          <t>08-05-2026 16:38 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
+          <t>Crossmark Global Holdings Inc. Has $15.62 Million Stock Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQQlJLWnQ2cHpETDROblRuYzRVRlVDV3Z3RHVfODdUdVplWUF0RGh6MzJkbV91TG5FLWpkR1RhUzE5TXV2WDB1NFJvNkR3SXBOekVHaW9hUmUzZ1Q1U1dpRWZfS3lZWGZpUWVyc19YenJIRkxUR3RJOXlILWMzRnpNQ2JfVFpteHlDREo4c1NTUF9VUE5YZFdBbUhUVGdGU1k1ZUtXbTNfcGk0cVlIQ3hHd2pGSENURVBTTmNfLWFCS2lhZTF5MEZSNTlVQ3lCSG9WY0FobnZWWQ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08-05-2026 20:24 UTC</t>
+          <t>09-05-2026 08:43 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1040,91 +1040,91 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
+          <t>Amneal (NYSE: AMRX) director exercises 48,747 RSUs and receives 30,837-unit grant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hcamag.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObFJ0MVBUOU54OFdjX3ZhLXFOMXYtN0J3eHpnQUpSQmhfMFJVYkJ2cmNJVHpmZzRaR1Rja3dGM1d2TW1JN2pETm9EcUFoVUdjdThuYzZaMmJNQ3JPamZjQlBBUW5GSC1CNkY3RVhzT2w1djlPUklHa29kNFFmRXViZm9fQ0NUTTdyWmpGOTJLR0hRTHRYbVhtODVkYVFHdi1qWkZ5ay1BVFUtV2hBVDN2RGM1TEp2NFFCOG1QZA?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08-05-2026 18:48 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
+          <t>Amneal (NYSE: AMRX) director settles RSUs, now holds 128,479 shares</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPRzBISHVCNmhqc2JZUHljSkprOWFpUDBSUHlCTGMwZ2VldGdnYXJKcUV2V2R2UnAyYkRMVE9QR3RHVWF5Uk1QQmpiMWlIQ1lFNHJ1ZXlPSjhrcGtZNVdmcERiaFB6X0Y0Nk5GMXlNZWFTU2NYbno4ZU50dWlQVVM3MGlVNXd5M2dPRzlFQl9fTEl2QVZld0FEYmszbUcyUEFqN2Z0MG9CWGJodjhENFpQVXZJYkdEMHpuWXZydA?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08-05-2026 17:46 UTC</t>
+          <t>08-05-2026 20:28 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Novavax Stock Jumps As Pfizer Deal Cash Puts Vaccine Turnaround Back In Focus</t>
+          <t>Director boosts stake with 34,819 shares in Amneal (NYSE: AMRX)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPdjdLQXA5dEc4TnJ5b3ZiUFBZUWJGbzBEUE5acG9DdFZJb1VzUkVZUWJLRXZtYXotcDNHX2lqbjV5TmVaUjQxWFcyNHVOUjlKTjRyRmtMWm9kOUhlMkpMOFZkNnlQOTN1WTZMaWt2ajZYcWtzdHZLRVFwTXBacGVpZnJzRGxMQzJPaEFKNTBnd1JUdTJPa0tnU0hoTDFnSGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQUmY5d1VmNXNpVzJkZlU0aUlBbndYMC1rck9CWnRLVVVPMFpnVlJEN2VxYUZqNWhyWER2dWtQLVh6UU5TTklRbkUwOTRxNXp0SllXUkliZFBCazlSY2ZCb2FSMUs0RXV2Z1VMN3JXUVM3VFd0WGhwLTVZRldpMzBtN241MEowa2t5WC1VSnBwN191RVc1WDA4bEkxcWtHb2xvQW4xc00yQXNyMVRfaEZOZTlSaDM4N0dmblFYQQ?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>08-05-2026 17:55 UTC</t>
+          <t>08-05-2026 20:23 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1136,27 +1136,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
+          <t>Amneal (NYSE: AMRX) director converts RSUs to shares and gets new grant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQLU9LV3Q4NUM1SWZlSHlwajJZbnQtNjFFbk0zTkZoSHJyUHk0VnFzWnZFZG5MRm9xcDZ2QVpFeDhJbC1QbU5ITVFIX18wMTRyUDhUdTV0TEFvMjR1RnB5N3ozNUh5aXBBUmswbDEzcjAwOE5GcWtvdXlLMF9Zb1RWVXpCR29WR1FJN3BCV1l2MkNLdHNQMGtHQ0JYZVprM2V2cXAtNTh2S2dxQlM4T2pwMnNxSFFGVllhdFItbg?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08-05-2026 22:36 UTC</t>
+          <t>08-05-2026 20:22 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,219 +1168,219 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
+          <t>Amneal (NYSE: AMRX) director exercises 34,819 RSUs and receives new grant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVDJlSU1KMzF0WUZjekFjMVkyaFVoUUFKWnVlR3JOR2xVdEgyZnczZ3lTMFU4akE1QTNfOGxLTG44Q011RllveS1EcVRSLVBTZjhHUE5aMDdTNjA5SHlSVm1pcVNPV0gyenRVRUtfZ014cUhQSjZZNzBYcHVYMF9BRDQtS2c5M3JoenhhbTUtVUdweGd2TXZXREFsQnFPQmt0OEc4ZlRTN0tQcXYySkZySXFEVWpjMlZuZGJwcQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08-05-2026 17:09 UTC</t>
+          <t>08-05-2026 20:29 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pfizer Viagra stock: What health-conscious consumers should know before considering alternatives</t>
+          <t>Amneal (AMRX) director exercises RSUs, now holds 260,252 shares</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portal CNJ</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxPZGdqUGIwcVY3NlpISG1ULWNyQlZOVW51bVgycHc2RUlYWXlIbE5jazdUQ2t3NFlvYVRkWjFXRVMzMWdVVm9adDVFMlRQRmhMSFdwUDhWTXRreUlqTFpfRXd1ZUxwNG5DeE1qdmxXaDZMUWlWOXVWbHlqT3NqUURucXFkNjVzLUVlRjMzeHpOa1JJRzliZUMteksxcG45X1dfQlBVODR1ZWQ2NnZ1NERka3J5cUdUY0Ezb3VjR29Ucm95N05td3lMRXVNMHhrRVRZRTZzS0hqajR1MzhTOXVRVDNsY0NqV01QWlpyZlBHODRwMHB3clVhaERUV1NpeUk0VV9tZEt6dU56ZmJL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPeHdoVS1nc3ROQkNndThyWXpaYUlJb2otdzVSTlVPSTJ2ckV6di1JS01mai03MTFDZXc1RGZldFoxWkJFcjZUZzdnMi15SHFrWVh5RDFYQnhFT1d3N3RRWU14dWg1a0UzdXpSU19PX3NQRGlnQ21mTW9KeEhfY0tKamUwLTllbTVKaE1GaUpZQ1E0cFVMUFNPWjJzR0VUTUd4cmEwYnVkaG9pOGh3QXhZeUlscDJTdU9lWC1mUQ?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08-05-2026 14:54 UTC</t>
+          <t>08-05-2026 20:24 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
+          <t>Amneal (AMRX) director Jeffrey George exercises 34,819 RSUs, receives 19,824 new units</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BioPharm International</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckHmZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNY0lHZnVFdXdjM29rODZLUWZDS1NpdFRNTkdJWkR0WXJVazJRZndTQ0Y4cmpCVThkNUg0VXZrQk1sN3pwNF9MT09PUXc1b0pEb1RCZjR4RkIzUEg4TGt1N3dIOHVwMXE3U2pIOXVqN3VaTHIyTllCbm9TaldPQ0wxT2F2TW9DT0RMNHhGdTdJUnlyQkJpN1c3OEpVVlV2VEFVNHR4OGhYNU9McDhKYUd1S2pMLThhUmxxOFJrUA?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08-05-2026 16:47 UTC</t>
+          <t>08-05-2026 20:27 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alteogen posts strong Q1 earnings on GSK, Biogen licensing deals</t>
+          <t>OGN (OGN) Form 144: multiple RSU vestings and dividend-equivalent share listings</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrd9IBckFVX3lxTE4zSF8tczZrbmZ0eTJWUDB0c2QybTlzZXc2c1N6bkUxLVJ5Y255ZW9GVldQTUM5aktPcEdWWkh5UERvVjBNaFJhVGtObUVvaTEzUV9rUDdPcFdBSUlwTW9uZjRKZnlfRHBSZzQtNk0xXzVrdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOODZSaVB2X2ZYQnVkRHZlcWRKa3liUUhqTTNhNVhtX0RQWlJIeTlIUTQtY21ZZzJuVDR3cE82ZElaYTNXU2hObl9qU01UMjMzOUVra0VoUVlfNnlXUnRfUzk4NndhM2NMWE1WNzd0YlBoZmtjRTJQQXduNUQ5OVBlVWFhejN5SWlmOUFvZk9pWQ?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08-05-2026 08:28 UTC</t>
+          <t>09-05-2026 00:35 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
+          <t>Generic Ozempic approvals signal a turning point for Canadian benefit plans</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>hcamag.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VTX0dZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfTXVVMG53RElIeG1TeGJTRVpfdXlhZHZPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNelZjNFFmYVlMVmNYX0Uxb1hSRzI2NmdWLW9SbVRIN2Uxcm5IcFFyWDhZZmR6b2FpQk5DRnhBbU8tdjIzZ1BJSUxaZUFlNmY5QW1sanBtc1Y0UEw5d2xtZU5hdE1vdm15NGRKWC1tS3EyXzZheGhWQzNGOTdxLS1ldWJjU1M4SC02U2hFY0FZRmFIbHZQeHFYeDhRVHpwY2hqSHZEaFlUNHFQTUpkNUtVSG9VWVdpOHl1czgtcUE0MkR5d2lrZlZXX3hOZU8?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08-05-2026 18:54 UTC</t>
+          <t>08-05-2026 18:48 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage</t>
+          <t>Meet the People of PGS: Julie</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOd0luWGNUam9MUlA2N3pBU3hZeXJoX0R5NVNrdThOc0s3TWlSV3JDZEp2dnVfS1hNeGJZdzlNQWdtSTMySnlOMGFJY3FXVjhydzF5OFRLNW0yZGNvdlhmcS1FTmlIb2g1eGlicS1uNm1YbW05UVpyYjFwaklmOVhFTi03L1VVRDhkY05vMDlvU2h4SjctcEFZVG5nV1YzV09nOUJGZzlGSXBHVFJsakJEOXZJSW81UTF3aUlhRjdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE13Rzl5MkNtWnRRTVkxRkljMHpSNm1ZUTItYktwRGxfTE1jMUgydFc1UjlFRmhUY3JVR0dPaGJxMnlMNWlBS0xnMmlGQmlFamcyLVhUTjlSMUh4bHRJUHR5ZVRraElkQUp6YUE?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08-05-2026 23:47 UTC</t>
+          <t>09-05-2026 06:41 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations</t>
+          <t>-3.15% for Pfizer stock as new share registration weighs on outlook</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOVlJIWnFlWXo2TjdzQmxPZWYyeXk2c2NfRHVwdWliajZUSEZiSUhJSlAtT0o5MENTYzZMdGEyMEJPejVoX2dsLWNYQ0d6c1UxbHZGYW1qWUFNSDVNSHhhRW5vQ2liV2xMbUZWZ2hBT3ZMd2dBNkJVU0ZmUG9ENmRKejdIdjktY2RXNWloeUNvUWN4Y3hJd3kyZlpKMHZTQy1zclZETmQ0aHhRd09yVF9oM0ZqbzI4ZzRicFZQTzRna0xqWTNvUjl6TVRGbzV3a0M5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQbkZXcjdsUExxNlEwbWU2aFpPZmdhSGFsdWc5TUgyVVo2ZFF2MzNCM2pPVTlOSFA1b1U0cXBPeWY5OHNTMHlFcElKS0hoMXZaTnp1bGhwVHI4aWlNWFdpcFFJektDNFhTNzhmMDlITE9ZUEVfMFZLVHc0M1o1a2YzVndSeGpkREROMnhXV2xBNllkMjFleTRPag?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08-05-2026 21:40 UTC</t>
+          <t>08-05-2026 20:08 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,59 +1392,59 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s-Nestlé Health Science Launch Celevida® GLP+ to Support Patients on GLP-1/GIP Therapy</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 2026 results and recent share price move</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Indian Practitioner</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQNUlZRGNfUVg0NXFGNm1ydkYyYkxRMkozR0hkQjd6T0dMYVRBZnZldS1HQ0ZvQ004bV9uSmhVaWUtcUtSLTZHdHNON18td08tdTJIN1V1OV8yUFUwNHd5aEhldm8zZkQ1TnpleGJsS0xTalM1UkxtZmZnOV9BVTRiaXdWLVVUa1Y4X1dfSXlyd0tReUJ4Y0VzSGh2NmVhSzlocTBiNmxWcXVpQnktUW1nUm1sdk9odXcteHA0dWlVN3lLS2dOVXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNeEh3d3FGeXBJeUlBUnRDRnowblNwNWtxQTkyRHp4OWRNT2dxQUtlYzZ6WXhscmtBUW5fVjl1N0MxTGc0a0trTDR4a2ZzajNUSnc0QjNXc3lfQVF1Q01tQTNnS19hOUx2R2lmT3JYY1lza3VodDU3MTdiM29wRUZxRjh1dDBXSmN1SGdzemVHWUZnekVIOWstUkFPcWxVY0JKaDJsT1NaVnZpNzFqbmQtcm9kRmVhdUpNam00ZGFCZXhDLV8waUE?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08-05-2026 12:52 UTC</t>
+          <t>09-05-2026 08:57 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories slips Friday, underperforms market</t>
+          <t>Here is Why Pfizer (PFE) One of the Best High Volume Stocks to Invest In</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPVnRxYWF5YzVBNXF5cU56TjlzSmgyc0ZsMmtGenA1OVJWMEVBYzJSWFRpZUZ0dTRpb0Z2WTh3aUZXVmdtZGZSMjF0YWRNOHNhUXZ0dGlONzlTZ3pKRmlibXRKdWp4Y2I5eE9TS2VRWmtNdUdzTktiUUN3Q19HMkpraldTcEhVdjF0TWdRZEZfY1RrLVhkeDhfeDc3LU1ZWVJCRUxab1lLZWFBOGtBaEYtWU5xOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5JWEhkSjZUODA5THFlVjRTQUVhZF9UUnU3a25uRjhYc3VxVC1DSWJta1BGOGs5LWxjQS1tWW1FMFRXVHBTSkVsOVZmQmUwb2otREMwUnh4dXR1N3pMQ2VqNHZPeVUxak1mR2hYM2hUOGNtalVibW5zaGVmcXI?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08-05-2026 10:30 UTC</t>
+          <t>09-05-2026 04:57 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1456,123 +1456,123 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Biocon reports 63% YoY fall in Q4 profit, final dividend of Rs. 0.50 recommended</t>
+          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWWVrTmpvZE83YjI5NFp1djBMczliVmROVVdxeVlnaWFkZmk0bWVLUGdCU2VWMlQ2WEotUWlQYmlrWmY2aGVISGhjaDh4aTlzTnJuQV9WREVGelVob29GbUV2ZnBSNGM2WmU0Q2MxUHVqWjB6WWJoT1lGUS1wTV8xaDlRNVl2R2hldlJFa1RnU0ZENlhwb3pTaDJQQUg4RTBnWFhyUWhMdmxGa2JKb2xTSkdnYjBWZ0U1ZU5jRkZqWHF4aWpyWUpVUTREcE9lbHBWZVJ3enFmbk9ob0hnSy1pYlNpMkZQTTdibkhR0gHwAUFVX3lxTE1kNHVlZDFzaHZpbUd4U1c3VWd1WEVlc1Y3X2NNT2lENGVOSEJBdEt5NElTMGRLcnBjUlVGLXl4RGdDeGhdTGdDZWdBMl8yOWsyc18ybW4ydHY1Uzc2MWRFX0FmR0h5WFFLYkZNb1Nuc3JGLU1pZ0tRN0k5Wll0SkFYajlfNzV6N0M3RkhhY3g1WlhDRm1CS0lNNmVpeGg2NzBoNjJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTEBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08-05-2026 10:58 UTC</t>
+          <t>09-05-2026 11:16 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Biocon eyes in-licensing deals to expand biosimilars portfolio in FY27</t>
+          <t>Fact Check: Hantavirus infection is not a confirmed side effect of Pfizer’s COVID-19 vaccine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQcUhDX3BBemNPc1RTTGhHUU1PUkZUR05iS1RNbFJwSFg5dktHcnphX052QjdKc19uOF9GVnZhRlhoT2czRWNERFI3YXh2RTZLU3FKTG0taWNCREhiM1I3cmFYVm5uWjE3WGM3dU10dEZKWmhsbFVGd3RuTnFYdVBOTzFxUVBldnlRbmU3Nkg2SDBucDNvbGpieHRKZlE2RnE1Q0dzWWUtMzVDbGhMbUpDb2Zzb2pEakg1OFpTNV9zMnp0Qmp4bFg2NzZjMDVXYkpucXhqMlJXZndQR1XSAdsBQVVfeXFMUHFIQ19wQXpjT3NUU0xoR1FNT1JGVEdOYktUTWxScEhYOXZLR3J6YV9OdkI3SnNfbjhfRlZ2YUZYaE9nM0VjRERSN2F4dkU2S1NxSkxtLWljQkRIYjNSN3JhWFZubloxN1hjN3VNdHRGSlpobGxVRnd0bk5xWHVQTk8xcVFQZXZ5UW5lNzZINkgwbnAzb2xqYnh0SmZRNkZxNUNHc1llLTM1Q2xoTG1KQ29mc29qRGpINThaUzVfczJ6dEJqeGxYNjc2YzA1V2JKbnF4ajJSV2Z3UEdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQjAxUjYtNmQ1TUt6Mm9DTGdlaGt3R3pjcjNWcUtNb3BNVGZNN2tNdGhBY0VCc05lQ05JOGtDSlJOdjhyMGZvNVYzZTVFS0k2N0pTSk55OFo1aEJfOWxXYmFvSEpSaXBVRWJQUlotMExaUTZUSTctdkRQekpYMmlHUll1RUkzejZVdGZ6ZVVJWWUxc2JrZFlrQ3lBdjJYUzUxUVpMZ2RDZjk3MFVRTHM0akZXeTNYcGdkVDY2TlR3?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08-05-2026 12:54 UTC</t>
+          <t>08-05-2026 16:45 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqWzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqWzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08-05-2026 18:15 UTC</t>
+          <t>08-05-2026 17:46 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
+          <t>Pfizer Inc (PFE) Shares Fall 3.0% -- What GF Score of 76 Tells I</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOS2prNW1waGtmNEpjY2JZTGtWWGlmaG0xT0tlbm9nVU9Lb2Y1SHl4OWE1Smt3SkV6MFl5U1FtMkZHM1N5S1ZzMVpuaEJ0N1F4QTIyVUM3c1ZFWU1zS1lTMG1VLXVMMjk0U180cnV3Z3lmU0RIekZFeEZ2d001Nm9tYzBYNUhIT0pfbGEzcGpFVE9HOWFaU28xMXFTTXhyZjQ4YjB5RXZzaW9BRjFwbDZQR3RIZkNYa1E?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08-05-2026 16:42 UTC</t>
+          <t>08-05-2026 22:36 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1584,59 +1584,59 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
+          <t>Pfizer Inc. stock underperforms Friday when compared to competitors</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>indiaherald.com</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fcjNZaldTbnc2b1gxRk5xZ2tjRm96am5mcld5ZktIRXRSQXlHX2M3TFFnNTZlekhRMUHSAa4BQVVfeXFMTmNaVjgwdkJHQl9xMFdXbEtjN1UwQ09FdzRlakZZS2wzWDNCamlJU1F2ZmRac1p1ZjFSUWNfQnFXYV9qMHJXWFQxbFFjaGo2UWhDb185N3Q5QWlrVHRoeUxFcGY3bGk3TWN2ekZaa25oZUNQc2hMNlBzeXMtX3IzWWpXU253Nm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPUDVGSFNMTHBBdk9ZaHdmc1NBY1dqOF92WDdEWXJVZ2ZEdWluejkxVFJtNTlYcnlBQ2Nib2tCdFJmcTJkNVJNTUNYd3lLeWQyNFdkd2NHN0NTcWdDNmoyOGFEQ2NQaEdicTR4aFk5S1RkblFRRS1odGpRTlZWRlBDbU4zUlpXSjhvMGdaSDJURWJmVmJmdk5yOGlzejFMR0phaHBVbUduSmd6b2tWcGNuTERPX1F0RGdzUUtqVlhwUV9DQmVK?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>09-05-2026 06:04 UTC</t>
+          <t>08-05-2026 20:36 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Board Meeting Scheduled for May 19, 2026 to Consider Q4FY26 Results and Final Dividend</t>
+          <t>Vaccine and blood thinner help drive Pfizer to quarterly earnings beat</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaXNBTm50RkIyTHVsS0UyajVqdkVMMkRuMm5yWjl5aEwyMW5UbE5JZ1ZHNEVPZUVNM2V5SWVwYlFmQ09lMXRkN0s3ZnY3VzdtaVZmd2dLQ2QwdzFlMjBnYVlZbFF6Sy1fS1Z4dHp5ZmExSG9ybERJRlh6aWxNejJxSnVNeXgzY1JGeWV3ck05MEM5aC16V0JuZUN6aW1ETlZ4N2ZmNFhyWllYcUgwQzl5TGlscWZlYlhYOGljUFh0NTRzeHVPMFRyQ1UzRTFJZnJRRW9hc2xyRDJWdWlLTGRnVzdkLUpmQ1NlTUpiX2dRaXNILUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQalp6Unljel83ZnRVMF9McnpwMWNQaEV3bHlVOFNXNlpEQ25SUzBzRERaZzl4YWFZdmpTanp0YkdtUmVtNHVuMER4QkZMQUZFS2o4bHJRYXZKRUlSNFkyVVR4VEpjTThVSUgxZnNrTGtpVFVOaDFiM1R0bWV5RE9SYm9sT1h5eEVRdjh3Q09HUWt3WXE3dFlv?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08-05-2026 14:17 UTC</t>
+          <t>09-05-2026 08:23 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1648,59 +1648,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
+          <t>Eisai, Biogen Receive Extended FDA Review for Lecanemab Subcutaneous Starting Dose</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZE13SWpQdUlEamNKSGExdEJmQi1jVU00aFZTckhtZXU3S3RoOTRiTzFUbVF2bjhobXgtU091RXJYRzluci1VN1J6ZzU5R3c4aUtISF9VUVBSeXBuWTVyNFJtMmpnVU9ST294WHdQc2p0ZHlQNGVaUkFMYTc3YXVvZVgzVzF4VE1idFB1TWlMN19XeVNqVW43czNOV3g5OEQyd3V4bTdGOEVmTFV6T1UwSFgycFduMk5VbU9yaUtCZFVSdw?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>09-05-2026 07:21 UTC</t>
+          <t>08-05-2026 16:47 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
+          <t>Biogen Inc. stock (US09062X1037): Q1 earnings beat but guidance cut weighs on sentiment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPMndzbFgteVpacmNvRUNrRkdUX0dkcVBWcGt3cU9pZEFPVEkwTEt0U0lHWnhZVmNsTEFBWmNOWFdOM2FRNHdnSzRZQlpJdmxCdFZ3emt4LWY2Z3o1eGRwUEMwZ1dhVy1EYWR3M1dyMEFtUG1yWE9uMDR3TnM0UjNsNkdGZElTSDFkUTMyNjhTVVpvODBYVm1RN1ZQYmw3RHFtT3NuNzVMeHdyb0V6MHh5aHk3R3hzQXpTaHZQV3ZCTDVSaHNRd2JjNA?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08-05-2026 14:47 UTC</t>
+          <t>09-05-2026 10:56 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1712,27 +1712,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo – Cleanroom fit-out for the fill &amp; finish area</t>
+          <t>Biogen to Participate in the Bank of America Securities 2026 Health Care Conference</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleanroom Technology</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPQndjUGlfVVY2QWw0eWFrSUFEUW5ReGw3SlVIUFlMUnFHRGl2bjQxVVhnX0ttN1VQT0dIZkZHOVlVWGY5Sm1aSjVObzJiSEhkOWhnRjZXUFJ5OThKQUlWODBOSS1rZllEeHlzbzRnMXNobHJfTXk4ajRiQ0hpOEtHMFR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNSXFtaUhnV2lEY2p0T0gzWGQ0UEYtYjM3Nm5JUG5CMjRkbGZFYUNKWmdJbHZDNWxBT01iV21VRjNLVUJaUUxaYWd3WWVTWVMzRGRObko4THRFSDl2T3ByZjd1YThoX3Jmc0ZKWkM0STVnQVozb1ZnTGZBZGh0bG9Ra3M1VEpBMmt4c080bVVTd1FEVUh5enJRWTlnbVlFNlZaRTZsMw?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08-05-2026 11:30 UTC</t>
+          <t>09-05-2026 08:58 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1744,44 +1744,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Merck : Statement on Daiichi Sankyo Update to Manufacturing and Supply Plan - Merck.com</t>
+          <t>Biogen Inc. stock outperforms competitors on strong trading day</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQd2w0T3UwdXY1b1hNem1Dd1d2N0U4WURZNVdOV09BZi02TDJ4OWF6Y21GRnlsN2FmV3lHSk5xRjU4TE5EdGY4MUZNRnhsNWgwb2N5aHZhM1NST2ZBdHk4S2pMVWh1NVhUN0EtTGJGb3E5dXA1LU9HcllyNzB6eExJdjJVd2hPSFhkLXRzRERKNlAxVzZId0F2bkFRM2pYdVhCWktBRnpTaVJDZDZ1OW5uVjNXQ0pnZ1RLRU1TMFNfQkpsTkZLVGFKWHNaV3hZYnVlZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQcGtNS3E1MV9xbnJiX3pxT1Uxb09CY0k5Zi05M19VMC05cHZBSThzUURYb3VFdUpMS2Fyb2hiRWVING9wM0VLZVVYTDMxR3F6ajZWOWM0MUVBc3JtbnQyQktrY3FYeEhrSmNmYllUUHFVWWp3OVVBN1lVbkVmZnVSanNwYmd1UDNMSGhqbF9vN0pEQ0RreEdGRHlZOWEycDJCbXlMdVFRUVNuaEl0aGs4SjdxbXh3ak1ISVBCdTRfNA?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08-05-2026 10:37 UTC</t>
+          <t>08-05-2026 21:00 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kyowa Kirin (TSE:4151) Margin Improvement To 13.5% Reinforces Profitability Focus Narratives</t>
+          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Pipeline Prospects</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPRGxMN3Q1RVBsbnFsN1Nja1JtaVlVclBCNUtSUWRibEZOYkJkYUZGS2Myc2I3eGw4NEREZF84SnpHajRTY0hDMG1kWGZURTR5TVVOLTV4UW1zOUM0U3pEX3lrcDNTbVNmUFRhWVFldFVjWWp3VUZ1SGdxa1Q2dU1Cc0lCNGJiTHVfWnFFemZMdVVyWlNFbzJIR2VpekJJZFRqUC1PbmRKcEY5UWhoNldHVzNJTExSNFRsWS1vMGtjclVncWtRVGFvM0Q4WGREc29hVUFSZ0hFSjI1Y0Rtblg2c3pVSFB1alFT0gHoAUFVX3lxTE9EbEw3dDVFUGxucWw3U2NrUm1pWVVyUEI1S1JRZGJsRk5iQmRhRkZLYzJzYjd4bDg0RERkXzhKekdqNFNjSEMwbWRYZlRFNHlNVU4tNXhRbXM5QzRTekRfeWtwM1NtU2ZQVGFZUWV0VWNZandVRnVIZ3FrVDZ1TUJzSUI0YmJMdV9acUV6Zkx1VXJaU0VvMkhHZWl6QklkVGpQLU9uZEpwRjlRaGg2V0dXM0lMTFI0VGxZLW8wa2NyVWdxa1FUYW8zRDhYZERzb2FVQVJnSEVKMjVjRG1uWDZzelVIUHVqUVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNOG1vVTZLUnZtWm1Zb3BPaWUycVFORXExbW9WdVExdVNMM3dHaTBpV0tVU19HWWJNWFZDTENzYzZ1aWVxQ1BIU0x4aF9ObF9YRkZDa1QxRV9sa3NPMC0tb1Q0b2lOTHB2SGhaWmVpME5zTi1Gc3FDYl91ZUlLa0hVNE51Z0RwUjZqX0l1VTBud0RJSHhtU3hiU0VaX3V5YWR2Tzh3M2huN2VnQWFiTTdkYXJMdUVUNktBbWZWUVQ0X3lGYXZ3Xy1VcTBuWVEtVUdrSDNteDZjSUJxLWNr0gHcAUFVX3lxTE04bW9VNktSdm1abVlvcE9pZTJxUU5FcTFtb1Z1UTF1U0wzd0dpMGlXS1VU_EdZYk1YVkNMQ3NjNnVpZXFDUEhTTHhoX05sX1hGRkNrVDFFX2xrc08wLS1vVDRvaU5McHZIaFpaZWkwTnNOLUZzcUNiX3VlSUtrSFU0TnVnRHBSNmpfTUlVMG53RElIeG1TeGJTRVpfdXlhZ2JPOHczaG43ZWdBYWJNN2Rhckx1RVQ2S0FtZlZRVDRfeUZhdndfLVVxMG5ZUS1VR2tIM214NmNJQnEtY2s?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08-05-2026 08:59 UTC</t>
+          <t>08-05-2026 18:54 UTC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1808,27 +1808,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
+          <t>Why Biogen Stock Was a Winner on Wednesday</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOOWp4b2pHaFdQQTNXYWxiRE5Iekw0V05zRmJ1dlBFMDhUczYyT1g1ekxoXzdaUVlTVlZJbkdDMHhIYVRNRmY4M0dwQjF2UlRPNnB1Nms2VDRybXAtaE1IdzNYM01oUXowMHBtR0UzSGxTVGZwbjd1RFcwbnl1ZkdteEhGVQ?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>09-05-2026 07:53 UTC</t>
+          <t>08-05-2026 22:29 UTC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1840,59 +1840,59 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Infusion Therapy Market Is Going to Boom | Baxter International, B. Braun Melsungen AG, Fresenius Kabi AG</t>
+          <t>Biogen Stock Gains Despite Extended FDA Review For Alzheimer's Therapy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOSUQxSmFjRG9xUWJPSXhGMzhYVnkxNk52dXNvalRVSG1FNmVFbkRMY2FQSnBjcGZfMDRWTk9sQVN5cGppY1hDcjFVeHdFWXpaU21wWnlGTU9KdGZHOW9xMncwZXEzbl9OWE5Qa01QY2VnRk5Bdm5fTVFSZ00tMVFZQmNTckhhdzlBWE9BNi1yTXktSDV2MzkyX3Y2bE9rZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZzBhQmNrbXV3cGlBcHlnX21CdFg4QzBhUXdab25wVUZDWFBEWi16TW9hbE9WZnR5b25td0lKTGI0NWJuQ2NselhvNFN5R1Vxak9xN01kZml4SVhTUVhXckJnWWxRYzBMOElFUnlPMVBkUU1HSWFjeDE1ZS1PeldRVlZob09vcjRjRXVLRnMwY2pOa053UU9USXB6WThKOERkSUpQZmRCZ3BCTEZWTHptczRNMGxjMlNmeHc?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08-05-2026 11:31 UTC</t>
+          <t>08-05-2026 15:31 UTC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
+          <t>William Blair Maintains Biogen(BIIB.US) With Buy Rating</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>富途牛牛</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvVXRyRGZ6UnhQSVZSazU5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaFlxSTcwWTFVMlducW5URDcyRDhua2M4ekYxZGtXcEdHbEdNOE85ajJZTlBoZThQMnBpTWhFQUNyMko0SF80ZGJFUTB0M2l1RTFDcTljUTl0QzluYjBTeVFkNFdLbDExbXFJU1d6ZmRKaDNPcFAwY2V0TExJVkdQQ0tjd0dVZWJsWVloYUdrOUVrNzVUdERwXzl3?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>09-05-2026 05:06 UTC</t>
+          <t>08-05-2026 19:54 UTC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1904,27 +1904,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alvotech Earnings Call Balances Risk and Growth</t>
+          <t>Blau Farmaceutica Q1 2026 slides: 17% revenue growth, zero leverage By Investing.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPWi1XVGtENkQ1Ui1SVWxzdXlfOXpDeUJ0VmNYX1ZZN1U4Umt6ZXpYSnFmUF8tZE42SHkxOFBQVEROcVd2VFl6OGlRSmJHTDRPRmNrWThjalB4Tnp1U0xzR1luek93TFQ4c3JhMm5KSVhWQUFKeWRQV3FxOTlib2Y5QmpLbU5GbE9MYmVSOThjWVRxNTFlSXpxVmp2ZWY4ck9NY0lzUlQwcm1kM3l1X0MtNXNocUtiOWd6SmhpTg?oc=5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>09-05-2026 02:07 UTC</t>
+          <t>09-05-2026 05:28 UTC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1936,27 +1936,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
+          <t>Earnings call transcript: Blau Farmaceutica misses Q1 2026 earnings expectations By Investing.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Investing.com Australia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1NTHp4RmJRVXNtRC1nYWMwNlh5MzV1SjhWZzY2ck5VY0NTeko4MVVBWHNTcXhnZVk3NFoyX1M2NVhSbGtiTVZ5aWVmdTRZVG91Mm1qWmNfV1BjY2NJMzFwQVdFVXFwS1AzZ2FPSlkzUDB5VHphdTZCb01lc2x5RHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOMURvc3R6SWxia3IwR01FLVBUZ211TVROT2s4N2hTcmI5VW9ORTNOUWE3STNraTZac3ZMTDBKcEEyUHJsZkhiQzJOMnh5el9PQ0NDcFBwM2hmMkItSERyU1pZRk1XOXhodVRuX0dOT2RKSUtteDhyaGFlNTBTR0Z3cElZeTFIbjBseG9FcnNOR2dIdFo0ZXBfUXVDNGxPSkVXUER5ZTFUTy1KbVlfMlhhX2swMHAwN0x0VS12Z0h6VzZmLUI1Undpa21FRm5kZXFKOFUxUGpoYw?oc=5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08-05-2026 15:32 UTC</t>
+          <t>08-05-2026 21:42 UTC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1968,27 +1968,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alvotech Q1 2026 slides: revenue dips 20%, EBITDA rises on mix shift</t>
+          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Investing.com Australia</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPdmZOYlZveWVsQklZNl93RzVEeVBScF9MUnlHeUlxMlRUOE9QY2RLcE5IYmxicm5QblJYSHVsUkhpNUlJUHNEcnc5bnlpMG1vX3FNSVI4V1hJZzgyRVJJczJYVUI1c2UwOVgyVXdTaG5aQm9uS2ptY19sYTlaWmFYekxoUXpkT2Noa0FoV2dMZmlNWkV4WXlHUWZiR3FXb1I5eWFUUkNFdjAwbTJOb1Q0V1lyQWt0TXFqWUJSdXJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORmRqVGtSb1gySlNPZ0dRRk80YjBnNmt5UVRSLTNDUFBVdlZhS1RPWlgyLThtemlHQzdBQmRsdk0xU215dEwwdlRRY0R4a3FrMzU2SEVBMkl3WjVXMUtrdk5qU1IxZzlDMm9BazB3cjBoMVpEYnV5RmNyLVdGWVRiR2V2cndQUW1GdjdKRm5IbWp1dmZUWldKbFJtcUwtSUFzNlhXUVlpQkFnQURQMFJ2VlRHNVRmQndjcXhXSXZnWUFLVkFUWHJIVTY2S2pzQQ?oc=5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08-05-2026 12:20 UTC</t>
+          <t>09-05-2026 10:54 UTC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2000,64 +2000,768 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (7tUaFMHsUE)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>Fathom Journal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGoySDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE10Wm9zY09jbHdKMGJJNzR6OHZJTHN1V2FIVnZoamYxOGtLcVRmSmVYZW5vaGZzZ1RydTJTa3lacnB0STd3YW9FbURuLWduc3BPLW5yckVTM1lweEp0UGlEMURkLVNJbGttS2d4RlBib0s?oc=5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08-05-2026 19:21 UTC</t>
+          <t>09-05-2026 06:47 UTC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (5kmIsDEMbP)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fathom Journal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1WaXRZT2dtRmFuRE1fRmNEWHRTQXNocFZvWUpxNllOVWNreXBvNFl0QVBna3J4RlBndEo0bEtKaDYwQ3pleDE0VlROOEZPd1NFdWhNN3RqY1hCcVBYVm1qY0h6NVpQSmtQUHFkOTAyNUV3aExOdFE?oc=5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>09-05-2026 05:03 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Share News | Dr Reddy Share Latest News | Dr Reddy Share Latest News Today (uqC6xl9C4m)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fathom Journal</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBhQU1TRl9pS0tHYXM2SmlTRVNUVGtNdDh1cDJ5eFYtYng1V1Nfb2JoLVN4NGNaekFVX25lYXVpSlF2UURxdEFGNlNub0daS3BuTEEtVHN3RFRWR0R0d2Y0WllwaTBlNUFQSWZvWl9lc1U0bUNvT3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>08-05-2026 20:19 UTC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Natural Biocon (India) Limited Reports Net Loss of ₹4.00 Lakhs for FY26 as Revenue Declines Sharply</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPTVFVV2FrSXF3cGk5UGVkaW1JS3FTa3dCMHExdkZQQ1R3TGRUc3JoRDlad01VN2NBcENJNkFlM3BpLUtkTWEtdGNTZ0dDWFhHVXJMNnVidm1JVnQ1NUE4dFcybjBtRkc3N0hYWmIwbjR3bnRpRHZnaVA2NHdlY1FrOWlmSjFmblU4MHZzWnRubjk5VTlhSlRWLWpKOE5xb29Sdm0yX1d1Ri1IdlpaRUlIOTZqQUtwVGF1bElTbmt2eFBTMzJ5eElEbEhfdU16VGhLZmE1Rm8zOUZ6OG0wZl9GeDFqNHJtZkpH?oc=5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>09-05-2026 13:44 UTC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Biocon shifts focus to margins, capacity utilisation after expansion phase</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETPharma.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOcTVDV29rYVlZLWZmX0RQbUVaeXFQTWtwZl9nV2VGTFoyQTN5bnVzRnFhM3NVcjhuX3R0cGlDTXU2cF9JSGZQUzdxQURTdnkwalVhMWVsYThUVFNoMWRqSXp5NlFUcm4xWFdhOXI5ZDZScFpHdUxKaVotTWpWZkNLSk5qZXNPbjNEelNKSEk4S1ktb3RNYnJvOFRXVVRxY2Q0WWYwUFNzUTVlTXBoQU5pUmdPQkVfWmFmc2NlT19saW9sRk5QWTRnUElTN05rSW91dE9ZbFEtaF80dTRuNXpnVllkQUxFTUXSAecBQVVfeXFMTnE1Q1dva2FZWS1mZl9EUG1FWnlxUE1rcGZfZ1dlRkxaOFEzeW51c0ZxYTNzVXI4bl90dHBpQ011NnBfSUhmUFM3cUFEU3Z5MGpVYTFlbGE4VFNDaTFkakl6eTZRVHJuMVhXYTlyOWQ2UnBKR3VMSmlaLU1qVmZDS0pOamVzT24zRHpTSkhJOEtZLW90TWJybzhUV1VUcWNkNFlmMFBTc3E1ZU1waEFOaVJnT0JFX1phZnNjZU9fbGlvbEZOUFk0Z1BJUzdOa0lvdXRPWWxRLWhfNHU0bjV6Z1ZZZEFMRU1F?oc=5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>09-05-2026 02:46 UTC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Biocon registers net profit rise of 5% in fourth quarter at Rs 126 crore</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Deccan Herald</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNWkxaHJod2ZSSW5yMTI4dGVWRHNsRlVnQUc2RFd2eTM4S3M3VlJMM21hSnBGamNPUzRObTlUVXhRdEhweFBfWVVOLUktSk56bzdHWGZ5cG1ENXlQc1E4NGxPd2QybENHUkY4eHZrZXF0MTltRnpLTXFEZHEyRHN5WHZOX0lUdE1tSlVpU0hDSDBHRlo5RFFfd0NoNk0tTnVpZ3otOWhmMDNZMkZvci1rYW5ONXBnSDZXS0JER3IwWjVqNUVDNVE?oc=5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>08-05-2026 19:21 UTC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Biocon Ka Profit 74% Gira! Ab Margins Par Full Dhyan, Naye Drug Ki Umeed</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Whalesbook</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOWmVwaVVDaThRbGZhMElYc3J6OTNxQnZxYzgwV25CdzNXSTZsS3dzdUp6ak5yYTg0U2hyWlAtQ3pBYjRFMHBhMDVlNEdOS2pCVUtGRjhpVXkzOG9hbVdqeFZiN3phZUdPX3puQ0JlV1dGa0FkcUhpbVhPZkxRN2RkaHA1eFZweHRubmRYNkw0S18zZWRMNVhZTElNY3Z0RG5WOWdCVTdZV3lzSlVCUEZWRC1QN1diTkZ4VGVzQTVyYjlSLUJ0MmlQc0RFVmJaRFhYUkhTYkJHUTUxQllUNzc1Mw?oc=5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>08-05-2026 18:06 UTC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Claire has what it takes to lead Biocon forward: Kiran Mazumdar-Shaw</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QdIB2gFBVV95cUxPbjBFVFhlWmZYd1A0a3doeWtOVFBHYS05Tm9BbEw4WnRHU2tDYnVndEEtc3I5R2hqbms3UG5kcmJmR19oZFFDcGpka1NncXdmZFQtYVRVc2pMek1LYU9yUjU0ZWtiR1M5QWw5WXVuSThTQlg4ZHRuZjdscFJOVTg3V1duMGhZcDRvOVAxdW54d2ZzTC1yWVFmS0d1ZGU4ei1oWWlvR1B4NFBpX0lnSzZqVzhYbzFTLW96ci1SNEc0b19tczhEMFlyb1Jpb2JDaURTVEdJc0RTVHE5QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>08-05-2026 18:15 UTC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Arm Apitoria Pharma CEO Dr Sanjay Chaturvedi Resigns</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Medical Dialogues</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSUxfV2YzSVRsd0xLNDBPVU9GSUdsSDZUWmlaUDRsYWFSXzZ2M1BQZi1Bc0VRY1h2UjVKVWZ0WjZmR1BKX3FuZWF6bnFXNUs5NzgxUVNQY0pmbXVTdERZSVptZG5QbGxoQlhfdDVqMXBtb0FLc1dWQUdoNng1YWJTbXpLQ09RMkJGYnVpR3V0WnRJUmZ1amNOVEVPOExTeTduTTd0Y2Z0T2RUcURta2VJdWo0QzhtbjdQbE5LS1FaYlRyZzjSAcgBQVVfeXFMT2lVX3Y2UUQyNTNqZW1zY3pyS2ozM2JldnhuaTN0SEJuaEVocU54ODJ4X3FqV1I3c0FSU1dqZXF1MERoejBGY0dJUU9vRlAzQ0xjem42MTFLZC1WSjBWdW9Tbm9yNUdmX3JCODlNWnAxR0U1X056dTZvbnNJMHlLR0dRMlFwZ2V6T3VwPDRCM0lZV3lOcldDQXNiRGZBcGF4Vm92R3RFSERyazByTy1zRTRSbHM1S2tkdnVaSHVMWEY5bWt2OHRMcE4?oc=5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>09-05-2026 11:10 UTC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Completes Buyback of 54,23,728 Equity Shares at ₹1,475 Per Share for ₹800 Crore</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOQThLZTY2aURBa3lTV3UzUkFaTzNpYlRSTWx6VTNsS3pPeXFXWmF0VFBrazdwWUFIdENVRVJ0X1F4cVgyM0dXd28xb0hFY0c3MW8zdDJSVTRTOVdVaDN6N3dXbk9wcHZtNy1jMDBKOFNoWFZFX1g4RzlVX0ZwWkJsSEpVOGxuSzV2SVFRWnMzZi00YjltY1lhelAxQTZJNk5hbHFvRVhtNHpkX01BWE5zRWYySDZyVU1Kc1dxTmx2eGQ5ZFdHZklmMjg5M3c1UDBkQmM5LTdyakRrSWRFVXBKeDlWNkY1Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>08-05-2026 16:42 UTC</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>📈 Aurobindo Pharma Zooms After Getting EIR for Telangana Unit</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>indiaherald.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOY1pWODB2QkdCX3EwV1dsS2M3VTBDT0V3NGVqRllLbDNYM0JqaUlTUXZmZFpzWnVmMVJRY19CcVdhX2owcldYVDFsUWNoajZRaENvXzk3dDlBaWtUdGh5TEVwZjdsaTdNY3Z6RlprbmhlQ1BzaEw2UHN5cy1fclMyalVXTmZzNm9YMUZOcWdrY0ZvempuZnJXeWZLSEV0UkF5R19jN0xRZzU2ZXpIUTFB?oc=5</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>09-05-2026 06:04 UTC</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IndiaWest</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>08-05-2026 18:14 UTC</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Torrent Emerges Early Leader in India's Generic Semaglutide Race with 38% Market Share: Report</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Medical Dialogues</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UdIB5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>09-05-2026 11:53 UTC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Celltrion Inc stock (KR7068270008): Buyback wraps up as Q1 profit soars on high-margin drugs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQRDNjQ2pBOWE2SGVwTHlLcjlKclYyUDRrNGRlbXdpdExOelIxdWNZY1RpVUMxMGFpcFpVS2xYSXJIcWUydmlMZG0zVUg5RHRsZld3dng0THgyZk02OC1reDRwSFd3QTVzdTdIRlloUTFhMmhwZUY2dnFGbmZqaVNxaFg0dVdrNUhvMzhRRDRaYWVZRHkyUEUtMWdSU0RXY2kwa3lHTGVVb2pXU1liYWZPNExMd0MxZzFSdFR5YjAzc05qYzFnQmhFLS1n?oc=5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>09-05-2026 07:21 UTC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Prestige Biopharma</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>OneSource Pharma Stock: GLP-1 Ka Gold Rush Ya Valuation Ka Trap?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Whalesbook</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPc3BoaWg4SUtEbXlyLVhGUkdiMkVNX0JfblJyYS0xT1FsZjZ0cHlLUmhzbURTYmJUUHJpQ3BNRkF1WllOLUQ0QnV6QllzcUJVbjBaN0szTzBkcWtzU0ZuY0ZLX0RlYlJJT1BGMDM3akd6cGpqbTJVWmhiNkhlOWJfbU9HSnhNQ25LRFQ3ZHBFX2lwekIyU1QySk9qc1ZjeUlTV2lSbHRRcml4QktIVUt5bGtyWU5DU2JBTVljNzhxV1VXTEg0QjVENE9BeU5INk94bEhfMTdoTmdxR1ox?oc=5</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>09-05-2026 02:29 UTC</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo takes $610M hit tied to ADC manufacturing losses</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fierce Pharma</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdGY5SFBfV1hyN0R1TUxMdkp3a3RJS1VXM1Vzal94YldVMUQ0SzZrdzVzZ21JODdpRnBjODY0OXlSLS05TzlkS3A5VVk1MFp6SW1NU2VzdGhGcDJpSUNiNUQ4SUluT0JfMUdKQUttRzhQRXVOeWZDWVEyN09UTDh0UkpxbWtOWGd3UzA3VjNMekZCNFpQSlpPR0VGV2I0NEpkSTJmaDdaRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>08-05-2026 14:47 UTC</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dong A ST - Meiji Seika</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BTgen expands global CMO push, boosts capacity and eyes Korea IPO - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQczhRTUYwVV9nOW1zZjhSbHFVQjNsU1IycmdoVWlXelNlb2pxcEw2b195UmxMcEQtdzdWeW1INnlGckZQLXh4M3JGZjJYODUweFV1RFdBRFN2ZWJweDVSdlFRWHM2Z2N6MGMzclc1LTNtYi1aR1Jpd3NjQnVUZ1B1YtIBlAFBVV95cUxNUHgtczd2N1pkUWVKcWZKNEFyNmdnaVZDYjhQMlp5aUU5SnZ5YjlVLXVnUmQ0bmxuQW1rRXRYVUQzdnFsY2hxemRMZTNYbUs3ejgwNVpSdWlPZ3VPQXBvVW12RUJIbktkRGdDeVZRX1pJZUZob0pFOEF6Tm9ES1RjQ25CN2ozaGZrZGJyR1lCdXZJLUtl?oc=5</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08-05-2026 22:08 UTC</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Healthcare group reports Q1 2026 results and confirms</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQemRza0Z6SFdmSlhmRl9jbmdzZ2VTdHNJcDFKLUloSDlEblE0TnhyMzJ4STdLeGZJNzdlb25IWHNSV2szRlFmTlVRQzZjZVYwVWlJbkZ2ZHluLTZCLUNWLWFKNTNqZ2lqSVJIQ3E1QzkyWDBjOUYxaUd4VzQ2LTZRaFpNUzVwQ1JrRDBJdXg1c3RQVE5ZM0NtUHpUc3BvM2dNMHk2WERVVkU0N0t3ZGlFYlB5ZENYZEJnU3J1LUZzSFhKRjJ3S3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>09-05-2026 07:53 UTC</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FRE.SW Stock Plunges 31.8% in Pre-Market Trading on May 9</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Meyka</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPenRpTHVPa21IVmtsYm1HajV4QTVXaFBBWml3NmhiTElIcm51LThhSEJXWm5RenM0U0ZQQmRFSjBZUkJEZEMyWWVGdmdtV0liZXJNSElvQm5Wc1lNZ3JmME12WnV2cFMxaGlROGdNcXBwZ1JpVjk2b2U4RDhBY2tMYklRaVF5bFAtdF84?oc=5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>09-05-2026 01:15 UTC</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mississippi to receive $41 million from settlement with defunct pharmaceutical company</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SuperTalk Mississippi Media</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNM01xSlowWWlzYmpXLXFNZ2tnN3FLMTd2enhRcktmS2pfc3dEc3Z2UF9tUmYyWFYwb08tcHgyMmQtYXQ4T1JBOWNJNjFGRjRxYmI1VTlXOXVERXpoNXhpQ084V2hkTmRRSHFOeWZJXzdmTkxvX293WEV1U1Zlc3JPQ2hzVDJrU24zZldJUUsxc3RaM2M4Q2hXVFdYVU9CZUJmZjFVSFNNVXpZMnlXWFl0cg?oc=5</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>08-05-2026 15:40 UTC</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A Look At Alvotech (NasdaqGM:ALVO) Valuation After Weak Q1 2026 Results And Biosimilar Pipeline Updates</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQMHdvT3dNRE92aWp1MmgzSks2Zm4zbU5VemhvYnJ4S2s2aWhCX19lc25BTXlZdGpFSVBrckJDRjdoWTFyRS1XdFdZSVlvOEl3YU1nUGluRVpiTDlQTHRWZWhuSkEtQ0pVQWlIQkxlQjFjMmFFVWhPS0xsSkcyNWNVMk9rRTRxRG9mVUgwZFlXRFYxNkhJNVdDR2Vvd0Rzb1htZnJjVkh2RXVzWjNUQlFNZ2Nib2FWcXVPUjdzWEF5aENHNm54dWlsVzlvU3RyRGZ6UnhQSVZSazU5Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>09-05-2026 05:06 UTC</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alvotech Earnings Call Balances Risk and Growth</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzBGaFlLOG1RZkFIOWRBYnd3M0tDTUU5dXZLWGU2LVBrR2hGaVBHcnFGTV9SYzdwWkVxeGlfenVwcDUyQUlpSnRxTldnREpIRTlpSl90ZEtGZmZ5dG55V2FGMXBaVW9XWE94NGxRN1dLTFZDNFdtVU1Hc1lUVFdyX2JONzBQWnQtLTc2a3NvdkdNT2V1Q2QxQ2RhenJiOHo1?oc=5</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>09-05-2026 02:07 UTC</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Alvotech (ALVO) Q1 2026 Earnings Transcript</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9jMjdOT3hjWFdlSjAyLWhDSDM3aUtIUEp6R0ZWOTY5SXZ3Snl3TGh4dDYxVEtEV290a2FEMllPMVJWVmRYNFBjV1BIMG9rV1NtVGVCbUhTbG44V2hpNDRoNkpOTU1yY3plbTFOVHZybU9sMEVMbVF4ajFHa2Z0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>08-05-2026 15:32 UTC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>How Teva (TEVA) revenue breaks down and what it means (Near Lows) 2026-05-08 - Verified Stock Signals</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>newser.com</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeTMxM19VWXRKbS1yTkdvajFEOWRxYWRYejNmdlZudVhCb0FlMGNzanZyUTgxdzNJM2ZCcWM0UjR6MHVXYzlVbGRvZzhqb24xWHdqOUQtc0N5bmhkQnNGaE9HOGFDY0x3dXE2aDRYTjZHWkFPS1ExblduYkQwcjlLcnIxc2hjQWpZanAwdmpiRzUyc3ZpVG1SM0JDNWtIWnpyZHdYTG91dHJIMzFIb3VLSmhqNjV5S2c?oc=5</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>08-05-2026 08:43 UTC</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Financial</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sciatica Treatment Market Expands Across North America &amp; Asia-Pacific | Pfizer, Novartis, Teva</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPcDVHRk9TcGo2SDRsUG81c3hEd2hydVI3ekhNWmo4al9FOG5fTDNzWFJWQkdVOHNZRVJMb1h4UWFOM3RjT1FsUGhnX1gwVGVhZXp4TEpYUHdSTUJpUWJGX2JBdVNlR1VRRnFBc0lGWEU0VzlIb2g5dmhtREJfekFOWTF0c1p0OXpLbC1sNzhmRmJWWkR1?oc=5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>08-05-2026 19:21 UTC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2789,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09-05-2026 13:58:42</t>
+          <t>09-05-2026 20:15:26</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,534 +469,534 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antibiotics: Europe at risk with fragile supplies and heavy dependence on Asia</t>
+          <t>Harmony Biosciences Expands Patent Protection for Sleep Medicine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Il Sole 24 ORE</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOeXVQZFVhWHY3Uy1hQkNvX3JxdW5FLUEtVklxMUNnRTNNSlZ5UVRrSHFNRGdScUV2ZnpoMzNDM1g5T0FQVlpseE5idW9Ccy10TWxvTUhXSDJVZU9KU205STNNT1Rvek8tTGZWVjFObnkzQk0zWUlFTDhnYk4yblpnOWljeS1oMF9zZjFscUd0ekdqenpGZkNXeE1iclAzS2JxZ0tSaldIRzcyS20xLWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMV9FT2NJdFVXREZfV19HNUxYM0lxeXFoeVRMR0tnNWpMczVheVFmdF9wNWtEVUhvWk0wbVA3NTdFcXFJMHMwUGZQcFdqWkV1Q1RhY1ZPQTlheWhmNzFVVnZFQTlKQ2JqR0hYZW9aVWxKcmNEcFl1VzhtazVJVUVfSA?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09-05-2026 14:50 UTC</t>
+          <t>10-05-2026 02:59 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): Biosimilar developer eyes growth amid new launches and partnership</t>
+          <t>VIDEO: Bevy of psoriasis data at AAD 2026 promises more to come</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Healio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbnV3UzQzWDB4ZnUxSUtkaXVQQ1Zrd3FwQ1IyY25FZldEWFVKbnEwblB6WEFVVHppUDlYR0tjWHlMeUxZeV9FYVgzWVpSdTl4LUFWQS16TWVfRElDV2RacGdka3dNR2NtT0tMMDVxOGJmeDYyc0VtQUUtOF9fcWNLUEJZbzNHaXM0NFd0VVo3cFU0c0F3X0hpdGMwNEU4NjhSTUJBNDNXU0NYa0ZsdnRHY24yUW9INXZGWkFleFFscnhkcFNUNkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPSHk3UEkxRkh0dFp5VWppQVFRaHJKSkZfRG5fYnB5czJXN0I4dU95MlNqUkdQTm1XSUh3WmxIbnNVcW0xSjI5T3d5U0VTZG9vdUk1WUd6Q2NOT3dJdGs3V1Q3ZTZSUUNmMkRLV1J2OFltU2RUc3FyOUNPemlsckp6am16LTNZdldyNFhZdlpMNDhoaXd0LWNvSTJQazE1cVc2VFVxTm81NlVGZWZaRi0zRw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09-05-2026 14:08 UTC</t>
+          <t>10-05-2026 12:43 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Richter Gedeon Nyrt. stock (HU0000123096): Shares rise on strong quarterly performance and dividend</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPcXB6eUswMWowQVB3QkMzLXJBYnFuNkJzMW5xaVp3dlBKcWdnVGdvQXFJdDQtYVlIbHdmM3NYaUtjLXc2X1U0UDl1cFB3SG50Z3dCMEdxNXMxMXZaU3dwX21jcU5NQWVmUTFIYVpzandrUWZLb2lmV0RXUFoyRDl0bnNYNXU0ZU9uS014dmppWnozLXhUa19TVmlCa3dZclBoek5nRWpEb1drYnRldkdBOHZJUUg0WjFSekZyNF9CZFZnWTBkZE1Saw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-05-2026 08:02 UTC</t>
+          <t>09-05-2026 23:01 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>World Ruminant Vaccines - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Amgen’s Real Time FDA Trial Pilot Puts Oncology Execution In Focus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQQ1hsc2F6TlRnV3oydWZzVmdYc2hjWE5HWDZ0dUJJX2NiNGNxOEVwQTJKSWZWcmJhZVJwTzhkek1sZi02TzFhOHBYWHRxaFBXdDZzY1NGSnNJZk11QmtkM0hxNm1GMGh6bWtlelhUNzlFOWY1TUJpdHdreEQtMlI0QWRNelpqVklsRmlJUkRqVktPWHVwTURFSWZCSzlyZUotQzNYbEowSUkwWm4zdlRyQmRESktWRmtCaEROYlpkTG5KR1BDLVNaYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPVnRLUzdjbDhzMVJKcVJLLXFlM0RaaGFra2JvVllMYnZtb2lsdkE5bUFDT1hjTUtRY0YxaW96bWZONmc4RWVrQUNPUlFZR3pkbEVIbXBaN3FfZU0yTlRieGc0bnJ3dFF6WVV0M0tySXh6cWZFVmZ5bjI1SDBqa0M1MTFFLTA1bnVMNjdQN0wzZjg2T0FEcUg5UlBR?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09-05-2026 16:16 UTC</t>
+          <t>10-05-2026 14:09 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How Germany is tackling a €40 billion drug shortage</t>
+          <t>Inside Amgen’s Next-Generation Labs: Powering Faster, Smarter Small Molecule Drug Discovery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>logos-pres.md</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQY0VxZHRPQlFsWm15NktCQTFNa3RMOXlBMnhuNHRkV0VBbEdYeEVhOGdSY0IySFVBN1FJNVJkTDBWQ0JSWU01T085TE9mSl96M2VHUVBGTEtNS0EyWTlkWm9feDhCenE4aTZaX21ycTh0ZWppRi1WZm5qMkpmNHdLSG91QzZubElfekE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTWxMdmxiLUhRT3lrMWRmWDByeE9vU0J2UmYwSVE3cGV5eXR5dWJmZ1phUkJnaG91WE5RaXlkWjJodHA2X0xRRlhxLWNPd0V5eWRfcERIb1hJd29PX3NnaWMtaVo3Q1QzVEZiZW5vV19JRW5rbDd6V2UzaE9FTUZGbGxvdXFZY3JNS1ZVa2Y0d0EySXRRd2lLYlpqelBELXRmQnItSXAyN2s2aDd5ZlRZVlEyeF93R3ozRlltemdFc2l1WDlH?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09-05-2026 18:44 UTC</t>
+          <t>09-05-2026 22:09 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Business Viewpoint Magazine</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnR0hjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09-05-2026 23:01 UTC</t>
+          <t>10-05-2026 06:07 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Amgen Q1 2026 beats EPS forecast, stock dips</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNTkYtdUZIUmhVb3N1RUdGU3loOUp4VDBTeG5nR0s2dEhlUlFXb0Q0ZjBtU1Q0N0VSNjVnTllQdzR0d0k1UEVSczE1NE0tdENuZHlWc1RMazRoV1Y4LXVyZGwxa2JyWUhkYTBFdE1BTFJ3Nk9pVm1rLWxmNjdlWUh4Q0hxdWl2WWpjeHJxQ19mS3ZodUdERTc5d1lRdGRpYm5KS2V0eU5BSGZZcDZBVjZNZHhZcWRqVEdaa1dIQ2NUVmpUYzRRNGF3SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09-05-2026 15:12 UTC</t>
+          <t>10-05-2026 10:38 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inside Amgen’s Next-Generation Labs: Powering Faster, Smarter Small Molecule Drug Discovery</t>
+          <t>Bust Fake News With Bangalore Mirror: Hantavirus infection is not a confirmed side effect of Pfizer’s CO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Bangalore Mirror</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTWxMdmxiLUhRT3lrMWRmWDByeE9vU0J2UmYwSVE3cGV5eXR5dWJmZ1phUkJnaG91WE5RaXlkWjJodHA2X0xRRlhxLWNPd0V5eWRfcERIb1hJd29PX3NnaWMtaVo3Q1QzVEZiZW5vV19JRW5rbDd6V2UzaE9FTUZGbGxvdXFZY3JNS1ZVa2Y0d0EySXRRd2lLYlpqelBELXRmQnItSXAyN2s2aDd5ZlRZVlEyeF93R3ozRlltemdFc2l1WDlH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxOX3hraFZBVmo5ZDFWUzhObVdYQWlPRGQ3NnBrampUQUpWdXBXN2I0WHZHY01WUHMxV3g5dkliaTlyN0Vsd3J0WXpBeXY0Nm5yZ05MQVk5WUdFMXhKYVFlSVZKcVdlUjd4N0VpeUxpWUZIRXM5czByVHNPQUgzMWczeWQzWW9USGVyLWQtaW5fbTkzd3NrYUJBTjRyaGtTblAxQnlreXFNOUdlb1ZmbnNYMWJOOWVXTlNFYUk3dk9QWERVbkQ5ZW1aTElna2g2X3JOdUpxRUM0bWdPb0d4am9rLWx2LVFqVjRVaTBSdHB0UGhnWFpqWWdMckJzR3JXSEJTeVJZVFVBVmJ6QVl6clRTOGR5dUVSdTNSdEFSS09BdmlCQXc00gGqAkFVX3lxTFB3MmxMamJIWF9fUG5IbmxRajBnUUREa2J4LXVFWUVZbjV0RGo0NnBjWmZxWTMtMW1tMDlUNDN3aEE2R2w5Z2RiNUN4MWlTZWdqbng1dFBENlY5THJubnctMjNSQ2x3d3VuNlNOOERnbHRSTktMMmdpREp5VU5yY0NNVGM5cDF5OGZFUnZIVHlaTW5vTWp1aGVmM2p0VllFRE9PZ0R3bS00WGltdEtCNmpENTdjMWNKTUhMZTAwOElLc0Nnb2dQM1VqMzV3eWUxTm51blFqNlV0WXVlQ2JPWUR5TGNYOE9UeWp3OUlrbXBpY25pZkdxM0VQSGR4emU1NWFPRDRQa1U4Yi1jQ3dDWF9NSDlRX2tfZUo2RF9FaHU3cW1yeXdoem5QalE?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>09-05-2026 22:09 UTC</t>
+          <t>10-05-2026 00:30 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Biotech giant eyes growth amid patent cliffs and pipeline bets</t>
+          <t>Apellis set to report earnings ahead of Biogen deal closes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPS0VvTzJmZm9WYUY1YUVrcnJXdmtldlNEbGw1UmJEZWkyRkRVOXlFb3FDbmV5YXl6dnRhajJUTFB5Q2dybEVIaEFDaVhZakQxOG1jaXRSRF93cGdHSkItTlV3b2Y1b1IxSkdPZVFONEpQSUxLN3VJNTFFZVpBSGd0dDluOUotRHcwb0RQbmg4UW9KTk12WFZWNjJKNWZfdDhQZmJHV1VaTHBJcmNDbk41UnlFdUYtd2EzUkdlUzdDZUNNQzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQNVhaSFZCMFV4bVpZdTA2VEdLM3JlZkQ3anRaWDZPQnE3aUhNTmc5Uy1DM0xxSU55YWZNZzhBTGZvMUZjNmU0YUxOY0FnbEo4MjVDMFVkMFZmS0FKQThRY3c2VGZFeS0yQ2d6aVJ4ZDB2QTNQdzIyY0FvMmI1REhrYjF5M3hycW91N1BDeDU5TTV6b1I3dU11RzFLemJ1S0VsVUhjQkFYd1lIaGtiVUU4?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09-05-2026 11:08 UTC</t>
+          <t>10-05-2026 13:41 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Q1 2026 slides: six growth drivers fuel 24% expansion By Investing.com</t>
+          <t>Biogen: FDA Delay on Subcutaneous Lecanemab Seen as Timing Issue; Hold Rating Reiterated with Unchanged $203 Price Target</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Investing.com Nigeria</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWUJYTzdTb29ibWd0ZklYUFpzcS1RVng2YlRLQ0hYdzFaQ3NtZ3Z5RnJNTXZNVkhLQjJNeEptNEN4Y0JLbzA5SFVaWjRZNng2LUlWSUYxbVMxUFRTX09EN21ydGtuRUtUM0pOWFVrY1ZoSFpIN3lYME1BckdKYVpBd3pKWlAwSk4ycGliSEc1YnJQVWVEWjhzaEtKVExFYVhOd2NaTHBkY3JHRk13RUtteFgwMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQzNsenViTVBUb05nZXBHNHVsNEc2cDNLOHZocFV6V1pJaEE2aG8wYV9oRTQzYnhpZk4xNEJ4bExUS2x3Y1ZmNklKVFRtbWVSRWFEZHJkMFoyaUZkOVZIcWlRSGZRMVp2RkhlRTNkS040b2RxaTk2Ym1OVUVWTEdUTXpRSkVfeENkQmFfZnBTY2lyZFlzR2RfM0Y1Mk9HQzRIUFpJbHpmMWI5b2FwVllrYzAtc3FNcXpfNTZ4QVNHZWVyQ1lnbjl1MGNVSHM4Q0hBeTZlTGlXS3J1SmFYQ3VKamgyQXd5ZnFxTmVhVkJjcG5QTURLOGxsM1U0NDZZUQ?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09-05-2026 21:27 UTC</t>
+          <t>10-05-2026 13:39 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Inc. $AMGN Shares Acquired by Wesbanco Bank Inc.</t>
+          <t>Milestone in the fight against ALS: new treatment makes patients better</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPUjNOZ25oNFdGMTc2Y29HNlRuXzdyVk1HRVVRb0p2Rnh1Q0R2TTF6TkR4Z01BQTBTeEp5WWVMN2pJRkV1WjM1TGY1NDhhdUpIUzIyVHdBb0F1N3I3clJVRVpmQnpKSTB6bnhaRlpuVVQ4SVk5OUNhSXdNWWl4bEdoS2dQLVhRclBGOEI5NkJNS0tVLWxNVVQwTmNKaVR1N19kV3puWktmQTAxaDBMeV9rV1F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQWZhckp5UngzZWI0aFZ0dkI3NTlncjNYQW5Uajc3WVpBUDNjdXJFc1o0d0kzZloyUjczUExjYzVoZGpwc1h3a0FxdnBnZkFxZjJiVzRQWC1TN25RcFQtQTV5Zlk2S2YtMDZGbldGMjhkbmNLUXhrbE9VSWJEWmRVbF94cjR6SkZ0VTRpdXloUHRLRjdUQm1aNG5rdHdJLURPMzA4N05vZmdVdjRsaFE?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09-05-2026 12:05 UTC</t>
+          <t>09-05-2026 14:45 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): U.S. manufacturing push and Q1 2026 results in focus</t>
+          <t>China Cancer Drugs Cut India Prices, Disrupting Western Pharma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNTjlvSWVSZENTSEk4VzJRdXpQLWNLU3NWcWN0WmY0cGpCSi0zOWIzcmRnM3gyZUQzSmsyQXhteU5Vd3B0SGdFa2Q4RTI5dmFBRnlDVnVuZHRjRDFCRC1EOGQ5Ul91Nll0SVlqcFZBbjdhMVRGX25MNURIaERtWnlaTHhEZGdqU2lvY0hNSko5dTVVNXJJVUFWZVFKVi0wWkRSb1pRdk1BRS1hN3F1blJnOV9sdnVNaVZNaWZRd3pROA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQMzBud1hCLVNfQ3YxTnRIY295dUNBaWFkWTlvOHdub3RnMjRIU2tFY2pIaWFLdDhqYVNjVHp5WEF3aF90c0F0QmN2Ykk4cUtVOW5nODkwVDRXemEtdEFJV1l6TVMyeUVQMHlxT050ak9vekhERVhZTFdyQnNCbEdCSS11WlBNV1dfVEMxbnNSYWRTWGdxZGVtMU40UFQ5bjJldldRZE1NUTRXWmpBR2dRRlBseHNhSnVudW1rSkRFRlY5RGUxTXEzWnIxOG94QjRzWWVnclBPMXU5TFdK?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09-05-2026 13:49 UTC</t>
+          <t>10-05-2026 03:45 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
+          <t>Chinese medicines bring relief to India’s cancer patients</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business Viewpoint Magazine</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOWXBQTEIxejVickl5NDBCbVgtcjc3Mmh5a29OU3hIWFhOQWUwbmJvcEltbjMwd0ZKWTN0RS1xNkg5RHR0N2pIWGE0UmZ6UVh2VXpsZjZlaXRFcV85Z3VuWHNSNjB0SkFIUkEzNllpRzk5MVhXU1BWcTFRcWZWbU5iMWtZc0ZNNGFSMUI0YkZEWDNsMV8xc0NlakdlYURYY09XSGd6b3J5TGU1Uk1oYVNMbkJnNUdnTl8yYXVhTVB3QUx0WVlyaG9qMXFrUdIB0AFBVV95cUxNal9kUmxTX0FLMmlNYVJmUFRZLUdRZE9ZbDRjQ0gyT0d4UFB3WWJPTHJfNmFFZTk2a3RMU2t2YllKS1FSQ1BuZURyWFlZUHQ4SWRETGRlVFgyblRVZG5aWU5wdDJGNDZFMVhRU2ZKenh1eVQ2N0o0UldXSE1RTTlVdmt5YURFVGsyOUVMUm5rWkJlSzNnbWZBbjFvSkVjZnRkWVZvSkl6d09CMXJnTzNYZFM1OEZ6SFEzeXEzbW9scUU5c2ZCd3pYQjFKMmtZaGx3?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-05-2026 06:07 UTC</t>
+          <t>10-05-2026 07:42 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What Pfizer (PFE)'s Earnings Beat, Reaffirmed Guidance and Oncology Wins Mean For Shareholders</t>
+          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQVXBhbDZyN0ZnYzZaRWpKdU80bHhNejNKbm5Fd2JSZ1VQUVZxdk5Oc0hQYkpiOVpxdzB5ajkwemdZWXRhUWZURXhSeWRkQ3RMTUhTY25oc2ZiNlc5Y1B1WDB3TDd4V1dlb3gyV0RXTEpsdS1EZHZmeHhKWFI2aldhUGlCclhlY2RmV2ZFZGZGZ0x0cTdRM1BONGVTVmkzSGZCb3JYZUlsR0tmSk5tQl9ta05tN2s5QU5LQU5La3JGWG5mT0dJVGs2aXU0VWJlZnNidTNV0gHYAUFVX3lxTE1Kbk5UYk5BNXdwZi0tUkZ5ei1abXE2bmJETEtZdmMwc3FQdzlGS3ZrNmoxZGVmTEJEeGx3aV9zZlljYVZNYzc1V196N2tlLUlQLVlXNGg2MERQNFJodHE0T2dZTjZ1YV9tNy14X192WU9kNEVuY0pNVnlUaWFKV293d1IwcnZnOEd1OWJHVDl4UFpjYmJ0WW04cWs4QUVoa0ZyYmFpbVIxckN1amI5dXdDbE0tOUQ2RlNueDNSbHNRMWRPMDVGOG5feHRydmZ3SERYNGhjWmt1aQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbjhFM3pYdVEtUUJkTklzcHZrR0U0MmhnbTlYTkZLYUVHX1NQOG45TW9qWkE0S0VmbFFKUUhOcmJ1Zw?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10-05-2026 02:42 UTC</t>
+          <t>10-05-2026 05:00 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bust Fake News With Bangalore Mirror: Hantavirus infection is not a confirmed side effect of Pfizer’s CO</t>
+          <t>Xbrane and Intas Revise Financing Terms for Opdivo Biosimilar Xdivane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bangalore Mirror</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAJBVV95cUxOX3hraFZBVmo5ZDFWUzhObVdYQWlPRGQ3NnBrampUQUpWdXBXN2I0WHZHY01WUHMxV3g5dkliaTlyN0Vsd3J0WXpBeXY0Nm5yZ05MQVk5WUdFMXhKYVFlSVZKcVdlUjd4N0VpeUxpWUZIRXM5czByVHNPQUgzMWczeWQzWW9USGVyLWQtaW5fbTkzd3NrYUJBTjRyaGtTblAxQnlreXFNOUdlb1ZmbnNYMWJOOWVXTlNFYUk3dk9QWERVbkQ5ZW1aTElna2g2X3JOdUpxRUM0bWdPb0d4am9rLWx2LVFqVjRVaTBSdHB0UGhnWFpqWWdMckJzR3JXSEJTeVJZVFVBVmJ6QVl6clRTOGR5dUVSdTNSdEFSS09BdmlCQXc00gGqAkFVX3lxTFB3MmxMamJIWF9fUG5IbmxRamtnUUREa2J4LXVFWUVZbjV0RGo0NnBjWmZxWTMtMW1tMDlUNDN3aEE2R2w5Z2RiNUN4MWlTZWdqZnhPNFA2VjNSLVJsYU5SOXBYWWxMbnN4T0k5MC1Hek13YnRKUHZkeENtS2UyaGxvQV9jUUpZMTVhUlpVYUowaUIwbzZkQXdVMDdSWDVWVjczX2NOZFBoNzNUc0hMb0NFQmRtU1RleXQxWmlvbEowbTF1VVdQSzRaUHNMbGhDWklYOF80T2FpamtmRVFCb2Rodjl0WFFEd0Y2OC15QTRKMVdLVHpIM05NanREVlha?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZGJqb0dfeG5Db2NCV2JiYXcweFpDWTA4Z3dMYVJPZHlCbDZjNVZXUWFXdHd3Zi0yTlJjczduRUxnaVM2aUFxb0ljbHdCS3BVRmpEYVMzWVZybnJ5RkRfWWJDVVJlM2FYTi1ibHZZcjVsVGcyZTFXOFZJUlRnZzRjSUtaTmR0cGRQRTVMV094QkFxM19ybHlZQmg1aE5ITzNISnllMDFNVWVtd0dUbmNObEU5VlhTb0JHdlo1T3ZR?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10-05-2026 00:30 UTC</t>
+          <t>10-05-2026 03:58 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Beats EPS Estimates, Reaffirms Full-Year Outlook</t>
+          <t>Fortune India Exclusive: Succession and the road ahead at Biocon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNRlRlcFYybUFZNVlVS0FxWUVNYjNZNEEwRjhyUDQ5WnB3Tk5NZlM1Rk4wYVRHVm0yVkp4dGhyRkxiZHhkVVU1bFo0UlhYcG9pY0tqY21VaVJRZmQzMC0wMkdXRjNJUVQ4b1JzT0NJbWc4VjVjcEZqcDJQcWlGSU9vbHF4eW9pOFBNNEZPakZuTGJacDJjX0ExTXdBUUpNbXhqdDVzTm1jZ0J1dWU5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPRTlHcXBUT1JqU0phNS1seDRSVnRxYzFHUVFSUTNPb1RyX1JrY001aGkwWU5zOTZLdWdYZXhUNG03azRkM2ZRQUdBVXk0Nzl2RlVlem1uTTdMNUxtc0RVaHlrTmlnc2w2b1F2Ui1FQzRWc191cHljMkprRDNtelREWG15aUlTTmFpWk5xMzVPc9IBnAFBVV95cUxQTHIyWWc3cnBxVGRSUEJlWUdUUnpfY0J4MHBZTkduWnNqdFItYmdGclBjYTMwanN0ZUpXRWJpMndxb2dESElkWGJjR3FtcnpJX1k3X3lURnZraHQwaVRSbktOV19mM2JRVUxlbmJMLWVUOXZQX1NVd2MzdnJSWi1Fb3cwU3ZYYVN6WG94SzV6anlIY3E5WGxtWmthYWI?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10-05-2026 01:02 UTC</t>
+          <t>10-05-2026 09:09 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
+          <t>From a garage venture to an industry bellwether: Biocon under Kiran Shaw</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDVadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNWDlmQVhxLVUzak81SmJXWWFrTjdaVnIxM0NsNU9weUMxVUJYNkpPRWt6S1JoX0lvQ2ZVTWp3Q1N5N3lOejJreU44OWdlRkRUN1hqdnpqMW5DTWxRMEZRSzBVWi1DZVlaMjJSRkpTQzdZUVdVU1JaSlZ1NTRVVUR3TnJEc0Z4dVRqcENKRFZoQWVTNmFyenYwbXhoazNVd0JteHlLZTFXcC1TNGluaGRPclRvX3c0S25OcG5rQ09neUFfeFA3VXJTWS1B0gHKAUFVX3lxTE1YOWZBWHEtVTNqTzVKYldZYWtON1pWcjEzQ2w1T3B5QzFVQlg2Sk9Fa3pLUmhfSW9DZlVNandDU3k3eU56Mmt5Tjg5Z2VGRFQ3WGp2emoxbkNNbFEwRlFLMFVaLUNlWVoyMlJGSlNDN1lRV1VTUlpKVnU1NFVVRHdOckRzRnh1VGpwQ0pEVmhBZVM2YXJ6djBteHhrM1V3Qm14eUtlMVdwLVM0aW5oZE9yVG9fdzRLbk5wbmtDT2d5QV94UDdVclNZLUE?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10-05-2026 01:39 UTC</t>
+          <t>10-05-2026 03:13 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,864 +1008,192 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Viagra vs generic: what actually matters when choosing between them</t>
+          <t>The next 10 years will be about high-value innovation, says Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portal CNJ</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxNdll0Sk1Jd0RuWVJMaW1CaHJpU1NLVVU5Vk5odktwSWY1fFhMGZOQVk0YkV0NDVfRzRPOVp6QlNRSHVqRVVyREdtbmI4bkVWN29VcmxhSHVNbVVmTWtwaVNQUlh5SkNLV1dPcTdINGdKZjJNQV9RYmRxYjZReDZqa19PT1ZlX2FMUVhTeUh4bDNIY2NuTnRJUTktUnZXa2VpSG10cmtpSGZKTHNOT21sMGhHSDZrR043aHJ0TkJvaDNaNzZYbThHemwwODVMT0tBLW52cTZCdEYzS1VlWkFOX2FjVjBIUnpmSHJtd2t2WEozWldnTFJvODdzaHBTdWx1RW9oeW1Xdi12VW1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOWEc5ek9ab2hCeFhuTjBzUVdiVWFNZm1fYkFNdnUzMnZhY3BXOUd3VmxMVllTUF9wN3loZVlrdURCS0RYVTdBOVBXTzAwSlFaMklnWnBzdldIWElVMWprS3o3Mk1oM3V1R2JRRXRfQ3pUNlRfTzhYVkwwbFZyREtQNE1pQVdtRmdla1Rpc3ZxR1ZJWnB4RmlJRkVQMDQ0bG9VNUN5dkl5M05ldi1wcXdIby1SLTItUTJPSXY5RlFLQWFrWnFmbTQzZnpiM29LSTI00gHQAUFVX3lxTE5YRzl6T1pvaEJ4WG5OMHNRV2JVYU1mbV9iQU12dTMydmFjcFc5R3dWbExWWVNQX3A3eWhlWWt1REJLRFhVN0E5UFdPMDBKUVoySWdacHN2V0hYSVUxamtLejcyTWgzdXVHYlFFdF9DelQ2VF9POFhWTDBsVnJES1A0TWlBV21GZ2VrVGlzdnFHVklacHhGaUlGRVAwNDQsb1U1Q3l2SXkzTmV2LXBxd0hvLVItMi1RMk9JdjlGUUtBYWtacWZtNDNqemIzb0tJMjQ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10-05-2026 02:37 UTC</t>
+          <t>10-05-2026 09:14 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vaccine and blood thinner help drive Pfizer to quarterly earnings beat</t>
+          <t>Aurobindo Arm CuraTeQ Clears Key CDSCO Hurdle for Bevacizumab Cancer Biosimilar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQalp6Unljel83ZnRVMF9McnpwMWNQaEV3bHlVOFNXNlpEQ25SUzBzRERaZzl4YWFZdmpTanp0YkdtUmVtNHVuMER4QkZMQUZFS2o4bHJRYXZKRUlSNFkyVVR4VEpjTThVSUgxZnNrTGtpVFVOaDFiM1R0dWV5RE9SYm9sT1h5eEVRdjh3Q09HUWt3WXE3dFlv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPRy1BejAtcDlsbm9rLWtQSklFR203YTRrS1lrYXJlOHBOTEtQLXB4VHJmQkdjVk96WWlrWDdvN19KWnNvdHFWZmVCU2daQWlIcnl4VUNqX2VFLWxVUWozOTNCUlV4MEZ4MEhvS2FrajJHRl9wSXR4VWU5NTE1MUJRM2lGdmdoUEVvOERNMGRFNkYxbW1YazhMczNuT2w0d1lVaDRSV2tvRkl0WmNsUFpPX0dWeUxXREFEamtqYzBUOWVjQ2dLLVlSVDJCdjdCRDBNZ0lNWHA2QW7SAd4BQVVfeXFMT0x4dHpndTBndHhNUVpMQUFiMlZpZFdVbXFMLXp0dV8wYnJ4aW1WeTVEbUJPN2ppQ2FiM1AtTjAwYmthUFBIeXZSSmwtZ1V4N2dwVUZCd2JBb1N2bEkwSFNteFlXbXRPNUxDRHlJRXY1ZDNmLUZUV3ZKeXZNU0czMkdnNF9RdlZFNDJtZE41OE5aMFBJbHRkODQtRGFEUUdhQmx0bVhBbDh0eDVvS1RzMXJUR3dNLTVJS0hYcE1ad1hGMWJleEZrNEZvbnM1UGF5UmFCUnNGQ0xxbnJrSDZB?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>09-05-2026 23:15 UTC</t>
+          <t>10-05-2026 04:30 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock (US09062X1037): Q1 earnings beat but guidance cut weighs on sentiment</t>
+          <t>Biosecure-driven China shift boosts Korea API and oligo CDMO expansion - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPMndzbFgteVpacmNvRUNrRkdUX0dkcVBWcGt3cU9pZEFPVEkwTEt0U0lHWnhZVmNsTEFBWmNOWFdOM2FRNHdnSzRZQlpJdmxCdFZ3emt4LWY2Z3o1eGRwUEMwZ1dhVy1EYWR3M1dyMEFtUG1yWE9uMDR3TnM0UjNsNkdGZElTSDFkUTMyNjhTVVpvODBYVm1RN1ZQYmw3RHFtT3NuNzVMeHdyb0V6MHh5aHk3R3hzQXpTaHZQV3ZCTDVSaHNRd2JjNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOa0JYbFhPRWtqWlYwRFh6VlpVWEpGYkpid0YwbmoybGxNb2FoeGs0bEFHZ3U2ZzRWN2pfcU5GcHpXMVp5VGVjX0xMem9HUW5aYS1UZXlSS0hnNXdpMm94WldTSnlZQkw5ZHdKcUNVU3haYlRwYlliUHc4aDRzcXNHU1RJMFBDekI3bVJNU3hwX04tWUhX0gGUAUFVX3lxTE5rQlhsWE9Fa2paVjBEWHpWWlVYSkZiSmJ3RjBuajJsbE1vYWh4azRsQUdndTZnNFY3al9xTkZwelcxWnlUZWNfTEx6b0dRblphLVRleVJLSGc1d2kyb3haV1NKeVlCTDlkd0pxQ1VTeFpiVHBiWWJQdzhoNHNxc0dTVEkwUEN6QjdtUk1TeHBfTi1ZSFc?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>09-05-2026 10:56 UTC</t>
+          <t>09-05-2026 22:04 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDA Extends Review of Eisai, Biogen Alzheimer’s Drug</t>
+          <t>Daiichi Sankyo Waiv Alliance Ties AI Pathology To ADC Valuation Story</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>International Business Times</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQi0ybkVGWE9LaG1sbUxiRWdYSXdTam96WS02RHpBdE9zVWhJNGlnYXQ2Zk5kblFRM0hpX0dzMUZRakIyM08wMkRuaEZ6eGlQdzloano4Mko3aWhHZDJSeFJhbWNBeEJZWEI1ZlhfSWV3c2FuSzhyUGdCUGoyWDhsREhORjhKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPeU1VU3cxbXJza3dJeGlIaTMtbVE4YzdSSHZZVHFhYTJOVFMwTTBpMWNFbjZJMTBHajJfaFZtY045dlF1cW1YYkZBNFZORzU4SElIZE5nc2pBYmZxR1JRTXZCRF96M2JnSmZkRTBwUUJyeFphQ1haci0xWHdDME8wTldyMGZTZDVEOWVSUmtkVTRhOHFsM1pfT1V1RXJNSXJBa3poSDBGaWtMel9BY0ZiVGluOUZwOExPNjdabXJ3VlBxQk5oWENsT0toS3pSVmpvUFhxSkEzWkxVdkRJTkl1cElfSDFoOWPSAewBQVVfeXFMTUdVeFBsZURHMTEzd0w5V1oyVWdsNFJfUWlTcU9la08yeFprS183TGZfcW5DckxPWmU1ZUZwODJPSFJTVG9PeEVpZE5DYU9Ub0p1QTA4UUUyUUdjUTVsU1BxeUhIZmx3Ym5lR3F2SFNqa3FIUVl5aS1lNkVDZDJWTjg3MlhxWnh1RDJOVmxKV011elR0RWRueVl3N3lIYjlNV1plNmxLWGRTV1pRMENLMnNTVlFqN2xDcTRCWEF5OGNNbU5ORHgzaFlvUEZHYzhWVm0yZnZqb1B1YW5JdnQ2X1lVVXNwMXBQQnA2dDA?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>09-05-2026 14:05 UTC</t>
+          <t>09-05-2026 22:51 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Milestone in the fight against ALS: new treatment makes patients better</t>
+          <t>Daiichi Sankyo posts 1.4 trillion won loss after revising ADC strategy - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lnginnorthernbc.ca</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOQWZhckp5UngzZWI0aFZ0dkI3NTlncjNYQW5Uajc3WVpBUDNjdXJFc1o0d0kzZloyUjczUExjYzVoZGpwc1h3a0FxdnBnZkFxZjJiVzRQWC1TN25RcFQtQTV5Zlk2S2YtMDZGbldGMjhkbmNLUXhrbE9VSWJEWmRVbF94cjR6SkZ0VTRpdXloUHRLRjdUQm1aNG5rdHdJLURPMzA4N05vZmdVdjRsaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPQVVrd0RCSE9VMFpUODROTU9hTmNPYU9FWkdONGNKOXNrV3lmaHBEQlJtaV9XeExqZXlmY2phR2dpRGt0OUxPZk9HNUxhYlQwUmxwVEV0ZGkyUjlNZllYWUJDUU5JT1lNaW80d2wydlZZMDJhYUNGU3dUZUdDd2diRNIBlAFBVV95cUxNRTNmSE5vQmNSamhabW5qV3d1WEpvamFQVGl6eEtfN3hpcDBWd1R6Ukg3WldZaW5qSXFtWEk3ZklMV1pLTFRZbjdtd1ZMaTIxVHJNbGxxX2JzaEYzdTBPZm1CcjMxWEphS2ZfOUliWHRPdjZHTThZVFYxbUpoRnNvTXphNDA5VDA0TUV2M2Zjb3EzNjUw?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>09-05-2026 14:45 UTC</t>
+          <t>10-05-2026 05:02 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q4 Earnings rush: Dr. Reddy’s, Airtel, Cipla, Tata Steel, SAIL among 400+ companies set to announce results</t>
+          <t>Fresenius Kabi Nutrition Solutions: What U.S. Patients and Providers Need to Know Now</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPV1UxT3hyQ0FEcHNuQ1lDaUdEQ1FVcjRXSVp3MXJjbHBDTlNORGNjVU1qaG9hUGd5TnMwdlNscWU0bjRVRUhZS1hSMkltTEQ0b2lQcHVhV3hVZ3pYTjlaUmpvenZmS2dHTG9xTW94X0VJNjBqbnRTS2hIamRqTU9ZNlJNZ1hheWNKTjZnbW81NGFKLVBvWHEwX3RHRFhFTGdQV2hZdXIwMjZVNlcxV1RRSkdFX2RyYXBwaEpJY2J6eGdXQXJiYm90UkR2VllwVTYxaG9OWmwwR182akh0dWF3NVJROHBINVdKQW9lR0ZNbXZSSzFxY3fSAfwBQVVfeXFMTzRlUnZLUHFmajFNSHVRQjFKQmFVU3R4dFRjZklySXJBdEVQTHpPYjB0bkFyQ3p0Sk5uY2Rhc1JZRXZoVUxkMlVYeF81d181ZDBUcXY4VVVvQThQOEtJc2hJVHoyVmFId2JORGFFdzkyOHRBa3FUWk8waUY0SG1vQUNCYXhuMFViOWxfeE10UlpFQ1F6c21VaUxvVjJjNGxIQmxHZHhneVFBblZrazh1WDhkX0VBTERqWDdBWXVDQk9hTzVidndmUWNaMktxSkg4X1hHbTFJRTRKTTUxVzh6Y21kTVBCdUxsdmdQMnZDWC03dTh0bWFXQS14VG9y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOWFpQZ3dFUllPVlpnQXhfX2k0MnRUMkwybTFTb3FRMEhvcTB3clFQTTFudWkxbHVwaTVYN1IyOGQ0VmdrMWV5WE1zdWRQWHNjOGEzdFhkM0pnYUJuNllIUXpnRTBGWUF6Z1FHTUt1cHJOalptLWlrQXpFZGNDQjBYaEtHSkg3a0YwNkczX181RXNRYWgwQkc3bVM3d0N0YjNnNVdRV2xqT3J3akM3dXo4Sm9NcVc3eU1SeXNBV2dCUVpCV2taVDU3U1VR?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10-05-2026 04:21 UTC</t>
+          <t>10-05-2026 11:49 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Number of shareholders of Dr. Reddy's Laboratories Ltd. – NSE:DRREDDY</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPSUViaWhsakVaXzV4WXRodWVVaXVJbjFIeXJKSC1IRzJmNUEtQi1zUlI2TG9CVVEyVGNiTG9DWTFZM3pweTUzWGVzYjdpYnBVM3RZZU5pYThvdDAzaEtNZHhjbHRwRHhYMVh2UkpNNG83Uml0V1c2ZlY5bGJjUkczRWxKVTN0ZURrc0ZqaWdHZXY0aUlJd2hpOHdxZ05tSGtSN1ZFaERJcw?oc=5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>09-05-2026 23:15 UTC</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's Laboratories Ltd stock (INE089A01023): Margin expansion and steady growth in generics</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOSTJscEpVQ21QcTJKMTZ2eTZEeGlaUDA2aFBNcmVZbG1vbzVXNC1xWnFWbWJwQ2ZCcVc4MUJZd2xOalVXSmZRLXhpM085VVV4SmN3empKQ05ZNXU4RFNoNGpHTW1KRENVWXQ2a3Q0cEltdkhqUzZWZG5WQjV4UHc4Sm5xck9BOWVCeXJGazJsSWg2S0FOZjBBczZvU0lMSHlfN1BlV1VvMVpRM09SVERwNlF0eEp4dmZUT0hycm5Eb3A4RFBw?oc=5</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>09-05-2026 17:26 UTC</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Govt Releases Updated List of Approved COVID-19 Vaccines in India for 2026</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPN3lEb29oTGNzZlhTR1I4dGVGWHJ1VnV3blNscm5oV1NDdi1yR0J3bE5XOWRVeEtfSmRlMDVzcFEwNG5wMEhxT2FEeFlHVmgzVzdBZU5oRGszeGRpT1NTendJSTE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB0gHPAUFVX3lxTE9qS0diZkRvZmh1aUhuYlV6QTAzQmVyWU5VVWx4cjRGRGYyWTAyY2FQM3ItaERaZ1o0a3lGNzVYRDR1UEd5M3lXT3VzWkZ2V2o4UFk2b0ZJLWYzZS1YT3ZhcTlGUDdGYmJlNFdFZy1TbTBtUGhmZ1BqTjRWSnJJQzVZcTBPRnZDZ2dwdkFpY2FFa2tzbThEbnJRTN6WHVRLVFCZE5Jc3B2a0dFNDJoZ205WE5GS2FFR19TUDhuOU1valpBNEtFZmxRSlFITnJidWc?oc=5</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>10-05-2026 05:00 UTC</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Dr Reddys Laboratories Ltd Technical Momentum Shifts Signal Bullish Outlook</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Markets Mojo</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxORmRqVGtSb1gySlNPZ0dRRk80YjBnNmt5UVRSLTNDUFBVdlZhS1RPWlgyLThtemlHQzdBQmRsdk0xU215dEwwdlRRY0R4a3FrMzU2SEVBMkl3WjVXMUtrdk5qU1IxZzlDMlBHazB3cjBoMVpEYnV5RmNyLVdGWVRiR2V2cndQUW1GdjdKRm5IbWp1dmZUWldKbFJtcUwtSUFzNlhXUVlpQkFnQURQMFJ2VlRHNVRmQndjcXhXSXZnWUFLVkFUWHJIVTY2S2pzQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>09-05-2026 22:40 UTC</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dr. Reddy's</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Chinese medicines bring relief to India’s cancer patients</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPU3ZlU3JwSVB3YmxNTXZ2akNaY19pNzRVZGk0WXloRTZGZ2t3VW52ZFp4TUtMWmR0SGxxaVhTdW01V2hBa0RJT3pMZWw1ZDFyd0RBdm0xNUlBc0FHNHNCaWJvZnJFT05xMGVYdFFmeFRVellZQVJLcE53TGZwOFM4Y09aMjBrTHdta3kwYi01eTRXTlJwYm51aUMzUkZiNDZBcFpXVDdQaTJxSkxtYWI1Ymg0V3RlbzZjc19IX1FUaW1mVVJmalM4V3NGZmpMZ3FkNEdqTW5DMW5JenI3WWlrLUYtMnBQQ1Fs0gHoAUFVX3lxTE9TdmVTcnBJUHdibE1NdnZqQ1pjX2k3NFVkaTRZeWhFNkZna3dVbnZkWnhNS0xaZHRIbHFpWFN1bTVXaEFrRElPekxlbDVkMXJ3REF2bTE1SUFzQUc0c0JpYm9mckVPTnEwZVh0UWZ4VFV6WVlBUktwTndMZnA4UzhjT1oyMGtMd21reTBiLTV5NFdOUnBibnVpQzNSRmI0NkFwWldUN1BpMnFKTG1hYjViaDRXdGVvNmNzX0hfUVRpbWZVUmZqUzhXc0ZmakxncWQ0R2pNbkMxbkl6cjdZaWstRi0ycFBDUWw?oc=5</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>10-05-2026 03:20 UTC</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Intas</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Xbrane and Intas Revise Financing Terms for Opdivo Biosimilar Xdivane</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>TipRanks</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPZGJqb0dfeG5Db2NCV2JiYXcweFpDWTA4Z3dMYVJPZHlCbDZjNVZXUWFXdHd3Zi0yTlJjczduRUxnaVM2aUFxb0ljbHdCS3BVRmpEYVMzWVZybnJ5RkRfWWJDVVJlM2FYTi1ibHZZcjVsVGcyZTFXOFZJUlRnZzRjSUtaTmR0cGRQRTVMV094QkFxM19ybHlZQmg1aE5ITzNISnllMDFNVWVtd0dUbmNObEU5VlhTb0JHbVloNW9R?oc=5</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>10-05-2026 03:58 UTC</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>From a garage venture to an industry bellwether: Biocon under Kiran Shaw</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNWDlmQVhxLVUzekhOWWV3YWdOekJWRHdpNWRLMnNGUUlQd3Y5RzZ2M1JMRl9tRE1IekZ3TUtMWmR0SGxxcVhTdW01V2hBa0RJT3pMZWw1ZDFyd0RBdm0xNUlBc0FHNHNCaWJvZnJFT05xMGVYdFFmeFRVellZQVJLcE53TGZwOFM4Y09aMjBrTHdta3kwYi01eTRXTlJwYm51aUMzUkZiNDZBcFpXVDdQaTJxSkxtYWI1Ymg0V3RlbzZjc19IX1FUaW1mVVJmalM4V3NGZmpMZ3FkNEdqTW5DMW5JenI3WWlrLUYtMnBQQ1Fs0gHKAUFVX3lxTE1YOWZBWHEtVTNqTzVKYldZYWtON1pWcjEzQ2w1T3B5QzFVQlg2Sk9Fa3pLUmhfSW9DZlVNandDU3k3eU56Mmt5Tjg5Z2VGRFQ3WGp2emoxbkNNbFEwRlFLMFVaLUNlWVoyMlJGSlNDN1lRV1VTUlpKVnU1NFVVRHdOckRzRnh1VGpwQ0pEVmhBZVM2YXJ6djBteGhrM1V3Qm14eUtlMVdwLVM0aW5oZE9yVG9fdzRLbk5wbmtDT2d5QV94UDdVclNZLUE?oc=5</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>10-05-2026 03:13 UTC</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Biocon Q4FY26 &amp; FY26 Results: Revenue Up 10% YoY; Key Corporate Actions Approved</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxQUDdSRFlsM3FJM3hrZ29QOWVZc093YVRoVUJoZjlGejRKS2NyN3dXaFJ2cXhUR3RHLUNkcG15WEZ0WkUtM3VpTWNONzdyczcydnR2Smt0Z1JfZFVRbzNpZGxrWlhEcWt1aVzE3RjgzaDdRdVFvNjFGOTJINThEV05uSTNoZ2pKWUVWRGszLVhEUE9nRzlnZm4xOFdLaUFLRDZzQXFpek5STDdWQ21ncEVUYWFxSXJJLTNVQ1NsM2tacDhxTkx0Z2JXQ05PVzlxajRB?oc=5</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>09-05-2026 20:50 UTC</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Biocon’s Kiran Mazumdar-Shaw Plans Succession; Claire Mazumdar Tipped As Next Chair</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BW Businessworld</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQaG9PVkZfbEV6RWpLdkhTMUNXcnVZNkNWR2s0dk1ESFJoZVplbDdLQjRQTWZ3VTNJQ2RYWkFMdWE1YUJtVS12cHdBbGxOZS1waU5QMjI1Y3doMzJXc3NMV3dTdjVqLW55amN4a00wVC04Z0Y2VElQeFUtTUtCNVR0SjU1M1ZzZGVCREV5RTdGSUpjTWJsWWhrOHdCdGQ4STRHUklVVlJjNXNWdC12allBVk9kMVFrb2NTZ2JPWjItdDl1OFZUSWR5Wg?oc=5</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>09-05-2026 15:59 UTC</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>The next 10 years will be about high-value innovation, says Kiran Mazumdar-Shaw</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Fortune India</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQWlhtQlhWSjllNWJpVjRzQjR3bHdXTnlUdHhXbWRRZkhLQkhRVUhnVWp3SVQtQkpxT0owMTdsSE5fcjBzTlpIX1pnZ04wX0kwYmRJaWdzY0hUV3lPMUdFbzc1dmhBaHFQN1Rfekk5T3dFamFHbElNakhtMkc4OEdva2oxQWZ5SlM5dFlLU19rV2hnYXFmbmNwSzR2REpURVE4VERZVnc4NUllZDZWUGZwVWJ4c2FvOUtFZ2NWZXNPbWlzaWvSAdABQVVfeXFMTlhHOXpPWm9oQnhYbk4wc1FXYlVhTWZtX2JBTXZ1MzJ2YWNwVzlHd1ZsTFZZU1BfcDd5aGVZa3VEQktEWFU3QTlQV08wMEpRWjJJZ1pwc3ZXSFhJVTFqa0t6NzJNaDN1dUdiUUV0X0N6VDZUX084WFZMMGxWckRLRDRNaUFXbUZnZWtUaXN2cUdWSVpweEZpSUZFUDA0NGxvVTVDeXZJeTNOZXYtcHF3SG8tUi0yLVEyT0l2OUZRS0Fha1pxZm00M2p6YjNvS0kyNA?oc=5</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>10-05-2026 09:14 UTC</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Natural Biocon (India) Limited Reports Net Loss of ₹4.00 Lakhs for FY26 as Revenue Declines Sharply</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPTVFVV2FrSXF3cGk5UGVkaW1JS3FTa3dCMHExdkZQQ1R3TGRUc3JoRDlad01VN2NBcENJNkFlM3BpLUtkTWEtdGNTZ0dDWFhHVXJMNnVidm1JVnQ1NUE4dFcybjBtRkc3N0hYWmIwbjR3bnRpRHZnaVA2NHdlY1FrOWlmSjFmblU4MHZzWnRubjk5VTlhSlRWLWpKOE5xb29Sdm0yX1d1Ri1IdlpaRUlIOTZqQUtwVGF1bElTbmt2eFBTMzJ5eElEbEhfdU16VGhLZmE1Rm8zOUZ6OG0wZl9GeDFqNHJtZkpH?oc=5</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>09-05-2026 14:25 UTC</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Aurobindo Arm CuraTeQ Clears Key CDSCO Hurdle for Bevacizumab Cancer Biosimilar</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPRy1BejAtcDlsbm9rLWtQSklFR203YTRrS1lrYXJlOHBOTEtQLXB4VHJmQkdjVk96WWlrWDdvN19KWnNvdHFWZmVCU2daQWlIcnl4VUNqX2VFLWxVUWozOTNCUlV4MEZ4MEhvS2FrajJHRl9wSXR4VWU5NTE1MUJRM2lGdmdoUEVvOERNMGRFNkYxbW1YazhMczNuT2w0d1lVaDRSV2tvRkl0WmNsUFpPX0dWeUxXREFEamtqYzBUOWVjQ2dLLVlSVDJCdjdCRDBNZ0lNWHA2QW7SAd4BQVVfeXFMT0x4dHpndTBndHhNUVpMQUFiMlZpZFdVbXFMLXp0dV8wYnJ4aW1WeTVEbUJPN2ppQ2FiM1AtTjAwYkthUFBIeXZSSmwtZ1V4N2dwVUZCd2JBb1N2bEkwSFNteFlXbXRPNUxDRHlJRXY1ZDNmLUZUV3ZKeXZNU0czMkdnNF9RdlZFNEptZE41OE5aMFBJbHRkODQtRGFEUUdhQmx0bVhBbDh0eDVvS1RzMXJUR3dNLTVJS0hYcE1ad1hGMWJleEZrNEZvbnM1UGF5UmFCUnNGQ0xxbnJrSDZB?oc=5</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>10-05-2026 04:30 UTC</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma Arm Apitoria Pharma CEO Dr Sanjay Chaturvedi Resigns</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSUxfV2YzSVRsd0xLNDBPVU9GSUdsSDZUWmlaUDRsYWFSXzZ2M1BQZi1Bc0VRY1h2UjVKVWZ0WjZmR1BKX3FuZWF6bnFXNUs5NzgxUVNQY0pmbXVTdERZSVptZG5QbGxoQlhfdDVqMXBtb0FLc1dWQUdoNng1YWJTbXpLQ09RMkJGYnVpR3V0WnRJUmZ1amNOVEVPOExTeTduTTd0Y2Z0T2RUcURta2VJdWo0QzhtbjdQbE5LS1FaYlRyZzjSAcgBQVVfeXFMT2lVX3Y2UUQyNTNqZW1zY3pyS2ozM2JldnhuaTN0SEJuaEVocU54ODJ4X3FqV1I3c0FSU1dqZXF1MERoejBGY0dJUU9vRlAzQ0xjem42MTFLZC1WSjBWdW9Tbm9yNUdmX3FCODlNWnAxR0U1X056dTZvbnNJMHlLR0dRMlFwZ2V6T3VwUDRCM0lZV3lOcldDQXNiRGZBcGF4Vm92R3RFSERyazByTy1zRTRSbHM1S2tkdnVaSHVMWEY5bWt2OHRMcE4?oc=5</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>09-05-2026 11:10 UTC</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>India's Drug Panel Recommends Wegovy for Metabolic Liver Disease Treatment</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNal9UeXlITjk0dzZtR0QyNkQxX0Q2VFZEd2M5cHpVOXhkZHRSdGM4NVJlUUdTMGNRMFlSSk5RX1FaaHhfUmwxQkNrQy01UzB0SVNmQlBpSElRbE85ajJndXllSnRLQ2xGMDZqNTlCdVhXZHgtYWVaUlU2cmt6VkZINXFOMDdoYXlvMjdoMVJRRUEwNUdINFlUVVE3Q2syRUthbXh6LTJEU25WSzd6VnBJbnNJMXg1TWtlak52YUlyVUkxT05VazlueTVPaW5VemNiLWxKVDJtOXFUT3YtSG9zaVhhaXJUNTZfYlk5ODFlOVhFNTl6YVpUaWl30gH6AUFVX3lxTE1qX1R5eUhOOTR3Nm1HRDI2RDFfRDZUVkR3YzlwelU5eGRkdFJ0Yzg1UmVRR1MwY1EwWVJKTlFfUVpoeF9SbDFCQ2tDLTVTMHRJU2ZCUGlISVFsTzlqR1o4eWVKdEtDbEYwNmo1OUJ1WFdkeC1hZVpSVTZya3pWRkg1cU4wN2hheW8yN2gxUlFFQTA1R0g0WVRVUTdDazJFS2FteHotMkRTblZLN3pWcEluc0kxeDVNa2VqTnZhSXJVSTFPTlVrOW55NU9pblV6Y2ItbEpUMm05cVRPdi1Ib3NpWGFoclQ0X2JZOTgxZTlYRTVKOXphWlRpaXc?oc=5</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>10-05-2026 06:15 UTC</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GSK Moves Closer to India Launch of RSV Vaccine</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQaWdGYVJfSjlzU0R3MUl3bWYxcU9OclMtckN5V3BCd1hTMjBKdWdNTDlueldPZVhNOFBOc2hZTEdxODR4OWNndG12MDRZMV9OVzdTcm41dUMtbHY1WHRrc1dGdFh4ZmNCVUxLTUNfOXcwdkdaVHlsWDN5eno2RElXUGg0VkRWOGVMYTQzemtrQlZLbWtnRkhwTmJXcnBwd1VfN0NDaXMyWVNHRGxOZmY1OFp0QXlTbW5USGZTLS1HdjJ2c1dKdFpBRTNYYklndEFo0gHQAUFVX3lxTFBpZ0ZhUl9KOXNTRHcxSXdtZjFxT05yUy1yQ3lXcEJ3WFMyMEp1Z01MOW56V09lWE04UE5zaFlMR3E4NHg5Y2d0bXYwNFkxX05XN1NybjV1Qy1sdjVYdGtzV0Z0WHhmY0JVTEtNQ185dzB2R1pUeWxYM3l6ejZESVdQaDRWRFY4ZUxhNDN6a2tCVktta2dGSHBOYldycHB3VV83Q0NpczJZU0dEbE5mZjU4WnRBeVNtblRIZlMtLUd2MnZzV0p0WkFFM1hiSWd0QWg?oc=5</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>10-05-2026 06:00 UTC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Torrent Emerges Early Leader in India's Generic Semaglutide Race with 38% Market Share: Report</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Medical Dialogues</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDcrllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UdIB5gFBVV95cUxOVEpmS290Z0FVbnQ2cUFXZVRPY3BKM2JkVVp6VDh5RkZnb3k3X1RTazVuLTU0WDl2N1J0M3ZRVk8xNmU1SHFseWQ0LUtvYm9jM3l6VU9Pc043c0ZhNEJDdThJV2hmYWYyR2piSklOOUtSUEU2ZjE2MWw3dHU4d3d6TVpLYkVDclllZV9YakNrT1B3SkNaSHNIUnd1LXdDTU52TEx6cllmbDQ3SWp1U2RuTE00M01JQzFUTFFBVTdUM2lxOE9RYW1McXlDUzh2UWIwUUkyemFQSnF3ckl5U1lpR1RGLTc0UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>09-05-2026 11:53 UTC</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Biosecure-driven China shift boosts Korea API and oligo CDMO expansion - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOa0JYbFhPRWtqWlYwRFh6VlpVWEpGYkpid0YwbmoybGxNb2FoeGs0bEFHZ3U2ZzRWN2pfcU5GcHpXMVp5VGVjX0xMem9HUW5aYS1UZXlSS0hnNXdpMm94WldTSnlZQkw5ZHdKcUNVU3haYlRwYlliUHd4aDRzcXNHU1RJMFBDekI3bVJNU3hwX04tWUhX0gGUAUFVX3lxTE5rQlhsWE9Fa2paVjBEWHpWWlVYSkZiSmJ3RjBuajJsbE1vYWh4azRsQUdndTZnNFY3al9xTkZwelcxWnlUZWNfTEx6b0dRblphLVRleVJLSGc1d2kyb3haV1NKeVlCTDlkd0pxQ1VTeFpiVHBiWWJQdzhoNHNxc0dTVEkwUEN6QjdtUk1TeHBfTi1ZSFc?oc=5</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>09-05-2026 22:04 UTC</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Prestige Biopharma</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Brazil's EMS acquires Medley for R$3.6 billion, targets US market after 2030</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Generics and Biosimilars Initiative</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSWV0ci1oUzJNV3lyTTBfano3V2JGbTdBSkcyTnNNN2hQRW1iT1ZCcGd3MWdVd1lHRTBkT05sclFCaEdPbzdEWi1waU5vbzVQVUhWYjV6cjZWanNzek84SWJjZnBFUXBKZk8wYXJ6QnFRR21aS1hNNEtPaHcyUWt2YTZiZnEwYU5hOFNhcF9BUlFsMFVoc0tBRWc3WWxYMHJnNEhrZEQwbHBZRm8wMGRF?oc=5</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>09-05-2026 21:23 UTC</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo Waiv Alliance Ties AI Pathology To ADC Valuation Story</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPeU1VU3cxbXJza3dJeGlIaTMtbVE4YzdSSHZZVHFhYTJOVFMwTTBpMWNFbjZJMTBHajJfaFZtY045dlF1cW1YYkZBNFZORzU4SElIZE5nc2pBYmZxR1JRTXZCRF96M2JnSmZkRTBwUUJyeFphQ1haci0xWHdDME8wTldyMGZTZDVEOWVSUmtkVTRhOHFsM1pfT1V1RXJNSXJBa3poSDBGaWtMel9BY0ZiVGluOUZwOExPNjdabXJ3VlBxQk5oWENsT0toS3pSVmpvUFhxSkEzWkxVdkRJTkl1cElfSDFoOWPSAewBQVVfeXFMTUdVeFBsZURHMTEzd0w5V1oyVWdsNFJfUWlTcU9la08yeFprS183TGZfcW5DckxPWmU1RUZwODJPSFJTVG9PeEVpZE5DYU9Ub0p1QTA4UUUyUUdjUTVsU1BxeUhIZmx3Ym5lR3F2SFNqa3FIUVl5aS1lNkVDZDJWTjg3MlhxWnh1RDJOVmxKV011elR0RWRueVl3N3lIYjlNV1plNmxLWGRTV1pRMENLMnNTVlFqN2xDcTRCWEF5OGNNbU5ORHgzaFlvUEZHYzhWVm0yZnZqb1B1YW5JdnQ2X1lVVXNwMXBQQnA2dDA?oc=5</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>09-05-2026 22:51 UTC</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo posts 1.4 trillion won loss after revising ADC strategy - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPQVVrd0RCSE9VMFpUODROTU9hTmNPYU9FWkdONGNKOXNrV3lmaHBEQlJtaV9XeExqZXlmY2phR2dpRGt0OUxPZk9HNUxhYlQwUmxwVEV0ZGkyUjlNZllYWUJDUU5JT1lNaW80d2wydlZZMDJhYUNGU3dUZUdDd2diZNIBlAFBVV95cUxNRTNmSE5vQmNSamhabW5qV3d1WEpvamFQVGl6eEtfN3hpcDBWd1R6Ukg3WldZaW5qSXFtWEk3ZklMV1pLTFRZbjdtd1ZMaTIxVHJNbGxxX2JzaEYzdTBPZm1CcjMxWEphS2ZfOUliWHRPdjZHTThZVFYxbUpoRnNvTXphNDA5VDA0TUV2M2Zjb3EzNjUw?oc=5</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>10-05-2026 05:02 UTC</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin Co., Ltd. Just Missed EPS By 16%: Here's What Analysts Think Will Happen Next</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPZnN2amVaQ3hBMFpPRkp0aHNIZUhWdWk1WFpOSnFySDg4REZmU0VFdHExTjZHaldyS0F2OGQ5NVZYaHFVcWZrNFVxOWw4RXpNM0hSZEZ5M2p1aFo5Tmc0WnlpTzdPMGNUWm15QUNTTENfQ0Z4WEU4dXJvN0t6QWllYXZheW5ZVjZibEs0Nk0zZFVBUmM2ZWZHYmdCb2RRRkRyYkFvakpHdjZtRllWanVXclZ3V2FLT3lxT05SNmFvTnlwcjRZZWIzOE05NFFKZFUwbVNKSzFXQzlTZGIwQThJVVkzTdIB6AFBVV95cUxORnM2M3QwTkV1OTh4eVhWbGRiMXRSM0w2MnJKTWhVbkR1WlY3UGJ1b2g2RzlWc0d5bFhqVkxGVnVRSFJEMEoxNzZJVS0wai1PNm1MSFpyUDNwRHZtZVh2bkZOSnFhTXRiVlBNbWI1aDhoanB5VEZoYkFXRjRFU2hsczM0ZWJrNUZxdHZ5Uzl1N3JmVnFZTHY2bUI2NEdXZ1MtalhoZnNBQWlSeFRyLVhfaENiQVZWVjBXckJOQ3E1LVRhSmRXczZvWkRDSzRHdjF4MDJVUGNVTE5ibGdPN2dEOGZHTXNSTkRE?oc=5</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>09-05-2026 23:23 UTC</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1221,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-05-2026 14:48:47</t>
+          <t>10-05-2026 20:15:45</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,22 +501,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global shortage of ADHD meds means some patients may miss out</t>
+          <t>5 Questions For Sandoz Global Head Of IP Julia Pike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Te Waha Nui</t>
+          <t>Law360</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE9DNDllNjdhd3BfSXpieGdjNmRlcy0tOVdUNEp4OWphb2IyNElxZkxURm1YUlhUQ29nRTlYbWQwRUJtVEc4X0RmQndWcTAtcDZ1MHRMYUhnXzlOYXV5Qms5TFFVYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQa1FmSUtHdXBtNC1JR25DYjRvWVpIQXRFd3I3eHNvMDFtNnNUajhhbFA3aXZzWFlkVTJsMk1OYkRuU21wVmo5WUZWZ3V2akVRaU1vaW93eUZSS1Bid1VjWDRmQmY2OU1BMXl4dm5TYklUUHlCRnNPM3BHRHR3cnpvUEVULURCMC1sbC1ULWtvQnYyaGhSSHfSAVZBVV95cUxPc2pFeDJlbkxZN2xkQVNhRTlZbEJ2MlJ0ek1WblFYNWRvbE0tU0tkamdWellHZDhERnNDd2N3THJ2WUVaUUY2SFRGdTBtRXBsbUtEMmxJZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11-05-2026 03:59 UTC</t>
+          <t>11-05-2026 18:03 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,155 +533,155 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Partner’s Bizengri cleared by FDA for ultra-rare cancer days after winning priority voucher</t>
+          <t>Department of Medical Service Administration, Boehringer Ingelheim sign cooperation programme on NCDs prevention</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>vietnamnews.vn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxObUJKWlE5RkFUcnBxMEFBLUdWUTctdUhrbVFUZXF2bzRxaHFRS2FRdXFWaV9jNW5Qd3FkREF2aTljUFBqUjJZN25fdTcyUTZBaVI2dzc2Zlo4MDRqYmlKdERXdlQwRjdBN3Q0YjhCU09OT29DRW1WSUJ5RWNHTjhlLXFkb0UySFhPS3ZEYUxyb1kzLVdqU0p0UWV2b2ZIWkhXN0JjZVdLcHg1RURPb053emlhdEl2eHBhbnZj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNeFNkYlZobVZMeldmNmpZdEzZVItWXNaZ2dvczMwQkdpM29rTFhkNVJjbGxhTml1Zi03enRGUTFtVjlKNWliSWt1a3AwV3hMTi1NaWRZcC1uRmpDWW55V21fOEM1RE1IVDVCRGI5TnZaek9KZGdkY0lhNlZqeXoyVWUzTElpQlNxOWRvQ0Z3WWtXX0w1bVdQekMtQTBoeHVMRFk4QmZIcExzOFdHa0JjUFJUSWc5NTRfRWVmYUZuVFZhWjNXa3JBajdUU2t0U2UzVE1UdUZpWXNraURxTjFNYVJrRzBJMF9FblNF?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11-05-2026 11:26 UTC</t>
+          <t>11-05-2026 13:33 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Dividend payer with buyback and growth plan to 2030</t>
+          <t>Ribo and Boehringer Ingelheim achieve third milestone in siRNA program</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Scientist Live</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOSzhCTk9DbGp4RUpKUVZGekV1VDNBLUJkRGZrbWl2U05hN3p3clM0NXQ2UDN0RDUzRk1rMlBNUWxla2RZZFVwbDhhRlRsbk9XODJ6SFVja1NyVnhYbVZ2ZlFERzVJRllsNHc3STcwX19LZTRfTXp5NEpxeVNYTmxGdVdtN3FFVVZqMzlwOXdwWFpRRkloSTFrRWFrQmpGT0ZVVmJHQkpoQWlOZmhxSDR5enpaNnRGQmZMYjRsUTVITFM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPeTBwdUwzSGpuR1g4SjRRU3J4TmRFX25sX2E0bHBDZUxEZV8zSGpkaTZwcWNfSkpzQ1VJdXY4ZzlCal9UTmM5YjNQVmota2JqNE1FVTFuWmlIZUQ2blcxUlBRNGV3YW1QdVdic0pobFg4NnBmRFRpeXN2S1I1TVh5TE5TTl9oSVZuakNMcEo4dU1WenhPWDUxYTJEckQyaGxhSGM?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11-05-2026 08:03 UTC</t>
+          <t>11-05-2026 15:11 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hikma Advances $250m Buyback, Tightening Share Count</t>
+          <t>Partner's bispecific Bizengri nabs FDA national priority nod in rare bile duct cancer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON0JtU2huZ2RTcEYwaUNRSE1fTlNxT2dPVzBwektDckx3b05zSTBPSHZPYzhIRzhRSmx4UlJlLXFNNm00bExlVW83NjFHZnhham0wbnY1WEkyU3gwRDBFZTA5NU9SaUwwLXF2Ti1fYVV2UzhpYkpNU3Y3UU9wZktkN2RzZjgwcUF6WUdwWm0tNVlwSVhheVk0YUpPYmJnMnRwU1Jkcg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPX05UVUhGVkNiYlpRanV0LUk1QUVMWm1SdlVWVkFVcHFETjRnZWRQbmtZR0hLYkl2ZG81OHBoa1k5Y0Vib1NDc09YRmdJdlFZSGx4UE1YUWxnSDJkODFRaTRrZEZnTXpRTExadVBtcXBIeTBKNFNSUWV0a21wUk40NnNrZWlNY1lwdG45YXNuYTA2SmtQcnVBVHJvdG9Zd2FWV2JLaGNvYjJtVGFKN3VzZlpzT1BLOHg1dVB5bkFB?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11-05-2026 12:25 UTC</t>
+          <t>11-05-2026 15:08 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
+          <t>FDA Grants Fast Track Designation to Zai Lab’s DLL3-Targeting ADC for epNECs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>BioPharm International</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOX3hnNU1ybU0zbjFLeFAxbVU2WEU2RGZYZzNlbWFyU0lMQVdodWdxdjEzNGE1cjVxbVp5Z2RDRVdqclRjdHlqUGN0RzhQUkJZT1dUblZfM3pESzdLSmNrSDgyWmc4WFh5Z2dUQXlCRWlqemZUWXhRbG52ZjNMVjZtUHNMN0JOc1NmcDNSR2hhWF9FSlRiYUZ0N2xfdHBjbl9nVERtOFZRVHcxeHFNX2NBazQ1VkhERDJsMHBV?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11-05-2026 07:53 UTC</t>
+          <t>11-05-2026 13:21 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen’s New Puerto Rico Biologics Investment Might Change The Case For Investing In Amgen (AMGN)</t>
+          <t>Sino Biopharmaceutical and GSK Announce Exclusive Strategic Collaboration to Launch Bepirovirsen for Hepatitis B in China</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Minichart</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWU5WUG1OQjNmak1YTEdFWWROVmM4eHpYT2ZtZEd2Ukplb3F4VDM1UzRRek5xWHJrUGJua0tCbTgybm9CTlFTTHBZUE9FbHVUVHNJOVRvMVRlNEYyQjd1eFJ1MmdZZGRMRWRfOXZ1UmVVLTI3dWFtVWZWRncySnFMR1BRLVxsZVh3Q29YcDB0SzZXQUlQZ1Y5MTdaZkxfLTg3UWNxaTBvY0tqdUllc05VYWhjRVpjUmZJN3BiSVZuRGF2RFJ4Mm9wZjJPRE1FaVZzaTEycEZR0gHbAUFVX3lxTE1LcTVjOEpzY09BQmtjNlJNOGIxUHN4U3d6aG1ESDRjRzNkX3ZxQ0NhVVUzLVg2dFA2N0szc1BscGpHcUVaZHlCUWM4bFBfcDlGWVF0OTN4ZU8xbVdHX2hRMmhJOXd3WXIxLS1TQ0VMZjNKNnJ4U2ZkRk4xWDZvUXQzbjBONlpKUmRNcGFsdUQzc0ZOY0lOV2lncmYxemFmX2xtZDdTM3JUcGZoRk1WZE5uZUtqaUdGUl8yY0xHbGNZWVM1VHJxWVlhMW1wamV6MmpnSDZJaUlCbE9xbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNaUpQVzdQX2NuVnJfWmNOV0REY1JCck4xdWZQRXNZQjBXQTF0OU1MT2M4VHpEb0E3cHROaXFNcUdocDZadFRpMzM3NktXbTIxR29yNlRwLUJ4cVRjV2FjTlZxbDlTaDlMSDdTTm1EWEtiQV9lUlR0dHV2TmVSckZ4a0N6YXNHLWhfTGFsQUllMDV2MEo5TUcwbG13bVlwTjR5aFFJVFlTVlI0NHV5XzJUZmtVREpwTmcya0I2WWlIR2JvcmdHLUlNOVc4RGpRZm94UTlQYVVFaGRadUVZNWtPUzJDNEtMX1NoNWFPWDd6TlhUXzh3?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11-05-2026 08:38 UTC</t>
+          <t>11-05-2026 08:21 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Pharma giant navigates C-suite transition and Q1 growth</t>
+          <t>Amgen’s New Puerto Rico Biologics Investment Might Change The Case For Investing In Amgen (AMGN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQbkkzdWNSV1I5X0FIaFdPQjFnTnYyeDRId1VfZFlkRzVNMXd2NFZ3UVpjT1QxbUFYYW4tSXQ2MXljSzBBU2pXZ29Sa3JZeGVHQ0ZFMHl0dHZneHVXclZvYmFFS3dodS04ODg1VzdSM01fQ2w5QVNQWG5UdjBoaVZRT1A2djFpVFlFakg2NjdSb1lpdV9PNkZsY0FLMmp6MWJfVjVrek85Z0VLWktlaXNHdE0xYTJaaXF6VjdLcDN0Q01FeHd1QWoyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWU5WUG1OQjNmak1YTEdFWWROVmM4eHpYT2ZtR0d2Ukplb3F4VDM1UzRRek5xWHJrUGJua0tCbTgybm9CTlFTTHBZUE9FbHVUVHNJOVRvMVRlNEYyQjd1eFJ1MmdZZGRMRWRfOXZ1UmVVLTI3dWFtVWZWRncySnFMR1BRLVhsZVh3Q29YcDB0SzZXQUlQZ1Y5MTdaZkxfLTg3UWNxaTBvY0tqdUllc05VYWhjRVpjUmZJN3BiSVZuRGF2RFJ4Mm9wZjJPRE1FaVZzaTEycEZR0gHbAUFVX3lxTE1LcTVjOEpzY09BQmtjNlJNOGIxUHN4U3d6aG1ESDRjRzNkX3ZxQ0NhVVUzLVg2dFA2N0szc1BscGpHcUVaZHlCUWM4bFBfcDlGWVF0OTN4ZU8xbVdHX2hRMmhJOXd3WXIxLS1TQ0VMZjNKNnJ4U2ZkRk4xWDZvUXQzbjBONlpKUmRNcGFsdUQzc0ZOY0lOV2lncmYxemFmX2xtZDdTM3JUcGZoRk1WZE5uZUtqaUdGUl8yY0xHbGNZWVM1VHJxWVlhMW1wamV6MmpnSDZJaUlCbE9xbw?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11-05-2026 12:13 UTC</t>
+          <t>11-05-2026 08:38 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOLUkyMmlZQVVxOFhvbWY5cHkxSUJXZUY5dHZHWlhxSmQ5cnRsWGZ5N3pZUVc4LUMwOVhKNEVOal_9c3FoOW9tYUpkSHFKTEZ0eDlBWmJ4NlhnYVlsOUZybFdLYmgxSjd3empoOU9QdDBfVVBaZjlGOXpQZlQ5cFl1RmdiTFF2UTlFeG5uVlFGSTM2ckF5LWJ5ZElHS0IxZ3RPcFktcDNvNENzRThsLWhmYjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOLUkyMmlZQVVxOFhvbWY5cHkxSUJXZUY5dHZGWlhxSmQ5cnRsWGZ5N3pZUVc4LUMwOVhKNEVOal85c3FhOW9tYUpkSHFKTEZ0eDlBWmJ4NlhnYVlsOUZybFdLYmgxSjd3empoOU9QdDBfVVBaRjlGOXpQZlQ5cFl1RmdiTFF2UTlFeG5uVlFGSTM2ckF5LWJ5ZElHS0IxZ3RPcFktcDNvNENzRThsLWhmYjB3?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -784,160 +784,160 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Biotech leader navigates patent cliffs and pipeline momentum</t>
+          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Business Viewpoint Magazine</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNQzNpM2wyREV1OWlpY1FBRzJ5MUtFWHJuOUxYa0h6dkhWaVNWcDRzeWpFei0welI4NklfN2x5bHB4czFPczlwMnQ5aWYtaDFneXZUWUNnekphMkxIcHp6RFFZdVJ0Q2s5dW44Tk1Ob2dYTDVHVmlFX0cteTBOOTNoVUxXTUV6Q1N0VUxaMWRDQmFPQ1NJRmY0b3lqdFdzbE9DMmR2UFRmVE8xWWc3dURscXpXamhPQThkeGxqbjRVcHNyT3lu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnR0hjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11-05-2026 11:13 UTC</t>
+          <t>11-05-2026 06:06 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Organon deal impact: Sun Pharma surges 16% in 10 days, nears record high</t>
+          <t>US FDA flags three observations at Piramal Pharma's Sellersville plant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>ETLegalWorld.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQTTVubEJfOHU1WnRwYTlWQ21HS3ZMVWlUVlpJMGlIa290U0FaVlE5aHZxbkpnMXB2Rl9wRTdiRTBJZXYzc3JpV2JhbnF3VnFFWTlMMEE5bkl6M25rMF9neGs0MW1NVU5pcFNxUWFYdkVvZ3VfRnRibG1ZWEd4RGNiWWJkV0dJbTkteF9zSTJJQ1BEUkR1bGljNUh2SHZuc3VnM1FKYjFsZUVJbVZPTWJGSDJMUzdTakNKcmloOGtnM2g2ZG92SjVNdnE0VzNWWXN4VmfSAdcBQVVfeXFMTWdGcDk0cXJxMEo0aXdaVzZJRzQzd1FwaUM3T1BvTzVyRG05QlYySW92OF_5VHN2OE5maW1pa0pGX2lJbFdhNlFZX0JveEJuWGJzNDJjYXV4LURxZ1ItMmFxTzhaekdzTGM5Z19QOUlhRVJXY0lpdTQ0SUxrV0lhT3hZRi1DWHF6VkFSclpkbFhkUXlfbnhDR0RXVHIwYlI1bkt0QkNIY1BXUlcwMFZzTV82Z2wwMzN5TWtIZ1oxb0hSUGFhZXRYSFdnWlY5YVRwYlJOcFp4bDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxObnRsRkhrdjk4Smx2dlpmdEp2OGxwYVZCbGdlanBoOE03dnNIckVjNkZxbWZrMTVfRU5kQ1pMb1FQZTV4dl9lQkwwNVpHSzBIUDFQS0pJZjhCMDFrb25LdGdwaklBWC1qYURxMEJtREFoX2ljSXcyTktLelZBcEVYY3Nmck5MU2g3R0pBYVBDd3ZMaDNMb1hqWW43bENoa1ktbDZVMkVINm05VzhlOWlYdzBrUkplczdGaVY4STN5bm1hczgzV29iTVZR0gHKAUFVX3lxTE5udGxGSGt2OThKbHZ2WmZ0SnY4bHBhVkJsZ2VqcGg4TTd2c0hyRWM2RnFtZmsxNV9FTmRDWkxvUVBlNXh2X2VCTDA1WkdLMEhQMVBLSklmOEIwMWtvbkt0Z3BqSUFYLWphRHEwQm1EQWhfaWNJdzJOS0t6VkFwRVhjc2ZyTkxTaDdHSkFhUEN3dkxoM0xvWGpZbjdsQ2hrWS1sNlUyRUg2bTlXOGU5aVh3MGtSSmVzN0ZpVjhJM3lubWFzODNXb2JNVlE?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11-05-2026 06:43 UTC</t>
+          <t>11-05-2026 06:55 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sun Pharma’s $11.75 Billion Organon Deal: Dilip Shanghvi’s Bold Move Taking India to the World</t>
+          <t>Fact Check: Hantavirus Infection Is Not A Confirmed Side Effect Of Pfizer’s COVID-19 Vaccine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Open Magazine</t>
+          <t>Republic World</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBEU2t3bEJ0OGMwZWRRNWVVMW9QaG1NYjIwdWY4QUFWSHBZdWctbkcwdDI2Rko2M2ptLW1EdGk2cGpoQ3pFWXBncjB4STBQaDlqdHhmMU55V0NuUHA0dWsxQWhZcEZHWnllTWw2dXA1aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQM3BfaUJ2YTl6SXprLWxLZUJNUUR1QlFVeURmYUItZnI1cU9oMWN5R2dVVWtNdldnQlh1VnJuOGoxMjNDYzBiS0pqby1xX2tOMkZHM0p6Nk1FcFNqZXB0SWFkcjZWSVNCM190d1JONm5lM1VvUHluU0toSG5mTlB4RlRPZ19qYkRHWGlRQm51RjgzMG9oZ0ZhOGhMLVE3SjdPZS1HaDUzVC1UTGFSaW9iMnl0cHFhQ09yN3BzUkVRcjJITWcxRXdMRnQ5OVdkajliLVpCQmc0Nm42VVFEd0HSAeMBQVVfeXFMTkJneU13YUtYalg2STc5R3ZucC01NkJ5S1VBQ29XSzFTcEk2TmdtM1BIN3ZTSGRRU0lKSFdYTlhnR2lSTXFqdFBfN1cyRUF2eVpXNjZHakRVd3VhZS1tRnY4YlNnUUo3NE9iVmhXU05DN1oxLWRnWFhja045MUMxS1JiSWl6ai1XM3otZTJ1ejZuc1NHU2dlTngzMVFTbkl6R2otd3FuZDVjQnV3RUh4S0p3bUxTREpyVlBpZDlFWnRHWEpCVkRUSzRQMkc0eUsxaGMwNkRPLUQ5YThoRDZPcjFCYVU?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-05-2026 15:50 UTC</t>
+          <t>11-05-2026 07:50 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries $12B Organon Deal Marks Innovation Shift</t>
+          <t>Novavax (NVAX) Valuation Check After Pfizer Licensing Deal And Partnership-Led Earnings Beat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Business Viewpoint Magazine</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBZdDRfUUNvd0JuLVd0ek80U3N1eG11ZGtEbS1BenBjWU5LMmtXczdCM2V1NmoxZGRpQTNnUXBXa1o1VjQwTlBnSkhjYmthejRaNjBFWnJhZ0I5TzRkaE8tTTZIVE5HRjFTZ0hHV09ZMnRNYnhtc2N5S293?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNQUl3akM4dUJFVndFY29Lc1NjRDhhd2lDNm56dGJINUdVUTd6ZjdnRWVBOHRpa1pQMzB2cGc0ejJlZUR3aDBkQzk4aWNFRkpOS05hYlNiUFBZWkVnY1pJaHRJYlJMYVB3c3lYYjN3YzVJU2xZWEcwMDlxN2p1UVhFcWl6eHhuSkZDbUJLUnYzb25EYzZZZC1oSmJYRzFEWXdXemRPdG5laUF1ZnUtOHlablhhbXlBQlEtaFNlTm8wX1BjWlYwMUhIRGdIUFVPVFFSRUZ0dThfUTXSAd4BQVVfeXFMTnJoZ3g3TUpoajg3TENMRldwdlFDOWs4VDNIMG02dGgwamlKUEk4TUhpUTFXSEZyaFVnMlI5d1dxSXpCOUFjTjg3MTJXMjM4cHBMYlFBbFJUSFltbS1Rb28ydVJZdVQxT0UxVEVIN1JvcW9XcndCa2hITDR4Qk50X2xTejNQY0E1a0xfcm9oaGhfRWxhdU5oUThTbThocjJTcGxKZE9OeHpoS25mbE1xZ19oVmFkR0EtQ0ZTalVzN0Q0VURNaUM5dklYeGxIcXpqRDdwRE5vNm9FdzN3N2pR?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11-05-2026 06:06 UTC</t>
+          <t>11-05-2026 08:40 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Piramal Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>US FDA flags three observations at Piramal Pharma's Sellersville plant</t>
+          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ETLegalWorld.com</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPT3lOWHVPTlpEdHN6a3NpTE01ZGdkQ3RmRHhnVFhucFNsTUFlSkRSTHB6VVpuMnQ4My1xLUxZbE05QkdvODVWNHBnMzlJRFZveGdEN0J1R3pNY01fcDFodkpNVkhDX0ZUa0Y4aHpKcGxMLXdoVlZKQVNXUG04dEFZcGdjdWdGdEUtX1dnNldERlk5QW1WeVNrd1pTQm02MEhpZHBOelNuVGVBUlMyZUpWQURXSDRUWjRiUlh0bFRlYzZnRU1h0gHKAUFVX3lxTE5udGxGSGt2OThKbHZ2WmZ0SnY4bHBhVkJsZ2VqcGg4TTd2c0hyRWM2RnFtZmsxNV9FTmRDWkxvUVBlNXh2X2VCTDA1WkdLMEhQMVBLSklmOEIwMWtvbkt0Z3BqSUFYLWphRHEwQm1EQWhfaWNJdzJOS0t6VkFwRVhjc2ZyTkxTaDdHSkFhUEN3dkxoM0xvWGpZbjdsQ2hrWS1sNlUyRUg2bTlXOGU5aVh3MGtSSmVzN0ZpVjhJM3lubWFzODNXb2JNVlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNSEFPZGZOM05pZWRTYlpCT25VbHRfWkhhci12aFBZcUpKc0QwYXJJX1hJNzY4d09IdU5yc1VXZmxkQmFVcDZUTE95MFh4TTdjcDJHcS1mcjlOdVdfLUxjU2lPWnY3OEQtYllnVXFUSzMzUGhSUEpKay1nUlhBZF9DVW5qSGxsNm9JQVJON01XdHRUS1pIMzY0d0xZcUZCblk?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11-05-2026 06:55 UTC</t>
+          <t>11-05-2026 13:05 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fact Check: Hantavirus Infection Is Not A Confirmed Side Effect Of Pfizer’s COVID-19 Vaccine</t>
+          <t>Pfizer (PFE): Faces Fresh COVID Patent Overhang After Delaware Court Dismisses GSK-Linked Challenge to Comirnaty Claims</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Republic World</t>
+          <t>parameter.io</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQM3BfaUJ2YTl6SXprLWxLZUJNUUR1QlFVeURmYUItZnI1cU9oMWN5R2dVVWtNdldnQlh1VnJuOGoxMjNDYzBiS0pqby1xX2tOMkZHM0p6Nk1FcFNqZXB0SWFkcjZWSVNCM190d1JONm5lM1VvUHluU0toSG5mTlB4RlRPZ19qYkRHWGlRQm51RjgzMG9oZ0ZhOGhMLVE3SjdPZS1HaDUzVC1UTGFSaW9iMnl0cHFhQ09yN3BzUkVRcjJITWcxRXdMRnQ5OVdkajliLVpCQmc0Nm42VVFEd0HSAeMBQVVfeXFMTkJneU13YUtYalg2STc5R3ZucC01NkJ5S1VBQ29XSzFTcEk2TmdtM1BIN3ZTSGRRU0lKSFdYTlhnR2lSTXFqdFBfN1cyRUF2eVpXNjZHakRVd3VhZS1tRnY4YlNnUUo3NE9iVmhXU05DN1oxLWRnWFhja045MUMxS1JiSWl6ai1XM3otZTJ1ejZuc1NHU2dlTnhzMVFTbkl6R2otd3FuZDVjQnV3RUh4S0p3bUxTREpyVlBpZDlFWnRHWEpCVkRUSzRQMkc0eUsxaGMwNkRPLUQ5YThoRDZPcjFCYVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNREdLdkZPRFF0RTdNOE0xc3Y4b3E5dWVPb09fa1JPZnlXZ1lPMGxRd08zVE9ycTk3SkgyaXpvN3FwdUxDR09udzBZYWhNck9hVHBmOHhBdWpFVWFhZlZ4RnhZZEFQTjRoQXBLVDVZNUt5QTFqRnZwbTU2SE1iXzNvNVFMcm1TRHNwRmJBTUxPU3RrZzdXSVFOOFVmNHY3cmlGVnhhNnVzVFpCV05McXE1Ykl4U1pZZTRsMElVT3cxMGRpTm5PTnRHTHo2dlMwMWg3cUNiRA?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11-05-2026 07:50 UTC</t>
+          <t>11-05-2026 07:04 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -981,39 +981,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
+          <t>Pfizer Strategist Andrew Baum Shifts to Senior Advisor Role Under Bourla</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24/7 Wall St.</t>
+          <t>thekeyexecutives.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOSXdkOUZGSTNfNEFfNTdQcVdFX2NUWHRIdW1wMVZUVmY5b09BUThCcHRxdk9VejU5elh6NWhldnl0WnZCRzU5ZGJVVEllempCa1NVY0dmaG1yNVhPazh0Rl8yaGIzanJQMkN6Mzl6VXdaYWI5aHREU2tOX0JZbU1jeE15ejZ5QlNNelVUMjZlOEp6NWVXQUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPc0o4ZFNrT0lNZ05QeWdoNTRESU14MjRXRl9IYnNuTlZCMzhaUnEwNkowWXVsVWZNQ1RzSXpVNFE5TGg5MUFwT2VsUnh2TFluMzhXRmE3SFpXMUpwLVBZUXdrSWIyWlN2WWo2WFFSaEJwekVmT193ZTNwNDhHV1A1dVdyTmhGU3R0T21GellrNktLcmdNMUdIcm4xeG1jakl4cVRQaDZ6bnhHX3cyNGY1Z251dENGTjY5?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11-05-2026 13:05 UTC</t>
+          <t>11-05-2026 08:00 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Novavax (NVAX) Valuation Check After Pfizer Licensing Deal And Partnership-Led Earnings Beat</t>
+          <t>Should FDA’s LEQEMBI IQLIK Review Delay Reshape How Biogen (BIIB) Investors View Alzheimer’s Strategy?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1023,76 +1023,76 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNQUl3akM4dUJFVndFY29Lc1NjRDhhd2lDNm56dGJINUdVUTd6ZjdnRWVBOHRpa1pQMzB2cGc0ejJlZUR3aDBkQzk4aWNFRkpOS05hYlNiUFBZWkVnY1pJaHRJYlJMYVB3c3lYYjN3YzVJU2xZWEcwMDlxN2p1UVhFcWl6eHhuSkZDbUJLUnYzb25EYzZZZC1oSmJYRzFEWXdXemRPdG5laUF1ZnUtOHlablhhbXlBQlEtaFNlTm8wX1BjWlYwMUhIRGdIUFVPVFFSRUZ0dThfUTXSAd4BQVVfeXFMUFJrZFA3TUpoajg3TENMRldwdlFDOWs4VDNIMG02dGgwamlKUEk4TUhpUTFXSEZyaFVnMlI5d1dxSXpCOUFjTjg3MTJXMjM4cHBMYlFBbFJUSFltbS1Rb28ydVJZdVQxT0UxVEVIN1JvcW9XcndCa2hITDR4Qk50X2xTejNQY0E1a0xfcm9oaGhfRWxhdU5oUThTbThocjJTcGxKZE9OeHpoS25mbE1xZ19oVmFkR0EtQ0ZTalVzN0Q0VURNaUM5dklYeGxIcXpqRDdwRE5vNm9FdzN3N2pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNU21MZ1FwejFnVUF3d3h2dWR4Sjd3SGFUVG5OZXNrbDJyU1R3QVpWUFhkbzFub2otems4ZW51OEl2NWRVUkVvMkp5Qkc3ZDBqa1ozMFg1aVN5clZoTDBtVy1jeGVPXy1vNGpfM2ViVGRqWlZSMUVhbzNVTVlTNkpVeEdmM3Nyc0F4T0Jncl9pVXZXOGUzcnVwVG5QTWF0RTBUa05lcVdrZEpRalNtMWJETjBwYWs2TXRhM2NwLUV6NVRoYmJaZUl2cE0xT2hHN2ZlQ1VzWWdxRdIB3AFBVV95cUxOWlhVM2FwX1VKR2JFc0pMUm9NZVBuamdwaDhTVVBIREJNcGNOS282UVUwWkZGbGNxNHRZUk1sQXRGb2JuWGYtUFNYemxMNjY5Y3FWamJqOTNOV1ZoT3U1NGhiSUh0S09wQTUxS2dObThwX0dKM1d1TVlSRlA4N08yYVRlZmtGR0h0UjNFYm84enRNVXRmbHBOMGZsZS1NRUItaWQxNnFJTllkWEJoRWFEeldfM3VIcHdJYmhhUWVob3FPbnZSclp4Z1dCMDVPRzQzNmFvQlVtenA0UjI1?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11-05-2026 08:40 UTC</t>
+          <t>11-05-2026 16:56 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Stock; Edges Lower as Investors Weigh Ongoing COVID Franchise Pressure</t>
+          <t>WATCH: Longford siblings with rare disease who 'don't have time' issue HSE plea for drug</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MEXC</t>
+          <t>Ireland Live</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE05enJBdV9aXzFpYkFEck04UGp1eFprMVFwNGhta1VmaVE0RzFGQUxWQ1lndlBDeUdoSUg5ZWI1VTh3Y0Nsbll1Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNbVQ3YzJUcWNLVHBUa0s2UkxQSFh0eUJRSVlpMUN6bDM2dTFzUzdHN1RhenpUREQ4SHBZOHJoMG5HRjdkdC0xNjY2Qm1DRUNTTjhPM0NJZDg2MjcyQ21WYjMwX3RtV1BSYkdLSWttWVgwd2M5cVpZVUw5VndIZlp1cVFIaUUxMjRaVW1naUZ5Q29nZEd1cEx4aE80RkpRYlY0dHRrU2xWNlo4dHBNMmxKSjdUbkdQd0lidVdLdzI3ZjVhTFlCQW5Sc0twdk9oTndnTlMtTU5kVjVyTzRDZ2RF?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11-05-2026 11:29 UTC</t>
+          <t>11-05-2026 17:41 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pfizer (PFE): Faces Fresh COVID Patent Overhang After Delaware Court Dismisses GSK-Linked Challenge to Comirnaty Claims</t>
+          <t>Dr Reddy's: India Strength, New Drugs Offset US Decline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>parameter.io</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNREdLdkZPRFF0RTdNOE0xc3Y4b3E5dWVPb09fa1JPZnlXZ1lPMGxRd08zVE9ycTk3SkgyaXpvN3FwdUxDR09udzBZYWhNck9hT3BmOHhBdWpFVWFhZlZ4RnhZZEFQTjRoQXBLVDVZNUt5QTFqRnZwbTU2SE1iXzNvNVFMcm1TRHNwRmJBTUxPU3RrZzdXSVFOOFVmNHY3cmlGVnhhNnVzVFpCV05McXE1Ykl4U1pZZTRsMElVT3cxMGRpTm5PTnRHTHo2dlMwMWg3cUNiRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPRklpbDYwNEg5bnNNclAyQTRZZkpRRUtybjd1c1FQY3h4cGw2YmpoVm9CV1JBY3gxa0swWUtCellwbC1RNTNfWkhBSjl4T0pZVFpkMXVTQXRMZmVGTnZneC1idWZaSkpGS3h6UnZkOXJuNElhMFJpOUVDX2tPVzlaNWROTjZJWWluRkw4U1hSYTQ3Y2swZ0RVdEpuQzhlMXBRbk95c1hCeGI0SjQtalFKX0hDcHlWT3NvRnVWNEl5dk9oelg1NnhMWkdPVGRVUXFS?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11-05-2026 07:04 UTC</t>
+          <t>11-05-2026 09:09 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1104,187 +1104,187 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pfizer Advances Oncology Portfolio While Extending Vyndamax Cash Flow Visibility</t>
+          <t>Dr. Reddy’s and Nestlé Health Science Introduce Celevida GLP+ for Diabetes and Weight Care</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>This Week India</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmxSaTdmOHJESG5HaGh3NW5TUWZyeWJsRjlTYkhEbXhOdXZkVVU1NlQyQjVrMWJweE1uQ0dQUm5mNzVEcnRSSEJxeXpndGEteHdudkVrVXdxNWRNLVV2THI5d0RKTU91NzZvbExyUl9fc0RQcnNWd0NuSnN1cUZ4MTZwaVA1M0wtMG5FMVYtVDFjSV9rbHdBREtqUnNPUWJORU1nVXdEQ3NFVEhjU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeXJpLVBheDJsQmFWVjViaTZUai1mUmdtQXE5TS1lakE0VEdTbUVuMlV2NWtad0hYbko0UmdsbnNFTElNWURDV0dxYllhZFFRR2VMc1JFRzlrSlhNenB4WkdQbXJoMUFYMEp5Z2hKbkd6ekFlUE9qbk42VmJoM1NZVGVSLXZSOHRvWHdmVmtybW5XR2tSUHJGZ3d6X2hGUmt2eEhBcGdRTHFMOC13cVNLaXR6ZTNuUQ?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10-05-2026 15:11 UTC</t>
+          <t>11-05-2026 16:39 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pfizer vs Moderna: Only One Pharma Giant Is a Winner In The Post-Covid Era</t>
+          <t>Biocon arm gets Health Canada nod for fungal infection treatment injection</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBUUlNVMmVOeE82bDdjNDdadDBSb1ZIV1dVUVBLaEpMTHRFclVVU0EwYXlBNG40STNNSDZNcEVlN0xLOXcxVG41WVBMczd0c1FPX3RvdzY4QlJ3a1VvZjlPUDVHYVplUlRKbjhTVGtfdFIzcXExRzFKakRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmJNQTk3NzFnUjZTamc0NDIxLWl4MkR2aDlScThjcHNHM0NPRjFXRHlaZmNhN0d5X0JuV3duZEZEb3o0ZDNUcko5eEs1bVVFTkowVnkwMXJYVkRUWHZEd19EbjBQcTRJSWF5a2tTVEZ0cnJNM29IZ3l3anZDRFltajE3emNzSjZrblcyWUhQSl9uOGIxMVB5dU5lMDVwR2pOX1dPTHdNcGVQRTVfQS1QUFRyXzZUei05dW5xaXlGSFE2ZGRhZjZKd0twZ2RGSlZHdmRzRFkxQU5iRDRLMkRjYUNCeVZwYjVUMFlPVTRNclVaTlVDVUNBak53cnpFOF92VVHSAYcCQVVfeXFMT2pTakRkWU9KNlZkd3R0QXphcXFOWWx5X0ktT2xMMHBzdFgzNmMtY1MzcFhSYnFPZGdBbUNyMmZkRnNNMUZRdE9LajBySFRrYm9QNHJqazExZVFRLUJjTXF1ODUtY1laVlJabVYyRjFqZFVwTk9jLXVNZGZIbldwYWEwX0FldXlfNnFMa3huOEhQRE1DWnFibFREd2s5UGUwTVM0NmM2aHZIWjAxNGhHZjM1NDIwM285dnlMSmJRR1FENWVqVmJ4OU9ycGQ0ZmFKREpfVXlsbGN2cWdta0RBWUtyZlZjOWFyeGtwekEzWlYxaEU5bC1PcElPU3NDNEVGTUJuZWxtMnc?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10-05-2026 19:53 UTC</t>
+          <t>11-05-2026 05:33 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Surpasses Q1 Earnings Expectations, Reaffirms 2026 Sales Guidance</t>
+          <t>Biocon eyes in-licensing deals to accelerate biosimilars growth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPdG1kSm1tR3JiNVYyVEJZVDJYaXlJUlY0OXFaSUFjM2N0QUpxaldaVW9iSGx0b21USmRualRuMGhhTFg4YVE1bGh6bVU4MzY2ZEJhQjkzaDVqcFhDaklvVE8yc1llVGhqZG5WYzVyYm92ZUJYdDJCVTU3dkhSUDNDekVBTk02MGltNldIRU5xaVpmYmNGUUlKUTd4WU1MUlhzMWhIeExGeXBwbHpmRkg1cTZaVFc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOd2RZemZXcl8yUTRZbm82QXRXNkpXdmVRS1B2Smk2ekdtVF9wR0Y3NWE4NzRvV1BMZ2FVRmM2Y2VNM1BuOTJtNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UdIBwgFBVV95cUxOd2RZemZXcl8yUTRZnm82QXRXNkpXdmVRS1B2Smk2ekdtVF9wR0Y3NWE4NzRvV1BMZ2FVRmM2Y2VNM1BuOTJtNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0ozaGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10-05-2026 14:26 UTC</t>
+          <t>11-05-2026 09:47 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apellis set to report earnings ahead of Biogen deal closes</t>
+          <t>Watch India's Biocon on Generic GLP-1 Push</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Investing.com Nigeria</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNdTNDWWZ6VXNYN1pqaVZvQURxM2NSREFYVlBjVlFSR3ktRk15SVdESWpWRzhmeVZrLV93d0NqU0wxUFBpRmdNQ0YwLWgwSVhjRDM0QjZnc1h2VFd2eXJzaXFzdmFBd1N0WVZ1bFlkaUZGX2hBTmtMOUJja1laZDZkMldWVjVyeTZJbzZrY2xrSVBwVDh1OG5aMUozci15WlRVQ1VfSk5oSjNSVTU4QnVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQell5ZjBUZUdtVHEwX2pteVl3SmV2RFEzVkNrRmtHOVhORmRCczNaZEhlRV9jSW5CbmNBSzllYnhkVmhEOGNGcjNlSy1rcVJBa2V3UXE2ZlJsay1xRk1Lb0F6eWxWNEZoUWNnSFFUSFhCck9tX3NfTUtfNjMzeW5zUThycU9JQVdBLUZmXzdNbGcya0pMRWc?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10-05-2026 13:41 UTC</t>
+          <t>11-05-2026 00:00 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Biogen: FDA Delay on Subcutaneous Lecanemab Seen as Timing Issue; Hold Rating Reiterated with Unchanged $203 Price Target</t>
+          <t>Kiran Mazumdar-Shaw On Claire Mazumdar &amp; Biocon’s Future</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNQzNsenViTVBUb05nZXBHNHVsNEc2cDNLOHZocFV6V1pJaEE2aG8wYV9oRTQzYnhpZk4xNEJ4bExUS2x3Y1ZmNklKVFRtbWVSRWFEZHJkMFoyaUZkOVZIcWlRSGZRMVp2RkhlRTNkS040b2RxaTk2Ym1OVUVWTEdUTXpRSkVfeENkQmFfZnBTY2lyZFlzR2RfM0Y1Mk9HQzRIUFpJbHpmMWI5b2FwVllrYzAtc3FNcXpfNTZ4QVNHZWVyQ1lnbjl1MGNVSHM4Q0hBeTZlTGlXS3J1SmFYQ3VKamgyQXd5ZnFxTmVhVkJjcG5QTURLOGxsM1U0NDZZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdW1qUktleWdJVlctbXdsamlBNUlmN1JyUVRraVhqQVRNT0x1eXp0bHEtSEVDUlRTcndrejFUbzE1X2l6dmVzZlBfRHBDdlhDaXpVSlkzNG9Kd1BUSE41M3ZXUlEwSmJlM2xOclJNdnZuSjc5WEVRNzVjYnNXRGhZMVVQZ09kZXZ6QTVHWW13d0RVQ3JJZTROVm8wSnU3MS0wNWFubTRwSC1fcFQzbUpjbmJyQkptS2JCR3hRTEZOTmFQWFZa0gHEAUFVX3lxTE11bWpSS2V5Z0lWVy1td2xqaUE1SWY3UnJRVGtpWGpBVE1PTHV5enRscS1IRUNSVFNyd2t6MVRvMTVfaXp2aXNmUF9EcEN2WENpelVKWTM0b0p3UFRITjUzdldSUTBKYmUzbE5yUk12dm5KNzlYRVE3NWNic1dEaFkxVVBnT2RldnpBNUdZbXd3RFVDckllNE5WbzBKdTcxLTA1YW5tNHBILV9wVDNtSmNuYnJCSm1LYkJHeFFMRk5OYVBYVlo?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10-05-2026 13:39 UTC</t>
+          <t>11-05-2026 08:07 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Q4 Preview: Dip in revenue, net profit likely</t>
+          <t>Indian pharma majors commit $19.1 billion to US expansion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnA0SXA5RDR1VmlnLVAxclB1NXhRUXpOaHotbG40MlBrWVQtOVRVUVNyYVhuc3FEWHdSNDZrU0dXNWxNNkJwWGt6cUV2WGRLYnNTLXlCTExrTWI5cUo1SHJ5ZDhBR1ZMRUt2Ry1wWjVUTm9ndkFUVkVlNWJJV1ZuZHBiXzMzLWZwRjhkbWgzcXRRTU5ZQmg4Ym50dFN2V3N1ZUdRWk9WTi1RWFFpMkFzRVh3NmhjQdIBvAFBVV95cUxNY2RVaDRDZ21lQlVrWWZEdHdWUVdUbFNwYzBqZ3JzbWpFSU1nb2ZYbTR2Y1BRZm9vNTBVRS12dHFQZmhzN2M4YTg4TjdxNi1ycm42cTBrUkFKSTUwcG5OWVRJN0UyR20wd1BVQ3V2aWRaakowcGJNY09BdWRKTEwyenNzWGR4N2QweGVXRDBnd2p0MllKQnBIdjRfSXNGdmxhYm1XUTFWa3lXNzBxOWRrdWNDUUVISjlXQ012VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOZmRyeFRDbDFiYklqTmNqNE1QckpBQnVodFBqeUd3enN1c0ltcS15WUpvcWVOMnVrUUNrRUtkOFloZ0Mwd1UwNk4yblR0R0VtTkhtY0tFSUNVT2d6Qm9ZTzlBUWxSeVB2S3pJd0lZUkNOTVZDem8zVEg4blZLSVUwTi1oUFV2a2p1WlYteXk0eHF2RVl2dG56cE9ON2ZJbTZEaHc?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11-05-2026 10:41 UTC</t>
+          <t>11-05-2026 10:17 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1296,59 +1296,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biocon Profit Falls Despite Revenue Growth | News</t>
+          <t>Zydus collaboration lifts Agenus (Nasdaq: AGEN) to Q1 2026 profit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNV243eGlIUTFyZmNWTVp5QlhYMGpnbXJJVklBV3VtenJRamFOenJhcnhlMUlxcGlNYzBhRGNJSzJBV0RBcEt6cDFvVlAyZmI3THkwMkl1Znp3ZFNBc3hVaFFLVkxsRm4zaF9JbHp2S2dhbWdFa0VpMTNPQm9EcS1UcmlXaFNiUlN6and0clZHWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbHd5VEFOTk5FVHpDRWZicWx2SDNTUTZSZk1kd3dKTmFWUnU3RVlDVGFaT3dzd3NHZlFsN0ZZSXI1TFZqT1gwQW5ScEY4OHRmTGQ1dmFibEFxdTdMQW5uSjBreWdiVmFOd1NpV1Q0X3lTRExuRndNUnpjMVBoMEdoT0xYWjM5dnE3WmZqdndoTmJKWjFOOE5jbnFlekRSM0Z4?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11-05-2026 11:11 UTC</t>
+          <t>11-05-2026 12:52 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Biocon eyes in-licensing deals to accelerate biosimilars growth</t>
+          <t>Daiichi Sankyo targets global top 5 oncology rank by 2035, $1.3B efficiency drive in new 5-year plan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0o3aGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UdIBwgFBVV95cUxOd2RZemZXcl8yUTRZbzZBdFcySld2ZVFLUHZKaTZ6R21UX3BGRjc1YTg3NG9XUExnYVVGYzZjZU0zUG45bTJwNTJjcmNLNl9VWHVHaS1oQVJzb25XVm1ubXZKQnlLUFVWMEs5ZXFQUXpacEJjS0o3aGFVVm05TDB3WVVGYnNRRU96MTJsQXllZ1NSVUk3Ykc0bmVpaDA4SG9ESVNrRWtWX0MxazBUWDNNaDd0TjlVOWkxMU44Ti1iSFQ0UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNdkpSNE9GbGRxNWxvOVZQaTdQQUxSYVBhZzlqSWNvRjhTX0gxaWFoVHRGbjJIVHpwM1F6U1oydE5aRkZQQWlueDVzekQySVI4SElvNy1VSlBuMFVtVlNtMW1IblJBOW5zX2szbW1IWnpJaTNVbGFJN0FHeS0tRXVNV1YwT1lua1VHTDY4MjN4c0ZqajQ3U1NPQnBJM1RTc1FheTRqRmZPUndlWkE4aFB0VTZEZUU5dS0yelNIS0VtdU5wWlphTmc?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11-05-2026 09:47 UTC</t>
+          <t>11-05-2026 14:22 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,928 +1360,224 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Biocon arm gets Health Canada nod for fungal infection treatment injection</t>
+          <t>Daiichi aims for $14.6B in oncology sales by 2030</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmJNQTk3NzFnUjZTamc0NDIxLWl4MkR2aDlScThjcHNHM0NPRjFXRHlaZmNhN0d5X0JuV3duZEZEb3o0ZDNUcko5eEs1bVVFTkowVnkwMXJYVkRUWHZEd19EbjBQcTRJSWF5a2tTVEZ0cnJNM29IZ3l3anZDRFltajE3emNzSjZrblcyWUhQSl9uOGIxMVB5dU5lMDVwR2pOX1dPTHdNcGVQRTVfQS1QUFRyXzZUei05dW5xaXlGSFE2ZGRhZjZKd0twZ2RGSlZHdmRzRFkxQU5iRDRLMkRjYUNCeVZwYjVUMFlPVTRNclVaTlVDVUNBak53cnpFOFl2VVHSAYcCQVVfeXFMT2pTakRkWU9KNlZkd3R0QXphcXFOWWx5X0ktT2xMMHBzdFgzNmMtY1MzcFhSYnFPZGdBbUNyMmZkRnNNMUZRdE9LajBydFRrYm9QNHJqazExZVFRLUJjTXF1ODUtY1laVlJabVYyRjFqZFVwTk9jLXVNZGZIbldwYWEwX0FldXlfNnFMa3huOEhQRE1DWnFibFREd2s5UGUwTVM0NmM2aHZIWjAxNGhHZjM1NDIwM285dnlMSmJRR1FENWVqVmJ4OU9ycGQ0ZmFKREpfVXlsbGN2cWdta0RBWUtyZlZjOWFyeGtwekEzWlYxaEU5bC1PcElPU3NDNEVGTUJuZWxtMnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE40UGF3RWRNUVhyRk9nMUtsTDF4SGNVcWdJTy1iTkI5WnJxakE5UExDZzdOakVqWjYyY1g3WjlLV2RnQUtNLXE2OHF0ampDRWM5VmE0?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11-05-2026 05:33 UTC</t>
+          <t>11-05-2026 18:11 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Watch India's Biocon on Generic GLP-1 Push</t>
+          <t>Polish pharma firm moves to acquire Romanian drugmaker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>TVP World</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQell5ZjBUZUdtVHEwX2pteVl3SmV2RFEzVkNrRmtHOVhORmRCczNaZEhlRV9jSW5CbmNBSzllYnhkVmhEOGNGcjNlSy1rcVJBa2V3UXE2ZlJsay1xRk1Lb0F6eWxWNEZoUWNnSFFUSFhCck9tX3NfSUtfNjMzeW5zUThycU9JQVdBLUZmXzdNbGcya0pMRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOR1FvZjVFYVRDZFNwYnJURERMZzhnVmhMLUJNVXBqaVEzR0dENGNEQ0h6OEFhS1hrSF83U0c3aWZBMmlZWWVqbHBzWEhlWDdVYUZadjZZcnd3TE5obVVfME9JejgzaFZqaXRKZS1DeGVselZHcVNrVldjZHAzb1hQdEFiYmJ0QnRPV2pERWUxbUw?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11-05-2026 00:00 UTC</t>
+          <t>11-05-2026 06:24 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Natural Biocon Standalone March 2026 Net Sales at Rs 0.88 crore, down 34.99% Y-o-Y</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Nutrition solutions gain traction in US market</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPZTVVb2I3dndmMjM1Nmh1d2Z2Y2RBbTgxWGQ4TVdNbWw5d1VWbnZ0T3hqMGxSdVpISThUU2x1Um5ySDVfQUdtM2pObDJYUHlMMEVDeDE5M1pEel9BcXdVY0pKTTdTTnB5a3JhZWRaTWt5RjAwNGtldWpScmJKYmoybTJzVkRMMGVtdlBHNnVLSkwzZjAyaGZxR1lFNDhocU9GR1kwN05kQkc0M19XTlQxZjc4NzZUNlFNbnBNTVhnTk13M1JJVDRjTFV0SGZjU0huMFp6dmhTUzJBd2U4eHNZ0gHkAUFVX3lxTE5EZ2x1YWtFMmpBQ1dSODI1c21uYU12ZEVsUFFVNnFWOGdaWFdHU1ZXMGhmVmg3X1U2TTh2VHhZdHhuWFl4OU13dnlmYUlDRnJfMVppelNqTXlGVWhSTEFXci1pSG5VQnNRMUJsOWVNUmxvaDg2UE1ZNTJMbTdpN0xJRTN5RzRpMDhha0g4OURiUXM2OWE1MjJnX3lGUXJ6V2FRVFRtLTBhNkFmWGhmLVE2Ymp4V3Y0NURESWZqbUhlX3JDcXdLSmF0M29WcmtXOFpLNGpWWkZtXzBnMlpHM2hLeWUxTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPNjFFMUlScnlMN2wyNEtaRDZFRmpMZnRQOTZINE4zTW1SSWRPSHU3UDVUa0ZMVmZSUDdLR2hFUThBYjl2YTlLUnByZ3RzOV81SEVhdDM4T0VGM09XRXNOX1doNml2WU0wcnZ0RWZzdWV6blppRmlQM0VmRS1WZTlPdmhIT2N0d0pqdEFBVUFYNkpHbUZDcXQ3bU5YSTExNGZxX2lIYlljcU5yNHlHbDRsV0pHYi1SVlpiTjd1MVVZcC1jTDBUaHc?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11-05-2026 05:17 UTC</t>
+          <t>11-05-2026 11:29 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw On Claire Mazumdar &amp; Biocon’s Future</t>
+          <t>Hansoh Pharma’s B7-H3-Targeted ADC HS-20093 Granted Breakthrough Therapy Designation by NMPA for Esophageal Cancer Treatment 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Minichart</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNdW1qUktleWdJVlctbXdsamlBNUlmN1JyUVRraVhqQVRNT0x1eXp0bHEtSEVDUlRTcndrejFUbzE1X2l6dmlzZlBfRHBDdlhDaXpVSlkzNG9Kd1BUSE41M3ZXUlEwSmJlM2xOclJNdnZuSjc5WEVRNzVjYnNXRGhZMVVQZ09kZXZ6QTVHWW13d0RVQ3JJZTROVm8wSnU3MS0wNWFubTRwSC1fcFQzbUpjbmJyQkptS2JCR3hRTEZOTmFQWFZa0gHEAUFVX3lxTE11bWpSS2V5Z0lWVy1td2xqaUE1SWY3UnJRVGtpWGpBVE1PTHV5enRscS1IRUNSVFNyd2t6MVRvMTVfaXp2aXNmUF9EcEN2WENpelVKWTM0b0p3UFRITjUzdldSUTBKYmUzbE5yUk12dm5KNzlYRVE3NWNic1dEaFkxVVBnT2RldnpBNUdZbXd3RFVDckllNE5WbzBKdTcxLTA1YW5tNHBILV9wVDNtSmNuYnJCSm1LYkJHeFFMRk5OYVBYVlo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQVndGUXVlUHp3ZUp2UUNxNEd3X3NOTGdoWG05aWxNT05SZzhkWDI2MHFxR01yNi1IZVZya0pVSjY0enVMZjZwNWhfRGkwY2cxcTI4cXJJQW5neVNDdEZyV3hsTnlmRlVCeURhNDNGaEVROUFJRlF1WHA4ajZHWWx6X1NPdllrOEItZnBySHlHeWhneWtfeUcySGNLc1VXQmdJWkl4Rm41c0Y2emFlWkR0eHFzV3FnR2h6V1NWT0JuZHNNRGxuT214Q05obE5yZVBZUDhSY3BCLVpqRFY0Y0UxZnQ2QUtQemhzVjZDcUhKNUpFLU5MQ3VWSkJ3?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11-05-2026 08:07 UTC</t>
+          <t>11-05-2026 03:03 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar-Shaw Reveals Biocon Succession Plan In First Interview After Announcement</t>
+          <t>Alvotech (ALVO) Is Down 7.4% After FDA Form 483 on Key Site Inspection Has The Bull Case Changed?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQZ3NNMU9HVjlPeEFlOHRyYW9BRkVlaTNWLVB3V3VSc3NHeklXVzBYVTgzUDVORFFCNk5ueENHVUozRndVbG5KQkhwTEFRN2lxNk01SHA1dFBqdTJtVDJLRG9lazQyUEpSaXhmOVB0VlJIeEsyTkxMbjU4U2pvdVllQm1CTW9yNmJvLXF1a3BqQWRnamU3ZFF4YXJzWnZQZ1Bhd2ZrbXQxaExJS0ZjMmliX1VoTUJqaF9wRVFsUlNLeWh4dTRlakw1WGVOa2txeWRTYUlMY0luQ0hGdDZoaTVEMHhRYnZ0VDh1WUdFbnc3eEJnbzTSAfMBQVVfeXFMUGdzTTFPR1Y5T3hBZTh0cmFvQUZFZWkzVi1Qd1d1UnNzR3pJV1cwWFU4M1A1TkRRQjZObnhDR1VKM0Z3VWxuSkJIcExBUTdpcTZNNUhwNXRQanUybVQyS0RvZWs0MlBKUml4ZjlQdFZSSHhLMk5MTG41OFNqb3VZZUJtQk1vcjZiby1xdWtwakFkZ2plN2RReGFyc1p2UGdQYXdma210MWhMSUtGYzJpYl9VaE1CamhfcEVRbFJTS3loeHU0ZWpMNVhlTmtrcXlkU2FJTGNJbkNIRnQ2aGk1RDB4UWJ2dFQ4dVlHRW53N3hCZ280?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNSC1Kd3B1ZlZSakJwak9WTF8xU09vZ3ZuU3N2Y2N4VFVoeGxRdFVlRkFFemZrS3pWTUtBMzBqdlFJaDFMV044SXo0bE5fTXk1U0xZbEFzMk42eHA5Mnkyam82R3NGLWdrcS1wZXkya202WmZlbUluaWp5ZGp0SUpld3lNWHpreXhEbzlwOW13TG9CUzJ1RVRVbURLYXI5VEZMMDc4LUdmRy1DWWdacWFINDBWcng0eUM5SlFuR1BQb0JZVzVEcXhGZUlBV0xrQ29LdjE2YkRBNFBhUdIB3wFBVV95cUxNSXYtZ0pWbWFmX0VZSGtSMUxqV3JrQUxBYlpfS3pvWHhsNXRaSzRYTjdMYUI4YXdEZTY3Y2tpVXpNaEkxOEVKQVVKdVloTjFVWHZpNkp1VW1qS1Z1R25YOGkyY2l4SFo3bkJPUGF5RVlFV0NiZ3B0N0d1d2tIOUV1X1l4TE1KdUVuWmpWcjNXVmN4ZXdVc3U4amtUeHdsR045NFppaHp3WGZIZnBmUXJDaGkzeDVqWXF1ajFwbHdHck9BNHlMNk9IcDRIeFNyMEpocWxtdHdzNnk1WFRTaHRn?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11-05-2026 07:48 UTC</t>
+          <t>11-05-2026 17:34 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indian pharma majors commit $19.1 billion to US expansion</t>
+          <t>Teva’s CNS Portfolio Is Growing, But Valuation Is Stretched (NYSE:TEVA)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOZmRyeFRDbDFiYklqTmNqNE1QckpBQnVodFBqeUd3enN1c0ltcS15WUpvcWVOMnVrUUNrZUtkOFloZ0Mwd1UwNk4yblR0R0VtTkhtY0tFSUNVT2d6Qm9ZTzlBUWxSeVB2S3pJd0lZUkNOTVZDem8zVEg4blZLSVUwTi1oUFV2a2p1WlYteXk0cXZFVXl2dG56cE9ON2ZJbTZEaHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPbG52RlhSOTlUMjVFVTlYNHk0T2tMWThSVGFIWnRIVlFfUzFOZk5nQ2k1dVVBVlpEVm1NMXJ3clNOT3lGbWhaamJ4UlRSOHd5dFVnbUZfU2NjaUpmQWg1c2JDNnlibXJKZ2ZWVExNenI4SDlkejhacWN1OWNHeXM1cndGTG9LeUNNaHdveWxwd1J0ZWdORWYxNGd4RGZBQQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11-05-2026 10:17 UTC</t>
+          <t>11-05-2026 12:34 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Global Oxycodone Drugs Market Size to Reach USD 9.21 Billion by 2035 – SNS Insider</t>
+          <t>Russia expects further growth of generics share in domestic pharma market</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GlobeNewswire</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPa2lWVGNmRTZkcDNjQ2piOXRPWWRBSC1VcFdlelM0VHhRV0h3V21TX0dkVXRLWTNDRVppMXB6YnVnXzUzY0gtc0JiS18tbGdTT0NLYVlER0hZamFKX2I2TklHTUJwbk5GOE5vVXdob3NTYnhyQlpVRVM0TUJsWTVRN1htTnVhbnBWSXBtMzEwTkl5ZzRpY3lrWWIxOXVTWk02VVlic3A5VlEzV0pyVS1YZGRvZC1aXzkteFVUUzVXVkJaakZYWkZKZzJqZjFUZEJHMGNIRWNvTnJGVVo1enY3cTcxaHdZR1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPUldZdGhhRzV4blVlS0NXWlczS0s4OTFiQ0lKTHRkcmJwemlnT1V6cFVhYlcwQmhyVzlYdDhoWmpsMzdpQlNOaXhpQ0kzZE1rLUhaY2NFbHotMGIxTXpQNlRua3MyQTJtNW1OeDZ5elVjMnNzelRvTjc5R2RQUlJDSm04M3RpbjNOYWJ6blpwcm1XdmVsZktKemJlSFBPUEtPWVQ0OUhESnE2QlVUNDJKbTZfY1JJUzBmTWIw?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11-05-2026 12:29 UTC</t>
+          <t>11-05-2026 10:17 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Zydus Biotech</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Zydus collaboration lifts Agenus (Nasdaq: AGEN) to Q1 2026 profit</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbHd5VEFOTk5FVHpDRWZicWx2SDNTUTZSZk1kd3dKTmFWUnU3RVlDVGFaT3dzd3NHZlFsN0ZZSXI1TFZqT1gwQW5ScEY4OHRmTGQ1dmFibEFxdTdMQW5uSjBreWdiVmFOd1NpV1Q0X3lTRExuRndNUnpjMVBoMEdoT0xYWjM5dnE3WmZqdndoTmJKWjFOOE5jbnFlekRSM0Z4?oc=5</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>11-05-2026 12:52 UTC</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>"Confirmed Infection Within 20 Minutes" Celltrion to Launch COVID-19 Diagnostic Kit in July</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>아시아경제</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPWk43Zk9VLXlTdENJWGRRMWhOZUNJWkRzU2NHOFdNUnVPeGd0NlZRRVI0S0lsTnNkeVBiVzYwNk9nZUpTYlVTcmZhOWZWMEw3dy1xM0hPYUthQk9uRGp6SEpVYktha0hCVHhobjYxeWlLblo3ei1vdXE2Q0tkbWduWHFybFZueTNVRUIxUHprRFJNUS05NUdOb2cxUk9tT21xd0lDOTI3cVRKR1FRMl96NXFDaGtSSWZ3bkpPT1JDaVVoOWZiTXRBY0JBa29BQjhtZTV3?oc=5</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>10-05-2026 15:04 UTC</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Japan's Daiichi Sankyo unveils five-year business plan focused on oncology innovation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>BioSpectrum Asia</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPdXFRYlJJUEZWV2w1U0djSGpHMFpGWmpSSnhnVktadVUzdW5HVy01WHRVWHlEMUplNkZpb1Y1Mng1eEl5b1F2dVJvb1VxOElyc0ZNSVJrZXJ1ZXJQcjJCSWVkS3I3a3lpQmZkQXdjaHpoak1DZFhKdUVvSndwZ2I0NFoxN05lYWJoNUNIeXdaNE1QTVhmci1OM3drcGlQQldhaE1hLXE0SXV1UVJRWEZ2MXNpcnlzaXFnMldNMVh6d2NLZVJzWFRsTF9zSUhFVk4w?oc=5</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>11-05-2026 07:23 UTC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo posts Q4 revenue growth but reports operating loss</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Investing.com India</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNYkJIbzNZNDR2TXdYUkM0SHZfNEhZY0tCei11TGZTNjVWSF9vT1VnNTVlWEFhRnBQLTZnMURxa2o5VEQ1TkUxdGFuQmpPOVhKeklRNHhnNFFQOVFnZ2lwYW16TW42QjB6MUFTLU92VjFXeVdzVEE5TnZZaUhyUlU1N1NpQ25BTnRQaGdxN0pZcXlINmpqWk5vM2phYk95c29SaEpBZzlxT1JsZTRjUDZIWEdJMzNfdHNs?oc=5</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>11-05-2026 11:26 UTC</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Daiichi aims for $14.6B in oncology sales by 2030</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>FirstWord Pharma</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE40UGF3RWRNUVhyRk9nMUtsTDF4SGNVcWdJTy1iTkI5WnJxakE5UExDZzdOakVqWjYyY1g3WjlLV2RnQUtNLXE2OHF0ampDRWM5VmE0?oc=5</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>11-05-2026 06:55 UTC</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo's Attributable Profit Falls 12% in Fiscal Year 2025</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQVkNVMWJDLUVqTHk4azlzdmhWWkhZWU82ckZlTWN2ZG5UVkgtZ3llakdlRDA4YndKRU5jcDZJSm5vN3hsMm55UzdCMlZLT3RYUEJRRXkyQTA5eHJ5d25kdEV0RXFicmpFMVbidmhzUVY4TmxfZDJkdU1FQTZHbm9KY2NVb0Z0dmd0R1p6ekRlR2U3WlBOSXVSYXhMNmxnNFdENnZ1UERYbGl4U2ExLVphZGxSMDRlQ3FoM3c?oc=5</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>11-05-2026 09:48 UTC</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Daiichi cuts forecast after $606 million ADC supply-chain hit</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>The Pharma Letter</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTDhmdkZYODJ4d21IUHBoZHBrUkJoU1poZDhqa0d4MEVPZU51SU13X2ZkNDY3X1hyTTNrZnh0eV9YR1BlQm03dms4TV9qdTROQU1EN1NZeld0emRkdHdfMjFPNTZyUG5ZZnlWRDBDMTlHUThzeUN2RUQ5VlY3amktTl82MkhPSXhJZGZ5WmRzaVJMa3dzenBURWx0WDFFSk0yLWM1VjZnbw?oc=5</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>11-05-2026 10:17 UTC</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Daiichi takes $850M charge, axes facility investment as ADC demand forecast falls</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>BioSpace</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNTVBXRlc0eURfUU5Ec0MxY29TNk1STkFPMUl0NWZKZEdQQ191cmpkdVBJUGdDNnktbHl0cXZkbWc1ZnBWTW05T1R6MFNFSXFJV1JfcE53RkNiZ2JZZjJ2ckdSMGxEUHpkTklhRWF5RVJ4aFNjSzlMR0R5TFBXeTFKZkNodkV1YkpweXpFSms3ZEpsU2RKTHNWc0tQWFlZcllTU193b0Z0T2NUcmI1ZTVaa2sybw?oc=5</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>11-05-2026 13:21 UTC</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo Co Ltd - to cancel 31,457,200 shares, 1.73% of issued shares</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQYWV3VXFzSmhlVkl2a3dGWDhKWFRNYlpFRi1HZzhEWm43bjFZS1pnR2tfdGhkQTdJbWlqbHBVbVZUbU14RlNhREYyU2JHZWNPQ3FEb19CVTllVl9aai0wcnZ4ajJwRExWbzM2cjQ4TFlrNEwzNzdQMEh2TThTbTlXV1d4MTktYUVJLW9MOUtCVDRNeFpXZ1hjYmNRMks5ZkhMMEdBRDA1RWRual9Cam1wTzA1Y08tS014elNMaTc2T25Zdw?oc=5</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>11-05-2026 06:38 UTC</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Nichi-Iko</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Japan Compounded Sterile Preparations Market to Reach USD</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNTkdUcThBcVR0TDBzWnZYcDBmTUhVUFhzQzBGM2xRaHVKQ1gxM3N1cElRRGVRNXNscU43bXZXa3FXS3BuNUpLQTZvdFk4S2dBNXN6SHJxbUNPQ2RpejhJUWFHRlNhb08xVTNCTVhkblVqT2pmeEt5ZmRTdV8xbC01ZFRTMDVzck1HbVpad0JROTVJRnJSaHZzaQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>11-05-2026 09:21 UTC</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Polpharma</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Polish pharma firm moves to acquire Romanian drugmaker</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TVP World</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOR1FvZjVFYVRDZFNwYnJURERMZzhnVmhMLUJNVXBqaVEzR0dENGNEQ0h6OEFhS1hrSF83U0c3aWZBMmlZWWVqbHBzWEhlWDdVYUZadjZZcnd3TE5obVVfME9JejgzaFZqaXRKZS1DeGVselZHcVNrVldjZHAzb1hQdEFiYmJ0QnRPV2pERWUxbUw?oc=5</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>11-05-2026 06:24 UTC</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): Upcoming dividend payout</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOR3d1WW9KT1hhVTc2Mzl5VW00NVVFUURaeEhHTGZRbVVQcmJzaXhfWExNYXlHam1IRFlCbE5NSm1UVThEUU1YTHFUQ2Z0a19XN3FtMzJFSE5BeFhLRmtIVVVES2JBX2VGQXczdHRWMVROaFRSbXVNdl9HcklrSVQxQXhnNmNfdWlwXzh0dmRtSFhhMEMwOUMyUFdMM2xSRG8xNGQyYUgtcUdWVE50UFRVaGRpWWN4QUdTcjdsWG16c1JTQmp0anc?oc=5</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>11-05-2026 09:06 UTC</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>AI in pharma/biotech fundraising, partnering and finance</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GoingPublic.de</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNNHZzdFhnUm5JWUZCSDNzelREQmU3OVRSVmhJU3RlbXBrVDdzeDE1UldYWThQUUpCRFZTZHFWWVBxNndCVGtWVWlMNWlKV2NKUDU0eHRQeGJ1MUFKTV_4MGxKR3lUTUpteU81THRiS1_0LUNMTVFuMTI1ZXJNSm9KaUx2WkVUbVhIYzZDaWlDTk13cmZxN0ZmYWpLWnVCZw?oc=5</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>11-05-2026 13:18 UTC</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Alvotech (NASDAQ: ALVO) reports FDA Form 483 but maintains 2026 BLA approval outlook</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Stock Titan</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxON05jZTFyT1M2SVEzUmRoZHJYOTlUdVhWWTgxZ2Vld005ZFRkbG15MVBOUXJPWHZENUlKMTJrNFA0RE1HRU5FRmlXbDNnVW1yUTVaTW4yUDVOVk8zMVJNdmRVaUJzU0I0bm00V3ZfUFpiOTVUSmZiS1dGLW9tUTNqOUp6cDlzODJVamluZUhhSWdORWIyaXFMWkFyYWVfNDdrWkswMDFqTQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>11-05-2026 12:30 UTC</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Alvotech stock (LU2557688560): Q1 2026 revenue dip and EBITDA rise on mix shift</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQUUZCQy1qSjlDUm5Qdmg1eTRxZXBKQXo5NEczNzVCaFh4YTFPT2VUZjI3cWFveGJQOGprdmc3QldIMTBUWEVxLUFTdkVGOTBGMnBhZDRaMjN3dHFielFZVXcyNHZxV2N5Yy0xbmlkY0FNZEZBbUVCYVd1N0RMTG1YamFjdGVtUWVpaURQbEQ3TDRqa0g4VkEya0tTR0IzQ01kVFNkei0wdmp1WGpjMHVPYXIySmltQWkwbm9hSmJOc3ZTLV9QdWZ4OA?oc=5</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>10-05-2026 19:55 UTC</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Teva’s CNS Portfolio Is Growing, But Valuation Is Stretched (NYSE:TEVA)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPbG52RlhSOTlUMjVFVTlYNHk0T2tMWThSVGFIWnRIVlFfUzFOZk5nQ2k1dVVBVlpEVm1NMXJ3clNOT3lGbWhaamJ4UlRSOHd5dFVnbUZfU2NjaUpmQWg1c2JDNnlibXJKZ2ZWVExNenI4SDlkejhacWN1OWNHeXM1cndGTG9LeUNNaHdveWxwd1J0ZWdORWYxNGd4RGZBQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>11-05-2026 12:34 UTC</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Russia expects further growth of generics share in domestic pharma market</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>The Pharma Letter</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPUldZdGhhRzV4blVlS0NXWlczS0s4OTFiQ0lKTHRkcmJwemlnT1V6cFVhYlcwQmhyVzlYdDhoWmpsMzdpQlNOaXhpQ0kzZE1rLUhaY2NFbHotMGIxTXpQNlRua3MyQTJtNW1OeDZ5elVjMnNzelRvTjc5R2RQUlJDSm04M3RpbjNOYWJ6blpwcm1XdmVsZktKemJlSFBPUEtPWVQ0OUhESnE2QlVUNDJKbTZfY1JJUzBmTWIw?oc=5</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>11-05-2026 10:17 UTC</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Rheumatoid Arthritis Drugs Market Set to Record US$</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNQUNhcmRUZmd6a1o2R2ZwTTJNLTZHZ3kwTWhQX0YwM2NnZGdKUEdOcG8yb2ZMZFNZNmN6c19Xcm05Q0VoN0U5Z3JBNFZDb01FZzFPTWhyc2g0QndBODROMGJBRnJqYmtWcFZKSFFKOFVvYXlnRFFEZ2lOX3NfNHFibFJHbnlPa1czNVdtNE1mWQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>11-05-2026 10:11 UTC</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Wilson's Disease Treatment Market to Reach US$ 1,022.4 Million</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeUxtTEE0alFDTEdldUpEOEtvUV9JQWc0cWN4M1Jfc3pha3Z6VzJxd2pPYXJlQzBXSWlhOG13N0JocnVPSVBvYUlOODNWMTkwQmQ4MFZfYzlCNlhfZG9fTm5jeHlYc2g5UGhhVDFXYlRLeFAxYzc0bXMxQzc5aURDV2ZBaDhPTW5TZnBMX09MUFVhMm95cGNyY2RtREtPQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>11-05-2026 07:00 UTC</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Bisoprolol Market Size Accelerating at 8.57% CAGR |</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMmtMdnN1YXVBQ2xJZUplSmtSNFYxWllzTENVNkxsRkdlWk9vaE9mTTk4dU9FN0RJTFc2LUtWUFJFS2RHT0xaLXNYOE9KejBKNHVVS2toX0hmd2dYNDd3NEdBZzZVdlZLZWpkNXVSY1UyUlZnNjY2YjFGV0toWmpRU0M2d3pPVV9MTjU5Yw?oc=5</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>11-05-2026 09:41 UTC</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Dexamethasone Market Size Accelerates at 6.8% CAGR Through 2033</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>openPR.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVjF6aFlJS3FFZzVVNUl6a0VKRGhFeFdhS3ZEcFVRaFdMRjIxSk5mUkxFaERCdGdTOVRyVFI5LXliUk1ydUxybXdUT3hhY3RSMnFYUFhudmtmVW5tcGM2V1prNXFSLXlKQTU3Q1laVVg3cWtPMF8taGZWTm1tREpFNElIOGwwYkNNQ1JCZzVZQUh6VDVjRld2emVhUTNzNTA?oc=5</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>11-05-2026 07:53 UTC</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>CORRECTING and REPLACING Samsung Epis Holdings Reports First Quarter 2026 Financial Results</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>The AI Journal</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX2JFZTAydDc0NHp6dXpMX2RKR20zNkR4bjVoc2g4UFo5RlhZcWE3YXpxTnh0eTl3RERRb1hNRjRiTTQyOW1lemdDcW4xQWp2V3RFUFpORjZxaVMzWkN1MXd6SGRGQ2JpbjBVY0xMN1k5dlp6M0lseHRUWV9OdndwX0k3OHB0VHFqSnZ1ODZCMHFNX3QyLVdnazBPX2NBQVpMZTV1SG9uNEJkYWJBNmdpVFlR?oc=5</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>11-05-2026 05:26 UTC</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -2309,7 +1605,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-05-2026 19:15:27</t>
+          <t>11-05-2026 23:50:51</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,32 +464,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Chime Biologics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nevian Lifescience begins pharma exports to Canada</t>
+          <t>Recapping the “Must-Know” Information From the 2026 AAD Late-Breaker Sessions—Part 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bangladesh Sangbad Sangstha (BSS)</t>
+          <t>Dermatology Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZTJyb09pS1NON0N6SjRfd0thMnNWTFdwSmVzWi1uNlNGTEdVdThRQ25LV0p3RmdKMXo0ZFlVRmcxMHdNdVhWZmJ4TGtpSHA0Yk9zX3VaMzhqZTBHR05pY01JR0tYcUNHQWpvR29wX1psZVhza09OdmwxcUhva3U4LXV2RW1Tek5WOWhBZUdkVFZoenEtOG1OSzNfaGVlYVc4bWdxN1JFUHlwck9xc3FqU1puczNtZ3lUOEp4Rg?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38 UTC</t>
+          <t>13-05-2026 20:00 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -501,22 +501,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
+          <t>Nevian Lifescience begins pharma exports to Canada</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amader Barta</t>
+          <t>Bangladesh Sangbad Sangstha (BSS)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-05-2026 15:14 UTC</t>
+          <t>13-05-2026 16:38 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,91 +533,91 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Developments in R-R Multiple Sclerosis From AAN 2026</t>
+          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>Amader Barta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPdUJ5TkUwM0MwTnFQZ3lHM3hWbmxaREZ4dFk5Y3dZaklvanpBeEVGQVoxdEpWTERlemdaZmNCXzUtRWdfUGJ4SU40eU56NEFJSEZ5a1gxWWc1OEpGV2VSZDA3ckZQNjQwaDV1OXpYSENBcnc3aGZ1djBaVVdieTdsT0dQajhmUjFVMmVCSTZKaGhPT0doMEdyZDE5SDFFSE5OSENyb01xVkFCdHBQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12-05-2026 20:56 UTC</t>
+          <t>13-05-2026 15:14 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
+          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates competitive pipeline</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeDlVVG5HQzJKVWg1NC1fRHBZeHBjYWlDcVB0c0NCNFdVZWFZb0RwTWcxUG93S1d3QzZBR3k0UWZaTXluRnVKaFphLU9WQ0FqdUp3NEd4MFBwWERrRGVMdWZicVYxTkdfYW91X3JXMXZnSmJaa21JU3Q0ZmRwMUstR3JNcFBYeGJCcExfUUJIWDQzMGhkcnZ5VzJmNU1OWUlsNGdtSVpmUVRjaTk5WlZPTEtVQmFQUTlyZlRDYzI0el9TQQ?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13-05-2026 13:36 UTC</t>
+          <t>13-05-2026 12:51 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
+          <t>Richter publishes Q1 2026 results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>Gedeon Richter Plc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5MeHNtY05Odlh0ODRab1BEcnplUFVDRDBUenZBU3dxeTdyU2YzUjVGekUxTUQxOTZQcnQ3TEh0TVh2VngzbjVZejM4aW1MQjN4d3FxZ3ZZSQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-05-2026 12:02 UTC</t>
+          <t>13-05-2026 16:46 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -629,86 +629,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Both the drug orforglipron and a probiotic supplement help patients with obesity maintain their weight loss, according to two independent clinical trials</t>
+          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Science Media Centre España</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOYXpadmJKYXo5Qzh4VEdlNDdHc3M0bXNsWkJIVzIzS0o5bElXSVBuR0xsZVdsdzVEZTRuTXlMbjJJZFFTMEJ0TnFnY0FORXVsNnZyZkFBdndPVEw2SEhISHpoUUx6bkFBUndPalotXzJfNE1rbktySVpfZWJkd0NVWS1DOUpFWVhlX0djRGhaRk9rX0piNWhGTURVYWszSnpKX0ZrcThIVWlPZVZYZkp2U1pxdDFwUGM3OXhJcGpQY2puaHlnTmZrdA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12-05-2026 22:00 UTC</t>
+          <t>13-05-2026 13:36 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tezspire (tezepelumab-ekko) for the Treatment of Severe Asthma, US</t>
+          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clinical Trials Arena</t>
+          <t>PMLiVE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOYTdfUjB1SDNKbFJ4WDltZ1dNcThZNGFBZFd4T1o1b0pPaW5EN3Vwb1lFRFBHakwtLTU2RU9vc3ptUHRRRjA3YndJdVI2eVAzN29sdlFMMUtEaFM5X0lBQ2ZFclY5YzZESGZNNlNLZ2tRUTVSc2RDWlExR180ZF80NGlDcXhCbmNpYzRNM0pEQUZDYlNvZlZrVTQzcFV1ekZSU09oOUhST1FVVmJoajcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13-05-2026 02:48 UTC</t>
+          <t>13-05-2026 12:02 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Join and Learn More About the Evolving Obesity Treatment Landscape at ECO26 – Amgen</t>
+          <t>IPF patients call for greater awareness and treatment support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oncodaily</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9wVU1VSGdDTmg3NXJZNmZBa1VEUEZOLUtYLU9yYzdibWdwR2NHcm52V2hHOXRIY3MtdHFTSE5ReThjNUFPSjVHVndwWkFHc2pzYnE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12-05-2026 21:00 UTC</t>
+          <t>14-05-2026 05:36 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -720,283 +720,283 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Myasthenia Gravis Updates From AAN 2026</t>
+          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>Pulmonary Fibrosis News</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZ0x0S3NOdjhXaFJjZnQyTVlfNmdBdkpPVXpsdDBCTEo1YUZBN3c1V3JWcEtvbHg0WE5wNGNUODRXMUJQLWw3VTctUXVyM0o1S0xETGJiamh0YS1HWllVWHFraDZmOWJRaHBxNlpFOHFrVHdDbnFiRzUxUkpLd0dnVTJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROajQyWnprQQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12-05-2026 20:15 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Real-world TED data finds disease advances beyond acute phase</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Active in growing psychedelics and iron drugs market</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eyes On Eyecare</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQNVVVRkduWDF2VEJIZlRPZTA5U2tBS2VfdjJJSmxkVExURy1RbW1yXzl2U2MwSWhrOFBGSms5aEpLMlFXLXAxYXNfSGZhU1FsNXVxTjFlcEw3YzU3YlJfT1g1cVBISFRLc1lpZmpkczJNMjU2R0ZNa040U2l3M28zRUpYX3BUUXdxRXlnZU42R2VPOVZPUml1Z3FyQkpUZWpTOG1VVm9ubHNXWUljU3ZZcjUweXlHVHlNWmktVWF3N3BUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQR2hUQTZnWjdIUGZKb1pjOXJTWVdtZ25rVWdyNGY2dE5yRWxoU1VWNDJGdDNFYnlSMWNsUVJZSjR5Uy1aUFZnWm9lWTFOeWNXMHd2NWlVMFFfTk5lOXROM3hDVmNjajh3RHloMGtkT2lUa3lXQUljZDFDbURUZTRtMElRR2c3V0dWX1ZoelVxekRpRjFFdUhPRTVNQ0FXSzRlc3JwMVFvXzZydG5jNWp6SGZNS0h0b1RGUHphNzN3?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12-05-2026 18:39 UTC</t>
+          <t>13-05-2026 12:43 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
+          <t>Amgen expands U.S. manufacturing footprint with additional $300m Puerto Rico investment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>The Manufacturer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZfNfdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcTlIckFocHo5eFNvTGJSS3ZVRE1BbElIZmlyNndMMHdXckZOLW82cVJ4UjFfR0s3Tm82Qi1pR3I0cTZCTDJ3cGtzMXBUMEw1LXlWMWlDR2ZGXzlWUDlzdkZ6VXE2YjVUaTNzMTJVVEQ3ZGdjNFRFSHRTU0JNc3A2T1ZBNERQSTJleVlxcFdaVC1sYnlVNWQtVThqNS1iMUc5NHFpSTF1UkRNMHUzMEtUNnkzM1VHWXptY3lieGhQYVNjamtBNXc?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>14-05-2026 05:08 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EC approves added indication for Pfizer’s Hympavzi</t>
+          <t>Amgen stock (US0311621009): Q1 earnings beat with revenue up 5.8%</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWVdYS3laT01nMm5Fal81LXRaUHA2YUFOdFFSVFFVUUdiSHFpV0FBbWlWcnVQVWhnWkpnZEpoUE5LOGQ0U1RFSW44ekwwdDRDT2RKVElPYmRyOUhGV3lJcUFZemYzRDJVTUVNajY1anhWMy15WVVXUWpBenI3OVNMdXlOOXBXVHJWU05USURENU93c3puWlgwZUNGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRDk2SjhDeUNYbUhCajRrR0hjSUk2UDZyQzNvZ1J5cmNJd2hFMDZLQWlmaXY2eXZQUkNsR3hwdmF1UnJ6dXlMWWtiT0VfZXpPUUJHbHgxOFdadDh6NHUwQVZ6VExxX00zNWVKMXowOE1iOU54SWNqQjQ1bW0xNkdLSlpyeEpTbG45SXhMTERZQTNaTE5Xd2RFbjhQQTFHV3Fnb1diZ185dTYzeUlmRFFCc1hPUmppRTRWamo2VzFaaVFueXpuQzQ0?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-05-2026 15:00 UTC</t>
+          <t>13-05-2026 16:03 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pfizer PROTAC Licensing Deal With Rigel Adds Royalties To Valuation Story</t>
+          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQelpsYWlfSU9MSUVGZjlkNDBlYWV2dGJJaXJPRnlaMjV3cGh2SEV3ZlVGUk1uMlJOQ3ZLUUlPUkIyWUZtYjZjeEhXZ2Q0eVpkanNOaktKdjZabnczX1FVMGt1UmVmai1zek1Hd0o2UEFxZzBUN1UzaFlJTkRjc3RpXzU2cG1NdGZEbGE3TDV5WnBjM1ZVRWFoQWxhN1RrdEVkYkp6Mk91Rmd4eFo3NVRPR05mRHZuX1M2SUI1Q1J1MG10VzNTZkhlS2dBU2lOWHpfVmUw0gHYAUFVX3lxTE1CLTdFcThDZ2g5b0VxdHpLbTFqeFNkeUhPcVRsbC14RTVSckVNb0FoN0JyVG9vcW11TnFWbFR1UnFVMnRWMU00Sk5uZzN4S094b2hfQkg3VGItNktPaHpnb0N2TjFaQU9jTlZ3c2wtTmw2cVZvUTlWU2Q4M0hiMG9vMWQ4eDBPQm9GWEVqaW1xRTZhemxJLXYzQkJ1cnh1OGlBT2o2YU1EdElEQWtaTUE4UTNKRW1wc0JlTjJWQk5WZW5QVUN0dUlHMDNHTk5fZlFnaTdfWVQ3aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZk5fdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-05-2026 01:05 UTC</t>
+          <t>13-05-2026 13:54 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pfizer Shifts VEPPANU Rights To Rigel As Valuation Gap Persists</t>
+          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQeWtIazV0T3Njb05oU0pOUmEyODRtTXZRS0puUDR6M3pva1FMbF9xNFo0ZFNXM203amJSVktuSmhORmJVbFgtSjkyM3NtWVZDeTJobzhSZ1JKQTRaZk9GUzVnNTlwbHdyN2FKRTRMb2kycnpUOFRDUXVuemlJYzRUTHpmMDhBWk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZm5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13-05-2026 08:17 UTC</t>
+          <t>14-05-2026 03:22 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock (US09062X1037): Q1 milestone payment amid partner C4 Therapeutics earnings</t>
+          <t>Pfizer Research Grant for Non-Hemophilic Bleeding Disorders</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOclpWQ0dzSWstNk9OcERqTVE1cVJ4MFF6YXhISzhHUUpUd0RIVUxUN2FCenBrWUdxMVVyYS1jZnhMdXlTR215dVRRR0Q2c2Y1MEd1SHdhNmhCZ3RfM0g5Rko0c2NBYzQ0ajhERGxubzYyOWNpbmpZcnpHTGVBOVZFbkNabGxtSDF0Y0U2NnUyaURsYlhtZEhqbW9GVURKUk9aX3puTlM3dHg1YTc0RXpMQ2pYeVdDYWdNUU9CektxZnVMLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12-05-2026 18:41 UTC</t>
+          <t>14-05-2026 05:29 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>High-Dose Nusinersen and the Future of SMA Treatment</t>
+          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NeurologyLive</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOaFFMcy1UYld2UnpfcUdGMzVZWHNmdV9DQkpnNEljZ21Tc2zacnZycVdEVDNUWkc3TlVvUGVsV1ZHY08yUXd2ZGhHZHNMSGdQd01iMlJuM2xYRW1xVDZFVDdaQm1OOEc2dkNla1Z4SHVWLWxoTHpTZ1BzenpiLUFCX3dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-05-2026 13:16 UTC</t>
+          <t>13-05-2026 19:26 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leqembi to Launch in Brazil for $2,255</t>
+          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNSF9pUlJVazF2YVdpUF9sT0c2OXE1V0tWaXhOQkY1cXJaRGJWcjkzN1J4LXJMUDltdmt2T0J4TkQ4RXhaS3NMbTBvd01QYVZ6LWFHbFFqRlN2Z0FvOEF3Z1pwcWFBdEdiSHFveUNpU3REWWYwSXBDY0xkX3BmUXppQ09CcTRFUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2dUY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12-05-2026 18:55 UTC</t>
+          <t>13-05-2026 19:16 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,155 +1008,155 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr Reddy’s revives India business in FY26 with portfolio, productivity reset</t>
+          <t>Rigel Pharmaceuticals Enters an Exclusive Global Licensing Agreement with Arvinas and Pfizer for Veppanu | PharmExec</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSm5qT1JsS3REbnd2UnJfTTV3QlhPdGNtOG5kMkVPV2hOM09URXhOU1VVM0NMSWFOUHdFZUhxTGFSelp1X3loZUNJZ2hNbVBmemRxQWVEcWtfOGI1VTFxcFUtNVlGeHJmbHhoa21vM3phQU0zVG1YR1VabHJvMWhHT2d2RUlQRmRMa2lCMklsRXdyUkt5S2lkc0RmSDhYdkJ4bjFmNUFGZ0MzOXp4WXBtZDlkUWJqS08wSHVXTFBObkJXS0JQN2RwQzNXaG7SAdIBQVVfeXFMT2k5YllGaGt3aFZzZGtNc29DU0hMaThNaENFZWNlUDQ4SlE0ZzNwVnR5Yldab0dES3RqSlF2U193R2Zrd3RmWGxySWZfNnc5N0xNd0ZlNVNNM2IxNV9YczU5eGwzRzVDcF9jQnUwekE2dHBkOVE5dzRMcko3LS11NGt1Z1RrX0MxNUZ1c0piZ3Q0b1BVU1NYRFRjTHJPVEJZNl9rYWhCSktaTkFUOVllN29Ecm8zZ2pHUVpydm5pTGFDeEFqdHVobGlqcUV5aGlycGZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdXpwSEt0WGNHSXBrV3VtLXNWbEFIZl9kRzh1ZnJtc0JPS1A1TEw4NVhmbDZwaHBucDFlNkxlbWZqWWdyZ0tPYzVPZEstMHJSLUZ2YWFxSGFQUG9QMDd5VjFYc1lKUUNncXo1aUE2eGFzTlVXTnIwM3p1NG9CMlAyNzlsR1I1am9HUmpYeGNIeGp2M1h5amh2NU5tdV85V19NUzRpVkx0SS1lYWZLRXc?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-05-2026 12:17 UTC</t>
+          <t>13-05-2026 18:47 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Canada approves generic semaglutide from Dr. Reddy's, a G7 first enabled by Novo Nordisk's lapsed CAD$250 patent</t>
+          <t>Pfizer stock (US7170811035): Q1 earnings beat estimates with $14.5B revenue</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>drugdiscoverytrends.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPTW03ODZVV0ZCZ3lfUVk5Y2N1dUk4MExycC1jODhOMmlZZ0h6TWJrLUg5WWgyYUhtbkN1bWx6WDMyVE40dE5sVzRMSzVrTnNWMXUwRzlFTHF5TVhSaDJOOWpVcFpObG5nbHpNMzJISzl5cWpBRWFBSHlRdnJFN1kwSTFNVEhqN05oYkxneW1LTmFEZ09PS1VDS3pZdVh6OGtVVTdCT1pWd3JEbFp4N0dReDc1YXRzV3JENG1jWFg1ajRvNjVBTE1MdjBhVFMxaTJ0SGxGMTdXSklkTnNx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQNjZYTFU5clo5NVRrTVVHczJRQmw3SGt5aTV5cWxlSVNUdkowV3lnaGJDRnhxQnFvM3UwTWFPQWotS1A4YnJMYkN5ZzhldDRSVjd1bVg0a013RFBNUS1IUnNyeHdVNzZUbXJFczliSVoxMXZ3U3J4U3F5SHowUGVoUWhJdHhwWUhqSl9xYlNLbHpnWkVOaFczT3NleGxXYXl3OE84WmExMk9wY1lWbVVqZWRVbmFxU2lwNTMzNFU0?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13-05-2026 16:11 UTC</t>
+          <t>13-05-2026 15:30 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Sets Out Details Of Imminent Semaglutide Launch In Canada</t>
+          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMVVEQW12cUlTOElKTi1KQkY2eVIzRVlFcmRlZ29XTjRmMGZ5Q0l3elFMNDVneVYyNU5KRU93ZVJBNUpSaXplbU9uMTg1RUhMZDBmS1Z4QURrd0k3N1RKSmx1eGZGMWFqdXM5SERueUVGZ0xIeDhPSHl2ZjFkQ2o2eExCWkhKQUZOSzg2cTdCVnlibUdsT2MzZHVEaU1rMDZYSEh5bWNMSjhHampvaXhVV1RrZThnTllWaDIzUWdRNld0TnRKYVYyZTlLZzE4dGFXQVlrYm5ONGF6UVdHLW9HcEpDdmxEeUdzV0ZFdWt5MVlSdzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNXVaaUJRLWVNNmk3RlN4X3h1cGUwVVRQNllwMktEU2pJLXRSM25wdWNNNFZmV1BoYjhLSFphajk3UE41dzdnSmVJaGNVbVdDSngwWE9zSV94eUlRYkN2ZkFsTlg1Y3ZMVk1EY05HM3RkazdEdmRtRDdwckh6N0oydV9JWGdMV3hlMWxjTGgxYWs?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13-05-2026 16:41 UTC</t>
+          <t>14-05-2026 11:05 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Drops CAR-T, Eyes GLP-1 Upside</t>
+          <t>Biogen plans registrational study for Alzheimer’s drug diranersen By Investing.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Investing.com Canada</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZGl4YUlzUnpWWGpFQzlHTkVubGlMVnNLMXJFaEJxdTVwN2FTN0k5SkY1YVNfMmtJU0xka1ZHeVBYZTd1RnZzTzBaX3FsNlRBNjd2UHlHdU1SekVTUF9mcEFqWENWMkdNZWEyR3J1aml5WGFYRW5PV1UxWVVHQ1dqa0NpZzF3ZkRwcnY2Q185UHlRaUp4N2JULWJ2Zm14bnl3ODJtOFRHX0dHSDBhenFXcVhBazV1Q1pzQ3pFcldvTnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa2tidUxrODZCOF9sSjZuRXBCS0lua2p6ekVMRElQdEhId1o4Um5GTGhiOF9iQlNIWDFLU0htNzllY1dnVHlfV0w2dDBHOGhmTVcxcXYwYmNsM05jRDJLTFE4c3g1X0Zvb2V0bVJSbTJ4OUhwVXlLWEJOQW51Y3FtZmw3SXA3c2NDYVk4MEVwUXJqM2MxT3VvaEJQa2tjQzFFTXc5amJ4VDZQQ2hQUVp6c3ZUZU1rTFM3U1FDMnpRZi1WLW8?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13-05-2026 12:33 UTC</t>
+          <t>14-05-2026 11:15 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
+          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNmFpemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08 UTC</t>
+          <t>14-05-2026 07:29 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,251 +1168,251 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences close to buying US oncology drug maker for $100 to 150 million: Sources</t>
+          <t>Dr Reddy's Q4 Profit Crashes 86% to Rs 221 Crore as North America Generics Sales Slump</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxOZFMzT1FGWXJqTWV0M3pPdm1tVlpZV0FkdWtXeGFVdXRlSUV6Y0J0QWNaM19ZNXlPdFlFMGR0R0N0cGZWUENZTGNNbUszMHlRQWJaZFhTR2pldzVlQXlLTDZmVkpxY1RhOFBDUEZ5Tjd4TjRwUzBjYmluWW1XYjFDajNuS0UyZzI5OHlwLTdrOVN4VXJsRG1laElHenRLa01EODVXQkZ1RV_zTEE5MDduUDB6S2ZXVmpTUmI1SkFULVNYOEF1QkdzZHgwNHFqQ3d4RUVCY1NhbnVuSEZRaFhKUUxjSml4SlVGMFo4S01NWnkweU9vLTRyUGRsZVMza05XcGV2SElmZFJFNkZkRUd4S1U0ZlnSAZoCQVVfeXFMTjh1N0FyT09CTGVYN1FIQjM0TjZEY1BleU5sZ0w4UkZvdm1XRllieG9HVXgwUG5kRGtkdUgySWRZS19zU1YxZmdPa1BmamhHcmFtVGpjV1ZCRXdCUEhjU0JCQm5zRkJpWS1ERmZZaUExS0Z4SXJDRlczM1NmSlFFZjJ3eWVscWVZMjhCMTVPUmd2cTFhaTBHMjJjVFVNYVVLcVQ4Z1hfMDF6cFBYbmdQNjJqUHF1NU5NQWoyZGJBaXJ4Nk96d0xvRTlxUTV3dWdlZjJxcldCaDRsbENSQ0d1bFhSVzVzYXlTakcxTzJtaXB6WGlEZVYya1RjelVSaDE1RDhoekJmRXpVbUt1eXAxT0dyZG5xYThOQmh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNTFExREh4a044UGNwR3lhdnBiWUtvYjdTS0lHRUE3cGJJblItVkc2T3Awb190WkxIX0Zwejg0bUZxS3Jjc0FBbVhQc3BSdEd2dDNQRWduQXV1dVUyaXNscVZwQUd2VUNBQ1diNWtfYXQ5TGp6THE0UDV3eld5Z3pOUS02cThOWmpBSDdfOFF6d0dzY3I1cm05dHJZZW1ZbGgyRm43d2xZdTJpaTNySTItN0dCLUctTWhQbjdxV2RnT29JbERGYi1GNWlVZFBJVXAyeVF3VEFIY9IB3AFBVV95cUxQaGVOQi1xT3JnNjFYenhkejI1RlpySFJQOWU2Q1dzU3VwWGJkTXhQdmdENkpFU0tGVUNNY1NyNjJmUXVpUUJQYTE3UTRxbXBCT3FVSUljMVg0bk1nVWI4U3lFSG50bzVsaXgwNGhkZF9HUlFSTFVDNDA3ZXlxUTZQdjBkUHFQQXRHNi04OE9ENFVjR1lWcDFlOWxnRWlKZS11UDZ1UGtZTFFCTkVreDZhOFlVQWgybXNIUWdpQ3REVjVSVVFKd3YwMExXQko4ZlgtODktMDBhY0dOU3da?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13-05-2026 12:15 UTC</t>
+          <t>13-05-2026 15:23 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Celltrion Makes Consumer Health Play With Gifrer Acquisition</t>
+          <t>Indian drugmakers turn to buffers stocks, contract tweaks to tackle Iran war fallout</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOS1JKRmRmYlRfdjNxWnl3UGhERlQ2T0lieEhRRExsT0l5UXpacW0xdC1pQW5WNVU3UWdIT2poOF9qamtwSGkxdlNTWHJyTE5zX09TcjFVS2R6Z2RkMllHbHVlTElCcjJVSXFUM3JYN19xaGkwV3BaY3Nza0diODRGa1FORVROMUVMZS15SXBDcjFINFU1WTJkYXB1Z3NsQ09mWXsyRFAxelY5X3A4WnpvdTJXdU0tenBid3RPMFZfdldBcHhZT09abHpaU3AtN1BLb2dTajdJNEpxS01xMUZWYVEtc3ZPNTNtLTBmM3FMQVZkd3VLaWRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTmNtd0lLbG9mYkt0dkU3VWhCU19DbmMwQ1d2Um4tS19vZldBaVp5Y01rMXk0T3dZaHlfSDdmR0llbTJwVm9hMTFyckZ2QzVEUjBIaFVaaC1XUkZKT0lsalZBQjlTVmlJMm40MUNzWWh0RWV3OURaUmhBbXI2OXZwTEE3VGNZRG8wNHo0U2Y5SmdmOVFmNjlNNTNBdDFRUVk0ZkpVMFNqWTVrdnlSSll2enZGS2EyaXBYMk1WMHMwTHgyeXhOcDBCUkF0S2NzUzNseXlEc0JJUWhpbzJiZ0hR?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13-05-2026 11:16 UTC</t>
+          <t>14-05-2026 03:38 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Celltrion USA, Inc. announced that it has received $516.1 million in funding from Celltrion, Inc.</t>
+          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Capital-Riesgo.es</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOMDV4djNfbWs1M2NoZHptelhHYWN2U21wRXVzLXlXaHZRZFdkYTNNbFlGNkc4dDNMRDg2X0xWYjhVS0pFdThhQU1kdmp2S296Z1J5MXE4TDdReWVLWmp2WHpkLUNndl8wY2FTTDVzaUNTSk0wZVZWSWZLNkdmQ1NZVDJMV3VxZ1B3MU9zcXNRbTk2TDNmYXZLOUY1V0lJT1dyQVl1QWhXcTJnSnR5MWt3cUZKbWdVSlJRRnVXdlZFMnlENzYtaVRWWDNIbjVNWHFvNU05bFR0LXA1RmsySXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYk5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDZaOXlKMkE?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13-05-2026 06:51 UTC</t>
+          <t>14-05-2026 05:06 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Founders exit as Seo brothers steer South Korea’s Celltrion toward sole-CEO shift and drug expansion - CHOSUNBIZ</t>
+          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQV01CMmxTeFY4UkhCWVJzd284bVUyMl94NGdVUlRGRDlzNV9EZHlHNzMtMmVXXzdnMzZIYTJsdlRpMnVEakpsX0F3WGg1SEt6TUVCc25Eczh5c0VkMjlhVEtBNFBsT1pUMThzemFTTE5oRURlZzVNNVB6V3J6WlRKdtIBlAFBVV95cUxPVzRmUFV1VnhTVXpYTGljc1NqLXUxOWdoNDNwVTg2bHJkZm1JLWhOQnIyQlFJdGhiRU9FZmQ0WVo4RXFBZ09HWEFScFg3QTlvTTI0cE1MNlZ1dWtfNG1lU1F2YWtnZnJMTWFkLTVSNWhOVks4bTh1YXJaUFM4OGFoLXM3SDdQenl5aU5ma3VCTWpyajZy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12-05-2026 21:01 UTC</t>
+          <t>13-05-2026 15:08 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo's Antibody-Drug Conjugate Platform Shines but Faces Increasing Competition</t>
+          <t>Zydus to buy Assertio for $166.4 million</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQWUl5NzZZLVF1VVpSWm9XQWRRTlJqVENBNG8tQUI2OGJHYzJJMy1ZU1J2Y0xTcXhlRm54NW1JaHg1a0l1cTZZY2w5VXhCWHhpZFMwcVBIZkEwV2pvc21ieTJyV1VwbHRlWkt4MjdaMlN5TzhJUVBfYXVmR0hycVhVQU9wWTBTNGNxdUhpSmh6NXRiZlNyel80aHBhWEdERVN6RlVYQjk2SnZGZVplTmRkOGFmY21HZUg1Y0dHejVYWEZ3enVGWjdZcU5TWnJpMmMzbk1NYy14VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUHk3SXJBMDJvWVV6aExfeFVvVzZySGdiR2hLcUhCemRBWkpuajZVWXpUVXZ2dUR4djEzdnhoaFpXRkpNQkd3cFIzUWVnSE1XLU9yNWloM3lGTlRuTk54bXRibmZmN3N5Z3BjTkVwZHhyZVhrX2twa0lUZE82YXJnUTI1RWpSQWNuMWFORFRNNFFQLU0zZm9MTjl6bUJDNmt5eGtaV2FFNHFXbTNtRzN0ZGVxeUE4Ym4yRDJTbmxWZ1JieHh3b21LR09pamPSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFS0xRMGhJpHQ90</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13-05-2026 06:05 UTC</t>
+          <t>14-05-2026 05:45 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Corrects FY2025 Presentation Materials Without Changing Financial Results</t>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcnJtZ0hKU3ZRbjFvaGotT1lJdXRhQzZ5aUdlbGdBRkxOYXZZdzZ0UXBIS19kS2tGTGVPd09TckVCcVVfRjVEanN3RjVGd3lCMnh5SWxSeWg4TkMyX3pRLUJXUjN5bm00czhCMHV1ODVKbnM3STBOdTJWdnlXMlNnZTUzZTh5WEc2QVMzOG1NU3pvYWIzSkVndS1NbmNLLXlkRzdmaTZucHZpem8tUmRXdFd2d2xDREQ4Q0x2aUFDaWR0WnNTSW9nZi1ETmJfcWxuMUo4WmY2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13-05-2026 10:08 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kura, Kyowa Kirin to present updated frontline data from Phase 1 KOMET-007 trial</t>
+          <t>Celltrion gains 70% Europe infliximab share as SC formulations surge - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxObl9vOEhENFcycmlSbmNZaWEtZ1hzb3ZVc1NxV1JHNFVVUVp0bThIdWhmTmtYZFN6WHFoZ2Nmd3lHQ0dzcGFXdUdRbHVzVmtEZjlIaUl5YmdoLUplYS1zSVF1R1dSTkhSNnZCOFM5eFEwNjVEcTQxMzZiZGptSXIwUzNmdG9Ia3J5N1djNTVibnNneTJyZGx3aDhMdTlYcXRPU0hNb05FbjJ5N2lxWmxIcWdlYzl4TFBMZ3ItU1YtN0k5dU91Y29YZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVGRZcDRheFB2ODlMVDJWc0xINXE3bjBhRGZDYWZqZzdsbkZBbjl6cE9qR0QxR3VTVl96RnZtZ2lrbmgwTGJ6aHVSR1V3WTc0NVJYbnozUFQ3aHN1b2x2dDVFUU44dmljMVZBcG5ZY09BczZQcTlrVUhHRC0zRFllZtIBlAFBVV95cUxPQzB5ME94VGhaOXlpTk9jVW5Geno2dlZSSWNOMTZ6T1hJR2pHamNWT21CU0Nzb0lVMldNZ09yY1liVFprV3F6ZjZzS0VFaEFVSjRERjVhUHhZUVNmc1FPTkxsSlNKMDItQ0VoQ2kwR0VXcXR2bi1iTUZCWkpENU5VTXh4TFBLSzA1M2VnRjNfck5MS1RX?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12-05-2026 19:48 UTC</t>
+          <t>14-05-2026 00:37 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
+          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13-05-2026 13:39 UTC</t>
+          <t>14-05-2026 07:08 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,96 +1424,288 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>‘Fix them without delay’: Supply shortages hit Parkinson’s drugs</t>
+          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chemist+Druggist</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNR3ZvRjlhU05reXplOTQyeElFZU9kci1kc3BaZnJvVUFkRzNSOXBDMUU1NTdHQ3lJWUVReVFGU0g0LWduMnpFZ3JRT012azA2SG5FeHBQZXQ0a3VKck9yNXg0Y3V1Uk90YW0xemNBLXBTSVI2ZVpObV9oU3JqUG1tWU54NGIxZFROSE56Q1NwY3JablRWVzFSMkxKUk1objlEVkltQmtsX1R6cDcwa19KYURfVS1YTU82YnRqY0JfU1MtN2JFWTd5WnlyVF9yMnZ5ZXRTSkVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bk1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHJ3MWd3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVzdsQWpTNjJhU0FZYWEwTGxxR0kxRUVKX1NoRzdtWFM0a2dwWkhvRkJDUUd4TU9rZW90OHZTeVd1eTRuTWhORk15YmR1YlVocHBkcWMzOXEtWG5rWnBES0NXcjdkTS12SU5KVHlYOHVwd2x1NVlONjg3VXQ1ZDJ2dGo?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13-05-2026 15:22 UTC</t>
+          <t>14-05-2026 04:27 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Kidswell Bio</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Samsung Bioepis and Seoul Bio Hub launch program to boost Korea bio startups - CHOSUNBIZ</t>
+          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOT3ZqMERwMmhLSnJfcFlZeUxFMzJYV3NzeUdpNGdEYUFCYjZOZ05DOU9MT3VHb1FUbDZXRDVrUmtaNnpjYnNKY1VXQVNNX2Z2LVVCZEhjd3ZTUUVOckxmcVpoaE9nNDJ0cGNmYmxOdUtjd2Q0VE5nd0R2RzFyYlZRMdIBlAFBVV95cUxPUWJUZm54Z1dnVjVnaV8xZEc5NjNOeTVnUGZyajN3ZWVsRkp0Z25XRXRuM0dLdy04TlJ3bm1UejRsRlBpSFFHLWZDd2E5dnhQcTYtWDhqckVwZ25JYWw3aHdVNHhuUm5rMk5lMmN4LTBZREs2S05laG5abnp4d19QMmxXVlR1Q0N6UHlQNzN5cmpsN3BQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaGlRMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13-05-2026 06:31 UTC</t>
+          <t>14-05-2026 09:33 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>13-05-2026 20:55 UTC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Live Law</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZ9IB_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:13 UTC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Indian pharma fuels Africa’s ‘zombie drug’ and opioid crisis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>The Straits Times</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOUTVkNnQxLWJFZkFidzlBV0dLNGIwc0FlWGdhamFBTGxkM08wS1hnY0pfTWdZdkdIbXN4VkpnaDc4THJ4UmNmWkM0cUVjVlhzblJBY29NeVJZWEVXeEVZUm5fUEZYZWlqR3QzMXVLQVRHNGR4Q0NHU09idU1TbEE0WlB2VXFHNW9XUVBVc0pwYXJiZ3ZYNElr?oc=5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>14-05-2026 02:05 UTC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:13 UTC</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>14-05-2026 10:46 UTC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13-05-2026 13:39 UTC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Samsung Biologics showcases oncology CRDO platform at PEGS Boston</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Samsung Epis Holdings earns MSCI ‘AA’ ESG rating in 1st global assessment</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>koreabiomed.com</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1CSkZnOUh2V04yWUNpYmJBOUVCWEM2Uzg2VklBODk0RENsTWlnY29pVjRDWEJVOWlfVG1qN19DSUZaWWhYX3ppZnJUa0UyWjBUdnA2bUw1eHFVT0wtUld2NXRIRDF6Yk5IM2c2WHZR0gFyQVVfeXFMUGZHeWM0OFc0RzlBS1NnVGdaOEtlMDhxT1hMbUY1bWl4NTRRZTJoS0ZsVl9PeDVKNk8yeE5FakhhTEFOM1YwLTVxT0IzZy1pTmx4Yk4zTEZ6Qm9oMEE1aFlUZThPelVwSVJhQ25fdFhvdXln?oc=5</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>13-05-2026 01:04 UTC</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9zSnR0VW5KVlJVMWpTSEtZdmJuSDE4ZDBlWEhOMlhjSDNxWFVCOXdTYzRjaHo1a1FmN1VoRVhCbUxuNG1ZTXlsWjBqUkw2THdQNFpEUjNGd1gzZG55djl4UjU3cWVsZFotZzVDSDhn0gFyQVVfeXFMUFdWY2E4SXNLXzJVcUNGNXRxdTVsd19XZkx2X180dWRLUmJVUHRkSHNSUU9fNU1FLUltZWJvZXVfMkt3cFIwQzZhWGdjeVZZS3V2Mk1USWhhQVVCRDNvQWJtTWxJd1dza0hjNktfcEdIa1N3?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:44 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-05-2026 00:00:07</t>
+          <t>14-05-2026 16:55:06</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,12 +484,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13-05-2026 20:00 UTC</t>
+          <t>13-05-2026 23:00 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -501,22 +501,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nevian Lifescience begins pharma exports to Canada</t>
+          <t>Sandoz climate targets validated by Science Based Targets initiative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bangladesh Sangbad Sangstha (BSS)</t>
+          <t>Drug Store News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1BbGc1SDBDU3JxNzlUQm9WaThjTkhaNXhZOUlLUWd5UDV3ZkRmTld5dk54M1puOXotMXVsOUJwQ1ZlR0RCSzBZYW1tT0p6ODZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUEs5U0JOTWpURld3VjVZVWJFLXhvNUFVR0pfeWJzdm81ZlJUbHBDcWxBUGE1U1lFS3V4bnRkbHZiTGpXUjdDYnJWdTRkQWM0LWI3dDd2eTYzZ2ZURkVQRjZqTmNsR0h6eHBuLTUwYWF2bDhUTjl5QTlJVll5b29KY3ZpYkQyR2JXWGNkUEpZeXpWSGY2Nmc?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13-05-2026 16:38 UTC</t>
+          <t>14-05-2026 14:15 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pharmaceutical industry key sector for diversifying export basket: Health Minister</t>
+          <t>Nevian starts exporting medicines to Canada</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amader Barta</t>
+          <t>Prothom Alo English</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxObjBhdTQwMVNqdlcwSTBDSnZIN2RSNlc2Vng4eWFqaFdHM0JQZXV4TzFnb0VjMU1rUnotS2NnYkNIV0hOMVo2Ym1fZXNRS3pXVFVIRjlOalZSTnVFTzFWVE1LVGF5QXZJeTN5cDliM2FlQkJKUlk4a3lGZUlxNmlvempMQ0g5T2U1X0FxR3M0RTJQS0txY3JIYjJ4LWRkdzB3NmEyWmR0blMwUUlGdjdkenBhZUxGVFRLaU1EX1lwTVczUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uR2F1aVg3d0Fjcm9uRERKM0kzRmtqM1VVcFVnTlZmVHVxeE1UX0kyOG1DOFJfcmtBcTFrdlVjanpRb0hDd1FJVzRHU0J1R29RcjVUTjJSQjFxV3FVUzZuR2oxNTRkbDTSAWdBVV95cUxNbkdhdWlYN3dBY3JvbkRESjNJM0ZrajNVVXBVZ05WZlR1cXhNVF9JMjhtQzhSX3JrQXExa3ZVY2p6UW9IQ3dRSVc0R1NCdUdvUXI1VE4yUkIxcVdxVVM2bkdqMTU0ZGw0?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13-05-2026 15:14 UTC</t>
+          <t>14-05-2026 12:53 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,64 +560,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Formycon stock (DE000A1EWVY8): German biosimilar developer navigates competitive pipeline</t>
+          <t>IPF patients call for greater awareness and treatment support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeDlVVG5HQzJKVWg1NC1fRHBZeHBjYWlDcVB0c0NCNFdVZWFZb0RwTWcxUG93S1d3QzZBR3k0UWZaTXluRnVKaFphLU9WQ0FqdUp3NEd4MFBwWERrRGVMdWZicVYxTkdfYW91X3JXMXZnSmJaa21JU3Q0ZmRwMUstR3JNcFBYeGJCcExfUUJIWDQzMGhkcnZ5VzJmNU1OWUlsNGdtSVpmUVRjaTk5WlZPTEtVQmFQUTlyZlRDYzI0el9TQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13-05-2026 12:51 UTC</t>
+          <t>14-05-2026 05:36 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Richter publishes Q1 2026 results</t>
+          <t>Boehringer Ingelheim Secures Next-Generation Autoimmune Therapy Candidate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gedeon Richter Plc</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE5MeHNtY05Odlh0ODRab1BEcnplUFVDRDBUenZBU3dxeTdyU2YzUjVGekUxTUQxOTZQcnQ3TEh0TVh2VngzbjVZejM4aW1MQjN4d3FxZ3ZZSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1uNktXM1JuSUg4Vm8xbUQ0YXFBS3Q4Q3Y0SVFmRy1KRzlvTHRFNlI3SGdrNUFrc0xORU1LajZJUWZmLUJ3empHOUV4cVpMdXhfbmF3TXRYWThtLTI2UDIwUW81QjVjLTQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13-05-2026 16:46 UTC</t>
+          <t>13-05-2026 23:00 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -629,214 +629,214 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brainomix and Boehringer Ingelheim continue partnership in pulmonary fibrosis</t>
+          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>Pulmonary Fibrosis News</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPbGliS3lfVzhER3JUNW5va19pZG1QMmNZYTYwQUZYa0pTSXUzeTlIb0o1YmNXRl83N01sTDVsZU5MTU14Y256c2dzTm9zXzJaRmM0SHdmS05IRmNSamZWc1NLdHZxYW5RSU93eExYZGdjTk1UX19tVUVHSTYySVFtTFBvQWNEM2RpT3Z5NXR0ZFhOV1NWd0llTnB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROakQyWnprQQ?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13-05-2026 13:36 UTC</t>
+          <t>13-05-2026 20:14 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boehringer and Immunitas agree on licensing deal for chronic inflammatory and autoimmune diseases</t>
+          <t>A Look At Amgen (AMGN) Valuation After Q1 Beat Guidance Upgrade And US$300 Million US Expansion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ0pzeENDSjZVUU9SX29rc2R5RW5qX1JDTmtEcVY2UXM5clRJb0w0alVTMmo1dEpwMDhCcUVsNmF3Q05LWkpKRW82UWFwVkZRbldaZGVNSG1tVXg5TG5TNDRQMXYtaVNaSUNhWW5QcEZjUDk1UUpiVzBHb2dHR014OHVaNlV4anEwLWY5Wnkyb3AyUWlhckttRzJYcXY5bnBLRzZyWWdUVnh6UGJmSV9IbC1mOUZnOXgtLWx2VDR4RTRQclRFN0NqTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQbF9pVnlGNFRSVU1DTEdITl9CNl9NTGpOVGMtSkk1bExUeDRRSEpidExac0JmWnViUk1jcG9tcDR0QmNRWHhCajZmdnZzTmlLczZqNWdscGh3T3hHQmpkTlV2WnlWdGQxRWs0QXpGd0UtWDdrTTBwQllEaXRTMmQ2bkJHclhrN2Z2Q1h5cjVfQkZOaGg2bE02MDdoOTQwRVRwMEN1X0xmLThCb0ExbnFSWG5fWDNqX0NQQ3duRDhmMDVMSEZ1bXZEWEJEU01ZZHV0dC01VThR0gHbAUFVX3lxTFBkYTVRLWRDS3FRenZSTzVvaHJXOXhUZWxVams3WW9FSnJOMXBzOXNWZ0wyQjJuc2tmazhfOUtPZTVBaUxQNHBFNW5nb09FNXJiTXFHM3A5dE1wNURmNklobnA2cHgzUUZkLXhIQ2xtR1ZnN3JYQ0tJR2JQQTRQUFk1eFBmQVl6MmpLYWhVYkJxTUcwcDFZX0VPVFhGMmtHR0U5cm13V0NCQXA0UWxiTzE5NTBrcUlyUVlCcDEwV1FGWUlMSXlZUHh5T1VpUnFzT1FRd1YzMDJDZWJsOA?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13-05-2026 12:02 UTC</t>
+          <t>14-05-2026 01:07 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IPF patients call for greater awareness and treatment support</t>
+          <t>AMGN: Key products and pipeline assets drive growth, with 2026 targeted as a pivotal transition year</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9Xc1k2RUJYRjNtWmVDa1dEVUo3ZDlOaGNCREJyeTcwRG9ocHJyZENSMS1hck5OMFd3SUwyMldwNll6clFPbjBzdTd6TmR2RXZhU0dGMnpodHJBX25keE5OZXpveHFyTm1INHBUbEN30gFyQVVfeXFMTTZBaGVDSDR5N1RIUTNGMHFGbENOa01oTF9aRmRLX1hlVUt3SWdlXzJwU0xmdFNyRjZOQTVFeklxMk5HenQwNXM0SGtNN3R6aFBOV1hwdU5nUmhQanp6NW9mdDluYTNrLVBPQWRZYlZhbjB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPU0JDdmQ0dHlscl9Yc255dmRtd0tlRmh4bnc0ZFozeXNyOG43Q1FsTEdEOVhIWXlFdEctZGRXSV9tYjBkWld5NHExSnFOQmY0YlVpR24xajJhODdfWmpEcjI0WVgxRmw1T3plVUV1T1FYeEhCTjE5Z1pYRDY2ZzhVRklyVjlrN2RaVXdIV2JCdGFrUXlRWk5GMTRqZ3ZZd081YWc4SmVnYUlkWjl2SzVSWTRqSWdQQW51cjE2bk1QNG1pRk1wOUdWQk5ES3VjcEIyRG5nb1pzVXJYNVNQd01GVkYzdjlrWlBjelk1eFpTc3Z4aFRKaUd1bWRERGoxTzFoMXVPTXVncXVaRlpMcXNidUhlWQ?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-05-2026 05:36 UTC</t>
+          <t>13-05-2026 18:04 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Companies testing AI analysis tool for early diagnosis of PF</t>
+          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pulmonary Fibrosis News</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPSzJKbjUzNVVfY1RmdXRZbG84SUp2TXRfV3U0STRoSHYxbFBtTFNrMV9KMFl5WWtZVTdiajRvOVYxcUQ0MG94blRiVm5QS1RrTEZUS2RZM01pdXlKbkhFY3JsYW0tUWFaMGZTbDF4Y3dLaWZLV3RKSEZGMUhpZ1pwelZrMmc0UFlCZmJOOUcwaEROajQyWnprQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZk5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13-05-2026 20:14 UTC</t>
+          <t>14-05-2026 03:22 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Viatris-Mylan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): Active in growing psychedelics and iron drugs market</t>
+          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQR2hUQTZnWjdIUGZKb1pjOXJTWVdtZ25rVWdyNGY2dE5yRWxoU1VWNDJGdDNFYnlSMWNsUVJZSjR5Uy1aUFZnWm9lWTFOeWNXMHd2NWlVMFFfTk5lOXROM3hDVmNjajh3RHloMGtkT2lUa3lXQUljZDFDbURUZTRtMElRR2c3V0dWX1ZoelVxekRpRjFFdUhPRTVNQ0FXSzRlc3JwMVFvXzZydG5jNWp6SGZNS0h0b1RGUHphNzN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeHk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13-05-2026 12:43 UTC</t>
+          <t>14-05-2026 12:50 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen expands U.S. manufacturing footprint with additional $300m Puerto Rico investment</t>
+          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Manufacturer</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPcTlIckFocHo5eFNvTGJSS3ZVRE1BbElIZmlyNndMMHdXckZOLW82cVJ4UjFfR0s3Tm82Qi1pR3I0cTZCTDJ3cGtzMXBUMEw1LXlWMWlDR2ZGXzlWUDlzdkZ6VXE2YjVUaTNzMTJVVEQ3ZGdjNFRFSHRTU0JNc3A2T1ZBNERQSTJleVlxcFdaVC1sYnlVNWQtVThqNS1iMUc5NHFpSTF1UkRNMHUzMEtUNnkzM1VHWXptY3lieGhQYVNjamtBNXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOaVQwNGItRUpuZEJpZHhVMjVPR0NrMHRvQUVwa0hjYURXbjZzcGlaS3FheDZ6QlJfOGh1THJjX0dFbXJUcEFIUG90QXFtRHVQeURGQS12RU1CdTlqQ19adTBKNWdLVGM5ckFOa21yNUdXWThvZGwxdlVnaWFqVDhNa3hybVhfZnJJUi1CUQ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14-05-2026 05:08 UTC</t>
+          <t>14-05-2026 08:51 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): Q1 earnings beat with revenue up 5.8%</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQRDk2SjhDeUNYbUhCajRrR0hjSUk2UDZyQzNvZ1J5cmNJd2hFMDZLQWlmaXY2eXZQUkNsR3hwdmF1UnJ6dXlMWWtiT0VfZXpPUUJHbHgxOFdadDh6NHUwQVZ6VExxX00zNWVKMXowOE1iOU54SWNqQjQ1bW0xNkdLSlpyeEpTbG45SXhMTERZQTNaTE5Xd2RFbjhQQTFHV3Fnb1diZ185dTYzeUlmRFFCc1hPUmppRTRWamo2VzFaaVFueXpuQzQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQWWdabGFYSUVHbWk2VEY1Z1FzSXU2ckxTOHh6NUNKRG85dmduVG9IeE0wMXA0OUlfQWN3SmdMWDBUajBFS3lwMlR1aVpDaHpTUkhEaTcwQnFQY2tFMERWMG1tT21IY0hCWGI2ZlBVZGxzaVU2Mll3bTh5WjBhSFcySVVBbmtjYW5NcW13dHRqUlNVdWtLaWhnSWdR?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13-05-2026 16:03 UTC</t>
+          <t>14-05-2026 15:20 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -848,64 +848,64 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aiming for the Sun: How the $11.75 billion Organon buy is cementing Dilip Shanghvi’s legacy</t>
+          <t>Pfizer discloses new dual calcitonin/amylin receptor agonists</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNSnZOV1FkZk5fdDYwOXRlZm5uTW1rWk9kNE9YWmhUdlFMdTI0OWhyUDhmc1h0enpzWDRxN21zanY4SGxBeVlNblVNeXhFc0h6SzA1Wm9QSU9fOXhXaGJlYjN4ZU40amlrWE5TajEydjlkUEFlT0g0T2xJMFBxbEdQWS14UGVCLUtJWlZ3THZnQ3p3X3UwZlZESFlNNlF1eUUzd3lMV0sxQnBLeDMzSllvOElDSkY1X1J3U1hZVllqemNUcHBVSlZ2QlVxSkVseF9VbkxnU1lBOTZRSGVlb0k3YVhEWGZxYTBlenFsYi1ZOGVIWjFx0gH6AUFVX3lxTE5fR0I5R1ctbVRjTW9IUnVFaEhDLXBxUlZyaXI3c0E1Z054NERGMG45aG00MmtrMURJRG5iRjBJZVZmbXk3N3EtMmdBVE5lU25ISWJBaXNMRDBfYTZGWE53c2dKNmFVdDY3RHEtMUl5WWUwbWZxaHJrdUd0ZkoxczQxSzZNTjdyOURDMXo3dzNveDVVSjcwSHdiNVJ6S2FvQWlmZFZ5UDZhZnJVX29WUmRBZDRCb18xZngxZkpaZ2o3TjBzQklvNnBMTC12M3luWElMaFI1MjB4SkluT2ZZLU1FV0VOY1RZUnNiQnFNVzdvdDIxeWdacFVYeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOWEdFWjVHeHpmY29DZmtNZk1iRkd4Um1VaXlZT0twSFk3U2lIVW5iR2R5SHRpcjM3THBwWGZJc2FpcU1XMlJicUlHbVhHU1RmRHlOUE5nN2ZWcXNGU0NybXZsdm1rQ0Vjb2ZveG9GX3AwZWpPTXBWakhBQWU3MGlqTXZOSTM5NHcyU0lfakQ5aGlrRWs5aTk2bDZxdEQtaTZaTy1Paw?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13-05-2026 13:54 UTC</t>
+          <t>14-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CCMB scientists in Hyderabad discover plant protein that may aid dementia, cancer treatment</t>
+          <t>Pfizer's Turnaround Is Taking Shape (NYSE:PFE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNU2ZJTDBmUk53MWJIckE3aVl1bXhBbExVcW5XU1g0bmtCODdHTE83ZlY0dmVqZHdXM0FSbjYzSDhWSW5yX0RkV3Vldmt2Y1pxODg0Tnd6RjBXcUtaOGZleHZXSW9CRU4zdzZZMDNSSUhoXzQ4REc0SWk5TE9MTU40bDdXbThwUTZRdmtNZ2VhcHR6QVpkRTlVaXJmZF9jSDdFbFVWc2NZOTJlMHUwa29ZckM3UXRxY0Y0TmstY184ckR0eXdUN2NhMGpxMW1sNk1qbXY1Z0plN3RVREhZWFhaZm5KazJLQ2_SAfQBQVVfeXFMTXBFdF9EUy1wRzJYZm5wYzdYRmVvSUVrdmI5dFBGOWs3VncwRlZYa0c1dG1MN0JRbDBvSHdLYnlYNHp3NTk5Qm5MZXJieElsSXdfUFVyUG1JWE4wYjByZlU0c0VXQkJWNkMwTG1ZSXBrUTRXMkxiZ2sxLXVMbi1TM1prUUw4UnZQcFVWT01sVFNqM2h5Y0lCSW5QRXFRYWEtaDdtMXRVbFdOWUczbGxUZHBNZmxwTWNNNF9tOTZadEdReHA3Uk1FdlV4THhKMGs2STNPVnp2eEZOM3BFQ3BlUjFUT1VPZkRDcWJsOURYbkprT2RVRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY0JXVkdneHBUc2lzY3Q0SFpfMWFWUXR5UFM1b0g3SnYzbHlpYllCTjR3UWx0d19ZLWs3LUFOYTdTRllxcThVUlJ6eDF5LXEtRW5FUGNtNlFYN3E2QzNkOEJUcC05WnR1bjFtNXBvb2pKZzBEU2hrZnNlYVFWSi1jSA?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-05-2026 03:22 UTC</t>
+          <t>14-05-2026 13:30 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNMDlDaGpZMGEwQUJBdEJTc1VENkVVa0tmZUpkSDYxUnJkRVNXVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNrYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0_SAagBQVVfeXFMTTA5Q2hqWTBhMEFCQXRCU3NVRDZFVWtLZmVKZEg2MVJyZEVTVmRUY05tR2VRTjlXMlktNUZUZU1IeS05LVdxM09BQjFRMDNpYWxjdjBfcGNXS0VXaHQ1RUhZN1BnS0N5X3lyeTBzdjltN0FCeDFKZXFLck9RSS1PQWxPOFZIODlQTURSeVVvbzVrTmhiTG5KMVJiNWpnZ19pSlR6WEFhU0?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -949,27 +949,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
+          <t>Pfizer stock (US7170811035): Q1 earnings beat with revenue growth and 2026 guidance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contract Pharma</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTXdCZEdhOEhiQ2UwWS01bUlsS3l0ZGtfWlJSMHBKVnY3aVE0b2JMQjRZUk96MWYtWFRXMzkteGM2bjBodnZ2T0otdkdHZHQzV1RlcnFvLTZTSnhIdHJKSGVweFFRNjZ2NUdJM0UwTi1RdGdVYjdsSko3b2d2ZWRwbVQ4VUdDWDBrUWdkb0Z6T0pOc0hic1RHdEZzN3ZlMm9hYWppVGZQdGRFaU96djVtSUE4cHpTeWpoOW9zMFhQVVIyV2RmMW9WaWF3?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13-05-2026 19:26 UTC</t>
+          <t>14-05-2026 16:01 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -981,27 +981,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
+          <t>Pfizer’s Hympavzi Indication Expanded in EU for Treatment of Hemophilia A or B With Inhibitors</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2dUY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPUXRvOXZMVlcxRl9EdTBFX2JJRi1vU2t1T0tFTTBYTjNVZEVtVWltNXBZZWJHUnZzTlBSOXNfMTVXbGQyZTRPZFF3LVh5V2lxMTdqa28yb2dHdjc4Wkh1SWlId2JSbW5fUUZ6LUVhOEdYNUM4UHdEcmhHc2w4b3VSU0psV3dobGVtWHNvY3BjbmVSNWtsY29jWFZuLVRycU01QXJWWkEzX1Z5YnJ4eHhzYWs4RTBCWUhCaS16Wm1vY1N6VzFBZC1wQlJONm04NHRuNHhSQXpB?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13-05-2026 19:16 UTC</t>
+          <t>13-05-2026 19:26 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -1013,59 +1013,59 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rigel Pharmaceuticals Enters an Exclusive Global Licensing Agreement with Arvinas and Pfizer for Veppanu | PharmExec</t>
+          <t>From oncology to obesity, Pfizer bets big on India for its next growth wave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pharmaceutical Executive</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdXpwSEt0WGNHSXBrV3VtLXNWbEFIZl9kRzh1ZnJtc0JPS1A1TEw4NVhmbDZwaHBucDFlNkxlbWZqWWdyZ0tPYzVPZEstMHJSLUZ2YWFxSGFQUG9QMDd5VjFYc1lKUUNncXo1aUE2eGFzTlVXTnIwM3p1NG9CMlAyNzlsR1I1am9HUmpYeGNIeGp2M1h5amh2NU5tdV85V19NUzRpVkx0SS1lYWZLRXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPc2ZfWjJ6bk5QajVUdnlTUXBXM1VkaVlmNG5nYUh0UTl1VC1XUlpReTQ5UEFfX2tzckRpWTlsNGhwQU05allXcHJ5TGc0bWcybk1HTk9XRWxjY3NFZUpJblZkeXpJYkQxQ0V3ZXhGQ0ZaQ3o1b0tpNEhGRmwxYWpQek81d2ZiVFU3WlIwNFhNU1p4U2ZPMTFDU2Y2TFY2aGRLdExmMjhGSkl2RXhDSTBDWmJtbC1PdUxwN1pPMnE4ZEE4WEJBcmxZa21RdFdZRUFXNU05bFRXbEFIM3UyQjJEdUtGaDhvbVJ4NzBpNjBEYjdteEZ6QmxJZVRLS3JBYVRmcHfSAYcCQVVfeXFMTW1TR29qc3JXSS1QaXFFMnlQY0k4ZUg4Y1d1Ri1ueHUxRjhCYXlDNlpDUnI2MUlZSkxyWFA3ZlhUWnd2bzJrUHpubHlFVUJ2SXZEWWlGaVdpd0VUTzVvRWJ1OXY4QjctRWs1bGROcE5TWVhTYUtkM19idF9WLVVDT3JvSkpBSk5yampPWTFaV2hMZlpHSUNOaEpuaTNPbExxekJFcktZUml6c1VaZFVDVDQ5UmRtTjV2eEVUa21JYXNTWndTOEExank1c2k2T2tkVFg3a2ZnLUsxaENXa1lTMEJLd1VZVl9td3JiYUlrMVpGZWNUZ3pWTGlEUzRmMTVzZEYwaHF6UFU?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13-05-2026 18:47 UTC</t>
+          <t>13-05-2026 19:16 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pfizer stock (US7170811035): Q1 earnings beat estimates with $14.5B revenue</t>
+          <t>Biogen Completes Acquisition of Apellis Pharmaceuticals</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQNjZYTFU5clo5NVRrTVVHczJRQmw3SGt5aTV5cWxlSVNUdkowV3lnaGJDRnhxQnFvM3UwTWFPQWotS1A4YnJMYkN5ZzhldDRSVjd1bVg0a013RFBNUS1IUnNyeHdVNzZUbXJFczliSVoxMXZ3U3J4U3F5SHowUGVoUWhJdHhwWUhqSl9xYlNLbHpnWkVOaFczT3NleGxXYXl3OE84WmExMk9wY1lWbVVqZWRVbmFxU2lwNTMzNFU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ256enZtNjcySFlVRFVBdlVmVlIxLVFUYVZGVVJCMWJyaEVwaG1XSFdrOWxZU3ZDWGtiZmVUNkRtSmtKeTIyaldoQ2xuQ3JzaXdQeUNteGZOM3hZYzI5UUJ0MXVYNDBjVGZrSldQQUFSaF9MUUphR1lyX3daMl9pODJkdGU1NWRLM0NLRDlvelJmOEkzYV92VkY1TE1qWEFXV3dyWW1FeGJObnowT0VfUlRISFR0YXc?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13-05-2026 15:30 UTC</t>
+          <t>14-05-2026 12:38 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
@@ -1077,22 +1077,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
+          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPNXVaaUJRLWVNNmk3RlN4X3h1cGUwVVRQNllwMktEU2pJLXRSM25wdWNNNFZmV1BoYjhLSFphajk3UE41dzdnSmVJaGNVbVdDSngwWE9zSV94eUlRYkN2ZkFsTlg1Y3ZMVk1EY05HM3RkazdEdmRtRDdwckh6N0oydV9JWGdMV3hlMWxjTGgxYWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFlDbDJSQ21yUHpqZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14-05-2026 11:05 UTC</t>
+          <t>14-05-2026 16:39 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1109,59 +1109,59 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biogen plans registrational study for Alzheimer’s drug diranersen By Investing.com</t>
+          <t>Biogen Pharmachem Turns Profitable with Net Profit of ₹85.95 Lacs in FY26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNa2tidUxrODZCOF9sSjZuRXBCS0lua2p6ekVMRElQdEhId1o4Um5GTGhiOF9iQlNIWDFLU0htNzllY1dnVHlfV0w2dDBHOGhmTVcxcXYwYmNsM05jRDJLTFE4c3g1X0Zvb2V0bVJSbTJ4OUhwVXlLWEJOQW51Y3FtZmw3SXA3c2NDYVk4MEVwUXJqM2MxT3VvaEJQa2tjQzFFTXc5amJ4VDZQQ2hQUVp6c3ZUZU1rTFM3U1FDMnpRZi1WLW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNRWJfaFBXWmVQQ0tzZTczdGczZVBwNWNXd3dFWkRTV001dFNxQlBwV0FueUdXTGEtMGRUZm5ZODB0bWxVS1ItTU1uVjI0b25BOTJ4Wkt3S3ZFUkxpQjBSTW5vcFdGbEF6RU9qMjVuQWhLWkwyZk83Wk0zUDYzQlZKVEFSTHdZdzN4UGhybmFUTVdMc3p0aTFMd0t6ak40NEFJUjF0S2NydWlTTGYwS1ROV1dod0RrYXRGenNvdFZnSjYzM2lZRkEtbzVnd1dFVDluaWVnZWROT2tTeDRSNng0TE1ybkVnWHVIbUI4eTNyTWVjVTNRNWc?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14-05-2026 11:15 UTC</t>
+          <t>14-05-2026 15:56 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
+          <t>Ionis partner Biogen announces topline results from Phase 2 CELIA study of diranersen (BIIB080): first study to show reduction in tau pathology and cognitive benefit in patients with early Alzheimer’s disease</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chemical Industry Digest</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNmFpemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AJBVV95cUxOVFp1c2VXa1dRNDBzUGtUd0VpOFZXMm5MNVVXY1VtLXdEUmxkdGhpeURQYnBONEpObHBDWmE2RHNsNFNNWkpWVzQ0ZmhyNW9BOGljQllSTUJQenRMT1A5QXppajBSQzlDY2FHMHNOYVNwby15eGxfSUpIcVN2LXBmSnFTZGlEZXUxaU1hbFNmcjdVOWtpMHh5ckZjWnZjT3lqWUFUZVIzUVFxQVNyZWRvUUswR2xCMVlwUjc2SDU3SkFldTRmdnRCeGYweFJVdnFoZzhHcnlfbnNNeW1udUUxUlNYV2I1UVNldGZCaVZtYWg3Q3ZrVlNXaF82clg1OXFmNHJOOUt2Tzh3UWk1ZUZSUXRwSWhWSlRXR0tfMTFWTk56RUxfMG1Lam5zdUxBVEc4UUc3U2ExM3BpcGJMTkt2S3RWaG9VT21Odmc3TkpHdE9iZ2s0OWpuaUh1dVdsMWd5OWJzcmduU0ZpTC1UbmNFQ3JwMnNxQ21D?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>14-05-2026 07:29 UTC</t>
+          <t>14-05-2026 11:05 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4 Profit Crashes 86% to Rs 221 Crore as North America Generics Sales Slump</t>
+          <t>Dr. Reddy’s Laboratories Secures CDSCO Approval for Generic Oral Semaglutide in India</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Chemical Industry Digest</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNTFExREh4a044UGNwR3lhdnBiWUtvYjdTS0lHRUE3cGJJblItVkc2T3Awb190WkxIX0Zwejg0bUZxS3Jjc0FBbVhQc3BSdEd2dDNQRWduQXV1dVUyaXNscVZwQUd2VUNBQ1diNWtfYXQ5TGp6THE0UDV3eld5Z3pOUS02cThOWmpBSDdfOFF6d0dzY3I1cm05dHJZZW1ZbGgyRm43d2xZdTJpaTNySTItN0dCLUctTWhQbjdxV2RnT29JbERGYi1GNWlVZFBJVXAyeVF3VEFIY9IB3AFBVV95cUxQaGVOQi1xT3JnNjFYenhkejI1RlpySFJQOWU2Q1dzU3VwWGJkTXhQdmdENkpFU0tGVUNNY1NyNjJmUXVpUUJQYTE3UTRxbXBCT3FVSUljMVg0bk1nVWI4U3lFSG50bzVsaXgwNGhkZF9HUlFSTFVDNDA3ZXlxUTZQdjBkUHFQQXRHNi04OE9ENFVjR1lWcDFlOWxnRWlKZS11UDZ1UGtZTFFCTkVreDZhOFlVQWgybXNIUWdpQ3REVjVSVVFKd3YwMExXQko4ZlgtODktMDBhY0dOU3da?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNbEJpUjRTMk9RWTEtOS0yRTNYcWdkSi1uZm95RExNZ09Pd0pQLUdWQ3pvbnJqaEV1UWUxR1k3eHR4a1pOT3RGTV93cTlJQXRlc0JWMnE0c25fYnJIRXlqSXZFZzdZWThOYWU4M21xcks1N3l1ckROa2ZfVFRMdGZaZFBMMzlsc2tUUjJDNm9BemRMVWRZb1BudjJSYUFrYld5Z295NHIzd3MyV0h4UUE?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13-05-2026 15:23 UTC</t>
+          <t>14-05-2026 12:59 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -1205,182 +1205,182 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Indian drugmakers turn to buffers stocks, contract tweaks to tackle Iran war fallout</t>
+          <t>Dr. Reddy's Laboratories Q4 Earnings Call Highlights</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPTmNtd0lLbG9mYkt0dkU3VWhCU19DbmMwQ1d2Um4tS19vZldBaVp5Y01rMXk0T3dZaHlfSDdmR0llbTJwVm9hMTFyckZ2QzVEUjBIaFVaaC1XUkZKT0lsalZBQjlTVmlJMm40MUNzWWh0RWV3OURaUmhBbXI2OXZwTEE3VGNZRG8wNHo0U2Y5SmdmOVFmNjlNNTNBdDFRUVk0ZkpVMFNqWTVrdnlSSll2enZGS2EyaXBYMk1WMHMwTHgyeXhOcDBCUkF0S2NzUzNseXlEc0JJUWhpbzJiZ0hR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPLTN5OE5MMnR5bW5tSHo0Y3AyYlJadjFYNjExaDdaaVdVS0JybnBmTE1NZWJ5TXNjdHo1cldabFRHa3NxY0V5RDNoa3ZBNks3SVJsOFg5eTI0ZUlQVU5rUVZURm9kTDl4T1pmZk05OHJtRnZNWE5XUEhVYUFydHhpQ2RUVUN6VGhMcW56bUV5V19QNkNOMVpJbXo4bzNDVFEwMzFmNnV3UQ?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14-05-2026 03:38 UTC</t>
+          <t>14-05-2026 12:22 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
+          <t>Raja Sekar Balasubramanian Appointed Head – Digital Process &amp; Excellence (SCM) at Dr. Reddy’s Laboratories</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Capital-Riesgo.es</t>
+          <t>CXO Digitalpulse</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYk5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDZaOXlKMkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxORzg1N3d5Zkx0ZmdRNFRSejNSbDctc3V0eEoxdGFKTlp0SzByQWd5U1oxcWQ1eDU3dDVITGdCR2pZNVFUYkpTLXNPNnBTQ2RzVnJVUm9pZkk2MnEzXzIyQ1dNZzUwSkNjYkZYTmhaRFQ2Yk1IM1lFbjhVdktJdUlWXzRTVmNUcWFKWjM0MFFvbjY2cUwtSWRxTzNvNnFraDV3M1RKLW90cXNXUWFYanM2WGg2V2RPM1o2QUExVjkwSGJSLVZqanlmS0pTMA?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14-05-2026 05:06 UTC</t>
+          <t>14-05-2026 13:08 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biocon Arm Gets Health Canada Nod for Micafungin Injection to Treat Serious Fungal Infections</t>
+          <t>Margin revival, Semaglutide launch to drive Dr Reddy’s growth momentum in FY27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPeXZfaGNUQzUzNU83dVlFaHBFM0NJekhsY29CaTlFRURFNWxKT1RqOVJWSGg1UFFGYzVZc2dTRG9XZnJpcTlud1JuOUlrZnFCbWxYaUNfWTVPQVlwZzZsVXJkbHNoVlUzUmd6ZHVza09GcThSMjkxNGRUOUVhOXpGQkl2TmlndDF1Y3VTOEpEaG1DR3BpYTBVZG9oNV9iVFIzNmo1dm5ES1dKZXVuV1NWcWlWaWRieGtnUWt3d2RvVWp4ZExUcFNsc0IycTZGSkt2Ull6N0IzZjU1Y1lwT3Y0c2dhSdIB6AFBVV95cUxOX0xkRWlxOGlRMks4aEtRdmlheUxNWUxkY2JNeGE2OGNGeWNpdGNtUjFPcXd1SjMxdVJoVzVKUTBLUE91MnZoZmVmOGo1TFFhQzRYSmxHdjRuTFR1NFNyZi12cUt3OC01Z3NsZ2drb0I4LWZXamp1aTFTX21BSTdxaE9wQlUwZjNuYjVNOERRWnhXSkpOS0VQQkJmWTBsdXVnTWg1VHNseGo3anp6MmJNZG1kYVNKdERKNjlFVnBQT21Fa2djUVFVSTJSMGZBRWpjdnpfNFRhNTdIcVpIOUo3WDBzRWluSE55?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQMFhOQTd5Rk93OFlReHJGMVFoNlZlRGpJYmtydlpIRjREZ3Z2M2x4bEYtcHVFT1FtZjI5OXZfVVZGWEl5dVUtS2U0d0Nva0VOMnV1VHhCNnFJSV9YYVVyMnJmVUZob0ZxdmtsNHJ1U1BLZWJmYnBULTlLck1tMDFYWW9fV3NxUHRHV1NWRE04TUZkYmk1VzZ4cGZCai1LbmZWcTN5TVhOcHRVWnBOZlJ5YkJtbXhleEE3cndkZTIzOTNfVERLLVAyTklrakxVVlg2TU1sV1ZYNHhzTGlFaTBEQ0Y0MlhvelRYSnc?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13-05-2026 15:08 UTC</t>
+          <t>14-05-2026 00:44 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zydus to buy Assertio for $166.4 million</t>
+          <t>Mrugank Sheth Joins Intas Pharmaceuticals as General Manager – Marketing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>hrtoday.in</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUHk3SXJBMDJvWVV6aExfeFVvVzZySGdiR2hLcUhCemRBWkpuajZVWXpUVXZ2dUR4djEzdnhoaFpXRkpNQkd3cFIzUWVnSE1XLU9yNWloM3lGTlRuTk54bXRibmZmN3N5Z3BjTkVwZHhyZVhrX2twa0lUZE82YXJnUTI1RWpSQWNuMWFORFRNNFFQLU0zZm9MTjl6bUJDNmt5eGtaV2FFNHFXbTNtRzN0ZGVxeUE4Ym4yRDJTbmxWZ1JieHh3b21LR09pamPSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFS0xRMGhJpHQ90</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY29aaUxSSno0SHRHb0IxcndNa01ickpQNTVmT2h2cXZkZzdFbFpQZTRPMFliREx3MUNQQ2p2YWxrYUFyM2dLeGt1TEJGclRleElsUzZGMTUzSUYzVXhzc3BsN1owQVRzaE1kV1RZOXFfNFJMaERHM0ptbU45dVRDZFpCVm0wd0tFSWdpa01WOEVkZ3lv?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14-05-2026 05:45 UTC</t>
+          <t>14-05-2026 11:32 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
+          <t>Baker Tilly advises CYGYC Biocon on its sale to WVT Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Capital-Riesgo.es</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNX2RQRVVOYm5YcERpbHBzb1hpajBaVGl3elRycHp2VDBPUUpXR1hWNUk5allmR0c3YnlwRk1nT1ZlYWd1a04xZmZ5WVpqWkNKSV9GR2VtTWxIVnVsM1NVQ3ktZEF5MWRfVnlQbmFhX1QxMnFrWFpvM2pLVXhQbjVFMkFsOVZBQzhJWC13bXI5MEhmVjVzaDdaOXlKMkE?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-05-2026 07:44 UTC</t>
+          <t>14-05-2026 05:06 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Celltrion gains 70% Europe infliximab share as SC formulations surge - CHOSUNBIZ</t>
+          <t>Zydus Lifesciences GST Appeal Order Upholds Rs. 10.12 Million Penalty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVGRZcDRheFB2ODlMVDJWc0xINXE3bjBhRGZDYWZqZzdsbkZBbjl6cE9qR0QxR3VTVl96RnZtZ2lrbmgwTGJ6aHVSR1V3WTc0NVJYbnozUFQ3aHN1b2x2dDVFUU44dmljMVZBcG5ZY09BczZQcTlrVUhHRC0zRFllZtIBlAFBVV95cUxPQzB5ME94VGhaOXlpTk9jVW5Geno2dlZSSWNOMTZ6T1hJR2pHamNWT21CU0Nzb0lVMldNZ09yY1liVFprV3F6ZjZzS0VFaEFVSjRERjVhUHhZUVNmc1FPTkxsSlNKMDItQ0VoQ2kwR0VXcXR2bi1iTUZCWkpENU5VTXh4TFBLSzA1M2VnRjNfck5MS1RX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObzlFc2ZuTFZ3QXB0ekRwNkFUWEVOaFZyejY3c1ZDN1JKU0VQNVpYU2dPSTlMLXhCdDZVUjNqTHBuT094ZktTRjB5dTByZTZ0aEhTQWh2T1B3WUs0OGV0SDhJRWFHUVF2bFBTS09hQ3Vic0cxZmVwMWpoeVZvc3RvZ3VaS2ZUT0d4RjM1clBSQmJfOUFYdXhKSW1hQ2ttYlg2QU1OU2lWYm9rZGhNd1VSMEE4TDlmSnVSc3hsRlZuMW1NZTlubmxwdXcxQmRjVm0tbjhHWVlZbEI4VmVTTjRJbmQ0a0Y0d09XQ0pFdWZCNUxkcnBXYVZDQ05JNWpsUQ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14-05-2026 00:37 UTC</t>
+          <t>14-05-2026 07:29 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,123 +1392,123 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
+          <t>Zydus to buy Assertio for $166.4 million</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNdFNkREV4WFFZUy1fdDZXOFlvVEdvTnoxVE1IdFJUcmhDdUVRYkE0bWE1aDhxN2dnc3JfZmZ5c0c0eXlSQXVKcGpLUDBVZjZ1cUprSEpfR1hYcmY3Q1NFSU5ENFpJTURXcmE2TFdnVW1nOGhxUFhsYmc0aDMxa2N4TWVETjVwVHFvY18xdUdUazlseWxMdlpTUUVFS0xxMGFJakdvWXhHRTUxVUdIMmtrZllTci1Qa2NzaWxzUXM1andPVmdqODNQc25MMlhHSkNlNlHSAdIBQVVfeXFMTXRTZERFeFhRWVMtX3Q2VzhZb1RHb056MVRNSHRSVHJoQ3VFUWJBNG1hNWg4cTdnZ3NyX2ZmeXNHNHl5UkF1SnBqS1AwVWY2dXFKa0hKX0dYWHJmN0NTRUlORDRaSU1EV3JhNkxXZ1VtZzhocVBYbGJnNGgzMWtjeE1lRE41cFRxb2NfMXVHVGs5bHlsTHZaU1FFS0xxMGFSWpHb1l4R0U1MVVHSDJra2ZZU3ItUGtjc2lsc1FzNWp3T1ZnajgzUHNuTDJYR0pDZTZR?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-05-2026 07:08 UTC</t>
+          <t>14-05-2026 05:45 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
+          <t>Analysts grow more bullish on Celltrion as margin expansion gains traction</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bk1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHJ3MWd3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVzdsQWpTNjJhU0FZYWEwTGxxR0kxRUVKX1NoRzdtWFM0a2dwWkhvRkJDUUd4TU9rZW90OHZTeVd1eTRuTWhORk15YmR1YlVocHBkcWMzOXEtWG5rWnBES0NXcjdkTS12SU5KVHlYOHVwd2x1NVlONjg3VXQ1ZDJ2dGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE0yQ0dibnJ6cVIzOWJvdDZmTG0xZ05PQ0dBMjB6UXR4dklIQzdwQVFTWVlLOTZxaHBfcFl5em04bXFlWGJwd2l0VTBTZjZzYnJYTWNxbkZSd2k4QmlydGxfbXlQR2ZEQlVjMUN4MWZ30gFyQVVfeXFMUENMM19meXJDWFNOaUVRTjFMOURncHBkUU1NLWUyWlQ1WGd3N01xV1JYeHgzZ1NYR2RoY0RwWmIzOUE2WTExM3ZneHlOYjZUd2RxQzJMMXJNd2ZhOF9sSGk1SG9RMU1ycGVPdkhTOXNjWGVR?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14-05-2026 04:27 UTC</t>
+          <t>14-05-2026 00:08 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kidswell Bio</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
+          <t>Celltrion Inc stock (KR7068270008): US biosimilar launch and facility acquisition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaGlRMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQak1zS2RSWk16TTlwcHRPUDdkQnhWXzRJc1JVbTNyRUM0SmdvNUhQWEs3Mno3RU9YenRKc0ZoS01sbHNzc2JlZnVSMk11ZEtQM3JJMm55dzBKR3ZRSFBYNEtROXhpQjFCMGRET1ZpNG9RODc5RG5ka3R4dEd5MVBlZ3JzcmhTQVM1R1RQcERqRjE4WHhjWXVOX21GU2FkMEw1VVZyNGZNNEg4bzhETU0xd2FfMjJ5Y0xOTFdldHNkSkFSRjA?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14-05-2026 09:33 UTC</t>
+          <t>14-05-2026 07:44 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
+          <t>Celltrion Widens Europe Share, Eyes Profit Beat</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBBanNBdGhOVVc5eUc2MjFERXNscGdMakdsc0tRZnVVdXhhN1h2YVRGX3RnYWtqN3BTdGJNelYzZkdUVi1hSllndmdRekJUYmtPOW5PSUw1TWRQU0ZrUzdacFNMWFJZOV9QN0pfV3l5VGxJYTJl?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13-05-2026 20:55 UTC</t>
+          <t>14-05-2026 02:49 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1520,155 +1520,155 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
+          <t>Celltrion Maintains 70% Combined Market Share for Remsima in Europe... Growth Continues Across New and Existing Product Lines</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Live Law</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZ9IB_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS05MEJnMUZPSHlkS3ZHekU1NTRWNUlLUnZlbjRIQzR1UEplR0tyTGpYcE8yZTlseWtoWkZ0ODNRUmphYm5pRHpENU9FZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1UazFJLTA2QmlDOFRPc3FJSlJRRXdsTTM2b29SLTE1Z3h0ZFo3ZEpRN1plWGRBMXZyVS15T0EzSHpiakZZYWdGdkxjMGt4UkFrdVR6NjA3Yk5mZHNHZC1iamVleVY?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14-05-2026 09:13 UTC</t>
+          <t>13-05-2026 23:07 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Indian pharma fuels Africa’s ‘zombie drug’ and opioid crisis</t>
+          <t>Daiichi Sankyo Company, Limited Just Missed EPS By 12%: Here's What Analysts Think Will Happen Next</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The Straits Times</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOUTVkNnQxLWJFZkFidzlBV0dLNGIwc0FlWGdhamFBTGxkM08wS1hnY0pfTWdZdkdIbXN4VkpnaDc4THJ4UmNmWkM0cUVjVlhzblJBY29NeVJZWEVXeEVZUm5fUEZYZWlqR3QzMXVLQVRHNGR4Q0NHU09idU1TbEE0WlB2VXFHNW9XUVBVc0pwYXJiZ3ZYNElr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQdGNfQ216Njlpdk5XdUJRUVhSVmV6Q0E2b3VpbHV5SW4ybUlJUmZvb1hDRDFlYXkzOUE2dzI0WUhzT3QzWU9mQ1lJMkZtRXhVV2hXR3FBM0oxY0JmWkhySUtEaDMteXBoNHhPaDNqM0tIeU96ZzlkOXRMczZBaUNRSUcwUFJKTWx5MERxb3k5SHdhSEQtUTlKZGpEeE1odFZGOUJ0dEJWQkVKc3pDVW4yQjZORXZpUzROdHpzdkhaRkpNaWppOUlXNEIyQ2xvX240WTVMM2J3a0JQaDg0RmNGY2dBeG1IZknSAewBQVVfeXFMTVAybGZncmNSSFFlcVZXcHUya19NV0tDczZWT3FZX0V4TzJ0b1J0Vm4xX2ZNLVlkSWJoSjdodl9UUkVXRHlvUWlFM0VFSUNrNm5RYkRKYWM1aEFZa2JxWVl1TmRVblllQm9LUGwyZGl1eDdZeERDRWxJYkRBNFpVYUl3bVpPMHlqMGV1eFZiTE5DRnFsSVZheUhhQzJYR19MczFzRldPVkhvWTdmclFoTVV5YWtyNUhEajhiRzFyVlh2RDF2N1gzOGxKYzZIaDQ2WFFnV2pNeTMwR3B5bzZ1R3ZmZEh2dXpVU2pvZGo?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14-05-2026 02:05 UTC</t>
+          <t>14-05-2026 00:09 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
+          <t>Kyowa Kirin Co Ltd stock (JP3249600002): CRYSVITA gains reimbursement in Canada</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQdXRkLU9IZlFabEo3WGgxZW9kN3VNbVhGOFVfQlJkSDIxcEMzR2RQa00xN2ZrYkpTeUZyTl94b0dKWDUwaUJiV2RHLUE5bWo0TDNNNlgwaDlacm1qN0txdmF2a3hMa3RpX1p2dGRFSmFrZjFwQ1lheENOd01uZGNjQVN0eG5oQm9waVgzTFpmZjRPRlROdUlXaDBBMGRyWDJYZHM4dGR0SXNVMnhmYV9QMXdvMl9iZk9VXzlsNm00TXVFZ0EweW1R?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14-05-2026 00:13 UTC</t>
+          <t>14-05-2026 07:08 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
+          <t>A Look At Kyowa Kirin (TSE:4151) Valuation After Positive KOMET-007 Leukemia Trial Update</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQX0NBd05OVXhfUlk5eWQ1NEhyM2kxdzdnZmRwRWhVRWxPRU9WOW5ic01ySVNmR3dWdUxncExPQktXNGtrMV9mQ09rQkkzRXNIb2RMblhpZXRPZlFMUkQ1MmZUSEJNWVl2VS1zN1Q5U1c3bEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bm1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq0gHoAUFVX3lxTFBfQ0F3Tk5VeF9SWTl5ZDU0SHIzaTF3N2dmZHBFaFVFbE9FT1Y5bmJzTXJJU2ZHd1Z1TGdwTE9CS1c0a2sxX2ZDT2tCSTNFc0hvZExuWGlldE9mUUxSRDUyZlRIQk1ZWXZVLXM3VDlTVXcybEFqUzYyYVNBWWFhMExscUdJMUVFSl9TaEc3bVhTNGtncFpIb0ZCQ1FHeE1Pa2VvdDh2U3lXdXk0bm1oTkZNeWJkdWJVaHBwZHFjMzlxLVhua1pwREtDV3I3ZE0tdklOSlR5WDh1cHdsdTVZTjY4N1V0NWQydnRq?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14-05-2026 10:46 UTC</t>
+          <t>14-05-2026 04:27 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Teva Cleared to Sell Generic Effexor XR -- a Pfizer Blockbuster</t>
+          <t>FDA Approves New Dosing Option for CRYSVITA® (burosumab-twza) in Adults With XLH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9jX0RSZzhuUjNZWW4yRUNERnl2ak9oU2pqa0NFNFpwbl83YmFNUmdWSXd0ckdSV3dDNG5XM2JlLUFMOWlDa3YzMXFvWGVTcUhnQmFlUEVDNWZJNjNLUlNTWDEyTzF1Mjc3amc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOSEhpdmsxTmFDMTljSWxndzBxYmhRZGlEV1NWYks4cXdPd0hZWk5vbEsxQ3FCOW1odkNMR2dlQmFFUjFrTWJHN2dmVzUwTDRfNWUxQ3B0b3RhRGRCTXFaLXFKQ1cxdmJQWmtyaHVCRUxGQmZrTExSNWQxRUtMb1V2dmVNWGdfZm8ydWRYaEtJSzNKQVpqVDJYN0prV25wZnZIUUpmcDlDV0dkazUwWXZsMnZyakR2eGVSdkg0NHczQUNLdlp6QmhfMWxYbmk3am1wY2RUREo0bWx6b2d5cFlpTlJPcGZTQdIB6wFBVV95cUxQdUdsclVGdlQyM01NWHdLQ3JlTFJxbUNQRzBsTFVWNmQzekdyRllndGlpX3B0eTItNzhwUkVfcm56NkV5bVpTeWRuUDM2Qm5EVFVlU2lxS0pyTlRqUGRiSm9hczN3UTNqcUFYMWdnOWZNcEJMa1BhSGhfdkQ4Z215b3p0TW5wNXdxeHpiUFRFNnJCaWM2ZmFEZU1Ha3ROanpRYXR2bmpERTFiamNzNzhnbVFyWFpEWnlMQ1Y4Qk84Rmo2eFcxZG1meFFWbXlnRVVaYVdJcHlGNGVWY3Nocm5GQktFd2lvczFSUjdR?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13-05-2026 13:39 UTC</t>
+          <t>14-05-2026 12:35 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1680,30 +1680,286 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Kidswell Bio</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kidswell Bio Swings to Consolidated Loss Despite Higher Sales, Targets Return to Profit</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOcnQxdEx2dlV1WVVYcXJHR3B4cE1MN0dibUI3NGx1clhUeGpSUWFEUzZZTHVXSDQ3WGVKNGpMUkZiLWF4V1N3N1d4eVRPUWp5ZUxjQmplR09vWThzYUlrRC1EOUFSSUs1RDc2MHg4YXBfc1BoVUJTVFgxc1ctaGxSWmJqemIwQmFJWG5WZkhJQnlPODBnV21JSWpXQ0pHMmU3VVhDNkozejdXZ0RMUXVqLUQtMnFZTEtGVnJuczVCbEhEM0dXenBTQXQ1MVhCQUxTYWwtZA?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>14-05-2026 10:38 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kidswell Bio</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kidswell Bio Outlines FY2025 Results and Strategy in Biosimilars and Cell Therapy</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPY25aMkVsYm9CYjNLR0ZoaTNMZG1RTzF6M2phWHRpTnNrUlNQQ0toQTNoV0YwRXhDT01JakZMZk5ZNU4xOWxzUGRuaWJBdnN6QW9aeGdUY2szM2Q5NUNKS2RqSkhibEZ1dG1fOGNnM1dPN1pNeWpXZ1ZPbHVncE9YaVFDbVliM2JmLW9ZS1pMaF9nUWdjaXhmbGJWQklHaG5RMllwNW4xNEk4MTVqVGwtaEZiQ0NoeUMwaUM3andIOUhQdVNqUWMzN01xekhlZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:33 UTC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mochida Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mochida Pharmaceutical stock (JP3778400006): Japanese pharma expands generic portfolio</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZ3B6LVM1ZWdkVS14d1R0eDJmczM2WTRneXdWbUdWWTc4RVd3TXNPRkxWUVJob0Z0Qmx3aTNLUzIzaTNyOGxkLVdxVzVzQXhaWXJGZk9LTDVfLVVrampvOTBKNzB6REFUUlRyTTlVTDF2Z3pXMm14VHdsVWVCLVpydVh1ay1zZ1lIQWJSQ2d5TmJhbm9tLVpxZnZZdmhod3dGelhXc21FNFlRa2hpN21UdElUVU5ZcmNZZG4xVDVqOTZUZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14-05-2026 12:14 UTC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings in focus</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPTE9hVmhmZTlUZ19vMkNWZDBlc2pBUzFrNGlCbHpTSGFpckVJTjBkWG00U092eGVrS0Z6NEpSWWE4OHBnVUNZUEJMQm9wTEZhdXBRZHRkXzRfUmtCdDc2RDlsMjZBVEg3czBlTmk3REZseHFmUlE2b1VXdmJYQnBDbi0tZ2x4SzFKTGd4U1NMMTBhcHZlbGI0cHVNSFZ2NTRWb3hkc1drM0tDTlFzTXBFWHBpVEp5YTZ4LTZucmZ2a1FaeFE?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>13-05-2026 20:55 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bombay HC Grants Passing Off Relief In 'OCTRIDE' vs 'OTIDE' Pharma Trademark Dispute Despite Bar On...</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Live Law</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxOWTRmLV9GRl9SdWNHR2xxZUl2b2hSOEEzMEdJa0l6WmR2bW1kY0UzcGpHbUh6WVJYdTdiWC1sMS050kBgAUFVX3lxTE5ZNGYtX0ZGX1J1Y0dHbHFlSXZvaFk4QTMwR0lrSXpkdm1tZGNFM3BnR21IellSWHU3YlgtbDEtOTBCZzFGT0h5ZEt2R3pFNTU0VjVJS1J2ZW40SENEdTBQRWpHckxqWHBPMmU5bHlraFpGdDg1UWpqYWJuaUR6RDVPZUpTcW1aakJvNVRWNTZfWF83RHFiNDltM3FDRWhRd0x1d0ZYUllSZHBFNVNqV0o4cl9PRmZHR1dBMWZ0NTI1alp2TG0zeGY0Q2xJRHBNX0wxUmxhaHJnMGFJNUxHYVEyWW5VNXpYRk1GMGJTTGR3cDY0NTBVTXBPWUdCZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>14-05-2026 09:13 UTC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alvotech Plans June FDA Resubmissions, Sees Biosimilar Approvals by Year-End</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQbXI2eF9aMkdCalNMcnY3UDdUblR5TjdQYzlnaVhRcTlNcjk4WFpTbzNFUVJUcko2c3JuUVJoYmlhZnJIVDBodllqMEdMOE80dTlMWDVyMmJ2M0dqS0ZtQWZXNGJZbWNpRHdzaVZkZ25GQVVGanBHbmxqYmt6OFlqVVRBSU1NTUdmMjNfVTdNSGF1azVUcUplb3JidUQyQWU5QzVLRzYzSjB0Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>14-05-2026 00:13 UTC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>How Investors May Respond To Teva (TEVA) Showcasing CNS Growth And Emalex Deal At Key Conferences</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPV3BNcHg0aFZzcGFfdzdhU2g3dHBEckEybW84bFFMdlpWNU1SSU80elhhSmFzc3NEXzhSUGRwcHdzSnA5bkpndmRWUzhtRDVpYklDTzh6aEZXUUMyYjZrZlVNNWZEMGZEcVhKVmFYZTFKQUVnQlMwOUhVZ1dYZ1NxSmNDa0pNdmY3NGpQLUFSbkVIQno3RzBLOTVBN3RLSXFvSm1iM2g3dldsaVBZYWtmWWJzak5KdlZXdUptTkJwekQ5WjJsbV9OVktURTd0akd2QVg0QlBRd1k3QURZLWJrN1drclgxdjROQWd0NkdaUlBhOXFf0gH6AUFVX3lxTFAwZ3VlbG5lZnlZUVkwU2kxN1Y1aFZmcmcwRE9ndllOWUczcjlEWmdjdk5mcnJSZzBoRDFvUGZWdUVJYmQ1VnNRUk9BZldyTTdtd01oUU1vRFdKc21adE55ZHRjYXk4Q2xCb0c1ZEhNdFZNLVNwdVZTSWxVTnJqb2ZBdWhYMGs0RW05NloyMXZiajFuekJJNzFLblBxRlVWVmtSTE9OZ1hKZktub0VMd0VHdHpseHBaTUF1bWJjWVlkYzZYUUR4U0pUSmhMNUxlZTBMMS1nX1Vic1NrTngza29ybkNVTzlBWEE1R2FoT2lRQXZwQXZZbEVIRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14-05-2026 05:52 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical stock (US88162G1031): Beats Q1 2026 earnings with CNS growth</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNUGo5OG0ydHRxdmFXZlRSQUFtemZOY0RxaUZCWWlhamkyR3ZXaTkzb0lxRnltWUYxaFJuN2ZNNG9QaHVHTExyZzZhdVNOTW1tenFlZmhyQVhDbUtaUVNRb3lraS1tbnplalVzaURadHZDVC1BTlJ1Qk0tMWFlT2tYSnh4M084OTRoWFlnNkd2QkhRWktMNE9sdGVxRkdQTmlOa1hoaGlEMWpOQXlzU1lYZ1p6UWU0SUNyTjVhQU8xR0hHQzBDdGtwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>14-05-2026 10:46 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Samsung Epis Holdings earns MSCI ‘AA’ ESG rating in 1st global assessment</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>koreabiomed.com</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9zSnR0VW5KVlJVMWpTSEtZdmJuSDE4ZDBlWEhOMlhjSDNxWFVCOXdTYzRjaHo1a1FmN1VoRVhCbUxuNG1ZTXlsWjBqUkw2THdQNFpEUjNGd1gzZG55djl4UjU3cWVsZFotZzVDSDhn0gFyQVVfeXFMUFdWY2E4SXNLXzJVcUNGNXRxdTVsd19XZkx2X180dWRLUmJVUHRkSHNSUU9fNU1FLUltZWJvZXVfMkt3cFIwQzZhWGdjeVZZS3V2Mk1USWhhQVVCRDNvQWJtTWxJd1dza0hjNktfcEdIa1N3?oc=5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>14-05-2026 00:44 UTC</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1733,7 +1989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-05-2026 16:55:06</t>
+          <t>14-05-2026 23:02:30</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,6 @@
           <t>Tag</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,7 +492,6 @@
           <t>Clinical Trial</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,22 +501,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandoz confirms European Commission approval for biosimilars Bysumlog® (insulin lispro) and Dazparda® (insulin aspart), strengthening position in diabetes</t>
+          <t>Sandoz wins EC nod for two insulin biosimilars</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>boerse.de</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxOSGdwbXVXaS1KbTRQSEMwN1ZEazhxZHJIWC0zX0lTWXRvOVBQdXM4OENXT0YzWGx3eU85aXJvd1hHaUlsU3EwWi1PSXJiRnd6cUJtMzBIdFFKYkE0RkFBd0lObWtTdzZoVmdJZWhoclcyc0RFcVNhSkxVdC1iUHhaUTFhWjlwVmtYQVRUQ01UYTBrbW5VMTN4d3hJSjdLTGIwMy1YNlVNbGZxSnZxb3NBZFE1V2thUFUxTjZSc3NOeVJfUmp4UnNQVEtzVFdXNzZTUEVNcG9fZUFpbzFLN0RXNGtrWDZiV1pqTFpDRll3aU9JLU1NRTM0YW1BSUdpcmwwcFJqQzdfQ21FUlV0d3A0Y0RSNXROVG5YZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQMzl2dWRydmd4RHVydjhtRGV2Q3BvTFdYN1UxTnBwaXIycUpxNE1nUF9laGxNdS1aTURLTVE0a1Atc1l0eU91WEIyLUUxamZVRW9wNTFFZGhGcUlFMDJSTjF3TzZNNDNMWWhjRG5qZFVSaVNYNDVxNkJ0dXliYUpvMDB5eGZxS2tBRXdUTHVPcDJnc0RQZkpzOWx3NA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15-05-2026 11:00 UTC</t>
+          <t>15-05-2026 12:42 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -526,7 +524,6 @@
           <t>Approval</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -536,55 +533,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>Rwanda, German drug maker sign deal to boost access to health products| The New Times</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>The New Times</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOdDFwOWpMQkdNMEt1ZnQ0NXlFeUttVTNBM19JeW5BNnVoNTNySzY3elUtZ1QweXdJeEVRak5qMjUtMTQ0ajNBQ2xwM3NJRFJzamNhM09JSnI2bFRlSlFoVHpZWkhsQmFEaXJLS2NIdHhWZ0NBSFFzODU5VlI2dWthTnlrMDE2Y3B1MjZMQ1RTclhEVXYtbXZXWE0yQVRXMGlSRTFvT212QlFfeW83aUFwWmNRT0JIVDQ0RkHSAb8BQVVfeXFMT1d4QU9QMVBkbHR4aThxd0hBQ3BpeHdiZHNoTnZvNXFDa1ZZUW13Wmw0X0FwMm8wZWJYdENmQ2E3MlUzLXNUaWhoSVdvRG9weXA5LThCSS1maEFBNXJXbVZzaVlTdnhpOTUxbXNxZFFPU0xmY1lIYWtteUZ4MHZyVWRQYjBUN1EwbnFRTkJXc0Z6a0loN241TnZ3OTVZekczS3ctNkFIbENtckFwOGkyakNUWkdkc0pqYzJnV3JNbDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSVVMOWx6WHgycVFaRVRUUE5VUHc3dFRvaGxIZVhjZ1MwMlVWWlFFU3ZYV3dLMU45Z205Q1FHMnFUY1pFN1JRMjRTTGdaaWc1MjljZFhjYkxJQVdLS1BoVzlpbnY4dHN1MXB4Z2VyTVM3eGFmeGNGcjh1ZUdmYVlwRHEwaG1SQVVpM2IyZ1BXbTVVbTZTa01fa3lMLUpiM3JxVGtPLW9hQ1E5cWk0OXlHWW81MVhKb1ZZaTVwN1F0c2lubWPSAcMBQVVfeXFMTklVTDlselh4MnFRWkVUVFBOVVB3N3RUb2hsSGVYY2dTMDJVVlpRRVN2WFd3SzFOOWdtOUNRRzJxVGNaRTdSUTI0U0xnWmlnNTI5Y2RYY2JMSUFXS0tQaFc5aW52OHRzdTFweGdlck1TN3hhZnhjRnI4dWVHZmFZcERxMGhtUkFVaTNiMmdQV201VW02U2tNX2t5TC1KYjNycVRrTy1vYUNROXFpNDl5R1lvNTFYSm9VWUk1cDdRdHNpbm1j?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15-05-2026 09:19 UTC</t>
+          <t>14-05-2026 18:42 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Collaboration</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rwanda, German drug maker sign deal to boost access to health products| The New Times</t>
+          <t>Boehringer Ingelheim India signs MoU with the NIPER Ahmedabad and Hyderabad to expand research collaboration across India’s largest pharmaceutical hubs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The New Times</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOSVVMOWx6WHgycVFaRVRUUE5VUHc3dFRvaGxIZVhjZ1MwMlVWWlFFU3ZYV3dLMU45Z205Q1FHMnFUY1pFN1JRMjRTTGdaaWc1MjljZFhjYkxJQVdLS1BoVzlpbnY4dHN1MXB4Z2VyTVM3eGFmeGNGcjh1ZUdmYVlwRHEwaG1SQVVpM2IyZ1BXbTVVbTZTa01fa3lMLUpiM3JxVGtPLW9hQ1E5cWk0OXlHWW81MVhKb1ZZaTVwN1F0c2lubWPSAcMBQVVfeXFMTklVTDlselh4MnFRWkVUVFBOVVB3N3RUb2hsSGVYY2dTMDJVVlpRRVN2WFd3SzFOOWdtOUNRRzJxVGNaRTdSUTI0U0xnWmlnNTI5Y2RYY2JMSUFXS0tQaFc5aW52OHRzdTFweGdlck1TN3hhZnhjRnI4dWVHZmFZcERxMGhtUkFVaTNiMmdQV201VW02U2tNX2t5TC1KYjNycVRrTy1vYUNROXFpNDl5R1lvNTFYSm9VWUkwcDdRdHNpbm1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOZVpUeXpZTDYyY1hGRV9GaEU0ZHM2UTBZZzBPWmJHeWhkY3Q2eWJMdU91c1AzbkxkOWllZlJ6U09rR0Y0YzQxSzYycE9nTUk1RUZVcnUxV2RvM1QzVlV1MHNIcFRkaFl2R2VZMUpqVUw4ZUlUY1pSaENSSzE4Y0tuai1XVlBpLVVVTTJOcGdIaFRPd1hNTHJKRTFHTlJtSmpoZC1yMmRMQW5DZG5FZG5nWGl4Ull0V2ZRc0Vla1dPclhNb2ZBTHg0a0RncmxhOUJvYlE?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14-05-2026 18:42 UTC</t>
+          <t>15-05-2026 01:55 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -592,7 +588,6 @@
           <t>Collaboration</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -602,22 +597,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim India signs MoU with the NIPER Ahmedabad and Hyderabad to expand research collaboration across India’s largest pharmaceutical hubs</t>
+          <t>Boehringer pens $478m deal with Immunitas for antibody asset</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>BioXconomy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOZVpUeXpZTDYyY1hGRV9GaEU0ZHM2UTBZZzBPWmJHeWhkY3Q2eWJMdU91c1AzbkxkOWllZlJ6U09rR0Y0YzQxSzYycE9nTUk1RUZVcnUxV2RvM1QzVlV1MHNIcFRkaFl2R2VZMUpqVUw4ZUlUY1pSaENSSzE4Y0tuai1XVlBpLVVVTTJOcGdIaFRPd1hNTHJKRTFHTlJtSmpoZC1yMmRMQW5DZG5FZG5nWGl4Ull0V2ZRc0Vla1dPclhNb2ZBTHg0a0RncmxhOUJvYlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPNEtmMGY5WnlBb3lxM0YzY3V2LVVXVS14YTlycTZrbXM2azdwSXVIMGlYQXdMTzQ1VXNFS2F5M1IzemJyZ3VpVDdMUVNfUWZfek5QTWRnWEhPbU1iYjBkeTlndk1qeV9fcFdHMUFickcyRlU4LTVLMHp3eVJOYjVlUkIwdGItZExnSXBTTFRxZ3plTk1GMVNTYlQ4SXBtUQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-05-2026 01:55 UTC</t>
+          <t>15-05-2026 15:11 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -625,40 +620,38 @@
           <t>Collaboration</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alumis pulls back from would-be rival to Amgen’s Tepezza after assessing prospects</t>
+          <t>PRISM BioLab to End Drug Discovery Library Agreement with Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fierce Biotech</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWEpmeFhVcHhocU04bTRDTzBzZE90eTBHLWpHNmc5RU5jaV9kenBxMEg1ZG14Q3RQOWNTY0Zxdk9iOEVlTkktRzlCUUF2a295MmJoeGUxd3hRRVdTb3BOMnNFMDYyX2ctQ0JoWEJPNUdiRmFwSHA1OUt1VVE3ODVNNmlqZi1YSHBHb3ZCUW9OYkJwdFI3M3o0bmNEbWdjOGxXVVpYZ1cwaFI2elhRRGhYaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPaDBZbHJWZEVJWEE5dDM3NnFTNHc3QkFTSDJlcHZ6ZG5MczJUVlVJcDVhb21ZRlp1VHV6ZXRYTnJrSHI4N1FPMGd5TmZXeVN3bG5Zcm53S0hJQTlockoyTkh6a2txVS1WTGhFbFF1S1A2RjJtUnhiUXF1c2dyX2VwOWgwVl83d3N6NWk0bXIxS2UzWGFZVFpBc09Udkh5MkdVNDJDN2hkb0ZBblktakV4eFh3a2hVTVpHT284bnVPeDkxQmlrUUVSN1VB?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-05-2026 07:44 UTC</t>
+          <t>15-05-2026 09:31 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Collaboration</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -668,30 +661,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FDA Approval for WEZLANA issued to AMGEN INC</t>
+          <t>Alumis pulls back from would-be rival to Amgen’s Tepezza after assessing prospects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quantisnow</t>
+          <t>Fierce Biotech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ0h6OW43RGJwMXZMOEtfRnEzYTg4LXFZZnBwT1k4VEdlRnZGQmlvTHRjUWJ1MylVeFJidDRaRFZhc3BQT3lfN1pXOGhBUzNubURJdEhDQk9DdG85SHlUY1JBZThWc1FvLWdfSHZ6RDhvRE9KYkpYVEVpLUlMb0dXM2d5UFdZZUROQlFRV2hMVkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPWEpmeFhVcHhocU04bTRDTzBzZE90eTBHLWpHNmc5RU5jaV9kenBxMEg1ZG14Q3RQOWNTY0Zxdk9iOEVlTkktRzlCUUF2a295MmJoeGUxd3hRRVdTb3BOMnNFMDYyX2ctQ0JoWEJPNUdiRmFwSHA1OUt1VVE3ODVNNmlqZi1YSHBHb3ZCUW9OYkJwdFI3M3o0bmNEbWdjOGxXVVpYZ1cwaFI2elhRRGhYaw?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-05-2026 06:05 UTC</t>
+          <t>15-05-2026 07:44 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Approval</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -701,88 +693,86 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BioAge Labs, Inc. joins Amgen and Novo Nordisk to outline future obesity drug innovation at Fierce Biotech Week</t>
+          <t>FDA Approval for WEZLANA issued to AMGEN INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Traders Union</t>
+          <t>Quantisnow</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNTU5RWk1UWDNBU3E5ZkM2b1RyYU9TOUxjWGFQVGFCNXRsMlpqdE1NaGo5SmMtZ2NsR3ByaG9od3JicGcwbnFSYlNRSDFDUC0xOFd3bS1RZUI0Y3RVeXQ0U2JxSVA4a19OQnhDWjFqLWtFU01qWVlKYzJoUUk2SnhVdXVMMXVnTS1NTjJiLXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ0h6OW43RGJwMXZMOEtfRnEzYTg4LXFZZnBwT1k4VEdlRnZGQmlvTHRjUWJ1aTNVeFJidDRaRFZhc3BQT3lfN1pXOGhBUzNubURJdEhDQk9DdG85SHlUY1JBZThWc1FvLWdfSHZ6RDhvRE9KYkpYVEVpLUlMb0dXM2d5UFdZZUROQlBRV2hMVkw?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-05-2026 22:28 UTC</t>
+          <t>15-05-2026 06:05 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Approval</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Apotex launches Apo‑Semaglutide Injection™, a generic equivalent of Ozempic®, in Canada</t>
+          <t>BioAge Labs, Inc. joins Amgen and Novo Nordisk to outline future obesity drug innovation at Fierce Biotech Week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Traders Union</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNdzVwUm9XNVlaT29GNkRONFM4YnlRelJlMWttRF96dTBaOVlGRzdDb0xrcTIzcVBoUkc5TUNURm00ZzhJYTZzZEg5NmxkQ2xXUlhWRm91X1hYcGFvQkRHNE1taG9pOE1jaEZ2UUFsTEJnOE00QVE4cTVLSDl1eVpqc202ZGdxSEJ1QVhGc3BsekRZd0kzNDNmb1lSWWliUkhhb3pESk5QejNXZkkwWGxuTnU0WXpibnVXMnpGNW5FNDVwTjE2S2R6S05KeC1WNENNcUwyRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNTU5RWk1UWDNBU3E5ZkM2b1RyYU9TOUxjWGFQVGFCNXRsMlpqdE1NaGo5SmMtZ2NsR3ByaG9od3JicGcwbnFSYlNRSDFDUC0xOFd3bS1RZUI0Y3RVeXQ0U2JxSVA4a19OQnhDWjFqLWtFU01qWVlKYzJoUUk2SnhVdXVMMXVnTS1NTjJiLXl3?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-05-2026 20:23 UTC</t>
+          <t>14-05-2026 22:28 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Viatris-Mylan</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mylan Epoprostenol Win Clarifies US Measurement Rules And Equivalents Limits</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPbHM4VWQtSndIMzVDaVlsc3BjdWdqTDFvaTdUMWFPQzhSYjdTdlEyUnNJSkt2WnprQVNhd1dPYWdMYXlUOV9xYnQ5Y2xyeXk0ZERUX3dvSEM4cG1YNTd2ejFkSDhhcEo2V000cGhCd0lWUmdWTVZZd0hYUjdkbUVtUWRlc2NrVDRiOG41UXZjaHp4TjYzTDQwbFF4dmdndzdxMkpoVUtJcWRDZS1vdlAxRWQ4U19aWGt6RW14cmt0cnhFUFYxQ2ZfbFdlQW9la3pMNUVYbUYydXJuMTNLV29mQVJydjJWUzJmdVNITElTSlFJVmhpOHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOU0hnRXdSdl9IZVowNDg2MFRyVG5IaE5IWDdrN3hRVTNKdlp0ZTBGdk9EeDBiT0ZvbEdreUs0U3FiZE1nY2h0YWNzSDhpVHBaaXBsblRLYTBYaHF5VV90ZXFFNnF3NkdMXzZLQnJrMU00cjhqa0RxZnZWck9GM1k0a1BMUjNGaTdzbjk1aW1TRQ?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14-05-2026 12:50 UTC</t>
+          <t>15-05-2026 11:30 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -790,40 +780,38 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pfizer's Q1 revenue rises 5.7% to $14.5B, beating estimates and showing growth in acquired products.</t>
+          <t>Apotex launches Apo‑Semaglutide Injection™, a generic equivalent of Ozempic®, in Canada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPT09ySEFVcUlwUlcyWlFYR0xmLWNZZHhPN2ZzbkpteS1xaG9UV2lEMWNXQTdoTk1XMWlTdGl4UTJqWmZKXzZnX2lxckk1Sm1xdVlpenpXc0JRaE12dUZ5cjEyVkpsVjBvZUZpZWFXRnNEUHZRY0g2ZF9DRXVMSURsUmdPT2E0dUlhN045SWx5WlRvUDFJMUUtRW1tRE1UVkJCSUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNdzVwUm9XNVlaT29GNkRONFM4YnlRelJlMWttRF96dTBaOVlGRzdDb0xrcTIzcVBoUkc5TUNURm00ZzhJYTZzZEg5NmxkQ2xXUlhWRm91X1hYcGFvQkRHNE1taG9pOE1jaEZ2UUFsTEJnOE00QVE4cTVLSDl1eVpqc202ZGdxSEJ1QVhGc3BsekRZd0kzNDNmb1lSWWliUkhhb3pESk5QejNXZkkwWGxuTnU0WXpibnVXMnpGNW5FNDVwTjE2S2R6S05KeC1WNENNcUwyRg?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15-05-2026 00:48 UTC</t>
+          <t>14-05-2026 20:23 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Approval</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -833,30 +821,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>‘Pfizer and AstraZeneca were ABANDONED, yet…': Sen Johnson drops bombshell on COVID vaccine injuries</t>
+          <t>Pfizer’s HYMPAVZI Earns Expanded Marketing Authorization in EU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Contract Pharma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxORmFseEF3SkJXYm85VDhzRFBfUmxmUXJnVTBlVDhIZzFYWmZnUFZsb283R1lpOFZJS2swb0wxbk9hZEgwNnpjemxKQlAwRGdBOXlIVVZOZ1VKRVpHeWRXNlQySWQtWkJJTHlmcmNaRDV3OEJHYkhaNUN5ZVktQU4wYmVEd3dUM1k4NE4ycTJkcWNlLW5KVHFoRmlxd0N3OFBNQ3lncm4tZlo2NElJMnFwWWZvMnh4eldSMldRbUtFOU9OWFduQWFnTC1ydlJIVmFlYmNNTndLZDZKR3Y0bjU2dXFmTzlOMWJkQ1VHeXZXUVlxcHVUcm9HSEhxdlVjYlJMemNiRFpvV012RnQyOGdQRFFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNQjQxUFZtc0gzT19HV0F6NUc5ZEFqamdzbXE3ZXhya19VLVFkMG1sX2FsZXRHd2xJMkNvQjFYR3JlS3dpSmhxNEJSdTdxUVRlckhmdmIwM0pFeHlVUHA0cGY5NTEzaThrNkxmN0IyN1lCWE5QaUltWVBINWN5bk9EZG1yNHF6WnBnUmI1d1FsY0JndU9WYWNHUno3dHhrVGd5d0ZPbEFucGFjdkk?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14-05-2026 20:13 UTC</t>
+          <t>15-05-2026 13:57 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Approval</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,30 +853,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Pfizer's Q1 revenue rises 5.7% to $14.5B, beating estimates and showing growth in acquired products.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPT09ySEFUcUlwUlcyWlFYR0xmLWNZZHhPN2ZzbkpteS1xaG9UV2lEMWNXQTdoTk1XMWlTdGl4UTJqWmZKXzZnX2lxckk1Sm1xdVlpenpXc0JRaE12dUZ5cjEyVkpsVjBvZUZpZWFXRnNEUHZRY0g2ZF9DRXVMSURsUmdPT2E0dUlhN045SWx5WlRvUDFJMUUtRW1tRE1UVkJCSUE?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15-05-2026 00:28 UTC</t>
+          <t>15-05-2026 00:48 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -899,30 +885,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pfizer receives EC approval for Hympavzi to treat haemophilia</t>
+          <t>5 Must-Read Analyst Questions From Pfizer’s Q1 Earnings Call</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPZnBaSjdfazl1N0VMZGJqRDh1UmpsTHBEaGtCeDE2NmdiMHo3UlZxbG9TN0c4OWQ0bXVFWEpRVDQwajRsa1YxbkZTeGdTT21QcGRaMlhwWTQwbGE2QlhNWHN3ZWcxRlhySTRrUVpTa0JLNEEwS2RxRXhzS07N3hET3ZBT2FZTjFYVDRBYUtCaHk5LTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQYjBVMWkweUttMEhWbmt3TDlLODFyTW5ybmM1cms5c2RtZFo2dHBEYjFheE5KTy1JLUF4Qy1PMlJGbzdzV3BZRXppUjNMbXNEaWpIMEdHbEVFUmk4MzRES0hvQlB1UDJ3bWdIWklzM09NVDVUeEt1Ynk0UUhxQXk0d0V6WS1ad0NGcDJ1MHNEV3kwWUZtSWtuYlphTGp1Vjg?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14-05-2026 16:45 UTC</t>
+          <t>15-05-2026 08:52 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Approval</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,30 +917,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pfizer discloses new dual calcitonin/amylin receptor agonists</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOWEdFWjVHeHpmY29DZmtNZm1iRkd4Um1VaXlZT0twSFk3U2lIVW5iR2R5SHRpcjM3THBwWGZJc2FpcU1XMlJicUlHbVhHU1RmRHlOUE5nN2ZWcXNGU0NybXZsdm1rQ0Vjb2ZveG9GX3AwZWpPTXBWakhBQWU3MGlqTXZOSTM5NHcyU0lfakQ5aGlrRWs5aTk2bDZxdEQtaTZaTy1Paw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TmtrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14-05-2026 13:00 UTC</t>
+          <t>15-05-2026 00:28 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -965,63 +949,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
+          <t>Pfizer Refines PF-07799933 Dosing in New Phase 1 Food-Effect Study</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOcWJsQnYyV2k5Q1V3RnJKb0ZzTUJWbFEtU1l5TWZqU3p3TWxRMDBSRUE0NTduYmNkSzhkQVFxNlpOSkNkeGpGNEVPWjZhZTZWbFEwZnlMbEFWTUtqYVdaRDM2alRJcUp5S0hnZGsxTmVLQnAwcTVPVnJCTF9zcDdhaC1pZ0hfUGNLejh6NWhjeGpTTFNUOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPSHhGWm1hZldxYWxLUVhxcnUzRWlMTHJxUFNzRzVxZTAzd1hUcE5zRTRDejZWUjZWY2RWMEJHbFVXY3pBSHRiaUVkWm9ib0Vwbmk3eW1NdkpzMnBTZ2E2SjRxV0x2SnRHanhYeTN3VjFLUmJpR1loYTVIRER2WkJTdG0zbko5ZlNxeXprQU5Wa2Q0MTNKcXJqSGxSNVRjX3FJVE9XMWstZEtlOW1hYm5vWkVMa09aa0p0NUE?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14-05-2026 16:00 UTC</t>
+          <t>15-05-2026 16:45 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biogen Completes Acquisition of Apellis Pharmaceuticals</t>
+          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOZ256enZtNjcySFlVRFVBdlVmVlIxLVFUYVZGVVJCMWJyaEVwaG1XSFdrOWxZU3ZDWGtiZmVUNkRtSmtKeTIyaldoQ2xuQ3JzaXdQeUNteGZOM3hZYzI5UUJ0MXVYNDBjVGZrSldQQUFSaF9MUUphR1lyX3daMl9pODJkdGU1NWRLM0NLRDlvelJmOEkzYV92VkY1TE1qWEFXV3dyWW1FeGJObnowT0VfUlRISFR0YXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14-05-2026 12:38 UTC</t>
+          <t>15-05-2026 13:51 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,30 +1013,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
+          <t>Biogen completes $5.3B Apellis Pharmaceuticals acquisition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>qz.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUHNzbmJucnlUdy1SRVA1RFlXcGN5MVZoODNGQ2E4alYwS2VIQ3o0NzF4RUZvS1dCR2xnTVZUelB1QzBpNmJWbDByVTFETkVRUjJxYWU3dDFCVURMdXM3TWcteUwzaVBLZ2VibkljbGlPN1oteFNDbS0yUkNteVB6ZHo0cUIxWUhLdlhVT25LRV9fWFpIWEtGNUh6bmpqRlNsdjNrMm95NWoyWGZlWWZLTzZoNWlQLWlTV2JpNHhtNkNJdnpfM0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE82b2I1Rl9FNHVyazNiNnFSa1ExUEJQUWo4TVdCZ3VNOF9SSEo0WUxCSVF1bmthSXJkWTRsbENoYllOVU9laEkzWUprRm5LbUlUUWJkYUdoU283RTZPVEcyUVVNOFRucEgt?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14-05-2026 16:39 UTC</t>
+          <t>15-05-2026 12:22 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Acquisition</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1064,22 +1045,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biogen’s Diranersen Shows Tau Biomarker Reduction in Phase 2 Alzheimer’s Study</t>
+          <t>Biogen’s Alzheimer’s results bolster tau theory—and Denali’s next gen candidate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPTmtpQWtTMzZ6Y3dDMWlkeTlWQWhUNWNlUUVZUUtkRWxEYkpPZ1B0LS1Pd20wX2lfc3FEeHFOVG5pQVRRRzAyTUdQQi1VcGsyWnlIZ0tsLTB3MXoxRVRCN0dPSTFLR05yQkV3WEVaekRTZG1ndjVncV83TllhSXN0aUtpVVYyVDVGdng0eXp5Q3c5T2JkOEE0b294dDA5cWlrUGRBS2ZaRExpUXYzSzZNYVV1YnFNbEM1VDgtbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPS1c1YjJtSVd6Z3BxakpYSjNnM0tpcVZDc1U1UFdMX3VhamZZMm9LZldLa3dLZUJFTE9VSnhKNmcyMkNoeURqaUcwRjFQRWc3bkNWaXFBQXJYOTh6UEJCWWZRTVpMZy1xclJkemN6Slh2Y0ZtV1NPWnNBUFh6SFJuZXlnUWQ2T0hVY2lrY2ZFV2VyTFFJOHBSUHVOdjRLb1E2ZnBvNUxMOHZURjhYUzBYTXRXcURXQ3FCMFE?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15-05-2026 06:49 UTC</t>
+          <t>15-05-2026 13:34 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1087,7 +1068,6 @@
           <t>Clinical Trial</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1097,22 +1077,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The ADDF Highlights Encouraging Progress Toward Targeting Multiple Alzheimer's Pathologies in Biogen's Phase 2 Tau Study</t>
+          <t>Biogen to advance experimental Alzheimer's drug despite mid-stage trial miss</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQakloZHFKUnRBZUQtUlBLSDIxdFQ3MzZJZWhWNEVGS1RWZjZwQ3RKUHdIc0NDY0pXOXhsdV9xMzRYcEdCb2w1bU1QRE9MbFp2VllHSml2TkptWGVva3hYeVplbzhnZnpaOEkyUG9wTDZqR2FGLU9EOFdvSlZZZnhyN3l3RHBnRU9FenJSZ3psWVhtb045eHNRMURZWFZLYkRCMU04eGRmSEZuTHBCaEVka1RkSXl0V3F4OGVHSjhxREVhNEgwdlViNjN3Q2FGT01idTNlamxFYTcyZlY5Umx0SXcyUEZXclRWRmxWYmxkTlNKb05rODlQeThLVjZoREhVcFpZSw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOVDdpcEpFSTN1c1A2ZE5Jb0VTWlV4TTdCTzdVaDRRNHFBTzVaZ1k2Ry1qZG50bWdkd010RHd2S2VQcGxHSHhPMU03Vi1JcElUV2wzMC1wS2hiU2J2WVo5TXFSMEh4TVNldEVzWDBMMVpscWd4TV9pbTdNY003SXUwM2dZb2ZEYzRJRmwyU0gxQ21YamZGUWxRQWt0S3pkSU9pNWRSWERsaTNScUVQaEtiSlhRM1JFY1ZubWdDT2tDckFfRFNLRnE0UTNkTm1Sa1MyUGNFbmthcWd3T3FsV1RQck5reXM2TEVfNlZqZWh6LXjSAfYBQVVfeXFMTWRxSFZTN2tEWVBkWWR2Tk5odlZTY1VOc2k2aThCZTZXN3IyRmJUVGNmLTdRWG5uX0J6ZnpjX01hekR3MkxIY1N0UlhDdC1VSE5SWHFKMEpaWWxtb3FHbmpxSmQ2LWh1OFlxODJOVFZiMWZFR3ppbGlpODBoaDlwUnNUTHF6cE9RV1c5RXkxZk1PaEktODNPWFR0cjBBaEF5YWpYaHJPUjN1aGxSZzhzMWlqN25aSzhFRWROeHhUM2RLZ0ZhZEk0MkJ2VG9zZzNFSkkxMUhTdG0yVzJjMDVIdlNkTkYtNjVGUXFKZjJYR1lxSlR3Q1F3?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15-05-2026 00:48 UTC</t>
+          <t>15-05-2026 02:31 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1120,164 +1100,159 @@
           <t>Clinical Trial</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dr Reddy's Laboratories Q4 FY26: Sharp Margin Compression Triggers 86% Profit Crash</t>
+          <t>Biogen’s Diranersen Shows Tau Biomarker Reduction in Phase 2 Alzheimer’s Study</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQT0xRbmtIRUNDUUVvZ0NUQU9oSXJKWUlySnozTW1xY09YcVQ2WXBHZVpPMW9VeTBaM0pUZmdCRkxjNkt1bk5sX3lyRVNlNnRfMGM3RU1UbkNObmdvSkZFSDM1eV9WWEFSTGstZjZuekJZbk9GOTZaTk1hN0w3ZXFuNEVtaDR5OWROd0FRUEFCQ2QzM0hKbjJPT19VRlZlRjR2TlpqYVY4bWZMYUMwZHdlWEZ1Qjd0ZUtVRjNERlJuQkhtT1FFN2pEcXhZUm5XR2hTY0pn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPTmtpQWtTMzZ6Y3dDMWlkeTlWQWhUNWNlUUVZUUtkRWxEYkpPZ1B0LS1Pd20wX2lfc3FEeHFOVG5pQVRRRzAyTUdQQi1VcGsyWnlIZ0tsLTB3MXoxRVRCN0dPSTFLR05yQkV3WEVaekRTZG1ndjVncV83TllhSXN0aUtpVVYyVDVGdng0eXp5Q3c5T2JkOEE0b294dDA5cWlrUGRBS2ZaRExpUXYzSzZNYVV1YnFNbEM1VDgtbA?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>14-05-2026 20:06 UTC</t>
+          <t>15-05-2026 06:49 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apotex Leapfrogs Dr Reddy’s With First Canadian Semaglutide Launch</t>
+          <t>The ADDF Highlights Encouraging Progress Toward Targeting Multiple Alzheimer's Pathologies in Biogen's Phase 2 Tau Study</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQQVN2cUViWDJHMjlmX3ZrS1RYZ1B1RE5NZTFicEJlMDc2S1J3MGNvU2NsVU9CRHVLNGNfc0E2aUdERnQ5Y3h1Y1ZyLVY3Qm5POHNVX3l0SGg5dEdCVmRnSXRfTG9ZNEl3VzFCTW0tcW94SmJpbzhTdW5ranlOTEFFaEdwb295c0plTDZzclJZM2FCM2pfTFJOMElsX25tbmxTcVNZVk9jc2hQQjhvSThibF95eWlocW9xUVpyMzJuS2ZveVlEdTVPNEhxRVlac2h4UlZzdHlTYlZEM3RFdWRkQ3BNQVNfdXhPYW1nUFZMYmV3eHlYekxOQUNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxQakloZHFKUnRBZUQtUlBLSDIxdFQ3MzZJZWhWNEVGS1RWZjZwQ3RKUHdIc0NDY0pXOXhsdV9xMzRYcEdCb2w1bU1QRE9MbFp2VllHSml2TkptWGVva3hYeVplbzhnZnpaOEkyUG9wTDZqR2FGLU9EOFdvSlZZZnhyN3l3RHBnRU9FenJSZ3psWVhtb045eHNRMURZWFZLYkRCMU04eGRmSEZuTHBCaEVka1RkSXl0V3F4OGVHSjhxREVhNEgwdlViNjN3Q2FGT01idTNlamxFYTcyZlY5Umx0SXcyUEZXclRWRmxWYmxkTlNKb05rODlPcHk4S1Y2aEppdVBpWSw?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15-05-2026 08:00 UTC</t>
+          <t>15-05-2026 00:48 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mrugank Sheth Joins Intas Pharmaceuticals as General Manager – Marketing</t>
+          <t>Biogen Pharmachem Industries reports standalone net loss of Rs 0.36 crore in the March 2026 quarter</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hrtoday.in</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNY29aaUxSSno0SHRHb0IxcndNa01ickpQNTVmT2h2cXZkZzdFbFpQZTRPMFliREx3MUNQQ2p2YWxrYUFyM2dLeGt1TEJGclRleElsUzZGMTUzSUYzVXhzc3BsN1owQVRzaE1kV1RZOXFfNFJMaERHM0ptbU45dVRDZFpCVm0wd0tFSWdpa01WOEVkZ3lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUdIBkwJBVV95cUxPYlFMS18xSWRGekhrRm5yVkJkcjRzRUJoZlpWaS1FUGRFelU4WklBbU8wbW1xT19OQXRxblgxNzU1a3Z1alFlS1RtLV9lTDBDcmZPQ1p6dmpCUGwzSlJXLTduaFdlbmdLTVV2OFNzNHFIc0JJTGxmQ3BHSUNLZHJDNTZNZ3Nram1JYkJmR1NLZlk1NzViMnpGeC1idDdpc2xVYWJDNm5ILWNVT3EtaG9WdVpHSElodEd2U3RsMVhJMnNzbWtCWDV1Vl9DYXZGelo5eWlDeWFLRS03cXE0Wmk2bDN4RzVMYktFWU9PR2o0R2c1V0QxVDZwZTk4ZENQVFlPUDdtLWc3eXZlbU9xSXRGaEVEUQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14-05-2026 11:32 UTC</t>
+          <t>15-05-2026 03:34 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kiran Mazumdar Shaw’s plan for Biocon is a template for family business succession</t>
+          <t>Earnings call transcript: Blau Farmaceutica Q1 2026 misses expectations</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxORVBwajZlSEFOM01OeHY4U2xYZlhPanloRmRFQXdLNUZPMFVWMmFyRFRTYmlndGtlRzdhVWphWURxRVVpNlBPZV8xUjZkd1hjTkRTVWRxZjlJeExXMFloajdCOC1ONHJoN0xXVDgxNUlCd3RQaXFnenYxMkdOYnFLeDNxd3FlUDBHaFU5aGlvbkRCaVpNckZZNE92ZmdyV3BiRVp0WGFSVmxNTkZXU0dtTE1URF93WTRFaUNIY1lmenNOSzU0WHU0eGYyRTZtQlV0Q0UzYdIB2gFBVVfeXFMT19wQ0VFWDBrTlowYUV6MWNDUmgyMDhBb1pfR3dwR1dTamxpd2NCTXB6UDVYUE45cDNidlNVSS1BRFRqQjM1TGlqUmM3MEY3b1RLMWRFNWQ1ejNOUE4taFpKenhHZDZDOFQ0Q2dvdmJRYW1Kd1pBZ2ZEX0paV1J4YjAyRF9NYWJvcEVPdmJuOWVkcXlZRVZhRkVaMkZVNTI1enBUTjJmQ01MelJOMExINWFjSlhHamtIb3VTLXY1NENGMFVZMmsybE9VSnVuREVaYk5uSDNhRWktUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPX2V2UFZlZWJtMXQ5dS1mNGVvMTRMcllLWGs2X0lHWFdwNlZvZktIM01GVWVwRWQ3bWx6V2xacVdiYzNuOUNSazJXNkNiQ3FvNnNuRnJmLUhvYTFIbmM5eWFxUUZnaUYtR0hONFpQNU95TlFYSjV2OVRHNWRnT3pPVklUeHZCdnpYbnJabGxxd0VubURDY3dGYl9XSGJzaVFUOWFxcTlSOXd0OHJUVlIxVlBuMVN0a3h3MHZzQ09zMF9GUFps?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15-05-2026 03:49 UTC</t>
+          <t>15-05-2026 14:54 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Schedules Q4FY26 Board Meeting on May 21 and Earnings Call on May 22</t>
+          <t>Earnings Miss: Dr. Reddy's Laboratories Limited Missed EPS By 16% And Analysts Are Revising Their Forecasts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOSU9XUEdSRFkwTHRTNzV0S2Z0ZUtiWUZqYmlDMnRzamVVb1JudUJka2dBLXZyS1QtTHhxMlRsU01IOVQ1WDVrVWVDc0RidElYSUdsQU5XX21LRXRNY3pmS0RxQTFsNjRWNmdQcVVfMmt1akNCaXBNZndNeW5GSlRxRFNnNktPVW14MFFLU2oyNEVzUklvbThMS3dyQ2JCaWJMeDAxb2hfZVFVS1RlVlJCVUxGRmlobnhESTNqNG1jdnppV210eHd4dm1MYXFySTFFalZqY0xrNTQ5RVVucnRKOEVtb3hWc2JESG42bEczWmZqZDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPQWxFNGRoejRBdjRuV0dYUWlMOC1ZSnpNS2poeVphSHBnTzJoR0gyVUpNdE9SR0FQeFh5bER2THR5WHdab1EtUjJPWE5YSngxZnVzaDhpUGNTbm54U1AwNG1QR2txZ015V0Y1TVBveEJCRG1IRzc4WF9RNTZYVDQtU2JNc3JleVFGZ3B2ZVRfSDFPUmNWUjN4aE9Bd2p0aUdoVVoxZno0bWFLa2R3OE1oNF9EMC0zS0t2eUdMdWlJZkFaRmRnUHAwY1A2eEcxUTR1T29iV3lNY1lHdlZyVzR4VndvNk1zY2VJMHpCV0RzQlF2a2FZa29RY9IB_gFBVV95cUxOMTZ4M2dJOUlMclYwcHhKS19SRlRqMzNwYjBnQ25NSk43bU9oNDBiTzFDTDBLVjltdllkVVJrckNEb2pyWVFERURKWnN1N3BKeG1UbVM3ZTRrTEpfZWdBa0FoVmp3dzFPdUdaWjl5UnctN1hEeGVlcXRZdnFlMjNkd2VoZm8tTklVLXpOTk9KdEhyX2FZNTE0b1ZKZGJ3ckd4SzhrdzJScFdwMG5SLWdkNnhaLVk3c1pkZXRwZUJGUVlESUFqQ3czdWFlU0kya0haRmNrUkMzZEYxMWVWekFxcjZOdGRiU19kUlRDanVpc2lBc2tTeFFkekRyZjVQQQ?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14-05-2026 13:03 UTC</t>
+          <t>15-05-2026 00:59 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1285,32 +1260,31 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+          <t>Dr Reddy's Laboratories Q4 FY26: Sharp Margin Compression Triggers 86% Profit Crash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IndiaWest</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQT0xRbmtIRUNDUUVvZ0NUQU9oSXJKWUlySnozTW1xY09YcVQ2WXBHZVpPMW9VeTBaM0pUZmdCRkxjNkt1bk5sX3lyRVNlNnRfMGM3RU1UbkNObmdvSkZFSDM1eV9WWEFSTGstZjZuekJZbk9GOTZaTk1hN0w3ZXFuNEVtaDR5OWROd0FRUEFCQ2QzM0hKbjJPT19VRlZlRjR2TlpqYVY4bWZMYUMwZHdlWEZ1Qjd0ZUtVRjNERlJuQkhtT1FFN2pEcXhZUm5XR2hTY0pn?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15-05-2026 04:40 UTC</t>
+          <t>14-05-2026 20:06 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1318,73 +1292,70 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zydus to acquire Assertio in $166m deal</t>
+          <t>Aurobindo Pharma Successful Completion of ₹800 Crore Buyback Program</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pharmaceutical Business review -</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBqMFRiVldMNk9lUFNMRFBiYUtWbWNxOVIyb0dWR0cyNHZ1QVN2NlZlb0pib29kVmItRE16RjlzOWczeFpBa3JuU3ZyVVpOT3gteFlLY1NjTXBlUEdINzltN0dBeGFyYU13cWdPcHgzTzV5SDk0ZXBPa2ExNU5rejQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lSVI1bHBtQzJIbUg1RHc2RmNteHd6SkJ2bDVOUFNJNENZQndQS0NBWHJfRDF6ZzhDUGZfT1RUTTFfbEt1a2pFQlNhWEtYUkxOcUNZY19iUFhua2ZwX0ZvWm9fdy1QYldOdUY0NVVhZDZyS0lSUGtJLUFveXI2Zw?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14-05-2026 12:06 UTC</t>
+          <t>15-05-2026 13:36 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Acquisition</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Celltrion's Remsima Captures 70% of European Market</t>
+          <t>Zydus Lifesciences to Acquire Assertio Holdings in $166 Million Oncology-Focused Deal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>ChemAnalyst</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPempJYTZVcnEtTFhFUVBmUUFfVkxaSG1xQmxBZ1pLdjJ2ODdQQTUzdXRmdFc2VGEzOV9Qa2sySzN6eEp0Qk9uenNZRDR6TDBwbldSVUZoLXBkajBZMlpCNnJuWEZPVXZpVnZDak9JR2JPMktreHBZeFdsOEUtQUZYQ3RoSHpFOE0yMlVFd3dPRU02bzZ4d1Z4bTd3TklWcVpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOTm5XTVlTTmZkTmlWeFNnMEJpUmhJM3lka3BITWdjSTljMGV0Mm14RUgteUp2MnNKQldFQlpEOHZMWkZHX1pHa0phWDN3SktqdjVDZFEwUEVrajVIS051ZGZJQ3JDNEc0YkFNdjd4V0NzU3dCSzNkWDZlYWtyLUJUa2RWYWU1eExSWTFKOEhOTFdJOHRYaktUQTV0b1lSeTlaaG1qajZNVnY3RU1obFl6aWhvcGt2SGdZcUpGby1Ob29iamRxY2M5ZV9B?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14-05-2026 22:02 UTC</t>
+          <t>15-05-2026 16:36 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Acquisition</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1394,55 +1365,54 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Korean Pharma Giants Post Strong Q1 Results</t>
+          <t>Celltrion's Remsima Captures 70% of European Market</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1BWmlGQkpsY2JCZ0s5S0REMkxxaTJTZzhlQjBrUHAyaUJKY3p1NjlVY2Z0bngwOHBtX1ozclYwS096TE9RU3JvYUR6SU5xZ0Y2TjNIY3FPQTd4UkphaUFpNGllTndzOUVOaUJ2SDl4Uy14MHpW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPempJYTZVcnEtTFhFUVBmUUFfVkxaSG1xQmxBZ1pLdjJ2ODdQQTUzdXRmdFc2VGEzOV9Qa2sySzN6eEp0Qk9uenNZRDR6TDBwbldSVUZoLXBkajBZMlpCNnJuWEZPVXZpVnZDak9JR2JPMktreHBZeFdsOEUtQUZYQ3RoSHpFOE0yMlVFd3dPRU02bzZ4d1Z4bTd3TklWcVpJ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15-05-2026 09:13 UTC</t>
+          <t>14-05-2026 22:02 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo Company, Limited (DSNKY) 2026 Guidance/Update Call - Slideshow</t>
+          <t>Korean Pharma Giants Post Strong Q1 Results</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seeking Alpha</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSUozMFZJblRlaklsX2tKMGVuclIzcm5BZElRVW1ERzV0dVY1QzJpeFo1T1BndE9sZklSeU9JbnBXblFxd1NRMlBCcFA0NFFmYUxEVWt3dFQ0VUZLNjVMdEJ2YnNKMmNPMWUtUWhQb0EwdWp4ZFVTTFAxdWc1RGgxMEFFd0dmOWp4WjZ0ekF0UnBsNThZZGZIY0hSZFd0SnRhN01JLUhpejEzcFJRRExHOGxuVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1BWmlGQkpsY2JCZ0s5S0REMkxxaTJTZzhlQjBrUHAyaUJKY3p1NjlVY2Z0bngwOHBtX1ozclYwS096TE9RU3JvYUR6SU5xZ0Y2TjNIY3FPQTd4UkphaUFpNGllTndzOUVOaUJ2SDl4Uy14MHpW?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>14-05-2026 23:43 UTC</t>
+          <t>15-05-2026 09:13 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1450,7 +1420,6 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1460,22 +1429,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAR T May Target Residual HER2-Mutant NSCLC After TKI Exposure</t>
+          <t>Fierce Pharma Asia—BMS-Hengrui's $15B deal; Takeda’s 4.5K layoffs; Daiichi’s oncology ambition</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Clinical Oncology News</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdDJoM2NSaV9jTU82VzRlYVBJaUdxQkQ5Y2hTV0VEanE1aUsxY1BOSXZoUW9NX0dVNE8wb1dUZmI4dk1odlNxTVlsaEpoRUxLSW5iT2IyM1NkMlhSdFN0SmdXVXRoYkJzTzFwTldzc0lQSzIwSGxUUkJ1Yk1JbnRDNEJreFNRWDVOS0RzazVDTXB2dDZ1LTRxczJlZWtXZzFxc1ZRcFVLcWZIUGp0N0RyakFvMGc2eUVlb05VRXh1UlM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOeVRFVW1UMkV0Z0had0gzSUpSWHhMZGRCc1B2MGxSd0stc1RyUnA0TmU4YWFkNmYxQ1JELS1HX3RWeVAxUEQwbnRtUExkcFk0V2ZWSzl6bFZRSmtVbGE5eU81ekc1T2RVT2dkRzduYW9QR3d3aWRxR2w5czdObnJoNWE1MEFsQ20xT1YxZi1IZDVpSGd4dnRFWDYyZUdtaHNsSUsycw?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14-05-2026 16:00 UTC</t>
+          <t>15-05-2026 12:30 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1483,40 +1452,38 @@
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kyowa Kirin secures FDA approval for Crysvita dosing update</t>
+          <t>Daiichi Sankyo Company, Limited (DSNKY) 2026 Guidance/Update Call - Slideshow</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNb1U0Qi1RUEh0TjNxcXdmS1NFT0VqNWZRY0xOeXA3dl9faTBWTDBoQUUyMGdLZ3pXV3pvWk41SGFsV3VoakVwa2dDRVdxOVV0bW1LQXVaMTlQRV9wb05BNGhiV0V0S0otc2FESlBIR0xjdHlQQ3BmZDFSX254Sk1HR01FZEZKQW4y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSUozMFZJblRlaklsX2tKMGVuclIzcm5BZElRVW1ERzV0dVY1QzJpeFo1T1BndE9sZklSeU9JbnBXblFxd1NRMlBCcFA0NFFmYUxEVWt3dFQ0VUZLNjVMdEJ2YnNKMmNPMWUtUWhQb0EwdWp4ZFVTTFAxdWc1RGgxMEFFd0dmOWp4WjZ0ekF0UnBsNThZZGZIY0hSZFd0SnRhN01JLUhpejEzcFJRRExHOGxuVQ?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15-05-2026 08:44 UTC</t>
+          <t>14-05-2026 23:43 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Approval</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1526,55 +1493,54 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kyowa Kirin : Transcript of Results Briefing Fiscal 2026 First Quarter</t>
+          <t>Kyowa Kirin secures FDA approval for Crysvita dosing update</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQNVhoTU1hSFRCOUp0bmpuV2lDSVdyT2QwUmlRQUoxUkEzeTNYTEpOZ0FPQXZNVlR6am5ybzFTYl9MLVJvSG9rQzExTlRzcUUzZndiQXVUZzV4dGNXaDRsMjc2UGlFT3I4dWFHVEpKejRLcXlMajlScnpBSUlYel9Ka2hHUnZuYkZMNE0xR0FRVURDLTY1bmNxSUYzZnlvYXUzTlpla05INWFZeW9FOUVpMXQtS3FBV2JUUU9oUGJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNb1U0Qi1RUEh0TjNxcXdmS1NFT0VqNWZRY0xOeXA3dl9faTBWTDBoQUUyMGdLZ3pXV3pvWk41SGFsV3VoakVwa2dDRVdxOVV0bW1LQXVaMTlQRV9wb05BNGhiV0V0S0otc2FESlBIR0xjdHlQQ3BmZDFSX254Sk1HR01FZEZKQW4y?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>15-05-2026 03:05 UTC</t>
+          <t>15-05-2026 08:44 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Approval</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JCR Pharmaceuticals (TSE:4552) One Off Gain Driven Profit Challenges Bullish Earnings Narratives</t>
+          <t>Kyowa Kirin : Transcript of Results Briefing Fiscal 2026 First Quarter</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPN3lUNWZKTlgtWnd1T0Nwc0NLRWpkcmU3TU9vWldMVDJOMmwxb3FGdzVPVW5FN3VQYm11TGpWNEFJRXVXS0lldHBqNnNuYUMzUjdCMkU4UE5kZ2FTamdnWFoxWWctODgxSTJoMkhWWjZyY3AxajdlUjRGRmlXZ1FrUk5HVzhwZ0VlbTRzMW1VdlByUWZsVTVUZ0Z5VVNJanVtUnFUcDVLUmNuLUs5LW1HSUx1c3ZvaUpELU5UUHNQc1psXy02V0JXTEdwOE5RLTZRdDQyX3NMNnE1c2dlQlp4LTN3WUdmaXExc1luX3NaN3A4eTDSAfMBQVVfeXFMTzd5VDVmSk5YLVp3dU9DcHNDS0VqZHJlN01Pb1pXTFQyTjJsMW9xRnc1T1VuRTd1UGJtdUxqVjRBSUV1V0tJZXRwajZzbmFDM1I3QjJFOFBOZGdhU2pnZ1haMVlnLTg4MUkyaDJIVlo2cmNwMWo3ZVI0RkZpV2dRa1JOR1c4cGdFZW00czFtVXZQclFmbFU1VGdGeVVTSWp1bVJxVHA1S1Jjbi1LOS1tR0lMdXN2b2lKRC1OVFBzUHNabF8tNldCV0xHcDhOUS02UXQ0Ml9zTDZxNXNnZUJaeC0zd1lHZmlxMXNZbl9zWjdwOHkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQNVhoTU1hSFRCOUp0bmpuV2lDSVdyT2QwUmlRQUoxUkEzeTNYTEpOZ0FPQXZNVlR6am5ybzFTYl9MLVJvSG9rQzExTlRzcUUzZndiQXVUZzV4dGNXaDRsMjc2UGlFT3I4dWFHVEpKejRLcXlMajlScnpBSUlYel9Ka2hHUnZuYkZMNE0xR0FRVURDLTY1bmNxSUYzZnlvYXUzTlpla05INWFZeW9FOUVpMXQtS3FBV2JUUU9oUGJn?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15-05-2026 10:36 UTC</t>
+          <t>15-05-2026 03:05 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1582,40 +1548,38 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical stock (JP3778400006): Japanese pharma expands generic portfolio</t>
+          <t>JCR Pharmaceuticals (TSE:4552) One Off Gain Driven Profit Challenges Bullish Earnings Narratives</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQZ3B6LVM1ZWdkVS14d1R0eDJmczM2WTRneXdWbUdWWTc4RVd3TXNPRkxWUVJob0Z0Qmx3aTNLUzIzaTNyOGxkLVdxVzVzQXhaWXJGZk9LTDVfLVVrampvOTBKNzB6REFUUlRyTTlVTDF2Z3pXM214VHdsVWVCLVpydVh1ay1zZ1lIQWJSQ2d5TmJhbm9tLVpxZnZZdmhod3dGelhXc21FNFlRa2hpN21UdElUVU5ZcmNZZG4xVDVqOTZUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPN3lUNWZKTlgtWnd1T0Nwc0NLRWpkcmU3TU9vWldMVDJOMmwxb3FGdzVPVW5FN3VQYm11TGpWNEFJRXVXS0lldHBqNnNuYUMzUjdCMkU4UE5kZ2FTamdnWFoxWWctODgxSTJoMkhWWjZyY3AxajdlUjRGRmlXZ1FrUk5HVzhwZ0VlbTRzMW1VdlByUWZsVTVUZ0Z5VVNJanVtUnFUcDVLUmNuLUs5LW1HSUx1c3ZvaUpELU5UUHNQc1psXy02V0JXTEdwOE5RLTZRdDQyX3NMNnE1c2dlQlp4LTN3WUdmaXExc1luX3NaN3A4eTDSAfMBQVVfeXFMTzd5VDVmSk5YLVp3dU9DcHNDS0VqZHJlN01Pb1pXTFQyTjJsMW9xRnc1T1VuRTd1UGJtdUxqVjRBSUV1V0tJZXRwajZzbmFDM1I3QjJFOFBOZGdhU2pnZ1haMVlnLTg4MUkyaDJIVlo2cmNwMWo3ZVI0RkZpV2dRa1JOR1c4cGdFZW00czFtVXZQclFmbFU1VGdGeVVTSWp1bVJxVHA1S1Jjbi1LOS1tR0lMdXN2b2lKRC1OVFBzUHNabF8tNldCV0xHcDhOUS02UXQ0Ml9zTDZxNXNnZUJaeC0zd1lHZmlxMXNZbl9zWjdwOHkw?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14-05-2026 12:14 UTC</t>
+          <t>15-05-2026 10:36 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Financial</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1643,8 +1607,7 @@
           <t>15-05-2026 05:31 UTC</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1668,7 +1631,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOQjRKWUthTzducXFFTEkwRVViWXVFYmVHMjJ5TEpkZDhSTUhrTzNGc0tJZ3ZfNVNWS1NkV214WFJPQXBwM29pX1Y2M0VOMERWTFFzNEl5ajNMeDlqQkk3WWtqMjYtZmR4ZV9zQ0FQdUR6UFBlaHRmUlY2amZfcWtHbnYtY2pWU2xsc0M4SF85QXpPakNlS3ZTNGxaQk44aEt3WUNvc0NydENMdFdobUcwWG1ZSEdCYzRFZUhfMmZrTE53dHJ6RGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOQjRKWUthTzducXFFTEkwRVViWXVFYmVHMjJ5TEpkZDhSTUhrTzNGc0tJZ3ZfNVNWS1NkV214WFJPQXBwM29pX1Y2M0VOMERWTFFzNEl5ajNMeDlqQkk3WWtqMjYtZmR4ZV9zQ0FQdUR6UFBlaHRmUlY2amZfcWtHbnYtY2pWU2xsc0M4SF85QXpPakNlS3ZTNGxaQk44S0l3WUNvc0NydENMdFdobUcwWG1ZSEdCYzRFZUhfMmZrTE53dHJ6RGc?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1681,32 +1644,31 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Teva Q1 2026 earnings beat forecasts By Investing.com</t>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and recent earnings in focus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbDlDaHJseUdqSEcyVTFRRHhxNVA0R0h6RkI1WHQ1WjlNMEpmRVBDM29YOHUxbE1GN1NTX0lJZE5BanZ2amZXLWFoazIyajVDS2NTU2ZQZUs4SDFqRGRjVS1WNnZxSlFvLWc5VnFjXzJLXzlkSDFIR005QUF5RnRyQi15Vk52Si15d2lxclVwamYyRFo2Yy1ERm1QaVZ5X1M0WEdORFd3TnZ1R3I4ZWF2UjRxUDVWSDY3R1hQcUJoOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWXRUVFN2dnB0b2JvWEQycy1zX3A1N3MxNkxLdGdlak1XUmlBUkFic19QYjMxUWVPWXNVTzRMVkllZDJtMTB0QzlHUlp2RnJRSGN1S2xwUjVzbVFNN3dMQXgycF94czdlYXFXZkJja2FQaXpnaHJWNk5xd0NuMTM2UVAzMXM4ZjVUeWwyY2dtRXk5TndhX3BfVzJiczM5aDNNeHd2dWtLVkxNeGR4Sk1udXQ5RnE3bDVJMWxqaThEY2FyaUU?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15-05-2026 10:46 UTC</t>
+          <t>15-05-2026 04:36 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1714,40 +1676,166 @@
           <t>Financial</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alvotech Plans June FDA Resubmission for Three Biosimilar Products</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HarianBasis.co</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBIakNKV2UzcGs0VVRoRW9UUkI4cFpYUnAzQ1FBOXhmb0prbEF1VUhMXy1aTnRkcHVzQXlKY2hNUW5IeTEyOEtiMVhCT1JsVlAxV1RGQ2dVSmprLW1TY0FiblZpRGREWnFNRUxyUDRlYjdnaU9lTVFwUHlhVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15-05-2026 11:43 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Teva Q1 2026 earnings beat forecasts By Investing.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Investing.com South Africa</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPb05Rb1I5WWFsVnc5Q3d6OTlrbHVCQ0d3MEVEek9mWm5ZSmxWZFA3bHBwLVFES1g2Y1FzTkpvTzd6dF9rRFB0OWE5cjJPOVZmZWY5WDBoWGJncklSSFppUmZJcDhJWUd4TGY4VVFacWE2Q1VyaGtUQVd3aVMxXzNnaHpZS21ZRGZXcEZXMUF6b0VmUEtXYzFqMGZVbENhUVdFcW04UjFsOXJfaEpVeXhaTEdueU80UVpNS044TVI0VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>15-05-2026 11:01 UTC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical Industries (NYSE: TEVA) reports proposed insider sales of ordinary shares</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Stock Titan</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPb0FYbWxZUEVkM1NSeUh4VV8wOVNiaGpCMTM1N0pGWDF0enF2VUVfV2o5c3hQRHUybmFHbnJvQXpWNEtUWmxGVTFSbDBEdXdVZVh2eW9HSFFaNDB1TFZpZUJGUzBBdUl2azdGakMwdUl4dktvaFcxaE40T0VzVm5PS3RMR29KZzVMWnlVN05FTzhpLV85SC1UOXlVU3o2UlFzZ0dlM053cFpqTEx2QTRaUg?oc=5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>14-05-2026 19:59 UTC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Is Teva Just Looking Out for Itself</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5lM1Z3bUdUSjNQMkMyT1pWX3BHLXRzMG85aEJTVXNWWEE4MkpBOFBBdzFFLWc5WjUzXzk4bGVRekhGMl90cFMtUUNoc01IdGloNkk2MnBzZU5NenZLRmVlSzQ3d1VGY0Y4NkFMU01sTjdBZXFRQTFqNWhZMl9oZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14-05-2026 23:15 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Oral obesity drug race accelerates as Korea speeds phase 3 and commercialization - CHOSUNBIZ</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Chosunbiz</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOX1dHRndPZERjY1RNLTl2SGNXY3N3bE1vVUIyOWpCTjRCWHNic0RhcDZYSFFpX2RZYjdCcE01NmJMeWNaUUowV2w5aFNfdmVwYnBFNXg1dE9HZU1fRGJyaTNTbWZPSXRRZEdsYXNxU256TGJpUXBMRnlJMlBRUi1YOdIBlAFBVV95cUxQWGdaYWtIMEQ1YWM3UVFKMmhzWl8xWjlXYU5LTndDaUh6M0lwRzg0SGI0RDBoWFpuQ3p1UzNnN3pGa2lQOEUxdVZYMm5XUUFkRTAyWU5JMUtyZGJnYlpjajE1eXZsU05kR1JhOWlxTEdHYWtjVDQ3SHhKS2pGdUtheEtlMkNoLUtsWVVmM3dEaG5tYU9p?oc=5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>14-05-2026 21:46 UTC</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1773,7 +1861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-05-2026 17:04:16</t>
+          <t>15-05-2026 22:48:48</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,66 +489,66 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FDA approves first interchangeable biosimilars to Simponi and Simponi Aria</t>
+          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPdVVkX3pEaGJLOHRkd28xZkFOajBhQl9SM3piLVBUUWtsNktyQy1ZTi1zZzg1YjVycTc2cHl4dUVaSnZhbnhCbEN5amFlLWJoSktkelBjcTNnd1J6LXpZVS1aQnBjYjNna0hUYVJvdU9IM2ZqWWJSclU4Nmd3VW9iMklDekhWY0tmRTFhNDN1NUJONDJ3M0FGSTVmQXZwVnZSekFWdW90eEppNHQ2YjJJR2hna2IxdU4wdVVnZzVObGk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacmptZnNqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-05-2026 13:54 UTC</t>
+          <t>17-05-2026 05:00 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From Tongi to Canada: Nevien Life Science marks export milestone in global pharmaceutical supply chain</t>
+          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Business Standard</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOdDFwOWpMQkdNMEt1ZnQ0NXlFeUttVTNBM19JeW5BNnVoNTNySzY3elUtZ1QweXdJeEVRak5qMjUtMTQ0ajNBS3JwM3NJRFJzamNhM09JSnI2bFRlSlFoVHpZWkhsQmFEaXJLS2NIdHhWZ0NBSFFzODU5VlI2dWthTnlrMDE2Y3B1MjZMQ1RTclhEVXYtbXZXWE0yQVRXMGlSRTFvT212QlFfeW83aUFwWmNRT0JIVDQ0RkHSAb8BQVVfeXFMT1d4QU9QMVBkbHR4aThxd0hBQ3BpeHdiZHNoTnZvNXFDa1ZZUW13Wmw0X0FwMm8wZWJYdENmQ2E3MlUzLXNUaWhoSVdvRG9weXA5LThCSS1maEFBNXJXbVZzaVlTdnhpOTUxbXNxZFFPU0xmY1lIYWtteUZ4MHZyVWRQYjBUN1EwbnFRTkJXc0Z6a0loN241TnZ3OTVZekczS3ctNkFIbENtckFwOGkyakNUWkdkc0pqYzJnV3JNbDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dm5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-05-2026 13:04 UTC</t>
+          <t>17-05-2026 06:01 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -560,32 +560,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacG16bnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lub05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-05-2026 05:00 UTC</t>
+          <t>17-05-2026 04:56 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -597,22 +597,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXJ0Y2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17-05-2026 04:56 UTC</t>
+          <t>16-05-2026 16:22 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -629,182 +629,182 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
+          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXIwY2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-05-2026 16:22 UTC</t>
+          <t>16-05-2026 20:34 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The National Law Review</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaThuWmJQYUZiTnZNeE5UU2xFZHUwZ1BiVDNBX3FkSXlUWFcyQ1ZST2xJcTJYSWZQUmItb3hxazA4NmF6QTlQTXlOcmt2X2tPaTZqT0dlNy1DRzVXelhfWS1VR2MtV2R2WnMtdkFvZ2NKdzZmeVRnQ2xaYTYwM2hnaUExcktqSGd3OWk3Y3U1dENpM0ZvWC13Z0hzZ0E?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-05-2026 20:34 UTC</t>
+          <t>16-05-2026 18:05 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scientific Approach to Obesity</t>
+          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE54Zm1kUk9Ldmp3Vk1yTUFjT0lKTkxtSWx5bHVZb2xWd1ZSSTZjc2E0emRWc251cG9pWE5zdm51eHVhNkI3bGFJSjJ3eDVPWTY2ZGpkWmhlMXhOSGVLRUhBN0JZLW4wN1ZSTDB3Uw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6bDRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16-05-2026 10:27 UTC</t>
+          <t>17-05-2026 10:24 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): focus on latest earnings and drug pipeline developments</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQVmVydDY1NjlFOFVnZGZ3eW5kXzFXNDhodWhIMmdwNjdxa2dRZGtGNlFJX0JWSDRJdkJhMmh1alhIcEVfaDNnMU1Nd1QzdklmQlNhY3VmU3BIcEZFNVV2dGpMaFlickRVcWJMMlJsby1TV2xkSHNyNHpFdlZMaHo1b1JpZm1sNVE5NklsQ0ZkQ2Q2TTF6Uko1blVXU1d2RUplMGI4eFIwRE9wVktJQk8yVElYQjFWMk1ibXpSY1Rn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16-05-2026 13:33 UTC</t>
+          <t>17-05-2026 02:32 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Emcure Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emcure Pharma receives 7 observations from USFDA after Gujarat plant inspection</t>
+          <t>Pfizer Inc stock (US7170811035): new trial data and pipeline focus keep attention on the pharma gian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Hans India</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNYUlrRFZuR3ZrNlh4dklJWjBLaXNTcnl5SjRRZHo0MS14d2E2N3RlUGVTSlU4NUJoazlTUVYtTDJhdk1DY0tXaF91c0tMN0JfbHd3SXExTU55cjAyelRTQVVvRkcwdE00ZDh5LWJ6d2FKWUVfRi1ZNXo2SGhOb3RTeG1WTDFtVlFoWnRhWjNwZTgtaUk0Z2M2NFJIUlAwTUVZdS1HbTAtNUF5MnFfNmFwVDE4NnhYSWMxajdUQWtVdEZHVHBIMThGRdIByAFBVV95cUxNYUlrRFZuR3ZrNlh4dklJWjBLaXNTcnl5SjRRZHo0MS14d2E2N3RlUGVTSlU4NUJoazlTUVYtTDJhdk1DY0tXaF91c0tMN0JfbHd3SXExTU55cjAyelRTQVVvRkcwdE00ZDh5LWJ6d2FKWUVfRi1ZNXo2SGhOb3RTeG1WTDFtVlFoWnRhWjNwZTgtaUk0Z2M2NFJIUlAwTUVZdS1HbTAtNUF5MnFfNmFwVDE4NnhYSWMxajdUQWtVdEZHVHBIMThGRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdjBLX3gtTjg4cFk2VEtYZ0pQS1N0QzE5NGRnZmE0cWRaZ1VyaFZVWlZqektEbURqUFhEOFRnRnl5NWJTTE5XWW9GcGNmQXd0bHR6eDJfcWdMOGxESWROZ0FZbmpfaVVwa0RNemUxYnVvZnJIQ25hZUktX3VfQl9LSFo5TXhoRC1ZZnl2V2pQOXdSTlZhenpxa2c3d29PV2VxdVM5M0x3U1ZiOC10TkdXeXowcm1HWUQ1MW5FVVVGZXhlTXo1aFE?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16-05-2026 16:30 UTC</t>
+          <t>16-05-2026 15:29 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): earnings miss keeps focus on turnaround plans</t>
+          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPTVRPdzJSLWEzVVJNblM3Z3lFMU5tb0ZDbmtvb2dlcEFENDJoTnRPTUxCLWlXZW56MGFnSkdUQW02NUNoRVZqQ19BUjVpQW1QNGNsWG94VldZdWhjRDhGOTA3Tlp0WURGUVVXal9sa1dzZ010SHFLaGt2WVlRb21tZ19oQURGUXN3Tzl0SmpyNGhQTWpvNEllakpKSy1SaWQ4VERNa24wXzF4ZVlXcXMxMDdfdnY2aUhBaUwwR29USXdCU1Bv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16-05-2026 15:25 UTC</t>
+          <t>17-05-2026 01:38 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17-05-2026 02:32 UTC</t>
+          <t>16-05-2026 15:10 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -853,71 +853,71 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. is Rated Sell</t>
+          <t>Comirnaty mRNA COVID-19 vaccine explained for US users</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNjZmUEJDWWM2RnE1Y1hRcklDcGhva3YwdkFTcVVzUXUwbTVKSldISWZHRDdWSlJuc2duTFVNUnIxTXphU2J3X2k5TWozSWwyZ3dVenZXeVJ5MjlyTFZkcmpLVFVRdnViQXhkekxWbGc0VE5wcDJCUmJIM2h5NXlfODRDTkFBaktHdW13d3gyOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOLUV5UHd6VzAzUnRHaFhLNWpDT3VmMzFCWWpyazBIU2hCek4wdjlNYk91T2w3Y1dYb2VVU1M2S3N6MWdtZkhFRFZqdDZ1cVhOOFVHM3hhWmZ3MUdkcGVzYnozendObzZqQ24xTW43dnkwVkVlQXNWQ3RvcHo5RDk5UXZnai1XcmdqcTB4RGZBamRBN2RyUk1JaXVkRzV3aUJZT1gxWWlFUkg0b3N3ZEpSbGNYMA?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16-05-2026 11:50 UTC</t>
+          <t>17-05-2026 11:37 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pfizer Inc stock (US7170811035): new trial data and pipeline focus keep attention on the pharma gian</t>
+          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdjBLX3gtTjg4cFk2VEtYZ0pQS1N0QzE5NGRnZmE0cWRaZ1VyaFZVWlZqektEbURqUFhEOFRnRnl5NWJTTE5XWW9GcGNmQXd0bHR6eDJfcWdMOGxESWROZ0FZbmpfaVVwa0RNemUxYnVvZnJIQ25hZUktX3VfQl9LSFoyTXhoRC1ZZnl2V2pQOXdSTlZhenpxa2c3d29PV2VxdVM5M0x3U1ZiOC10TkdXeXowcm1HWUQ1MW5FVVVGZXhlTXo1aFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16-05-2026 15:29 UTC</t>
+          <t>16-05-2026 18:51 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -927,44 +927,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17-05-2026 01:38 UTC</t>
+          <t>17-05-2026 01:39 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wolfe Research Says COVID Uncertainty Continues to Weigh on Pfizer (PFE) Outlook</t>
+          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNWDlPcmdiN0FoRC0xQzFTMFlMV1Y0RjZlVFNVRVhMb0xSNjdiZ3FOZUxETkhETldwSFA2QVFLOGZkNThHNWdNOWR2RGFDOTAyalNWNHFIcnd0cnY4Z0V0a3pGYThta1Rfckx1U0J2TllSRE84bEN5V3RvV1BOMDRCRGxWaTJiMFNZSW0tc3NpZzdfVGlDbVRZWkt3TVBEeFNNUW5jT215V3F5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16-05-2026 10:56 UTC</t>
+          <t>17-05-2026 09:43 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,283 +976,283 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
+          <t>Dr Reddy's Labs Among First to Launch Generic Semaglutide in Canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORHJITjBjOUJmUVhGZ3I5amhKX1ZUU3lNSTl4TDZweXg4U2xlYkZaMkpiS1N6OXVIV1FyT0VuUjRoajZIRU5uelprSldVSUxlWmhNTWIwelU5VHBvMEV4MUw1aFB4VlJ4U3ZuR1cyRDBZRVZSMHJWUGVFNHg0UHVoWHR3ajFkM0REcFBnOWI5VUxtN04wUTZfZFFpSUlRVjFCaE5SX0U5UXJndm9aU3ZZLThQUG9nbzRuZURMdV9ub9IBxAFBVV95cUxNckpKeFBGeXhHQ2NDdUtmZW5jYW9CN2FNcVVncmI3MUJ6eEJWUWJoTXFyczI2Vjd6eWdlT0dOU3hKN3BjS2dPV1RoSlZ1T2l6alQ5bTd3Wk9pUGV1ODRYSmU5U043SVVEZmJqSHJNSFhvT0ItSklJbDlLSkEtZF9oVWdmblhaSC1RTGlGQzBXRF9LOVo0dGoydU5GZnVMZTZPUzJuQVpoRkxlSjlSeUVNbTJzQmpscnBNNUdFRUF4NUhjcDdT?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16-05-2026 15:10 UTC</t>
+          <t>16-05-2026 16:38 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biogen’s Diranersen Moves To Late-Stage Alzheimer’s Trials And Investor Focus</t>
+          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNWEZISFVBaWRFNEpLYVZPbUhCeE9xTlVMTTdiU1Jjdk5Eajc4NmFzZzR6UXhZVnRZcWlycGpvN2ZkZnMwbndOakZqRXN2SVFTOF9RdWZnLWY3UFRSaGEwWUc3SDlROE1ZVldPemx3ODdmYldQajdmckFwdFIxZnJ5c2FKZmFRbS1VdjdlQW5leFpkTWY4WFpLVUhwd3BYSTZwb05aZ3A2ZTdKamhnYnVjcUNwY2xzaDF3MTMwVGJTOHc3VUlFQ1lIN2pkSG9UVnNORVpLX0hiRdIB3AFBVV95cUxOZExINnQwZXR5emQ5TXFVUXl2TGNDTEpta2puV0E3Y0R1MWVkSVA4bmlsQVAyU2I5elJ4ZVBCci1QY2lFbE52OUd6ZjZWOGNYOC1nVlBESVpiNEphN21wR2lJaC1xeWpRY1JycU5fLXlQNDRFWkR6dlQySzdlX2ZTaVoxZ096T0JNaU90a2VhZmxqdFRQVGxoejJqa29CM0o4V2NZZDJyRkZ5WFlTVWJJOHZ6SDV4MGxqYnlvc1Fkc3pGZkhOaFVMZDVhdk9pc3ZtNFlKSTE3cFAwWlMx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl8za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-05-2026 14:43 UTC</t>
+          <t>16-05-2026 23:53 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Makary resigns; Biogen reports Alzheimer’s data; and more</t>
+          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQRDAwTVhJQW10RWgyanU4azJuU3NaM0Y2QnJGcmdkT2RmZ3YyRnhYRnFQMDJrZ0o0NFdEOTA5aE1LUjE4b0JCTjRxUmZvRFU0MVJMUGhPWlZ1dFpEdkpPRG5RQVNpRFBjSVNPbEtTR1hHb3oyVmtLZmpQWmEwNDNvQ3ZFVG0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16-05-2026 10:00 UTC</t>
+          <t>17-05-2026 00:16 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkdThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-05-2026 01:39 UTC</t>
+          <t>17-05-2026 00:16 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why Is BIIB Stock Soaring Despite Its Alzheimer’s Trial Miss?</t>
+          <t>Interview | ‘India, Ireland stand to gain enormously from collaboration based on co-creation’: Kiran Mazumdar-Shaw</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stocktwits</t>
+          <t>theweek.in</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTzFrb1RQd2JYNGl4dXdpOUpmajFmTXA0WUtONHN1NlJoeDlwTXR2Sk5sQlBSLTNoUnJELVRUY3JmSTFvUUExbXdZN2NERE9uSEdXM0dWWGVyOWNZVWwxZFd6TWJGTkgyOGdEbHk4c2hvcE9qWUhDWWFsOUo3MDhVOVotTUd1a2hTNjNlUmJQNGpKTTlQX29tLWx1VUozRVJlc1FUMGVfQ1o3THBMakQ2QnN0NXNKTFYxazY0anNXd2NsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNTU1TS2NlMGFJZ2RBQ3BOMm8ySXFISUxmMXhLU0dRc1ZreUVrWkhMeEo1Tk1jMG9QRkZIaTRJaG0yV2p1clJtQldNeDZGU2tPenhoZk85dGJpRzFKMjdGRHYteG5FTkVxMkRabnVmNW5rb0Nad19yOE84bXVnUVBJT25pVl8yQ1V6M1pTdEZPRVlUdVF2Wk0xYUxTN01mT1lEM05ZRUdFTFdhQjJvMjBCVzZXR0lCNU1ndjQxRjJ4Ukl4OHJXMk5iYUNsYnF0amYwYlZ1WDJIbnQ0NmNfMU9hVXBWVm81ZHctWnlSc3N6Y3ZVWkVWeE530gH8AUFVX3lxTE1vWVhxd1NqWXFESU1lczdibjJJdW15b0UyZkJSTC1ZVlRFdzJsWWItUGVYN3hFVWJ5TkhwcklqRGkzR21aRXJOME1tSnNFR2VVMGY2Q091TUEyRWRzcWI3UVh4cndMTkRZemdFU1RSRVhwbXR0WGs4UTVoQTR3RXlRbmJGTG1ST3ViMkVrc1p4Z2JOSUs1d1lnUjljTFV1MGFJaHVFQXoyMDhnR0pKS2RlaFhaUnJyU0dWZVp1Z2RUUGlvR0ZPODd3OU8zSHd6VzJfTm9DSGx6LVpsOVNzZzA5LVZNTVZpS0pWa3pBSXVHRWRLclRYWkw3dUt1bw?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16-05-2026 21:20 UTC</t>
+          <t>17-05-2026 02:22 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>17-05-2026 10:43 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dr Reddy's Labs Among First to Launch Generic Semaglutide in Canada</t>
+          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORHJITjBjOUJmUVhGZ3I5amhKX1ZUU3lNSTl4TDZweXg4U2xlYkZaMkpiS1N6OXVIV1FyT0VuUjRoajZIRU5uelprSldVSUxlWmhNTWIwelU5VHBvMEV4MUw1aFB4VlJ4U3ZuR1cyRDBZRVZSMHJWUGVFNHg0UHVoWHR3ajFkM0REcFBnOWI5VUxtN04wUTZfZFFpSUlRVjFCaE5SX0U5UXJndm9aU3ZZLThQUG9nbzRuZURMdV9ub9IBxAFBVV95cUxNckpKeFBGeXhHQ2NDdUtmZW5jYW9CN2FNcVVncmI3MUJ6eEJWUWJoTXFyczI2Vjd6eWdlT0dOU3hKN3BjS2dPV1RoSlZ1T2l6alQ5bTd3Wk9pUGV1ODRYSmU5U043SVVEZmJqSHJNSFhvT0ItSklJbDlLSkEtZF9oVWdmblhaSC1RTGlGQzBXRF9LOVo0dGo3dU5GZnVMZTZPUzJuQVpoRkxlSjlSeUVNbTJzQmpscnBNNUdFRUF4NUhjcDdT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16-05-2026 16:38 UTC</t>
+          <t>17-05-2026 11:47 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
+          <t>FDA greenlight for Enhertu in two new indications</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcy1WcGMwX2lWYXNXSVVQVDlvRmhxYnlaTVJtSUh6OE9qcFdtS2lmZlY2U25mZFlZdlNscXN1cWtLLWZ6U1kzQkhCeUJvUUVQS01NdFVMZUFQeXFMaDdXdEFJdWNRREhWTzJJVVZsejJ3LVNJeUFKOW9mY3ZOTnppX2paSWZUYWFDVnU0OXp1T3RGYjVVdjhtY1V3?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-05-2026 12:17 UTC</t>
+          <t>16-05-2026 19:18 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
+          <t>Is Kyowa Kirin (TSE:4151) Pricing Reflect Its Mixed Long Term Share Performance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl_za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQczlsYy01RTI4VGJCU2QwSHJFV0t1QWtXWDh4X3pJMGZtS0dlQm92ZWYzS3NxV3dhZU1fZW5TY3IxNW5VVjVCc0xRVEZuVVQ5aUJFUmlQTVlxYTdjdUlCWEdkWHktLThQMW40ZEZLdlBRRWpfN1pzTWw5UGRUY0ZqZzdRZFNCZkdvUkdpVF9BbFFtTkpiTVN0T2hUbW9zRDBIcXZUbGQ0dDFueW9vNUNFMVRsa2FUNlMwWExUVV9walVQbm5DcEEzeGhWUlBENkhldVFWeDVIODFpSWRfNkFTU2Rya9IB6AFBVV95cUxNLVFhS2NFYkpKZDQ0aVN6NnBJN21QWVplZTlQRDlCdmt6THVnejZCUThNNFZ3cDFaSzFXUlpWQm10WUFmN0c4SXpkX21DUjlZQTJ4SHQtTnozR1ZMaEw5S2I0cVpreVVfcXYtajNjYkVGVGJFUjQ1OWhmZEFxRzNFbnp2Mm9fcTJxYTFjVm44b210d2NEaXozbE5fMVZiVTRVMk01S1lNMlg4SEppZ0dXX2J5cDg0YkpCbkdkb3RYSi13YnVLVmlJMERPeTVBczRfamRQRTNERHFjYzIyLVhwSWFOMjdtcWdT?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16-05-2026 23:53 UTC</t>
+          <t>17-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1264,91 +1264,91 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>MS Pharma</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd stock (INE089A01023): earnings miss and dual-market focus draw attentio</t>
+          <t>Real-world effectiveness and safety of ranibizumab biosimilar FYB-201 in Saudi Arabia (Ravegza) and Jordan (Uptera): a middle eastern extension of the FORCE study</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Nature</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPNUI1bXhqVkhYRHozcnJGOVR4eVNNWm1KRkpaX1cyaGdnNjB4UXBPT3RsVHF6MEEzaUJ2Ykw4Y2hyVEJmUkpWVVZERXhVeklPZzdEdnRWdjgyNEFkYnFxR2dDRGJLWFRYZFl6VDB0MlVRODJrWHdlZHNNWFVZc0g2eERPa0VlMkp0Wk9uY1l2am11VnFfMmRNMmlMTmNIcm9Za1hHcUxicWxyVXBGelZnSmVBUFZSTG00XzdiWTBMcXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9MeGlsYjR5dmx1MGxIV2lNQmdWMkduZVEyWUFCTjlxbEgzczVON2ZUSzg4bjB1LU9BRl9PczVwMXpCTmFuRkZMbEZqTmVOTXgxZldWdzA5b0RUNW1nd1BR?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16-05-2026 10:27 UTC</t>
+          <t>16-05-2026 18:40 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
+          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYZWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>17-05-2026 07:37 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
+          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkOThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQWtBRW8zMzVhcUYyTjRvLVRaNHNXVTg5V0dMY3FpZXVQRldSOXU2NHZDOEhiU1k3bW90SDJCRHFvUU51UXNONlpHRFR0cHJsX2YwVHhWT1Q2U1NsWkJONU1LdUlKSU1Jcmwtcm5rZzRDNFdtSjJpUWc5VWU0S0V0Z0c3eWZmTmRiXzBGTmFXb3puYlo3STZPM0JwajlSYmxRZ3QyT0F3VQ?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>16-05-2026 18:03 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,27 +1360,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
+          <t>Teva sells remaining women’s health line in deals totaling $1.38 billion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Times of Israel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNb2k2b1pUWXY5ZmdTYU1zem9tNnZMMTFraW9mLXh1Wmc4b2pKdlEtSDU4dkMzVzFzTDdVSFcyQVl2cGFVT3FSSXpwaGtRODJxc29GN2RhWmJROVE3SC0ybVJJd2E4QmNodUthSnZzR1RwQ1VpLXljazBLVVJwc3hxYUJucW94NmdDMzdwN09CTUEwMWNQYTNvSDY5Vlc1b0hOYTVSVXpRMWpISm5CSWRCWFUzODZ4dkpxWTF4eVhJSXNZekQ0cWxIOVlCQdIBqAFBVV95cUxNNFR6ZEtPWmFyeEhfTFFmN2d0STRjQjZVU0p0eUVoR0VVOXFfNC1fNTRtVzEtdGZEME03Rk1nSU8xUTdxODh1bzE5RFdXdVNha2d4R0gyUXh3elV4WVQ5RzNiMnVPVE9Fd0JfMVJmdVJHb3pKUURNUjNCWkJrVDEtR1JpNDRyYzFEZFlfS3hiUmVQTVMxa0FjTHY1Y01UZlVPeHhNSWxySjQ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16-05-2026 11:51 UTC</t>
+          <t>16-05-2026 22:51 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,27 +1392,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ETFs Investing in Biocon Limited Stocks</t>
+          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE05UUdIX3ljdGprNU5TUTM5QkFzenRkMU9pdjZwZGRHcld0bEhIczFmRHF6V2lGaUpKbWNIYXhiR19lT0lUclk2MGlSZTIxaUxDTndXVUJTUzlXckhSdThOSGlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16-05-2026 13:49 UTC</t>
+          <t>17-05-2026 11:47 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,352 +1424,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Samsung Bioepis</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Technical Momentum Shifts to Mildly Bullish Amid Strong Returns</t>
+          <t>South Korean drugmakers chase monthly obesity shot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Borneo Bulletin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPLW1ETTJ4ODU3dTNhcUlnTmhybjVuSDNfVWU0X2h0NDF6U0tlOHp5WDFMZXpxcVZ6Q1BTM0dyZWNvdXVfb2hONngtb253ZV8zZ3BYekN2OVdPZlJHRWc3NUJYb0p0c3lac3pvYklmUkJFT3BYRGJYLTB3eWJxM0lad1pKRXRkU1FhWkdyWnNuY1dHbWU1eUJVUnRsalQ0dlhGLTVJcHYzcUFfR2NXZFVncDJlOUhrOGUtVTUzZ3VOQ3Y5dkwyQ09KLTI5MHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSjZybUVPS2NhU3kyZ3BDc3Q0NERscWEtSTlYbHE4MEUwbV9kNUk0eGNDVUc5MzZPX2tjWmNIT0NFWkxfcHJVUE40WGVvVUl3Q3g1ZHQ0bHVJa3lDWjk4aHhxMlNQbV9fZkhVekVJYW1jcGhRX2lTaW1ZWlNNNTdUTF9pMktVZ3VX?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16-05-2026 11:41 UTC</t>
+          <t>16-05-2026 21:14 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma Ltd. is Rated Buy by MarketsMOJO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Markets Mojo</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOei1lTkwtOWNHSXI4TFZzN3RSRng5akJnMEhiSGZxaDJ4TGtJX051LTRqTU9na3RMcm5veFh2bFdCbjE0bUtOZFdaMlVOY21SOWIzY1hTa1JteWJ2dHl4WGpwREJtNG9qRENNb1JtREhxWnZZV2NVQlNHZ0hTRHBkOEpVazRzb0dGREdwSnVVaXh0Nm9LMUFwUVozTHBmOGQyTHJJT2FlNVVreWhOWlNJ?oc=5</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>17-05-2026 00:20 UTC</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>South Korean drugmakers chase monthly obesity shot</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Borneo Bulletin</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSjZybUVPS2NhU3kyZ3BDc3Q0NERscWEtSTlYbHE4MEUwbV9kNUk0eGNDVUc5MzZPX2tjWmNIT0NFWkxfcHJVUE40WGVvVUl3Q3g1ZHQ0bHVJa3lDWjk4aHhxMlNQbV9fZkhVekVJYW1jcGhRX2lTaW1ZWlNNNTdUTF9pMktVZ3VX?oc=5</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>16-05-2026 21:14 UTC</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
           <t>Pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FDA greenlight for Enhertu in two new indications</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>The Pharma Letter</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcy1WcGMwX2lWYXNXSVVQVDlvRmhxYnlaTVJtSUh6OE9qcFdtS2lmZlY2U25mZFlZdlNscXN1cWtLLWZ6U1kzQkhCeUJvUUVQS01NdFVMZWFQeXFMaDdXdEFJdWNRREhWTzJJVVZsejJ3LVNJeUFKOW9mY3ZOTnppX2paSWZUYWFDVnU0OXp1T3RGYjVVdjhtY1V3?oc=5</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>16-05-2026 19:18 UTC</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo Co Ltd stock (JP3475350009): FDA approval for Enhertu adds new US oncology momentum</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOZTQzcHVLSWN0Z09GWWdrQ3lpXzdwbkJfNUktc1JNeDRreXhkU0Z3dU1Pd3BxNE1VUGQzWkRnaHJBTE40cm5FbXViRXRXeDJCYlZleXVFNkZvZWx0ZTM3eVdrdzZLVjhrNW1qUjlIZm9YelE0SWpRMnlmb3MzSWI4d0t0NHZKWUQ1QmluX1NFcFl6M1VVQjJKUllSS0lDSGNoNDAyZzhyOVU2MFhWZTYwTy1oUVpkNExPZGxPOGpvcHgtWmoxc3Qzaw?oc=5</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>16-05-2026 13:04 UTC</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Kyowa Kirin Co Ltd stock (JP3249600002): oncology and rare-disease focus after recent earnings updat</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQaXhlNVF2SC0yZE1yUl9JN3RvcnFvaEtfLWRNYUNPakViQkRnaUt3YVhRZUVjaDFJMWVrRUdsZlpIM2tNcXZnVzRRSkZJaHpmZjJLcEg5TmV6emtXa3FseWpMSWlBdi1BNDJlMmI5WU1OdmVyY0dLNmhsUTBiMmJMSjZva2psWUdjNGg0U0xfRjdGT0pmWHo5OWVmTGdYWWxNbG84RGNlU3FhOHlkTWhOTnFiZnM5YkxjSEhvYWo5RWFwUWtyU09v?oc=5</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>16-05-2026 13:02 UTC</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MS Pharma</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Real-world effectiveness and safety of ranibizumab biosimilar FYB-201 in Saudi Arabia (Ravegza) and Jordan (Uptera): a middle eastern extension of the FORCE study</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9MeGlsYjR5dmx1MGxIV2lNQmdWMkduZVEyWUFCTjlxbEgzczVON2ZUSzg4bjB1LU9BRl9PczVwMXpCTmFuRkZMbEZqTmVOTXgxZldWdzA5b0RUNW1nd1BR?oc=5</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>16-05-2026 18:40 UTC</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Alvotech</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYZWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>17-05-2026 07:37 UTC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQWtBRW8zMzVhcUYyTjRvLVRaNHNXVTg5V0dMY3FpZXVQRldSOXU2NHZDOEhiU1k3bW90SDJCRHFvUU51UXNONlpHRFR0cHJsX2YwVHhWT1Q2U1NsWkJONU1LdUlKSU1Jcmwtcm5rZzRDNFdtSjJpUWc5VWU0S0V0Z0c3eWZmTmRiXzBGTmFXb3puYlo3STZPM0JwajlSYmxRZ3QyT0F3VQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>16-05-2026 18:03 UTC</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Teva sells remaining women’s health line in deals totaling $1.38 billion</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>The Times of Israel</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNb2k2b1pUWXY5ZmdTYU1zem9tNnZMMTFraW9mLXh1Wmc4b2pKdlEtSDU4dkMzVzFzTDdVSFcyQVl2cGFVT3FSSXpwaGtRODJxc29GN2RhWmJROVE3SC0ybVJJd2E4QmNodUthSnZzR1RwQ1VpLXljazBLVVJwc3hxYUJucW94NmdDMzdwN09CTUEwMWNQYTNvSDY5Vlc1b0hOYTVSVXpRMWpISm5CSWRCWFUzODZ4dkpxWTF4eVhJSXNZekQ0cWxIOVlCQdIBqAFBVV95cUxNNFR6ZEtPWmFyeEhfTFFmN2d0STRjQjZVU0p0eUVoR0VVOXFfNC1fNTRtVzEtdGZEME03Rk1nSU8xUTdxODh1bzE5RFdXdVNha2d4R0gyUXh3elV4WVQ5RzNiMnVPVE9Fd0JfMVJmdVJHb3pKUURNUjNCWkJrVDEtR1JpNDRyYzFEZFlfS3hiUmVQTVMxa0FjTHY1Y01UZlVPeHhNSWxySjQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>16-05-2026 22:51 UTC</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AOL.com</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE82X3RIZjJ4MGdwdThuX194S1JwN3RSd25jVEhJYmpJMmRuSmpLexI2c1NwSVdsSTdBeVA0Si1kN0JjVXEwb2w5MUFMbVlvN2p4bklFOW0tLTV3MHl5bzZ1bzlqa1NDdkRQT0RLeEVCbkNqQzdPYkFIT1hhWG9VUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>16-05-2026 20:25 UTC</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-05-2026 14:56:20</t>
+          <t>17-05-2026 20:20:28</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,64 +464,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chime Biologics</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recapping the “Must-Know” Information From the 2026 AAD Late-Breaker Sessions—Part 1</t>
+          <t>Sandoz Appoints Aarti A Kapoor As Head of People &amp; Organisation Operations For Region International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dermatology Times</t>
+          <t>BW People</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZTJyb09pS1NON0N6SjRfd0thMnNWTFdwSmVzWi1uNlNGTEdVdThRQ25LV0p3RmdKMXo0ZFlVRmcxMHdNdVhWZmJ4TGtpSHA0Yk9zX3VaMzhqZTBHR05pY01JR0tYcUNHQWpvR29wX1psZVhza09OdmwxcUhva3U4LXV2RW1Tek5WOWhBZUdkVFZoenEtOG1OSzNfaGVlYVc4bWdxN1JFUHlwck9xc3FqU1puczNtZ3lUOEp4Rg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQNHlxRHRBMUxsQzVETU1BdFhaWGdIVm8tUUNCMzZFOWRLWUhqTC1rQ1N0LUxBcVMxYU1JLW9aTi1EVXBqVUFoc1VuS3NEZGdIRUNNcVhzc2hfc0FRRXI3cGdqTmpWQ2NBdE0yd2I5OC1yTnpoZ0VPYm5Ua0hvcVBTb29zRE9wNTNveEpmV0NrUFhUb25jMWhDOHFhS1MwUjgyd2xIVmFLUXUxMmtqNXRmNUxzbzBzVFF5bF9LTmZoNlNxTC14S2tiQVliUG5ETkhtSGc?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-05-2026 15:00 UTC</t>
+          <t>18-05-2026 05:33 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
+          <t>Formycon AG stock (DE000A1EWVY8): biosimilar specialist updates investors after FY 2024 report</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEw2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacmptZnNqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNSS1sZmI4cHcwWW9pZG9iYUdBbkpvVXVMU0F4MkNkcWdIUFdXMlZ3UEVERGd1aVlDTUphMFF5bmtpSFBMcW8yS0thalk4ZDZNYXdYVjJIN3I4WVJLSEM3ZUtPUWJvOUU0eG53bzU1N2UyblQxdXltbWZJMC1jMFVNV1k1WVRkNWkzRkFhd3hnMW5MNEc1MUk2NFl2NVRaZ29Ka21iREJ2VFFROTBRWlk4bkxLYXJSRWNMXzlrZ1VCbnNwckp5djJydA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-05-2026 05:00 UTC</t>
+          <t>18-05-2026 07:24 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -533,91 +533,91 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
+          <t>JASCAYD approved in Japan new IPF and PPF treatment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dm5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOTlzUmdlVFV0UE1iaGRnNXQ3ZVFUbUlNVTZxejI2bGRHa3JrMGpwVnoyaENkTU5EMU5xYmNTZUd6OHkwQVMxYlI4X3JUY0ZZUlZNMjVXLXFfa0xjRHd4Z2V1MFdhUFo4VFItQXR3STFDNUFXZlhIUkhlVTVPTjNGY2xXLTZzU1J6djFzbHo0Y25SR3oyamhNZXFibm32dHV5MVdvUlE4cWcwRE9RclFpYXd6bFphbGRuSjJEQVRWcl9lVXRIcVd2M3NPYw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-05-2026 06:01 UTC</t>
+          <t>18-05-2026 07:10 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lub05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-05-2026 04:56 UTC</t>
+          <t>18-05-2026 00:25 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan Flags 20 Deaths, Liver Injury Risk in Amgen's Rare Disease Drug Tavneos</t>
+          <t>Hikma steps up $250m buyback, cancels shares to tighten free float</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPLXJ0Y2JKZ3RwRmZvNXJrajgtWHhaaEFWaW1NaTVPemx3dnFNdVVES014bWtKTVdySHBXVWVPRHF6Um5WQlNVUzlrU1lHVmZqbFNSU2NzVE1OQVpDYmRsbUMtWEVKdDVyS0JEc2pZRW12QVg4X0M5MUctMmI5NXJKMHJNYU5EZWF0Zi10aW84Y0xuRzBIcXRCLS1EYlJIbGUtcWM3b05iWUJaSjMyTDZUc0dvRklBY3lmTGFrbk56dkdYZ2lSOTFRQmI5RdIB0AFBVV95cUxQYUhJaGxfQUN2cnFIeFVQRXV1aDZ4STdWcWdka0hlUGRRMllmM1RRNUVzbXl2bEtxUVVXLXF1QmUycl9qSUI3X0VkanVNd1hOblV1Rk4yaXltVXFkU01rMllhOUlnZmZVZ1FuOTc4TGJDWE9WX0VNcWlHRms4UEV3M29USFQ3akl4QjhnLTVkY1hieU1KOHpsbkZBdXROMXdnYkNodjZyWEMxU3dPOXhJVHJ5MEx4YmdCYzBpbXdnU3cyb2tlT1dlb29FLTB5SEVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZ2gzYmFhNDNoS0wyRlY4RERCMzBSNi1MbzA1ZmxzSFRHVGNKbV9TTEdMLXNOeFRpNTFGQWNnVzdtX3VuWlpLVkRRREtnU2dGNl91bFV6Q3NWUWFvSHBZdzFNNWJmLWhZVS04NTFJcUxwcWNrVmtrY0ZOTmpxSGx2TDdEaC1GYjZSN1RsU3NQZUVjMGhIa0xldzRqQ2p2R1J3dGxFR3VCaEUzVXNvZFdBanNWdE8taXM?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16-05-2026 16:22 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen Inc stock (US0311621009): lungs cancer setback meets steady biotech cash flow</t>
+          <t>Amgen Inc. stock (US0311621009): focus on Horizon integration and latest quarterly results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -639,44 +639,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxONXBWTEJSeV9VenBoWVVkT3FheC1zZDRFTjhlVWdPQTdaVlNYeDc4UmlxNUVaYXRjelVpd2lTRUxBY0hZcE9pVDFVcFhRTUVvbjFvLWdrX0NvVlZhVGRVY0FQS0lUU1hUS3NTVkcxcU9CMzNuNG1aUDh6VlJVcTBsanR0ZWkxWURlb0otTnFJZnY0WDNCdGJ1dXBiOGh4N1FoMGl3bDBtVUVudHl5ZjhHZ0JfSkdfZ3BQM19iVDlkTGJhbHhNOC1BMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWnFkVmxWYXlxd25EelhqcXVodmwwZEtUV21BRktTNVIxaUZTM1gxcUNSdFc5dlc5bUIyb2Zrd0d0cEJvUk4tb3c2dUlxdV9ZUENzQ0NNTXE4bHNvYjI3ckk2QmpYSHhpai1NMGJ5UldjWWNfOVlzUXdlaV8wNndaSVB3RWUxekN6akF4OXBLM1lJUjEzc2k3ejd1ZmFfUzJkODJ5NXk0RnhWTEhYbTFmWFRUTGVLeG1KVXFrSUtTdWpqRkdZMlE?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16-05-2026 20:34 UTC</t>
+          <t>18-05-2026 14:37 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
+          <t>Amgen’s rare disease drug Tavneos tied to 20 deaths in Japan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The National Law Review</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNaThuWmJQYUZiTnZNeE5UU2xFZHUwZ1BiVDNBX3FkSXlUWFcyQ1ZST2xJcTJYSWZQUmItb3hxazA4NmF6QTlQTXlOcmt2X2tPaTZqT0dlNy1DRzVXelhfWS1VR2MtV2R2WnMtdkFvZ2NKdzZmeVRnQ2xaYTYwM2hnaUExcktqSGd3OWk3Y3U1dENpM0ZvWC13Z0hzZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdDVhWTJ1dTNFTkx4TlJDUDIxbmpEUFd3c2ZkeG91RUlBZGlNdDBLVlRoUi1Fa1F5TmFfa3liRjJ1WGtSbGc4OVM1Tmtxblp3OWcyR2dITmFRUEpCLUJ4bUNKQ180a0tqcjg0RlFHN05XTHBNMndOUGlZYmhHTmN2cDZ0UmNNYzhPRkNwcV85RlplX1d4Z2lrdQ?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16-05-2026 18:05 UTC</t>
+          <t>18-05-2026 12:37 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -688,27 +688,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
+          <t>Amgen Stock Analysis: Repatha Surges 34% But Tax Litigation Clouds the Return Case. Here’s What to Expect</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6bDRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUTgydTY2cVlsZFZDMWx4ZVZ1b2dRbG5sOXhLaTJqNWF0ZUdXSHVwTG5aalhnNHFkem1aUWgwekNIZkR3ZUJZdk9tMERwaXNTLTByVnhPbDM3dGVhbTM5dmtHM0Q0SURPVno0ZE1GT2l2VnhWTlZxNVRsbHNsWWJ6c2I1dm5fTDJJRmxJSlRKVVNXVUpWMmVwTWh6aWxhZ0FXcmhrc0VjNnZRU2YwUi00c015UUhaVjFUNFk0NEdaX3F3a1RpQmc?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17-05-2026 10:24 UTC</t>
+          <t>18-05-2026 12:29 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -720,44 +720,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Amgen’s ChemoCentryx to Pay $69 Million to End Investor Lawsuit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxPVnU1X0hLdnNoem8xSWwtUm9LQ28wXzM4aUFsUUN2U1ZsM0Fwb2dIWmNPdGphRVd3cm9RUzBtT0gzYVlyYUV5aHBnOEt4ck9CVnV0NEs5NTJkV2d1WnZSaGs3bUJYUHlzVVBMV2xwRDhnakZiWVlkNG5kTFBmTm0zNHJGNDlhdHhNcVNEQUtaX0ppdlZ1SFlXekZ0Z0Rtemh4TktrWGdPN1VIYnhGZmZnWURLWlhQTjNhUXN0RkV5eE01ZnhhVHd0RXlFNm5PNDBQTjQyOWpHMWRpTUJfV0Y5NjBqcmJvZ0FGWGtZQjdtZW5LcFI4S3U5ZHV6Zl9uc0NZQkpEcDQ1TjRiTnk3MjBGYS1RdjhNaVhvQjVveW5FRFpWQkVicHE1MVlLbURUZTFObTZtS19qN3JrdDF5c0RHb19WZzNTQW5OcWU2MEdGR3pqREVjQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTkdJbXFhZnJLWkUtR2FLdW5FSEM2Mi1Gdmc0T3Zyc3k2bmVHcFJfa0xtV2Q5dGdMR1RhR3RCZFRhWHdmaU5QaGt4UE9KTldueEpwSDJMZG1pMzUxT0J0c1h4QWFjREdPMVpiNHdDX3dwTGFBZ3BaM3FIX09VMHg5SkNtM0hrcXh3WFBwWG42aHNEbVJtdVh5R0pVTDFFUlFFZG4yaWplcm9fUQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17-05-2026 02:32 UTC</t>
+          <t>18-05-2026 14:24 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pfizer Inc stock (US7170811035): new trial data and pipeline focus keep attention on the pharma gian</t>
+          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -767,44 +767,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOdjBLX3gtTjg4cFk2VEtYZ0pQS1N0QzE5NGRnZmE0cWRaZ1VyaFZVWlZqektEbURqUFhEOFRnRnl5NWJTTE5XWW9GcGNmQXd0bHR6eDJfcWdMOGxESWROZ0FZbmpfaVVwa0RNemUxYnVvZnJIQ25hZUktX3VfQl9LSFo5TXhoRC1ZZnl2V2pQOXdSTlZhenpxa2c3d29PV2VxdVM5M0x3U1ZiOC10TkdXeXowcm1HWUQ1MW5FVVVGZXhlTXo1aFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0WUhfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16-05-2026 15:29 UTC</t>
+          <t>18-05-2026 02:16 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Is This a Sign Pfizer's Aggressive Growth Strategy Is Paying Off?</t>
+          <t>Cash per share of PT Organon Pharma Indonesia Tbk – IDX:SCPI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXNtMGl5X0tLZjRZYkplcmtsbjhldWxteXdJR05hMmhhaGNPWjY4cExVUXVSaThDNjJLT3doY0dXR05mTVlUZ0p1Mm1na215aGg1MWpETGhOSkUwUVhiZjl3YVNBaGpFZFZPQVVWdlJMYnozd0NpY2VnREdUVVZzUHVJR0NqQXRCck5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObnFETi1EcjMxUVYyMHNaN2JyTWM0aXIzRmlfdEM3OUNINy1Oa2M1cUpTVkVrOUZLZU9UbktRajJUak50NTNnYWtEbEtFcE9oTWtiSlBJZHRYc3RVblQzb1JsdVVrYUhaNmtPOUY4TXdmVkdDTjRsWlppR1phZ2lFZ1BKN2hpX29CaHotZ0hIV2VGWWhOYXp6VA?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17-05-2026 01:38 UTC</t>
+          <t>18-05-2026 12:49 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -816,155 +816,155 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pfizer (PFE) Juggles New Trials, Site Shifts and Mixed Wall Street Bets</t>
+          <t>Organon &amp; Co stock hits 52-week high at $13.44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQYXo0bzN6c3NRR01nNElGNmxNWGdCVTVGNTN6OW1uWDVEamhMZjFHbDhwMGtNaFQwcGNFUGQxWGxqUjhoLTBhNG1EWXluZDlNZFhKcjhoc09iUF94dHZSeTFNQzR4MVh1SnNVcmNWQm1ybVU5Qkx4TVc2Z3FYNmstczVGUHhUX0VlRG5PZjVKSUlaSHF4cHVES0N6eUlURFN2aGFqMnpoTTJ5WVAzbFJDTFpmb3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMW1ib2NjZUtVeksyeW91dm8wcGxoVE1TUGFKT2VoNjN1ZnVGMlBDeUJCVXcwVk9aSmo3Q1d6LWlTWjBHX1NZOGJwVmVyT3Jza29YV3VjQVpCMXh3X0RLNzRtN1FSeTdnS3JXZUdCdVVjYXhmTEFYb0lnQjNPRTlSVy14dU9wRWlNVkFTM2l5OHJNcjMtaHU3WGNpSFBHaHVR?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16-05-2026 15:10 UTC</t>
+          <t>18-05-2026 13:41 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comirnaty mRNA COVID-19 vaccine explained for US users</t>
+          <t>Organon &amp; Co. (OGN) is Attracting Investor Attention: Here is What You Should Know</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOLUV5UHd6VzAzUnRHaFhLNWpDT3VmMzFCWWpyazBIU2hCek4wdjlNYk91T2w3Y1dYb2VVU1M2S3N6MWdtZkhFRFZqdDZ1cVhOOFVHM3hhWmZ3MUdkcGVzYnozendObzZqQ24xTW43dnkwVkVlQXNWQ3RvcHo5RDk5UXZnai1XcmdqcTB4RGZBamRBN2RyUk1JaXVkRzV3aUJZT1gxWWlFUkg0b3N3ZEpSbGNYMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMzdMVl9fNmI4MUdpVUQxaUtIUmdQM19ROVVMOHhxOGJGWHpJSldXRFY4X0pkMkZJaVVWczA1aXUycGtPbFFDbFhtdVBVMVVhWW90Z245UUNfYl92R3hYOHBGZmE0Q3ViMTFNdUVNV1JfbkdLSVJpRkwxRWNuN1Zud1lXNzdNZmFIaDVxa29GSGlYV3VuZHlXLXZ3THFXdDVH?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17-05-2026 11:37 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A Look At Apellis Pharmaceuticals (APLS) Valuation After The Biogen Acquisition Announcement</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNcE9JN0M3bU43ZGR0LWNvOHNTcmY2YUtydklxTDMxZGRpTW11QW13RDg2WkNiU2RRaHd1Qi1lNmFsanNEeUJDZzRHSGVzeUkxX2VJdHRKTUdlUFdPaEFwbEJ1NHRTMjctSmd5aGhKRjFhV2JRdkJMc095Yjg5aG1xVlZBd3ZTbTMyQmRMTXRRMUJseUIweEtZM2hiRFJKWnBKN3BTR3JRT1ZVVFI0c1lodUZRbW1QVUdwM05jWkhaRGduNmtEOHJjWWZPVUk4bW44RllUcmYyUHhKUUZVX05Jd1dJNnhvbDdob2FSWkFR0gHzAUFVX3lxTFA3OUNZVnA2bFY2MWZGenlDMXRORlota05QZnR6LWJoc05kQUdVYVBnZUptc1pLYnRYY09ITUdRVFllQ2pxTjl4NWN3TVZVN2ZIdnJac0ItV1hDcFQxSmxkU18tQW5lalZIUzZqdWdfcUE0SGdiMEJyTkV4OXA1X3Z6a2N5RlVGU0tleGM0WkpJVG53b3V6Z2dZb2hZdUY2aGFSWXpXSzY3NmpjUTkwSG1kYkJzV1haNzhYVEZEcGVSb0JCVHJ5X0l4Yngxd1M0YkZoUG5zbTQ5YTlnTFNla21meGZfVU1MalZyZTJ2X3VWcTlwaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmhxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16-05-2026 18:51 UTC</t>
+          <t>18-05-2026 01:17 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Earnings call transcript: Coherus BioSciences Q1 2026 revenue miss prompts cautious outlook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQQWZIcXE1bHc0eEkxWk8tUGpZdTJNaGNBUGlXT1J1RWluSlpKblJ6NnZYOFBzQkV0V05pQzZ1TWgzMWw2dHBoVHFDSTJNVTFsZF9JdG5KazRyX1JqVzBTZzZ2RFVxT2t6X2doQ1RlZWstbGJUREp3cV9LUXZfa285RWxlVmdsUEJCMnRjUkF3OFZFLU02RG9FNktFWS1KcU1PVmhrNDNYb0VCcHpFd1U0cTNoSlc1WnlpSnB5MnlZWldFX3F2SEtGNno2UFUxM0FKYVIxbkZad3RITlhMdi04?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17-05-2026 01:39 UTC</t>
+          <t>18-05-2026 09:47 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield in</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1pRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQNC1CM0pHSXd1MGd2MUJDZnIxWHVsY0JRLUxjZGEzYlNnVGN2NE04Sjk2MUdzZG5mQkpjX1lwb0tBalFnYmF3RjlsQ3RWZDlwSGppcGxlMFpUYTZHb1ZLNTl4VFFuaDZZT0tsSHd3ZWZtV084cmhITDl0aERKM1lmMC1BUDVFTHF3alV1ek1ORll1NVcybDJxRjZEc3BFdXBSX2JSekltRnVCaGJWUVljdUx6cHkzOUZPX1FMUHh2b3phVGVM?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-05-2026 09:43 UTC</t>
+          <t>18-05-2026 01:54 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,91 +976,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr Reddy's Labs Among First to Launch Generic Semaglutide in Canada</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxORHJITjBjOUJmUVhGZ3I5amhKX1ZUU3lNSTl4TDZweXg4U2xlYkZaMkpiS1N6OXVIV1FyT0VuUjRoajZIRU5uelprSldVSUxlWmhNTWIwelU5VHBvMEV4MUw1aFB4VlJ4U3ZuR1cyRDBZRVZSMHJWUGVFNHg0UHVoWHR3ajFkM0REcFBnOWI5VUxtN04wUTZfZFFpSUlRVjFCaE5SX0U5UXJndm9aU3ZZLThQUG9nbzRuZURMdV9ub9IBxAFBVV95cUxNckpKeFBGeXhHQ2NDdUtmZW5jYW9CN2FNcVVncmI3MUJ6eEJWUWJoTXFyczI2Vjd6eWdlT0dOU3hKN3BjS2dPV1RoSlZ1T2l6alQ5bTd3Wk9pUGV1ODRYSmU5U043SVVEZmJqSHJNSFhvT0ItSklJbDlLSkEtZF9oVWdmblhaSC1RTGlGQzBXRF9LOVo0dGoydU5GZnVMZTZPUzJuQVpoRkxlSjlSeUVNbTJzQmpscnBNNUdFRUF4NUhjcDdT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16-05-2026 16:38 UTC</t>
+          <t>18-05-2026 12:49 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Reports Sharp Decline in Quarterly Financial Performance</t>
+          <t>‘Regulators were WELL AWARE…’: Whistleblower 'exposes' FDA, CDC over COVID-19 vaccine injuries</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOZWJjZFUzYjVsekJ4Zlo3THBySUhyTTd1Y3R6X2UwRk5mRk96Sjh3a2JCLW9xaFhwYUhDZW82WkFzNUh1NFhvRjdwMFF0ZUNfSW0xd1NKNjBNSl8za3RsMUxjVklOZUdlRnhaZHBPdllxNlZUNDhQTjFsR290Q1dicXJvcjFDSXF0VVlVWGlVMEpvTHJhaUlqZEhTU1N0RVFxRXZnRDNzaWVPX3o4NVBpUUFPSkVRU2JsaEJ5MUh6Y0ZGX3ZRM3Mya292dm5nUC0xaTVib2xJWko?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQa3VsbEpHdVNKRkdVS0R4cEs3R3gwUl_0SG5UdS1yYlRkR182NjBrcmswcFBxTUVxYXhpNEpveE5xSlFhZnFiQkdXeUpWR1FESkUzMkRxOWNON0xQaG9iUWNRaHlVYjlGRlc2a0U4LWNMbUo5U0p3eDNEYXhwbll0VU50TENBZ0U4ZHRqWG1jWDJUMEhmTDhYdjh2Z2dfUkk5aFI2ZnlNc193NEZUbFNfcDc0ZEd0TXdiQTRTUjI2TW5YQUZpYktuMmY5eExPUDFaSTVjb1JLQVFWUGQwa1IyNFo2aXFGVjdmNlV5enRoc25HRGk4dTRVaEg1Q1hZZ9IBgwJBVV95cUxPbXVpWG0wNkFudE55X3dNMlVhUUtsVE00NEp5eFdSV3l1V1hDS0djLXVGdC12ZmpnLUdNVllkVjhZVkRjOW1rU3dmNjJmU1lGOGVKYWppcWFGeFBMLTl5QXZxX3QxVjlmUTdTeWhPWlFzcjR6OWJCcEZKZXJ6WXJkTkozYndyZjRzaEVGbnRrQmVKYmQwRjQ2M2tSLXVGVnF0S0tnYXhLdzl5c3BjSHU5Mjhvc0ctY0tkOWI4OE1BUWlCQi1oZU1ZNTNtNFBjMTF5Y2Z2Z0ctUG83R0NsX0c2anlyRkRNWUZGVWQyb0xoSzFDMnVSSkgyRkI4WlAtZmJxd1Z3?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16-05-2026 23:53 UTC</t>
+          <t>18-05-2026 11:10 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
+          <t>BIIB SHAREHOLDER INVESTIGATION: SueWallSt Investigates Biogen Inc. for Possible Securities Law Violations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQRUM1WVEtenFuMTBGT0IyMzU2U0c4RWgxNFlSS0RUSWdrSWdDS2s2djJ6NkpjZWFQUFU5dF9JS3RVN24xRDZpNlhqS0J6dTJxYlJjVHFhbG1ocE1ZcGVyVWFfNjhVbEotQlZhd0s3SEVwelhjTWd5azYwTE1qN1dvUUJmb2pkTm1NZmxVUWtGZUhNUVBEdnhCeVIwTjdWYXNYMkZibEZ6ODFUNDBBMHlsTHZPVFJlUEZOa3hpa1JvSmhMRHIyVldpb1QydVpFV0NjbDJkczYtaDlwSE5KRUFUbE5PbW5jYUxVSXp2NWVZeTE?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1072,27 +1072,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Quality Grade Downgrade: A Detailed Analysis of Business Fundamentals</t>
+          <t>Biogen Inc. stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWlAxdU5WTkpfeVVIeHk1MlVkdThSQmlfUTFaaUZwcmVvZXpvNXR5MUNwa0c0dndMdmlTLVRxeHJyNkpIcU9MX1lsTUlKaEpqWkNQXzBGdVJseDNaSXBBek5fVnkzUmRBbG5DSTV3UlBWdDNJUGRONXl4bzRnWTJjdERrQ2llRUYtaU1GOExnbWp3bG80RVJVaTlwamdhTHJTQlRSUU01RGZVWEJJNEZsSVZFdGFaNGp3Z1Z2ZGdyci12QVA1OG9hZzJaS09Kb01fZmJIQVNOdEE2dTQwWTFVWTRZbWdqcF9Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR1NDb0Q2ME9WVU1sR042WG05TE9DLTVieVI2cWZLdnJfZUN3aFpXYWphUEpzLWdQNVhZQkdYcXhBMHhnbzEwZEE3WXFWc1o3cTVta2RKYXY5STVtdzl3ZkVlam1UNEZRTm5FblhoMUdDRzFwM3k4WHpwRVVsNXFJR053WEszcTRnT2NPVUF6RDFQazBJRUExb3hYYjN4cnBnSW5YLXJvdE1lbzVIRnBQMlRILUVpaVNGcmFUSG41bjdSTUg4S0lF?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-05-2026 00:16 UTC</t>
+          <t>18-05-2026 02:55 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1104,59 +1104,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Interview | ‘India, Ireland stand to gain enormously from collaboration based on co-creation’: Kiran Mazumdar-Shaw</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>theweek.in</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNTU1TS2NlMGFJZ2RBQ3BOMm8ySXFISUxmMXhLU0dRc1ZreUVrWkhMeEo1Tk1jMG9QRkZIaTRJaG0yV2p1clJtQldNeDZGU2tPenhoZk85dGJpRzFKMjdGRHYteG5FTkVxMkRabnVmNW5rb0Nad19yOE84bXVnUVBJT25pVl8yQ1V6M1pTdEZPRVlUdVF2Wk0xYUxTN01mT1lEM05ZRUdFTFdhQjJvMjBCVzZXR0lCNU1ndjQxRjJ4Ukl4OHJXMk5iYUNsYnF0amYwYlZ1WDJIbnQ0NmNfMU9hVXBWVm81ZHctWnlSc3N6Y3ZVWkVWeE530gH8AUFVX3lxTE1vWVhxd1NqWXFESU1lczdibjJJdW15b0UyZkJSTC1ZVlRFdzJsWWItUGVYN3hFVWJ5TkhwcklqRGkzR21aRXJOME1tSnNFR2VVMGY2Q091TUEyRWRzcWI3UVh4cndMTkRZemdFU1RSRVhwbXR0WGs4UTVoQTR3RXlRbmJGTG1ST3ViMkVrc1p4Z2JOSUs1d1lnUjljTFV1MGFJaHVFQXoyMDhnR0pKS2RlaFhaUnJyU0dWZVp1Z2RUUGlvR0ZPODd3OU8zSHd6VzJfTm9DSGx6LVpsOVNzZzA5LVZNTVZpS0pWa3pBSXVHRWRLclRYWkw3dUt1bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-05-2026 02:22 UTC</t>
+          <t>17-05-2026 23:42 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+          <t>Blau Farmacêutica stock (BRBLAUACNOR1): Brazil drugmaker’s profile and US investor angle</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IndiaWest</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOREF5MkI4WmlmVVBtSmlBbkJleU1qQUNFcmhJaE1kbjJDU1F1cUQ5ZzRZUi1vazdrdk10OVg1LW9oUTJHY3FLcWowUGhPZjluYWVFLXptT1AwS2lqSG14MF9URkstWjVqbGVNNVV0Rl96RUZDOGNtWTREeUV1RERBSFhPNE5va0dPRTJ0WHFEb1ZqMzRKdVpaYjlxd0dEQWJIZzFrd0tVOC1uQ28wOHhGbndhbVJCRUlSUWtzNEtTTlRQM282?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-05-2026 10:43 UTC</t>
+          <t>18-05-2026 09:51 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,91 +1168,91 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
+          <t>Dr. Reddy's Laboratories launches its generic Semaglutide Injection in Canada</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNlpNbWVzaExidUZRaC1QQWY4SFZBRWJuZmRlYzV2NmRzUjBkN0xQMU51ZmNydjlaenhqbi16V0NWaWNIcnVZNS1SVFlCR2hkVFhHaDZDajllVm9qMXRQR3RWaEliSkk5dDlaYUJ4ZTVpb1JrcDVBcHFZOVJ3OUpWcGF4VVpOQW9hZ2QyQkhkS3A1TU90ejJ1MHUzWVp5eEstQVMwam5CbnDSAa4BQVVfeXFMUGRkRDAtR294VDREUENuT2lJLVdUUllqd3FMOEFzSTR2VTV0cFJJQWJVQ2dldkJoYkZtY3NiYTI5bGtPeTNJLWFGYTYzR0RkMk00SFhkbDZHNUo5dFk3SDFDd2N2M0k0T19HVTMxejVWLUVJdUxDM2hzUWlidGpaRlBOUjJhZEkwdmc1a3RqYzV4VHEzWEJfYkVmNWhEc3NTcWxnY2F4Sms5LTFKWl9R?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-05-2026 11:47 UTC</t>
+          <t>18-05-2026 05:56 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FDA greenlight for Enhertu in two new indications</t>
+          <t>Dr. Reddy's Laboratories slides Monday, outperforms competitors</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPcy1WcGMwX2lWYXNXSVVQVDlvRmhxYnlaTVJtSUh6OE9qcFdtS2lmZlY2U25mZFlZdlNscXN1cWtLLWZ6U1kzQkhCeUJvUUVQS01NdFVMZUFQeXFMaDdXdEFJdWNRREhWTzJJVVZsejJ3LVNJeUFKOW9mY3ZOTnppX2paSWZUYWFDVnU0OXp1T3RGYjVVdjhtY1V3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQckk1bS1kMS1tVERiM0J4SW1qejJqT1RTZlNRTHhNdkdJNnBDSGpRN0ctLU1yM1VYMWZtUlZ3SktsTTk0bEZkeUFFc1JwdzhDczk0WEhrX1AwRnJYYUx6dXhMczlMN1FjVEM4UURfMWNtMkROcmxtaGdtMFBMZWtkSUJIcVRJczRHUHl5aXZDTWs5WDZKdW05RFlSSWtla245MGZEdFNlTlJSREFvOXpUNlpZVThDZ1ZZNG1kb3JWRjFZNHZiTWVSMXpGSjlqOE1Cbl9oeEFuMm1sSTV4?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16-05-2026 19:18 UTC</t>
+          <t>18-05-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Is Kyowa Kirin (TSE:4151) Pricing Reflect Its Mixed Long Term Share Performance</t>
+          <t>Global investor meetings for Dr. Reddy’s (NYSE: RDY) in May–June 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQczlsYy01RTI4VGJCU2QwSHJFV0t1QWtXWDh4X3pJMGZtS0dlQm92ZWYzS3NxV3dhZU1fZW5TY3IxNW5VVjVCc0xRVEZuVVQ5aUJFUmlQTVlxYTdjdUlCWEdkWHktLThQMW40ZEZLdlBRRWpfN1pzTWw5UGRUY0ZqZzdRZFNCZkdvUkdpVF9BbFFtTkpiTVN0T2hUbW9zRDBIcXZUbGQ0dDFueW9vNUNFMVRsa2FUNlMwWExUVV9walVQbm5DcEEzeGhWUlBENkhldVFWeDVIODFpSWRfNkFTU2Rya9IB6AFBVV95cUxNLVFhS2NFYkpKZDQ0aVN6NnBJN21QWVplZTlQRDlCdmt6THVnejZCUThNNFZ3cDFaSzFXUlpWQm10WUFmN0c4SXpkX21DUjlZQTJ4SHQtTnozR1ZMaEw5S2I0cVpreVVfcXYtajNjYkVGVGJFUjQ1OWhmZEFxRzNFbnp2Mm9fcTJxYTFjVm44b210d2NEaXozbE5fMVZiVTRVMk01S1lNMlg4SEppZ0dXX2J5cDg0YkpCbkdkb3RYSi13YnVLVmlJMERPeTVBczRfamRQRTNERHFjYzIyLVhwSWFOMjdtcWdT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOalVhUmUxYTFxc1JEOXZuNnNFcnd3VHcxRlg4MDdYN1Y0VWdmVXZKYWpkQlNoNDFmbi1pZnU3endaeV80dkw4THRGVHRWV3h1NGZWUUJsdl9PdDNRcXZRY3ZmZzRzU0piV08wdzBRSnotSzlVR0wwSkQ3cmpnS3YzZGxJSzZtTGc1MEdWeUREQ1FweExSbzFFVHFGZTZISnQwVms1dkxEMGFKYkR0ZFpMQVdyTXZSbmQyMWNWMWp3?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17-05-2026 10:03 UTC</t>
+          <t>18-05-2026 10:45 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1264,123 +1264,123 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Real-world effectiveness and safety of ranibizumab biosimilar FYB-201 in Saudi Arabia (Ravegza) and Jordan (Uptera): a middle eastern extension of the FORCE study</t>
+          <t>Earnings call transcript: Dr. Reddy’s Q4 2026 misses earnings expectations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9MeGlsYjR5dmx1MGxIV2lNQmdWMkduZVEyWUFCTjlxbEgzczVON2ZUSzg4bjB1LU9BRl9PczVwMXpCTmFuRkZMbEZqTmVOTXgxZldWdzA5b0RUNW1nd1BR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNY3NLLUpXWVBDVk9PdnNfaWNBZFk5bGtsS1p1UjFLUE95amRDUDd6UkVrdjZFVjVoajBkTFRudm14RWsxalQzT3o2RzVPNVN6VEZreTFHclMtcy1jMTBpRmg1cEN2TThMYnFWUlZLT3VGSjgxUF9QYU9ReXl0TEliSlY0TmVSRTRLa3FBbmY2VnhhRFVGWUcxWkZFY3Y1RVpaWDFMYWY3RUtSNzRhTVBfRjY4bE93N0ZWbllkVGRxUm5NVnFJVWl5SE1tRWE?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>16-05-2026 18:40 UTC</t>
+          <t>18-05-2026 07:04 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
+          <t>Biosimilars could surpass generics in US mkt by early 2030s: Dr Reddy's CEO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYZWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQZ2stSVlrS1Q0QVJHY3ZWV25Ob1FkOUM1TEw2OUZZc1g4Z0JwRUZTdGQ1djRXUFUwbThPSUp4NGV4dDdRMXVOdmNBXzZFZVBrZklkZ3BDblJDcnYzTzg4T3ZKbzNFV3JFRHozbm5vdEV5MWtOTzBnTzl2S2RvV2Zld182eFlqV1pBZ2VUNDN0WUZEaHVPNUppTml6ejVHaWZETnlReTcxaFVURDVQeDlzYWl4UWt1MDZ1YVd1RVhiSUR2UXhQeVNBY3lEUVROc3JHQVc1anZJVmpQN2NjbFHSAeMBQVVfeXFMT3Utd2U1RWg3NWZENW0ycG0wNmh0NzJ4aDNWUlU0aHJ4N2FPYlJBb1RIYkdnMHpDeHhZc05CcS1QYXAzaFZvUWhHa1JOMmVuWS1sSVZiTktUWTdvNUV1SGVrVVpIT1FQNGVHY2IzTTMtT2hnZGxRRGFqQTJicm1uYU9Ka2hDR3FXUFhJUk5GZ1ZWM0tMdHloeV93cEpzaG5KLVI5Rnh6MTY4N3NDY2VhM2JyenlqdEtSZFpNWXpTZ0NMeHlNUTBzR2VJU3owTzlUemswRHRRcjJka0ZMWEh2ZFEyN0E?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17-05-2026 07:37 UTC</t>
+          <t>17-05-2026 18:19 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical (TEVA) Reports Q1 Beat, Plans Amylyx Deal</t>
+          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI™ (golimumab-sldi) in the United States</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQWtBRW8zMzVhcUYyTjRvLVRaNHNXVTg5V0dMY3FpZXVQRldSOXU2NHZDOEhiU1k3bW90SDJCRHFvUU51UXNONlpHRFR0cHJsX2YwVHhWT1Q2U1NsWkJONU1LdUlKSU1Jcmwtcm5rZzRDNFdtSjJpUWc5VWU0S0V0Z0c3eWZmTmRiXzBGTmFXb3puYlo3STZPM0JwajlSYmxRZ3QyT0F3VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijANBVV95cUxNWWtCYzgxanJCTFhtRGVIM2xYaXROTzRPSklLQkwtOUZDeExSbTFaV3VERTNBUHBTcDBaV3RpSkxGMFg2bFFBRWFnMDZ6blY3YTZNZWZWQUZuYl9aMDBjdlJocGgxcGdYVW93b0lfVGhjajQ5OFMyV0RETjBSRjlIaHlpaklnbmptaWl2NFJZTEx3aHVWLXB6ZnNkeGcyMlNQRlRGX0JnSmdHcXZFZHRmSE9hbG0tNUpoeWt3dDdPLVNyYV9iaEpaZjgzblBoQXpXd0hEaEhlMTh0WDVUUmhDR3BwcnVFVHd6czRSSWRMZXotX2dVcVh0TjhlRUxLT2ZuLVNxV1hFQ0o2b19TSlBxVjJjV3p3MkJRZWZLVV8zOGhKd2M5V0hOYWM5bU85THNmemtyX25VNU8yaGdUWHo1WWQ3UGtpT0EtQXRPb2FJVVNzb0pvdEs5OVBDYlhuTnh4ZHhwOENCX0RLQmNiTGF6QUg1V0duaXlFOWJxZFlGWkNBMURsQ1B3ZlN6WDE?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16-05-2026 18:03 UTC</t>
+          <t>18-05-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Teva sells remaining women’s health line in deals totaling $1.38 billion</t>
+          <t>Should you buy Biocon shares now? Key takeaways from Q4 FY26 results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Times of Israel</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNb2k2b1pUWXY5ZmdTYU1zem9tNnZMMTFraW9mLXh1Wmc4b2pKdlEtSDU4dkMzVzFzTDdVSFcyQVl2cGFVT3FSSXpwaGtRODJxc29GN2RhWmJROVE3SC0ybVJJd2E4QmNodUthSnZzR1RwQ1VpLXljazBLVVJwc3hxYUJucW94NmdDMzdwN09CTUEwMWNQYTNvSDY5Vlc1b0hOYTVSVXpRMWpISm5CSWRCWFUzODZ4dkpxWTF4eVhJSXNZekQ0cWxIOVlCQdIBqAFBVV95cUxNNFR6ZEtPWmFyeEhfTFFmN2d0STRjQjZVU0p0eUVoR0VVOXFfNC1fNTRtVzEtdGZEME03Rk1nSU8xUTdxODh1bzE5RFdXdVNha2d4R0gyUXh3elV4WVQ5RzNiMnVPVE9Fd0JfMVJmdVJHb3pKUURNUjNCWkJrVDEtR1JpNDRyYzFEZFlfS3hiUmVQTVMxa0FjTHY1Y01UZlVPeHhNSWxySjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWEFZSE5GbjhLc0luN19jU2tJTVU3bDF0VWdSQTM0MElBUUpFcjdUcWtsbzhBUHotOFNlUzdXXzBjYzFKaVc3MDItQ1dpY2tBbHhmcE1PWmR5NmdkSXFzcGxEX1lWMjhPOFhoWFJHRnpDUmNLa05IZ3BzWkNuaXl2ZmhVX250UXI4Mk5lNkJYVWZZNC1YeGdSOFR0ZGd5OTlWT0htb1lQTmxaS2VRWUhCcmN2QUdMQjdqTU1YMFJoUEU?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16-05-2026 22:51 UTC</t>
+          <t>18-05-2026 01:36 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,27 +1392,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
+          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17-05-2026 11:47 UTC</t>
+          <t>18-05-2026 02:31 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,32 +1424,480 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Board of Biocon recommends final dividend</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dailyhunt</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQXJweHFyTG8zRUhvZng0SEN5Y1NuTExFZWlFV0xtTkF5Q1J2a21aR1RZM1ZZTjJjaU9keTlmVXRRZGw1T0FaRG9BWXk4NHNId0FTMU5QM01tOE9HNXphZFVtZzlMeXdKTFRiUVVXMnBtYVlYZHhxdTJJREtZOF9kbjJadHkwSDlYNjdVQ2lURk9EazhMQzBhTkViQUZ3azZCU2RvVGczbC1xd1BoVzRVdElWWkg4eEtWbEJfUkNxZGtpSnlQcTBzNExn?oc=5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>18-05-2026 01:39 UTC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CDSCO Approves Aurobindo CuraTeQ's Bevacizumab Biosimilar Bevqolva for Cancer Treatment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Medical Dialogues</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQQUZNWWhrREJJVEkzVlF5QWJ2dWVpZk1JVV9ob25IMklTNzlOQWJRZENob2lRdzdEaFFqNGtkSS11YXNKNC1NLVRmaFRLTGhYNERDY05qS21fS1pzZmhkMjk2bk5SRTVLSVg5TzBXUTNlVEIybEJfdGJfd0ZHNHQxWDA0b0E2TWo1cVM5ZHR5R0hRekxWYUJLa1lFZ3hZS3BQdlZVZjB1Sk1NMGJBOUd2aW5tZFBrWlRfVk40TkhsNkZMX0prRkh3X1RUcm9qOXpBX3JmNmp3eWhMbmREQUJuZU5B0gHnAUFVX3lxTE9qZ1hkTHh3bnUta0M3S0Y3YWlRYXNzajk3T0hDY1JuaWtJd2VLanZJYmM2cTMxZ2xFVFFlWmZoSE51cjluaUwtNkRxRmFkaU5rSEtBMkRaM0VzVFNCYzlMbnJjcDA5aWpwTVFtSnFfRDZYMWxPVWx1N0M5ajZ6eUJDcFBwWHUtLXM0RThOTDJBS3hNY3hTRi1xSm9rbVVFTy1vN2JJNGtMQ0JEbzZpVFRSQWswMk8xY0hndUh2dmNKVzFWY2VXNGtSVm9Say02LW5JU05RSk9SUUZRT3hCTjlKanp1a0VuYw?oc=5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>17-05-2026 16:52 UTC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Samsung Medison Leads Women’s Health with Life Cycle Ultrasound Solutions at ISUOG 2025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Spherical Insights</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPYU4wbktrVFRkOXlNNnQzbk9TWGpaOFc3T1BuRVF0emtieVQ1Z19rQTFoenBEMVBybjhjQXVTTG9hMEJEYWp0RmZBSy0ybEtzRms5dTJ1R1NFVmJzd3JPR0dCV3dXVF9ETlhQX0VsU3dvZGRvbG5QWmdoQ21NZ3k0NkMtRG5ZUVdiVG9nQ0VNbjM2d3Jsc3BKWDZWT25oTkZJXzVJS3dVbFhUTkh1SURYUENYU3VRazNva0xDTFZOQVFfaGpScWc?oc=5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>18-05-2026 13:01 UTC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Celltrion’s Vegzelma strengthens lead in Japan bevacizumab biosimilar market</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>koreabiomed.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5DQjAzWWtGVmNmSXB1el9wZ2k2c2t6UzVRY1ZmM0RpTVFQNm9aeEhueDlfQUFWaVBQV2diOXZPV19HM2dUTDloZGJFMUVXbHJ3Q2pJN05LOEZFdXg1cW9xUmV6WHFELXlqUC1UMzdn0gFyQVVfeXFMTjB6QkNWYU9UZElLQUtGMmR4MVdKd2NESWhtOTl2VE4xMFh6MUVCbDlIbkRJRUFLT0FSZ1JvNUJMcnlfRGdlZllxcGw3dHl4dGp4TjFaaWlVWmxPY1A5bUNIWkoyT3ppa01lNFAyTFZPSHZR?oc=5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18-05-2026 04:51 UTC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AstraZeneca To Pay $155 Million Milestone To Daiichi Sankyo After US Approvals</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPVU16VGpjMnhVNnhmaHNNeGVIWTZtNnJfN0JqTENIYlBfNmNhazNCLWFvanpOcHlRU2YwbnBicDcxZFZwaEd1M0RSdnVKYWRqUTFCWUNlYjA0XzBTcTYtNmMzb0FwRDhPWkl6NzlmQm9iZFB2QWxkZ3RJUUo2NHRaSWNqbjM2VW5Kc043Y2tKSFl0T3BmQjlOQzNLS2VhWVNrWldkSnREVwBWTE4xZThGNmo0d1hvNWVmVWFzeVZ6dE93cW44QmczVk9ENkh5V3g3aldoQkoxQWd6eFRyM3pKZg?oc=5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>18-05-2026 06:27 UTC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AstraZeneca And Daiichi Sankyo Secure FDA Approval For Enhertu In Early Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DirectorsTalk Interviews</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOVUw3cWpiMVhkSmF4VjI5VG5ZeTd3N3JOMXdzb0QtdlBmNm13SC1UZGJPZlo2WXloTjluUUN2ZFoxanpaemZhdmd5YkRGMWg4Z21zNElDOXFPYXh2SmdGS1hlMzdRX29OQTR0WGFOLVpfNlUtTWcyemFPYUVfdFZ4cVNMVm4wMTBxZG5iRFo5Q2VxZjlRZU1NeWIxSVE1Qzh1b3g4ajNnOWdQYkg2Q05MUUxIRy00ZHlFQ2Q5N0NLWEpJc1pNMW9DNWQ3aXJ4bUVUclE?oc=5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>18-05-2026 06:29 UTC</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mochida Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>'Skinny Label' Arguments Spotlight Induced Infringement Risk</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRndZS3RaSDBlcnduU0o5bVphUzk0M1Buci1lWVR1ajR6VEJocHVaZ284ZENoaEtKbFVVekg4NEVHS3NQV1BWR014SFNwaGlwS3M4c2N3ckxIbVdGU3FJOE0yeUJHLUlFZDdJU0kyR1VtUnExNjhYNWRrSEozX3hUM21DTnJqcllMazhJczVGTkFDcFFia0lCV2M3eW9naDAt0gFWQVVfeXFMTzd2cFViMFFfUlE0TVdHSktaS2QwU1QwNl80V1FxY3lTaDljMlVVMS00SnZDTXdabjBiX1ZGNzhETFFUUGhaaXVIVXdYTW9EZXBzQW81NkE?oc=5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>18-05-2026 14:12 UTC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): dividend, restructuring and healthcare focus in the sp</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQMFRZc2E5T1REUnp0YnFtU0gwMFdFbHBUSlF2SGY5NXFIa1Z2WFJYc1VtZmN4X3NsbmtncVA1a1NqSUNMczJPT2JHeXRtVGptN1ZEX3ptT0dGQnB5WldVb1JwcjJjdEJrNmllZ01aamJhS3BPNk9SbnpLaEVIRjNxUFZqT3FBVHdhRlVVREktSzEzalI2X2U2cmpOM0lKQ3ZBUmg2UGxJcmVGa0I4MktZYUNiQXl3MUl1Tm5vQWhWQVoxNUU?oc=5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>18-05-2026 02:56 UTC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fresubin clinical nutrition explained for US patients</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVWlPVnRmVlhQNGxxdmN2eTFCWVpMemI1cFdBUzNSU1l6eEZjYWo3MFFYT0wtR0w3bFJHVFlHc09BbVRFWVJqSVIxd3NxdHA2VnI0UllVYWdSamdtUi1fRnM0bUI4cjFmMlhQUkVTcG9QLVo3aTFCWHE1clN2d0pHWW5zRDJtUzQyUmZ6djk5T3FZVnpxSHZHNzhGc29kMnZoTVg0UmMzNmpGNWJpekFzSFdn?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17-05-2026 15:30 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MS Pharma Announces Strategic Growth Investment from Olayan Financing Company</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPT3E2dXZfNXFIQkx3RW5Zekx3QklhRlVJSzBiSmR6X0ZuamdhcXZJbndOOXBURU1aOWI2bXQ5bk5DWHJqZGhndmZ6a0RxTWh6LVFRRnV0UzY2UUt1UU1fODV5OFVJWGVEQXJsakNmazZtRUJGMldfenk2QnlZeEN0dHc0MHFxbkd2UURCd3hrM2EtUDFtY3pZMzE0Q0xhQU5zZmc5V2o3SFhBdG9CeXJxQTN3aWt1STg0RmtmYXUxOTY0ZzVUN2htWWxkbFRaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:52 UTC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): latest FDA approval progress and biosimilar pipeline in focus</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQOGhWOTFuM3JscWQ5WDlSRnhzT3Q2Z3RoSWlJYW1Nc0RvWFRCOEhzZ1FKMHV6emJCcEZPU1Y5MHYwVWFpRjcxeEdfeWt2SFFNS1FpT2c1WVdDdUhUdUZUWEZzLUdydm9QdHBFOTJSb25RTEVCRmo3N1dCZk1pY3Q0UzBSMHJTUUxlSTVIUHVnZGdXS3hNbndDYURZZUpfYkdldEpfcjQtOHMxS3BvWVpwRlBNNTZ0M0wyTDYtVXJ3bkNrUnFyeWdoYmdB?oc=5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:17 UTC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Teva reports diagnostic gap in tardive dyskinesia patients</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVHpNOXhfaWFkMlNWcFpqeFRxdENQSzVNNUN4M3hubVVKcWt0U2VCb2RBaU9WWExFWjVSYjhoNldOWU44eVpSd2dRN0pJMzVRM0JZeTg3NHgxRkEyWGpuMmRVTW9Ubm55YWIwdERDSmhsS1dVa3AwMHFZVXdBSTlHU1lyeHhfbnlsaTN2Um40eHk0M2w0b1NXa2dkX3hBRXNodndnMUUxRk5oVXVIU0RvTll2M1VWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>18-05-2026 12:30 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Fitch lifts Teva debt to investment grade as drugmaker shifts to new meds</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Stock Titan</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSkFhc0RpZW8tVnE1ZU5fbWhHNWJCZGJvT1pma1Y3WHkwVzFOMldCTkRSOGNBODJPM2V0NnZGRlNJN3JoT1FhaTR6LUdvYWttcTB5aDV5ZW8yRFJSQ2pBVEdUMUxDR0FFQU5MZGFZMnpBVnZ3WUU3N0ttMHNDbUZ6bVlxeUpZYy1PeWlRejZZckVMalZ3emdOZjYyaUJ3V2dsN25rcFVUc1dXVzNJeERzVmxhUmRmZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>18-05-2026 12:30 UTC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical stock (US88162G1031): new weight?loss strategy and Q1 results put focus on turna</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcDZGYW5MRHFpSkRQc0VOZENZMWktcTFScHZtTDlDWnQ1QnZ1cnZNT0RkT3pyZ1BkNE9YV29QNnRWTldkN2Z6ZEViUDR1RGVGMzlDbjJ1azdxYXJhU0FTT0JudVJmZjg3SUdjTlJON0VlQ2wwN1MtcHluNXhSQkRqWE9wOThpRlRyb1VEeEFhamphYVdUaEQtSk5KQURDY3dZS2MxLXTON25NMlVsVGdDeVdpbVZ3UWJXRlFEMHJoV285eWxoanliNw?oc=5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17-05-2026 17:06 UTC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>South Korean drugmakers chase monthly obesity shot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Borneo Bulletin</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOSjZybUVPS2NhU3kyZ3BDc3Q0NERscWEtSTlYbHE4MEUwbV9kNUk0eGNDVUc5MzZPX2tjWmNIT0NFWkxfcHJVUE40WGVvVUl3Q3g1ZHQ0bHVJa3lDWjk4aHhxMlNQbV9fZkhVekVJYW1jcGhRX2lTaW1ZWlNNNTdUTF9pMktVZ3VX?oc=5</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>16-05-2026 21:14 UTC</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Pipeline</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis presents real-world Humira biosimilar data at KCR 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>koreabiomed.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZ9IBckFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18-05-2026 02:58 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1925,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-05-2026 20:20:28</t>
+          <t>18-05-2026 20:19:27</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,140 +496,140 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): biosimilar specialist updates investors after FY 2024 report</t>
+          <t>Sandoz urges faster access as government signals biosimilar consultation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>PharmaDispatch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNSS1sZmI4cHcwWW9pZG9iYUdBbkpvVXVMU0F4MkNkcWdIUFdXMlZ3UEVERGd1aVlDTUphMFF5bmtpSFBMcW8yS0thalk4ZDZNYXdYVjJIN3I4WVJLSEM3ZUtPUWJvOUU0eG53bzU1N2UyblQxdXltbWZJMC1jMFVNV1k1WVRkNWkzRkFhd3hnMW5MNEc1MUk2NFl2NVRaZ29Ka21iREJ2VFFROTBRWlk4bkxLYXJSRWNMXzlrZ1VCbnNwckp5djJydA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPdlJnMjNzdGoybkEwWWVZSzdXV2lHUHNLeXEzUUFiUllmQUoyV1VaZmFQMjQ5MHBDU2FQUWQ3NDRSRzZ5Yk50bkU0ZTBtRkdaOFQyTVNMREJhZVV5SnFGT3N0V25sYmxRdjZEb1FMNjhwZ3lqbWwwOVZCUENOTlVPblFla0dVSHRTTjFmMHpCV2hSdW9KNXhGQVEyUkYzdVUtaGhIMHhhaExIMWJGaHVpcHRPZUFTZw?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18-05-2026 07:24 UTC</t>
+          <t>18-05-2026 17:18 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JASCAYD approved in Japan new IPF and PPF treatment</t>
+          <t>Oncology Biosimilars Market is expected to Hit US$ 30.83 Billion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOTlzUmdlVFV0UE1iaGRnNXQ3ZVFUbUlNVTZxejI2bGRHa3JrMGpwVnoyaENkTU5EMU5xYmNTZUd6OHkwQVMxYlI4X3JUY0ZZUlZNMjVXLXFfa0xjRHd4Z2V1MFdhUFo4VFItQXR3STFDNUFXZlhIUkhlVTVPTjNGY2xXLTZzU1J6djFzbHo0Y25SR3oyamhNZXFibm32dHV5MVdvUlE4cWcwRE9RclFpYXd6bFphbGRuSjJEQVRWcl9lVXRIcVd2M3NPYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMHdIMGhoNEZyYWpLNXNWWHVkRklJb2N6R0ZvbF9qeUp3NVVQNXNmYjYxY0VzR2RKbDJXc2pfejFOSW9UZ3RBRXc5QkJPTXJ2eGdFajFENUFsUWQyRG9MMWJLeXJfMmk2MVk4TXI2OW1CaElidDh0VTVDT2ptVWdsVi1vdWZzVzBpZVVwVlBLdVUyTUwxRTZLRjVmY2FIU2h1?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-05-2026 07:10 UTC</t>
+          <t>18-05-2026 09:44 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
+          <t>JASCAYD approved in Japan new IPF and PPF treatment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOTlzUmdlVFV0UE1iaGRnNXQ3ZVFUbUlNVTZxejI2bGRHa3JrMGpwVnoyaENkTU5EMU5xYmNTZUd6OHkwQVMxYlI4X3JUY0ZZUlZNMjVXLXFfa0xjRHd4Z2V1MFdhUFo4VFItQXR3STFDNUFXZlhIUkhlVTVPTjNGY2xXLTZzU1J6djFzbHo0Y25SR3oyamhNZXFibm02dHV5MVdvUlE4cWcwRE9RclFpYXd6bFphbGRuSjJEQVRWcl9lVXRIcVd2M3NPYw?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-05-2026 00:25 UTC</t>
+          <t>18-05-2026 07:10 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hikma steps up $250m buyback, cancels shares to tighten free float</t>
+          <t>Supreme Court declines to hear drugmakers’ challenge to price negotiations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Healthcare Finance News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZ2gzYmFhNDNoS0wyRlY4RERCMzBSNi1MbzA1ZmxzSFRHVGNKbV9TTEdMLXNOeFRpNTFGQWNnVzdtX3VuWlpLVkRRREtnU2dGNl91bFV6Q3NWUWFvSHBZdzFNNWJmLWhZVS04NTFJcUxwcWNrVmtrY0ZOTmpxSGx2TDdEaC1GYjZSN1RsU3NQZUVjMGhIa0xldzRqQ2p2R1J3dGxFR3VCaEUzVXNvZFdBanNWdE8taXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDB4NUI0a1hHMXc0aFJ4WWthSWFkenFJZkJEWHYzMEdCSUdPeXN1cHdUYjJPZDY2c21GMWprUzJzVVhqT0U1aU9LYzdUQVd0WHc3bVkwOExMUEhvNWo3eGgxb3dPMUVOOFY4aC1XSnhuYmxWYkxjNUNoaG1IODNEdHdQQ0c2blpDLXdqQ004bDF6dTJ2SzYtX204MnhtTzZ4QVpGSFc4Smx5Y1lUdjVB?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-05-2026 10:03 UTC</t>
+          <t>18-05-2026 15:24 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): focus on Horizon integration and latest quarterly results</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPWnFkVmxWYXlxd25EelhqcXVodmwwZEtUV21BRktTNVIxaUZTM1gxcUNSdFc5dlc5bUIyb2Zrd0d0cEJvUk4tb3c2dUlxdV9ZUENzQ0NNTXE4bHNvYjI3ckk2QmpYSHhpai1NMGJ5UldjWWNfOVlzUXdlaV8wNndaSVB3RWUxekN6akF4OXBLM1lJUjEzc2k3ejd1ZmFfUzJkODJ5NXk0RnhWTEhYbTFmWFRUTGVLeG1KVXFrSUtTdWpqRkdZMlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-05-2026 14:37 UTC</t>
+          <t>18-05-2026 00:25 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -656,32 +656,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen’s rare disease drug Tavneos tied to 20 deaths in Japan</t>
+          <t>Hikma steps up $250m buyback, cancels shares to tighten free float</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdDVhWTJ1dTNFTkx4TlJDUDIxbmpEUFd3c2ZkeG91RUlBZGlNdDBLVlRoUi1Fa1F5TmFfa3liRjJ1WGtSbGc4OVM1Tmtxblp3OWcyR2dITmFRUEpCLUJ4bUNKQ180a0tqcjg0RlFHN05XTHBNMndOUGlZYmhHTmN2cDZ0UmNNYzhPRkNwcV85RlplX1d4Z2lrdQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQZ2gzYmFhNDNoS0wyRlY4RERCMzBSNi1MbzA1ZmxzSFRHVGNKbV9TTEdMLXNOeFRpNTFGQWNnVzdtX3VuWlpLVkRRREtnU2dGNl91bFV6Q3NWUWFvSHBZdzFNNWJmLWhZVS04NTFJcUxwcWNrVmtrY0ZOTmpxSGx2TDdEaC1GYjZSN1RsU3NQZUVjMGhIa0xldzRqQ2p2R1J3dGxFR3VCaEUzVXNvZFdBanNWdE8taXM?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18-05-2026 12:37 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amgen Stock Analysis: Repatha Surges 34% But Tax Litigation Clouds the Return Case. Here’s What to Expect</t>
+          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TIKR.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUTgydTY2cVlsZFZDMWx4ZVZ1b2dRbG5sOXhLaTJqNWF0ZUdXSHVwTG5aalhnNHFkem1aUWgwekNIZkR3ZUJZdk9tMERwaXNTLTByVnhPbDM3dGVhbTM5dmtHM0Q0SURPVno0ZE1GT2l2VnhWTlZxNVRsbHNsWWJ6c2I1dm5fTDJJRmxJSlRKVVNXVUpWMmVwTWh6aWxhZ0FXcmhrc0VjNnZRU2YwUi00c015UUhaVjFUNFk0NEdaX3F3a1RpQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0WUhfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-05-2026 12:29 UTC</t>
+          <t>18-05-2026 02:16 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -725,27 +725,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen’s ChemoCentryx to Pay $69 Million to End Investor Lawsuit</t>
+          <t>Amgen’s rare disease drug Tavneos tied to 20 deaths in Japan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bloomberg Law News</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTkdJbXFhZnJLWkUtR2FLdW5FSEM2Mi1Gdmc0T3Zyc3k2bmVHcFJfa0xtV2Q5dGdMR1RhR3RCZFRhWHdmaU5QaGt4UE9KTldueEpwSDJMZG1pMzUxT0J0c1h4QWFjREdPMVpiNHdDX3dwTGFBZ3BaM3FIX09VMHg5SkNtM0hrcXh3WFBwWG42aHNEbVJtdVh5R0pVTDFFUlFFZG4yaWplcm9fUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPdDVhWTJ1dTNFTkx4TlJDUDIxbmpEUFd3c2ZkeG91RUlBZGlNdDBLVlRoUi1Fa1F5TmFfa3liRjJ1WGtSbGc4OVM1Tmtxblp3OWcyR2dITmFRUEpCLUJ4bUNKQ180a0tqcjg0RlFHN05XTHBNMndOUGlZYmhHTmN2cDZ0UmNNYzhPRkNwcV85RlplX1d4Z2lrdQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18-05-2026 14:24 UTC</t>
+          <t>18-05-2026 12:37 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -757,22 +757,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
+          <t>Amgen Stock Analysis: Repatha Surges 34% But Tax Litigation Clouds the Return Case. Here’s What to Expect</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0WUhfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPUTgydTY2cVlsZFZDMWx4ZVZ1b2dRbG5sOXhLaTJqNWF0ZUdXSHVwTG5aalhnNHFkem1aUWgwekNIZkR3ZUJZdm9tMERwaXNTLTByVnhPbDM3dGVhbTM5dmtHM0Q0SURPVno0ZE1GT2l2VnhWTlZxNVRsbHNsWWJ6c2I1dm5fTDJJRmxJSlRKVVNXVUpWMmVwTWh6aWxhZ0FXcmhrc0VjNnZRU2YwUi00c015UUhaVjFUNFk0NEdaX3F3a1RpQmc?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-05-2026 02:16 UTC</t>
+          <t>18-05-2026 12:29 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -784,27 +784,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cash per share of PT Organon Pharma Indonesia Tbk – IDX:SCPI</t>
+          <t>Amgen’s ChemoCentryx to Pay $69 Million to End Investor Lawsuit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObnFETi1EcjMxUVYyMHNaN2JyTWM0aXIzRmlfdEM3OUNINy1Oa2M1cUpTVkVrOUZLZU9UbktRajJUak50NTNnYWtEbEtFcE9oTWtiSlBJZHRYc3RVblQzb1JsdVVrYUhaNmtPOUY4TXdmVkdDTjRsWlppR1phZ2lFZ1BKN2hpX29CaHotZ0hIV2VGWWhOYXp6VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTkdJbXFhZnJLWkUtR2FLdW5FSEM2Mi1Gdmc0T3Zyc3k2bmVHcFJfa0xtV2Q5dGdMR1RhR3RCZFRhWHdmaU5QaGt4UE9KTldueEpwSDJMZG1pMzUxT0J0c1h4QWFjREdPMVpiNHdDX3dwTGFBZ3BaM3FIX09VMHg5SkNtM0hrcXh3WFBwWG42aHNEbVJtdVh5R0pVTDFFUlFFZG4yaWplcm9fUQ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-05-2026 12:49 UTC</t>
+          <t>18-05-2026 14:24 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmhxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmgxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -949,27 +949,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield in</t>
+          <t>Addressing Patient Concerns About Vitiligo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQNC1CM0pHSXd1MGd2MUJDZnIxWHVsY0JRLUxjZGEzYlNnVGN2NE04Sjk2MUdzZG5mQkpjX1lwb0tBalFnYmF3RjlsQ3RWZDlwSGppcGxlMFpUYTZHb1ZLNTl4VFFuaDZZT0tsSHd3ZWZtV084cmhITDl0aERKM1lmMC1BUDVFTHF3alV1ek1ORll1NVcybDJxRjZEc3BFdXBSX2JSekltRnVCaGJWUVljdUx6cHkzOUZPX1FMUHh2b3phVGVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQcmxHS3ZySWotMEkxY2JpcHY0N1RnaW1hS2I3Um40RkNZejZ6U0RleElBSXFvMHplSU5pUXZsb1Fvc0tEXzRYZ3U5ZV9iUXZnTk9ONktnVUlsT2pGLS1YTktoMlo1STZJNWdqSXZ4ZG5VeVJGWmp3Zzd5NVVNN2lHV0VkTi0tMS04RDhFOTNueHB4TldzbkE?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18-05-2026 01:54 UTC</t>
+          <t>18-05-2026 17:37 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
+          <t>Race intensifies to lead next wave of obesity drugs as trial results loom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Pharma Voice</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQOGhYeC1mbVd0akxkWV8xa1BoVEFrUUF0Mjc0ak41Y0ZZeTB4VWdLWEh3N24yZzF2UmF3a3NUeUFscng3NUNBSlRYVFRzUTNab21ETVNQdXl0RDI2UW5MZF9aRUJCel8yTlFVSnpYbkd1ZVdZeXRTS0oxNmN4cWFWdFM1Nkl3NnNwcGtTVlVhVDZTWUpuRzRDUnZ2TjVLWFdM?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18-05-2026 12:49 UTC</t>
+          <t>18-05-2026 13:25 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1013,54 +1013,54 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>‘Regulators were WELL AWARE…’: Whistleblower 'exposes' FDA, CDC over COVID-19 vaccine injuries</t>
+          <t>Depo Provera Lawsuit Settlement | May 2026 Litigation Update</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Lawsuit Information Center</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQa3VsbEpHdVNKRkdVS0R4cEs3R3gwUl_0SG5UdS1yYlRkR182NjBrcmswcFBxTUVxYXhpNEpveE5xSlFhZnFiQkdXeUpWR1FESkUzMkRxOWNON0xQaG9iUWNRaHlVYjlGRlc2a0U4LWNMbUo5U0p3eDNEYXhwbll0VU50TENBZ0U4ZHRqWG1jWDJUMEhmTDhYdjh2Z2dfUkk5aFI2ZnlNc193NEZUbFNfcDc0ZEd0TXdiQTRTUjI2TW5YQUZpYktuMmY5eExPUDFaSTVjb1JLQVFWUGQwa1IyNFo2aXFGVjdmNlV5enRoc25HRGk4dTRVaEg1Q1hZZ9IBgwJBVV95cUxPbXVpWG0wNkFudE55X3dNMlVhUUtsVE00NEp5eFdSV3l1V1hDS0djLXVGdC12ZmpnLUdNVllkVjhZVkRjOW1rU3dmNjJmU1lGOGVKYWppcWFGeFBMLTl5QXZxX3QxVjlmUTdTeWhPWlFzcjR6OWJCcEZKZXJ6WXJkTkozYndyZjRzaEVGbnRrQmVKYmQwRjQ2M2tSLXVGVnF0S0tnYXhLdzl5c3BjSHU5Mjhvc0ctY0tkOWI4OE1BUWlCQi1oZU1ZNTNtNFBjMTF5Y2Z2Z0ctUG83R0NsX0c2anlyRkRNWUZGVWQyb0xoSzFDMnVSSkgyRkI4WlAtZmJxd1Z3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB1X0VIdm5nRVF0LVBnMTU5RDBvZVZtaVN1Sk5UQkFaQVdKOTdfYnVQam9QelRvcEhWRGhMSTBJWUZibm1YNjMzNWlROUhpX3ZjTmw3bHk5TVVDVXM5UTVyUTdkMFRpTXZNVWVTUFNqVDBYNGoxTjg0?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18-05-2026 11:10 UTC</t>
+          <t>18-05-2026 14:20 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIIB SHAREHOLDER INVESTIGATION: SueWallSt Investigates Biogen Inc. for Possible Securities Law Violations</t>
+          <t>Why Pfizer Stock Still Looks Deeply Undervalued In 2026 (NYSE:PFE)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQRUM1WVEtenFuMTBGT0IyMzU2U0c4RWgxNFlSS0RUSWdrSWdDS2s2djJ6NkpjZWFQUFU5dF9JS3RVN24xRDZpNlhqS0J6dTJxYlJjVHFhbG1ocE1ZcGVyVWFfNjhVbEotQlZhd0s3SEVwelhjTWd5azYwTE1qN1dvUUJmb2pkTm1NZmxVUWtGZUhNUVBEdnhCeVIwTjdWYXNYMkZibEZ6ODFUNDBBMHlsTHZPVFJlUEZOa3hpa1JvSmhMRHIyVldpb1QydVpFV0NjbDJkczYtaDlwSE5KRUFUbE5PbW5jYUxVSXp2NWVZeTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPY0FOUG0tc1dQLXBwN3dfeXREYkUtLXVxLXF0VjlXMDB1UFZ0dFZwVkFITDdrVm1NVHp0T3ZiN1ZsNEMzMHZsTHp3ckV6TDZQOEJObFhuLXJwdmFCSjNHS05PWm5BcjhTSEZtcU43RUdTemJuQzhfTFdXTVJBVzNvb3kydWFTcWhFWHZQbDlsMlJMM3c3MHNHTUpmaDI?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18-05-2026 13:00 UTC</t>
+          <t>18-05-2026 13:28 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1072,27 +1072,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen Inc. stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
+          <t>Pfizer Stock Price (NYSE:PFE) Trades at $25.30 With 6.80% Dividend Yield After Q1 Revenue Beats by $649M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TradingNEWS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR1NDb0Q2ME9WVU1sR042WG05TE9DLTVieVI2cWZLdnJfZUN3aFpXYWphUEpzLWdQNVhZQkdYcXhBMHhnbzEwZEE3WXFWc1o3cTVta2RKYXY5STVtdzl3ZkVlam1UNEZRTm5FblhoMUdDRzFwM3k4WHpwRVVsNXFJR053WEszcTRnT2NPVUF6RDFQazBJRUExb3hYYjN4cnBnSW5YLXJvdE1lbzVIRnBQMlRILUVpaVNGcmFUSG41bjdSTUg4S0lF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPcDgyVHNMMjVlTTR3RXNKQW5mNkJlZVJoeVhfaGExMEQzVFFtWEdQUUFZYXJaYWpxa1Y1LWszT0htanZidlJtbi1IQzdJUEhuYWRnS3JaUnNCQlRCaWRCQUd1S1BHaXlEQkp4NVRUeWNBWTZGallZWGVVWW82b2dqSUs0cEtQS2t4TUFJaHFlNUNwdlJ5cWR4MHFmaXZzNnJvdmR4M3BtOWFTMzVi?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18-05-2026 02:55 UTC</t>
+          <t>18-05-2026 16:41 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1104,12 +1104,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1119,44 +1119,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-05-2026 23:42 UTC</t>
+          <t>18-05-2026 12:49 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Blau Farmaceutica</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blau Farmacêutica stock (BRBLAUACNOR1): Brazil drugmaker’s profile and US investor angle</t>
+          <t>Daiwa Securities Adjusts Price Target on Pfizer to $28 From $27, Maintains Neutral Rating</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOREF5MkI4WmlmVVBtSmlBbkJleU1qQUNFcmhJaE1kbjJDU1F1cUQ5ZzRZUi1vazdrdk10OVg1LW9oUTJHY3FLcWowUGhPZjluYWVFLXptT1AwS2lqSG14MF9URkstWjVqbGVNNVV0Rl96RUZDOGNtWTREeUV1RERBSFhPNE5va0dPRTJ0WHFEb1ZqMzRKdVpaYjlxd0dEQWJIZzFrd0tVOC1uQ28wOHhGbndhbVJCRUlSUWtzNEtTTlRQM282?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNTDRRM2ZpSVZPMGFRSDNVeDdYa3F1bEt3UDN4SkZYdzdJa1haazFwVVdMak80T2R3YVQxZTFiNkppaFd3QzJKSDZFZnp4TlZSTDlZajdyWV9tU1FvRG9WeDNyZ1JGREVYTEF5SHBFSVBWdTBEeVVDTnZFVVQ3RTMzRk1fVERVcnhmMUlnaVk2eXM5YWdqWENVSjBEcnhUUkVLMWc?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18-05-2026 09:51 UTC</t>
+          <t>18-05-2026 09:55 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,91 +1168,91 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories launches its generic Semaglutide Injection in Canada</t>
+          <t>Biogen completes acquisition of Apellis Pharmaceuticals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>Ophthalmology Times</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNlpNbWVzaExidUZRaC1QQWY4SFZBRWJuZmRlYzV2NmRzUjBkN0xQMU51ZmNydjlaenhqbi16V0NWaWNIcnVZNS1SVFlCR2hkVFhHaDZDajllVm9qMXRQR3RWaEliSkk5dDlaYUJ4ZTVpb1JrcDVBcHFZOVJ3OUpWcGF4VVpOQW9hZ2QyQkhkS3A1TU90ejJ1MHUzWVp5eEstQVMwam5CbnDSAa4BQVVfeXFMUGRkRDAtR294VDREUENuT2lJLVdUUllqd3FMOEFzSTR2VTV0cFJJQWJVQ2dldkJoYkZtY3NiYTI5bGtPeTNJLWFGYTYzR0RkMk00SFhkbDZHNUo5dFk3SDFDd2N2M0k0T19HVTMxejVWLUVJdUxDM2hzUWlidGpaRlBOUjJhZEkwdmc1a3RqYzV4VHEzWEJfYkVmNWhEc3NTcWxnY2F4Sms5LTFKWl9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPNXJMNVJXX0t6M0xBVkJMTC1tN3hEXzhFYi1paGlnZWh4Z3Z5VUgwNFpHUE5BeDJKbm9abjdsZVU0aXBiRVVCQ3BJYldIem90b1JpUXhKMlpuTVFCQ29pWHJaZUhRRFN1alA2cDR2djV5c284OTBoVkNGSjluV1Q0WlRSYXZvTTh3bmpVaHZtY2xmbFNUZVdIU3pQcw?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18-05-2026 05:56 UTC</t>
+          <t>18-05-2026 15:52 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories slides Monday, outperforms competitors</t>
+          <t>Biogen Faces Legal Scrutiny After Diranersen Trial Results, Stoc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MarketWatch</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQckk1bS1kMS1tVERiM0J4SW1qejJqT1RTZlNRTHhNdkdJNnBDSGpRN0ctLU1yM1VYMWZtUlZ3SktsTTk0bEZkeUFFc1JwdzhDczk0WEhrX1AwRnJYYUx6dXhMczlMN1FjVEM4UURfMWNtMkROcmxtaGdtMFBMZWtkSUJIcVRJczRHUHl5aXZDTWs5WDZKdW05RFlSSWtla245MGZEdFNlTlJSREFvOXpUNlpZVThDZ1ZZNG1kb3JWRjFZNHZiTWVSMXpGSjlqOE1Cbl9oeEFuMm1sSTV4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwRBVV95cUxQcGs4V2tWRUluV2hZdFpJYWdUbHB4Zl_mM3VCYk4wVHZ5ZkZNWWtTTTFaSW45N2VuVnRxZXlqY19CeHhmSjJTUzdQQjNmX2xNV0tGbnJhY2VxbzFBYkxKRHoySEMybl9IcUxYdFFacE5sU2t1ZTUzLWh2b0lXMWZfLXB2ZV9oaHJHdHMtS2t6SlJvUTBBODEyQi1OTTE2dHdrcmJaU0dlcDZIYk9nZnFmWFJkTG1vOWtVejl2ZXNmUEpNTUxnTkZKazg5Q2NRQTlVOEdISUR6ZjQwbUd0bzBERGM0bk9pZzJSTEg0M1o5ZzE3X1ZIWU5zV0NsdDg0RVRHVDNGNlRJYzI0QkZoVXozZl9MblFLYW1NLThZYjNienpfN2s5eGkxRmc0VF9MME04N2p6SC0zWnJlZzFudE02X0tnNzU5Yk5raFk3eVFnWW5qZEhBUllHaVpyazBaMFFNc2tUYVBDNWowUUJSNHF1OVk2X0ZqWlBWekppVGhGRDY3WkU1ckFSMk5RMkR3bm11bTBYX0VmSnVBTy1DNUNadjNSUVVtb1l5Nm9jb1Rjb1M1LTZlZmJkVzFCT294OWtMR2N0dnZjMk5MWVFmVjhTVUhjM2p2cWF2anVwdi1nMG00dHRNcE9KWlVfbFpWRU9SNGhGN1ZUdXc1V1FnSlItVzBvZ29USEVvTGV6UFE1Yw?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18-05-2026 10:30 UTC</t>
+          <t>18-05-2026 17:26 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Global investor meetings for Dr. Reddy’s (NYSE: RDY) in May–June 2026</t>
+          <t>Assessing Biogen (BIIB) Valuation After Recent Share Price Momentum And Earnings Expectations</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOalVhUmUxYTFxc1JEOXZuNnNFcnd3VHcxRlg4MDdYN1Y0VWdmVXZKYWpkQlNoNDFmbi1pZnU3endaeV80dkw4THRGVHRWV3h1NGZWUUJsdl9PdDNRcXZRY3ZmZzRzU0piV08wdzBRSnotSzlVR0wwSkQ3cmpnS3YzZGxJSzZtTGc1MEdWeUREQ1FweExSbzFFVHFGZTZISnQwVms1dkxEMGFKYkR0ZFpMQVdyTXZSbmQyMWNWMWp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOUTcteVhyZC1XUFNfMVlQTExTYjZ4MTk2MjR4T0RyUXVaYzVaWV9aTGc3SFBNZ0JCazlvZXlSbFVMUDI3UWRGMXpSY1kxUzVobWVhSTRpamhITDlCV0hfTWxRQjVkUG1EZ1ZpanFVcU5Mb1FIRjRWX0NoQkJPeVdsVDZLbkRTWWt4WnVwamhGNk9QN01fY0NwTkpDRi05eGdtcmU3WDkxUHpVcE9JQ1RTTUZkZDIyYTJDNHB1a01CM29vWUI5djh2Mncxb0prZGxKMzdFMlhJSUVZUdIB3wFBVV95cUxORmd5V3o1UG5sNzRSY2lEamN3SVE5MFQ4SlNZU3pnbGU3eE1OQWY3YndfaFQ0dVlGRF9Gal9wWWtyaHR4cFJTM2lVZ09XRWRmTzNQV1BULWotUlZyMzhiU0RXOWVxeVVRS3dSQVdRVUk5cUZCRF9CMDVrY21QZ1BlU0ZDYzE0TW1iaU1USkdDTkVSYmdGdnE0dGhiQnM3U2FlQUstZ3R4R2lJSlQ3Q1ZHLXRqTWFBN0pwOWlWQTFXd0sxRlZJSmhWY2FORllpVWVFODdDeWREb3NTVndibE93?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18-05-2026 10:45 UTC</t>
+          <t>18-05-2026 16:34 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1264,27 +1264,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Dr. Reddy’s Q4 2026 misses earnings expectations</t>
+          <t>BIIB SHAREHOLDER INVESTIGATION: SueWallSt Investigates Biogen Inc. for Possible Securities Law Violations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNY3NLLUpXWVBDVk9PdnNfaWNBZFk5bGtsS1p1UjFLUE95amRDUDd6UkVrdjZFVjVoajBkTFRudm14RWsxalQzT3o2RzVPNVN6VEZreTFHclMtcy1jMTBpRmg1cEN2TThMYnFWUlZLT3VGSjgxUF9QYU9ReXl0TEliSlY0TmVSRTRLa3FBbmY2VnhhRFVGWUcxWkZFY3Y1RVpaWDFMYWY3RUtSNzRhTVBfRjY4bE93N0ZWbllkVGRxUm5NVnFJVWl5SE1tRWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQRUM1WVEtenFuMTBGT0IyMzU2U0c4RWgxNFlSS0RUSWdrSWdDS2s2djJ6NkpjZWFQUFU5dF9JS3RVN24xRDZpNlhqS0J6dTJxYlJjVHFhbG1ocE1ZcGVyVWFfNjhVbEotQlZhd0s3SEVwelhjTWd5azYwTE1qN1dvUUJmb2 and pcbtTm1NZmxVUWtGZUhNUVBEdnhCeVIwTjdWYXNYMkZibEZ6ODFUNDBBMHlsTHZPVFJlUEZOa3hpa1JvSmhMRHIyVldpb1QydVpFV0NjbDJkczYtaDlwSE5KRUFUbE5PbW5jYUxVSXp2NWVZeTE?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18-05-2026 07:04 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1296,123 +1296,123 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biosimilars could surpass generics in US mkt by early 2030s: Dr Reddy's CEO</t>
+          <t>Wedbush Maintains Biogen(BIIB.US) With Hold Rating, Maintains Target Price $196</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQZ2stSVlrS1Q0QVJHY3ZWV25Ob1FkOUM1TEw2OUZZc1g4Z0JwRUZTdGQ1djRXUFUwbThPSUp4NGV4dDdRMXVOdmNBXzZFZVBrZklkZ3BDblJDcnYzTzg4T3ZKbzNFV3JFRHozbm5vdEV5MWtOTzBnTzl2S2RvV2Zld182eFlqV1pBZ2VUNDN0WUZEaHVPNUppTml6ejVHaWZETnlReTcxaFVURDVQeDlzYWl4UWt1MDZ1YVd1RVhiSUR2UXhQeVNBY3lEUVROc3JHQVc1anZJVmpQN2NjbFHSAeMBQVVfeXFMT3Utd2U1RWg3NWZENW0ycG0wNmh0NzJ4aDNWUlU0aHJ4N2FPYlJBb1RIYkdnMHpDeHhZc05CcS1QYXAzaFZvUWhHa1JOMmVuWS1sSVZiTktUWTdvNUV1SGVrVVpIT1FQNGVHY2IzTTMtT2hnZGxRRGFqQTJicm1uYU9Ka2hDR3FXUFhJUk5GZ1ZWM0tMdHloeV93cEpzaG5KLVI5Rnh6MTY4N3NDY2VhM2JyenlqdEtSZFpNWXpTZ0NMeHlNUTBzR2VJU3owTzlUemswRHRRcjJka0ZMWEh2ZFEyN0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdnVWTTViRmFqUl9hdkxQdEc2ODI2UG41cnFWb0tiUlFfNFljc0R3eVJkbTVFbVpPd1c3OHdSc3pGZER4b0ZIeVBXelBUZjY0eVd4NXBIZVdUT1VLdFVObmNoNERKeXNTWGtVZXI5QUY3U1pjMUlUNXJwSi1HSUZiQWpVUU15NXBGTnFqS1VkaE1ybmtyUEFBcks0bkl5ZDJEM0U4TTl3UVRFcmxKd2YwWEhrNA?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17-05-2026 18:19 UTC</t>
+          <t>18-05-2026 12:48 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI™ (golimumab-sldi) in the United States</t>
+          <t>Biogen Inc. stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijANBVV95cUxNWWtCYzgxanJCTFhtRGVIM2xYaXROTzRPSklLQkwtOUZDeExSbTFaV3VERTNBUHBTcDBaV3RpSkxGMFg2bFFBRWFnMDZ6blY3YTZNZWZWQUZuYl9aMDBjdlJocGgxcGdYVW93b0lfVGhjajQ5OFMyV0RETjBSRjlIaHlpaklnbmptaWl2NFJZTEx3aHVWLXB6ZnNkeGcyMlNQRlRGX0JnSmdHcXZFZHRmSE9hbG0tNUpoeWt3dDdPLVNyYV9iaEpaZjgzblBoQXpXd0hEaEhlMTh0WDVUUmhDR3BwcnVFVHd6czRSSWRMZXotX2dVcVh0TjhlRUxLT2ZuLVNxV1hFQ0o2b19TSlBxVjJjV3p3MkJRZWZLVV8zOGhKd2M5V0hOYWM5bU85THNmemtyX25VNU8yaGdUWHo1WWQ3UGtpT0EtQXRPb2FJVVNzb0pvdEs5OVBDYlhuTnh4ZHhwOENCX0RLQmNiTGF6QUg1V0duaXlFOWJxZFlGWkNBMURsQ1B3ZlN6WDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOR1NDb0Q2ME9WVU1sR042WG05TE9DLTVieVI2cWZLdnJfZUN3aFpXYWphUEpzLWdQNVhZQkdYcXhBMHhnbzEwZEE3WXFWc1o3cTVta2RKYXY5STVtdzl3ZkVlam1UNEZRTm5FblhoMUdDRzFwM3k4WHpwRVVsNXFJR053WEszcTRnT2NPVUF6RDFQazBJRUExb3hYYjN4cnBnSW5YLXJvdE1lbzVIRnBQMlRILUVpaVNGcmFUSG41bjdSTUg4S0lF?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-05-2026 12:00 UTC</t>
+          <t>18-05-2026 02:55 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Should you buy Biocon shares now? Key takeaways from Q4 FY26 results</t>
+          <t>Rare Disease Therapeutics Market 2025-2033 | Market Growth</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zee Business</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWEFZSE5GbjhLc0luN19jU2tJTVU3bDF0VWdSQTM0MElBUUpFcjdUcWtsbzhBUHotOFNlUzdXXzBjYzFKaVc3MDItQ1dpY2tBbHhmcE1PWmR5NmdkSXFzcGxEX1lWMjhPOFhoWFJHRnpDUmNLa05IZ3BzWkNuaXl2ZmhVX250UXI4Mk5lNkJYVWZZNC1YeGdSOFR0ZGd5OTlWT0htb1lQTmxaS2VRWUhCcmN2QUdMQjdqTU1YMFJoUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOOGxEOENOU2xVMEpic3ZoVVdybmRocmludjYtUENlc21NeVFuZDZQTng4WjkycjZDYVdvZnpEMW9fcEJaeDltd0tqSXFYbGZaeG4zdHlzMU1ERU1fVm1RVV9jalBjMlRqNTE3bjJIZlZUZ3FHZUZEVGhjWUluWTVfdHBiczB1bDFwRTJiaFNrYzIzM0dCQnBz?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18-05-2026 01:36 UTC</t>
+          <t>18-05-2026 11:25 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
+          <t>Blau Farmacêutica stock (BRBLAUACNOR1): Brazil drugmaker’s profile and US investor angle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOREF5MkI4WmlmVVBtSmlBbkJleU1qQUNFcmhJaE1kbjJDU1F1cUQ5ZzRZUi1vazdrdk10OVg1LW9oUTJHY3FLcWowUGhPZjluYWVFLXptT1AwS2lqSG14MF9URkstWjVqbGVNNVV0Rl96RUZDOGNtWTREeUV1RERBSFhPNE5va0dPRTJ0WHFEb1ZqMzRKdVpaYjlxd0dEQWJIZzFrd0tVOC1uQ28wOHhGbndhbVJCRUlSUWtzNEtTTlRQM282?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18-05-2026 02:31 UTC</t>
+          <t>18-05-2026 09:51 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,27 +1424,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Board of Biocon recommends final dividend</t>
+          <t>Dr. Reddy’s (NYSE: RDY) files FY26 earnings call transcript for investors</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQXJweHFyTG8zRUhvZng0SEN5Y1NuTExFZWlFV0xtTkF5Q1J2a21aR1RZM1ZZTjJjaU9keTlmVXRRZGw1T0FaRG9BWXk4NHNId0FTMU5QM01tOE9HNXphZFVtZzlMeXdKTFRiUVVXMnBtYVlYZHhxdTJJREtZOF9kbjJadHkwSDlYNjdVQ2lURk9EazhMQzBhTkViQUZ3azZCU2RvVGczbC1xd1BoVzRVdElWWkg4eEtWbEJfUkNxZGtpSnlQcTBzNExn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPNExJR0Z1N2M3QjRxRnNPRVFsOHRSNVdoS0ZDNnAwdTNGdkJmQms4RlNkNjhFTlF6WlNtSkRDRW1pY1BJWnl5TGNINUktN2JvM3N0MUlab1lXbVREek40dTh2TlpjcGxTLTJFWkxDWS00NW1IWXhReWVFTFJ2enhocTVwUFUzOTZaeTdrcTlndGZadXQxWTFVd3ZRekZVeVBNa3czcU8wVjJwRjVfa3JJSTdKNFRCTU9YT0d1R1lR?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18-05-2026 01:39 UTC</t>
+          <t>18-05-2026 17:00 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1456,27 +1456,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CDSCO Approves Aurobindo CuraTeQ's Bevacizumab Biosimilar Bevqolva for Cancer Treatment</t>
+          <t>Dr. Reddy's Laboratories launches its generic Semaglutide Injection in Canada</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQQUZNWWhrREJJVEkzVlF5QWJ2dWVpZk1JVV9ob25IMklTNzlOQWJRZENob2lRdzdEaFFqNGtkSS11YXNKNC1NLVRmaFRLTGhYNERDY05qS21fS1pzZmhkMjk2bk5SRTVLSVg5TzBXUTNlVEIybEJfdGJfd0ZHNHQxWDA0b0E2TWo1cVM5ZHR5R0hRekxWYUJLa1lFZ3hZS3BQdlZVZjB1Sk1NMGJBOUd2aW5tZFBrWlRfVk40TkhsNkZMX0prRkh3X1RUcm9qOXpBX3JmNmp3eWhMbmREQUJuZU5B0gHnAUFVX3lxTE9qZ1hkTHh3bnUta0M3S0Y3YWlRYXNzajk3T0hDY1JuaWtJd2VLanZJYmM2cTMxZ2xFVFFlWmZoSE51cjluaUwtNkRxRmFkaU5rSEtBMkRaM0VzVFNCYzlMbnJjcDA5aWpwTVFtSnFfRDZYMWxPVWx1N0M5ajZ6eUJDcFBwWHUtLXM0RThOTDJBS3hNY3hTRi1xSm9rbVVFTy1vN2JJNGtMQ0JEbzZpVFRSQWswMk8xY0hndUh2dmNKVzFWY2VXNGtSVm9Say02LW5JU05RSk9SUUZRT3hCTjlKanp1a0VuYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNlpNbWVzaExidUZRaC1QQWY4SFZBRWJuZmRlYzV2NmRzUjBkN0xQMU51ZmNydjlaenhqbi16V0NWaWNIcnVZNS1SVFlCR2hkVFhHaDZDajllVm9qMXRQR3RWaEliSkk5dDlaYUJ4ZTVpb1JrcDVBcHFZOVJ3OUpWcGF4VVpOQW9hZ2QyQkhkS3A1TU90ejJ1MHUzWVp5eEstQVMwam5CbnDSAa4BQVVfeXFMUGRkRDAtR294VDREUENuT2lJLVdUUllqd3FMOEFzSTR2VTV0cFJJQWJVQ2dldkJoYkZtY3NiYTI5bGtPeTNJLWFGYTYzR0RkMk00SFhkbDZHNUo5dFk3SDFDd2N2M0k0T19HVTMxejVWLUVJdUxDM2hzUWlidGpaRlBOUjJhZEkwdmc1a3RqYzV4VHEzWEJfYkVmNWhEc3NTcWxnY2F4Sms5LTFKWl9R?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-05-2026 16:52 UTC</t>
+          <t>18-05-2026 05:56 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1488,187 +1488,187 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Samsung Medison Leads Women’s Health with Life Cycle Ultrasound Solutions at ISUOG 2025</t>
+          <t>Dr. Reddy's Laboratories slides Monday, outperforms competitors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spherical Insights</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPYU4wbktrVFRkOXlNNnQzbk9TWGpaOFc3T1BuRVF0emtieVQ1Z19rQTFoenBEMVBybjhjQXVTTG9hMEJEYWp0RmZBSy0ybEtzRms5dTJ1R1NFVmJzd3JPR0dCV3dXVF9ETlhQX0VsU3dvZGRvbG5QWmdoQ21NZ3k0NkMtRG5ZUVdiVG9nQ0VNbjM2d3Jsc3BKWDZWT25oTkZJXzVJS3dVbFhUTkh1SURYUENYU3VRazNva0xDTFZOQVFfaGpScWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQckk1bS1kMS1tVERiM0J4SW1qejJqT1RTZlNRTHhNdkdJNnBDSGpRN0ctLU1yM1VYMWZtUlZ3SktsTTk0bEZkeUFFc1JwdzhDczk0WEhrX1AwRnJYYUx6dXhMczlMN1FjVEM4UURfMWNtMkROcmxtaGdtMFBMZWtkSUJIcVRJczRHUHl5aXZDTWs5WDZKdW05RFlSSWtla245MGZEdFNlTlJSREFvOXpUNlpZVThDZ1ZZNG1kb3JWRjFZNHZiTWVSMXpGSjlqOE1Cbl9oeEFuMm1sSTV4?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18-05-2026 13:01 UTC</t>
+          <t>18-05-2026 10:30 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Celltrion’s Vegzelma strengthens lead in Japan bevacizumab biosimilar market</t>
+          <t>Global investor meetings for Dr. Reddy’s (NYSE: RDY) in May–June 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5DQjAzWWtGVmNmSXB1el9wZ2k2c2t6UzVRY1ZmM0RpTVFQNm9aeEhueDlfQUFWaVBQV2diOXZPV19HM2dUTDloZGJFMUVXbHJ3Q2pJN05LOEZFdXg1cW9xUmV6WHFELXlqUC1UMzdn0gFyQVVfeXFMTjB6QkNWYU9UZElLQUtGMmR4MVdKd2NESWhtOTl2VE4xMFh6MUVCbDlIbkRJRUFLT0FSZ1JvNUJMcnlfRGdlZllxcGw3dHl4dGp4TjFaaWlVWmxPY1A5bUNIWkoyT3ppa01lNFAyTFZPSHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOalVhUmUxYTFxc1JEOXZuNnNFcnd3VHcxRlg4MDdYN1Y0VWdmVXZKYWpkQlNoNDFmbi1pZnU3endaeV80dkw4THRGVHRWV3h1NGZWUUJsdl9PdDNRcXZRY3ZmZzRzU0piV08wdzBRSnotSzlVR0wwSkQ3cmpnS3YzZGxJSzZtTGc1MEdWeUREQ1FweExSbzFFVHFGZTZISnQwVms1dkxEMGFKYkR0ZFpMQVdyTXZSbkQyaGNWMWp3?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18-05-2026 04:51 UTC</t>
+          <t>18-05-2026 10:45 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AstraZeneca To Pay $155 Million Milestone To Daiichi Sankyo After US Approvals</t>
+          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI™ (golimumab-sldi) in the United States</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPVU16VGpjMnhVNnhmaHNNeGVIWTZtNnJfN0JqTENIYlBfNmNhazNCLWFvanpOcHlRU2YwbnBicDcxZFZwaEd1M0RSdnVKYWRqUTFCWUNlYjA0XzBTcTYtNmMzb0FwRDhPWkl6NzlmQm9iZFB2QWxkZ3RJUUo2NHRaSWNqbjM2VW5Kc043Y2tKSFl0T3BmQjlOQzNLS2VhWVNrWldkSnREVwBWTE4xZThGNmo0d1hvNWVmVWFzeVZ6dE93cW44QmczVk9ENkh5V3g3aldoQkoxQWd6eFRyM3pKZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijANBVV95cUxNWWtCYzgxanJCTFhtRGVIM2xYaXROTzRPSklLQkwtOUZDeExSbTFaV3VERTNBUHBTcDBaV3RpSkxGMFg2bFFBRWFnMDZ6blY3YTZNZWZWQUZuYl9aMDBjdlJocGgxcGdYVW93b0lfVGhjajQ5OFMyV0RETjBSRjlIaHlpaklnbmptaWl2NFJZTEx3aHVWLXB6ZnNkeGcyMlNQRlRGX0JnSmdHcXZFZHRmSE9hbG0tNUpoeWt3dDdPLVNyYV9iaEpaZjgzblBoQXpXd0hEaEhlMTh0WDVUUmhDR3BwcnVFVHd6czRSSWRMZXotX2dVcVh0TjhlRUxLT2ZuLVNxV1hFQ0o2b19TSlBxVjJjV3p3MkJRZWZLVV8zOG9Kd2M5V0hOYWM5bU85THNmemtyX25VNU8yaGdUWHo1WWQ3UGtpT0EtQXRPb2FJVVNzb0pvdEs5OVBDYlhuTnh4ZHhwOENCX0RLQmNiTGF6QUg1V0duaXlFOWJxZFlGWkNBMURsQ1B3ZlN6WDE?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18-05-2026 06:27 UTC</t>
+          <t>18-05-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AstraZeneca And Daiichi Sankyo Secure FDA Approval For Enhertu In Early Breast Cancer</t>
+          <t>Mock drill conducted at Biocon in Pashamylaram Industrial Area</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DirectorsTalk Interviews</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOVUw3cWpiMVhkSmF4VjI5VG5ZeTd3N3JOMXdzb0QtdlBmNm13SC1UZGJPZlo2WXloTjluUUN2ZFoxanpaemZhdmd5YkRGMWg4Z21zNElDOXFPYXh2SmdGS1hlMzdRX29OQTR0WGFOLVpfNlUtTWcyemFPYUVfdFZ4cVNMVm4wMTBxZG5iRFo5Q2VxZjlRZU1NeWIxSVE1Qzh1b3g4ajNnOWdQYkg2Q05MUUxIRy00ZHlFQ2Q5N0NLWEpJc1pNMW9DNWQ3aXJ4bUVUclE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNZE96VjFkY0xBYW1HcHJpaHU5TGdBNWtLTnVWRnN3UjBNMEFkNkpSbk0tMFAwb3VLUmhVcXQ0N1BLNWl5RDVWUDFKRk9kczJkUGRyMmE3WkUwNUI5RjJGdWxrNEYzektxaEc4ZEVpUHdPNy1RX3o4T3pEbnVKREFvRHBjX0loeVoyREcwUmtRR2tOeUk?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18-05-2026 06:29 UTC</t>
+          <t>18-05-2026 14:52 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mochida Pharmaceutical</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>'Skinny Label' Arguments Spotlight Induced Infringement Risk</t>
+          <t>Should you buy Biocon shares now? Key takeaways from Q4 FY26 results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRndZS3RaSDBlcnduU0o5bVphUzk0M1Buci1lWVR1ajR6VEJocHVaZ284ZENoaEtKbFVVekg4NEVHS3NQV1BWR014SFNwaGlwS3M4c2N3ckxIbVdGU3FJOE0yeUJHLUlFZDdJU0kyR1VtUnExNjhYNWRrSEozX3hUM21DTnJqcllMazhJczVGTkFDcFFia0lCV2M3eW9naDAt0gFWQVVfeXFMTzd2cFViMFFfUlE0TVdHSktaS2QwU1QwNl80V1FxY3lTaDljMlVVMS00SnZDTXdabjBiX1ZGNzhETFFUUGhaaXVIVXdYTW9EZXBzQW81NkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWEFZSE5GbjhLc0luN19jU2tJTVU3bDF0VWdSQTM0MElBUUpFcjdUcWtsbzhBUHotOFNlUzdXXzBjYzFKaVc3MDItQ1dpY2tBbHhmcE1PWmR5NmdkSXFzcGxEX1lWMjhPOFhoWFJHRnpDUmNLa05IZ3BzWkNuaXl2ZmhVX250UXI4Mk5lNkJYVWZZNC1YeGdSOFR0ZGd5OTlWT0htb1lQTmxaS2VRWUhCcmN2QUdMQjdqTU1YMFJoUEU?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18-05-2026 14:12 UTC</t>
+          <t>18-05-2026 01:36 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): dividend, restructuring and healthcare focus in the sp</t>
+          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 430.2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQMFRZc2E5T1REUnp0YnFtU0gwMFdFbHBUSlF2SGY5NXFIa1Z2WFJYc1VtZmN4X3NsbmtncVA1a1NqSUNMczJPT2JHeXRtVGptN1ZEX3ptT0dGQnB5WldVb1JwcjJjdEJrNmllZ01aamJhS3BPNk9SbnpLaEVIRjNxUFZqT3FBVHdhRlVVREktSzEzalI2X2U2cmpOM0lKQ3ZBUmg2UGxJcmVGa0I4MktZYUNiQXl3MUl1Tm5vQWhWQVoxNUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOeXFBYXNUbllGMFlOdllVeVdTbnpvV214ckZpUWJtODVjNktpWVA5UW5Ebnh6SUZqa2R5SmdKRDNUajRQZWo5SWVaZkpWSnRoSzF3SWtrV2xVQVp6RFpnQk9fVDZaNS1rR0ZNS0x1eHhoME9WT21nOHZkclBPczB3S3Jzdkk2T0pMUkhyRkhZOVFvQTVUU0VSZmRmSmNOZ24wTzA3a25DVUpmcEhKNlBXX2FNTml4eVk2dnhuRnR1OG5CM0F3a3dQNDV3?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18-05-2026 02:56 UTC</t>
+          <t>18-05-2026 02:31 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1680,59 +1680,59 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fresubin clinical nutrition explained for US patients</t>
+          <t>Board of Biocon recommends final dividend</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVWlPVnRmVlhQNGxxdmN2eTFCWVpMemI1cFdBUzNSU1l6eEZjYWo3MFFYT0wtR0w3bFJHVFlHc09BbVRFWVJqSVIxd3NxdHA2VnI0UllVYWdSamdtUi1fRnM0bUI4cjFmMlhQUkVTcG9QLVo3aTFCWHE1clN2d0pHWW5zRDJtUzQyUmZ6djk5T3FZVnpxSHZHNzhGc29kMnZoTVg0UmMzNmpGNWJpekFzSFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQXJweHFyTG8zRUhvZng0SEN5Y1NuTExFZWlFV0xtTkF5Q1J2a21aR1RZM1ZZTjJjaU9keTlmVXRRZGw1T0FaRG9BWXk4NHNId0FTMU5QM01tOE9HNXphZFVtZzlMeXdKTFRiUVVXMnBtYVlYZHhxdTJJREtZOF9kbjJadHkwSDlYNjdVQ2lURk9EazhMQzBhTkViQUZ3azZCU2RvVGczbC1xd1BoVzRVdElWWkg4eEtWbFJfUkNxZGtpSnlQcTBzNExn?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>17-05-2026 15:30 UTC</t>
+          <t>18-05-2026 01:39 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MS Pharma Announces Strategic Growth Investment from Olayan Financing Company</t>
+          <t>Aurobindo Pharma Ltd. Valuation Shifts Signal Renewed Price Attractiveness</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPT3E2dXZfNXFIQkx3RW5Zekx3QklhRlVJSzBiSmR6X0ZuamdhcXZJbndOOXBURU1aOWI2bXQ5bk5DWHJqZGhndmZ6a0RxTWh6LVFRRnV0UzY2UUt1UU1fODV5OFVJWGVEQXJsakNmazZtRUJGMldfenk2QnlZeEN0dHc0MHFxbkd2UURCd3hrM2EtUDFtY3pZMzE0Q0xhQU5zZmc5V2o3SFhBdG9CeXJxQTN3aWt1STg0RmtmYXUxOTY0ZzVUN2htWWxkbFRaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMlZnQ3AwbWpnbmtZeHVvUWxHb2RObjNkRWJ5RDlaakwtVXBjYTM0OHBzd0tGZjVkREZlUU83Z0VvZkxLWWVnU2IzYzE4R1g5RE96MXRwc3NuX0RwOHl6QmhhanpJakVQcGRtemJocEZ0c2loU0pnY0ZFMEFRQldhd3VXV01ydEI0TUZ3N1hDM0NPNTNXdnFLNzBGLWtlZDRGRElUZW4zMFNDOEM1dGNkamk5OWVCeVVSTTdNTlM4QXdndU5TUmE5d0dubw?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18-05-2026 11:52 UTC</t>
+          <t>18-05-2026 02:31 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1744,158 +1744,574 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alvotech stock (LU2557688560): latest FDA approval progress and biosimilar pipeline in focus</t>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>IndiaWest</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQOGhWOTFuM3JscWQ5WDlSRnhzT3Q2Z3RoSWlJYW1Nc0RvWFRCOEhzZ1FKMHV6emJCcEZPU1Y5MHYwVWFpRjcxeEdfeWt2SFFNS1FpT2c1WVdDdUhUdUZUWEZzLUdydm9QdHBFOTJSb25RTEVCRmo3N1dCZk1pY3Q0UzBSMHJTUUxlSTVIUHVnZGdXS3hNbndDYURZZUpfYkdldEpfcjQtOHMxS3BvWVpwRlBNNTZ0M0wyTDYtVXJ3bkNrUnFyeWdoYmdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNREoxRU5pYko1aW00NVVwSUNBUzFHRlMtSHphUmRNdjg0Uk1YRnR6WnhPdkFKei1rU2d3UnJhbGVyMkZ5ZG1KLVN4anZjb0xjd0R1TGJZTTgwbFNtRVM5a21hY2xHamJkZW8zRm96SjlCTmNCMEl2VFVkQ2k3TFVDaHNoQnZZclBSSlFlREh5WWFTX0d1WVZ1ZnA0YXZoaFAwODVtNGdvVQ?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18-05-2026 11:17 UTC</t>
+          <t>18-05-2026 06:21 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teva reports diagnostic gap in tardive dyskinesia patients</t>
+          <t>Assertio Therapeutics to be acquired by Zydus Worldwide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVHpNOXhfaWFkMlNWcFpqeFRxdENQSzVNNUN4M3hubVVKcWt0U2VCb2RBaU9WWExFWjVSYjhoNldOWU44eVpSd2dRN0pJMzVRM0JZeTg3NHgxRkEyWGpuMmRVTW9Ubm55YWIwdERDSmhsS1dVa3AwMHFZVXdBSTlHU1lyeHhfbnlsaTN2Um40eHk0M2w0b1NXa2dkX3hBRXNodndnMUUxRk5oVXVIU0RvTll2M1VWUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUExURFZfcWpPajBmMlo1QXBTT0QyZUNUNXo2MnpFVHZwT2NlUnlWazVOUjAwMTJaQlZESHUwM0dMSDFxdFl0d2d2cEpWVC1sTVY3QmlzOHhiU3lLUU8xdDYyQzdBM3B2bVhrcVhXaTFhd2tNdlM1RUM1c0Z3ZmZ0U08ySVExcWUwSWlwZVlFRXRLVm5kRFppOVNvaVBYa1lFb2QwTFhybndjOEFSTlE?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18-05-2026 12:30 UTC</t>
+          <t>18-05-2026 14:45 UTC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fitch lifts Teva debt to investment grade as drugmaker shifts to new meds</t>
+          <t>Samsung Medison Leads Women’s Health with Life Cycle Ultrasound Solutions at ISUOG 2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>Spherical Insights</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSkFhc0RpZW8tVnE1ZU5fbWhHNWJCZGJvT1pma1Y3WHkwVzFOMldCTkRSOGNBODJPM2V0NnZGRlNJN3JoT1FhaTR6LUdvYWttcTB5aDV5ZW8yRFJSQ2pBVEdUMUxDR0FFQU5MZGFZMnpBVnZ3WUU3N0ttMHNDbUZ6bVlxeUpZYy1PeWlRejZZckVMalZ3emdOZjYyaUJ3V2dsN25rcFVUc1dXVzNJeERzVmxhUmRmZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPYU4wbktrVFRkOXlNNnQzbk9TWGpaOFc3T1BuRVF0emtieVQ1Z19rQTFoenBEMVBybjhjQXVTTG9hMEJEYWp0RmZBSy0ybEtzRms5dTJ1R1NFVmJzd3JPR0dCV3dXVF9ETlhQX0VsU3dvZGRvbG5QWmdoQ21NZ3k0NkMtRG5ZUVdiVG9nQ0VNbjM2d3Jsc3BKWDZWT25oTkZJXzVJS3dVbFhUTkh1SURYUENYU3VRazNva0xDTFZOQVFfaGpScWc?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18-05-2026 12:30 UTC</t>
+          <t>18-05-2026 13:01 UTC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical stock (US88162G1031): new weight?loss strategy and Q1 results put focus on turna</t>
+          <t>Celltrion’s Vegzelma strengthens lead in Japan bevacizumab biosimilar market</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcDZGYW5MRHFpSkRQc0VOZENZMWktcTFScHZtTDlDWnQ1QnZ1cnZNT0RkT3pyZ1BkNE9YV29QNnRWTldkN2Z6ZEViUDR1RGVGMzlDbjJ1azdxYXJhU0FTT0JudVJmZjg3SUdjTlJON0VlQ2wwN1MtcHluNXhSQkRqWE9wOThpRlRyb1VEeEFhamphYVdUaEQtSk5KQURDY3dZS2MxLXTON25NMlVsVGdDeVdpbVZ3UWJXRlFEMHJoV285eWxoanliNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5DQjAzWWtGVmNmSXB1el_wZ2k2c2t6UzVRY1ZmM0RpTVFQNm9aeEhueDlfQUFWaVBQV2diOXZPV19HM2dUTDloZGJFMUVXbHJ3Q2pJN05LOEZFdXg1cW9xUmV6WHFELXlqUC1UMzdn0gFyQVVfeXFMTjB6QkNWYU9UZElLQUtGMmR4MVdKd2NESWhtOTl2VE4xMFh6MUVCbDlIbkRJRUFLT0FSZ1JvNUJMcnlfRGdlZllxcGw3dHl4dGp4TjFaaWlVWmxPY1A5bUNIWkoyT3ppa01lNFAyTFZPSHZR?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-05-2026 17:06 UTC</t>
+          <t>18-05-2026 04:51 UTC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AstraZeneca, Daiichi Sankyo’s Enhertu Gets New US Approval for Two HER2-Positive Breast Cancer Indications</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Contract Pharma</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPOGNzekRWOUNIWDdEWTRJR1ZQdmVROTZLeE1jblJvbzFKQk92OVp4cl9hVW1XQkQyTWhjVHhacm8xNW41Sy1ENVFDRlJrZmo2NGZhYWNucTAwTjlpUUN1bHBxTUhGdFRIdkhmU1A5eHdNWlg3QUVqcGZRMGsxVldjOFlsM0tKODdpTEQ3Rmp3SmZDUVM0RVlDbkFmSjJ2Y19oa2pZcWNRYk5Mbm82dHdiOHJzNXNlV3IwcWllQi1wX1hyVzRHS1FKZ3pwdTdXUFF4MEdSajN5WHRDTEl4ZHlDaEQ2My0?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18-05-2026 17:09 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AstraZeneca To Pay $155 Million Milestone To Daiichi Sankyo After US Approvals</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPVU16VGpjMnhVNnhmaHNNeGVIWTZtNnJfN0JqTENIYlBfNmNhazNCLWFvanpOcHlRU2YwbnBicDcxZFZwaEd1M0RSdnVKYWRqUTFCWUNlYjA0XzBTcTYtNmMzb0FwRDhPWkl6NzlmQm9iZFB2QWxkZ3RJUUo2NHRaSWNqbjM2VW5Kc043Y2tKSFl0T3BmQjlOQzNLS2VhWVNrWldkSnREVzBWTE4xZThGNmo0d1hvNWVmVWFzeVZ6dE93cW44QmczVk9ENkh5V3g3aldoQkoxQWd6eFRyM3pKZg?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>18-05-2026 06:27 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Intratumoral Cancer Therapies Market is expected to Hit US$</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQM0JWWDVyNFhiZTVVX2d5SjBmdjI5LWtTWXpGMl9tZ3pJdUVZVHRGTzduZUhlMkR6bkN5RTM0YTBrZnlMbHNyRVpMbXZ6bUVBQkFGbksxRWZjWWlSdE91MWM4cGc1TWJPbWs3QVdfNWhHZUh1WDRTX3RfVDZybWQ3OHYteDhCUHRvQUlBN1NQcUV5bVRJd3Z4NWR3?oc=5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>18-05-2026 10:07 UTC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Mochida Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>'Skinny Label' Arguments Spotlight Induced Infringement Risk</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPRndZS3RaSDBlcnduU0o5bVphUzk0M1Buci1lWVR1ajR6VEJocHVaZ2o4ZENoaEtKbFVVekg4NEVHS3NQV1BWR014SFNwaGlwS3M4c2N3ckxIbVdGU3FJOE0yeUJHLUlFZDdJU0kyR1VtUnExNjhYNWRrSEozX3hUM21DTnJqcllBazhJczVGTkFDcFFia0lCV2M3eW9naDAt0gFWQVVfeXFMTzd2cFViMFFfUlE0TVdHSktaS2QwU1QwNl80V1FxY3lTaDljMlVVMS00SnZDTXdabjBiX1ZGNzhETFFUUGhaaXVIVXdYTW9EZXBzQW81NkE?oc=5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18-05-2026 14:12 UTC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): dividend, restructuring and healthcare focus in the sp</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQMFRZc2E5T1REUnp0YnFtU0gwMFdFbHBUSlF2SGY5NXFIa1Z2WFJYc1VtZmN4X3NsbmtncVA1a1NqSUNMczJPT2JHeXRtVGptN1ZEX3ptT0dGQnB5WldVb1JwcjJjdEJrNmllZ01aamJhS3BPNk9SbnpLaEVIRjNxUFZqT3FBVHdhRlVVREktSzEzalI2X2U2cmpOM0lKQ3ZBUmg2UGxJcmVGa0I4MktZYUNiQXl3MUl1Tm5vQWhWQVoxNUU?oc=5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18-05-2026 02:56 UTC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MS Pharma Announces Strategic Growth Investment from Olayan Financing Company</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPT3E2dXZfNXFIQkx3RW5Zekx3QklhRlVJSzBiSmR6X0ZuamdhcXZJbndOOXBURU1aOWI2bXQ5bk5DWHJqZGhndmZ6a0RxTWh6LVFRRnV0UzY2UUt1UU1fODV5OFVJWGVEQXJsakNmazZtRUJGMldfenk2QnlZeEN0dHc0MHFxbkd2UURCd3hrM2EtUDFtY3pZMzE0Q0xhQU5zZmc5V2o3SFhBdG9CeXJxQTN3aWt1STg0RmtmYXUxOTY0ZzVUN2htWWxkbFRaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:52 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>New MS PET scan in MGH-Quantum trial shows robust myelin damage signals</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Stock Titan</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPR29BbE5Rc0p1Sm00MVlveHltUWp5TmFoYlFxN29YME04N3hJRG95b1A0ZUdDX1dLLTJHOTJiY09hR2lDbFdhTkxreGFHMURNUlcwUWc1cjNqZkdCaVBKV1R3eVdVc1lybVZMNlVscF9Tbm5waWVJcXNSSW1CU3hUOHZYRlRINDExWmNqR2g2R1dHUno4a3poUnU3a191SnBsOGtTZk5UMXJNMzcxYUpzQlZSaUZHUFVPUGFNcFBhMA?oc=5</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>18-05-2026 07:00 UTC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): latest FDA approval progress and biosimilar pipeline in focus</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQOGhWOTFuM3JscWQ5WDlSRnhzT3Q2Z3RoSWlJYW1Nc0RvWFRCOEhzZ1FKMHV6emJCcEZPU1Y5MHYwVWFpRjcxeEdfeWt2SFFNS1FpT2c1WVdDdUhUdUZUWEZzLUdydm9QdHBFOTJSb25RTEVCRmo3N1dCZk1pY3Q0UzBSMHJTUUxlSTVIUHVnZGdXS3hNbndDYURZZUpfYkdldEpfcjQtOHMxS3BvWVpwRlBNNTZ0M0wyTDYtVXJ3bkNrUnFyeWdoYmdB?oc=5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:17 UTC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Advanz Pharma</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Addressing the Symptom Burden of Primary Biliary Cholangitis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Medscape Reference</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxON0NIYm8xb001d2VlelhkZXlQOFRaTWh6UlRERFFickZ6U21IbUFTT2FqYU9hQ0htME9ZaTdHUm5acTZFalJFRV9vWFJGMTg5ZWtCU3ViT3g5ekpZbTd1dHU1OVEtcVU5R3FtT3hjZ0xlam1ZOTJDc3VXcUMyME1RYzB1NDJqbUtIVDh6djVSWEJkX0RJbVd3SXpyZGowU3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>18-05-2026 16:13 UTC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Fitch Upgrades Teva to Investment Grade Amid Pivot to Growth Execution</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNcjhRbzBUemJ4aEtNT3FTdmQzWDlPX2lZeFladTd3QS1RamVIMnh2bC1GYU9EbW43QTZuM3dicUUzclVWdzBGWXBoN2pZcnBJZlM5TDZ0c1FHbG0wTEw4Z193SmN1QlhVdXdWNWRrTUVxbFVBY0h4SktqNWRod1RIOWw5MjhRQjBiSjE1MUNaWkVFN1F1d0h3d0RFWUZuMlhHRGJFcHRldkN3Q0wzaGJ6dURORU1VakE5X2lUdUhFUWxTcVJkb2VNaUJwOC1BVUEwNFF5aVlMV0RfUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>18-05-2026 12:30 UTC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Teva reports diagnostic gap in tardive dyskinesia patients</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPVHpNOXhfaWFkMlNWcFpqeFRxdENQSzVNNUN4M3hubVVKcWt0U2VCb2RBaU9WWExFWjVSYjhoNldOWU44eVpSd2dRN0pJMzVRM0JZeTg3NHgxRkEyWGpuMmRVTW9Ubm55YWIwdERDSmhsS1dVa3AwMHFZVXdBSTlHU1lyeHhfbnlsaTN2Um40eHk0M2w0b1NXa2dkX3hBRXNodndnMUUxRk5oVXVIU0RvTll2M1VWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>18-05-2026 12:30 UTC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1PUnRSaWM1eHlQWVpzbG40T2JxZkNkd0c2Ykl4aDY0WkZSUTUxYWhQN2pGMnpJSng4akZNYnZpTkd4dTR5VWtOcl9sNU15VFp6aTNucDcxemhtajhzc250ekRXazVla1FmWWh3QUdsWUJKY0ZZQnpQelU0MmgyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17-05-2026 23:45 UTC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Teva, Granules, Heritage $5.55M Metformin Settlements</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Claim Depot</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9NaGhIMlpjUncxaVdHTnd1RUtxdUxrWkszWk50ZUwyWURYNG1pVnVJQVZ5X1dDZHc4RmlMdnVWeEhsTVI1YkdzS2pLbkwtVXVDSXgyWlF6QTcwdmJCX3dWYlJQRjU1X3ZCNTEyV1VMVl9QcTA?oc=5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>18-05-2026 13:05 UTC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Samsung Bioepis presents real-world Humira biosimilar data at KCR 2026</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>koreabiomed.com</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMickFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZ9IBckFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZw?oc=5</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>18-05-2026 02:58 UTC</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Clinical Trial</t>
         </is>
@@ -1925,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-05-2026 20:19:27</t>
+          <t>18-05-2026 23:53:02</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,59 +464,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yi Chen Maintains Buy on Formycon, Trims Price Target to €36 on Strong EBITDA and Biosimilar Pipeline Momentum</t>
+          <t>Voices of valor: Kisumu women rise through STADA’s support - Radio47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Radio47 - Hapa Ndipo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOZEQyUHB3Y3lXOEJWcU92S2ZVcUwzQmM4VjNac3RDbmFjbGEwcjIyeXVaOUlFNHYyQVRpemU0Um5hMlo0a3doc1Y4eXVxcmFVTHlRNDE3V1BRclZjbENnNUlaQWpkc0d5WHdBSDJ3U1RvVFpQQmRBRGF0cXdIYklXMDZMZUktV1gtbGRjUjkteVFfM0lkcGRKTmFLY3VkUkpBQXV2cTB2MVEyYTRtcW9hcHRtU0tWVzRXWFV5QkFxazRSZEI4blU2bWVnMlQwQmtSRGxrVjFpMUlYdF9mdTJZT01yQjJ3YmljdWsxVFc2UGthQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUpxUmY2bDV1UTlGQjc2WE52T3cyWjUyc3ZUdFNnRV81NndCYTIyd3NtS0VXck1hOC1DRHNNNXRQSXBNa0oxdVE1R0pHQ1ZxTGtpUXppT0s5VGVKLWZrSFp6bTN0SW04YW1tR2ZWRTM3d0thMThkdFpaUnY3LVZ0ejYySmVEVVZ0bFpleUE0b0U5Z0hvcmNTalU0MA?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27-04-2026 11:07 UTC</t>
+          <t>17-05-2026 14:43 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dividend Stocks April 26: Richter Gedeon Yields 4.84% Gains</t>
+          <t>Formycon AG stock (DE000A1EWVY8): biosimilar specialist in focus after FY 2024 figures and pipeline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Meyka</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOQnlWcnhFWU0zb19pYW1mbjZwSVhncmNGZ2p5ZldyMzdXTWphUy02MmpXQmdMYzlWbUE4Y0VUcUwyRW5ucVpMOHppLVpwS28wSmF5LU1NdWpoSWZlZUstdE9iUHQyTjhDWnljbVhXUVBqVU5CSVRCZ1FYZmZ6czVkWklzbzdvTW84WjMzYUN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeVk1MGQta3JabkwyYTg5cXNYX1NTckFNMmkzTkJ1ZnVmY2U4bERwM0tId1hKRWxuM194OEI4MmtPYW9vR0J1V3QtTy1zVHA5dUxoV1p5NkE5a0luRUdFR25BdmM0ZlhBYVlZNnM2XzVhNGhKMkx5OEtjaTNqaTRUOXlzVExuVGNEM21GR29EcS1YT3hqOHZFQ1lYVk4zZTV3d3hkd1JfVndiWkhrZGRFNW5HblpXSW9CWmRjN05XOExqZ2NaVE1TNA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26-04-2026 21:00 UTC</t>
+          <t>17-05-2026 23:14 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,22 +533,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim India, NIPER Hajipur sign MoU for research and education collaboration</t>
+          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNNzBsZG1aYnBjSUFmaU9NeGRVaWVhUzFBV0J4Y0dsT0ZBb0oxZW9pV08wUEZ0UGRkZFNmMGNmMlVDSXpueTJMbE4wZWt1RzVZTDVXN1R0RW9meDdyRktuVGEwcXUwSXF3Y1FWOGhQQzAzOWI1S1NRSkp3UGVhS3o4WUthVXBDVXI0QUpJeVpqc0taNW03MW1KaDcwQXZMeXJpRm51WkgtS2NxZ2pONnFFcEpPZzRhWFFvYUVsYtIBwgFBVV95cUxNYXpSRmZmWFdxSU1DSTlBOUF0ME0yR2JJSUNTem8tZVhLazV6c2RuaEl0ZXJNSXhTQjhyUllpOE5yWkNNX3VYVnlVbWRtSk9ueW54X1UxUHhzSEh6N3RmVFluMW01WXFWZHZHT0hiZDJZV2hIajBBWTFyS0p5LWU3QVBmVUhYRlU4MGlLNzczeTVwdmRmbnVxNHU3bXY3eFNiQ1hPWjFKekw4TkZBV2FRREhLa3VweDQzVmZSbnlqdWV3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEx2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacGpsZnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27-04-2026 04:30 UTC</t>
+          <t>17-05-2026 05:00 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -565,22 +565,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barangay-based kidney health screening launched</t>
+          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philstar.com</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRG90X3EwZTZDbS10Q3RaUWd3NWRKc0t1NmZfR1RUbHBtNHVFb0ROUTZFUTRITGVNcGpxYkFPMHJwT2w1VXQzbUdxd3BlX1p2SEswQnNXM2RsN250bTRxS3ZaanVlNXhUZ2pmREhqRE9pMGlKQnNSMXJlNkhEeUNCMnpwMldwcUN0cG9ZVkhyWTY1Q3FCWThZSEt4WHpkZ0s5N1JpQmJWZklXd9IBqgFBVV95cUxQRG90X3EwZTZDbS10Q3RaUWd3NWRKc0t1NmZfR1RUbHBtNHVFb0ROUTZFUTRITGVNcGpxYkFPMHJwT2w1VXQzbUdxd3BlX1p2SEswQnNXM2RsN250bTRxS3ZaanVlNXhUZ2pmREhqRE9pMGlKQnNSMXJlNkhEeUNCMnpwMldwcUN0cG9ZVkhyWTY1Q3FCWThZSEt4WHpkZ0s5N1JpQmJWZklXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dk5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27-04-2026 02:30 UTC</t>
+          <t>17-05-2026 06:01 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -592,27 +592,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>World Cat Vaccine - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Johnson &amp; Johnson Launches 'Gut Tunnel' Experience in Singapore to Highlight the Importance of Endoscopic Remission in IBD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>Thailand Business News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPaUdJY1h6LXUyWDBZSm9JNHVSRXlOaDNuOHNEblEtdFgzVXphNFF4WWFkRExZZ1hyUzBOMm1xRkw3NzFjT09IUkhGM1Zmd3puaVEtaEZQekxPZmN6UWZxZ2w5QkhpYVhIVEpRTGJBbW1OZlFBRUk1b1lrWUtCZXZISmpXWVdNU01RdHJGM0xwdkVYbWh5MnY3MUs2RXB5SWtQR0tJSnZhem80SDh0My1KQnVsblVkd1lKTVc4bDFlUUI5UWdWSzlmS3JYQl9PY0RjV0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOQTNQTDhHVC1HN2VUVm9RSzZNODRMQmRaRHlhNVl3d0xDMEFETi10UFpZdm9WclR2akUxcW1ZSzBFa0JITF95UEs0ZVlpeEwzUXlCX1pNdVh5THZXMHZrVFRieHdfdm5kRjlPNjZkQVljSDcwQnk5UnhjMWkzZFhESnY1amRnaWxQbVZRQ0YwUWJ1LVdBdm9OQkE0dzZFd21sVG1CR013X1o0VTJzeklpOVlhNkdBdVc3eGZwSTJxdUJSS2tsTW53emo4NFViLUE3aGdMcmswUF9rQmRWLVBVTUJJcG1fcTJXemo5YWg5bHJNT052aWpzXw?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26-04-2026 22:31 UTC</t>
+          <t>18-05-2026 03:38 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,64 +624,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Leading Companies Enhancing Their Presence in the Veterinary Clinical Trials Market</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUzNCMVhlaVBDWmlJUkR1a2lvOXF0alpUWVAtcmRncHkycUNxZF9MQ1pUSnFsc3V5TzZBeUlrZ2w5UVBscWRHYVNacGhlNFhRQ2ZhNTl4SGwyb09Ed3dSdGwwNk1ZS2o0aDhiMHc4RDhhdkhLekNqbU5aZFJxZjB4M0FpV29tWG85QzY5eHJLTlJ1Ym5HdzdKNzQyV28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27-04-2026 05:15 UTC</t>
+          <t>18-05-2026 00:25 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hikma Advances $250m Buyback, Shrinks Share Count Further</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQdXdDLXFBMjZXeHRnWnN5blNmUnpLZFJRT0FOS252djJ4U0l1X3BQaDZVVm9jVm9GS0RERUFLbGlVcDhRcVU4Q00zaGhvVVJFcmNtbk0tLWkwb2ZEenQ1aExYSnJ1RXBBb3BVTGNadmZEbzJqZlZ0WkJadGhlakhkcndVQjdmbi0tckRiMlI2VW5Sb0xONUZSdEM2VWZOVm9Ga2tFc2pnZmM5eGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27-04-2026 11:00 UTC</t>
+          <t>17-05-2026 04:56 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -693,22 +693,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comerica Bank Has $50.76 Million Stake in Amgen Inc. $AMGN</t>
+          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MarketBeat</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQblo0TTZYS1_wd3hycXYyVFRaZmRpbGpaZzI3Z3U5MHk5VzF3MndHVWxUQ3FRX2JjbDNzenFGalpxRktEc1k2am9mQkdJZ21qMmdkZHVkd2E1TktuUjdaSy1CdTZUeVF6QlF6ZGpYaEFNSlZzVmNxNzVEbUhzTklGYlZ5ZDkxTzk4bWV0bDVRWVJjaFI1VUFzRjcyQlQ5Y3FNdGVVQ1J1Tl_yMGgxaGhoREVwV0g4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0SFlfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27-04-2026 09:03 UTC</t>
+          <t>18-05-2026 02:16 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -720,187 +720,187 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): Is its obesity drug pipeline strong enough to unlock new upside?</t>
+          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRXNaYy0zQjFLZ1F1TG1nN2FEd2FqTVJIemdaQmFLc1Nfb2o1ZHJVWTdCelJZVjQwQ3NWclZfVXlqSDNxNzl4UE5zWU5aQ0pWcUtrQ3FFZm5uWmFqWXN2UGJwLXY3Wk9BamNRaFVJVGxpbmlCbDJyRTE3N3QtSnJDc1pacU4tXzRDVnFyNjFwNGg2LXlRMnFqSU9kRkRGZVphVkt5akE4d0VBTjFWNXM3cms4eXJCR2txakhqWVl6YTM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmgxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26-04-2026 15:40 UTC</t>
+          <t>18-05-2026 01:17 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why Amgen Inc. (AMGN) is One of the Best Stem Cell Therapy Stocks to Buy</t>
+          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Insider Monkey</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPOTNtdl90VUJlMnJGY1BsNjdiNzBDQnpVaWlUczFMZm1OZEh5c0kyMUgyOFdfYW8yM3o4Sl9yRlZ0bFZaVmpJR0pZd25FWVBzWDZSbENsakgwNjZORnhkMVlCeUFMQzN0QzJHSFJ3U05HcGJjZEF2MnhnTm9aTWlCUVBGXzE1cngxTGpJTy1vaWtWR2FjbUZZbHBPT3IxU0pOX3RZNHItRzlYdDh5cXhhcTBCRdIBuwFBVV95cUxNQUpYc3BQQkp5SGtncTNNZUpMY0NnRm1mUFg5QTI0ZjFvcWJMSklLQTByQ2tUdGZtSlpUVWphX2dRa1FfR3lXdWxRSEtHdFlmc3pfRTZsNFl4UUlfMjdIdVRnSHRsRHZsalxuTnZnNTNtcW9TZDBRMHlicDBHNUpUSXd2MzQ5aHFSU09JLU9acXBoeXlvNzRtT0FXcW5uQ1d2VUhMZjdQTEwxZzdFVU83cmlRdjUwNFZ0T2Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6bTRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27-04-2026 06:00 UTC</t>
+          <t>17-05-2026 10:24 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amneal Pharmaceuticals To Acquire Kashiv BioSciences To Build Fully Integrated Global Biosimilars Platform</t>
+          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pulse 2.0</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPanNiVDVpR2oxRjU5QmNuRFgyVGRTeDJ0OEdOd0NkdmtlVFY5dGpUMFlBOFZ2b2JnQm80OWxmUWFhcV8wenFEa1o4eUpmZGJZSE9XdDZhZy1PYS1IQnRWYUNXTFZ0Zmdmc0VfT0QwZ1pmU2xmVkZnUE1KT1BYZGxJZVdIS0lYN2hEWk9FY1V0UnVFTWR3aTd5SlBZQzBoYlhaNWVZaS1laWQ3WlhRVWpjb2RNa0hZdC1KZU00UXhZdlB2V2VW0gHKAUFVX3lxTE1haEkzVnNSS0hQUjVHc0NkeHlqRGx5c0VCTGJtblVNZGx2UFRZR1djRS1lWUs4NzVDNGdkTjBaLXNjaHJmLVFKQThsQk9iLUJiNFRIZ042X0d0UlAwdlhZQlFiaGNTelREV0VIWmFtUllfaElHQ0VoejJaVzNOcUg4ZHU2WkNwMzZ3cE5WUVZ3bzlJcTNOblktdzRlQUljRVk5UTRXZllsVHh6S1lyZkdtOTRtbGJlS2VCM0o3ZHROVWNZNXZvVXMxOVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQNC1CM0pHSXd1MGd2MUJDZnIxWHVsY0JRLUxjZGEzYlNnVGN2NE04Sjk2MUdzZG5mQkpjX1lwb0tBalFnYmF3RjlsQ3RWZDlwSGppcGxlMFpUYTZHb1ZLNTl4VFFuaDZZT0tsSHd3ZWZtV084cmhITDl0aERKM1lmMC1BUDVFTHF3alV1ek1ORll1NVcybDJxRjZEc3BFdXBSX2JSekltRnVCaGJWUVljdUx6cHkzOUZPX1FMUHh2b3phVGVM?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27-04-2026 02:01 UTC</t>
+          <t>18-05-2026 01:54 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sun Pharma Announces $11.75 Bn All-Cash Acquisition of Organon</t>
+          <t>The week in pharma: action, reaction and insight – week to May 15, 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQRGVaOWxyTTRwMjJNOW8tUDEwM0Q1M2xpa3FLc3puVDU2Y1EzQzlpbjNTZGNkSGNXdWZJMWhUc2FtNE5VazJCMV9RcGxURmlEWEUteTkxYno3NVo0WVZxdzYzY1FIM3dHaUFKTlR3cjBfaks5WkJVdUQ3bE1hTi1FajJlaFFkWi1KMFhhOW8tM2lBTUI1TWFLYU9CWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOb04xYmh1V0VBX05OZ01haEl5NkJpNG1QbXBjckNxeUozeWZ4TEs4S0QzN3doUTNPQU9qWE1fNU1xUlVJYUxLNXFXRHpDb0Y2cjFUWEJDblF3Si1ReHJLVFlhWjhkTS0yOW5Ob3BTUnZVcDJuMnducW9hU3dzbUFTZGc1WmxDSGIwd2NVNEw1WXZZeUxPb0dlTnY0ZGJ4dW9uNmEzVzVCX0h1U3NoRVE?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>27-04-2026 07:47 UTC</t>
+          <t>17-05-2026 15:19 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amneal Kashiv Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quadria Capital-Led Group Seeks Majority Control of Samarth Lifesciences at INR 4,500 Cr</t>
+          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOeThtemtGYVdFQTZsZFg3aXdBdTR1YU1WQ3o3ZUQ2MDdQRU4zQUFibk5LdFpGbTFCUE1DWHo0MERGMzNiUTVtMkdmMUgzLVBuY1Z2WTY3OTNzSlNRSkozVlEwSGp1bUpfcW9UbWpUQWlFSmNnQm9oUm42TWo4YmgwVHdtaEtJQ1ZRbVJPa1ZoS0VubkZNdWZHb2hVckV0LWNxaUdKb3RJYVh0a2hKMnFieXlBZmhqR010RFpKd3Raaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27-04-2026 07:54 UTC</t>
+          <t>17-05-2026 18:16 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sun Pharma to Acquire US-Listed Organon in $12 Billion Deal</t>
+          <t>Seagen Inc (Acquired) stock (US8166361055): what remains after the Pfizer takeover</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQbTc1cDhOQWRUZExpZW5HU3VrR2lQWTZBZml5SmppZE4zemFKOWU1Q05tOHJRQS1Kd010QXRWUjE0cGh1TnNZNTJaSmxlTlhLSGxtcDJrdXI3aWJFUFZUMjdnaVVYclRIZGNadUhTaU8wOVlSdUtrQVg3NjI4WV9xMWFkNm1qZTRJdlpYdTlscXhUZnVsNjZtWDN5eDQxZWpObDAwOWJPOENORTFaZHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVmFNZlotaVg4Y2xEMG5iYUVFMHVRdE1ZT3lBblphdC1uaVMyekd2aWJEQzFrdjhsTm9mOS1GTGhhU2FfbjRaRWtaMGNKYjFHWE4xSTVvejF2empEdjdZUS1MLWtVcGg2WXcxUmh5YkkyY3E4eV9yRlFqS1JESWdVOFdob3RXenJHQ2I3SDBLN2RaVFE5TXpwYmhQMVE3WXVRYUtsb0NZYm5nYlI4ZlZiYVRBVXhZVXVZRDhVN1JzaWFXMzBlOGc?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27-04-2026 10:16 UTC</t>
+          <t>17-05-2026 14:59 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -912,32 +912,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sun-Organon buyout shows Indian Pharma's big hunger for overseas M&amp;As — Here's a list of other major deals</t>
+          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOSVdvWWxrYnlQeVlUQVRwTnBEajhjZ3ExX044ZE5VMVFiTHphZEFJWS1KRlJ5anFoQmdKNUEwUzVKOW53VDRnSHN1d2VNbnpILVdxdmtIVVFMN2lJbnhNRm9tUDJjS0FCcnB4R2hSOXFDUkFXUnNTN2VITXYtN2pvcGtwTFRNcUdPNTdTMzRDTmtucnJxMThTMWx0QVd4NXdISWw2UzZsNjlZaVF0bU52Q0x3NzJiZ3RkOElDZ1k4X3YzREhDQ1F0S2p0Z0tFQzhaczg2N3Nqc3NEakk4LUhFeWVRd2V6OG1fcDJXVHJlNmdwTWZkZTBmU9IB-AFBVV95cUxOSVdvWWxrYnlQeVlUQVRwTnBEajhjZ3ExX044ZE5VMVFiTHphZEFJWS1KRlJ5anFoQmdKNUEwUzVKOW53VDRnSHN1d2VNbnpILVdxdmtIVVFMN2lJbnhNRm9tUDJjS0FCcnB4R2hSOXFDUkFXUnNTN2VITXYtN2pvcGtwTFRNcUdPNTdTMzRDTmtucnJxMThTMWx0QVd4NXdISWw2UzZsNjlZaVF0bU52Q0x3NzJiZ3RkOElDZ1k4X3YzREhDQ1F0S2p0Z0tFQzhaczg2N3Nqc3NEakk4LUhFeWVRd2V6OG1fcDJXVHJlNmdwTWZkZTBmUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1fQ29hVzRoV1pxaXRYZFc5V0FTVG5KYTAyNFRwN0xucWxGNlpyVGJmTS0ta3FJYm5VNHFDWUh3YmMzY2oza0dnby1IQTRLUGkyS2hCOEVTbWh6WUI5MnZ1NTE0ZVVMdi1OQ21FQVdVU1JQYkxaY1JLLWtwTWRJUQ?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27-04-2026 05:27 UTC</t>
+          <t>17-05-2026 13:08 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Armata Pharmaceuticals adds Pfizer executive to board</t>
+          <t>How Pfizer Comirnaty Works and Where It Fits Today</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNcGZWZzZtRkZmNlBOWW5IaWdNN21XV1pkdG1yb0twdkNMZG9UYXVRdlpXY05EVFN6YXhnRkQ4QXVrTXdERGJxT0thZi1RUGg1eGlqRFF6S1VLMGkxTmtUMFpIUTBGN3NKZXpSOGRqVmZHenJSRFFUaWxVZW8xWWl0OUIyUmg5UEJ4ZlM4Ul9keWVGVlJHRWw5UDNVc1B0RkRRVU4tblFJM3AtREhQcnc0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQeURmdEw0S1RsZXA2ZHlJYXJ0bnI2aEdwSnRpV21OLU9VQk9feGFDYTZKUHRyNHIxQ2hubFZRMHR5VE9BVzY2WnNWNDVqdHVzLV9yNEhCV19qWGFqdXhySUQ5UC1nMWtGNlRIdFMtREs2RkpTQ0trZDktemRiaWVCbG5XZnJHbHktcVVEQjh5UVJycG5sVm1vYklyeWtuWExLUHVHS0U1QldIZTVtaWc?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27-04-2026 11:25 UTC</t>
+          <t>17-05-2026 12:46 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,27 +976,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer and 3 Other Stocks in Focus After Goldman Sachs and Others Buy and Sell Stakes</t>
+          <t>Biogen Pharmachem Industries Q4 FY26: Mounting Losses Signal Deepening Operational Crisis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trade Brains</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPeWR1TXlJeXNDTkRqaFZwTzZQZ3B0akh4WjRlcEExa1JvNnM1TG9GU2NYNDd5NHhFNEZ1REtpS0hoRlkweUsyNjdZZmdKYzY4bkJhQThUb2pqRnp3R2xIT25CbnBZdnJ5V3Z6TnlaZGRtcDFuREtpRkVOWTRhNTNLSklZSmNqTE5wNFRqSEJzb0hqTDZ4NVdWSGcyOUU1bDJfak85N3NQY2tuZFk5MkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNR3dHZjdXZGdtX2lKVFFySTFpZWVKNUVFUVBIMjhmcEJpU1Vra0Q2SUhmYXl6Mm90SHFkeC1EX092bl9US3VFc2xmQjhQUVA3WnZFVnQtNE8wUWlOaU92cUVnM1VIc0g0X2UyZlZjaENpYWZEbHJhdk5yaDJ2T2Yzd1dCWG85SnhoRkIwNm5wbjcwbzBqMm5iRmxQWnlnWHBRU1Z0V3ExaGxRMnkwSUNrajh4dmREYVhtWDRvbldPUXVPWDNldzNOS0Izc0VHa3ZiSHNsSkFuMFpzZHBaMGc?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27-04-2026 06:10 UTC</t>
+          <t>17-05-2026 23:54 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,251 +1008,251 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pfizer announces new candidate for lyme disease vaccine after phase III trial success</t>
+          <t>Goldman Sachs sets new Biogen stock price target on bold Alzheimer’s bet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The Tartan</t>
+          <t>thestreet.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQczFEdklFUEFjNkhsVzNtZ21fckVVeTRNZzdWY3VRb0N6RlFwaDZwbjBRekl0TUI5cWZldDZfUzNHQ3F0R0d2SkpZUUszLU9hMDNKel9nemxqc2FXLXZlQVpQWmllTDZ2U0dOZUNEWmxKT1MyMkFzaFdjaTRiaXVYVDN3MzdjZnVidE5FRVpFcXRZQzAzaDBwYURpNGpTajBVUDBxSTVPNk1NejhJZ1E5VmV3UVJMMUc5eUpPRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOZk55NnRjdjBjS0xtaDFKajBzVXBUdURmNF8wdWFNQjdvV216RVdENmVzZXVSYlZwc1Bxd1NNVEFlRzlJRk1ZZ01wbXo5dndnNFZGemJKcUs5VUx4c0VVWTJaTEZrYTI0VHZGUkJBM3I5RlE4Tl8xdkU0UlM2MWUtd05Qb21iNUNVakswZ2JmNFBRR2pPOGJTSkxmQUhqMDl2a3I1Mm1JOVhwQU0?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27-04-2026 12:00 UTC</t>
+          <t>17-05-2026 17:33 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jamjoom Pharma signs agreement to acquire pharmaceutical manufacturing facility in Saudi Arabia from Pfizer</t>
+          <t>Biogen Inc stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ZAWYA</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxPLVJwVjMxVDRPcUVPUjNhRHByeVpWNTRMeUNGUmVWLUJaU2dJZHl0RGk3M3lpWEp5azd2VUtDa3o0MkdJa0p2d0JBZ20ydmR5MTcxRkwyT1hCMDBKaUxXT3RmaWtILXh6aWtXbmhQME9LYUFIalJoUUtuaERzemZ0WXEtSEZIVnFyUnRTVkNIWVVPd0haVU91XzBHbW9PWXBGdjNRMjl4Y1doQTI4aEVzZXN1akl4X1dJYl90TS00MEYzeFl5RXZuOElzLTYyVTZrVXFqRGpINEl3eVNYd0pRRDdUSlZpZTdkM2JURlRRUTZTT09sWXVmeWlpQ1M0V00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPMkhFQ2lTYVZKUzVwcTR2NjNiaWFWdjZPNnkzNklYUy1uZi1qSHk4aldpRmNoZEJZcFBpVEdDLUp1ckFjZTg3WmFlRWh2SEFXc1BzU0tQRTdlWkRaOWstODhqTVNBUDAtTUY0R3hSV3hSMTJqOEVENU0wZWNsZjhBQ1ZzdERyc0VSYkhyWUFDZEpaWERwTFk2TkxZSjdsWjljYWJzZXBWb2RybVYwbHhMMUh0MVZhcV94V0swM3A5Nl8yTUxnb2RZ?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27-04-2026 09:46 UTC</t>
+          <t>17-05-2026 20:09 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BMS–Pfizer expands Eliquis access through Cost Plus Drug setting $345 monthly price</t>
+          <t>Biogen’s Diranersen Moves To Late-Stage Alzheimer’s Trials And Investor Focus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Sahm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNOWtXVjRRTElleXg0TVFoZkd4N2I4d2VJOFhwWUpJQXJObHZPOHVYMDBJRFpObVktbjlXTktOdDlKdGRseU0xdExZeERjSEFYRDl5dGh4ZWxHR1VyX1M5ZnozNzhzX2c0ZFJySmhLMFR6RVl6ZWRUXzU5SnZTMnNkYVRaVmFoNDRjTC1KWWl6UUxBMWdudVNGM25JVlVxSXpFTjJFQ1UxZjVER1dTdUoyMjVTOW01cnJVQWUyVW9DQmNKQ1VKd2RNYmMyYzBWQdIB1AFBVV95cUxOUGZ6elhaUkJRWURSclVKRHVBOVVONFV1WDJRQURoWVRpV1YwVnB4MnY0ZWlFeEUxN3NCQWxWNkNnMEJsYnRzcndueE1wajNxbTMwS2FoN2NpbHc2aWVBSUE1ZDZsWGpULUo1d1F5MlY2VzZYOFdSeUFXQk9BSXlFenVqWnBUN2k3V01WRGtpbFpibjJBR0ZQU2VpaG9YaEJZbjFua3ZTQTItQkZ2LUtuOHRaVFBpT25tZ1ZOTlNXWU9OUmJQaHdFa3NicUgySEVqS2xJVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPaWtsNE5TYW1lVlp1cjI4dzJWVV9PMGtGdnFtdnBFcWkyNjhXbFF6enkwcUlibUVQRjZZSlUyWlJFRW5DN0dmaHZ1SWxrc1FaY0cwbDZwZFhtYUVWZDN0Q0F3WHF0WUZyMHRDNldnWUE5Y2pPVVhwTC1sTFc3Wmpxa0xHYlVMUmRBWDZNZ0pENmJvR3VtMkVEVTFpMlFnSlZQVVp0dnpVWmp4T2J3NG5HWjFGX25hMTlmY3VWdzkyUWF0dUQ3THc?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27-04-2026 05:51 UTC</t>
+          <t>17-05-2026 06:27 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDA approves updated COVID vaccines with restrictions - ABC News</t>
+          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPWk9Tc0cwV2tCOUF4R1pMVjdYU2xzQnZnY0d1dGVpY05LU1pVS2pHMWQzNzNSQjJvVzdjNEZ4VVZEeHZ1aU41cnloR2luZXlXdF9oTW9IV1ZZRjBaUmJJNWtwYl_wYWVtQ2t4OEdwYldRaHlaRkdnTnpDN3NPNFlqd1NFS2hwSXJBR2tsSVR4eXhGNmVsbHM4X3FRWlZ4YzlsWUZVctIBqgFBVV95cUxNZXZXeXBOSHNkbXZDbmdtZ2ZWdVJTU0RKMURiQW1pYXk4SnZsMmg5eWltbWgyQWhPMnphYXpWMXZwR0JGRnJQSXRQMDU1SmpzNEFGUHRIaG9QQjhWdjB2eDJhaGVCcVQ1VlBUU1l0anF1NGtJY2JNNF9iZ0gwdTNPeEZLQXhLRldYd1dVQWtoNm5OaWVnY0JqX0tEZjhzVHdld3JhRjhfcUttUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26-04-2026 23:28 UTC</t>
+          <t>17-05-2026 23:42 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pfizer AGM: Shareholders Reject Independent Chair Proposal as Bourla Touts 2025 Gains and Pipeline</t>
+          <t>Biosimilars could surpass generics in US mkt by early 2030s: Dr Reddy's CEO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQYkxtZFVmUi1KZ085aXBkTS0tS0FwUjFiMk5hMDFQZW42M3lJWnM1MUhNa2tfUW9Vbi1BNE5TRWVJQXduSDZhSHhISVFlZEZIeWQ1WXhBMC0wUUtNbXd3M0lQd25kbEtvcHFWODg2Y3RZQmQwM2dpdU9kVURIaGRGNUpkcFNBbV81QUdxVDRqb2tnVU56T1FMMnJOZnY2OU9KYjJOM0FqYVNJMWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQZ2stSVlrS1Q0QVJHY3ZWV25Ob1FkOUM1TEw2OUZZc1g4Z0JwRUZTdGQ1djRXUFUwbThPSUp4NGV4dDdRMXVOdmNBXzZFZVBrZklkZ3BDblJDcnYzTzg4T3ZKbzNFV3JFRHozbm5vdEV5MWtOTzBnTzl2S2RvV2Zld182eFlqV1pBZ2VUNDN0WUZEaHVPNUppTml6ejVHaWZETnlReTcxaFVURDVQeDlzYWl4UWt1MDZ1YVd1RVhiSUR2UXhQeVNBY3lEUVROc3JHQVc1anZJVmpQN2NjbFHSAeMBQVVfeXFMT3Utd2U1RWg3NWZENW0ycG0wNmh0NzJ4aDNWUlU0aHJ4N2FPYlJBb1RIYkdnMHpDeHhZc05CcS1QYXAzaFZvUWhHa1JOMmVuWS1sSVZiTktUWTdvNUV1SGVrVVpIT1FQNGVHY2IzTTMtT2hnZGxRRGFqQTJicm1uYU9Ka2hDR3FXUFhJUk5GZ1ZWM0tMdHloeV93cEpzaG5KLVI5Rnh6MTY4N3NDY2VhM2JyenlqdEtSZFpNWXpTZ0NMeHlNUTBzR2VJU3owTzlUemswRHRRcjJka0ZMWEh2ZFEyN0E?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27-04-2026 05:04 UTC</t>
+          <t>17-05-2026 18:19 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Comparing the Pfizer and Moderna COVID-19 vaccines - ABC News</t>
+          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ABC News - Breaking News, Latest News and Videos</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZ3lzUU00S210NFh1bXRRb0hiMVFmOTJpOHpiRVAwMGl3b3JOajE4X0NXQ0VRZHVndUJ5dG5vS0RwbFlEbE9ScXdlaTZRd09XRFZJT3BLQlJ2YUltZFZURDZpU3NPS29VSlZNdHZRQWRwWDdwUzlqVW1fQXJBdGU3RDZNWUNZZ3lIZmgyU2xnbkvSAZYBQVVfeXFMTUoxak5ZejlTRWdiaEFkcnlxQUk0Yy1wWnJrbk5ac0pDWTR3MFBKSEoyQXBmQThjMHFVc1BHVklESk5wRlk0bmZLZUN2NUpfczNNQ3NGbHRwUjI0TVFHUDkzUU1mMVFyQkRTQlpmMGk4VGw3eXdWNHpWV19NUEFfYjNUUVM2dXBZZm5fdXZ1SGJWSjNKTU5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1ZRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26-04-2026 22:25 UTC</t>
+          <t>17-05-2026 09:43 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A Monthly Weight Loss Shot? Why Pfizer Could Topple Lilly's and Novo's GLP-1 Duopoly</t>
+          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5FNGVjc1hpVll0RE5HMno3R2NENERtOU1IeHJ0by16MXYxVlVRN3lTTE9ia3lRbTlZNWdCenAtZEZsdkkzZjVTSnR2V3Bra010WVFQODhCYnhKazIyejR5RVZEOENGSTFhWm9idWMzSlNzeTFZWTdqTDlmdzc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27-04-2026 01:01 UTC</t>
+          <t>17-05-2026 21:21 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MHRA authorises Biogen’s higher-dose Spinraza for SMA treatment</t>
+          <t>Dr. Reddy's (RDY) Introduces Generic Semaglutide Injection in Ca</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PMLiVE</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQN096NVdpV29FMXFXaVFZMjNPOVNSZzBkY2phU2QzYm8xVDlsVngxbnpNenlmMTJ1NWR2Y091R3JURm1CallFb3pxd295N29rQUVIbDQ5bHZ6UGgtZkowbzZvcGhhYnlaWjNvX0lYdDhaUV9SbWdob3BKSzJVZ3AyeGg1SUY1RThhTGo4bWw4RmVDVGsxUmdxclVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQeDUyMkNiOE81S2cycDUwUlBvTXVCeEVUTkVxWHd4MUNGSmhnaEd4UGNqaEhOVjZYd2JDcnBVVFFFR0tmOWV3YzlFcE5Ic1g1Zi1SaVNTWndLNXg0UzNNVFllMWcyUkxzR2oxRk1mWHV3dEhPV1RtZnlIWmdocVZyNUVxamEwT3B6UTF0ZWswaHFadkdaMlk2OElkd2NHZGtuUXJ1MlVxekt3bEFrSkU2TGttYkhHbW5UVlMwZnVRYnBoUXRhYXFWTG9JaHFtNjBwdXFTWWUtZDhWQTg?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27-04-2026 09:40 UTC</t>
+          <t>17-05-2026 18:45 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1264,59 +1264,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biogen Inc. (BIIB) Gets Upgraded by UBS on Upcoming Pipeline Catalysts</t>
+          <t>Should you buy Biocon shares now? Key takeaways from Q4 FY26 results</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Insider Monkey</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPbF9jUzg3RER2N3ZkV3RfNEZocEVpUzJ5Q3o2dHVjcHlvc3h1d2I5TjJnTWxRY2xTaXc3NEM1X21YaFN3SXl5eGtVV1VfSVkzMDk3RUhHOWltMUUxRnFLZWhiX0oxejVVdjBDUTdPY2Y3bU4wVmFVM2p1RXpUcnJndjZiMWI1alE1VGR1VjF6QS1VZzhZN1ZuQjJiWXZEdTRrb2ZkRE5TOGRPMkNOMzQ0eU5Bc0JkM1dR0gG4AUFVX3lxTE9sX2NTODdERHY3dmRXdF80RmhwRWlTMnlDejZ0dWNweW9zeHV3YjlOMmdNbFFjbFNpdzc0QzVfbVhoU3dJeXl4a1VXVV9JWTMwOTdFSEc5aW0xRTFGcUtlaGJfSjF6NVV2MENRN09jZjdtTjBWYVUzanVFelRycmd2NmIxYjVqUTVUZHVWMXpBLVVnOFk3Vm5CMmJZdkR1NGtvZmRETlM4ZE8yQ04zNDR5TkFzQmQzV1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWEFZSE5GbjhLc0luN19jU2tJTVU3bDF0VWdSQTM0MElBUUpFcjdUcWtsbzhBUHotOFNlUzdXXzBjYzFKaVc3MDItQ1dpY2tBbHhmcE1PWmR5NmdkSXFzcGxEX1lWMjhPOFhoWFJHRnpDUmNLa05IZ3BzWkNuaXl2ZmhVX250UXI4Mk5lNkJYVWZZNC1YeGdSOFR0ZGd5OTlWT0htb1lQTmxaS2VRWUhCcmN2QUdMQjdqTU1YMFJoUEU?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27-04-2026 06:16 UTC</t>
+          <t>18-05-2026 01:36 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sun Pharma, Dr Reddy's Labs, Onesource: Nifty Pharma rallies 3%; details</t>
+          <t>Board of Biocon recommends final dividend</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Dailyhunt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNQzNvcHpPZm1Fei1RYllNRzR3WnRMOV93a0ZTd0Vvb1VnSVZ2S3l2QmNtUXFWajZQNElIVUdCQUVCZFlNRUpGVDlnSWc3SHdwSDlHXzJmcEhEMWJydlc5ZHp5UjFOdWFKWFVkNHVXYV9zSVJ1ZmxGOHM4SHF2bldEWXQwa0dDUm1iWU01RmJOVHU5MXpqbnVVOHZUQ3NuX2Zydkx6dklJT0lvWFlRQ3lvUUZFVWhua2g5cjJGQUEyQVRlX3l5Ujd5b2stZE16OWhKZ1p6cHNlaTdWdDjSAeABQVVfeXFMTWJrZ0IwS25yWWZzMTFWMVpoLXNYeE1mMmVuN25iT0Y1Q3JVOEJkZVhpcURaTnpPaHJoV05YeHhTb2dFYjZlMHZfZndtWkQ4amZSN1FLRFp3QUNXTlU5aWlpa3VyVHBSZjQ5NUFaTWtuckM0MFBIeUtESm53Qk9rYjRaejBwZFR3QTJucmJnOEt6SGxZZDRQS094RTNrcTJYS25UNTlBRkotT1F0NVhoQ2hGOWdtbTlLc1lQeUE0NXpZZXVQTllVUWl5RzA4cWdnUHlFT09OV1dDNkFFdHh1RGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQXJweHFyTG8zRUhvZng0SEN5Y1NuTExFZWlFV0xtTkF5Q1J2a21aR1RZM1ZZTjJjaU9keTlmVXRRZGw1T0FaRG9BWXk4NHNId0FTMU5QM01tOE9HNXphZFVtZzlMeXdKTFRiUVVXMnBtYVlYZHhxdTJJREtZOF9kbjJadHkwSDlYNjdVQ2lURk9EazhMQzBhTkViQUZ3azZCU2RvVGczbC1xd1BoVzRVdElWWkg4eEtWbEJfUkNxZGtpSnlQcTBzNExn?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>27-04-2026 05:39 UTC</t>
+          <t>18-05-2026 01:39 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1328,32 +1328,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brazil rejects Dr Reddy's, Cipla GLP-1 generics on technical grounds</t>
+          <t>Aurobindo Pharma Sees Sharp Open Interest Surge Signalling Bullish Market Positioning</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNNlhzb2U3eGJUNFpsTkFKcjdBUEJLekxYTVVmNHd2SkVUQ0VGdW1xbGxIaXdNRGR3V3Y1ZFhQbl9qcWlRdWpuR3BhMk9wcUN4RllIaDFDd3ZHUHpkNmJWMXNuR1JvbVNic25qSTRpdFoxaWlIT3otcHFiMHJJMVA4NldlSm1RQk9YTVgzVWJNYWxTQ2hTeTh0anA3bi15bEs2YWJRei1OcHVBbDd4cUN4WnJQSjFpUjRvMXZFeDNYdmZxdHFzVFlIVmYyYkJ6WlZq0gHWAUFVX3lxTE9WNE1QUTI3SHI4QmlPN1dIM1NYZWVpcDB6VW9jU0QyZW9BV2Nrc1ZrUDQ3R2l0QS1LbzhXa2RvRGNPdUNSU0ZzZEZ1alhjemljc1R0VFQyMlNvUlVnY0NMdGQ4eFpWblZHRUNmemlBVmJkSF82N3UzeGhuSlZOLWE5TnRnUzhNT2pVNVh2SWNwd0ZNWGh4eGZQbGowaEQ4Wlk1VjVXWl8wVkxUYzZweTFSSUdabHlEWDN5NXZZNXRmOVVVTXd5VnlsUEdWcW5QMENORFhTRkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOUm9vZG52azB3ZENCY0JjTmFIQTBocXJLTmEzQVc0SDJDZ3c5a05VNTZfTF9UVE5YUDhCWnRWU0ZSV0l6N2Q4U3ZGeF80N2lYZjQ0cG5iNlVqbUtxcVVxbDZtcGZwZXU1Um43TC1nZ3VDMWJxQnp2d29fdDluTndrcTBmblh5Qmk2MGFhcUhORHRTVzk5VDZKem5TWUZycUgySkhIN2lNNFB3RzFtc2FXX0FkbkpodFZFSV9ZalF6NXhHUXVFRFRrZjRobU1nbTVaQ25GSWlkOGV2cUU?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26-04-2026 17:28 UTC</t>
+          <t>17-05-2026 23:46 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1365,310 +1365,310 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma's Rs 800 cr buyback closes this week: Should you tender shares?</t>
+          <t>CDSCO Approves Aurobindo CuraTeQ's Bevacizumab Biosimilar Bevqolva for Cancer Treatment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPZm4wTHhTN0dyRmxKQ3Q1Rzk2dW9MeUUwV2pRVmM1MVBlZUtURDdYbk5WV0psbDFYb0FIRDF2NjZyUUtsbEprTk9mMXpuZC1Sd2RtTjZRVllxN1BIdUVFYmkzdkxBc29jN3ctd2N6SE54Q2xXekRJQ01KVFdmVHhqZmltdlQ5SENMYzVMVldtNU16bXpZcnVQOGdlM1BibmlVbDIzdEJhdUI5emlKZGlIUXZpVEZwNGNCNi1CSllWT1VJZHVmVmhTVmxPZFlxejVHdHhsOUhnU0g1ck9YbUloOGN6T2MtQdIB6wFBVV95cUxOeEN4cTE0MjBUa1FNWno4QXVDT3Jkd21obmxwZ0xqNlJMTFRWQ1R1a2V4b2pBckVYV3JsY0NlZ25KS1dJNWVxaUVRcGZ1WVdMU0thNXFZd2EtSkdJcG9jRFlMQmhXTlFad3Itb2ozMlp1TEpSODBlbTgxdEljMWhMc29MeWFZLW12cGxnaDBsd0tqQmhJSzNFX293QjFpWUZVME51VjF6SEdqUFFLZktpRWptNTMtREJLYXRVenludkQzREl4VktMN005SW1Zd0VrU1lCZzlud3pZdUUtRUNsZzdZZlZLTFY4RzhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQQUZNWWhrREJJVEkzVlF5QWJ2dWVpZk1JVV9ob25IMklTNzlOQWJRZENob2lRdzdEaFFqNGtkSS11YXNKNC1NLVRmaFRLTGhYNERDY05qS21fS1pzZmhkMjk2bk5SRTVLSVg5TzBXUTNlVEIybEJfdGJfd0ZHNHQxWDA0b0E2TWo1cVM5ZHR5R0hRekxWYUJLa1lFZ3hZS3BQdlZVZjB1Sk1NMGJBOUd2aW5tZFBrWlRfVk40TkhsNkZMX0prRkh3X1RUcm9qOXpBX3JmNmp3eWhMbmREQUJuZU5B0gHnAUFVX3lxTE9qZ1hkTHh3bnUta0M3S0Y3YWlRYXNzajk3T0hDY1JuaWtJd2VLanZJYmM2cTMxZ2xFVFFlWmZoSE51cjluaUwtNkRxRmFkaU5rSEtBMkRaM0VzVFNCYzlMbnJjcDA5aWpwTVFtSnFfRDZYMWxPVWx1N0M5ajZ6eUJDcFBwWHUtLXM0RThOTDJBS3hNY3hTRi1xSm9rbVVFTy1vN2JJNGtMQ0JEbzZpVFRSQWswMk8xY0hndUh2dmNKVzFWY2VXNGtSVm9Say02LW5JU05RSk9SUUZRT3hCTjlKanp1a0VuYw?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27-04-2026 04:39 UTC</t>
+          <t>17-05-2026 16:52 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sun Pharma's $11.75B Deal, Zydus Drug Mark India Pharma's Global Push</t>
+          <t>Aurobindo Pharma Ltd. Valuation Shifts Signal Renewed Price Attractiveness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPMWdrTnhaMVdkZjFpNlpldy0ycEk0T0o2RXFTaWFjUFRaMm8xd3ktZnZCRE1pSGFhVEtHYmRRQUx2T1RTcWwxdllEaE8tRC1NakRsYjlEdVhqSWxCZUVid3BNd2xWMHJJRjBZeVhqWkxENGZsSFZuSFExY0lSMk1sakRadEFJZXM2cXdKYTYzeWRyaFc0Z3RfV2NJTGk1NHREclFuejlVdnVuU09XYWJ1Sno2bFU2TWc2SnhvOFBqaDBLNGdkbVlEdU1kNndaSVpycW9leS03a0Y1VjA1R21kcFVqSHo0anZ5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMlZnQ3AwbWpnbmtZeHVvUWxHb2RObjNkRWJ5RDlaakwtVXBjYTM0OHBzd0tGZjVkREZlUU83Z0VvZkxLWWVnU2IzYzE4R1g5RE96MXRwc3NuX0RwOHl6QmhhanpJakVQcGRtemJocEZ0c2loU0pnY0ZFMEFRQldhd3VXV01ydEI0TUZ3N1hDM0NPNTNXdnFLNzBGLWtlZDRGRElUZW4zMFNDOEM1dGNkamk5OWVCeVVSTTdNTlM4QXdndU5TUmE5d0dubw?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27-04-2026 02:33 UTC</t>
+          <t>18-05-2026 02:31 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3 Undervalued Pharma Stocks to Add to Your 2026 Watchlist</t>
+          <t>Celltrion Vegzelma Tops Japan Biosimilar Market</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>financialexpress.com</t>
+          <t>Businesskorea</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOLTZ4cW9tWTh0eWlKV3Jyd3pISHUwVDhKd2ktSFc3alJPM0FKR2l4MnAyYkVERm5RT3pTQ0tLbXF4eUQ2VVlPTlhKeXNEZDF5SENXMVRkeUZwbVVlQ2dlc0RVWmtrLTFYUXdjOW1YTTV6cGlmQWpvbE11a2pGaUVqcDlZUFdLRjB1UlVfLWtPUWJvVTlFWk1ETjJYbWphdndoZWFKLWI2N1dtc1ZpS0dzcVM4TUNLeUtMRy1CZWlR0gHEAUFVX3lxTE1DYjMzZkd6dnI0ZW1Qckd1dXJJVmMzd3JHbGRManNGMGxsaG44ajBrNFZiZ3dDdEJRNGQwcnp4c19lZjJ6MnhidjhXd0h0MjN6d18wM0Rtc0I3MEVPOU40QzNDNlhCbkZuZGNwUFVLUlBhRWNGckpzSE1pVDM2b1Zkdi1qWGM2Ty0wbHBwY25odVloQ3VnRUNmNm4weUlLTHVXa3F1LUowd21UTmhrSTFaVE9EdUpxNGg5eU5ySmptclByLVIz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9ialJUd2tadUY0Mi1FeUlHTS1BVmNnVHlHdDk1T3R2MG1mYlo4UHJRaDlJNWw0elA4aEhmbGVneFh4YnppdmJQS0hfYlp3Y0lpUmQtUEo0aDY3REhxWnRfb0pSb2dVSGRzajJIQTlDZlRGNV9n?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27-04-2026 09:22 UTC</t>
+          <t>18-05-2026 02:27 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zydus receives approval to conduct Phase III trials of Zintrodiazine for malaria in India</t>
+          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Express Pharma</t>
+          <t>thelec.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOYlZLMG56REZVb2N3VHlnYk1nV2xHMzd4MjRFMVdUaGpvVlY2Zmx1c1ZaeHlhdkZodzg3a2hRNFR6RG5wZ0sxSE5XcHh4Rk1hakpSdU8tdUdpT1RjbGI3TzVENzhiSEVWYnNVREFnV3lIYkpXb2VEU1JQNDBGM0lRbjBsWmtia3U3ZlZydGFDZ0swUmc0aVhRc3M4SzFMNTN3VWJHaE92NjgwR2h1Qjl3bGtvNjBMQlRkMU800gHAAUFVX3lxTFBkWkVURmRWRFA0dUVCRmVEZGZ5Y0wyY1hRa19TeUYtbnVjTEZ2a0tFb0U3aGlJZ1JlRng3cjV3WjVLbGUxYjBJOHp0V3BqblpvLWRMeFRkaG1RRm1nOUZpN24wNGJIUGN6QnpLckFnYlcwdmY1SWFUWnVHc215Z1FtUTlmYXRiUUZyZmRQNm1MZ29fU1ZiY2txSVdCV1FudnFiVmRRaV8zQ2ZQZC1VWkJRSjRzMFlKaUFvTDhPUWJFcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27-04-2026 08:30 UTC</t>
+          <t>17-05-2026 11:47 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Alteogen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AstraZeneca Outlook Steady Amid Daiichi Review Update</t>
+          <t>Alteogen Enters $13 Billion Eylea Biosimilar Market</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kalkine Media</t>
+          <t>aju press</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPQTNOdVpQbUZNcDhkTFRqTkJrZ0w3Uk1JYUxOcVRxMGVPblFmemMySXR2RkJJUm9jbW5JR3hvRDNKdGgxVWFUdFd6dEVlUnpGcVJiY3Q4Qi01Q3hLeDRnZG5TRjFpSjNPOThiNENrckZWcUpTSlAzMVZTUzVMbVM1d0luWjRCdXhlbGtiSEZKV09RUGdPMFNEQ1d2MzZtZGVW?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9hMn kockpJX1l4OXhHVkRrMTE2bXVrLUtYNWpWZmtXZ2J6VHJmcm9PSnNoVXBDaUhyMFdKZW5KWnhUc3gzVlpjdmgxdlpkeTA2cE5BUTVaZmhkQU3SAVdBVV95cUxOTzJ4djgtR3VRSGtqZEdqOW1xbVBPaktfbjZ5dVo3TWFvODlkUlhvVkpxREhHbWt2ZzZLbjU3dW92WkF1ZFh4S3hYN1hOa3praEt0TVhXamc?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27-04-2026 11:18 UTC</t>
+          <t>17-05-2026 08:46 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kyowa Kirin and Kura initiate Phase II trial of ziftomenib for AML</t>
+          <t>Enhertu® Approved in the U.S. for Two New Indications for Patients with HER2 Positive Early Breast Cancer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Clinical Trials Arena</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNM0p3dWZ0TlJ3dDk5M2RrdVVsN2UycnB0WVZZR1Bvczk2QzBlNkJHczhoWUZocXdqcGJrSEVQQnVWdDJ6VGk2S0ozWDRjLVpoUi1HdFRZVlQ5cGFqRE9xY29kZjlPVEUyc3cwdDVvemJuMlQ3SlIyNFJMNEphckloekIyc2t4akxfajZaTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeU9nc0RSWl94US1JbGoxWFZTX3p0eEoyMVM5YVM2bVlkc0Zhek5fbGZnVmZQZDA1NnFza3F3ZnhZbmF3M01VVGREX3Rncmx6YmR3OGkxZlNhUF9sT05yQV8tQXF4SmVPWDNIUTlCQzNrUkIzTGo2ZGYxM2JPSlh4RUwzaWxkSU1JSEQtX28yanZQdi1va21PRWlRSUlUZjB4V2tVSjZPT29iM3VSOUpDczZyMTJMV3VjNmx4ZWtueUlCYjJHVG9xWTROb25WTDctWUdiS2I0N3g3TFk?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27-04-2026 09:45 UTC</t>
+          <t>18-05-2026 01:55 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A phase 2 trial of burosumab for treatment of fibroblast growth factor-23-mediated hypophosphatemia in children and adults with fibrous dysplasia</t>
+          <t>AstraZeneca plc stock (GB0009895292): FDA approval boosts cancer portfolio and keeps US investors fo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nature</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBjRHNYWHhzbUZZQU9zRThXaktsTFVfWW5kczRKdVJBNGk3d2NtekswR3RVSTlKUHFxRXdGTTdIbFNzaUdMMHdZcUVlRDBuOHpXdC1uTk9fNDlId21EbjBr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMlAtaXNWMDY1WXJMTzdtajhoMDhCbVVtY2JqdGpaRlpUSmJLdmxOdVh5WU0td1lLakVlc3hJS0hWbWY3NFNsbUlER3RaUDlyWFpBWHFpdnpNRk51UU9kVHR0S1VPZ0xzbE5JWWFpLW5zbVp3YWNaZ3ZsR2NaSWY3SXctR3ZBOFZ2elduMHU5Q1Q1MmFLbFQ5TEZjNUtDQkRrSEJoU2xtSXQxZC1IYVNfbGo4U01keC02dGVWdmVKODVoTWpGMUJxUjZn?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27-04-2026 02:45 UTC</t>
+          <t>17-05-2026 23:44 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Esperion Therapeutics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leading Companies Advancing Innovation and Growth in the Urticaria Market</t>
+          <t>Esperion Therapeutics stock (US2964331002): Heart drug deal and revenue jump put focus back on the p</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNTVA0emdfNF9MTkZrbW9OVUpjbTM0M1BhdUFHSFJSV1NDdUduamYyZmRDTkhfTHdiNUZ5YjFGMzFIeTNIRzFWQmlWUFJyRHU4Umc2d29obnJKdzk1Uk42MVgyUlYwbTA2aWtHVW02WDdDNDFoUHowZmZGSUQxdHFkNnlsSXBtQkJ1ZW00Q3BCMkwxQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOakY4VzZ0NGNpNlphcUJTVzhKVk42U213OTczQXVBbkRJV3g1cGRMT0pYRXFnM2dTYktJRllseGlYWFZDQWZwenBDTTBUWlA0NUlGMjJyQ2ZFd2RNc1dVNmNYd3hIekk0cGJsQUFkVXRMTU9xMGJWOENwWkpkRDczckdxSTBYQW1mb0lrY2RieXZnR2s1bEltNGE2ci1mNjEtRWUxczI5YWJpeUNJZEh3YmRXSmN4WlJ3RldtTFBvbXVvUHhoc1E?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27-04-2026 05:07 UTC</t>
+          <t>17-05-2026 16:23 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>World Growth Hormone Inhibiting Hormone Drugs - Market Analysis, Forecast, Size, Trends and Insights</t>
+          <t>Is Kyowa Kirin (TSE:4151) Pricing Reflect Its Mixed Long Term Share Performance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IndexBox</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPUHFfcWhIZzNVMWJmZzh2ZHpWS2g0cVV0YXBZNGVQcXBKWmt4RTkySjVTZFVXbXh4WXdvUDRCQjd4N2RJWHEzWmdiYTVOd0J0NV9IZ3lmaGhCUHJOS29LWWJWS1NVTzlFSkJiRmpRMDRPWnNCZEJmdTE5dlkwOVJzWGpzMEVjRVZYWDdRQTh6d2xVdGtFU29mSUtEZklUTElxdk1YcldjbXY5bGZvcXlUSFpURG1vZXA4WHJsZEtQTkc3c0c1UjF1cHFuSWUwckZ4Wnl0SXphVzBlN0ZKZ1ZFME1EYjR6U3pfTy1neVBUNWd5SklEZ0M0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQczlsYy01RTI4VGJCU2QwSHJFV0t1QWtXWDh4X3BJMGZtS0dlQm92ZWYzS3NxV3dhZU1fZW5TY3IxNW5VVjVCc0xRVEZuVVQ5aUJFUmlQTVlxYTdjdUlCWEdkWHktLThQMW40ZEZLdlBRRWpfN1pzTWw5UGRUY0ZqZzdRZFNCZkdvUkdpVF9BbFFtTkpiTVN0T2hUbW9zRDBIcXZUbGQ0dDFueW9vNUNFMVRsa2FUNlMwWExUVV9walVQbm5DcEEzeGhWUlBENkhldVFWeDVIODFpSWRfNkFTU2Rya9IB6AFBVV95cUxNLVFhS2NFYkpKZDQ0aVN6NnBJN21QWVplZTlQRDlCdmt6THVnejZCUThNNFZ3cDFaSzFXUlpWQm10WUFmN0c4SXpkX21DUjlZQTJ4SHQtTnozR1ZMaEw5S2I0cVpreVVfcXYtajNjYkVGVGJFUjQ1OWhmZEFxRzNFbnp2Mm9fcTJxYTFjVm44b210d2NEaXozbE5fMVZiVTRVMk01S1lNMlg4SEppZ0dXX2J5cDg0YkpCbkdkb3RYSi13YnVLVmlJMERPeTVBczRfamRQRTNERHFjYzIyLVhwSWFOMjdtcWdT?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27-04-2026 08:31 UTC</t>
+          <t>17-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UAE pharma firms move to keep medicine supplies steady</t>
+          <t>Fresubin clinical nutrition explained for US patients</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gulf News</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQ2lmLWxpMmZkcEd5T001aEI0eDVJemlDWTh3anpRcmY2QkRUNG02S2pBX2NYV2lqTXlENzlJd1AtZkQ1VHgxeDN2ZmlaYVNYOGZVU2RZUTVoYjUzUzlaSjlVTkFUV1k5VUlVVVRISHd0LWxZaEVSOWZHbnJzZFJnbklDX2NNVUlYc255NFdVbUFpbThlbERjemZUNTM2Q1VUUmZkbzdxODh3Wm9RNjJfaXNiNGNtRDRj0gG4AUFVX3lxTE1DaWYtbGkyZmRwR3lPTTVoQjR4NUl6aUNZOHdqelFyZjZCRFQ0bTZLakFfY1hXaWpNeUQ3OUl3UC1mRDVUeDF4M3ZmaVphU1g4ZlVTZFlRNWhiNTM2Q1VSUWduUVlVMnNTVnJ6d252U3pGMWN3cm9kRDduMzhKRFVpU0dFMDVMUHVmY0MxR1pYQ1p6RGFyOHc3MjV2NXYyMk9mczlBTXk0c2lRczUyaW5mZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVWlPVnRmVlhQNGxxdmN2eTFCWVpMemI1cFdBUzNSU1l6eEZjYWo3MFFYT0wtR0w3bFJHVFlHc09BbVRFWVJqSVIxd3NxdHA2VnI0UllVYWdSamdtUi1fRnM0bUI4cjFmMlhQUkVTcG9QLVo3aTFCWHE1clN2d0pHWW5zRDJtUzQyUmZ6djk5T3FZVnpxSHZHNzhGc29kMnZoTVg0UmMzNmpGNWJpekFzSFdn?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27-04-2026 09:12 UTC</t>
+          <t>17-05-2026 15:30 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1680,128 +1680,256 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Glenmark Pharmaceuticals</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teva wins KESHET Award for gender equality in corporate workplace policies</t>
+          <t>Glenmark Pharmaceuticals Inc., USA Launches Vancomycin Hydrochloride for Injection USP in 500 mg and 1 g Vial Strengths</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The Jerusalem Post</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBXdzY3blVhbWRVU1B6RENJeGJCTlQyQ19JMWNTZjBIZTc3ZjBUMGhrczlacWlCbzhjRnZTcThfSDFqU0pMRkpzSlFkZGVYaEx4TTFGWnJkY0J2LVds?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxNb1haQk9hMG50a3FwV3pteTUycUNQRS14WTJQdlV3b0lFcWQwRTc5dm1BVXI5TmhxeDI0X1VreUFvRUpiZGw2Q29wYmY5Ny1QZERPNGxwSHlDLV9vRUZONmtXRGdPSkZFR2hIV1VKbjRGcHQzR2Jfcll1T2tPTjlTOHN5cENNck5pVmdHRWdvWmhpN09GRllNSk5nRF83ZG9QWm04YTg3bVg2ck0zYXRaa0g5bGlLbFBPNHFuUEV4dTJJTEdac25ST3ZWM0VCOEctN0ZSOWdQUEttQWgwLUtfTjVIdkkzd1dGVnhJdUhndkk3ZG9KVUI5Q2lpWlZON1RPNjJudA?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27-04-2026 08:26 UTC</t>
+          <t>18-05-2026 03:37 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Gland Pharma</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ajovy Market Overview, Key Trends, and Insights on Leading Companies</t>
+          <t>Gland Pharma Q4 FY26 PAT Surges 97% YoY; Revenue Hits Record ₹64,307 Mn in FY26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>openPR.com</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOLThvWWhscUF3UE1aWXd6dHp3dkNUUmhySFNmTy02NnZPUUdIcWJqbEZIRWFoYXpuOERLTkFWWThMNEVVemVEbEg4dGg3bER1N3oyM0c4SV9HLVdqQ2t6X3ZzRjA3bXdxZ1pqM0xCWURZMGk3T1dLaUpqRTU0bWEwUExpMzFIOG5xYkwzTmJLeTlEeU1XTjI4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNDN3UU4tYUxJaE56XzNjM0FObDFUYzRjWTcxN3RBazdYVjBmTTBscUFrdkZQOWhXMmVxYkhqQTdqTFNYYkRLWmp0UHFUemtJQzZuUnBiYVhrM2dSb0oxamRlTTNPX0hCRC1vWDAzNGlCTzVlcC1MODhFenA1ZEZ4TEFVcHFzZ0VzQnIwaEZ2OTFta3lSR0JqeGluZU9iY0tNVHFmN3l1ek9vdFhyN0pfZnNueFRFQ2gyUzk3Uk4yazQ2d2FESXpha1F5a0JUUWZCcXNKZU8zU0w?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27-04-2026 09:01 UTC</t>
+          <t>17-05-2026 15:24 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Alvotech</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Justices tell Baltimore City Big Pharma can't be held liable for abuse or misuse of legally licensed drugs</t>
+          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WMAR 2 News Baltimore</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPRkphc2xqUlRSeDBqVFB2WmJpLTU5VGNvQU5tM3ctdy1tRHk3dmlTM3lMbnBfand5aktVU2tqWjhEMFVKRl91NFhLZkFfNUtSOVNIZlRfVzJPaTZfeXBfMTRaYUROd0VOOFRsVTRPTGwza2dSM3dTUkZ4VENUcld5Q3M1dXdSQmwtRUZHMFlyZVFUUnZqLVk2S1NUZFpZelJqZWNnUjkyZnhRbFZlNmhTQ0R6UTZ2ZnFJVC10THYzWURyNUp2em5XMkt0MjNYZVNtaU4tVndnUFhDTUdLaVl2X0pmZXh3QjBOU2xpQjdzMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYYWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>26-04-2026 16:46 UTC</t>
+          <t>17-05-2026 07:37 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical stock (US88162G1031): new weight?loss strategy and Q1 results put focus on turna</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcDZGYW5MRHFpSkRQc0VOZENZMWktcTFScHZtTDlDWnQ1QnZ1cnZNT0RkT3pyZ1BkNE9YV29QNnRWTldkN2Z6ZEViUDR1RGVGMzlDbjJ1azdxYXJhU0FTT0JudVJmZjg3SUdjTlJON0VlQ2wwN1MtcHluNXhSQkRqWE9wOThpRlRyb1VEeEFhamphYVdUaEQtSk5KQURDY3dZS2MxLXRON25NMlVsVGdDeVdpbVZ3UWJXRlFEMHJoV285eWxoanliNw?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>17-05-2026 17:06 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A Look At Teva Pharmaceutical Industries (NYSE:TEVA) Valuation After A Strong Year And Recent Pullback</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sahm</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNRWtrMlUwZzdPNHRIWEQ5bUZGNDFtY3I4V2k4RGlsdS1pTEZ4QnFlNzFqRkZfckZ2Njl0Z1Fjc1JycEJwYUZXVzJOb0NWZzFyXzZkTVRjczc3amhEODBHR1d6SDBPLVI0LUkxNVJ5N2t3R0hTYmkzbjVUQlg5LTJrXzZXNlFGdzFvX0t5Y0hJMV91Z0hyLV8zVjdaaURvNlJORW9DLTRWSnBOS0RQNWdzLTZzRVJKOHVHUnZETUpWZkYxV0dMV0tMa3U4VXZlNlk0UWJHUHdzMmtqOGktQW1fd0pwN010QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17-05-2026 06:19 UTC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE82X3RIZjJ4MGdwdThuX194S1JwN3RSd25jVEhJYmpJMmRuSmpBazI2c1NwSVdsSTdBeVA0Si1kN0JjVXEwb2w5MUFMbVlvN2p4aUpFOW0tLTV3MHl5bzZ1bzlqa1NDdkRQT0RLeEVCbkNqQzdPYkFIT1hhWG9VUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17-05-2026 16:29 UTC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis Releases Second Quarter 2026 US Biosimilar Market Report</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Business Wire</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOLWxnMjc5SWx5UFJtazNOTGNMcnZsZDVvTHg5eFdmdzhJQnVNbERQMWhMeWpZYTRhdnYtMzMxV0c1MFVGTk5GY2NTMFJuQmlBcG9jT0UzUFV0TjNEcGJXNWd1NE96TmEyNURHNUZXWERkR0lESU93Z0dxU0lzX01uemRFUlFBM2tfZXdJQld3ajFmM3FCaFpzM3JKWGNVVFB5ZUhra2JuQ2RqNXJqZHVISkt6WDNXQWViOEpBRDJMU2lIRG5kZDI2TA?oc=5</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>27-04-2026 12:00 UTC</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Other</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis presents real-world Humira biosimilar data at KCR 2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>koreabiomed.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZ9IBckFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>18-05-2026 02:58 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis touts Adalloce data improving quality of life, confirming safety in Korea - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPRUpwdnFMLWFRWTdKWmZkUjY0TG5INWN3MUVtZHYyQkRnZXFPX1VmVUc1UkRNMWplc0lscW9DUjNhZUdJSDhRLWF5dWxTT0s1UWk5dWplLU1JUmJBeDBObkJHM1ItN2JBVFA3RzVKWTlKek9vY2VkaWdndi1teENwNdIBlAFBVV95cUxNQTNDSl9lczBtSmszNzBUcnRrOVZrZU5BeEs2bTdGM3RpQkxIWnNqVndSeDVYZTN1dWc5T0hkYUlmcFl4N2llY3IydVhyYWtlQ2RzRk4xek1DX1E3Mld0R00xV2tYam96Uzgxbm94S0tlNHVhajFyTkJjV1Jwc1pqSU5rczM3X1AxaXh0QWxQaTNGaXlLdXM?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>18-05-2026 00:03 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1957,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-04-2026 17:54:21</t>
+          <t>18-05-2026 09:53:50</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="News" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,27 +464,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Voices of valor: Kisumu women rise through STADA’s support - Radio47</t>
+          <t>Sandoz backs Budget consultation to improve access to biosimilar medicines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Radio47 - Hapa Ndipo</t>
+          <t>retailpharmacymagazine.com.au</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUpxUmY2bDV1UTlGQjc2WE52T3cyWjUyc3ZUdFNnRV81NndCYTIyd3NtS0VXck1hOC1DRHNNNXRQSXBNa0oxdVE1R0pHQ1ZxTGtpUXppT0s5VGVKLWZrSFp6bTN0SW04YW1tR2ZWRTM3d0thMThkdFpaUnY3LVZ0ejYySmVEVVZ0bFpleUE0b0U5Z0hvcmNTalU0MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORXBNYWlOWnIwNjg2OVB1a0RmdGlNUGJtVWJ0bGR2MG9wU1Fjb3J5NmJnaEVZeVBEVlpLMVRYMVBWUDAwY3g4ZVBBUVl3aVpmQmRMa2VVVjl5QTJFdUMycTZQQlZROHpFcG9kWi1wZ1JWYTJXdEwwVUdDTTBSamVKeVBIME53VVpHem4yYnEybFk4QnBTZlJGbUJGZUJNWGd0Z3RrRmx3aVlReVVzVnpha2dnOA?oc=5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17-05-2026 14:43 UTC</t>
+          <t>19-05-2026 00:27 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Formycon AG stock (DE000A1EWVY8): biosimilar specialist in focus after FY 2024 figures and pipeline</t>
+          <t>Sandoz Appoints Aarti A Kapoor As Head of People &amp; Organisation Operations For Region International</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BW People</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPeVk1MGQta3JabkwyYTg5cXNYX1NTckFNMmkzTkJ1ZnVmY2U4bERwM0tId1hKRWxuM194OEI4MmtPYW9vR0J1V3QtTy1zVHA5dUxoV1p5NkE5a0luRUdFR25BdmM0ZlhBYVlZNnM2XzVhNGhKMkx5OEtjaTNqaTRUOXlzVExuVGNEM21GR29EcS1YT3hqOHZFQ1lYVk4zZTV3d3hkd1JfVndiWkhrZGRFNW5HblpXSW9CWmRjN05XOExqZ2NaVE1TNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQNHlxRHRBMUxsQzVETU1BdFhaWGdIVm8tUUNCMzZFOWRLWUhqTC1rQ1N0LUxBcVMxYU1JLW9aTi1EVXBqVUFoc1VuS3NEZGdIRUNNcVhzc2hfc0FRRXI3cGdqTmpWQ2NBdE0yd2I5OC1yTnpoZ0VPYm5Ua0hvcVBTb29zRE9wNTNveEpmV0NrUFhUb25jMWhDOHFhazMwUjgyd2xIVmFLUXUxMmtqNXRmNUxzbzBzVFF5bF9LTmZoNlNxTC14S2tiQVliUG5ETkhtSGc?oc=5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17-05-2026 23:14 UTC</t>
+          <t>18-05-2026 05:33 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NIPER Hyderabad, Boehringer Ingelheim tie up to advance pharmaceutical research</t>
+          <t>JASCAYD approved in Japan new IPF and PPF treatment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxQTFpHTlQtZjNEM2d3VmxVam5Gbk5SWEphSGFnRU9CdVdhZHZvVm9mekl5bEIyVlc5c2xfLVAzUnBFZEx2ZmZ3TEVQMGw2S3RiNWpaTEV2VGNfUWZ6YkVQU0dkc0liZDZ6bTF2eTJKNGl6ajE1TTZ0RGhNUFM4VUdqbExCWEZRU0VELWJsWE93OFJsXzdER3lQTy1vWUJacGpsZnpqdUNmTDZDd1pDTFRreDhzNXY0SXp2VVJoTlVyR1BzS1B4dnEtMEsxZkVjNDJrWEZQaHZaSU9BblpMWVYwZjV0bW9XR2ZwSlpZV2UxTTJnYWJQN09XVENhQWsxTHQ0VFVNaXBDRW1OZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPOTlzUmdlVFV0UE1iaGRnNXQ3ZVFUbUlNVTZxejI2bGRHa3JrMGpwVnoyaENkTU5EMU5xYmNTZUd6OHkwQVMxYlI4X3JUY0ZZUlZNMjVXLXFfa0xjRHd4Z2V1MFdhUFo4VFItQXR3STFDNUFXZlhIUkhlVTVPTjNGY2xXLTZzU1J6djFzbHo0Y25SR3oyamhNZXFibm32dHV5MVdvUlE4cWcwRE9RclFpYXd6bFphbGRuSjJEQVRWcl9lVXRIcVd2M3NPYw?oc=5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17-05-2026 05:00 UTC</t>
+          <t>18-05-2026 07:10 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -565,59 +565,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Killer counterfeits: the flea treatments that could send you rushing to the vet</t>
+          <t>Supreme Court declines to hear drugmakers' challenge to price negotiations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>Healthcare Finance News</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNNUVLNUVsYzdlYy1CLTJ1SWFTejFjT2ZJaXowNGJtMG96dk5TbVdmcGIxbWhhMGZsS3p4TkZTd24xMDJwUzFtUloxYUE0QV9kNDdRVS0yQXBVQkdaMzFnN1J1ZTdxd3YtVURHOGVyUHBmcjRLTmV0eGpwSUZVM0VSVmt3T1E0YnJXM3EwZ3BvY1JLODgzdW1XZHA0ZnZtM1Vpd1VPdGZGUTNVYjdGMFQ2ZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDB4NUI0a1hHMXc0aFJ4WWthSWFkenFJZkJEWHYzMEdCSUdPeXN1cHdUYjJPZDY2c21GMWprUzJzVVhqT0U1aU9LYzdUQVd0WHc3bVkwOExMUEhvNWo3eGgxb3dPMUVOOFY4aC1XSnhuYmxWYkxjNUNoaG1IODNEdHdQQ0c2blpDLXdqQ004bDF6dTJ2SzYtX204MnhtTzZ4QVpGSFc4Smx5Y1lUdjVB?oc=5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17-05-2026 06:01 UTC</t>
+          <t>18-05-2026 15:24 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson Launches 'Gut Tunnel' Experience in Singapore to Highlight the Importance of Endoscopic Remission in IBD</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): recent AGM update and focus on injectable growth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Business News</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOQTNQTDhHVC1HN2VUVm9RSzZNODRMQmRaRHlhNVl3d0xDMEFETi10UFpZdm9WclR2akUxcW1ZSzBFa0JITF95UEs0ZVlpeEwzUXlCX1pNdVh5THZXMHZrVFRieHdfdm5kRjlPNjZkQVljSDcwQnk5UnhjMWkzZFhESnY1amRnaWxQbVZRQ0YwUWJ1LVdBdm9OQkE0dzZFd21sVG1CR013X1o0VTJzeklpOVlhNkdBdVc3eGZwSTJxdUJSS2tsTW53emo4NFViLUE3aGdMcmswUF9rQmRWLVBVTUJJcG1fcTJXemo5YWg5bHJNT052aWpzXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV_5cTFP5yFTZERKcmw2aFBkdjlKOXZ5RWpsYUNBb1N4b0wxTkZsSG9ZdTF2eXgwb3AtYXZycDFxN2gwUzd4Q3ZhV3o5UGNKNVlDdDRnTm5TYjc2X0tZY1hSa0UzblR5M0czTWpPWjFkT1JnQ1R6N1FRT3VSS3A5QWNkWmNZY19fZjg5ZUc0WkhKWHUxVURKam5PcTFibkZ5Wkt1S185V0xzOGU4aWV5X0lxdEhLd0JaWDlCRnpMTGRrSFlSUXhYWkk?oc=5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-05-2026 03:38 UTC</t>
+          <t>18-05-2026 19:27 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -629,22 +629,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): earnings momentum and US injectables footprint in fo</t>
+          <t>Hikma steps up $250m buyback, cancels shares to tighten free float</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPVkg5Z3BUMTRNTDJMSjVFN2NlYS12cVBnVFk2QnVLaWZocXNtRFMtcFU3djFnOTJsVGhBSlM2a0RnajBFZUZ4NV8yUU85SGM4Nk5FWm1NRVF2aWM3cEtOdGlxTDNqcnZXRy15dWNFUHdKN0I5RmRweVBnOG1ZX2N1eGREMHBwd1I1N1ptM3pxYlpwRGpnZ3RWU3hXd21aam5WU1U5Q0dQYVZ2SGlTelpZaEFacEU0dTFuWkpueXdmQ2pzLVlVM1ow?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV_5cTFPZ2gzYmFhNDNoS0wyRlY4RERCMzBSNi1MbzA1ZmxzSFRHVGNKbV9TTEdMLXNOeFRpNTFGQWNnVzdtX3VuWlpLVkRRREtnU2dGNl91bFV6Q3NWUWFvSHBZdzFNNWJmLWhZVS04NTFJcUxwcWNrVmtrY0ZOTmpxSGx2TDdEaC1GYjZSN1RsU3NQZUVjMGhIa0xldzRqQ2p2R1J3dGxFR3VCaEUzVXNvZFdBanNWdE8taXM?oc=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18-05-2026 00:25 UTC</t>
+          <t>18-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
+          <t>Biopharma bites: IRA is here to stay, plus more safety concerns for Amgen's Tavneos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRDRCa2dnZkdVYlZoYzd0OXpJYy1NV3ZFalNSdnZQdWk0bDRXMUtWWS1hMUtKU1lob05hNFp5U3pSN3FLRWRoUkZLM0xvWnNQdmp3NTRiMWc4cFBOdDFSTXkyQ2FKVkVZVUtDOFRsU1RVOVN0UXNEd0RaMEM5cGIwRTNSUTljeWRDdHhocVMxZDJzRUFQQ09QNjVfbnlhaVZiNjZXNHpSalNMcmM3cTJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FV_5cTFAxMzVQWWFJbGpRTDh6ZlVXWC0taDUyM2tMc0lvbUhlX0FsLV9RcmZ0WkJNQzZEZHhNU1lOaDBXdVFURy12WFZEbEc0TEE3X0dkUGQ0?oc=5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17-05-2026 04:56 UTC</t>
+          <t>19-05-2026 00:23 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -693,86 +693,86 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): earnings beat, dividend and guidance keep biotech giant in focus</t>
+          <t>Amgen’s rare disease drug Tavneos tied to 20 deaths in Japan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNTzVSejhPNWhScmJ6WGd3eTV0Qk9WM01DWFNUR0R6dFF3Q1RNZ0RFRW9iamlybjY0YUFrQVdSalZWeU9XUTh3N25sYjExQlAzLXdsWU5kc091VHFOcGdmbWJxaXZWMUxoUFdHcE5GN2Y2cC02dVV6c0ZGQnIzelZRaTBKNFgyTFp5VVJlWlhEaDVaa0JyZTYtempsQ2VjRC1LUWlaQ3ZxT21kNTg0SFlfWlN1X1FNVkJHVUxsaXZmY0NVZlp6MlJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV_5cTFPdDVhWTJ1dTNFTkx4TlJDUDIxbmpEUFd3c2ZkeG91RUlBZGlNdDBLVlRoUi1Fa1F5TmFfa3liRjJ1WGtSbGc4OVM1Tmtxblp3OWcyR2dITmFRUEpCLUJ4bUNKQ1_4a0tqcjg0RlFHN05XTHBNMndOUGlZYmhHTmN2cDZ0UmNNYzhPRkNwcV_5RlplX1d4Z2lrdQ?oc=5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18-05-2026 02:16 UTC</t>
+          <t>18-05-2026 12:37 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Organon to Present New Research on Access and Value at ISPOR 2026</t>
+          <t>Amgen Inc. stock (US0311621009): focus on Horizon integration and latest quarterly results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOalVKS2pkTUVYdVNoeGd4Q29hSHJZSHNsVDVINjZ5QnRGd045Y2JKbDUyR1JxYTJXMXJGLVloUGZzYkVYdHlNOXRiZFZxSFcybXFOUHJJZDlxWTNvbEwyXzhvWmdSSXhYUDFTSDlzZkI5cmgxbWlyNXRNNDlyeVFhQTJ0YWhDTjdvcUFiTFFMS1M3NF9aRm5WMWpWb25XS0NCYmx2ME9LdVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV_5cTFPWnFkVmxWYXlxd25EelhqcXVodmwwZEtUV21BRktTNVIxaUZTM1gxcUNSdFc5dlc5bUIyb2Zrd0d0cEJvUk4tb3c2dUlxdV9ZUENzQ0NNTXE4bHNvYjI3ckk2QmpYSHhpai1NMGJ5UldjWWNfOVlzUXdlaV8wNndaSVB3RWUxekN6akF4OXBLM1lJUjEzc2k3ejd1ZmFfUzJkODJ5NXk0RnhWTEhYbTFmWFRUTGVLeG1KVXFrSUtTdWpqRkdZMlE?oc=5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18-05-2026 01:17 UTC</t>
+          <t>18-05-2026 14:37 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coherus Biosciences</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coherus BioSciences stock (US19247A1007): Q1 loss widens as turnaround strategy shifts to oncology f</t>
+          <t>Amgen Stock Analysis: Repatha Surges 34% But Tax Litigation Clouds the Return Case. Here’s What to Expect</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPRGc3TV9jUVBPQndhdnRCWVRMQkdjUC1TMXBOVDhVTXc5SWo2VndJRXZsVDV6bTRRbFJuX2g5VU9Bekp1QkZieHdydThhaVdydWN2TTAtdm1LSTRnOTMyY09CR054ZDk1VEI3MlFpTV9uTnIxUWQzc3VUZkM4b2g3eHMxeTFkaDB4OG9nT3hmd1BEMWRINVY0eWNhQjd6UTRZT2hkY0YxOEhCYTV5Sm1fNVdYVXdQWDhPRFlSa3phSUJuTk54?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV_5cTFPQzkydTY2cVlsZFZDMWx4ZVZ1b2dRbG5sOXhLaTJqNWF0ZUdXSHVwTG5aalhnNHFkem1aUWgwekNIZkR3ZUJZdm9tMERwaXNTLTByVnhPbDM3dGVhbTM5dmtHM0Q0SURPVno0ZE1GT2l2VnhWTlZxNVRsbHNsWWJ6c2I1dm5fTDJJRmxJSlRKVVNXVUpWMmVwTWh6aWxhZ0FXcmhrc0VjNnZRU2YwUi00c015UUhaVjFUNFk0NEdaX3F3a1RpQmc?oc=5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17-05-2026 10:24 UTC</t>
+          <t>18-05-2026 12:29 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -784,27 +784,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pfizer Inc. stock (US7170811035): Q1 earnings beat, higher 2026 guidance and rich dividend yield in</t>
+          <t>Amgen (AMGN) Gets Price Target Cut at Piper Sandler Despite Long-Term Growth Optimism</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Insider Monkey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQNC1CM0pHSXd1MGd2MUJDZnIxWHVsY0JRLUxjZGEzYlNnVGN2NE04Sjk2MUdzZG5mQkpjX1lwb0tBalFnYmF3RjlsQ3RWZDlwSGppcGxlMFpUYTZHb1ZLNTl4VFFuaDZZT0tsSHd3ZWZtV084cmhITDl0aERKM1lmMC1BUDVFTHF3alV1ek1ORll1NVcybDJxRjZEc3BFdXBSX2JSekltRnVCaGJWUVljdUx6cHkzOUZPX1FMUHh2b3phVGVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV_5cTFNUmZYdU9IX25GSVVvTGtkOFRTcy1pZW43M1hscl9TVXRpcmpHVTZkMk9OMWhtUEtpbVJwYmlCajhiMjBDZjRtZ1FmTGhMcUNLTVhzS3F1RmZnQ05HM2kyX2VjSzRKRElUeklHUG5RWEl1SHRpSUFsUzBrZUQzUWM1SkszRG5TWE1jX2RzUXpOdXBtVzE3aDJsZFliQkJNVGFnRW1uOVFVUDFnTFRQb2d5aWt2T1dla0NlVmNONzRRNDlFSjdyVkHSAc4BQVV_5cTNOeHhCRnBTbHA2eHJzSXZWNElrN3dqbjZ2ZFlUbEtGejhWa3pyQTUxWUE5NU9hc2JLMXZQR2RqRFZ3RjAzbl9tdk9NielVLYkw0Vy0wVTR3RWpSdGZtSWF5TFR2X2pHdlNJMkhnV0JaUF9BNFBnRzlwOFFMWXlaWWM0eWNVWkVVNWd1Q2NYNjVJcmMxUFpXd1JwMFozdkRsczhfaGNmTEx0ZWdJeEsyYXo1cWFBSjhzVGV2a0FUMkthN3V0UDZNWHlJN0VwVlE?oc=5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-05-2026 01:54 UTC</t>
+          <t>18-05-2026 21:18 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -816,128 +816,128 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The week in pharma: action, reaction and insight – week to May 15, 2026</t>
+          <t>Earnings call transcript: Amgen Q1 2026 beats EPS forecast, stock dips</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Investing.com Nigeria</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOb04xYmh1V0VBX05OZ01haEl5NkJpNG1QbXBjckNxeUozeWZ4TEs4S0QzN3doUTNPQU9qWE1fNU1xUlVJYUxLNXFXRHpDb0Y2cjFUWEJDblF3Si1ReHJLVFlhWjhkTS0yOW5Ob3BTUnZVcDJuMnducW9hU3dzbUFTZGc1WmxDSGIwd2NVNEw1WXZZeUxPb0dlTnY0ZGJ4dW9uNmEzVzVCX0h1U3NoRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV_5cTFMMUs4cC1nVHRmT05sQmZ4OTRBVHo0NzlZRGdpWnI0dV_3MVI4Ql9QajB6RktjazVVcDlKRjZBQllCT0dsTHBTdFFIUXczR3VTQUtHUl9uZjZiQ0E0SzA0cHBibHBqTllQbjFDWlFSLUt0RWpoc0NOWllndmJDNUpsUXpQMHgyb2Yyd2ZjZnluMkdBeC1PVi1seUR5UGdxMlJLdmZZRnBka1Y?oc=5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17-05-2026 15:19 UTC</t>
+          <t>18-05-2026 12:32 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pfizer Just Locked In Its Next 5 Years of Growth -- Here's How</t>
+          <t>Amgen stock (US0311621009): obesity deal and recent approvals keep pipeline in focus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1wUTUxZXhWS0tQTHdkbWx6amFDb1FIT3FWMDNkUnpnNlIxSHh6akxPdUZLTWdOTjlqTW1WbEJRaTVWYW5BMUpZUEJhUl9maXhXdTBJQWJJWDFZTmt4MUp6bkpSTmdUQV9VYUhaSDRSSldFMlpVR2FBbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV_5cTFPdnB3RmJZcktuLWlTMWhkMnJZWkpaRVplOWxHVldZdGpqcGViNkZGeThQZ25Jb2dtcWdZM2hTVHRralY1eHRDelVDN0t4d3k4STNYczVpM3dFcFM0SGdQdDd3eERWYjhfd0pYLXBrRHJycWNCNENUc3lIUm1WbWhVdkhBLXhzc2dyZmI1NFExTkdfMFpRY0pWc3JSMkFsd1VUSzRxRkJ1amN4ZTZDMGx0LS0tWjctLTdlRTRxWmJDTQ?oc=5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17-05-2026 18:16 UTC</t>
+          <t>18-05-2026 12:48 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seagen Inc (Acquired) stock (US8166361055): what remains after the Pfizer takeover</t>
+          <t>ChemoCentryx to Pay $69 Million to End Investor Lawsuit (1)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Bloomberg Law News</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQVmFNZlotaVg4Y2xEMG5iYUVFMHVRdE1ZT3lBblphdC1uaVMyekd2aWJEQzFrdjhsTm9mOS1GTGhhU2FfbjRaRWtaMGNKYjFHWE4xSTVvejF2empEdjdZUS1MLWtVcGg2WXcxUmh5YkkyY3E4eV9yRlFqS1JESWdVOFdob3RXenJHQ2I3SDBLN2RaVFE5TXpwYmhQMVE3WXVRYUtsb0NZYm5nYlI4ZlZiYVRBVXhZVXVZRDhVN1JzaWFXMzBlOGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV_5cTFNVS1ma0UwZmlmQWkzZTNlMm9QZFVmOE9CSGVwMVB0cWVYY3I5cjdYUGRDYUV3cjQ2Z2ZxQkExVERaSHQwdzFUeGlGRWVJekFMRmJIcWN2RHJlUnRwV0RPZUVLU2ZzX0g1XzFnbXFoU0ktUFNQb3dTN0U0SEhvT1JBbUdnYmhQeGpvQm9OOW94eWlpSDlaSUV0WWREdGdkQTN5b1ExZExIMjJtSFZ2R3dr?oc=5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17-05-2026 14:59 UTC</t>
+          <t>18-05-2026 14:24 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pfizer vs Eli Lilly: Different Bets on Pharma M&amp;A</t>
+          <t>Earnings call transcript: Coherus BioSciences Q1 2026 revenue miss prompts cautious outlook By Investing.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Investing.com South Africa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1fQ29hVzRoV1pxaXRYZFc5V0FTVG5KYTAyNFRwN0xucWxGNlpyVGJmTS0ta3FJYm5VNHFDWUh3YmMzY2oza0dnby1IQTRLUGkyS2hCOEVTbWh6WUI5MnZ1NTE0ZVVMdi1OQ21FQVdVU1JQYkxaY1JLLWtwTWRJUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV_5cTFNWlhSQzBBNGc1c1V3ZmcwdmZHNHpPcjdMNHNMV2tNLWd3RWJkYlhqX2htWnVOeUZJQkt1aEl3TlcwZzRGTVQzV3ZNMVRKYUxEYWdYRXpBOExzQUtZS1NQV2trRG5vNkZFRW4tN1dhUUJYOU93amI1RUVPMndKN1ppUmRPVDE3M2xlQWxiUVRaaTVRMXJqbzBfbElkM1ZEU1BMOERxaHA5dWNfZC0yMGduc25SalpJaEl4NGN0WFNIZnZYMkZCa1gtazVvVU9MdWJETkFOUWd6T3p6U0RkdExlWWl2dE9aQQ?oc=5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17-05-2026 13:08 UTC</t>
+          <t>18-05-2026 10:34 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>How Pfizer Comirnaty Works and Where It Fits Today</t>
+          <t>Pfizer Viagra commercial: what it really tells us about men's health conversations</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>stat.gov.pl</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQeURmdEw0S1RsZXA2ZHlJYXJ0bnI2aEdwSnRpV21OLU9VQk9feGFDYTZKUHRyNHIxQ2hubFZRMHR5VE9BVzY2WnNWNDVqdHVzLV9yNEhCV19qWGFqdXhySUQ5UC1nMWtGNlRIdFMtREs2RkpTQ0trZDktemRiaWVCbG5XZnJHbHktcVVEQjh5UVJycG5sVm1vYklyeWtuWExLUHVHS0U1QldIZTVtaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwJBVV_5cTFNUa0pXbHJWdG9hczhlU213OEx5M2gxeXp1WDVuVE02TjhmYUNGQ0JjUGRTVUY4eEU0OVNFdTdpeHRTTXhJRkIzSmFkRFRxTjV2YTdRci1ZOEdNWWo0dFM1MUJUVmV5elRWa2o0WWJ6ZzZiRFJzTUh1aU13a0NuT2IybEpIcm5zdlV6bHdtbXJkZGFLNkhtNWR2U3J4MWtyZjFKa3BDM3pNYUoyUDBMc3ZHZEVxcUVIQ2NKUlFGVTZqWnl5QnBwNkcxaDJVV0ZtYVVfY2VwRUtJWHlmR01IejFiSm9GUmtrUHBIRDBfN0txTWExOXpGVzRYSUFvYWo1MmxFajlFQTNIZGZwX1NwR0J2eEpkMVE0WlJjYVhxUklLWQ?oc=5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17-05-2026 12:46 UTC</t>
+          <t>18-05-2026 23:23 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -976,27 +976,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Q4 FY26: Mounting Losses Signal Deepening Operational Crisis</t>
+          <t>Pfizer remains a strong buy with rising oncology drug sales and solid dividend yield despite FDA leadership changes.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNR3dHZjdXZGdtX2lKVFFySTFpZWVKNUVFUVBIMjhmcEJpU1Vra0Q2SUhmYXl6Mm90SHFkeC1EX092bl9US3VFc2xmQjhQUVA3WnZFVnQtNE8wUWlOaU92cUVnM1VIc0g0X2UyZlZjaENpYWZEbHJhdk5yaDJ2T2Yzd1dCWG85SnhoRkIwNm5wbjcwbzBqMm5iRmxQWnlnWHBRU1Z0V3ExaGxRMnkwSUNrajh4dmREYVhtWDRvbldPUXVPWDNldzNOS0Izc0VHa3ZiSHNsSkFuMFpzZHBaMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV_5cTNOOEpSWTNlV19ueWpGVHFfZWE3elB0UzBPWHo5MkFSczMzelp0czZjNEFYSUI5OGpvT0syV2Zac0lkUXpqU1I2RG1uUlk3OFczR3V1WWRubEFpT0xsSWo3X05TSWx3RmNDbkNlX29GdmhpTVcyRUVnR1J6cU92WWpCVDBpSS00eW1WNm1kcVZn?oc=5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17-05-2026 23:54 UTC</t>
+          <t>18-05-2026 19:20 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,27 +1008,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Goldman Sachs sets new Biogen stock price target on bold Alzheimer’s bet</t>
+          <t>Pfizer (NYSE: PFE) CEO receives 24 phantom stock units in deferred plan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>thestreet.com</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOZk55NnRjdjBjS0xtaDFKajBzVXBUdURmNF8wdWFNQjdvV216RVdENmVzZXVSYlZwc1Bxd1NNVEFlRzlJRk1ZZ01wbXo5dndnNFZGemJKcUs5VUx4c0VVWTJaTEZrYTI0VHZGUkJBM3I5RlE4Tl8xdkU0UlM2MWUtd05Qb21iNUNVakswZ2JmNFBRR2pPOGJTSkxmQUhqMDl2a3I1Mm1JOVhwQU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV_5cTFPZmlMOWJaNEUxalBaOW5STHZKUlB6YmF_59dOYXp2TnZpR0xRQmJyOWwtSFp4ZzY1VGMwcEVPN0FobUtiZmJiY0Q3S0dzZzZOTENxS0N1Tm1lTFVyZWxkUWp6R2lGSmdoM0R3UjBGRVNmU1k3UUpWTHpYczJTUWppZW5raUw3YWlrQ2Vfc0xiOGNXMEtrczFGcjVjYm8xNzNWRnA2ZkZ3?oc=5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17-05-2026 17:33 UTC</t>
+          <t>18-05-2026 20:39 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1040,27 +1040,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biogen Inc stock (US09062X1037): Goldman Sachs lifts target after strong Q1 and Leqembi momentum</t>
+          <t>Depo Provera Lawsuit Settlement | May 2026 Litigation Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Lawsuit Information Center</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPMkhFQ2lTYVZKUzVwcTR2NjNiaWFWdjZPNnkzNklYUy1uZi1qSHk4aldpRmNoZEJZcFBpVEdDLUp1ckFjZTg3WmFlRWh2SEFXc1BzU0tQRTdlWkRaOWstODhqTVNBUDAtTUY0R3hSV3hSMTJqOEVENU0wZWNsZjhBQ1ZzdERyc0VSYkhyWUFDZEpaWERwTFk2TkxZSjdsWjljYWJzZXBWb2RybVYwbHhMMUh0MVZhcV94V0swM3A5Nl8yTUxnb2RZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FV_5cTFB1X0VIdm5nRVF0LVBnMTU5RDBvZVZtaVN1Sk5UQkFaQVdKOTdfYnVQam9QelRvcEhWRGhMSTBJWUZibm1YNjMzNWlROUhpX3ZjTmw3bHo5TVVDVXM5UTVyUTdkMFRpTXZNVWVTUFNqVDBYNGoxTjg0?oc=5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17-05-2026 20:09 UTC</t>
+          <t>18-05-2026 14:20 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1072,155 +1072,155 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen’s Diranersen Moves To Late-Stage Alzheimer’s Trials And Investor Focus</t>
+          <t>Posts linking Covid jabs to hantavirus misuse Pfizer, WHO documents</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sahm</t>
+          <t>Yahoo News Malaysia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPaWtsNE5TYW1lVlp1cjI4dzJWVV9PMGtGdnFtdnBFcWkyNjhXbFF6enkwcUlibUVQRjZZSlUyWlJFRW5DN0dmaHZ1SWxrc1FaY0cwbDZwZFhtYUVWZDN0Q0F3WHF0WUZyMHRDNldnWUE5Y2pPVVhwTC1sTFc3Wmpxa0xHYlVMUmRBWDZNZ0pENmJvR3VtMkVEVTFpMlFnSlZQVVp0dnpVWmp4T2J3NG5HWjFGX25hMTlmY3VWdzkyUWF0dUQ3THc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV_5cTFNFm5MbkdYb2w2ekdtbVN4bHNfOEJsMlN1aExIdHFhb21aa0VRNlZNSE5FX25NVWhsX29HaW1vTENBbHhHTWgxN2h2ZkU2cUxON1lKc3A0N0lMeWxuTGRCdVBiQWNHdUQtMWY1VnJUUU93cF9JRWJOTFY1RVVtVjladXRacV_2bWgyWnc?oc=5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17-05-2026 06:27 UTC</t>
+          <t>19-05-2026 03:00 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biogen's Alzheimer’s drug fails to meet mid-stage trial goal</t>
+          <t>Pfizer Stock Price (NYSE:PFE) Trades at $25.30 With 6.80% Dividend Yield After Q1 Revenue Beats by $649M</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>TradingNEWS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPMklKdzZ4Zk9wdTY0UnJwQlVNUHVCc2R0eHo4WUFwWmhsMjVRaEZsX010VjkyX3JfejRNSFB1RTlvODMxUUlLSjFlZ01Cd0xqbS1DYUpNRUI2bWJVRkYwazRQV1Q5YXd6UUdhUFpyVFJaVkNVNDlRQ1NWdnh1TWNMVEpZWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV_5cTFPcDgyVHNMMjVlTTR3RXNKQW5mNkJlZVJoeVhfaGExMEQzVFFtWEdQUUFZYXJaYWpxa1Y1LWszT0htanZidlJtbi1IQzdJUEhuYWRnS3JaUnNCQlRCaWRCQUd1S1BHaXlEQkp4NVRUeWNBWTZGallZWGVVWW82b2dqSUs0cEtQS2t4TUFJaHFlNUNwdlJ5cWR4MHFmaXZzNnJvdmR4M3BtOWFTMzVi?oc=5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17-05-2026 23:42 UTC</t>
+          <t>18-05-2026 16:41 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biosimilars could surpass generics in US mkt by early 2030s: Dr Reddy's CEO</t>
+          <t>Biogen completes acquisition of Apellis Pharmaceuticals</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Ophthalmology Times</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQZ2stSVlrS1Q0QVJHY3ZWV25Ob1FkOUM1TEw2OUZZc1g4Z0JwRUZTdGQ1djRXUFUwbThPSUp4NGV4dDdRMXVOdmNBXzZFZVBrZklkZ3BDblJDcnYzTzg4T3ZKbzNFV3JFRHozbm5vdEV5MWtOTzBnTzl2S2RvV2Zld182eFlqV1pBZ2VUNDN0WUZEaHVPNUppTml6ejVHaWZETnlReTcxaFVURDVQeDlzYWl4UWt1MDZ1YVd1RVhiSUR2UXhQeVNBY3lEUVROc3JHQVc1anZJVmpQN2NjbFHSAeMBQVVfeXFMT3Utd2U1RWg3NWZENW0ycG0wNmh0NzJ4aDNWUlU0aHJ4N2FPYlJBb1RIYkdnMHpDeHhZc05CcS1QYXAzaFZvUWhHa1JOMmVuWS1sSVZiTktUWTdvNUV1SGVrVVpIT1FQNGVHY2IzTTMtT2hnZGxRRGFqQTJicm1uYU9Ka2hDR3FXUFhJUk5GZ1ZWM0tMdHloeV93cEpzaG5KLVI5Rnh6MTY4N3NDY2VhM2JyenlqdEtSZFpNWXpTZ0NMeHlNUTBzR2VJU3owTzlUemswRHRRcjJka0ZMWEh2ZFEyN0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV_5cTFP5rLNlJXX0t6M0xBVkJMTC1tN3hEXzhFYi1paGlnZWh4Z3Z5VUgwNFpHUE5BeDJKbm9abjdsZVU0aXBiRVVCQ3BJYldIem90b1JpUXhKMlpuTVFCQ29pWHJaZUhRRFN1alA2cDR2djV5c284OTBoVkNGSjluV1Q0WlRSYXZvTTh3bmpVaHZtY2xmbFNUZVdIU3pQcw?oc=5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17-05-2026 18:19 UTC</t>
+          <t>18-05-2026 15:52 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Schedules Investor Meets in May-June</t>
+          <t>Investigation launched into Biogen after Alzheimer's drug trial misses key goal, stock drops sharply.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPbDR6dWdlV25JTW9fS3dDNzJ3QmxIWS1WMGdZaml5U1JOUkRGa2YtT1ZRdWgtQTlNbmd0U3AzekNrVnRkWmJzX2tJSDJtR0gtbUZVTDJaMXpkdHlZVXMyUk1fSnpZYlFVb2o5NU56aklWNW5ScHFnN3RHZmU0MHdUQmdsSU9PSU9rSnNySUJLYlNwSVdCbXZuSVZDbkdmVlZESGYyckJyOUhXb2w4blhEWnFrbGV5UkRSZkpWVl9mSmhBeUVIeE1La3RPRGk2ejVmWC00REZhYVNDUGlUd2N6elhyLWprenlLcFlCcWliMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV_5cTFPX2ljTjczSk4wWTFFak5sLVF3V3VxcDFfbHVJT01oZzY5THNGQTVOUFprNzRVRmJoSW4tLXNqVGpvd2RvMzc0dUVuSmhoV1R1OXBHbi1VMUtoc2x5Y0NIWE9fa2ZJdmVGenpKS3FfM2pfVFloN1VUV3owZDVSTnNzRDBKcGRrTlJmRkE?oc=5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17-05-2026 09:43 UTC</t>
+          <t>18-05-2026 18:17 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr Reddys Laboratories Ltd Valuation Shifts to Fair Amidst Sector Comparisons</t>
+          <t>Biogen Pharmachem Industries Completes Allotment of 15,04,33,833 Bonus Equity Shares</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOS2x1N2I2MjFFT2hVWHI0STR4ZncxQkZKXzMzNXhtdnczNkc2UFVOX0Rsc09zeGhKUG5IOHZmVjlEY0lCOGpIeUx4T3M3ZGsxTmpYeTFkUG1DTWZTX0lzV0VacjljQUVxeUdrT2xiRkRtMDJ0NTl4NEFaOHB2cndpTG94TTVZbTBiblpqY2JZcHZmUGtxbHJ3VEU5MFNoWkRBd2JNd0R4ZzBfeE5nVzItQ3RSckJTZlZQejFSNzJRX09XOFpnbnNJMDlORzlxUUli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV_5cTFPVTdBeGVFNGdYdUVEMjhpZENKSU01V3dCUkJGT1_5U004VXR0MkFTSjFOeVl5VVNCTEVra2RhR3A5c2lITGp6dnpyaHY2UkNBR0xCZzRqRDB4SGEtODJTay1kcFVYQU80TEMzblozdVhONW0zMEZRWTFFYkxxZGdKYkE0VUFCa0FpNVV2cF9lSTJzRHpNd3VZNTV3Z1YtazBHWTVGVzVkRVVjTEFQeTdIajF6TGNGR1p3Wm1nZk5UNk9EQjFtR05WN3phQjhkZEZiYktqZFpWZVo?oc=5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17-05-2026 21:21 UTC</t>
+          <t>18-05-2026 14:48 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1232,59 +1232,59 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dr. Reddy's (RDY) Introduces Generic Semaglutide Injection in Ca</t>
+          <t>Biogen stock (US09062X1037): Alzheimer’s focus after Leqembi setback and pipeline updates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxQeDUyMkNiOE81S2cycDUwUlBvTXVCeEVUTkVxWHd4MUNGSmhnaEd4UGNqaEhOVjZYd2JDcnBVVFFFR0tmOWV3YzlFcE5Ic1g1Zi1SaVNTWndLNXg0UzNNVFllMWcyUkxzR2oxRk1mWHV3dEhPV1RtZnlIWmdocVZyNUVxamEwT3B6UTF0ZWswaHFadkdaMlk2OElkd2NHZGtuUXJ1MlVxekt3bEFrSkU2TGttYkhHbW5UVlMwZnVRYnBoUXRhYXFWTG9JaHFtNjBwdXFTWWUtZDhWQTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV_5cTFUVDVPTV9DLWhSdTZ3WWIyVzdHNjFfY0dMXzBDcU9pdnZjalUzcU5aeWUwUUM5enJjOHNxRHJPXzUwaDFsaFFkSEpPb1VYT0w2VjhmT0UzajdQOGRKUGc0bjNWTTU0djE0aTVnNFFLVmppSjg2UlFpVmVFSDdXeGE5VWlRX1NuQmpTeDZwcnNzZ3JRY2VmZm5UWTBrUVZOTG9iYUdDZklqTUpnVXpyVGlrSjBwQmw0Zlo5aGdoT2U4Uy1hQ0pmX3pV?oc=5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17-05-2026 18:45 UTC</t>
+          <t>19-05-2026 03:12 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Should you buy Biocon shares now? Key takeaways from Q4 FY26 results</t>
+          <t>BIIB SHAREHOLDER INVESTIGATION: SueWallSt Investigates Biogen Inc. for Possible Securities Law Violations</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zee Business</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWEFZSE5GbjhLc0luN19jU2tJTVU3bDF0VWdSQTM0MElBUUpFcjdUcWtsbzhBUHotOFNlUzdXXzBjYzFKaVc3MDItQ1dpY2tBbHhmcE1PWmR5NmdkSXFzcGxEX1lWMjhPOFhoWFJHRnpDUmNLa05IZ3BzWkNuaXl2ZmhVX250UXI4Mk5lNkJYVWZZNC1YeGdSOFR0ZGd5OTlWT0htb1lQTmxaS2VRWUhCcmN2QUdMQjdqTU1YMFJoUEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV_5cTFPQUM1WVEtenFuMTBGT0IyMzU2U0c4RWgxNFlSS0RUSWdrSWdDS2s2djJ6NkpjZWFQUFU5dF9JS3RVN24xRDZpNlhqS0J6dTJxYlJjVHFhbG1ocE1ZcGVyVWF_5jhVbEotQlZhd0s3SEVwelhjTWd5azYwTE1qN1dvUUJmb2pkTm1NZmxVUWtGZUhNUVBEdnhCeVIwTjdWYXNYMkZibEZ6ODFUNDBBMHlsTHZPVFJlUEZOa3hpa1JvSmhMRHIyVldpb1QydVpFV0NjbDJkczYtaDlwSE5KRUFUbE5PbW5jYUxVSXp2NWVZeTE?oc=5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18-05-2026 01:36 UTC</t>
+          <t>18-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1296,59 +1296,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Board of Biocon recommends final dividend</t>
+          <t>Blau Farmacêutica stock (BRBLAUACNOR1): Brazil drugmaker’s profile and US investor angle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dailyhunt</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPQXJweHFyTG8zRUhvZng0SEN5Y1NuTExFZWlFV0xtTkF5Q1J2a21aR1RZM1ZZTjJjaU9keTlmVXRRZGw1T0FaRG9BWXk4NHNId0FTMU5QM01tOE9HNXphZFVtZzlMeXdKTFRiUVVXMnBtYVlYZHhxdTJJREtZOF9kbjJadHkwSDlYNjdVQ2lURk9EazhMQzBhTkViQUZ3azZCU2RvVGczbC1xd1BoVzRVdElWWkg4eEtWbEJfUkNxZGtpSnlQcTBzNExn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV_5cTNOREF5MkI4WmlmVVBtSmlBbkJleU1qQUNFcmhJaE1kbjJDU1F1cUQ5ZzRZUi1vazdrdk10OVg1LW9oUTJHY3FLcWowUGhPZjluYWVFLXptT1AwS2lqSG14MF9URkstWjVqbGVNNVV0Rl96RUZDOGNtWTREeUV1RERBSFhPNE5va0dPRTJ0WHFEb1ZqMzRKdVpaYjlxd0dEQWJIZzFrd0tVOC1uQ28wOHhGbndhbVJCRUlSUWtzNEtTTlRQM282?oc=5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18-05-2026 01:39 UTC</t>
+          <t>18-05-2026 09:51 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Sees Sharp Open Interest Surge Signalling Bullish Market Positioning</t>
+          <t>Dr Reddy's Wins Higher Target As HSBC Backs Its Global Expansion Strategy — Details Inside</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOUm9vZG52azB3ZENCY0JjTmFIQTBocXJLTmEzQVc0SDJDZ3c5a05VNTZfTF9UVE5YUDhCWnRWU0ZSV0l6N2Q4U3ZGeF80N2lYZjQ0cG5iNlVqbUtxcVVxbDZtcGZwZXU1Um43TC1nZ3VDMWJxQnp2d29fdDluTndrcTBmblh5Qmk2MGFhcUhORHRTVzk5VDZKem5TWUZycUgySkhIN2lNNFB3RzFtc2FXX0FkbkpodFZFSV9ZalF6NXhHUXVFRFRrZjRobU1nbTVaQ25GSWlkOGV2cUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV_5cTFPb3liYUZCTFNGblJwZzZIbVRvOVZpUHQ3S2QyeTJnc1pDVFl6M2xBNENYS2N2REFMdjNQdVJMS2FobUJMVXl4eTVSN3hWaHdlZVRtSXRsbmxBZU9OS1RhZVFLRGlRSE1VaEdNaGhCOXotam83YS05Uzh1WmFXNEtDa1JxZ3pYU2xtNWtIMnNzU2hnLVkzSmhmZHAtOE5qcldYdXEtSjc5eXR1bUdjLXRRZV9ORnc1VThjTVByVkM1a2lBbkhFbGUzWUtZMNIB0wFBVV_5cTFPeklsWjdIdk5idTkwODVUOUF6ajJSelpncTFSekdtbEtGU3RKeTFZYVo4dW5QT3pvVGJxbUxhUDBaNHVSTlJCLXYxX0dMNlhDcnRDZDNQSC1CcE1kU1Foa0ZCX3RKV3B3ZU9ucEpJeGVENWgzSXB0eDJNdHg1VGxUYldqc3J3dV9GUDlFbDctX1dDa0g1cGJjd05JRjZiUHNMVWZYUW96ZldUcElMdHpGcW5HNkFvS0FNT0hIMm1Lc1ZEN1IyQU5hVklMR3FjUEJESzlJ?oc=5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17-05-2026 23:46 UTC</t>
+          <t>19-05-2026 02:32 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,59 +1360,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CDSCO Approves Aurobindo CuraTeQ's Bevacizumab Biosimilar Bevqolva for Cancer Treatment</t>
+          <t>Dr Reddy's Q4FY26 Net Profit Plunges 86% to ₹220 Cr on One-Time Charges</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQQUZNWWhrREJJVEkzVlF5QWJ2dWVpZk1JVV9ob25IMklTNzlOQWJRZENob2lRdzdEaFFqNGtkSS11YXNKNC1NLVRmaFRLTGhYNERDY05qS21fS1pzZmhkMjk2bk5SRTVLSVg5TzBXUTNlVEIybEJfdGJfd0ZHNHQxWDA0b0E2TWo1cVM5ZHR5R0hRekxWYUJLa1lFZ3hZS3BQdlZVZjB1Sk1NMGJBOUd2aW5tZFBrWlRfVk40TkhsNkZMX0prRkh3X1RUcm9qOXpBX3JmNmp3eWhMbmREQUJuZU5B0gHnAUFVX3lxTE9qZ1hkTHh3bnUta0M3S0Y3YWlRYXNzajk3T0hDY1JuaWtJd2VLanZJYmM2cTMxZ2xFVFFlWmZoSE51cjluaUwtNkRxRmFkaU5rSEtBMkRaM0VzVFNCYzlMbnJjcDA5aWpwTVFtSnFfRDZYMWxPVWx1N0M5ajZ6eUJDcFBwWHUtLXM0RThOTDJBS3hNY3hTRi1xSm9rbVVFTy1vN2JJNGtMQ0JEbzZpVFRSQWswMk8xY0hndUh2dmNKVzFWY2VXNGtSVm9Say02LW5JU05RSk9SUUZRT3hCTjlKanp1a0VuYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV_5cTFNURGpJZmZKaWV1eW5Lc0FJa1UyS0xKdHNDWERXMVFoRmpTZV_4cWtIalM1S01nNnhONWlURnZ5OTl5MExNcm5CRVgxbTRiUTFBSzBPeEZWVlh1T3dqRldNUDFPVE5QSThyMDdzMUxLWVZER0hGWHZyVkdEQzVjODZsUTB6UmRPNzFvSFpnMVh0azlsV2Y3WTREallEYVBuNWpDOHEtbkJvbFRCbll2cy15MUw0VktuaVhaUjdKeDJBdmhkMW5WdE8wR3dvZTMtLTF0ZXZ3a3FXeGZXaHNNT3h0TWo3TWJqVWM5T0RNZElHZWFSWGJ1TE9sRQ?oc=5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17-05-2026 16:52 UTC</t>
+          <t>18-05-2026 20:18 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd. Valuation Shifts Signal Renewed Price Attractiveness</t>
+          <t>Dr. Reddy’s (NYSE: RDY) files FY26 earnings call transcript for investors</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNMlZnQ3AwbWpnbmtZeHVvUWxHb2RObjNkRWJ5RDlaakwtVXBjYTM0OHBzd0tGZjVkREZlUU83Z0VvZkxLWWVnU2IzYzE4R1g5RE96MXRwc3NuX0RwOHl6QmhhanpJakVQcGRtemJocEZ0c2loU0pnY0ZFMEFRQldhd3VXV01ydEI0TUZ3N1hDM0NPNTNXdnFLNzBGLWtlZDRGRElUZW4zMFNDOEM1dGNkamk5OWVCeVVSTTdNTlM4QXdndU5TUmE5d0dubw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV_5cTFPNDlJR0Z1N2M3QjRxRnNPRVFsOHRSNVdoS0ZDNnAwdTNGdkJmQms4RlNkNjhFTlF6WlNtSkRDRW1pY1BJWnl5TGNINUktN2JvM3N0MUlab1lXbVREek40dTh2TlpjcGxTLTJFWkxDWS00NW1IWXhReWVFTFJ2enhocTVwUFUzOTZaeTdrcTlndGZadXQxWTFVd3ZRekZVeVBNa3czcU8wVjJwRjVfa3JJSTdKNFRCTU9YT0d1R1lR?oc=5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18-05-2026 02:31 UTC</t>
+          <t>18-05-2026 17:00 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,59 +1424,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Celltrion Vegzelma Tops Japan Biosimilar Market</t>
+          <t>Dr. Reddy's Laboratories launches its generic Semaglutide Injection in Canada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Businesskorea</t>
+          <t>Express Pharma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9ialJUd2tadUY0Mi1FeUlHTS1BVmNnVHlHdDk1T3R2MG1mYlo4UHJRaDlJNWw0elA4aEhmbGVneFh4YnppdmJQS0hfYlp3Y0lpUmQtUEo0aDY3REhxWnRfb0pSb2dVSGRzajJIQTlDZlRGNV9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV_5cTFQNlpNbWVzaExidUZRaC1QQWY4SFZBRWJuZmRlYzV2NmRzUjBkN0xQMU51ZmNydjlaenhqbi16V0NWaWNIcnVZNS1SVFlCR2hkVFhHaDZDajllVm9qMXRQR3RWaEliSkk5dDlaYUJ4ZTVpb1JrcDVBcHFZOVJ3OUpWcGF4VVpOQW9hZ2QyQkhkS3A1TU90ejJ1MHUzWVp5eEstQVMwam5CbnDSAa4BQVV_5cTFPZGRkRDAtR294VDREUENuT2lJLVdUUllqd3FMOEFzSTR2VTV0cFJJQWJVQ2dldkJoYkZtY3NiYTI5bGtPeTNJLWFGYTYzR0RkMk00SFhkbDZHNUo5dFk3SDFDd2N2M0k0T19HVTMxejVWLUVJdUxDM2hzUWlidGpaRlBOUjJhZEkwdmc1a3RqYzV4VHEzWEJfYkVmNWhEc3NTcWxnY2F4Sms5LTFKWl9R?oc=5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18-05-2026 02:27 UTC</t>
+          <t>18-05-2026 05:56 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Korean Pharma, Biotech Firms Post Strong Q1 Sales While Profitability Diverges</t>
+          <t>Global investor meetings for Dr. Reddy’s (NYSE: RDY) in May–June 2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>thelec.net</t>
+          <t>Stock Titan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9oZ2hxeXJ6VS1PZTR5SEFSQnUxbm4xQUZjOGFOUHVNbVU2LTVjWXZPcnJWdmY5TkRNTWJHY1FRM1RPR0JHdGk3NGFqelVLSEZZV1VnZ3VBTHZERkRpb1FoWjNyc3lNRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV_5cTNOalVhUmUxYTFxc1JEOXZuNnNFcnd3VHcxRlg4MDdYN1Y0VWdmVXZKYWpkQlNoNDFmbi1pZnU3endaeV_4dkw4THRGVHRWV3h1NGZWUUJsdl9PdDNRcXZRY3ZmZzRzU0piV08wdzBRSnotSzlVR0wwSkQ3cmpnS3YzZGxJSzZtTGc1MEdWeUREQ1FweExSbzFFVHFGZTZISnQwVms1dkxEMGFKYkR0ZFpMQVdyTXZSbkQyaGNWMWp3?oc=5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17-05-2026 11:47 UTC</t>
+          <t>18-05-2026 10:45 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1488,123 +1488,123 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alteogen</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alteogen Enters $13 Billion Eylea Biosimilar Market</t>
+          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI™ (golimumab-sldi) in the United States</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>aju press</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9hMn kockpJX1l4OXhHVkRrMTE2bXVrLUtYNWpWZmtXZ2J6VHJmcm9PSnNoVXBDaUhyMFdKZW5KWnhUc3gzVlpjdmgxdlpkeTA2cE5BUTVaZmhkQU3SAVdBVV95cUxOTzJ4djgtR3VRSGtqZEdqOW1xbVBPaktfbjZ5dVo3TWFvODlkUlhvVkpxREhHbWt2ZzZLbjU3dW92WkF1ZFh4S3hYN1hOa3praEt0TVhXamc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijANBVV_5cTFNWWtCYzgxanJCTFhtRGVIM2xYaXROTzRPSklLQkwtOUZDeExSbTFaV3VERTNBUHBTcDBaV3RpSkxGMFg2bFFBRWFnMDZ6blY3YTZNZWZWQUZuYl9aMDBjdlJocGgxcGdYVW93b0lfVGhjajQ5OFMyV0RETjBSUjlIaHlpaklnbmptaWl2NFJZTEx3aHVWLXB6ZnNkeGcyMlNQRlRGX0JnSmdHcXZFZHRmSE9hbG0tNUpoeWt3dDdPLVNyYV9iaEpaZjgzblBoQXpXd0hEaEhlMTh0WDVUUmhDR3BwcnVFVHd6czRSSWRMZXotX2dVcVh0TjhlRUxLT2ZuLVNxV1hFQ0o2b1_5SlBxVjJjV3p3MkJRZWZLVV_3OGp3Yzk0Q05hYzltTzlwTHNmemtyX25VNU8yaGdUWHo1WWQ3UGtpT0EtQXRPb2FJVVNzb0pvdEs5OVBDYlhuTnh4ZHhwOENCX0RLQmNiTGF6QUg1V0duaXlFOWJxZFlGWkNBMURsQ1B3ZlN6WDE?oc=5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17-05-2026 08:46 UTC</t>
+          <t>18-05-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Enhertu® Approved in the U.S. for Two New Indications for Patients with HER2 Positive Early Breast Cancer</t>
+          <t>Mock drill conducted at Biocon in Pashamylaram Industrial Area</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeU9nc0RSWl94US1JbGoxWFZTX3p0eEoyMVM5YVM2bVlkc0Zhek5fbGZnVmZQZDA1NnFza3F3ZnhZbmF3M01VVGREX3Rncmx6YmR3OGkxZlNhUF9sT05yQV8tQXF4SmVPWDNIUTlCQzNrUkIzTGo2ZGYxM2JPSlh4RUwzaWxkSU1JSEQtX28yanZQdi1va21PRWlRSUlUZjB4V2tVSjZPT29iM3VSOUpDczZyMTJMV3VjNmx4ZWtueUlCYjJHVG9xWTROb25WTDctWUdiS2I0N3g3TFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV_5cTFNkQ2xWMWRjTFFhbUdcHJpaHU5TGdBNWtLTnVWRnN3UjBNMEFkNkpSbk0tMFAwb3VLUmhVcXQ0N1BLNWl5RDVWUDFKRk9kczJkUGRyMmE3WkUwNUI5RjJGdWxrNEYzektxaEc4ZEVpUHdPNy1RX3o4T3pEbnVKREFvRHBjX0loeVoyREcwUmtRR2tOeUk?oc=5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18-05-2026 01:55 UTC</t>
+          <t>18-05-2026 14:52 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): FDA approval boosts cancer portfolio and keeps US investors fo</t>
+          <t>Aurobindo Pharma Extinguishes 54,23,728 Equity Shares Under ₹800 Crore Buyback Programme</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMlAtaXNWMDY1WXJMTzdtajhoMDhCbVVtY2JqdGpaRlpUSmJLdmxOdVh5WU0td1lLakVlc3hJS0hWbWY3NFNsbUlER3RaUDlyWFpBWHFpdnpNRk51UU9kVHR0S1VPZ0xzbE5JWWFpLW5zbVp3YWNaZ3ZsR2NaSWY3SXctR3ZBOFZ2elduMHU5Q1Q1MmFLbFQ5TEZjNUtDQkRrSEJoU2xtSXQxZC1IYVNfbGo4U01keC02dGVWdmVKODVoTWpGMUJxUjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV_5cTFPazV6WmtZTUVQZnlVZHdGNXVTT3pOVFpGVVRuQWhGdThJS2Z0OHVYdWs3dkxsbklJRTROd0RhVEVwanAwYWNuNVRNTUZLQmp0S0gwWDM5eGxDcU4wbVFkN21XOE5UY3hXSzU3WjNueEhpRG12UERHSk15TW1MZGVKeHJyLXFiN2V2TFp4SXB3Ym03cW8zWmdneXF1M0Z5V1VWV3huakJoQmpWbHY3LVJOZGdVcEdiNmtKblhvWmMtZkt3TzVLb2laUV_5Y1pNVXZfSWdHSmoza1VybUYy?oc=5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17-05-2026 23:44 UTC</t>
+          <t>19-05-2026 01:43 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Esperion Therapeutics</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esperion Therapeutics stock (US2964331002): Heart drug deal and revenue jump put focus back on the p</t>
+          <t>Zydus Wellness FY26 revenue climbs to Rs. 39.4 billion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOakY4VzZ0NGNpNlphcUJTVzhKVk42U213OTczQXVBbkRJV3g1cGRMT0pYRXFnM2dTYktJRllseGlYWFZDQWZwenBDTTBUWlA0NUlGMjJyQ2ZFd2RNc1dVNmNYd3hIekk0cGJsQUFkVXRMTU9xMGJWOENwWkpkRDczckdxSTBYQW1mb0lrY2RieXZnR2s1bEltNGE2ci1mNjEtRWUxczI5YWJpeUNJZEh3YmRXSmN4WlJ3RldtTFBvbXVvUHhoc1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV_5cTFORnRwSGhyMGhJN2s0N0pzc1k0M3JnbVZtTDBuc085RkRNMnBvTTJ5dkNFYVBTa3RhYkhOSm02SkUtRmU1QXJZdnRuc0F4bzNSbGJaQU9tMjd6Z1hQUGk3cWliZ2xnaXFnem4waldwZDNqS2dxNzNvdlpndzJyQlpKM2VyVE9XWjA2MnNnV3JHNDZVWFEtVlEwVTZZeEk?oc=5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17-05-2026 16:23 UTC</t>
+          <t>19-05-2026 02:04 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1616,123 +1616,123 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Is Kyowa Kirin (TSE:4151) Pricing Reflect Its Mixed Long Term Share Performance</t>
+          <t>Assertio Therapeutics to be acquired by Zydus Worldwide</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQczlsYy01RTI4VGJCU2QwSHJFV0t1QWtXWDh4X3BJMGZtS0dlQm92ZWYzS3NxV3dhZU1fZW5TY3IxNW5VVjVCc0xRVEZuVVQ5aUJFUmlQTVlxYTdjdUlCWEdkWHktLThQMW40ZEZLdlBRRWpfN1pzTWw5UGRUY0ZqZzdRZFNCZkdvUkdpVF9BbFFtTkpiTVN0T2hUbW9zRDBIcXZUbGQ0dDFueW9vNUNFMVRsa2FUNlMwWExUVV9walVQbm5DcEEzeGhWUlBENkhldVFWeDVIODFpSWRfNkFTU2Rya9IB6AFBVV95cUxNLVFhS2NFYkpKZDQ0aVN6NnBJN21QWVplZTlQRDlCdmt6THVnejZCUThNNFZ3cDFaSzFXUlpWQm10WUFmN0c4SXpkX21DUjlZQTJ4SHQtTnozR1ZMaEw5S2I0cVpreVVfcXYtajNjYkVGVGJFUjQ1OWhmZEFxRzNFbnp2Mm9fcTJxYTFjVm44b210d2NEaXozbE5fMVZiVTRVMk01S1lNMlg4SEppZ0dXX2J5cDg0YkpCbkdkb3RYSi13YnVLVmlJMERPeTVBczRfamRQRTNERHFjYzIyLVhwSWFOMjdtcWdT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV_5cTFPQVBMRFhfd2pPajBmMlo1QXBTT0QyRUNUNXo2MnpFVHZwT2NlUnlWazVOUjAwMTJaQlZESHUwM0dMSDFxdFl0d2d2cEpWVC1sTVY3QmlzOHhiU3lLUU8xdDYyQzdBM3B2bVhrcVhXaTFhd2tNdlM1RUM1c0Z3ZmZ0U08ySVExcWUwSWlwZVlFRXRLVm5kRFppOVNvaVBYa1lFb2QwTFhybndjOEFSTlE?oc=5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>17-05-2026 10:03 UTC</t>
+          <t>18-05-2026 14:45 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fresubin clinical nutrition explained for US patients</t>
+          <t>Zydus Wellness confirms compliance with SEBI regulations for FY 2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVWlPVnRmVlhQNGxxdmN2eTFCWVpMemI1cFdBUzNSU1l6eEZjYWo3MFFYT0wtR0w3bFJHVFlHc09BbVRFWVJqSVIxd3NxdHA2VnI0UllVYWdSamdtUi1fRnM0bUI4cjFmMlhQUkVTcG9QLVo3aTFCWHE1clN2d0pHWW5zRDJtUzQyUmZ6djk5T3FZVnpxSHZHNzhGc29kMnZoTVg0UmMzNmpGNWJpekFzSFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV_5cTFNX2o1MjJ2anVGejd3aUQ1blJIYUFMTjA0NWNReldtRWRDYUFyTlBnVDMtTWJ0aldPc3ZMRW5Rb3lfTG4zT0JpSWRfdnpUdmtzVXFkUFdYZkJXRXdfWk1OaUx0OV9BUk5VZmtaOHBNTnB1UThMZlY1VHhGVW83UXp3Yjg1WFRtRDU5U2gwMHJkYTI3R2lKWVhvR2RKMlRYN3F5bEFZR0tfeUlEOTRwd1E?oc=5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17-05-2026 15:30 UTC</t>
+          <t>18-05-2026 13:05 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Inc., USA Launches Vancomycin Hydrochloride for Injection USP in 500 mg and 1 g Vial Strengths</t>
+          <t>Celltrion said it will respond by closely reviewing the management situation and market environment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxNb1haQk9hMG50a3FwV3pteTUycUNQRS14WTJQdlV3b0lFcWQwRTc5dm1BVXI5TmhxeDI0X1VreUFvRUpiZGw2Q29wYmY5Ny1QZERPNGxwSHlDLV9vRUZONmtXRGdPSkZFR2hIV1VKbjRGcHQzR2Jfcll1T2tPTjlTOHN5cENNck5pVmdHRWdvWmhpN09GRllNSk5nRF83ZG9QWm04YTg3bVg2ck0zYXRaa0g5bGlLbFBPNHFuUEV4dTJJTEdac25ST3ZWM0VCOEctN0ZSOWdQUEttQWgwLUtfTjVIdkkzd1dGVnhJdUhndkk3ZG9KVUI5Q2lpWlZON1RPNjJudA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FV_5cTFNvNkthSVRVZ0NtLW5rZjhoc2FOZ0hUU0xNanhRN2pGV080REJJOUVQV1V4ZVE0R1RObm5JTDhBN3QwMC1zUTdiREJjWHBVdzg?oc=5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18-05-2026 03:37 UTC</t>
+          <t>19-05-2026 01:06 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gland Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gland Pharma Q4 FY26 PAT Surges 97% YoY; Revenue Hits Record ₹64,307 Mn in FY26</t>
+          <t>Celltrion: "Stock Undervalued... Reviewing Measures to Enhance Shareholder Value with Major Shareholders"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQNDN3UU4tYUxJaE56XzNjM0FObDFUYzRjWTcxN3RBazdYVjBmTTBscUFrdkZQOWhXMmVxYkhqQTdqTFNYYkRLWmp0UHFUemtJQzZuUnBiYVhrM2dSb0oxamRlTTNPX0hCRC1vWDAzNGlCTzVlcC1MODhFenA1ZEZ4TEFVcHFzZ0VzQnIwaEZ2OTFta3lSR0JqeGluZU9iY0tNVHFmN3l1ek9vdFhyN0pfZnNueFRFQ2gyUzk3Uk4yazQ2d2FESXpha1F5a0JUUWZCcXNKZU8zU0w?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FV_5cTFPYUh0TGFJQ2k4R1N2YTlLeHZRU0xFZVo1T1RpU2xJOUQtUFBhNi05eVY2cFpVLXNydl9mUTRTVUI1emFKUGVlX2JScFZKVVp6UnRrcjYwNWZ5TlVjWEp1em1QQ2p6S1YwMDNJV0R2ZDJaNm8?oc=5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17-05-2026 15:24 UTC</t>
+          <t>19-05-2026 02:06 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1744,59 +1744,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alvotech (NasdaqGM:ALVO) Valuation Check After FDA Form 483 And Reaffirmed Approval Timelines</t>
+          <t>Celltrion Pharm boosts Korea liver drug lead with 7.4b won prescriptions - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQWC1ybE1FalB5bXRoeU9rN2M5RGlwX21Kc1hfU1pENDFWU3RtZDhIMl9OWUJLMW91c3BIX0cwYlRDOU56V3gwNExlR1lRR2ZNY1B2Uk9MQ2E0Q28ybzdkRzRONTJ6aFp6WmFDMXJ0Y296YUFsSHhNTDlEREhiNmgwcENuRlJobHB0c3ptOVo0aDYzQnRiUWhhRmlpMTNVUGUzX1J3X0YyQ1BENkk0WXpzdUVreVFXclVNbzFiY3V5eVhLWVM3M0FYYWV5WGhJWkZCMHZHZXMtUTFod9IB3wFBVV95cUxPNUlXRzlwWTI1cy1lSzN2dDdCR2xLWmtBOHh0eFZqanBud3hWWDJldHhaSHpWcjZHcU1uQlZ2NmVUTml5QUh4UFlUMmkwajlhRTJCcXRBS1NZbmJkQnVXckxKS3htZi03cTlsZ3VGNHNweUE0ZW5XaW95cE13UFpOSnBlWlE3ZlhSUW1CVFl6S2ZyeTI2YnN0cjBjQUFDbmN2V3h6Z1FrY1Fzb1FxY0RIcTU3aThzMDNkVXNLVTNUMjJFTlYyS1QzSVVqNGtsY1NoT1lJSFpMNWJyU24zV093?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV_5cTFQTVRjcTJvNHRIdGNSaHZDcUVocGFlenNZUGRSeXpkLXUwZF9pd0pVeWNlQUxwMXVncllTcXRlc05LQnRtdWNaTEZoV2lRWmxEZldET2pWc05lLW0wNTFLZ20xU1gwMmRPREdsTDdnTmxNZE5ld092YW1yVWZoRUNFYdIBlAFBVV_5cTFQZm1yem9OeUZ2WndFYnJzbWpRMDNLQUdfZ2F6aGdaMjhReUFwWGV5MmRLYTVuMjdMRFB1VENJd0s2b2oyUWxfZ0tON1NOaWJwcUJyeVdvZk42Ukx5WFhIVXE3aGlnYVRwTGVWcElsdkJkZWhxTEFpYk5pRk5OQkZlSC14LW9MbVFCS3pSR1JtNUV1bUpq?oc=5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17-05-2026 07:37 UTC</t>
+          <t>19-05-2026 00:09 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical stock (US88162G1031): new weight?loss strategy and Q1 results put focus on turna</t>
+          <t>Celltrion Pharm's Godex Maintains Top Spot in Outpatient Liver Medication Market for Over 10 Years</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOcDZGYW5MRHFpSkRQc0VOZENZMWktcTFScHZtTDlDWnQ1QnZ1cnZNT0RkT3pyZ1BkNE9YV29QNnRWTldkN2Z6ZEViUDR1RGVGMzlDbjJ1azdxYXJhU0FTT0JudVJmZjg3SUdjTlJON0VlQ2wwN1MtcHluNXhSQkRqWE9wOThpRlRyb1VEeEFhamphYVdUaEQtSk5KQURDY3dZS2MxLXRON25NMlVsVGdDeVdpbVZ3UWJXRlFEMHJoV285eWxoanliNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FV_5cTFPYh4xcy1TYXBaMzhFNDR5M0VjS3NldmlvMVVULVZjV3F1em9KQUJqZ3FEeE5RMGZnaGpWT0tQQlNvQnZ2YVotYm1tVEZGbmJpNUdtbW1Oc2RNT1FqdGRsalNJdl_5aDJiQWFRdUduQlFJQmhCbVU?oc=5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17-05-2026 17:06 UTC</t>
+          <t>19-05-2026 00:09 UTC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1808,126 +1808,414 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A Look At Teva Pharmaceutical Industries (NYSE:TEVA) Valuation After A Strong Year And Recent Pullback</t>
+          <t>Celltrion is expanding its influence in the Japanese biosimilar market with anticancer drugs and aut..</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sahm</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNRWtrMlUwZzdPNHRIWEQ5bUZGNDFtY3I4V2k4RGlsdS1pTEZ4QnFlNzFqRkZfckZ2Njl0Z1Fjc1JycEJwYUZXVzJOb0NWZzFyXzZkTVRjczc3amhEODBHR1d6SDBPLVI0LUkxNVJ5N2t3R0hTYmkzbjVUQlg5LTJrXzZXNlFGdzFvX0t5Y0hJMV91Z0hyLV8zVjdaaURvNlJORW9DLTRWSnBOS0RQNWdzLTZzRVJKOHVHUnZETUpWZkYxV0dMV0tMa3U4VXZlNlk0UWJHUHdzMmtqOGktQW1fd0pwN010QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS1FV_5cTNO3E3MzJSYV9OZndTbXFoYWlRX1lpZm02ZXktRFRqSGJrbW1HUWxKcE5IN0JsU0xaQVplTnVYSVFva2RQNmp2aFI5Yw?oc=5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17-05-2026 06:19 UTC</t>
+          <t>18-05-2026 06:14 UTC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wall Street Thinks Teva Stock Still Has Room to Run After Soaring Over 100%. Here's Why Analysts Are Right.</t>
+          <t>AstraZeneca And Daiichi Sankyo Expand ENHERTU Into Early HER2 Positive Breast Cancer Treatment In The US</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE82X3RIZjJ4MGdwdThuX194S1JwN3RSd25jVEhJYmpJMmRuSmpBazI2c1NwSVdsSTdBeVA0Si1kN0JjVXEwb2w5MUFMbVlvN2p4aUpFOW0tLTV3MHl5bzZ1bzlqa1NDdkRQT0RLeEVCbkNqQzdPYkFIT1hhWG9VUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV_5cTFPQVpQUjl5clNxX0Jia0cyVm1pZ2lkQkRHRXdaSGRNVHVVd1dKSWw2LTVNTjVSTS1NcFVHLXh0aHNRM3M3SG80WWV6MnMzemVjTEowQ2NCVU1WSlVVRFZGXzNOd3NWaWxMcFlXLXJyY1NyX2I4bmNKTGx0TG1CYkVyTFhiMXZ4dy1pV215LVFrU3hUSFFQLUdtdlE2WGJBcFVrd0xOTGFxQ0d5dkdKckh0T2RlN0lLRm1zRFBPd290UzFqSWJxTFVrbS1GRUFRY2VqR0VCOGZ2Sno2VnBNdDhTYmxR?oc=5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17-05-2026 16:29 UTC</t>
+          <t>19-05-2026 00:07 UTC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Samsung Bioepis</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Samsung Bioepis presents real-world Humira biosimilar data at KCR 2026</t>
+          <t>AstraZeneca To Pay $155 Million Milestone To Daiichi Sankyo After US Approvals</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZ9IBckFVX3lxTE00cGZOLTBldkEyMnJqcWViV3ByUjR3R1BYQVNTU0lXdXVjXzlRSXY2aDlJU3JfZ25DYS1pVHROTU4wRVhFQ2p4V2hHSGUtXzJaQ1QzeVdLaVVBa3k5TU5tQ3Ftd05weVd3eTRIWUJoQ2UyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV_5cTFPVU16VGpjMnhVNnhmaHNNeGVIWTZtNnJfN0JqTENIYlBfNmNhazNCLWFvanpOcHlRU2YwbnBicDcxZFZwaEd1M0RSdnVKYWRqUTFCWUNlYjA0XzBTcTYtNmMzb0FwRDhPWkl6NzlmQm9iZFB2QWxkZ3RJUUo2NHRaSWNqbjM2VW5Kc043Y2tKSFl0T3BmQjlOQzNLS2VhWVNrWldkSnREVzBWTE4xZThGNmo0d1hvNWVmVWFzeVZ6dE93cW44QmczVk9ENkh5V3g3aldoQkoxQWd6eFRyM3pKZg?oc=5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18-05-2026 02:58 UTC</t>
+          <t>18-05-2026 06:27 UTC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ENHERTU’s Early Breast Cancer Approval Might Change The Case For Investing In Daiichi Sankyo Company (TSE:4568)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV_5cTNOVTh4aVJvdWZDN2VwMkhLbURjVHFnc1RLTWl1cEtTQmRBeVVVQ2ZTOTZiN2VQSWtoemItT3JHcXZDZFRFSExYYS1jaEFaNFR4cnRlalZQTUhVRWk2U3VLZ0NzbU5tR1cwV3Q2SnFYN29BZzhDMENmSFV5d3ByaWROcEdZVTdGTFNhVTZKMWJqVHplaHFVcEoyMmhjVlpoRVJEVXlES2drb1VjUVRNSW83R0NDNVdqUHhmVlZEeEY1aGpfVUZxZ3B4ZXZsdW9PVXBaSFRYWVEzeFY5UEdXS3FNSlBjdC1ISVZ4N25N0gHrAUFV_5cTNOVTh4aVJvdWZDN2VwMkhLbURjVHFnc1RLTWl1cEtTQmRBeVVVQ2ZTOTZiN2VQSWtoemItT3JHcXZDZFRFSExYYS1jaEFaNFR4cnRlalZQTUhVRWk2U3VLZ0NzbU5tR1cwV3Q2SnFYN29BZzhDMENmSFV5d3ByaWROcEdZVTdGTFNhVTZKMWJqVHplaHFVcEoyMmhjVlpoRVJEVXlES2drb1VjUVRNSW83R0NDNVdqUHhmVlZEeEY1aGpfVUZxZ3B4ZXZsdW9PVXBaSFRYWVEzeFY5UEdXS3FNSlBjdC1ISVZ4N25N?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19-05-2026 01:45 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>New Dosing Option Okayed for X-Linked Hypophosphatemia Drug</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Medscape</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV_5cTFPSElaYWdneXF0Mk5zVnFxckplSVVpaXZRN0g2OEJhOUpnYWcxYkV5TnctcHRBRGxXS0xsQ3huZVVqQlBhWVdLa1lSV0dIVXVYQV9vQWJLem1rQnRjWDFWUDVEemU2MW1GMU5qVEF0QkVJUzV4WE9zSnBCOHBjQk5TOUVDTFRaYjBTZnVrUl9KZWVvVVJzaFhtWHJ0U3o2VkpZREZZY2dMNkRWOA?oc=5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>18-05-2026 19:06 UTC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>JCR Pharma</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JCR Pharmaceuticals Presents Preclinical Gene Therapy Data that Demonstrate Promising Central Nervou</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PharmiWeb.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV_5cTFNNDR3aERna2lIdFBSRUFjdTR5MDhtWkd2UWw5WE1TNzRvQU9DZmhNdV9LeUxWZXZSSmdIM1RqTHVITXhhYnhPS0xWcHpxTWRPVjd6cEpQVmR3QkFIZUdVQ1Rqbi1sbTM5VW41S3ZYWkdmQkQzYWdTTEF4aTlodzRjakVCUWE3aWtIZkRwSjVfb2JLNEt1NENHY042WjlWS3Z4cFVvb1lGbC1pQV9NMnRicHpjZ05tRmxRYkM0UHlTVTdUV0lUSGttSmlOOFRMVmhxcXZycmpWYUVldWZTMDB2RXpmUXBidw?oc=5</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>18-05-2026 20:30 UTC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MS Pharma Announces Strategic Growth Investment from Olayan Financing Company</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV_5cTFPQzE2dXZfNXFIQkx3RW5Zekx3QklhRlVJSzBiSmR6X0ZuamdhcXZJbndOOXBURU1aOWI2bXQ5bk5DWHJqZGhndmZ6a0RxTWh6LVFRRnV0UzY2UUt1UU1_5dThVSVh1ZURBcmxqQ2ZrazZtRUJGMldfenk2QnlZeEN0dHc0MHFxbkd2UURCd3hrM2EtUDFtY3pZMzE0Q0xhQU5zZmc5V2o3SFhBdG9CeXJxQTN3aWt1STg0RmtmYXUxOTY0ZzVUN2htWWxkbFRaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:52 UTC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alvotech stock (LU2557688560): latest FDA approval progress and biosimilar pipeline in focus</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV_5cTFPOGhWOTFuM3JscWQ5WDlSRnhzT3Q2Z3RoSWlJYW1Nc0RvWFRCOEhzZ1FKMHV6emJCcEZPU1Y5MHYwVWFpRjcxeEdfeWt2SFFNS1FpT2c1WVdDdUhUdUZUWEZzLUdydm9QdHBFOTJSb25RTEVCRmo3N1dCZk1pY3Q0UzBSMHJTUUxlSTVIUHVnZGdXS3hNbndDYURZZUpfYkdldEpfcjQtOHMxS3BvWVpwRlBNNTZ0M0wyTDYtVXJ3bkNrUnFyeWdoYmdB?oc=5</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>18-05-2026 11:17 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Teva regains investment-grade rating from Fitch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ynetnews</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFV_5cTFA1Y1lCLUFEXzdEZDB6ODliQVpsVnFLLXlEb1hFbkpwOVB1cWU4Z1ZoVjh6NzFZZ0tyR21odlVmMDBiZjI0NzhSRGFhVnluTmFISUFaamp2dDlnVGp3YXJfbWFB?oc=5</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>18-05-2026 19:13 UTC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Teva reports diagnostic gap in tardive dyskinesia patients</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV_5cTFPVHpNOXhfaWFkMlNWcFpqeFRxdENQSzVNNUN4M3hubVVKcWt0U2VCb2RBaU9WWExFWjVSYjhoNldOWU44eVpSd2dRN0pJMzVRM0JYeTg3NHgxRkEyWGpuMmRVTW9Ubm55YWIwdERDSmhsS1dVa3AwMHFZVXdBSTlHU1lyeHhfbnlsaTN2Um40eHk0M2w0b1NXa2dkX3hBRXNodndnMUUxRk5oVXVIU0RvTll2M1VWUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18-05-2026 12:30 UTC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical Industries Insider Sold Shares Worth $5,457,375, According to a Recent SEC Filing</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV_5cTFNFdDI0aTBsQkpHQTNLYkgwaXV1SmpZZ1_5lEY3SEtscXV6bzA5dEplVHUyd0JnWTlaTDlMRlotVlBuOE4yUFpuWUpaOEJ3Q2dfR3RpS2h4MUFmTjNONkZmRFFKa1BNM0xycXU5bUE0U0wzLXBTWnlBXzFuWXN3N3lyczJzRTRZcXBHRlF0dEhkM25BOW0xWHRCQUJKblJ2WTYzam13bV_tWERicW9TUVM3eEpWRmxVSEh3UlN5SGpXVm9xa3o1ZDdzdzlFWU5iMnF3NUZpYkl1ejdXNmdlWk1EQU94a1kxUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>18-05-2026 20:20 UTC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Teva, Granules, Heritage $5.55M Metformin Settlements</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Claim Depot</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FV_5cTFPNaGhIMlpjUncxaVdHTnd1RUtxdUxrWkszWk50ZUwyWURYNG1pVnVJQVZ5X1dDZHc4RmlMdnVWeEhsTVI1YkdzS2pLbkwtVXVDSXgyWlF6QTcwdmJCX3dWYlJQRjU1X3ZCNTEyV1VMVl9QcTA?oc=5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>18-05-2026 13:05 UTC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Samsung Bioepis touts Adalloce data improving quality of life, confirming safety in Korea - CHOSUNBIZ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Chosunbiz</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPRUpwdnFMLWFRWTdKWmZkUjY0TG5INWN3MUVtZHYyQkRnZXFPX1VmVUc1UkRNMWplc0lscW9DUjNhZUdJSDhRLWF5dWxTT0s1UWk5dWplLU1JUmJBeDBObkJHM1ItN2JBVFA3RzVKWTlKek9vY2VkaWdndi1teENwNdIBlAFBVV95cUxNQTNDSl9lczBtSmszNzBUcnRrOVZrZU5BeEs2bTdGM3RpQkxIWnNqVndSeDVYZTN1dWc5T0hkYUlmcFl4N2llY3IydVhyYWtlQ2RzRk4xek1DX1E3Mld0R00xV2tYam96Uzgxbm94S0tlNHVhajFyTkJjV1Jwc1pqSU5rczM3X1AxaXh0QWxQaTNGaXlLdXM?oc=5</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>18-05-2026 00:03 UTC</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis Confirms Quality-of-Life Gains, Safety of Adalimumab Biosimilar Adaloce</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV_5cTFNcVd5UTNJNW01NmVJSHZtWmM1dmRzR002Vk0wQjRVX0hTc01XM2lHbjFyTFd5WUtVajlWcnNZeldZVHMyRTVnX1hiYWZwMEhSOEtNb2g4LXplZ0FFbE1GdVVmbGQ1ZUtocUU4Sy0zOU9FdU00T0otUGlOa182ekIxV2MzWUZZQ1dHVFRFMUtwYjJTYzhoWXlUaFZFQUo3QVE?oc=5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>18-05-2026 07:10 UTC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Clinical Trial</t>
         </is>
@@ -1957,7 +2245,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-05-2026 09:53:50</t>
+          <t>19-05-2026 10:28:49</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,96 +496,96 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eqs-News Formycon Aflibercept Biosimilars Ahzantive® And Baiama® Are Now Available In The European Union</t>
+          <t>Biosimilar Streamlining Means All Should ‘Reach The Fruits’</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/reuters.com,2026:newsml_FWN41V1HM:0-eqs-news-formycon-aflibercept-biosimilars-ahzantive-and-baiama-are-now-available-in-the-european-union/</t>
+          <t>https://insights.citeline.com/in-vivo/biosimilar-streamlining-means-all-should-reach-the-fruits-O65JTY5UAFFP7KDHOWXXWTNWAA/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19-05-2026 04:33 UTC</t>
+          <t>19-05-2026 10:57 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gedeon Richter</t>
+          <t>Formycon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Streamlined Biosimilar Guidelines A Fillip For Hungary’s Richter</t>
+          <t>Eqs-News Formycon Aflibercept Biosimilars Ahzantive® And Baiama® Are Now Available In The European Union</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/streamlined-biosimilar-guidelines-a-fillip-for-hungarys-richter-N47ONTCEQVG2FOR33DDU44NTXU/</t>
+          <t>https://www.tradingview.com/news/reuters.com,2026:newsml_FWN41V1HM:0-eqs-news-formycon-aflibercept-biosimilars-ahzantive-and-baiama-are-now-available-in-the-european-union/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19-05-2026 10:42 UTC</t>
+          <t>19-05-2026 04:33 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Gedeon Richter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Japan’s MHLW approves Boehringer’s Jascayd for IPF and PPF</t>
+          <t>Streamlined Biosimilar Guidelines A Fillip For Hungary’s Richter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/japans-mhlw-boehringers-jascayd-approval/</t>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/streamlined-biosimilar-guidelines-a-fillip-for-hungarys-richter-N47ONTCEQVG2FOR33DDU44NTXU/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19-05-2026 08:15 UTC</t>
+          <t>19-05-2026 10:42 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -597,27 +597,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supreme Court declines to hear IRA challenges from Novo, AZ and more</t>
+          <t>Japan’s MHLW approves Boehringer’s Jascayd for IPF and PPF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/amid-spate-trump-drug-pricing-deals-supreme-court-declines-hear-ira-challenges-novo-az-and</t>
+          <t>https://www.pharmaceutical-technology.com/news/japans-mhlw-boehringers-jascayd-approval/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18-05-2026 19:06 UTC</t>
+          <t>19-05-2026 08:15 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -629,86 +629,86 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>opnMe online seminar: Illuminating SYK function through independent research</t>
+          <t>SYNCHRONIZE-1: Survodutide Achieves Significant Weight Loss Versus Placebo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>idw – Informationsdienst Wissenschaft</t>
+          <t>HCPLive</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://idw-online.de/de/event81596</t>
+          <t>https://www.hcplive.com/view/synchronize-1-survodutide-achieves-significant-weight-loss-versus-placebo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19-05-2026 00:00 UTC</t>
+          <t>19-05-2026 16:04 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): guidance upgrade and FDA progress put focus on growt</t>
+          <t>U.S. Supreme Court Declines to Hear Pharma Challenge to IRA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>NAVLIN DAILY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-guidance-upgrade-and-fda/69369644</t>
+          <t>https://www.navlindaily.com/article/30573/u-s-supreme-court-declines-to-hear-pharma-challenge-to-ira</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19-05-2026 02:36 UTC</t>
+          <t>19-05-2026 08:30 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When a Common Disease Becomes a Rare Journey: Understanding Uncontrolled Gout</t>
+          <t>Cattle farmers face a new era in worm control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Agriland</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.amgen.com/stories/2026/05/when-a-common-disease-becomes-a-rare-journey-understanding-uncontrolled-gout</t>
+          <t>https://www.agriland.ie/farming-news/cattle-farmers-face-a-new-era-in-worm-control/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19-05-2026 05:35 UTC</t>
+          <t>19-05-2026 07:50 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -720,27 +720,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Biopharma bites: IRA is here to stay, plus more safety concerns for Amgen's Tavneos</t>
+          <t>opnMe online seminar: Illuminating SYK function through independent research</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>idw – Informationsdienst Wissenschaft</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7445196</t>
+          <t>https://idw-online.de/de/event81596</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19-05-2026 00:23 UTC</t>
+          <t>19-05-2026 00:00 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -752,12 +752,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): focus on Horizon integration and latest quarterly results</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): guidance upgrade and FDA progress put focus on growt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-inc-stock-us0311621009-focus-on-horizon-integration-and-latest/69366570</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-guidance-upgrade-and-fda/69369644</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18-05-2026 14:37 UTC</t>
+          <t>19-05-2026 02:36 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -784,44 +784,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): recent AGM update and focus on injectable growth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-recent-agm-update-and/69367834</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19-05-2026 04:35 UTC</t>
+          <t>18-05-2026 19:27 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Seagen stock (US8166361055): what the Pfizer takeover means for investors after delisting</t>
+          <t>Amgen stock (US0311621009): focus on obesity data and pipeline as investors await next catalysts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -831,204 +831,204 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/seagen-stock-us0311621055-what-the-pfizer-takeover-means-for-investors/69371827</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-stock-us0311621009-focus-on-obesity-data-and-pipeline-as/69375321</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19-05-2026 08:13 UTC</t>
+          <t>19-05-2026 17:22 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pfizer Limited Annual Secretarial Compliance Report for FY 2025-26</t>
+          <t>When a Common Disease Becomes a Rare Journey: Understanding Uncontrolled Gout</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/pfizer-limited-annual-secretarial-compliance-filing/</t>
+          <t>https://www.amgen.com/stories/2026/05/when-a-common-disease-becomes-a-rare-journey-understanding-uncontrolled-gout</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19-05-2026 10:00 UTC</t>
+          <t>19-05-2026 05:35 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pfizer (NYSE: PFE) CEO receives 24 phantom stock units in deferred plan</t>
+          <t>Biopharma bites: IRA is here to stay, plus more safety concerns for Amgen's Tavneos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stock Titan</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.stocktitan.net/sec-filings/PFE/form-4-pfizer-inc-insider-trading-activity-5ae7d4ace4fb.html</t>
+          <t>https://firstwordpharma.com/story/7445196</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18-05-2026 20:39 UTC</t>
+          <t>19-05-2026 00:23 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pfizer and Aristotle University bet on Thessaloniki as a digital health hub with new agreement</t>
+          <t>Amgen Inc. stock (US0311621009): weight-loss data and earnings keep biotech in focus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Voria</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.voria.gr/index.php/article/pfizer-and-aristotle-university-bet-thessaloniki-digital-health-hub-new-agreement</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-inc-stock-us0311621009-weight-loss-data-and-earnings-keep/69374326</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19-05-2026 13:06 UTC</t>
+          <t>19-05-2026 14:25 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Immunic appoints Biogen, Cubist veteran Mike Bonney as board chair ahead of key MS trial readout</t>
+          <t>Next in ingestible beauty: Plant-based enzyme boosts skin’s natural antioxidant defenses</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Proactive financial news</t>
+          <t>Nutrition Insight</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.proactiveinvestors.com/companies/news/1092532/immunic-appoints-biogen-cubist-veteran-mike-bonney-as-board-chair-ahead-of-key-ms-trial-readout-1092532.html</t>
+          <t>https://www.nutritioninsight.com/news/beauty-supplements-collagen-skincare-dermatology-glisodin.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19-05-2026 13:33 UTC</t>
+          <t>19-05-2026 12:27 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biogen completes acquisition of Apellis Pharmaceuticals</t>
+          <t>Pfizer, Moderna COVID vaccines 70% to 76% effective against severe illness in kids in 2022, data suggest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ophthalmology Times</t>
+          <t>cidrap.umn.edu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.ophthalmologytimes.com/view/biogen-completes-acquisition-of-apellis-pharmaceuticals</t>
+          <t>https://www.cidrap.umn.edu/covid-19/pfizer-moderna-covid-vaccines-70-76-effective-against-severe-illness-kids-2022-data</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18-05-2026 15:52 UTC</t>
+          <t>19-05-2026 18:14 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Investigation launched into Biogen after Alzheimer's drug trial misses key goal, stock drops sharply.</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pluang</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pluang.com/en/news-feed/biogen-inc-investigasi-pelanggaran-hukum-sekuritas</t>
+          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18-05-2026 18:17 UTC</t>
+          <t>19-05-2026 04:35 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1040,187 +1040,187 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biogen stock (US09062X1037): Alzheimer’s focus after Leqembi setback and pipeline updates</t>
+          <t>Posts linking Covid jabs to hantavirus misuse Pfizer, WHO documents</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>AFP Fact Check</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/biogen-stock-us09062x1037-alzheimer-s-focus-after-leqembi-setback-and/69369903</t>
+          <t>https://factcheck.afp.com/doc.afp.com.B2964NQ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19-05-2026 03:12 UTC</t>
+          <t>19-05-2026 03:01 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apellis Stock Delisted From Nasdaq, Focus Turns to $4 Payout</t>
+          <t>Pfizer Limited Annual Secretarial Compliance Report for FY 2025-26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TechStock²</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://ts2.tech/en/nab-share-price-slides-again-as-asx-rout-puts-big-bank-risk-back-in-focus/</t>
+          <t>https://www.investywise.com/pfizer-limited-annual-secretarial-compliance-filing/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18-05-2026 16:50 UTC</t>
+          <t>19-05-2026 10:00 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delhi High Court Upholds Dr. Reddy's Rights Over “REDDY” Mark, Rejects Acquiescence Defence</t>
+          <t>Seagen stock (US8166361055): what the Pfizer takeover means for investors after delisting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LiveLawBiz</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.livelawbiz.com/amp/trademark/delhi-high-court-upholds-permanent-injunction-against-reddy-pharmaceuticals-in-dr-reddys-laboratories-trademark-dispute-534797</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/seagen-stock-us8166361055-what-the-pfizer-takeover-means-for-investors/69371827</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19-05-2026 10:06 UTC</t>
+          <t>19-05-2026 08:13 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4FY26 Net Profit Plunges 86% to ₹220 Cr on One-Time Charges</t>
+          <t>Pfizer Takes Aim at Merck in New Phase 3 Endometrial Cancer Trial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-q4-results-net-profit-declines-to-2-21b-rupees-yoy-board-recommends-8-final-dividend/40144336</t>
+          <t>https://www.tipranks.com/news/company-announcements/pfizer-takes-aim-at-merck-in-new-phase-3-endometrial-cancer-trial</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18-05-2026 20:18 UTC</t>
+          <t>19-05-2026 16:44 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI</t>
+          <t>Pfizer and Aristotle University bet on Thessaloniki as a digital health hub with new agreement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>Voria</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/PRNewswire/Bio-Thera+Solutions+Golimumab+Biosimilars+Receive+FDA+Approval+as+First+Biosimilars+to+Simponi%C2%AE+and+Simponi+Aria%C2%AE%3B+Accord+BioPharma+to+Commercialize+IMMGOLIS%E2%84%A2+%28golimumab-sldi%29+and+IMMGOLIS+INTRI%E2/26510377.html</t>
+          <t>https://www.voria.gr/index.php/article/pfizer-and-aristotle-university-bet-thessaloniki-digital-health-hub-new-agreement</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19-05-2026 02:56 UTC</t>
+          <t>19-05-2026 13:06 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Accelerating Development Of A Unique Molecule To Treat Lung Cancer</t>
+          <t>Biogen stock (US09062X1037): Alzheimer’s focus after Leqembi setback and pipeline updates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bioprocess Online</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.bioprocessonline.com/doc/accelerating-development-of-a-unique-molecule-to-treat-lung-cancer-0001</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/biogen-stock-us09062X1037-alzheimer-s-focus-after-leqembi-setback-and/69369903</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18-05-2026 23:23 UTC</t>
+          <t>19-05-2026 03:12 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1232,155 +1232,155 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Extinguishes 54,23,728 Equity Shares Under ₹800 Crore Buyback Programme</t>
+          <t>Biogen Faces Legal Scrutiny After Diranersen Trial Results, Stoc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-extinguishes-54-23-728-equity-shares-under-800-crore-buyback-programme/40700416</t>
+          <t>https://www.gurufocus.com/news/8866732/biogen-faces-legal-scrutiny-after-diranersen-trial-results-stock-drops-biib?mobile=true%3Fmobile%3Dtrue&amp;mobile=true%3Fmobile%3Dtrue%3Fmobile%3Dtrue&amp;mobile=true&amp;mobile=true</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19-05-2026 01:44 UTC</t>
+          <t>18-05-2026 20:23 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Buyback Record Date 2026, Acceptance Ratio, Profit Guidance</t>
+          <t>Biogen’s Apellis Deal And Alzheimer’s Trial Shift Focus Beyond Price</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IPO Central</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://ipocentral.in/zydus-lifesciences-buyback-record-date-2026-price/</t>
+          <t>https://finance.yahoo.com/sectors/healthcare/articles/biogen-apellis-deal-alzheimer-trial-191746426.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19-05-2026 11:16 UTC</t>
+          <t>18-05-2026 19:17 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Q4 and Full Year FY26 Earnings Highlights</t>
+          <t>Dr Reddy's Wins Higher Target As HSBC Backs Its Global Expansion Strategy — Details Inside</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/zydus-lifesciences-strong-q4-fy26-results-and-buyback-announcement/</t>
+          <t>https://www.ndtvprofit.com/markets/dr-reddys-wins-higher-target-as-hsbc-backs-its-global-expansion-strategy-details-inside-11514943</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19-05-2026 08:50 UTC</t>
+          <t>19-05-2026 02:32 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Assertio Therapeutics to be acquired by Zydus Worldwide</t>
+          <t>Delhi High Court Upholds Dr. Reddy's Rights Over “REDDY” Mark, Rejects Acquiescence Defence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>LiveLawBiz</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/assertio-therapeutics-to-be-acquired-by-zydus-worldwide-2</t>
+          <t>https://www.livelawbiz.com/amp/trademark/delhi-high-court-upholds-permanent-injunction-against-reddy-pharmaceuticals-in-dr-reddys-laboratories-trademark-dispute-534797</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18-05-2026 14:45 UTC</t>
+          <t>19-05-2026 10:06 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zydus Wellness FY26 revenue climbs to Rs. 39.4 billion</t>
+          <t>Dr Reddy's Q4FY26 Net Profit Plunges 86% to ₹220 Cr on One-Time Charges</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/zydus-wellness-fy26-revenue-climbs-to-rs-394-billion-20244</t>
+          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-q4-results-net-profit-declines-to-2-21b-rupees-yoy-board-recommends-8-final-dividend/40144336</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19-05-2026 02:04 UTC</t>
+          <t>18-05-2026 20:18 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1392,219 +1392,219 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hetero Biopharma</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Annora Pharma expands collaboration with AI-native traceability platform AltiusHub</t>
+          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BioSpectrum India</t>
+          <t>StreetInsider</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.biospectrumindia.com/news/16/27833/annora-pharma-expands-collaboration-with-ai-native-traceability-platform-altiushub.html</t>
+          <t>https://www.streetinsider.com/PRNewswire/Bio-Thera+Solutions%27s+Golimumab+Biosimilars+Receive+FDA+Approval+as+First+Biosimilars+to+Simponi%C2%AE+and+Simponi+Aria%C2%AE%3B+Accord+BioPharma+to+Commercialize+IMMGOLIS%E2%84%A2+%28golimumab-sldi%29+and+IMMGOLIS+INTRI%E2/26510377.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19-05-2026 06:48 UTC</t>
+          <t>19-05-2026 02:56 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): biosimilar specialist in focus after recent earnings and pipelin</t>
+          <t>Biosimilar Streamlining Means All Should ‘Reach The Fruits’</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/celltrion-inc-stock-kr7068270008-biosimilar-specialist-in-focus-after/69371623</t>
+          <t>https://insights.citeline.com/in-vivo/biosimilar-streamlining-means-all-should-reach-the-fruits-O65JTY5UAFFP7KDHOWXXWTNWAA/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19-05-2026 07:34 UTC</t>
+          <t>19-05-2026 10:57 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Celltrion said it will respond by closely reviewing the management situation and market environment</t>
+          <t>Aurobindo Pharma Extinguishes 54,23,728 Equity Shares Under ₹800 Crore Buyback Programme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/stock/12051778</t>
+          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-extinguishes-54-23-728-equity-shares-under-800-crore-buyback-programme/40700416</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19-05-2026 01:06 UTC</t>
+          <t>19-05-2026 01:44 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Celltrion Pharm boosts Korea liver drug lead with 7.4b won prescriptions - CHOSUNBIZ</t>
+          <t>Zydus Lifesciences to pursue acquisitions in specialty, rare diseases</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/05/19/HGQ5R2S55BDQ5N2XGMX4FJIYPA/</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/zydus-lifesciences-to-pursue-acquisitions-in-specialty-rare-diseases/articleshow/131205005.cms</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19-05-2026 00:09 UTC</t>
+          <t>19-05-2026 15:28 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo charts aggressive oncology expansion with $14.6bn target by 2030</t>
+          <t>Zydus Lifesciences Buyback Record Date 2026, Price, Entitlement Ratio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BioXconomy</t>
+          <t>IPO Central</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.bioxconomy.com/investment/daiichi-sankyo-charts-aggressive-oncology-expansion-with-14-6bn-target-by-2030</t>
+          <t>https://ipocentral.in/zydus-lifesciences-buyback-record-date-2026-price/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19-05-2026 09:49 UTC</t>
+          <t>19-05-2026 11:16 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AstraZeneca And Daiichi Sankyo Expand ENHERTU Into Early HER2 Positive Breast Cancer Treatment In The US</t>
+          <t>Zydus Lifesciences Q4 and Full Year FY26 Earnings Highlights</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/73/7951/astrazeneca-and-daiichi-sankyo-expand-enhertu-into-early-her2-positive-breast-cancer-treatment-in-the-us.html</t>
+          <t>https://www.investywise.com/zydus-lifesciences-strong-q4-fy26-results-and-buyback-announcement/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19-05-2026 02:15 UTC</t>
+          <t>19-05-2026 08:50 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Full Year 2026 Daiichi Sankyo Co Ltd Earnings Presentation Transcript</t>
+          <t>Zydus Wellness FY26 revenue climbs to Rs. 39.4 billion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/stock/DSKYF/transcripts/8867432</t>
+          <t>https://www.indianpharmapost.com/news/zydus-wellness-fy26-revenue-climbs-to-rs-394-billion-20244</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19-05-2026 04:55 UTC</t>
+          <t>19-05-2026 02:04 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1616,219 +1616,219 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENHERTU’s Early Breast Cancer Approval Might Change The Case For Investing In Daiichi Sankyo Company (TSE:4568)</t>
+          <t>Celltrion Inc stock (KR7068270008): biosimilar specialist in focus after recent earnings and pipelin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/jp/pharmaceuticals-biotech/tse-4568/daiichi-sankyo-shares/news/enhertus-early-breast-cancer-approval-might-change-the-case/amp</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/celltrion-inc-stock-kr7068270008-biosimilar-specialist-in-focus-after/69371623</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19-05-2026 01:45 UTC</t>
+          <t>19-05-2026 07:34 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): US drug approvals trigger milestone payment and fresh attentio</t>
+          <t>Celltrion said it will respond by closely reviewing the management situation and market environment</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>매일경제</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/astrazeneca-plc-stock-gb0009895292-us-drug-approvals-trigger-milestone/69369988</t>
+          <t>https://www.mk.co.kr/en/stock/12051778</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19-05-2026 03:23 UTC</t>
+          <t>19-05-2026 01:06 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New Dosing Option Okayed for X-Linked Hypophosphatemia Drug</t>
+          <t>Celltrion: "Stock Undervalued... Reviewing Measures to Enhance Shareholder Value with Major Shareholders"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>아시아경제</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>http://www.medscape.com/viewarticle/new-dosing-option-okayed-x-linked-hypophosphatemia-drug-2026a1000g2u</t>
+          <t>https://www.asiae.co.kr/en/article/bio-health/2026051911060545512</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18-05-2026 19:06 UTC</t>
+          <t>19-05-2026 02:06 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JCR Pharmaceuticals Presents Preclinical Gene Therapy Data that Demonstrate Promising Central Nervou</t>
+          <t>Celltrion Pharm boosts Korea liver drug lead with 7.4b won prescriptions - CHOSUNBIZ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PharmiWeb.com</t>
+          <t>Chosunbiz</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pharmiweb.com/press-release/2026-05-18/jcr-pharmaceuticals-presents-preclinical-gene-therapy-data-that-demonstrate-promising-central-nervou</t>
+          <t>https://biz.chosun.com/en/en-science/2026/05/19/HGQ5R2S55BDQ5N2XGMX4FJIYPA/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18-05-2026 20:30 UTC</t>
+          <t>19-05-2026 00:09 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fresubin nutrition products: how Fresenius Kabi supports recovery</t>
+          <t>Daiichi Sankyo charts aggressive oncology expansion with $14.6bn target by 2030</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioXconomy</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresubin-nutrition-products-how-fresenius-kabi-supports-recovery/69373100</t>
+          <t>https://www.bioxconomy.com/investment/daiichi-sankyo-charts-aggressive-oncology-expansion-with-14-6bn-target-by-2030</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19-05-2026 11:19 UTC</t>
+          <t>19-05-2026 09:49 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): dividend season and restructuring keep DAX healthcare</t>
+          <t>AstraZeneca And Daiichi Sankyo Expand ENHERTU Into Early HER2 Positive Breast Cancer Treatment In The US</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>BioPharma APAC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresenius-se-and-co-kgaa-stock-de0005785604-dividend-season-and/69371730</t>
+          <t>https://biopharmaapac.com/news/73/7951/astrazeneca-and-daiichi-sankyo-expand-enhertu-into-early-her2-positive-breast-cancer-treatment-in-the-us.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19-05-2026 07:56 UTC</t>
+          <t>19-05-2026 02:15 UTC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MS Pharma announces strategic growth investment from Olayan Financing Company</t>
+          <t>Full Year 2026 Daiichi Sankyo Co Ltd Earnings Presentation Transcript</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>GuruFocus</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=186001&amp;sid=2</t>
+          <t>https://www.gurufocus.com/stock/DSKYF/transcripts/8867432</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19-05-2026 12:28 UTC</t>
+          <t>19-05-2026 04:55 UTC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1840,123 +1840,123 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Addressing the Symptom Burden of Primary Biliary Cholangitis</t>
+          <t>AstraZeneca plc stock (GB0009895292): US drug approvals trigger milestone payment and fresh attentio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Medscape Reference</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://reference.medscape.com/viewarticle/fatigue-burden-primary-biliary-cholangitis-2026a1000cej</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/astrazeneca-plc-stock-gb0009895292-us-drug-approvals-trigger-milestone/69369988</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18-05-2026 16:13 UTC</t>
+          <t>19-05-2026 03:23 UTC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Kyowa Kirin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Teva regains investment-grade rating from Fitch</t>
+          <t>New Dosing Option Okayed for X-Linked Hypophosphatemia Drug</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ynetnews</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.ynetnews.com/business/article/rys9fjt1me</t>
+          <t>http://www.medscape.com/viewarticle/new-dosing-option-okayed-x-linked-hypophosphatemia-drug-2026a1000g2u</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18-05-2026 19:13 UTC</t>
+          <t>18-05-2026 19:06 UTC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>JCR Pharma</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Teva Pharmaceutical Industries Insider Sold Shares Worth $5,457,375, According to a Recent SEC Filing</t>
+          <t>JCR Pharmaceuticals Presents Preclinical Gene Therapy Data that Demonstrate Promising Central Nervou</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>marketscreener.com</t>
+          <t>PharmiWeb.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.marketscreener.com/news/teva-pharmaceutical-industries-insider-sold-shares-worth-5-457-375-according-to-a-recent-sec-filin-ce7f5adad088ff23</t>
+          <t>https://www.pharmiweb.com/press-release/2026-05-18/jcr-pharmaceuticals-presents-preclinical-gene-therapy-data-that-demonstrate-promising-central-nervou</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18-05-2026 20:20 UTC</t>
+          <t>18-05-2026 20:30 UTC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teva reports diagnostic gap in tardive dyskinesia patients</t>
+          <t>Fresubin nutrition products: how Fresenius Kabi supports recovery</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Investing.com UK</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://m.uk.investing.com/news/stock-market-news/teva-reports-diagnostic-gap-in-tardive-dyskinesia-patients-93CH-4684969?ampMode=1</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresubin-nutrition-products-how-fresenius-kabi-supports-recovery/69373100</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18-05-2026 15:23 UTC</t>
+          <t>19-05-2026 11:19 UTC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1968,30 +1968,190 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings trajectory in focu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresenius-se-and-co-kgaa-stock-de0005785604-restructuring-progress/69374242</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:14 UTC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Therapeutic Plasma Exchange Industry Share and Growth Outlook by 2034</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>industrytoday.co.uk</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://industrytoday.co.uk/pharmaceutical/therapeutic-plasma-exchange-industry-share-and-growth-outlook-by-2034</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19-05-2026 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MS Pharma announces strategic growth investment from Olayan Financing Company</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Pharmabiz.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=186001&amp;sid=2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19-05-2026 12:28 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Advanz Pharma</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Treatment Sequencing in Primary Biliary Cholangitis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Medscape Reference</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://reference.medscape.com/viewarticle/second-line-treatment-primary-biliary-cholangitis-2026a1000cel</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19-05-2026 16:11 UTC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Teva regains investment-grade rating from Fitch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ynetnews</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.ynetnews.com/business/article/rys9fjt1me</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18-05-2026 19:13 UTC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>From Promise to Proof: The Shakeup in Today’s Biosimilar Market</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Pharmaceutical Commerce</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://www.pharmaceuticalcommerce.com/view/from-promise-to-proof-the-shakeup-in-today-s-biosimilar-market</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>19-05-2026 13:15 UTC</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -2021,7 +2181,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-05-2026 19:48:25</t>
+          <t>20-05-2026 00:07:53</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,27 +469,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandoz backs Budget consultation to improve access to biosimilar medicines</t>
+          <t>Parabilis reveals IPO plans the day after Regeneron deal as listings heat up</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>retailpharmacymagazine.com.au</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://retailpharmacymagazine.com.au/sandoz-backs-budget-consultation-to-improve-access-to-biosimilar-medicines/</t>
+          <t>https://endpoints.news/parabilis-reveals-ipo-plans-the-day-after-regeneron-deal-as-listings-heat-up/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19-05-2026 00:27 UTC</t>
+          <t>20-05-2026 10:40 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -501,27 +501,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biosimilar Streamlining Means All Should ‘Reach The Fruits’</t>
+          <t>Evotec AG Earnings Call Balances Setback And Strategy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/in-vivo/biosimilar-streamlining-means-all-should-reach-the-fruits-O65JTY5UAFFP7KDHOWXXWTNWAA/</t>
+          <t>https://www.tipranks.com/news/company-announcements/evotec-ag-earnings-call-balances-setback-and-strategy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19-05-2026 10:57 UTC</t>
+          <t>20-05-2026 05:19 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eqs-News Formycon Aflibercept Biosimilars Ahzantive® And Baiama® Are Now Available In The European Union</t>
+          <t>Takeover Candidates for 2026! The Life Sciences Sector Is Heating Up: Evotec, BioNxt Solutions, BioNTech, and Formycon in Focus!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>news.financial</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/reuters.com,2026:newsml_FWN41V1HM:0-eqs-news-formycon-aflibercept-biosimilars-ahzantive-and-baiama-are-now-available-in-the-european-union/</t>
+          <t>https://news.financial/comments/takeover-candidates-for-2026-the-life-sciences-sector-is-heating-up-evotec-bionxt-solutions-biontech-and-formycon-in-focus</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19-05-2026 04:33 UTC</t>
+          <t>20-05-2026 06:05 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -565,27 +565,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Streamlined Biosimilar Guidelines A Fillip For Hungary’s Richter</t>
+          <t>Gedeon Richter PLC 2026 Q1 - Results - Earnings Call Presentation (OTCMKTS:GEDSF) 2026-05-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/streamlined-biosimilar-guidelines-a-fillip-for-hungarys-richter-N47ONTCEQVG2FOR33DDU44NTXU/</t>
+          <t>https://seekingalpha.com/article/4906777-gedeon-richter-plc-2026-q1-results-earnings-call-presentation?source=feed_all_articles</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19-05-2026 10:42 UTC</t>
+          <t>19-05-2026 23:30 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -597,27 +597,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan’s MHLW approves Boehringer’s Jascayd for IPF and PPF</t>
+          <t>Anti-Obesity Drugs Market to Reach $104.9 Billion by 2035,</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pharmaceutical Technology</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.pharmaceutical-technology.com/news/japans-mhlw-boehringers-jascayd-approval/</t>
+          <t>https://www.openpr.com/news/4519358/anti-obesity-drugs-market-to-reach-104-9-billion-by-2035</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19-05-2026 08:15 UTC</t>
+          <t>20-05-2026 05:05 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Supreme Court Declines to Hear Pharma Challenge to IRA</t>
+          <t>Ladder Bio Adds Jay Fine and John Prufeta to Board as Company Expands Immunology and Biosecurity Strategy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NAVLIN DAILY</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.navlindaily.com/article/30573/u-s-supreme-court-declines-to-hear-pharma-challenge-to-ira</t>
+          <t>https://www.citybiz.co/article/848599/ladder-bio-adds-jay-fine-and-john-prufeta-to-board-as-company-expands-immunology-and-biosecurity-strategy/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19-05-2026 08:30 UTC</t>
+          <t>19-05-2026 17:06 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cattle farmers face a new era in worm control</t>
+          <t>SGLT-2 Inhibitors Market Size to Reach Significant Growth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agriland</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.agriland.ie/farming-news/cattle-farmers-face-a-new-era-in-worm-control/</t>
+          <t>https://www.openpr.com/news/4519583/sglt-2-inhibitors-market-size-to-reach-significant-growth</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19-05-2026 07:50 UTC</t>
+          <t>20-05-2026 07:22 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -725,22 +725,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>opnMe online seminar: Illuminating SYK function through independent research</t>
+          <t>Press Release Distribution India</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>idw – Informationsdienst Wissenschaft</t>
+          <t>Business Wire India</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://idw-online.de/de/event81596</t>
+          <t>https://www.businesswireindia.com/abbott-launches-ensure%C2%AE-strength-pro-in-india-to-support-healthy-ageing-100195.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19-05-2026 00:00 UTC</t>
+          <t>20-05-2026 09:11 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -752,160 +752,160 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): guidance upgrade and FDA progress put focus on growt</t>
+          <t>Supreme Court rejects bid to halt IRA price negotiations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-guidance-upgrade-and-fda/69369644</t>
+          <t>https://www.thepharmaletter.com/pharma-news/supreme-court-rejects-bid-to-halt-ira-price-negotiations</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19-05-2026 02:36 UTC</t>
+          <t>20-05-2026 10:34 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hikma</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): recent AGM update and focus on injectable growth</t>
+          <t>FDA Approval Of Tessie Puts Orion’s Animal Health Potential In Focus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-recent-agm-update-and/69367834</t>
+          <t>https://simplywall.st/stocks/fi/pharmaceuticals-biotech/hel-ornbv/orion-oyj-shares/news/fda-approval-of-tessie-puts-orions-animal-health-potential-i</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18-05-2026 19:27 UTC</t>
+          <t>19-05-2026 23:18 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen stock (US0311621009): focus on obesity data and pipeline as investors await next catalysts</t>
+          <t>hVIVO to host capital markets day as it pitches broader clinical development role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Proactive financial news</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-stock-us0311621009-focus-on-obesity-data-and-pipeline-as/69375321</t>
+          <t>https://www.proactiveinvestors.com/companies/news/1092586</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19-05-2026 17:22 UTC</t>
+          <t>20-05-2026 07:56 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When a Common Disease Becomes a Rare Journey: Understanding Uncontrolled Gout</t>
+          <t>Hikma Pharmaceuticals PLC stock (GB00B128J450): focus shifts to 2026 outlook after solid 2024 result</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.amgen.com/stories/2026/05/when-a-common-disease-becomes-a-rare-journey-understanding-uncontrolled-gout</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/hikma-pharmaceuticals-plc-stock-gb00b128j450-focus-shifts-to-2026/69376942</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19-05-2026 05:35 UTC</t>
+          <t>19-05-2026 22:49 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hikma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Biopharma bites: IRA is here to stay, plus more safety concerns for Amgen's Tavneos</t>
+          <t>Siga Technologies Balances Lumpy Results With Strong Cash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FirstWord Pharma</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://firstwordpharma.com/story/7445196</t>
+          <t>https://www.tipranks.com/news/company-announcements/siga-technologies-balances-lumpy-results-with-strong-cash</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19-05-2026 00:23 UTC</t>
+          <t>20-05-2026 03:37 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -917,182 +917,182 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amgen Inc. stock (US0311621009): weight-loss data and earnings keep biotech in focus</t>
+          <t>The Story of Maridebart Cafraglutide (MariTide)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-inc-stock-us0311621009-weight-loss-data-and-earnings-keep/69374326</t>
+          <t>https://www.amgen.com/stories/2026/05/the-story-of-maridebart-cafraglutide</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19-05-2026 14:25 UTC</t>
+          <t>20-05-2026 06:53 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plant Form</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Next in ingestible beauty: Plant-based enzyme boosts skin’s natural antioxidant defenses</t>
+          <t>Amgen names Thomas Dittrich as new CFO, succeeding Peter Griffith in September 2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nutrition Insight</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.nutritioninsight.com/news/beauty-supplements-collagen-skincare-dermatology-glisodin.html</t>
+          <t>https://pluang.com/en/news-feed/amgen-umumkan-pensiun-cfo-peter-griffith</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19-05-2026 12:27 UTC</t>
+          <t>20-05-2026 07:22 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer, Moderna COVID vaccines 70% to 76% effective against severe illness in kids in 2022, data suggest</t>
+          <t>Standing Bone Strong: Introducing a New Awareness Symbol for Osteoporosis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cidrap.umn.edu</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/covid-19/pfizer-moderna-covid-vaccines-70-76-effective-against-severe-illness-kids-2022-data</t>
+          <t>https://www.amgen.com/stories/2026/05/standing-bone-strong-introducing-a-new-awareness-symbol-for-osteoporosis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19-05-2026 18:14 UTC</t>
+          <t>20-05-2026 03:59 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy</t>
+          <t>Fideuram Intesa Sanpaolo Private Banking S.P.A. Takes Position in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://www.marketbeat.com/instant-alerts/filing-fideuram-intesa-sanpaolo-private-banking-spa-takes-position-in-amgen-inc-amgn-2026-05-20/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19-05-2026 04:35 UTC</t>
+          <t>20-05-2026 08:03 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Posts linking Covid jabs to hantavirus misuse Pfizer, WHO documents</t>
+          <t>Argus Adjusts Price Target on Amgen to $375 From $400, Maintains Buy Rating</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AFP Fact Check</t>
+          <t>marketscreener.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://factcheck.afp.com/doc.afp.com.B2964NQ</t>
+          <t>https://www.marketscreener.com/news/argus-adjusts-price-target-on-amgen-to-375-from-400-maintains-buy-rating-ce7f5ad9d989fe25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19-05-2026 03:01 UTC</t>
+          <t>20-05-2026 10:28 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pfizer Limited Annual Secretarial Compliance Report for FY 2025-26</t>
+          <t>Amgen stock (US0311621009): focus on obesity data and pipeline as investors await next catalysts</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/pfizer-limited-annual-secretarial-compliance-filing/</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-stock-us0311621009-focus-on-obesity-data-and-pipeline-as/69375321</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19-05-2026 10:00 UTC</t>
+          <t>19-05-2026 17:22 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1104,108 +1104,108 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Seagen stock (US8166361055): what the Pfizer takeover means for investors after delisting</t>
+          <t>Amgen Inc. stock outperforms competitors on strong trading day</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>MarketWatch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/seagen-stock-us8166361055-what-the-pfizer-takeover-means-for-investors/69371827</t>
+          <t>https://www.marketwatch.com/data-news/amgen-inc-stock-outperforms-competitors-on-strong-trading-day-8f9e1980-35e83e9d7302?mod=mw_quote_news</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19-05-2026 08:13 UTC</t>
+          <t>19-05-2026 20:34 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pfizer Takes Aim at Merck in New Phase 3 Endometrial Cancer Trial</t>
+          <t>Passkey Therapeutics Adds Former Amgen Executive Mandeep Kaur as Chief Medical Officer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TipRanks</t>
+          <t>citybiz</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.tipranks.com/news/company-announcements/pfizer-takes-aim-at-merck-in-new-phase-3-endometrial-cancer-trial</t>
+          <t>https://www.citybiz.co/article/848748/passkey-therapeutics-adds-former-amgen-executive-mandeep-kaur-as-chief-medical-officer/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19-05-2026 16:44 UTC</t>
+          <t>19-05-2026 18:36 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pfizer and Aristotle University bet on Thessaloniki as a digital health hub with new agreement</t>
+          <t>Fairtree Asset Management Pty Ltd Acquires New Stake in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Voria</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.voria.gr/index.php/article/pfizer-and-aristotle-university-bet-thessaloniki-digital-health-hub-new-agreement</t>
+          <t>https://www.marketbeat.com/instant-alerts/filing-fairtree-asset-management-pty-ltd-acquires-new-stake-in-amgen-inc-amgn-2026-05-20/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19-05-2026 13:06 UTC</t>
+          <t>20-05-2026 08:09 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Biogen stock (US09062X1037): Alzheimer’s focus after Leqembi setback and pipeline updates</t>
+          <t>Amgen stock (US0311621009): FDA data and pipeline updates in focus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1215,204 +1215,204 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/biogen-stock-us09062X1037-alzheimer-s-focus-after-leqembi-setback-and/69369903</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/amgen-stock-us0311621009-fda-data-and-pipeline-updates-in-focus/69376869</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19-05-2026 03:12 UTC</t>
+          <t>19-05-2026 22:36 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Biogen Faces Legal Scrutiny After Diranersen Trial Results, Stoc</t>
+          <t>Cullen Frost Bankers Inc. Cuts Stake in Amgen Inc. $AMGN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/news/8866732/biogen-faces-legal-scrutiny-after-diranersen-trial-results-stock-drops-biib?mobile=true%3Fmobile%3Dtrue&amp;mobile=true%3Fmobile%3Dtrue%3Fmobile%3Dtrue&amp;mobile=true&amp;mobile=true</t>
+          <t>https://www.marketbeat.com/instant-alerts/filing-cullen-frost-bankers-inc-cuts-stake-in-amgen-inc-amgn-2026-05-20/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18-05-2026 20:23 UTC</t>
+          <t>20-05-2026 08:29 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Amneal Kashiv Biosciences</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biogen’s Apellis Deal And Alzheimer’s Trial Shift Focus Beyond Price</t>
+          <t>Amneal Pharma Bets Big on Biosimilars in Q1 Call</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/sectors/healthcare/articles/biogen-apellis-deal-alzheimer-trial-191746426.html</t>
+          <t>https://www.tipranks.com/news/company-announcements/amneal-pharma-bets-big-on-biosimilars-in-q1-call</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18-05-2026 19:17 UTC</t>
+          <t>20-05-2026 06:56 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dr Reddy's Wins Higher Target As HSBC Backs Its Global Expansion Strategy — Details Inside</t>
+          <t>Net current asset value per share of PT Organon Pharma Indonesia Tbk – IDX:SCPI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/markets/dr-reddys-wins-higher-target-as-hsbc-backs-its-global-expansion-strategy-details-inside-11514943</t>
+          <t>https://www.tradingview.com/symbols/IDX-SCPI/financials-statistics-and-ratios/ncavps-ratio/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19-05-2026 02:32 UTC</t>
+          <t>19-05-2026 12:48 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Delhi High Court Upholds Dr. Reddy's Rights Over “REDDY” Mark, Rejects Acquiescence Defence</t>
+          <t>​10 Incredible Facts About Sun Pharma’s Historic $11.75 Billion Organon Acquisition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LiveLawBiz</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.livelawbiz.com/amp/trademark/delhi-high-court-upholds-permanent-injunction-against-reddy-pharmaceuticals-in-dr-reddys-laboratories-trademark-dispute-534797</t>
+          <t>https://www.aol.com/articles/10-incredible-facts-sun-pharma-192054000.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19-05-2026 10:06 UTC</t>
+          <t>19-05-2026 19:50 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dr Reddy's Q4FY26 Net Profit Plunges 86% to ₹220 Cr on One-Time Charges</t>
+          <t>Widely used asthma drug may improve performance of cancer immunotherapies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>WTAQ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/dr-reddy-s-laboratories-q4-results-net-profit-declines-to-2-21b-rupees-yoy-board-recommends-8-final-dividend/40144336</t>
+          <t>https://wtaq.com/2026/05/20/widely-used-asthma-drug-may-improve-performance-of-cancer-immunotherapies/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18-05-2026 20:18 UTC</t>
+          <t>20-05-2026 12:01 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Intas</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bio-Thera Solutions' Golimumab Biosimilars Receive FDA Approval as First Biosimilars to Simponi® and Simponi Aria®; Accord BioPharma to Commercialize IMMGOLIS™ (golimumab-sldi) and IMMGOLIS INTRI</t>
+          <t>Generic Ozempic is now on Canadian shelves. Is it the same as the brand name version?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>StreetInsider</t>
+          <t>CBC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.streetinsider.com/PRNewswire/Bio-Thera+Solutions%27s+Golimumab+Biosimilars+Receive+FDA+Approval+as+First+Biosimilars+to+Simponi%C2%AE+and+Simponi+Aria%C2%AE%3B+Accord+BioPharma+to+Commercialize+IMMGOLIS%E2%84%A2+%28golimumab-sldi%29+and+IMMGOLIS+INTRI%E2/26510377.html</t>
+          <t>https://www.cbc.ca/lite/story/9.7204671</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19-05-2026 02:56 UTC</t>
+          <t>20-05-2026 08:02 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1424,59 +1424,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Biosimilar Streamlining Means All Should ‘Reach The Fruits’</t>
+          <t>Coherus BioSciences stock (US19247A1007): earnings reset and oncology focus after Humira biosimilar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/in-vivo/biosimilar-streamlining-means-all-should-reach-the-fruits-O65JTY5UAFFP7KDHOWXXWTNWAA/</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/coherus-biosciences-stock-us19247a1007-earnings-reset-and-oncology/69376156</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19-05-2026 10:57 UTC</t>
+          <t>19-05-2026 20:08 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Coherus Biosciences</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Extinguishes 54,23,728 Equity Shares Under ₹800 Crore Buyback Programme</t>
+          <t>Coherus Biosciences Signals Momentum in Earnings Call</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-extinguishes-54-23-728-equity-shares-under-800-crore-buyback-programme/40700416</t>
+          <t>https://www.tipranks.com/news/company-announcements/coherus-biosciences-signals-momentum-in-earnings-call</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19-05-2026 01:44 UTC</t>
+          <t>20-05-2026 01:20 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1488,27 +1488,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences to pursue acquisitions in specialty, rare diseases</t>
+          <t>Research Rising: Recognizing Clinical Trials Day 2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/zydus-lifesciences-to-pursue-acquisitions-in-specialty-rare-diseases/articleshow/131205005.cms</t>
+          <t>https://www.pfizer.com/news/articles/research_rising_recognizing_clinical_trials_day_2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19-05-2026 15:28 UTC</t>
+          <t>20-05-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1520,59 +1520,59 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Buyback Record Date 2026, Price, Entitlement Ratio</t>
+          <t>Pfizer takes paediatric 25-valent pneumococcal vaccine to Phase III</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IPO Central</t>
+          <t>FirstWord Pharma</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://ipocentral.in/zydus-lifesciences-buyback-record-date-2026-price/</t>
+          <t>https://firstwordpharma.com/story/7450263</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19-05-2026 11:16 UTC</t>
+          <t>20-05-2026 12:08 UTC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Q4 and Full Year FY26 Earnings Highlights</t>
+          <t>How S&amp;P Drug Titan Pfizer Plans To Outdo Its Own $6 Billion Franchise</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>Investor's Business Daily</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/zydus-lifesciences-strong-q4-fy26-results-and-buyback-announcement/</t>
+          <t>https://www.investors.com/news/technology/pfizer-pneumococcal-vaccine-prevnar-merck-vaxcyte/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19-05-2026 08:50 UTC</t>
+          <t>20-05-2026 09:05 UTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1584,27 +1584,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zydus Wellness FY26 revenue climbs to Rs. 39.4 billion</t>
+          <t>Pfizer Stock Shares $49 Bil Success With Investors</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Trefis</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/zydus-wellness-fy26-revenue-climbs-to-rs-394-billion-20244</t>
+          <t>https://www.trefis.com/stock/pfe/articles/599911/pfizer-stock-shares-49-bil-success-with-investors/2026-05-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19-05-2026 02:04 UTC</t>
+          <t>20-05-2026 11:10 UTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1616,27 +1616,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Celltrion Inc stock (KR7068270008): biosimilar specialist in focus after recent earnings and pipelin</t>
+          <t>Pfizer Keeps Oncology Upside As Rigel Takes VEPPANU PROTAC Lead</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/celltrion-inc-stock-kr7068270008-biosimilar-specialist-in-focus-after/69371623</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nyse-pfe/pfizer/news/pfizer-keeps-oncology-upside-as-rigel-takes-veppanu-protac-l</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19-05-2026 07:34 UTC</t>
+          <t>20-05-2026 03:32 UTC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1648,91 +1648,91 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Celltrion said it will respond by closely reviewing the management situation and market environment</t>
+          <t>Pfizer Stock at $25: A $29 Wall Street Mean Target Backed by Two Legal Wins and 22% Portfolio Growth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>매일경제</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/en/stock/12051778</t>
+          <t>https://www.tikr.com/blog/pfizer-stock-at-25-a-29-wall-street-mean-target-backed-by-two-legal-wins-and-22-portfolio-growth</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19-05-2026 01:06 UTC</t>
+          <t>20-05-2026 10:44 UTC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Celltrion: "Stock Undervalued... Reviewing Measures to Enhance Shareholder Value with Major Shareholders"</t>
+          <t>Vaccination Services Market Is Booming So Rapidly with Pfizer, Moderna, GSK, Sanofi, Merck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>아시아경제</t>
+          <t>openPR.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.asiae.co.kr/en/article/bio-health/2026051911060545512</t>
+          <t>https://www.openpr.com/news/4520229/vaccination-services-market-is-booming-so-rapidly-with-pfizer</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19-05-2026 02:06 UTC</t>
+          <t>20-05-2026 11:21 UTC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Celltrion Pharm boosts Korea liver drug lead with 7.4b won prescriptions - CHOSUNBIZ</t>
+          <t>Pfizer stock (US7170811035): Pfizer reports first-quarter 2026 results</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/05/19/HGQ5R2S55BDQ5N2XGMX4FJIYPA/</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/pfizer-stock-us7170811035-pfizer-reports-first-quarter-2026-results/69376768</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19-05-2026 00:09 UTC</t>
+          <t>19-05-2026 22:17 UTC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1744,91 +1744,91 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo charts aggressive oncology expansion with $14.6bn target by 2030</t>
+          <t>Pfizer, Moderna COVID vaccines 70% to 76% effective against severe illness in kids in 2022, data suggest</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BioXconomy</t>
+          <t>cidrap.umn.edu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.bioxconomy.com/investment/daiichi-sankyo-charts-aggressive-oncology-expansion-with-14-6bn-target-by-2030</t>
+          <t>https://www.cidrap.umn.edu/covid-19/pfizer-moderna-covid-vaccines-70-76-effective-against-severe-illness-kids-2022-data</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19-05-2026 09:49 UTC</t>
+          <t>19-05-2026 18:14 UTC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AstraZeneca And Daiichi Sankyo Expand ENHERTU Into Early HER2 Positive Breast Cancer Treatment In The US</t>
+          <t>How Biogen’s Diranersen Alzheimer’s Bet Will Impact Biogen (BIIB) Investors</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/73/7951/astrazeneca-and-daiichi-sankyo-expand-enhertu-into-early-her2-positive-breast-cancer-treatment-in-the-us.html</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-biib/biogen/news/how-biogens-diranersen-alzheimers-bet-will-impact-biogen-bii</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19-05-2026 02:15 UTC</t>
+          <t>20-05-2026 10:32 UTC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Full Year 2026 Daiichi Sankyo Co Ltd Earnings Presentation Transcript</t>
+          <t>Biogen stock (US09062X1037): Alzheimer data and Q1 earnings keep focus on biotech transition</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GuruFocus</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.gurufocus.com/stock/DSKYF/transcripts/8867432</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/biogen-stock-us09062x1037-alzheimer-data-and-q1-earnings-keep-focus-on/69379931</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19-05-2026 04:55 UTC</t>
+          <t>20-05-2026 06:38 UTC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1840,91 +1840,91 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AstraZeneca plc stock (GB0009895292): US drug approvals trigger milestone payment and fresh attentio</t>
+          <t>Biogen’s Nicole Murphy Aims to Elevate the Manufacturing Workforce - National Association of Manufacturers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>National Association of Manufacturers - NAM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/astrazeneca-plc-stock-gb0009895292-us-drug-approvals-trigger-milestone/69369988</t>
+          <t>https://nam.org/biogens-nicole-murphy-aims-to-elevate-the-manufacturing-workforce-36467/?stream=series-input-stories</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19-05-2026 03:23 UTC</t>
+          <t>20-05-2026 00:07 UTC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kyowa Kirin</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New Dosing Option Okayed for X-Linked Hypophosphatemia Drug</t>
+          <t>BIIB Investor Alert: Levi &amp; Korsinsky Investigates Biogen Inc. (BIIB) for Potential Securities Fraud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Medscape</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>http://www.medscape.com/viewarticle/new-dosing-option-okayed-x-linked-hypophosphatemia-drug-2026a1000g2u</t>
+          <t>https://www.businesswire.com/news/home/20260519642939/en/BIIB-Investor-Alert-Levi-Korsinsky-Investigates-Biogen-Inc.-BIIB-for-Potential-Securities-Fraud</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18-05-2026 19:06 UTC</t>
+          <t>19-05-2026 20:00 UTC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JCR Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JCR Pharmaceuticals Presents Preclinical Gene Therapy Data that Demonstrate Promising Central Nervou</t>
+          <t>Eisai raises forecast for Alzheimer’s drug, nearing blockbuster status</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PharmiWeb.com</t>
+          <t>medwatch.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pharmiweb.com/press-release/2026-05-18/jcr-pharmaceuticals-presents-preclinical-gene-therapy-data-that-demonstrate-promising-central-nervou</t>
+          <t>https://medwatch.com/News/Pharma___Biotech/article19312619.ece</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18-05-2026 20:30 UTC</t>
+          <t>20-05-2026 08:56 UTC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1936,59 +1936,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fresubin nutrition products: how Fresenius Kabi supports recovery</t>
+          <t>Ionis Rises As Diranersen Phase 2 Spurs Biogen Registrational Plans</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresubin-nutrition-products-how-fresenius-kabi-supports-recovery/69373100</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-ions/ionis-pharmaceuticals/news/ionis-rises-as-diranersen-phase-2-spurs-biogen-registrationa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19-05-2026 11:19 UTC</t>
+          <t>20-05-2026 09:43 UTC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings trajectory in focu</t>
+          <t>Biogen Earnings Call Signals Confident, Investment-Heavy Transition</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AD HOC NEWS</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresenius-se-and-co-kgaa-stock-de0005785604-restructuring-progress/69374242</t>
+          <t>https://www.tipranks.com/news/company-announcements/biogen-earnings-call-signals-confident-investment-heavy-transition</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19-05-2026 14:14 UTC</t>
+          <t>20-05-2026 01:04 UTC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2000,27 +2000,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Therapeutic Plasma Exchange Industry Share and Growth Outlook by 2034</t>
+          <t>Immunic appoints Biogen, Cubist veteran Mike Bonney as board chair ahead of key MS trial readout</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>industrytoday.co.uk</t>
+          <t>Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://industrytoday.co.uk/pharmaceutical/therapeutic-plasma-exchange-industry-share-and-growth-outlook-by-2034</t>
+          <t>https://ca.finance.yahoo.com/news/immunic-appoints-biogen-cubist-veteran-133300748.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19-05-2026 13:58 UTC</t>
+          <t>19-05-2026 13:33 UTC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2032,27 +2032,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MS Pharma</t>
+          <t>Blau Farmaceutica</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MS Pharma announces strategic growth investment from Olayan Financing Company</t>
+          <t>Blau Farmacêutica stock (BRBLAUACNOR1): earnings and expansion plans draw investor focus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pharmabiz.com</t>
+          <t>AD HOC NEWS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=186001&amp;sid=2</t>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/blau-farmaceutica-stock-brblauacnor1-earnings-and-expansion-plans-draw/69378080</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19-05-2026 12:28 UTC</t>
+          <t>20-05-2026 02:07 UTC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2064,59 +2064,59 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Advanz Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Treatment Sequencing in Primary Biliary Cholangitis</t>
+          <t>Dr Reddy’s launches oral semaglutide biosimilar Obeda for type 2 diabetes in India - CNBC TV18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Medscape Reference</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://reference.medscape.com/viewarticle/second-line-treatment-primary-biliary-cholangitis-2026a1000cel</t>
+          <t>https://www.linkedin.com/posts/cnbc-tv18_dr-reddys-launches-oral-semaglutide-biosimilar-activity-7462829439165308928-lYGE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19-05-2026 16:11 UTC</t>
+          <t>20-05-2026 11:39 UTC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Teva regains investment-grade rating from Fitch</t>
+          <t>Five Stocks To Buy: BHEL, Dr Reddy's, KPIT Tech And More | May 20, 2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ynetnews</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.ynetnews.com/business/article/rys9fjt1me</t>
+          <t>https://www.ndtvprofit.com/markets/five-stocks-to-buy-bhel-dr-reddys-laboratories-acutaas-kpit-tech-siemens-energy-11520335</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18-05-2026 19:13 UTC</t>
+          <t>20-05-2026 01:45 UTC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2128,32 +2128,1440 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Reddy Pharma loses 'name' in Delhi HC ruling</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/news/india/reddy-pharma-loses-name-in-hc-ruling/articleshow/131209956.cms</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19-05-2026 18:56 UTC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>R-Pharm to localise production of novel cancer drug toripalimab in Russia</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Новости GxP</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://gxpnews.net/en/2026/05/r-pharm-to-localise-production-of-novel-cancer-drug-toripalimab-in-russia/?amp=1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Exit IRB Infrastructure, NCC shares; pick Biocon stock: Trading and investment strategy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/markets/stocks/story/exit-irb-infrastructure-ncc-shares-pick-biocon-stock-trading-and-investment-strategy-532507-2026-05-20</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>20-05-2026 11:30 UTC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts Biocon Ltd. to 52-Week High of Rs 436.8</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Markets Mojo</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.marketsmojo.com/news/stocks-in-action/biocon-ltd-hits-new-52-week-high-at-rs4368-mark-4001157</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20-05-2026 09:11 UTC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Biocon - ​Vodafone Idea and 6 other stocks hit a 52-week high, rally up to 40% in a month</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/us-stocks/news/vodafone-idea-and-6-other-stocks-hit-a-52-week-high-rally-up-to-40-in-a-month/biocon/slideshow/131199571.cms</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19-05-2026 12:42 UTC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Indian Pharma, Tech, Engineering Firms Pledge $20.5 Billion In Investments Across US</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IndiaWest</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://indiawest.com/indian-pharma-tech-engineering-firms-pledge-20-5-billion-in-investments-across-us/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20-05-2026 07:47 UTC</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Broad-Based Technical Strength Lifts Aurobindo Pharma Ltd. to 52-Week High of Rs 1539.65</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Markets Mojo</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.marketsmojo.com/news/stocks-in-action/aurobindo-pharma-ltd-hits-new-52-week-high-of-rs153965-on-20-may-2026-4000921</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20-05-2026 05:19 UTC</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd stock (INE406A01037): Buyback share extinguishment and fresh 52-week high draw</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/aurobindo-pharma-ltd-stock-ine406a01037-buyback-share-extinguishment/69376462</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19-05-2026 21:07 UTC</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences' Rs 1,100 crore share buyback at 13% premium: Check record date, other details</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/zydus-lifesciences-rs-1100-crore-share-buyback-at-13-premium-check-record-date-other-details/articleshow/131215762.cms</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20-05-2026 03:43 UTC</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Zydus plans semaglutide rollout across 20 markets; sees Biosimilar scale-up from FY29</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETPharma.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/zydus-plans-semaglutide-rollout-across-20-markets-sees-biosimilar-scale-up-from-fy29/131214277</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20-05-2026 02:01 UTC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences shares soar 7% to fresh record high after Q4 results. Should you buy, sell or hold?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/zydus-lifesciences-shares-soar-7-to-fresh-record-high-after-q4-results-should-you-buy-sell-or-hold/articleshow/131217213.cms</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20-05-2026 05:16 UTC</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences reports FY26 revenue of Rs. 27,148 crore, Q4 revenue up 16%</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/zydus-lifesciences-reports-fy26-revenue-of-rs-27148-crore-q4-revenue-up-16-20269</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19-05-2026 23:59 UTC</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences to pursue acquisitions in specialty, rare diseases</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/zydus-lifesciences-to-pursue-acquisitions-in-specialty-rare-diseases/articleshow/131205005.cms</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19-05-2026 15:28 UTC</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pharma Stocks Today, May 20: Zydus Lifesciences jumps 5.22%, Mankind Pharma rises 2.52%, Strides Pharma up 1.85%</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.businessupturn.com/finance/stock-market/pharma-stocks-today-may-20-zydus-lifesciences-jumps-5-22-mankind-pharma-rises-2-52-strides-pharma-up-1-85/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20-05-2026 04:17 UTC</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Celltrion Vows Special Measures to Address Stock Undervaluation</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Seoul Economic Daily</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://en.sedaily.com/culture/2026/05/20/celltrion-vows-special-measures-to-address-stock</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19-05-2026 22:01 UTC</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Korea pharma-bio widens profit gap as giants surge on exports, R&amp;D-heavy firms sink - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-science/2026/05/20/HJFTLWVELJA77CEIT4HMLVZM5Q/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19-05-2026 22:19 UTC</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo : Participation in WHO-GBCI Phase 2 through a Partnership with City Cancer Challenge (C/Can) — Contributing to Breast Cancer Care in Low- and Middle-Income Countries</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/news/daiichi-sankyo-participation-in-who-gbci-phase-2-through-a-partnership-with-city-cancer-challenge-ce7f5ad8de8cf320</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>20-05-2026 06:21 UTC</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Daiichi emerges from bruising 2 years with vision for cracking cancer’s big leagues</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.biospace.com/drug-development/daiichi-emerges-from-bruising-2-years-with-vision-for-cracking-cancers-big-leagues</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20-05-2026 05:01 UTC</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Enhertu Expands Into Early Breast Cancer Treatment, Boosting Expectations for Alteogen Platform</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>thelec.net</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.thelec.net/news/articleView.html?idxno=10608</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:19 UTC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kiwoom Securities sees Alteogen cut patent risk and gain momentum in SC platform - CHOSUNBIZ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://biz.chosun.com/en/en-finance/2026/05/20/M465WHTY2BDKTBWHJD67YPPIOI/?outputType=amp</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20-05-2026 00:01 UTC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kyowa Hakko to Highlight Cognitive Health at Complementary Medicines Australia Innovation Day 2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/kyowa-hakko-to-highlight-cognitive-health-at-complementary-medicines-australia-innovation-day-2026-302777086.html</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20-05-2026 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin Co Ltd stock (JP3249600002): biotech name in focus as AI deal and ETF inclusion highligh</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/kyowa-kirin-co-ltd-stock-jp3249600002-biotech-name-in-focus-as-ai-deal/69376415</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19-05-2026 20:57 UTC</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Kyowa Kirin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cohere buys biopharma analytics firm Reliant AI</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BNN Bloomberg</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.bnnbloomberg.ca/business/2026/05/19/cohere-buys-biopharma-analytics-firm-reliant-ai/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19-05-2026 15:51 UTC</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JCR Pharma</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>JCR Pharmaceuticals Highlights Preclinical CNS Gene Therapy Data for JUST-AAV Platform at ASGCT 2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BioPharm International</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.biopharminternational.com/view/jcr-pharmaceuticals-highlights-preclinical-cns-gene-therapy-data-for-just-aav-platform-at-asgct-2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19-05-2026 17:10 UTC</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Kidswell Bio</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Breakeven Is Near for Kidswell Bio Corporation (TSE:4584)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://simplywall.st/stocks/jp/pharmaceuticals-biotech/tse-4584/kidswell-bio-shares/news/breakeven-is-near-for-kidswell-bio-corporation-tse4584</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>20-05-2026 05:37 UTC</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mochida Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Idorsia Ltd Tumbles 11.7% as Biotech Faces Profitability Headwinds</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Meyka</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://meyka.com/blog/idorsia-ltd-tumbles-117-as-biotech-faces-profitability-headwinds-1905/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:57 UTC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Fresenius SE &amp; Co. KGaA stock (DE0005785604): restructuring progress and earnings trajectory in focu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.ad-hoc-news.de/boerse/news/ueberblick/fresenius-se-and-co-kgaa-stock-de0005785604-restructuring-progress/69374242</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:14 UTC</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Glenmark board meets May 29 to consider FY26 results</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://scanx.trade/stock-market-news/companies/glenmark-board-to-meet-on-may-29-to-consider-fy26-results/40747997</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19-05-2026 15:10 UTC</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Local Anesthesia Drugs Market to Reach USD 11,300.00 Million</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>openPR.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.openpr.com/news/4519462/local-anesthesia-drugs-market-to-reach-usd-11-300-00-million</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>20-05-2026 06:03 UTC</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Infusion Pumps Market Poised to Hit USD 9.1 Billion by 2036 Fueled by Precision Drug Delivery and Smart Healthcare Innovation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ACCESS Newswire</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.accessnewswire.com/newsroom/en/business-and-professional-services/infusion-pumps-market-poised-to-hit-usd-9.1-billion-by-2036-fuel-1168197</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19-05-2026 22:03 UTC</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Therapeutic Plasma Exchange Industry Share and Growth Outlook by 2034</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>industrytoday.co.uk</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://industrytoday.co.uk/pharmaceutical/therapeutic-plasma-exchange-industry-share-and-growth-outlook-by-2034</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19-05-2026 13:58 UTC</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MS Pharma announces strategic growth investment from Olayan Financing Company</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pharmabiz.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.pharmabiz.com/NewsDetails.aspx?aid=186001&amp;sid=2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19-05-2026 12:28 UTC</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HAB Pharma Completes Strategic Merger with Signature Phytochemicals to Lead Global Pharma Innovation</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IndiaMedToday</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://indiamedtoday.com/hab-pharma-completes-strategic-merger-with-signature-phytochemicals-to-lead-global-pharma-innovation/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20-05-2026 05:01 UTC</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ASCO 2026: A Glimpse of Key CML Treatment Updates</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Medscape</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.medscape.com/viewarticle/mdangle-asco-2026-chronic-myeloid-leukemia-preview-2026a1000csd</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>19-05-2026 19:46 UTC</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tiziana reports encouraging Expanded Access data for Foralumab in MS patients</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Proactive financial news</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.proactiveinvestors.ca/companies/news/1092553/tiziana-reports-encouraging-expanded-access-data-for-foralumab-in-ms-patients.html?region=ca</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>19-05-2026 16:55 UTC</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Sanofi therapy wins Australian registration for non-relapsing secondary progressive MS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PharmaDispatch</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://pharmadispatch.com/news/sanofi-therapy-wins-australian-registration-for-non-relapsing-secondary-progressive-ms</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>19-05-2026 21:31 UTC</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Reports 22% Revenue Growth, Net Profit Up 203% In Q4 FY26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Free Press Journal</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/business/mankind-pharma-reports-22-revenue-growth-net-profit-up-203-in-q4-fy26</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>19-05-2026 14:05 UTC</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Alvotech</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Alvotech Earnings Call Balances Setbacks and Momentum</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TipRanks</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/company-announcements/alvotech-earnings-call-balances-setbacks-and-momentum</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>20-05-2026 08:18 UTC</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Fuji Pharma</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Revenue per share of Fuji Pharma Co., Ltd. – DUS:FUP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/symbols/DUS-FUP/financials-statistics-and-ratios/revenue-per-share/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>20-05-2026 10:13 UTC</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Fuji Pharma</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Fujifilm Cellular Dynamics opens Madison iPSC manufacturing site as stem-cell science moves toward scale</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>R&amp;D World</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.rdworldonline.com/fujifilm-cellular-dynamics-opens-madison-ipsc-manufacturing-site-as-stem-cell-science-moves-toward-scale/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>19-05-2026 23:49 UTC</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Teva Pharmaceutical Industries Ltd. $TEVA Shares Sold by Gabelli Funds LLC</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MarketBeat</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.marketbeat.com/instant-alerts/filing-teva-pharmaceutical-industries-ltd-teva-shares-sold-by-gabelli-funds-llc-2026-05-20/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>20-05-2026 07:41 UTC</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Teva Stock Up More Than 100% in a Year: Time to Buy, Hold or Sell?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/markets/stocks/articles/teva-stock-more-100-time-152200118.html</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19-05-2026 15:22 UTC</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Vistagen Appoints Angel S. Angelov, MD, MBA, as Chief Medical Officer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>PharmiWeb.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.pharmiweb.com/press-release/2026-05-19/vistagen-appoints-angel-s-angelov-md-mba-as-chief-medical-officer</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>19-05-2026 15:35 UTC</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Jamp Pharma</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Orimed Pharma Expands PrLuxa-D™ Portfolio to Enhance Vitamin D Treatment Options in Canada</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PR Newswire Canada</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.newswire.ca/news-releases/orimed-pharma-expands-prluxa-d-tm-portfolio-to-enhance-vitamin-d-treatment-options-in-canada-804806625.html</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>20-05-2026 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>Samsung Bioepis</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>From Promise to Proof: The Shakeup in Today’s Biosimilar Market</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pharmaceutical Commerce</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.pharmaceuticalcommerce.com/view/from-promise-to-proof-the-shakeup-in-today-s-biosimilar-market</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>19-05-2026 13:15 UTC</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Other</t>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Samsung Bioepis launches Ustekinumab biosimilar in Japan with Nipro</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>The Korea Times</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.koreatimes.co.kr/amp/business/companies/20260520/samsung-bioepis-lunches-ustekinumab-biosimilar-in-japan-with-nipro</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>20-05-2026 07:31 UTC</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -2181,7 +3589,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-05-2026 00:07:53</t>
+          <t>20-05-2026 17:56:29</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,32 +496,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Formycon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Formycon AG: Preliminary announcement of the publication of quarterly reports and quarterly/interim statements</t>
+          <t>China approves HERNEXEOS initial treatment lung cancer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/eqs:de109bc0f094b:0-formycon-ag-preliminary-announcement-of-the-publication-of-quarterly-reports-and-quarterly-interim-statements/</t>
+          <t>https://www.boehringer-ingelheim.com/human-health/cancer/lung-cancer/china-approves-hernexeos-initial-treatment-lung-cancer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-05-2026 07:31 UTC</t>
+          <t>22-05-2026 07:59 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>China approves HERNEXEOS initial treatment lung cancer</t>
+          <t>Boehringer Ingelheim's oncology portfolio shows strong promise across multiple cancers at ASCO 2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/human-health/cancer/lung-cancer/china-approves-hernexeos-initial-treatment-lung-cancer</t>
+          <t>https://www.prnewswire.com/news-releases/boehringer-ingelheims-oncology-portfolio-shows-strong-promise-across-multiple-cancers-at-asco-2026-302779545.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22-05-2026 07:59 UTC</t>
+          <t>21-05-2026 21:00 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -565,566 +565,566 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim's oncology portfolio shows strong promise across multiple cancers at ASCO 2026</t>
+          <t>CHMP issues positive opinion for JASCAYD® (nerandomilast), bringing a new IPF and PPF therapy closer to patients in the EU</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>The Manila Times</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/boehringer-ingelheims-oncology-portfolio-shows-strong-promise-across-multiple-cancers-at-asco-2026-302779545.html</t>
+          <t>https://www.manilatimes.net/2026/05/22/tmt-newswire/globenewswire/chmp-issues-positive-opinion-for-jascayd-nerandomilast-bringing-a-new-ipf-and-ppf-therapy-closer-to-patients-in-the-eu/2350052</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21-05-2026 21:00 UTC</t>
+          <t>22-05-2026 12:29 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim India signs MoU with NIPER</t>
+          <t>Japan restores new patient access to Tavneos with tougher warnings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>metroindia.net</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.metroindia.net/news/articlenews/boehringer-ingelheim-india-signs-mou-with-niper--39937</t>
+          <t>https://www.thepharmaletter.com/pharma-news/japan-restores-new-patient-access-to-tavneos-with-tougher-warnings</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21-05-2026 16:30 UTC</t>
+          <t>22-05-2026 09:48 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen CFO to follow David Reese into retirement; Josh Smiley is out at Zai Lab</t>
+          <t>Organon to supply Hanmi’s 3 combo drugs in Malaysia, Philippines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>koreabiomed.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://endpoints.news/amgen-cfo-to-follow-david-reese-into-retirement-sanofi-lines-up-a-neurology-leader/</t>
+          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=31764</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22-05-2026 11:00 UTC</t>
+          <t>22-05-2026 05:59 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen’s ‘boomerang’ CFO reaps $12.5M in cash, retention bonuses</t>
+          <t>Two generic versions of Ozempic begin arriving in Canadian pharmacies this week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CFO Dive</t>
+          <t>Benefits and Pensions Monitor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.cfodive.com/news/amgens-boomerang-cfo-reaps-12m-bonuses-compensation/820910/</t>
+          <t>https://www.benefitsandpensionsmonitor.com/benefits/pharma/two-generic-versions-of-ozempic-begin-arriving-in-canadian-pharmacies-this-week/393598</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21-05-2026 21:26 UTC</t>
+          <t>22-05-2026 12:30 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amgen's Tavneos, facing liver injury scrutiny, gets label update in Japan as patient starts resume</t>
+          <t>Canadians can now get digital prescriptions for 'generic Ozempic'</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fierce Pharma</t>
+          <t>Financial Post</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fiercepharma.com/pharma/amgens-tavneos-facing-liver-injury-scrutiny-gets-label-update-patient-starts-resume-japan</t>
+          <t>https://financialpost.com/news/retail-marketing/canadians-digital-prescription-generic-ozempic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21-05-2026 15:38 UTC</t>
+          <t>21-05-2026 18:51 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen CFO Change Puts Focus On Debt, Growth And Capital Discipline</t>
+          <t>Pfizer Pneumococcal Vaccine Elicits Immune Response Across 25 Serotypes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Drug Topics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-amgn/amgen/news/amgen-cfo-change-puts-focus-on-debt-growth-and-capital-disci</t>
+          <t>https://www.drugtopics.com/view/pfizer-pneumococcal-vaccine-elicits-immune-response-across-25-serotypes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21-05-2026 18:33 UTC</t>
+          <t>22-05-2026 15:42 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Shareholders Reaffirm Board, Pay and Auditors</t>
+          <t>TREM2 agonists detailed in Pfizer patent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Globe and Mail</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theglobeandmail.com/investing/markets/stocks/AMGN/pressreleases/2075268/amgen-shareholders-reaffirm-board-pay-and-auditors/</t>
+          <t>https://www.bioworld.com/articles/731263-trem2-agonists-detailed-in-pfizer-patent</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21-05-2026 23:04 UTC</t>
+          <t>22-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Wants To Preserve Right To Seek Double Tax Relief</t>
+          <t>Kazakhstan and Pfizer advance healthcare investment project</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Qazinform</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.law360.com/articles/2480540/amgen-wants-to-preserve-right-to-seek-double-tax-relief</t>
+          <t>https://qazinform.com/news/kazakhstan-and-pfizer-advance-healthcare-investment-project-67288c</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21-05-2026 21:13 UTC</t>
+          <t>22-05-2026 07:53 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen's rare disease drug linked to deaths, liver injuries in Japan, WSJ reports</t>
+          <t>Biogen and Denali Therapeutics Provide Update on Phase 2b LUMA Study of BIIB122 (DNL151) in Early-Stage Parkinson’s Disease</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/amgens-rare-disease-drug-linked-201608000.html</t>
+          <t>https://investors.biogen.com/news-releases/news-release-details/biogen-and-denali-therapeutics-provide-update-phase-2b-luma</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21-05-2026 19:29 UTC</t>
+          <t>21-05-2026 22:03 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Organon to supply Hanmi’s 3 combo drugs in Malaysia, Philippines</t>
+          <t>Biogen Inc. (BIIB) Securities Fraud Investigation - Levi &amp; Korsinsky</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=31764</t>
+          <t>https://www.prnewswire.com/news-releases/biogen-inc-biib-securities-fraud-investigation---levi--korsinsky-302779232.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22-05-2026 05:59 UTC</t>
+          <t>22-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Generic Ozempic landing soon on Canadian pharmacy shelves</t>
+          <t>Aurobindo Pharma to expand manufacture of generic formulations in France</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yahoo News Canada</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://ca.news.yahoo.com/generic-ozempic-landing-soon-canadian-110010970.html</t>
+          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-to-expand-manufacture-of-generic-formulations-in-france/article71011878.ece</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22-05-2026 11:00 UTC</t>
+          <t>22-05-2026 15:49 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Building an AI-Fluent Organization: How Pfizer is helping colleagues understand, embrace, and apply AI</t>
+          <t>Aurobindo targets $2 Bn US revenue with in-licensing push</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>ETPharma.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pfizer.com/news/articles/building_an_ai_fluent_organization_how_pfizer_is_helping_colleagues_understand_embrace_and_apply_ai</t>
+          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-targets-2-bn-us-revenue-with-in-licensing-push/131264107</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21-05-2026 17:16 UTC</t>
+          <t>22-05-2026 13:04 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kazakhstan and Pfizer advance healthcare investment project</t>
+          <t>Aurobindo Pharma Q4 FY26 revenue rises 5.6% to Rs. 8,853 crore</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qazinform</t>
+          <t>Indian Pharma Post</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://qazinform.com/news/kazakhstan-and-pfizer-advance-healthcare-investment-project-67288c</t>
+          <t>https://www.indianpharmapost.com/news/aurobindo-pharma-q4-fy26-revenue-rises-56-to-rs-8853-crore-20308</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22-05-2026 07:53 UTC</t>
+          <t>22-05-2026 01:30 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Shilpa Biologicals</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pfizer targets VEGF bispecific white space | ApexOnco - Clinical Trials news and analysis</t>
+          <t>Shilpa Medicare Limited Reports Strong FY2026 Results and Strategic Investment in Renewable Energy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oncology Pipeline</t>
+          <t>InvestyWise</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.oncologypipeline.com/apexonco/pfizer-targets-vegf-bispecific-white-space</t>
+          <t>https://www.investywise.com/shilpa-medicare-limited-quarterly-financial-results-and-dividend-declaration/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21-05-2026 12:46 UTC</t>
+          <t>22-05-2026 09:29 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Celltrion</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pfizer advances next-gen pneumococcal vaccine after strong Phase 2 infant data</t>
+          <t>K-Bio Direct Sales Strategy Pays Off as US Subsidiaries' Earnings Soar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Seoul Economic Daily</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/clinical-trials/pfizer-advances-next-gen-pneumococcal-vaccine-after-strong-phase-2-infant-data-20297</t>
+          <t>https://en.sedaily.com/finance/2026/05/22/k-bio-direct-sales-strategy-pays-off-as-us-subsidiaries</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21-05-2026 15:44 UTC</t>
+          <t>21-05-2026 22:00 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pfizer wins Singapore trademark dispute with Merck over vaccine brand</t>
+          <t>FDA grants Daiichi Sankyo and AstraZeneca’s Datroway a key breast cancer approval</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The Straits Times</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.straitstimes.com/business/pfizer-wins-singapore-trademark-dispute-with-merck-over-vaccine-brand</t>
+          <t>https://endpoints.news/fda-grants-daiichi-sankyo-and-astrazenecas-datroway-a-key-breast-cancer-approval/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22-05-2026 08:00 UTC</t>
+          <t>22-05-2026 15:28 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen and Denali Therapeutics Provide Update on Phase 2b LUMA Study of BIIB122 (DNL151) in Early-Stage Parkinson’s Disease</t>
+          <t>Enhertu® Recommended for Approval in the EU by CHMP for Patients with Previously Treated HER2 Positive Metastatic Solid Tumors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/biogen-and-denali-therapeutics-provide-update-phase-2b-luma</t>
+          <t>https://www.businesswire.com/news/home/20260521833711/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-for-Patients-with-Previously-Treated-HER2-Positive-Metastatic-Solid-Tumors</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21-05-2026 22:03 UTC</t>
+          <t>22-05-2026 12:00 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Kidswell Bio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma edges past Dr Reddy’s in FY26 revenue race</t>
+          <t>Kidswell Bio Corp. Faces Financial Challenges Amid Market Evaluation Adjustment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-edges-past-dr-reddys-in-fy26-revenue-race/article71009129.ece</t>
+          <t>https://www.marketsmojo.com/news/stock-recommendation/kidswell-bio-corp-stock-downgraded-from-hold-to-sell-amid-financial-concerns-4003367</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22-05-2026 04:22 UTC</t>
+          <t>22-05-2026 06:18 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1136,59 +1136,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Polpharma</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Announces Launch of Oral Semaglutide Biosimilar 'Obeda®' (tablets) in India</t>
+          <t>Polpharma Biologics and Tuteur Sign Licensing Agreement for a Biosimilar for Autoimmune Diseases</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EquityBulls</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.equitybulls.com/category.php?id=371082</t>
+          <t>https://www.businesswire.com/news/home/20260521106271/en/Polpharma-Biologics-and-Tuteur-Sign-Licensing-Agreement-for-a-Biosimilar-for-Autoimmune-Diseases</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21-05-2026 15:43 UTC</t>
+          <t>22-05-2026 05:00 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Fresenius Kabi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biocon to attend investor conferences on June 2 and June 8</t>
+          <t>2026 Annual General Meeting: Fresenius delivers strong performance in 2025 and proposes 5% increase in dividends</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/biocon-to-attend-investor-conferences-on-june-2-and-june-8/40910908</t>
+          <t>https://www.tradingview.com/news/eqs:ea339e36e094b:0-2026-annual-general-meeting-fresenius-delivers-strong-performance-in-2025-and-proposes-5-increase-in-dividends/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22-05-2026 01:14 UTC</t>
+          <t>22-05-2026 08:00 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1200,478 +1200,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Biocon Limited Important Reminder Regarding Unclaimed Dividends and Share Transfers</t>
+          <t>TEVA's MAA for Olanzapine LAI in Schizophrenia Accepted in the EU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/biocon-reminder-to-claim-unclaimed-dividends/</t>
+          <t>https://finance.yahoo.com/sectors/healthcare/articles/tevas-maa-olanzapine-lai-schizophrenia-153800928.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21-05-2026 13:28 UTC</t>
+          <t>22-05-2026 15:38 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Teva</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Says Unit Incorporates New Subsidiary, Arrow Pharma Production SAS, In France</t>
+          <t>Teva says Humana can't rely on limited agreement with US DOJ in generic drug case</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>MLex</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/reuters.com,2026:newsml_FWN41Y15N:0-aurobindo-pharma-says-unit-incorporates-new-subsidiary-arrow-pharma-production-sas-in-france/</t>
+          <t>https://www.mlex.com/mlex/amp/articles/2480884</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22-05-2026 07:05 UTC</t>
+          <t>21-05-2026 20:51 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma Q4 net up 2% to ₹921 cr</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/business/aurobindo-pharma-q4-net-up-2-to-921-cr/article71007621.ece</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>21-05-2026 16:55 UTC</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Aurobindo Pharma Appoints RPR &amp; Associates as Secretarial Auditor</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-appoints-rpr-associates-as-secretarial-auditor/40939503</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>22-05-2026 07:39 UTC</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Zydus Biotech</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Zydus Lifesciences Limited Just Beat EPS By 9.8%: Here's What Analysts Think Will Happen Next</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://simplywall.st/stocks/in/pharmaceuticals-biotech/nse-zyduslife/zydus-lifesciences-shares/news/zydus-lifesciences-limited-just-beat-eps-by-98-heres-what-an/amp</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>22-05-2026 00:04 UTC</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Zydus Biotech</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Buyback alert! 5 stocks turning ex-record dates for share buybacks in May. Check details</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/markets/stocks/news/buyback-alert-5-stocks-turning-ex-record-dates-for-share-buybacks-in-may-check-details/share-buybacks/slideshow/131255240.cms</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>22-05-2026 02:55 UTC</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Shilpa Biologicals</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Shilpa Medicare Limited Reports Strong FY2026 Results and Strategic Investment in Renewable Energy</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>InvestyWise</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://www.investywise.com/shilpa-medicare-limited-quarterly-financial-results-and-dividend-declaration/</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>22-05-2026 09:29 UTC</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Celltrion Unveils Shareholder-Friendly Measures Including Bonus Issue and Buyback</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>알파경제</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://m.alphabiz.co.kr/news/amp.html?ncode=1065623594323998</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>21-05-2026 21:33 UTC</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Celltrion</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>K-Bio Direct Sales Strategy Pays Off as US Subsidiaries' Earnings Soar</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Seoul Economic Daily</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://en.sedaily.com/finance/2026/05/22/k-bio-direct-sales-strategy-pays-off-as-us-subsidiaries</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>21-05-2026 22:00 UTC</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP for Patients with Previously Treated HER2 Positive Metastatic Solid Tumors</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Business Wire</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://www.businesswire.com/news/home/20260521833711/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-for-Patients-with-Previously-Treated-HER2-Positive-Metastatic-Solid-Tumors</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>22-05-2026 12:00 UTC</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Kidswell Bio</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kidswell Bio Corp. Faces Financial Challenges Amid Market Evaluation Adjustment</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Markets Mojo</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.marketsmojo.com/news/stock-recommendation/kidswell-bio-corp-stock-downgraded-from-hold-to-sell-amid-financial-concerns-4003367</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>22-05-2026 06:18 UTC</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Polpharma</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Polpharma Biologics and Tuteur Sign Licensing Agreement for a Biosimilar for Autoimmune Diseases</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Business Wire</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://www.businesswire.com/news/home/20260521106271/en/Polpharma-Biologics-and-Tuteur-Sign-Licensing-Agreement-for-a-Biosimilar-for-Autoimmune-Diseases</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>22-05-2026 05:00 UTC</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Collaboration</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Fresenius Kabi</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026 Annual General Meeting: Fresenius delivers strong performance in 2025 and proposes 5% increase in dividends</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.marketscreener.com/news/2026-annual-general-meeting-fresenius-delivers-strong-performance-in-2025-and-proposes-5-increase-ce7f5adfdd89f122</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>22-05-2026 08:01 UTC</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>The European Medicines Agency Accepts Teva’s Marketing Authorization Application for Olanzapine Long-Acting Injectable TEV-749 for the Treatment of Schizophrenia in Adults</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://www.globenewswire.com/news-release/2026/05/21/3299597/0/en/the-european-medicines-agency-accepts-teva-s-marketing-authorization-application-for-olanzapine-long-acting-injectable-tev-749-for-the-treatment-of-schizophrenia-in-adults.html</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>21-05-2026 16:30 UTC</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Teva</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Teva says Humana can't rely on limited agreement with US DOJ in generic drug case</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>MLex</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://www.mlex.com/mlex/amp/articles/2480884</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>21-05-2026 20:51 UTC</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1701,7 +1285,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-05-2026 17:51:55</t>
+          <t>22-05-2026 23:14:46</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,123 +464,123 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Chime Biologics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Generics drugmaker Sandoz calls for EU to probe alleged China dumping</t>
+          <t>Recapping the “Must-Know” Information From the 2026 AAD Late-Breaker Sessions—Part 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Times</t>
+          <t>Dermatology Times</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.ft.com/content/9c830f87-01aa-4315-8920-78c517c2bf6a?syn-25a6b1a6=1</t>
+          <t>https://www.dermatologytimes.com/view/recapping-the-must-know-information-from-the-2026-aad-late-breaker-sessions-part-1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22-05-2026 05:32 UTC</t>
+          <t>22-05-2026 18:00 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China approves HERNEXEOS initial treatment lung cancer</t>
+          <t>WYOST® - Video Page</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.boehringer-ingelheim.com/human-health/cancer/lung-cancer/china-approves-hernexeos-initial-treatment-lung-cancer</t>
+          <t>https://www.sandoz.com/ca-en/wyost-video-page</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22-05-2026 07:59 UTC</t>
+          <t>22-05-2026 15:54 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim's oncology portfolio shows strong promise across multiple cancers at ASCO 2026</t>
+          <t>AGP Limited approves major pharma merger plan expected to raise revenue to ₨37.5 billion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Profit by Pakistan Today</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/boehringer-ingelheims-oncology-portfolio-shows-strong-promise-across-multiple-cancers-at-asco-2026-302779545.html</t>
+          <t>https://profit.pakistantoday.com.pk/2026/05/22/agp-limited-approves-major-pharma-merger-plan-expected-to-raise-revenue-to-%E2%82%A837-5-billion/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21-05-2026 21:00 UTC</t>
+          <t>22-05-2026 10:00 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boehringer Ingelheim</t>
+          <t>Stada</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHMP issues positive opinion for JASCAYD® (nerandomilast), bringing a new IPF and PPF therapy closer to patients in the EU</t>
+          <t>Meeting highlights from the Committee for Medicinal Products for Human Use (CHMP) 18-21 May 2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Manila Times</t>
+          <t>European Medicines Agency (EMA)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.manilatimes.net/2026/05/22/tmt-newswire/globenewswire/chmp-issues-positive-opinion-for-jascayd-nerandomilast-bringing-a-new-ipf-and-ppf-therapy-closer-to-patients-in-the-eu/2350052</t>
+          <t>https://www.ema.europa.eu/en/news/meeting-highlights-committee-medicinal-products-human-use-chmp-18-21-may-2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22-05-2026 12:29 UTC</t>
+          <t>22-05-2026 10:50 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -592,91 +592,91 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Japan restores new patient access to Tavneos with tougher warnings</t>
+          <t>EMA poised to be 4th regulator approving Boehringer’s Jascayd lung drug</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/japan-restores-new-patient-access-to-tavneos-with-tougher-warnings</t>
+          <t>https://www.bioworld.com/articles/731385-ema-poised-to-be-4th-regulator-approving-boehringers-jascayd-lung-drug</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22-05-2026 09:48 UTC</t>
+          <t>22-05-2026 16:00 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Organon to supply Hanmi’s 3 combo drugs in Malaysia, Philippines</t>
+          <t>Jascayd reinforces combination therapy shift in US pulmonary fibrosis treatment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>koreabiomed.com</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.koreabiomed.com/news/articleViewAmp.html?idxno=31764</t>
+          <t>https://www.thepharmaletter.com/pharma-news/jascayd-reinforces-combination-therapy-shift-in-us-pulmonary-fibrosis-treatment</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22-05-2026 05:59 UTC</t>
+          <t>22-05-2026 13:38 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Two generic versions of Ozempic begin arriving in Canadian pharmacies this week</t>
+          <t>Amgen CFO to follow David Reese into retirement; Josh Smiley is out at Zai Lab</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Benefits and Pensions Monitor</t>
+          <t>Endpoints News</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.benefitsandpensionsmonitor.com/benefits/pharma/two-generic-versions-of-ozempic-begin-arriving-in-canadian-pharmacies-this-week/393598</t>
+          <t>https://endpoints.news/amgen-cfo-to-follow-david-reese-into-retirement-sanofi-lines-up-a-neurology-leader/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22-05-2026 12:30 UTC</t>
+          <t>22-05-2026 11:00 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -688,27 +688,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Canadians can now get digital prescriptions for 'generic Ozempic'</t>
+          <t>Rx Rundown: Parabilis Medicines, Boston Scientific, Amgen and more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Post</t>
+          <t>Medical Marketing and Media</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://financialpost.com/news/retail-marketing/canadians-digital-prescription-generic-ozempic</t>
+          <t>https://www.mmm-online.com/news/rx-rundown-parabilis-medicines-boston-scientific-amgen-and-more/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21-05-2026 18:51 UTC</t>
+          <t>22-05-2026 11:04 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -720,283 +720,283 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pfizer Pneumococcal Vaccine Elicits Immune Response Across 25 Serotypes</t>
+          <t>Japan restores new patient access to Tavneos with tougher warnings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Drug Topics</t>
+          <t>The Pharma Letter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.drugtopics.com/view/pfizer-pneumococcal-vaccine-elicits-immune-response-across-25-serotypes</t>
+          <t>https://www.thepharmaletter.com/pharma-news/japan-restores-new-patient-access-to-tavneos-with-tougher-warnings</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22-05-2026 15:42 UTC</t>
+          <t>22-05-2026 09:48 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TREM2 agonists detailed in Pfizer patent</t>
+          <t>Pharmalittle: We're reading about a Parkinson's drug setback, a Merck lung cancer therapy, and more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>statnews.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/731263-trem2-agonists-detailed-in-pfizer-patent</t>
+          <t>https://www.statnews.com/pharmalot/2026/05/22/parkinson-drug-trial-setback-merck-lung-cancer-therapy/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22-05-2026 13:00 UTC</t>
+          <t>22-05-2026 13:33 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kazakhstan and Pfizer advance healthcare investment project</t>
+          <t>Sun Pharma sees steady FY27 growth, progresses $11.75 bn Organon integration deal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qazinform</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://qazinform.com/news/kazakhstan-and-pfizer-advance-healthcare-investment-project-67288c</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/sun-pharma-sees-steady-fy27-growth-progresses-11-75-bn-organon-integration-deal/amp_articleshow/131267780.cms</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22-05-2026 07:53 UTC</t>
+          <t>22-05-2026 19:29 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Biogen and Denali Therapeutics Provide Update on Phase 2b LUMA Study of BIIB122 (DNL151) in Early-Stage Parkinson’s Disease</t>
+          <t>Organon deal to strengthen Sun Pharma’s innovative portfolio, says Kirti Ganorkar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://investors.biogen.com/news-releases/news-release-details/biogen-and-denali-therapeutics-provide-update-phase-2b-luma</t>
+          <t>https://www.businesstoday.in/industry/pharma/story/organon-deal-to-strengthen-sun-pharmas-innovative-portfolio-says-kirti-ganorkar-532981-2026-05-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21-05-2026 22:03 UTC</t>
+          <t>23-05-2026 04:47 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Biogen Inc. (BIIB) Securities Fraud Investigation - Levi &amp; Korsinsky</t>
+          <t>Sun Pharma Targets High Single-Digit Growth Amid Organon Integration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/biogen-inc-biib-securities-fraud-investigation---levi--korsinsky-302779232.html</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Sun-Pharma-Targets-High-Single-Digit-Growth-Amid-Organon-Integration/6a10af8ee28c1d234359916c</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22-05-2026 13:00 UTC</t>
+          <t>22-05-2026 21:34 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma to expand manufacture of generic formulations in France</t>
+          <t>Hanmi Pharmaceutical Partners with Organon to Export Combination Therapies to Southeast Asia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>riauone.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/aurobindo-pharma-to-expand-manufacture-of-generic-formulations-in-france/article71011878.ece</t>
+          <t>https://www.riauone.com/global/sub/GlobeNewswire/Hanmi-Pharmaceutical-Partners-with-Organon-to-Export-Combination-Therapies-to-Southeast-Asia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22-05-2026 15:49 UTC</t>
+          <t>22-05-2026 10:39 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aurobindo targets $2 Bn US revenue with in-licensing push</t>
+          <t>Two generic versions of Ozempic begin arriving in Canadian pharmacies this week</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Benefits and Pensions Monitor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/news/pharma-industry/aurobindo-targets-2-bn-us-revenue-with-in-licensing-push/131264107</t>
+          <t>https://www.benefitsandpensionsmonitor.com/benefits/pharma/two-generic-versions-of-ozempic-begin-arriving-in-canadian-pharmacies-this-week/393598</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22-05-2026 13:04 UTC</t>
+          <t>22-05-2026 12:30 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Q4 FY26 revenue rises 5.6% to Rs. 8,853 crore</t>
+          <t>Pfizer Pneumococcal Vaccine Elicits Immune Response Across 25 Serotypes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Drug Topics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/aurobindo-pharma-q4-fy26-revenue-rises-56-to-rs-8853-crore-20308</t>
+          <t>https://www.drugtopics.com/view/pfizer-pneumococcal-vaccine-elicits-immune-response-across-25-serotypes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22-05-2026 01:30 UTC</t>
+          <t>22-05-2026 15:42 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited Reports Strong FY2026 Results and Strategic Investment in Renewable Energy</t>
+          <t>J&amp;J &amp; Pfizer Face Patent Risks: Which Stock Looks Better Positioned?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>Yahoo Finance Singapore</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/shilpa-medicare-limited-quarterly-financial-results-and-dividend-declaration/</t>
+          <t>https://sg.finance.yahoo.com/news/j-j-pfizer-face-patent-140100566.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22-05-2026 09:29 UTC</t>
+          <t>22-05-2026 14:01 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,256 +1008,544 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>K-Bio Direct Sales Strategy Pays Off as US Subsidiaries' Earnings Soar</t>
+          <t>TREM2 agonists detailed in Pfizer patent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seoul Economic Daily</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://en.sedaily.com/finance/2026/05/22/k-bio-direct-sales-strategy-pays-off-as-us-subsidiaries</t>
+          <t>https://www.bioworld.com/articles/731263-trem2-agonists-detailed-in-pfizer-patent</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21-05-2026 22:00 UTC</t>
+          <t>22-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDA grants Daiichi Sankyo and AstraZeneca’s Datroway a key breast cancer approval</t>
+          <t>Denali Therapeutics and Biogen discontinue BIIB122 after Phase 2b LUMA misses endpoints</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://endpoints.news/fda-grants-daiichi-sankyo-and-astrazenecas-datroway-a-key-breast-cancer-approval/</t>
+          <t>https://www.tradingview.com/news/tradingview:89e71ad8aa90e:0-denali-therapeutics-and-biogen-discontinue-biib122-after-phase-2b-luma-misses-endpoints/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22-05-2026 15:28 UTC</t>
+          <t>22-05-2026 10:03 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP for Patients with Previously Treated HER2 Positive Metastatic Solid Tumors</t>
+          <t>Biogen Inc. (BIIB) Securities Fraud Investigation - Levi &amp; Korsinsky</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>PR Newswire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260521833711/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-for-Patients-with-Previously-Treated-HER2-Positive-Metastatic-Solid-Tumors</t>
+          <t>https://www.prnewswire.com/news-releases/biogen-inc-biib-securities-fraud-investigation---levi--korsinsky-302779232.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22-05-2026 12:00 UTC</t>
+          <t>22-05-2026 13:00 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kidswell Bio</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kidswell Bio Corp. Faces Financial Challenges Amid Market Evaluation Adjustment</t>
+          <t>Biogen Drops After Alzheimer’s Trial Setback News Update</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>TradingPedia</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/stock-recommendation/kidswell-bio-corp-stock-downgraded-from-hold-to-sell-amid-financial-concerns-4003367</t>
+          <t>https://www.tradingpedia.com/2026/05/22/biogen-drops-after-alzheimers-trial-setback-news-update/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22-05-2026 06:18 UTC</t>
+          <t>22-05-2026 12:23 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Polpharma Biologics and Tuteur Sign Licensing Agreement for a Biosimilar for Autoimmune Diseases</t>
+          <t>Biogen Inc. (NASDAQ: BIIB) Navigates Alzheimer’s Drug Trajectory After Leqembi Updates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>foreignpolicyjournal.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260521106271/en/Polpharma-Biologics-and-Tuteur-Sign-Licensing-Agreement-for-a-Biosimilar-for-Autoimmune-Diseases</t>
+          <t>https://www.foreignpolicyjournal.com/2026/05/22/biogen-inc-nasdaq-biib-navigates-alzheimers-drug-trajectory-after-leqembi-updates/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22-05-2026 05:00 UTC</t>
+          <t>23-05-2026 02:13 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026 Annual General Meeting: Fresenius delivers strong performance in 2025 and proposes 5% increase in dividends</t>
+          <t>FDA Tentative Approval for PALBOCICLIB issued to DR. REDDY'S LABORATORIES LIMITED</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Quantisnow</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/eqs:ea339e36e094b:0-2026-annual-general-meeting-fresenius-delivers-strong-performance-in-2025-and-proposes-5-increase-in-dividends/</t>
+          <t>https://www.quantisnow.com/insight/fda-tentative-approval-for-palbociclib-issued-to-dr-reddys-laboratories-6569091</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22-05-2026 08:00 UTC</t>
+          <t>23-05-2026 02:03 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TEVA's MAA for Olanzapine LAI in Schizophrenia Accepted in the EU</t>
+          <t>Dr Reddy’s Launches Generic Semaglutide Injection</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>Machine Maker</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/sectors/healthcare/articles/tevas-maa-olanzapine-lai-schizophrenia-153800928.html</t>
+          <t>https://themachinemaker.com/news/dr-reddys-launches-generic-semaglutide-injection/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22-05-2026 15:38 UTC</t>
+          <t>23-05-2026 03:47 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma to Boost Generic Formulations Output at France Facility.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>News on Projects</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.newsonprojects.com/news/aurobindo-pharma-to-boost-generic-formulations-output-at-france-facility</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>23-05-2026 04:09 UTC</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aurobindo targets $2 Bn US revenue with in-licensing push</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETPharma.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/aurobindo-targets-2-bn-us-revenue-with-in-licensing-push/131264107</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>22-05-2026 13:04 UTC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd (BOM:524804) Q4 2026 Earnings Call Highlights: Record Revenues and ... By GuruFocus</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Investing.com Canada</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://ca.investing.com/news/company-news/aurobindo-pharma-ltd-bom524804-q4-2026-earnings-call-highlights-record-revenues-and--4655816</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>22-05-2026 11:34 UTC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shilpa Biologicals</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Shilpa Medicare Limited Reports Strong Financial Growth for FY26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>InvestyWise</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.investywise.com/shilpa-medicare-limited-robust-fy26-financial-growth/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>22-05-2026 09:54 UTC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Datroway approved in the US as first TROP2-directed antibody drug conjugate for 1st-line treatment of patients with metastatic triple-negative breast cancer who are not PD-1/PD-L1 inhibitor candidates</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/datroway-approved-in-us-for-1l-triple-negative-bc.html</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>22-05-2026 13:30 UTC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Enhertu® Recommended for Approval in the EU by CHMP for Patients with Previously Treated HER2 Positive Metastatic Solid Tumors</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260521833711/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-for-Patients-with-Previously-Treated-HER2-Positive-Metastatic-Solid-Tumors</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>22-05-2026 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Polpharma</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Polpharma Biologics and Tuteur Sign Licensing Agreement for a Biosimilar for Autoimmune Diseases</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The National Law Review</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://natlawreview.com/press-releases/polpharma-biologics-and-tuteur-sign-licensing-agreement-biosimilar</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>22-05-2026 11:29 UTC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026 Annual General Meeting of Fresenius: Shareholders approve all agenda items</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.tradingview.com/news/eqs:9a8bdf1ad094b:0-2026-annual-general-meeting-of-fresenius-shareholders-approve-all-agenda-items/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>22-05-2026 14:44 UTC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Teva says Humana can't rely on limited agreement with US DOJ in generic drug case</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MLex</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.mlex.com/mlex/amp/articles/2480884</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>21-05-2026 20:51 UTC</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Other</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TEVA's MAA for Olanzapine LAI in Schizophrenia Accepted in the EU</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/sectors/healthcare/articles/tevas-maa-olanzapine-lai-schizophrenia-153800928.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>22-05-2026 15:38 UTC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Teva Q1 2026 Earnings: Strong EPS Beat on Cost Discipline, Shares Edge Higher - Social Signal Watchlist</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Newser</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.newser.com/expert-time/Teva-Q1-2026-Earnings-Strong-EPS-Beat-on-Cost-Discipline-Shares-Edge-Higher-22-957</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22-05-2026 17:48 UTC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-05-2026 23:14:46</t>
+          <t>23-05-2026 15:07:09</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,64 +528,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandoz</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AGP Limited approves major pharma merger plan expected to raise revenue to ₨37.5 billion</t>
+          <t>EMA poised to be 4th regulator approving Boehringer’s Jascayd lung drug</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Profit by Pakistan Today</t>
+          <t>BioWorld News</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://profit.pakistantoday.com.pk/2026/05/22/agp-limited-approves-major-pharma-merger-plan-expected-to-raise-revenue-to-%E2%82%A837-5-billion/</t>
+          <t>https://www.bioworld.com/articles/731385-ema-poised-to-be-4th-regulator-approving-boehringers-jascayd-lung-drug</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22-05-2026 10:00 UTC</t>
+          <t>22-05-2026 16:00 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stada</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meeting highlights from the Committee for Medicinal Products for Human Use (CHMP) 18-21 May 2026</t>
+          <t>Zongertinib Shows Early Symptom Relief in LUNG-1 PRO Trial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>European Medicines Agency (EMA)</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.ema.europa.eu/en/news/meeting-highlights-committee-medicinal-products-human-use-chmp-18-21-may-2026</t>
+          <t>https://www.clinicaltrialvanguard.com/news/zongertinib-shows-early-symptom-relief-in-lung-1-pro-trial/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22-05-2026 10:50 UTC</t>
+          <t>23-05-2026 06:51 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -597,22 +597,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EMA poised to be 4th regulator approving Boehringer’s Jascayd lung drug</t>
+          <t>Europe's CHMP gives thumbs up to AZ's breast cancer drug after thumbs down from FDA adcomm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>Fierce Pharma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/731385-ema-poised-to-be-4th-regulator-approving-boehringers-jascayd-lung-drug</t>
+          <t>https://www.fiercepharma.com/pharma/europes-chmp-gives-thumbs-azs-breast-cancer-drug-after-thumbs-down-fda-adcomm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22-05-2026 16:00 UTC</t>
+          <t>22-05-2026 15:58 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -629,22 +629,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jascayd reinforces combination therapy shift in US pulmonary fibrosis treatment</t>
+          <t>A New Era for Locally Advanced NSCLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/jascayd-reinforces-combination-therapy-shift-in-us-pulmonary-fibrosis-treatment</t>
+          <t>https://www.medscape.com/viewarticle/new-era-locally-advanced-nsclc-2026a1000fnu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22-05-2026 13:38 UTC</t>
+          <t>22-05-2026 21:04 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -656,27 +656,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amgen CFO to follow David Reese into retirement; Josh Smiley is out at Zai Lab</t>
+          <t>How clinical research is improving patient care across south Essex hospitals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Endpoints News</t>
+          <t>Southend Echo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://endpoints.news/amgen-cfo-to-follow-david-reese-into-retirement-sanofi-lines-up-a-neurology-leader/</t>
+          <t>http://www.southendstandard.co.uk/news/26121758.clinical-research-improving-patient-care-essex/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22-05-2026 11:00 UTC</t>
+          <t>23-05-2026 03:00 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -693,27 +693,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rx Rundown: Parabilis Medicines, Boston Scientific, Amgen and more</t>
+          <t>Amgen Inc. (NASDAQ: AMGN) Stock Trades Near $330 as Japan Drug Safety Crisis Raises Concerns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Marketing and Media</t>
+          <t>foreignpolicyjournal.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.mmm-online.com/news/rx-rundown-parabilis-medicines-boston-scientific-amgen-and-more/</t>
+          <t>https://www.foreignpolicyjournal.com/2026/05/22/amgen-inc-nasdaq-amgn-stock-trades-near-330-as-japan-drug-safety-crisis-raises-concerns/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22-05-2026 11:04 UTC</t>
+          <t>23-05-2026 01:24 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -725,22 +725,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Japan restores new patient access to Tavneos with tougher warnings</t>
+          <t>Combination Therapies in the Acute Treatment of Migraine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The Pharma Letter</t>
+          <t>Medscape</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.thepharmaletter.com/pharma-news/japan-restores-new-patient-access-to-tavneos-with-tougher-warnings</t>
+          <t>https://reference.medscape.com/viewarticle/migraine-treatment-combination-therapy-acute-care-2026a10008ba</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22-05-2026 09:48 UTC</t>
+          <t>22-05-2026 15:56 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -757,91 +757,91 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pharmalittle: We're reading about a Parkinson's drug setback, a Merck lung cancer therapy, and more</t>
+          <t>Amgen Expands Lung Cancer Pipeline With New Tarlatamab Combo Study</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>statnews.com</t>
+          <t>TipRanks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.statnews.com/pharmalot/2026/05/22/parkinson-drug-trial-setback-merck-lung-cancer-therapy/</t>
+          <t>https://www.tipranks.com/news/company-announcements/amgen-expands-lung-cancer-pipeline-with-new-tarlatamab-combo-study</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22-05-2026 13:33 UTC</t>
+          <t>22-05-2026 17:28 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sun Pharma sees steady FY27 growth, progresses $11.75 bn Organon integration deal</t>
+          <t>Amgen Rehires Alum Thomas Dittrich to Replace Retiring CFO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>HarianBasis.co</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/sun-pharma-sees-steady-fy27-growth-progresses-11-75-bn-organon-integration-deal/amp_articleshow/131267780.cms</t>
+          <t>https://www.harianbasis.co/en/amgen-rehires-thomas-dittrich-cfo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22-05-2026 19:29 UTC</t>
+          <t>22-05-2026 22:14 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Organon deal to strengthen Sun Pharma’s innovative portfolio, says Kirti Ganorkar</t>
+          <t>Amgen Pipeline Strength and Rare Disease Momentum Highlighted as Key Growth Drivers - Expert Momentum Signals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Newser</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/industry/pharma/story/organon-deal-to-strengthen-sun-pharmas-innovative-portfolio-says-kirti-ganorkar-532981-2026-05-23</t>
+          <t>https://www.newser.com/expert-time/Amgen-Pipeline-Strength-and-Rare-Disease-Momentum-Highlighted-as-Key-Growth-Drivers-21-771</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23-05-2026 04:47 UTC</t>
+          <t>22-05-2026 19:21 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sun Pharma Targets High Single-Digit Growth Amid Organon Integration</t>
+          <t>Sun Pharma sees steady FY27 growth, progresses $11.75 bn Organon integration deal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Whalesbook</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Sun-Pharma-Targets-High-Single-Digit-Growth-Amid-Organon-Integration/6a10af8ee28c1d234359916c</t>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/pharmaceuticals/sun-pharma-sees-steady-fy27-growth-progresses-11-75-bn-organon-integration-deal/amp_articleshow/131267780.cms</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22-05-2026 21:34 UTC</t>
+          <t>22-05-2026 19:29 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -885,118 +885,118 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hanmi Pharmaceutical Partners with Organon to Export Combination Therapies to Southeast Asia</t>
+          <t>​10 Incredible Facts About Sun Pharma’s Historic $11.75 Billion Organon Acquisition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>riauone.com</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.riauone.com/global/sub/GlobeNewswire/Hanmi-Pharmaceutical-Partners-with-Organon-to-Export-Combination-Therapies-to-Southeast-Asia</t>
+          <t>https://www.aol.com/articles/10-incredible-facts-sun-pharma-192054000.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22-05-2026 10:39 UTC</t>
+          <t>23-05-2026 07:42 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Apotex</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Two generic versions of Ozempic begin arriving in Canadian pharmacies this week</t>
+          <t>Organon deal to strengthen Sun Pharma’s innovative portfolio, says Kirti Ganorkar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Benefits and Pensions Monitor</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.benefitsandpensionsmonitor.com/benefits/pharma/two-generic-versions-of-ozempic-begin-arriving-in-canadian-pharmacies-this-week/393598</t>
+          <t>https://www.businesstoday.in/industry/pharma/story/organon-deal-to-strengthen-sun-pharmas-innovative-portfolio-says-kirti-ganorkar-532981-2026-05-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22-05-2026 12:30 UTC</t>
+          <t>23-05-2026 04:47 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pfizer Pneumococcal Vaccine Elicits Immune Response Across 25 Serotypes</t>
+          <t>Sun Pharma Targets High Single-Digit Growth Amid Organon Integration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Drug Topics</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.drugtopics.com/view/pfizer-pneumococcal-vaccine-elicits-immune-response-across-25-serotypes</t>
+          <t>https://www.whalesbook.com/news/English/healthcarebiotech/Sun-Pharma-Targets-High-Single-Digit-Growth-Amid-Organon-Integration/6a10af8ee28c1d234359916c</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22-05-2026 15:42 UTC</t>
+          <t>22-05-2026 21:34 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J&amp;J &amp; Pfizer Face Patent Risks: Which Stock Looks Better Positioned?</t>
+          <t>Sun Pharma forecasts slower FY27 revenue growth after FY26 results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yahoo Finance Singapore</t>
+          <t>NewsBytes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://sg.finance.yahoo.com/news/j-j-pfizer-face-patent-140100566.html</t>
+          <t>https://www.newsbytesapp.com/news/business/sun-pharma-forecasts-slower-fy27-revenue-growth-after-fy26-results/tldr</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22-05-2026 14:01 UTC</t>
+          <t>22-05-2026 17:54 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1008,347 +1008,347 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TREM2 agonists detailed in Pfizer patent</t>
+          <t>Sun Pharma Q4 profit rises 26% in FY26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BioWorld News</t>
+          <t>newskarnataka.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.bioworld.com/articles/731263-trem2-agonists-detailed-in-pfizer-patent</t>
+          <t>https://newskarnataka.com/business/sun-pharma-q4-profit-rises-26-in-fy26/23052026/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22-05-2026 13:00 UTC</t>
+          <t>23-05-2026 13:30 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Denali Therapeutics and Biogen discontinue BIIB122 after Phase 2b LUMA misses endpoints</t>
+          <t>Ontario telehealth platform rolls out digital prescriptions for generic Ozempic to aid weight loss</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Guelph Mercury</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/tradingview:89e71ad8aa90e:0-denali-therapeutics-and-biogen-discontinue-biib122-after-phase-2b-luma-misses-endpoints/</t>
+          <t>https://www.guelphmercury.com/news/ontario-generic-ozempic-apotex-digital-prescriptions/article_8eb5957b-9e3a-5763-b9b0-f46d5eab9d39.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22-05-2026 10:03 UTC</t>
+          <t>22-05-2026 20:56 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen Inc. (BIIB) Securities Fraud Investigation - Levi &amp; Korsinsky</t>
+          <t>Generic Semaglutide Arrives In Canada As Ozempic Market Faces Major Shakeup</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>Weekly Voice</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/biogen-inc-biib-securities-fraud-investigation---levi--korsinsky-302779232.html</t>
+          <t>https://weeklyvoice.com/generic-semaglutide-arrives-in-canada-as-ozempic-market-faces-major-shakeup/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22-05-2026 13:00 UTC</t>
+          <t>22-05-2026 19:23 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Apotex</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biogen Drops After Alzheimer’s Trial Setback News Update</t>
+          <t>Generic Semaglutide Launches in Canada Following Patent Expiry</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TradingPedia</t>
+          <t>asatunews.co.id</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.tradingpedia.com/2026/05/22/biogen-drops-after-alzheimers-trial-setback-news-update/</t>
+          <t>https://www.asatunews.co.id/en/generic-semaglutide-launches-canada</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22-05-2026 12:23 UTC</t>
+          <t>22-05-2026 16:12 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biogen Inc. (NASDAQ: BIIB) Navigates Alzheimer’s Drug Trajectory After Leqembi Updates</t>
+          <t>CS reviews sustainability plan for Industrial Biotech Parks in J&amp;K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>foreignpolicyjournal.com</t>
+          <t>Rising Kashmir</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.foreignpolicyjournal.com/2026/05/22/biogen-inc-nasdaq-biib-navigates-alzheimers-drug-trajectory-after-leqembi-updates/</t>
+          <t>https://risingkashmir.com/cs-reviews-sustainability-plan-for-industrial-biotech-parks-in-jk/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23-05-2026 02:13 UTC</t>
+          <t>23-05-2026 05:29 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDA Tentative Approval for PALBOCICLIB issued to DR. REDDY'S LABORATORIES LIMITED</t>
+          <t>Pfizer’s SWOT analysis: stock navigates patent cliff with new drugs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quantisnow</t>
+          <t>Investing.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.quantisnow.com/insight/fda-tentative-approval-for-palbociclib-issued-to-dr-reddys-laboratories-6569091</t>
+          <t>https://www.investing.com/news/swot-analysis/pfizers-swot-analysis-stock-navigates-patent-cliff-with-new-drugs-93CH-4708039</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23-05-2026 02:03 UTC</t>
+          <t>23-05-2026 12:23 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dr. Reddy's</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr Reddy’s Launches Generic Semaglutide Injection</t>
+          <t>Pfizer's growth and cost savings boost revenues and dividends, making it a strong buy for patient investors.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Machine Maker</t>
+          <t>Pluang</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://themachinemaker.com/news/dr-reddys-launches-generic-semaglutide-injection/</t>
+          <t>https://pluang.com/en/news-feed/pfizer-risiko-paten-turun-dan-upaya-mna-mendorong-saham</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23-05-2026 03:47 UTC</t>
+          <t>22-05-2026 21:44 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma to Boost Generic Formulations Output at France Facility.</t>
+          <t>Pfizer’s 50% Stock Crash: A Hidden Contrarian Buy Amid Booming Healthcare Sector</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>News on Projects</t>
+          <t>NAI500</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.newsonprojects.com/news/aurobindo-pharma-to-boost-generic-formulations-output-at-france-facility</t>
+          <t>https://nai500.com/blog/2026/05/pfizers-50-stock-crash-a-hidden-contrarian-buy-amid-booming-healthcare-sector/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23-05-2026 04:09 UTC</t>
+          <t>23-05-2026 01:28 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aurobindo targets $2 Bn US revenue with in-licensing push</t>
+          <t>Effect of COVID-19 Vaccination on the Menstrual Cycle Among Women in Dubai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Cureus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/aurobindo-targets-2-bn-us-revenue-with-in-licensing-push/131264107</t>
+          <t>https://www.cureus.com/articles/393493-effect-of-covid-19-vaccination-on-the-menstrual-cycle-among-women-in-dubai</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22-05-2026 13:04 UTC</t>
+          <t>22-05-2026 21:18 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd (BOM:524804) Q4 2026 Earnings Call Highlights: Record Revenues and ... By GuruFocus</t>
+          <t>COVID pioneer BioNTech: The fall of Germany's pandemic hero</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Investing.com Canada</t>
+          <t>DW.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://ca.investing.com/news/company-news/aurobindo-pharma-ltd-bom524804-q4-2026-earnings-call-highlights-record-revenues-and--4655816</t>
+          <t>https://www.dw.com/en/germanys-biontech-from-covid-vaccine-breakthrough-to-crisis/a-77061364</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22-05-2026 11:34 UTC</t>
+          <t>23-05-2026 00:21 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shilpa Biologicals</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited Reports Strong Financial Growth for FY26</t>
+          <t>Pfizer Stock: Still Priced Like It's Dead Money</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>InvestyWise</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.investywise.com/shilpa-medicare-limited-robust-fy26-financial-growth/</t>
+          <t>https://www.aol.com/articles/pfizer-stock-still-priced-dead-233500000.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22-05-2026 09:54 UTC</t>
+          <t>23-05-2026 08:51 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1360,190 +1360,958 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Datroway approved in the US as first TROP2-directed antibody drug conjugate for 1st-line treatment of patients with metastatic triple-negative breast cancer who are not PD-1/PD-L1 inhibitor candidates</t>
+          <t>20 deaths: Kissei Pharmaceutical urges doctors to halt Tavneos use</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>朝日新聞</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.astrazeneca.com/media-centre/press-releases/2026/datroway-approved-in-us-for-1l-triple-negative-bc.html</t>
+          <t>https://www.asahi.com/ajw/articles/photo/79676583</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22-05-2026 13:30 UTC</t>
+          <t>23-05-2026 01:03 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Enhertu® Recommended for Approval in the EU by CHMP for Patients with Previously Treated HER2 Positive Metastatic Solid Tumors</t>
+          <t>Parkinson’s drug from Biogen, Denali comes up short</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>BioPharma Dive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260521833711/en/Enhertu-Recommended-for-Approval-in-the-EU-by-CHMP-for-Patients-with-Previously-Treated-HER2-Positive-Metastatic-Solid-Tumors</t>
+          <t>https://www.biopharmadive.com/news/biogen-denali-parkinsons-trial-failure-lrrk2/820961/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22-05-2026 12:00 UTC</t>
+          <t>22-05-2026 18:33 UTC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Polpharma Biologics and Tuteur Sign Licensing Agreement for a Biosimilar for Autoimmune Diseases</t>
+          <t>Biogen Faces Trial Setbacks And Probes That Reframe Neuro Pipeline Risks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The National Law Review</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://natlawreview.com/press-releases/polpharma-biologics-and-tuteur-sign-licensing-agreement-biosimilar</t>
+          <t>https://uk.finance.yahoo.com/news/biogen-faces-trial-setbacks-probes-201541282.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22-05-2026 11:29 UTC</t>
+          <t>22-05-2026 20:15 UTC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026 Annual General Meeting of Fresenius: Shareholders approve all agenda items</t>
+          <t>Biogen Inc. (NASDAQ: BIIB) Navigates Alzheimer’s Drug Trajectory After Leqembi Updates</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>foreignpolicyjournal.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/eqs:9a8bdf1ad094b:0-2026-annual-general-meeting-of-fresenius-shareholders-approve-all-agenda-items/</t>
+          <t>https://www.foreignpolicyjournal.com/2026/05/22/biogen-inc-nasdaq-biib-navigates-alzheimers-drug-trajectory-after-leqembi-updates/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22-05-2026 14:44 UTC</t>
+          <t>23-05-2026 02:13 UTC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TEVA's MAA for Olanzapine LAI in Schizophrenia Accepted in the EU</t>
+          <t>UBS Upgrades Biogen to Buy With a $225 Target: Are the Next 12 Months a Pipeline Catalyst Parade?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yahoo Finance</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://finance.yahoo.com/sectors/healthcare/articles/tevas-maa-olanzapine-lai-schizophrenia-153800928.html</t>
+          <t>https://www.aol.com/articles/ubs-upgrades-biogen-buy-225-142753000.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22-05-2026 15:38 UTC</t>
+          <t>22-05-2026 20:46 UTC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Biogen and Denali Halt Development of BIIB122 After Phase 2b LUMA Study Fails in Early Parkinson’s Disease</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minichart</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.minichart.com.sg/2026/05/22/biogen-and-denali-halt-development-of-biib122-after-phase-2b-luma-study-fails-in-early-parkinsons-disease/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22-05-2026 19:03 UTC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Denali Stock Dips as Biogen-Partnered Parkinson's Disease Study Fails</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/sectors/healthcare/articles/denali-stock-dips-biogen-partnered-161400202.html</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>22-05-2026 16:14 UTC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BIIB, DNLI Stocks Edge Lower After Hours: Parkinson’s Drug Misses Key Goals In Trial</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/biib-dnli-stocks-edge-lower-after-hours-parkinsons-drug-misses-key-goals-in-trial/cZXCkReRe8V</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>22-05-2026 21:17 UTC</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BIIB122 Fails to Slow Parkinson’s Progression Despite Strong Target Engagement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>The Clinical Trial Vanguard</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.clinicaltrialvanguard.com/news/biib122-fails-to-slow-parkinsons-progression-despite-strong-target-engagement/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23-05-2026 06:51 UTC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Biogen Q1 2026 Earnings: Strong EPS Beat Drives Post-Market Rally - Analyst Drop Coverage</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Newser</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.newser.com/expert-time/Biogen-Q1-2026-Earnings-Strong-EPS-Beat-Drives-PostMarket-Rally-22-964</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>22-05-2026 18:38 UTC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mr Daneshwar Kumar, Head – MSAT, Dr Reddy's Laboratories</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Express Pharma</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.expresspharma.in/mr-daneshwar-kumar-head-msat-dr-reddys-laboratories-10-apr-2026-hyd/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>23-05-2026 10:56 UTC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dr Reddy’s Launches Generic Semaglutide Injection</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Machine Maker</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://themachinemaker.com/news/dr-reddys-launches-generic-semaglutide-injection/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23-05-2026 03:47 UTC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FDA Tentative Approval for PALBOCICLIB issued to DR. REDDY'S LABORATORIES LIMITED</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Quantisnow</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.quantisnow.com/insight/fda-tentative-approval-for-palbociclib-issued-to-dr-reddys-laboratories-6569091</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23-05-2026 02:03 UTC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mr Sridhar Balasubramanian, Head Quality – Sterile / Parenteral, Dr Reddy's Laboratories</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Express Pharma</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.expresspharma.in/mr-sridhar-balasubramanian-head-quality-sterile-parenteral-dr-reddys-laboratories-10-apr-2026-hyd/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23-05-2026 11:09 UTC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Panel Discussion: Beyond generics: Moving into complex injectables, oncology and biosimilars</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Express Pharma</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.expresspharma.in/panel-discussion-beyond-generics-moving-into-complex-injectables-oncology-and-biosimilars-10-apr-2026-hyd/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23-05-2026 11:05 UTC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ozempic faces first major generic challenge after patent lapse</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dagens.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dagens.com/health-0/ozempic-faces-first-major-generic-challenge-after-patent-lapse</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23-05-2026 15:19 UTC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Generic GLP-1s, Biosimilars Could Aid UK Diabetes Care</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Pharmacy Business</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.pharmacy.biz/generic-glp1s-biosimilars-diabetes-uk/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>23-05-2026 11:40 UTC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma to Boost Generic Formulations Output at France Facility.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>News on Projects</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.newsonprojects.com/news/aurobindo-pharma-to-boost-generic-formulations-output-at-france-facility</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>23-05-2026 04:09 UTC</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Q4 FY26: Margin Pressure Clouds Strong Revenue Growth</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Markets Mojo</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.marketsmojo.com/news/result-analysis/aurobindo-pharma-q4-fy26-margin-pressure-clouds-strong-revenue-growth-4005346</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>23-05-2026 12:41 UTC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Celltrion</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Subcutaneous Infliximab May Improve Convenience, Adherence, and Sustained Remission in IBD Care</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BioPharm International</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.biopharminternational.com/view/subcutaneous-infliximab-may-improve-convenience-adherence-and-sustained-remission-in-ibd-care</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>22-05-2026 20:31 UTC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Datopotamab Deruxtecan Earns New Breast Cancer Indication</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Medscape</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.medscape.com/viewarticle/datopotamab-deruxtecan-earns-new-breast-cancer-indication-2026a1000gti</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>22-05-2026 17:48 UTC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FDA Approves Datroway as First-Line Therapy for Triple-Negative Breast Cancer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Inside Precision Medicine</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.insideprecisionmedicine.com/topics/oncology/fda-approves-datroway-as-first-line-therapy-for-triple-negative-breast-cancer/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>22-05-2026 17:21 UTC</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Datroway US approval in first-line metastatic TNBC announced</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>The Pharma Letter</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.thepharmaletter.com/biotech-news/datroway-us-approval-in-first-line-metastatic-tnbc-announced</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>22-05-2026 22:34 UTC</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FDA Approves Datroway for Patients with Metastatic Triple-Negative Breast Cancer Who Are Not PD-1/PD-L1 Inhibitor Candidates</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pharmaceutical Executive</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.pharmexec.com/view/fda-approves-datroway-metastatic-triple-negative-breast-cancer-pd-1-pd-l1-inhibitor-candidates</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>22-05-2026 17:44 UTC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Enhertu receives EU approval recommendation for HER2+ solid tumors By Investing.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Investing.com South Africa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://za.investing.com/news/stock-market-news/enhertu-receives-eu-approval-recommendation-for-her2-solid-tumors-93CH-4296692</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>22-05-2026 17:14 UTC</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Enhertu secures positive CHMP opinion for HER2 positive solid tumors</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>grafa.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://grafa.com/en/news/united-states/astrazeneca-daiichi-enhertu-eu-chmp-recommendation-solid-tumors</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>22-05-2026 16:45 UTC</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Panel Discussion: The next decade of injectables: Science, scale and new therapies</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Express Pharma</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.expresspharma.in/panel-discussion-the-next-decade-of-injectables-science-scale-and-new-therapies-10-apr-2026-hyd/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>23-05-2026 10:25 UTC</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Adoption of AI for Early Drug Discovery: Challenges and Opportunities for CROs</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fierce Biotech</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.fiercebiotech.com/premium/webinar/1381133</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>22-05-2026 20:46 UTC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Teva Stock Is at Its Highest Level in Nearly a Decade. Here's Why It Could Soar Even More.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AOL.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.aol.com/articles/teva-stock-highest-level-nearly-052000663.html</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>22-05-2026 21:53 UTC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Teva Q1 2026 Earnings: Strong EPS Beat on Cost Discipline, Shares Edge Higher - Social Signal Watchlist</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Newser</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://www.newser.com/expert-time/Teva-Q1-2026-Earnings-Strong-EPS-Beat-on-Cost-Discipline-Shares-Edge-Higher-22-957</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>22-05-2026 17:48 UTC</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1573,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-05-2026 15:07:09</t>
+          <t>23-05-2026 21:25:36</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,59 +469,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UK pet owners warned over 'very concerning' counterfeit flea treatments</t>
+          <t>Pfizer Oncology Partnerships Add Detail To Valuation And Earnings Concerns</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Birmingham Live</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.birminghammail.co.uk/news/midlands-news/uk-pet-owners-warned-over-33962931.amp</t>
+          <t>https://uk.finance.yahoo.com/news/pfizer-oncology-partnerships-add-detail-020827334.html</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23-05-2026 17:05 UTC</t>
+          <t>24-05-2026 02:08 UTC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Boehringer Ingelheim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Does Amgen’s CFO Transition and Board Structure Shape a New Governance Story for AMGN?</t>
+          <t>UK pet owners warned over 'very concerning' counterfeit flea treatments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Birmingham Live</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-amgn/amgen/news/does-amgens-cfo-transition-and-board-structure-shape-a-new-g</t>
+          <t>https://www.birminghammail.co.uk/news/midlands-news/uk-pet-owners-warned-over-33962931.amp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23-05-2026 18:39 UTC</t>
+          <t>23-05-2026 17:05 UTC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Legato Capital Management LLC Acquires Shares of 8,328 Amgen Inc. $AMGN</t>
+          <t>Amgen Inc. $AMGN Shares Sold by Swedbank AB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.marketbeat.com/instant-alerts/filing-legato-capital-management-llc-acquires-shares-of-8328-amgen-inc-amgn-2026-05-23/</t>
+          <t>https://www.marketbeat.com/instant-alerts/filing-amgen-inc-amgn-shares-sold-by-swedbank-ab-2026-05-24/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23-05-2026 11:06 UTC</t>
+          <t>24-05-2026 11:05 UTC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -565,22 +565,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMGN Q1 2026 Earnings: EPS Surpasses Estimates by 6.14%, Stock Edges Higher - Open Market Insights</t>
+          <t>Does Amgen’s CFO Transition and Board Structure Shape a New Governance Story for AMGN?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newser</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>http://www.newser.com/expert-time/AMGN-Q1-2026-Earnings-EPS-Surpasses-Estimates-by-614-Stock-Edges-Higher-22-4612</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-amgn/amgen/news/does-amgens-cfo-transition-and-board-structure-shape-a-new-g</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23-05-2026 20:40 UTC</t>
+          <t>23-05-2026 18:39 UTC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -592,128 +592,128 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organon</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>​10 Incredible Facts About Sun Pharma’s Historic $11.75 Billion Organon Acquisition</t>
+          <t>Amgen Inc. $AMGN is Smead Capital Management Inc.'s 5th Largest Position</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>MarketBeat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/10-incredible-facts-sun-pharma-192054000.html</t>
+          <t>https://www.marketbeat.com/instant-alerts/filing-amgen-inc-amgn-is-smead-capital-management-incs-5th-largest-position-2026-05-24/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24-05-2026 02:58 UTC</t>
+          <t>24-05-2026 10:23 UTC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Acquisition</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
+          <t>​10 Incredible Facts About Sun Pharma’s Historic $11.75 Billion Organon Acquisition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical Economics</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
+          <t>https://www.aol.com/articles/10-incredible-facts-sun-pharma-192054000.html</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24-05-2026 01:20 UTC</t>
+          <t>24-05-2026 02:58 UTC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pfizer Oncology Partnerships Add Detail To Valuation And Earnings Concerns</t>
+          <t>Anupam Rasayan To Acquire Up To 43.3% Stake In Bliss GVS Pharma, Deal Valued At Around ₹1,370 Crore</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/pfizer-oncology-partnerships-add-detail-020827334.html</t>
+          <t>https://www.freepressjournal.in/amp/business/anupam-rasayan-to-acquire-up-to-433-stake-in-bliss-gvs-pharma-deal-valued-at-around-1370-crore</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24-05-2026 02:08 UTC</t>
+          <t>24-05-2026 09:05 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Plant Form</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pfizer Collaboration Targets Faster Cancer Trials While Shares Trade Below Value</t>
+          <t>CS reviews sustainability plan for Industrial Biotech Parks in J&amp;K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Rising Kashmir</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nyse-pfe/pfizer/news/pfizer-collaboration-targets-faster-cancer-trials-while-shar/amp</t>
+          <t>https://risingkashmir.com/cs-reviews-sustainability-plan-for-industrial-biotech-parks-in-jk/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24-05-2026 01:32 UTC</t>
+          <t>24-05-2026 04:34 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -725,27 +725,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pfizer’s SWOT analysis: stock navigates patent cliff with new drugs</t>
+          <t>Pfizer’s Lyme disease vaccine shows 70% efficacy; Texas man sentenced to 12.5 years in $61.5M Medicare telemarketing fraud scheme; Novo Nordisk launches Wegovy subscription model – Morning Medical Update</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Investing.com</t>
+          <t>Medical Economics</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.investing.com/news/swot-analysis/pfizers-swot-analysis-stock-navigates-patent-cliff-with-new-drugs-93CH-4708039</t>
+          <t>https://www.medicaleconomics.com/view/pfizer-s-lyme-disease-vaccine-shows-70-efficacy-texas-man-sentenced-to-12-5-years-in-61-5m-medicare-telemarketing-fraud-scheme-novo-nordisk-launches-wegovy-subscription-model-morning-medical-update</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23-05-2026 12:23 UTC</t>
+          <t>24-05-2026 01:20 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
@@ -757,22 +757,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Depo Provera Lawsuit Settlement | May 2026 Litigation Update</t>
+          <t>Erectile Dysfunction After Pfizer Vaccine: What the Evidence Shows and Practical Support Options</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lawsuit Information Center</t>
+          <t>Portal CNJ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.lawsuit-information-center.com/depo-provera-lawsuit.html</t>
+          <t>https://www.cnj.jus.br/ojs/plugins/generic/pdfJsViewer/pdf.js/web/viewer.html?file=%2Fojs%2Findex.php%2Findex%2Flogin%2FsignOut%3Fsource%3D%2Ec%2Eopenf1%2Ecloud%2Fmale%2F&amp;id=0wSJzZ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23-05-2026 20:28 UTC</t>
+          <t>24-05-2026 09:24 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -789,27 +789,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A Monthly Weight Loss Shot? Why Pfizer Could Topple Lilly's and Novo's GLP-1 Duopoly</t>
+          <t>Pfizer Collaboration Targets Faster Cancer Trials While Shares Trade Below Value</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/monthly-weight-loss-shot-why-115000000.html</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nyse-pfe/pfizer/news/pfizer-collaboration-targets-faster-cancer-trials-while-shar/amp</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24-05-2026 07:18 UTC</t>
+          <t>24-05-2026 01:32 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -821,27 +821,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zim pushes for Pfizer deal to boost access to medicines and vaccines</t>
+          <t>Depo Provera Lawsuit Settlement | May 2026 Litigation Update</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Herald ZW</t>
+          <t>Lawsuit Information Center</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.heraldonline.co.zw/zim-puses-for-pfizer-deal-to-boost-access-to-medicines-and-vaccines/</t>
+          <t>https://www.lawsuit-information-center.com/depo-provera-lawsuit.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23-05-2026 22:02 UTC</t>
+          <t>23-05-2026 20:28 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -853,27 +853,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaccine for Lyme disease may counter some consequences of tick bites</t>
+          <t>A Monthly Weight Loss Shot? Why Pfizer Could Topple Lilly's and Novo's GLP-1 Duopoly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Toledo Blade</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.toledoblade.com/news/health-and-well-being/2026/05/24/vaccine-for-lyme-disease-may-counter-some-consequences-of-tick-bites/stories/20260509087</t>
+          <t>https://www.aol.com/articles/monthly-weight-loss-shot-why-115000000.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24-05-2026 04:05 UTC</t>
+          <t>24-05-2026 07:18 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
@@ -885,27 +885,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2 Reasons to Watch PFE and 1 to Stay Cautious</t>
+          <t>Zim pushes for Pfizer deal to boost access to medicines and vaccines</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yahoo Finance UK</t>
+          <t>The Herald ZW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://uk.finance.yahoo.com/news/2-reasons-watch-pfe-1-173255559.html</t>
+          <t>https://www.heraldonline.co.zw/zim-pushes-for-pfizer-deal-to-boost-access-to-medicines-and-vaccines/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23-05-2026 17:32 UTC</t>
+          <t>23-05-2026 22:02 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
@@ -917,59 +917,59 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pfizer's pneumococcal shot shows stronger immune response in mid-stage trial</t>
+          <t>Viagra by Pfizer price: what it actually costs in 2026 and how to evaluate the options</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Ministerio de Salud Pública de Tucumán</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/pfizers-pneumococcal-shot-shows-stronger-090837000.html</t>
+          <t>https://msptucuman.gov.ar/wordpress/wp-content/uploads/tours-virtuales/padilla/?xml=data:image/gif;base64,PGtycGFubyBvbnN0YXJ0PSJsb2FkcGFubygnL1wvNm1nLnRvcC8yMDI2L21hbGUvP3ZpZD00dnRnUDEnKTsiPjwva3JwYW5vPg==</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23-05-2026 21:43 UTC</t>
+          <t>23-05-2026 20:58 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ionis Pharmaceuticals (IONS) Valuation Check After Biogen Releases Phase 2 CELIA Alzheimer’s Study Results</t>
+          <t>2 Reasons to Watch PFE and 1 to Stay Cautious</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-ions/ionis-pharmaceuticals/news/ionis-pharmaceuticals-ions-valuation-check-after-biogen-rele</t>
+          <t>https://uk.finance.yahoo.com/news/2-reasons-watch-pfe-1-173255559.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24-05-2026 08:42 UTC</t>
+          <t>23-05-2026 17:32 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LUMA trial shows BIIB122 failed to slow Parkinson’s despite target engagement</t>
+          <t>Ionis Pharmaceuticals (IONS) Valuation Check After Biogen Releases Phase 2 CELIA Alzheimer’s Study Results</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The Clinical Trial Vanguard</t>
+          <t>simplywall.st</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.clinicaltrialvanguard.com/news/luma-trial-shows-biib122-failed-to-slow-parkinsons-despite-target-engagement/</t>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nasdaq-ions/ionis-pharmaceuticals/news/ionis-pharmaceuticals-ions-valuation-check-after-biogen-rele</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24-05-2026 06:51 UTC</t>
+          <t>24-05-2026 08:42 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1013,22 +1013,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UBS Upgrades Biogen to Buy With a $225 Target: Are the Next 12 Months a Pipeline Catalyst Parade?</t>
+          <t>Wells Fargo Maintains Biogen(BIIB.US) With Buy Rating, Maintains Target Price $250</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>Moomoo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/ubs-upgrades-biogen-buy-225-142753000.html</t>
+          <t>https://www.moomoo.com/news/post/70482166/wells-fargo-maintains-biogen-biibus-with-buy-rating-maintains-target</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24-05-2026 07:22 UTC</t>
+          <t>24-05-2026 02:44 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1045,22 +1045,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biogen Pharmachem Industries Ltd is Rated Strong Sell</t>
+          <t>UBS Upgrades Biogen to Buy With a $225 Target: Are the Next 12 Months a Pipeline Catalyst Parade?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/stock-recommendation/biogen-pharmachem-industries-ltd-is-rated-strong-sell-4002822</t>
+          <t>https://www.aol.com/articles/ubs-upgrades-biogen-buy-225-142753000.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23-05-2026 14:08 UTC</t>
+          <t>24-05-2026 07:22 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1077,54 +1077,54 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biogen Q1 2026 Earnings: Strong EPS Surprise of 26.34% Boosts Investor Confidence - Revenue Estimate Trend</t>
+          <t>LUMA trial shows BIIB122 failed to slow Parkinson’s despite target engagement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newser</t>
+          <t>The Clinical Trial Vanguard</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.newser.com/expert-time/Biogen-Q1-2026-Earnings-Strong-EPS-Surprise-of-2634-Boosts-Investor-Confidence-22-4810</t>
+          <t>https://www.clinicaltrialvanguard.com/news/luma-trial-shows-biib122-failed-to-slow-parkinsons-despite-target-engagement/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23-05-2026 22:46 UTC</t>
+          <t>24-05-2026 06:51 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Biocon - 6 pharma stocks that Bernstein sees up to 40% upside potential. Do you own any?</t>
+          <t>Biogen Pharmachem Industries Ltd is Rated Strong Sell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/markets/stocks/news/6-pharma-stocks-that-bernstein-sees-up-to-40-upside-potential-do-you-own-any/biocon/slideshow/131289347.cms</t>
+          <t>https://www.marketsmojo.com/news/stock-recommendation/biogen-pharmachem-industries-ltd-is-rated-strong-sell-4002822</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24-05-2026 07:00 UTC</t>
+          <t>24-05-2026 09:28 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1136,27 +1136,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biocon Ltd. Upgraded to Buy by MarketsMOJO on Strong Technical and Financial Grounds</t>
+          <t>Biogen Q1 2026 Earnings: Strong EPS Surprise of 26.34% Boosts Investor Confidence - Revenue Estimate Trend</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Newser</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/stock-recommendation/biocon-ltd-upgraded-to-buy-by-marketsmojo-on-strong-technical-and-financial-grounds-4002277</t>
+          <t>http://www.newser.com/expert-time/Biogen-Q1-2026-Earnings-Strong-EPS-Surprise-of-2634-Boosts-Investor-Confidence-22-4810</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24-05-2026 06:32 UTC</t>
+          <t>23-05-2026 22:46 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,59 +1168,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma FY26 Revenue Tops Rs 33,600 Cr, Europe Sales Surge 30%</t>
+          <t>India’s pharma logistics faces the patent cliff head‑on</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medical Dialogues</t>
+          <t>Indian Transport &amp; Logistics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-fy26-revenue-tops-rs-33600-cr-europe-sales-surge-30-171242</t>
+          <t>https://www.itln.in/amp/supply-chain/indias-pharma-logistics-faces-the-patent-cliff-headon-1359256</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24-05-2026 06:00 UTC</t>
+          <t>24-05-2026 10:13 UTC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Limited (NSE:AUROPHARMA) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹1,466</t>
+          <t>Biocon - 6 pharma stocks that Bernstein sees up to 40% upside potential. Do you own any?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>simplywall.st</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/in/pharmaceuticals-biotech/nse-auropharma/aurobindo-pharma-shares/news/aurobindo-pharma-limited-nseauropharma-released-earnings-las-1</t>
+          <t>https://m.economictimes.com/markets/stocks/news/6-pharma-stocks-that-bernstein-sees-up-to-40-upside-potential-do-you-own-any/biocon/slideshow/131289347.cms</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24-05-2026 02:30 UTC</t>
+          <t>24-05-2026 07:00 UTC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1232,27 +1232,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma - 6 pharma stocks that Bernstein sees up to 40% upside potential. Do you own any?</t>
+          <t>Biocon Ltd. Upgraded to Buy by MarketsMOJO on Strong Technical and Financial Grounds</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/markets/stocks/news/6-pharma-stocks-that-bernstein-sees-up-to-40-upside-potential-do-you-own-any/aurobindo-pharma/slideshow/131289355.cms</t>
+          <t>https://www.marketsmojo.com/news/stock-recommendation/biocon-ltd-upgraded-to-buy-by-marketsmojo-on-strong-technical-and-financial-grounds-4002277</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24-05-2026 06:16 UTC</t>
+          <t>24-05-2026 06:32 UTC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1264,27 +1264,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biocon</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Unit Launches French Subsidiary</t>
+          <t>Bernstein bullish on India healthcare, sees $195 bn biopharma market by 2035 driven by innovation 'rainmakers'</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Big News Network.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-unit-sets-up-french-subsidiary/40981442</t>
+          <t>https://www.bignewsnetwork.com/news/279072340/bernstein-bullish-on-india-healthcare-sees-195-bn-biopharma-market-by-2035-driven-by-innovation-rainmakers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23-05-2026 23:32 UTC</t>
+          <t>24-05-2026 04:59 UTC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1301,71 +1301,71 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Q4 FY26: Margin Pressure Clouds Strong Revenue Growth</t>
+          <t>US FDA Classifies Aurobindo Pharma Subsidiary Unit as OAI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/result-analysis/aurobindo-pharma-q4-fy26-margin-pressure-clouds-strong-revenue-growth-4005346</t>
+          <t>https://scanx.trade/stock-market-news/companies/us-fda-classifies-aurobindo-pharma-subsidiary-unit-as-oai/41171059</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23-05-2026 12:41 UTC</t>
+          <t>24-05-2026 12:27 UTC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sakar Healthcare partners with Zydus Lifesciences for GCC Markets</t>
+          <t>Aurobindo Pharma FY26 Revenue Tops Rs 33,600 Cr, Europe Sales Surge 30%</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Medical Dialogues</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/sakar-healthcare-partners-with-zydus-lifesciences-for-gcc-markets/articleshow/131288861.cms</t>
+          <t>https://medicaldialogues.in/news/industry/pharma/aurobindo-pharma-fy26-revenue-tops-rs-33600-cr-europe-sales-surge-30-171242</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24-05-2026 04:56 UTC</t>
+          <t>24-05-2026 06:00 UTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Will Teva’s New TD Data on Young Adults Shift Its Neuroscience-Focused Investment Narrative (TEVA)?</t>
+          <t>Aurobindo Pharma Limited (NSE:AUROPHARMA) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹1,466</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1375,47 +1375,207 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nyse-teva/teva-pharmaceutical-industries/news/will-tevas-new-td-data-on-young-adults-shift-its-neuroscienc</t>
+          <t>https://simplywall.st/stocks/in/pharmaceuticals-biotech/nse-auropharma/aurobindo-pharma-shares/news/aurobindo-pharma-limited-nseauropharma-released-earnings-las-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>23-05-2026 17:43 UTC</t>
+          <t>24-05-2026 02:30 UTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma - 6 pharma stocks that Bernstein sees up to 40% upside potential. Do you own any?</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/markets/stocks/news/6-pharma-stocks-that-bernstein-sees-up-to-40-upside-potential-do-you-own-any/aurobindo-pharma/slideshow/131289355.cms</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24-05-2026 07:25 UTC</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Unit Launches French Subsidiary</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://scanx.trade/stock-market-news/companies/aurobindo-pharma-unit-sets-up-french-subsidiary/40981442</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23-05-2026 23:32 UTC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Zydus Biotech</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sakar Healthcare partners with Zydus Lifesciences for GCC Markets</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/industry/healthcare/biotech/healthcare/sakar-healthcare-partners-with-zydus-lifesciences-for-gcc-markets/amp_articleshow/131288861.cms</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24-05-2026 04:56 UTC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Informa Markets Puts Bangkok at the Center of Southeast Asia's Pharma Industry, Uniting 400 Exhibitors, Experts from 70 Countries at CPHI South East Asia</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>aap.com.au</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.aap.com.au/aapreleases/cision20260524ae66198/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24-05-2026 06:44 UTC</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Will Teva’s New TD Data on Young Adults Shift Its Neuroscience-Focused Investment Narrative (TEVA)?</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://simplywall.st/stocks/us/pharmaceuticals-biotech/nyse-teva/teva-pharmaceutical-industries/news/will-tevas-new-td-data-on-young-adults-shift-its-neuroscienc</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>23-05-2026 17:43 UTC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Clinical Trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Teva Q1 2026 Earnings: EPS Beats Estimates, Stock Slips on Mixed Market Sentiment - Real Trader Network</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Newser</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>http://www.newser.com/expert-time/Teva-Q1-2026-Earnings-EPS-Beats-Estimates-Stock-Slips-on-Mixed-Market-Sentiment-22-5497</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>24-05-2026 04:46 UTC</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1445,7 +1605,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-05-2026 15:10:59</t>
+          <t>24-05-2026 21:24:03</t>
         </is>
       </c>
     </row>

--- a/news_results.xlsx
+++ b/news_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,91 +661,91 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OGN Q1 2026 Earnings: EPS Misses Estimates Despite Modest Stock Gain - Share Dilution Risk</t>
+          <t>Organon Acquisition To Supports Sun Pharma’s Specialty Growth Strategy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newser</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.newser.com/expert-time/OGN-Q1-2026-Earnings-EPS-Misses-Estimates-Despite-Modest-Stock-Gain-22-7640</t>
+          <t>https://www.businesstoday.in/bt-tv/whats-hot/video/organon-acquisition-to-supports-sun-pharmas-specialty-growth-strategy-533209-2026-05-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25-05-2026 07:36 UTC</t>
+          <t>25-05-2026 11:50 UTC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Acquisition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Funding Opportunity for ALK-positive Lung Cancer Education Initiatives (US)</t>
+          <t>OGN Q1 2026 Earnings: EPS Misses Estimates Despite Modest Stock Gain - Share Dilution Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fundsforNGOs</t>
+          <t>Newser</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education-2/funding-opportunity-for-alk-positive-lung-cancer-education-initiatives-us/amp/</t>
+          <t>https://www.newser.com/expert-time/OGN-Q1-2026-Earnings-EPS-Misses-Estimates-Despite-Modest-Stock-Gain-22-7640</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25-05-2026 05:09 UTC</t>
+          <t>25-05-2026 07:36 UTC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Organon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Late-breakers to look out for at ASCO 2026</t>
+          <t>Sun Pharma: Acquisition Boosted, But Margin Pressure and Risks Loom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pharmaphorum</t>
+          <t>Whalesbook</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pharmaphorum.com/news/late-breakers-look-out-asco-2026</t>
+          <t>https://www.whalesbook.com/news/English/brokerage-reports/Sun-Pharma-Acquisition-Boosted-But-Margin-Pressure-and-Risks-Loom/6a141128b979113840c9c91c</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25-05-2026 09:18 UTC</t>
+          <t>25-05-2026 09:06 UTC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -757,406 +757,406 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Monthly Weight Loss Shot? Why Pfizer Could Topple Lilly's and Novo's GLP-1 Duopoly</t>
+          <t>Funding Opportunity for ALK-positive Lung Cancer Education Initiatives (US)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AOL.com</t>
+          <t>fundsforNGOs</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.aol.com/articles/monthly-weight-loss-shot-why-115000000.html</t>
+          <t>https://www2.fundsforngos.org/education-2/funding-opportunity-for-alk-positive-lung-cancer-education-initiatives-us/amp/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24-05-2026 18:15 UTC</t>
+          <t>25-05-2026 05:09 UTC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Biogen and Denali discontinue Parkinson’s candidate BIIB122 after Phase IIb LUMA study miss</t>
+          <t>Late-breakers to look out for at ASCO 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manufacturing Chemist</t>
+          <t>pharmaphorum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://manufacturingchemist.com/biogen-denali-discontinue-parkinson-candidate-biib122-phase-ii-study</t>
+          <t>https://pharmaphorum.com/news/late-breakers-look-out-asco-2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25-05-2026 07:05 UTC</t>
+          <t>25-05-2026 09:18 UTC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clinical Trial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BioArctic's partner Eisai presents sales simulation of potential future sales of Leqembi® at its Investor Relations Day</t>
+          <t>A Monthly Weight Loss Shot? Why Pfizer Could Topple Lilly's and Novo's GLP-1 Duopoly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>AOL.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/news/prnewswire:9faf9f90b3499:0-bioarctic-s-partner-eisai-presents-sales-simulation-of-potential-future-sales-of-leqembi-at-its-investor-relations-day/</t>
+          <t>https://www.aol.com/articles/monthly-weight-loss-shot-why-115000000.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25-05-2026 07:33 UTC</t>
+          <t>24-05-2026 18:15 UTC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Telangana facility gets OAI classification from FDA</t>
+          <t>Biogen and Denali discontinue Parkinson’s candidate BIIB122 after Phase IIb LUMA study miss</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ETPharma.com</t>
+          <t>Manufacturing Chemist</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pharma.economictimes.indiatimes.com/amp/news/pharma-industry/aurobindo-pharma-telangana-facility-gets-oai-classification-from-fda/131303647</t>
+          <t>https://manufacturingchemist.com/biogen-denali-discontinue-parkinson-candidate-biib122-phase-ii-study</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25-05-2026 06:43 UTC</t>
+          <t>25-05-2026 07:05 UTC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inspection</t>
+          <t>Clinical Trial</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma</t>
+          <t>Dr. Reddy's</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Q4 FY26: Margin Pressure Clouds Strong Revenue Growth</t>
+          <t>India issues urgent public health notice for all GLP-1 drugs including semaglutide</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Markets Mojo</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.marketsmojo.com/news/result-analysis/aurobindo-pharma-q4-fy26-margin-pressure-clouds-strong-revenue-growth-4005346</t>
+          <t>https://www.livemint.com/news/india/india-flags-safety-risks-semaglutide-weight-loss-glp-1-drugs-11779703314814.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24-05-2026 20:03 UTC</t>
+          <t>25-05-2026 12:28 UTC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Intas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>India oncology leader Zydus targets US specialty market growth</t>
+          <t>EMA recommends approval for ranibizumab biosimilar Rexatilux</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Generics and Biosimilars Initiative</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.thehindubusinessline.com/companies/we-are-the-largest-oncology-player-in-india-says-zydus-md-eyes-us-speciality-push/article71020276.ece</t>
+          <t>https://gabionline.net/biosimilars/news/ema-recommends-approval-for-ranibizumab-biosimilar-rexatilux</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25-05-2026 08:54 UTC</t>
+          <t>25-05-2026 17:01 UTC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zydus Biotech</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Signs Oncology Supply Deal with Zydus</t>
+          <t>U.S. FDA classifies Aurobindo arm’s formulation unit Official Action Indicated (OAI)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Digital Health News</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.digitalhealthnews.com/sakar-healthcare-signs-oncology-supply-deal-with-zydus</t>
+          <t>https://www.thehindu.com/business/us-fda-classifies-aurobindo-arms-formulation-unit-official-action-indicated-oai/article71020730.ece/amp/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25-05-2026 11:06 UTC</t>
+          <t>25-05-2026 16:11 UTC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Inspection</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Celltrion</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK bioscience loses R&amp;D talent as Korea bio talent war intensifies - CHOSUNBIZ</t>
+          <t>Aurobindo On US Atopic Dermatitis Drug Launch, Biologics Manufacturing For Merck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chosunbiz</t>
+          <t>Citeline News &amp; Insights</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://biz.chosun.com/en/en-science/2026/05/25/FQNUKTA545DQZO35CZKDRRJVBY/</t>
+          <t>https://insights.citeline.com/scrip/new-products/aurobindo-on-us-atopic-dermatitis-drug-launch-biologics-manufacturing-for-merck-SNKX5CKKQJE3RC26CGNVEFJQVA/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24-05-2026 21:02 UTC</t>
+          <t>25-05-2026 14:11 UTC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pipeline</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daiichi Sankyo</t>
+          <t>Aurobindo Pharma</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DATROWAY® (datopotamab deruxtecan-dlnk) approved in the US as first TROP2-directed antibody drug conjugate for 1st-line treatment of patients with metastatic triple-negative breast cancer who are not PD-1/PD-L1 inhibitor candidates</t>
+          <t>Aurobindo Pharma Q4 FY26: Margin Pressure Clouds Strong Revenue Growth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BioSpace</t>
+          <t>Markets Mojo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.biospace.com/press-releases/datroway-datopotamab-deruxtecan-dlnk-approved-in-the-us-as-first-trop2-directed-antibody-drug-conjugate-for-1st-line-treatment-of-patients-with-metastatic-triple-negative-breast-cancer-who-are-not-pd-1-pd-l1-inhibitor-candidates</t>
+          <t>https://www.marketsmojo.com/news/result-analysis/aurobindo-pharma-q4-fy26-margin-pressure-clouds-strong-revenue-growth-4005346</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25-05-2026 03:17 UTC</t>
+          <t>24-05-2026 20:03 UTC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Approval</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polpharma</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Polpharma Biologics And Tuteur Sign Landmark LATAM Biosimilar Licensing Partnership</t>
+          <t>India oncology leader Zydus targets US specialty market growth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BioPharma APAC</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://biopharmaapac.com/news/34/7972/polpharma-biologics-and-tuteur-sign-landmark-latam-biosimilar-licensing-partnership.html</t>
+          <t>https://www.thehindubusinessline.com/companies/we-are-the-largest-oncology-player-in-india-says-zydus-md-eyes-us-speciality-push/article71020276.ece</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24-05-2026 20:11 UTC</t>
+          <t>25-05-2026 08:54 UTC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fresenius Kabi</t>
+          <t>Zydus Biotech</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fresenius Celebrates US Federal Win On Ustekinumab</t>
+          <t>Sakar Healthcare Signs Oncology Supply Deal with Zydus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Citeline News &amp; Insights</t>
+          <t>Digital Health News</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/fresenius-celebrates-us-federal-win-on-ustekinumab-D2ED55VYJZBSVKENQMIJ7L2RTY/</t>
+          <t>https://www.digitalhealthnews.com/sakar-healthcare-signs-oncology-supply-deal-with-zydus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25-05-2026 11:20 UTC</t>
+          <t>25-05-2026 11:06 UTC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alvotech</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alvotech founder Robert Wessman threatens to quit Britain over ‘anti-wealth’ tax regime</t>
+          <t>DATROWAY® (datopotamab deruxtecan-dlnk) approved in the US as first TROP2-directed antibody drug conjugate for 1st-line treatment of patients with metastatic triple-negative breast cancer who are not PD-1/PD-L1 inhibitor candidates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Business Matters</t>
+          <t>BioSpace</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://bmmagazine.co.uk/in-business/alvotech-robert-wessman-uk-anti-wealth-tax-exodus/</t>
+          <t>https://www.biospace.com/press-releases/datroway-datopotamab-deruxtecan-dlnk-approved-in-the-us-as-first-trop2-directed-antibody-drug-conjugate-for-1st-line-treatment-of-patients-with-metastatic-triple-negative-breast-cancer-who-are-not-pd-1-pd-l1-inhibitor-candidates</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25-05-2026 02:34 UTC</t>
+          <t>25-05-2026 03:17 UTC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Approval</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Teva</t>
+          <t>Daiichi Sankyo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EMA accepts filing for Teva and Medincell’s long-acting schizophrenia treatment candidate</t>
+          <t>AZN, Daiichi's Enhertu Gets Positive CHMP Opinion for Solid Tumors</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indian Pharma Post</t>
+          <t>Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.indianpharmapost.com/news/ema-accepts-filing-for-teva-and-medincells-long-acting-schizophrenia-treatment-candidate-20337</t>
+          <t>https://ca.finance.yahoo.com/news/azn-daiichis-enhertu-gets-positive-153700306.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25-05-2026 05:20 UTC</t>
+          <t>25-05-2026 15:37 UTC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1168,30 +1168,190 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Polpharma</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Polpharma Biologics And Tuteur Sign Landmark LATAM Biosimilar Licensing Partnership</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BioPharma APAC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://biopharmaapac.com/news/34/7972/polpharma-biologics-and-tuteur-sign-landmark-latam-biosimilar-licensing-partnership.html</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>24-05-2026 20:11 UTC</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fresenius Kabi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fresenius Celebrates US Federal Win On Ustekinumab</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Citeline News &amp; Insights</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://insights.citeline.com/generics-bulletin/products/biosimilars/fresenius-celebrates-us-federal-win-on-ustekinumab-D2ED55VYJZBSVKENQMIJ7L2RTY/</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>25-05-2026 11:20 UTC</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MS Pharma</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CPHI South East Asia unites 400 exhibitors and experts from 70 countries in Bangkok - Vietnam Investment Review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Vietnam Investment Review - VIR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://vir.com.vn/cphi-south-east-asia-unites-400-exhibitors-and-experts-from-70-countries-in-bangkok-153350.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>25-05-2026 04:18 UTC</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Teva</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EMA accepts filing for Teva and Medincell’s long-acting schizophrenia treatment candidate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Indian Pharma Post</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.indianpharmapost.com/news/ema-accepts-filing-for-teva-and-medincells-long-acting-schizophrenia-treatment-candidate-20337</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25-05-2026 05:20 UTC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Teva Pharma posts strong Q1 2026 with 41% revenue growth in neuroscience drugs, confirms full-year outlook.</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Pluang</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://pluang.com/en/news-feed/kisah-pertumbuhan-teva-tidak-lagi-hanya-generik-tapi-juga-branded</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>25-05-2026 08:03 UTC</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Teva</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>$5.55M Teva, Granules and Heritage metformin class action settlement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Class Action Lawsuits</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://topclassactions.com/lawsuit-settlements/open-lawsuit-settlements/5-55m-teva-granules-and-heritage-metformin-class-action-settlement/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25-05-2026 17:01 UTC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
@@ -1221,7 +1381,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-05-2026 19:57:39</t>
+          <t>25-05-2026 23:06:24</t>
         </is>
       </c>
     </row>
